--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-14T04:30:12+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-15T04:35:52+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -10,19 +10,19 @@
     <sheet name="作品数据" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作品数据!$A$4:$O$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">作品数据!$A$4:$O$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="68">
   <si>
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-15T04:35:52+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-16T04:31:27+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -68,13 +68,170 @@
   </si>
   <si>
     <t>达标日期列表</t>
+  </si>
+  <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>游走神话时代，开局拜师道门天师</t>
+  </si>
+  <si>
+    <t>武侠网游，开局三个神级词条</t>
+  </si>
+  <si>
+    <t>无声1937</t>
+  </si>
+  <si>
+    <t>火影：扉间问谁断后，我当三代！</t>
+  </si>
+  <si>
+    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
+  </si>
+  <si>
+    <t>魏家孽种成首辅，全族跪求我认祖</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>穿越成国公，咋就是封建余孽了？</t>
+  </si>
+  <si>
+    <t>我一写网文的，你让我混娱乐圈？</t>
+  </si>
+  <si>
+    <t>西游：大圣闹地府！始皇长生啦</t>
+  </si>
+  <si>
+    <t>死刑当天，修仙者夺舍了我</t>
+  </si>
+  <si>
+    <t>我都永生了，会亿点技能很合理吧</t>
+  </si>
+  <si>
+    <t>人在高中，香火证道什么鬼？</t>
+  </si>
+  <si>
+    <t>综漫：表白被拒就变强？</t>
+  </si>
+  <si>
+    <t>无敌江湖后，我隐退于世</t>
+  </si>
+  <si>
+    <t>奥特：天蝎座第一道光</t>
+  </si>
+  <si>
+    <t>重生八零渔村，带仨前妻赶海暴富</t>
+  </si>
+  <si>
+    <t>无职：验牌洛琪希，牌没有问题？</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>末世：我开局拥有一艘驱逐舰</t>
+  </si>
+  <si>
+    <t>从金丹仙族开始的老祖之路！</t>
+  </si>
+  <si>
+    <t>一心求死，反倒成为千古一帝？</t>
+  </si>
+  <si>
+    <t>娱乐圈在线吃瓜，嘎嘎吃瓜嘎嘎香</t>
+  </si>
+  <si>
+    <t>洪荒：我十凶天角蚁，躺平就变强</t>
+  </si>
+  <si>
+    <t>斩神师兄太我清道德天尊社恐反差</t>
+  </si>
+  <si>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
+    <t>模拟未来：我是叛徒？请世家赴死</t>
+  </si>
+  <si>
+    <t>西游降临：开局拜师通天教主！</t>
+  </si>
+  <si>
+    <t>打卡双人骑行圈，开局拿捏假名媛</t>
+  </si>
+  <si>
+    <t>一毛一天修为，我靠直播氪穿宇宙</t>
+  </si>
+  <si>
+    <t>诡异世界，我的神通无限升级！</t>
+  </si>
+  <si>
+    <t>穿越黄毛，女主们把我当白月光了</t>
+  </si>
+  <si>
+    <t>灵气复苏？前世女帝老婆也复苏了</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>别人穿四合院，我为啥上战场</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>天渊</t>
+  </si>
+  <si>
+    <t>玄幻：多管闲事，成人间武圣</t>
+  </si>
+  <si>
+    <t>不是，啥叫世界会自主更新版本？</t>
+  </si>
+  <si>
+    <t>分手后，她们变得不对劲了！</t>
+  </si>
+  <si>
+    <t>刚上大一，哪来五个病娇未婚妻？</t>
+  </si>
+  <si>
+    <t>老师，男生也能报考魔女学院吗？</t>
+  </si>
+  <si>
+    <t>青梅是天命之女？可我既是天命！</t>
+  </si>
+  <si>
+    <t>名义，汉东刘长生，谁与争锋！</t>
+  </si>
+  <si>
+    <t>爱情公寓：开局拿下林妙妙</t>
+  </si>
+  <si>
+    <t>楼层求生：从垃圾场开始变废为宝</t>
+  </si>
+  <si>
+    <t>列车求生：我的乘员提供暴击结算</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -105,6 +262,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -126,7 +291,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -149,11 +314,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE6E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE6E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE6E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE6E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -163,6 +343,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -458,7 +650,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:O54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -561,12 +753,1716 @@
         <v>16</v>
       </c>
     </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="5">
+        <v>100</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7">
+        <v>848000</v>
+      </c>
+      <c r="G5" s="7">
+        <v>81000</v>
+      </c>
+      <c r="H5" s="7">
+        <v>3</v>
+      </c>
+      <c r="I5" s="7">
+        <v>86000</v>
+      </c>
+      <c r="J5" s="5">
+        <v>85.5</v>
+      </c>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="5"/>
+      <c r="O5" s="4"/>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="5">
+        <v>84.59999999999999</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1549000</v>
+      </c>
+      <c r="G6" s="7">
+        <v>67000</v>
+      </c>
+      <c r="H6" s="7">
+        <v>3</v>
+      </c>
+      <c r="I6" s="7">
+        <v>74000</v>
+      </c>
+      <c r="J6" s="5">
+        <v>74</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="5"/>
+      <c r="O6" s="4"/>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="5">
+        <v>100</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="7">
+        <v>246000</v>
+      </c>
+      <c r="G7" s="7">
+        <v>41000</v>
+      </c>
+      <c r="H7" s="7">
+        <v>3</v>
+      </c>
+      <c r="I7" s="7">
+        <v>39500</v>
+      </c>
+      <c r="J7" s="5">
+        <v>73.90000000000001</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="5"/>
+      <c r="O7" s="4"/>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="5">
+        <v>100</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" s="7">
+        <v>155000</v>
+      </c>
+      <c r="G8" s="7">
+        <v>32000</v>
+      </c>
+      <c r="H8" s="7">
+        <v>3</v>
+      </c>
+      <c r="I8" s="7">
+        <v>29000</v>
+      </c>
+      <c r="J8" s="5">
+        <v>71.2</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="5"/>
+      <c r="O8" s="4"/>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="5">
+        <v>89.5</v>
+      </c>
+      <c r="D9" s="4"/>
+      <c r="E9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" s="7">
+        <v>384000</v>
+      </c>
+      <c r="G9" s="7">
+        <v>40000</v>
+      </c>
+      <c r="H9" s="7">
+        <v>3</v>
+      </c>
+      <c r="I9" s="7">
+        <v>43500</v>
+      </c>
+      <c r="J9" s="5">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="5"/>
+      <c r="O9" s="4"/>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="5">
+        <v>95.90000000000001</v>
+      </c>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="7">
+        <v>344000</v>
+      </c>
+      <c r="G10" s="7">
+        <v>26000</v>
+      </c>
+      <c r="H10" s="7">
+        <v>3</v>
+      </c>
+      <c r="I10" s="7">
+        <v>26000</v>
+      </c>
+      <c r="J10" s="5">
+        <v>68.2</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="5"/>
+      <c r="O10" s="4"/>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="5">
+        <v>100</v>
+      </c>
+      <c r="D11" s="4"/>
+      <c r="E11" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" s="7">
+        <v>131000</v>
+      </c>
+      <c r="G11" s="7">
+        <v>18000</v>
+      </c>
+      <c r="H11" s="7">
+        <v>3</v>
+      </c>
+      <c r="I11" s="7">
+        <v>13000</v>
+      </c>
+      <c r="J11" s="5">
+        <v>67.2</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="5"/>
+      <c r="O11" s="4"/>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5">
+        <v>88.09999999999999</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="7">
+        <v>421000</v>
+      </c>
+      <c r="G12" s="7">
+        <v>68000</v>
+      </c>
+      <c r="H12" s="7">
+        <v>3</v>
+      </c>
+      <c r="I12" s="7">
+        <v>37500</v>
+      </c>
+      <c r="J12" s="5">
+        <v>66.8</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="5"/>
+      <c r="O12" s="4"/>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="5"/>
+      <c r="C13" s="5">
+        <v>83</v>
+      </c>
+      <c r="D13" s="4"/>
+      <c r="E13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1517000</v>
+      </c>
+      <c r="G13" s="7">
+        <v>31000</v>
+      </c>
+      <c r="H13" s="7">
+        <v>3</v>
+      </c>
+      <c r="I13" s="7">
+        <v>45500</v>
+      </c>
+      <c r="J13" s="5">
+        <v>66</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="5"/>
+      <c r="O13" s="4"/>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5">
+        <v>99</v>
+      </c>
+      <c r="D14" s="4"/>
+      <c r="E14" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" s="7">
+        <v>220000</v>
+      </c>
+      <c r="G14" s="7">
+        <v>24000</v>
+      </c>
+      <c r="H14" s="7">
+        <v>3</v>
+      </c>
+      <c r="I14" s="7">
+        <v>6000</v>
+      </c>
+      <c r="J14" s="5">
+        <v>65</v>
+      </c>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="5"/>
+      <c r="O14" s="4"/>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="5"/>
+      <c r="C15" s="5">
+        <v>83</v>
+      </c>
+      <c r="D15" s="4"/>
+      <c r="E15" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" s="7">
+        <v>894000</v>
+      </c>
+      <c r="G15" s="7">
+        <v>35000</v>
+      </c>
+      <c r="H15" s="7">
+        <v>3</v>
+      </c>
+      <c r="I15" s="7">
+        <v>40500</v>
+      </c>
+      <c r="J15" s="5">
+        <v>64.8</v>
+      </c>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="4"/>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="5">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="D16" s="4"/>
+      <c r="E16" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="7">
+        <v>129000</v>
+      </c>
+      <c r="G16" s="7">
+        <v>22000</v>
+      </c>
+      <c r="H16" s="7">
+        <v>3</v>
+      </c>
+      <c r="I16" s="7">
+        <v>20500</v>
+      </c>
+      <c r="J16" s="5">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="5"/>
+      <c r="O16" s="4"/>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="5"/>
+      <c r="C17" s="5">
+        <v>86.8</v>
+      </c>
+      <c r="D17" s="4"/>
+      <c r="E17" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" s="7">
+        <v>275000</v>
+      </c>
+      <c r="G17" s="7">
+        <v>35000</v>
+      </c>
+      <c r="H17" s="7">
+        <v>3</v>
+      </c>
+      <c r="I17" s="7">
+        <v>29000</v>
+      </c>
+      <c r="J17" s="5">
+        <v>64</v>
+      </c>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="5"/>
+      <c r="O17" s="4"/>
+    </row>
+    <row r="18" spans="1:15">
+      <c r="A18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="5"/>
+      <c r="C18" s="5">
+        <v>82.8</v>
+      </c>
+      <c r="D18" s="4"/>
+      <c r="E18" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="7">
+        <v>403000</v>
+      </c>
+      <c r="G18" s="7">
+        <v>44000</v>
+      </c>
+      <c r="H18" s="7">
+        <v>3</v>
+      </c>
+      <c r="I18" s="7">
+        <v>35500</v>
+      </c>
+      <c r="J18" s="5">
+        <v>63.4</v>
+      </c>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="5"/>
+      <c r="O18" s="4"/>
+    </row>
+    <row r="19" spans="1:15">
+      <c r="A19" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="5"/>
+      <c r="C19" s="5">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F19" s="7">
+        <v>199000</v>
+      </c>
+      <c r="G19" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H19" s="7">
+        <v>3</v>
+      </c>
+      <c r="I19" s="7">
+        <v>19500</v>
+      </c>
+      <c r="J19" s="5">
+        <v>63.2</v>
+      </c>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="5"/>
+      <c r="O19" s="4"/>
+    </row>
+    <row r="20" spans="1:15">
+      <c r="A20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="5"/>
+      <c r="C20" s="5">
+        <v>92.8</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F20" s="7">
+        <v>181000</v>
+      </c>
+      <c r="G20" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H20" s="7">
+        <v>3</v>
+      </c>
+      <c r="I20" s="7">
+        <v>12500</v>
+      </c>
+      <c r="J20" s="5">
+        <v>63.2</v>
+      </c>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="5"/>
+      <c r="O20" s="4"/>
+    </row>
+    <row r="21" spans="1:15">
+      <c r="A21" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B21" s="5"/>
+      <c r="C21" s="5">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="D21" s="4"/>
+      <c r="E21" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F21" s="7">
+        <v>105000</v>
+      </c>
+      <c r="G21" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H21" s="7">
+        <v>3</v>
+      </c>
+      <c r="I21" s="7">
+        <v>10000</v>
+      </c>
+      <c r="J21" s="5">
+        <v>63</v>
+      </c>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="5"/>
+      <c r="O21" s="4"/>
+    </row>
+    <row r="22" spans="1:15">
+      <c r="A22" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B22" s="5"/>
+      <c r="C22" s="5">
+        <v>83.2</v>
+      </c>
+      <c r="D22" s="4"/>
+      <c r="E22" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F22" s="7">
+        <v>282000</v>
+      </c>
+      <c r="G22" s="7">
+        <v>20000</v>
+      </c>
+      <c r="H22" s="7">
+        <v>3</v>
+      </c>
+      <c r="I22" s="7">
+        <v>32000</v>
+      </c>
+      <c r="J22" s="5">
+        <v>62.8</v>
+      </c>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="5"/>
+      <c r="O22" s="4"/>
+    </row>
+    <row r="23" spans="1:15">
+      <c r="A23" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5">
+        <v>91.8</v>
+      </c>
+      <c r="D23" s="4"/>
+      <c r="E23" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F23" s="7">
+        <v>162000</v>
+      </c>
+      <c r="G23" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H23" s="7">
+        <v>3</v>
+      </c>
+      <c r="I23" s="7">
+        <v>12000</v>
+      </c>
+      <c r="J23" s="5">
+        <v>62.5</v>
+      </c>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
+      <c r="M23" s="7"/>
+      <c r="N23" s="5"/>
+      <c r="O23" s="4"/>
+    </row>
+    <row r="24" spans="1:15">
+      <c r="A24" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5">
+        <v>85.7</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F24" s="7">
+        <v>213000</v>
+      </c>
+      <c r="G24" s="7">
+        <v>22000</v>
+      </c>
+      <c r="H24" s="7">
+        <v>3</v>
+      </c>
+      <c r="I24" s="7">
+        <v>23500</v>
+      </c>
+      <c r="J24" s="5">
+        <v>62</v>
+      </c>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="7"/>
+      <c r="N24" s="5"/>
+      <c r="O24" s="4"/>
+    </row>
+    <row r="25" spans="1:15">
+      <c r="A25" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5">
+        <v>88.8</v>
+      </c>
+      <c r="D25" s="4"/>
+      <c r="E25" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F25" s="7">
+        <v>423000</v>
+      </c>
+      <c r="G25" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H25" s="7">
+        <v>3</v>
+      </c>
+      <c r="I25" s="7">
+        <v>16000</v>
+      </c>
+      <c r="J25" s="5">
+        <v>61.8</v>
+      </c>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
+      <c r="M25" s="7"/>
+      <c r="N25" s="5"/>
+      <c r="O25" s="4"/>
+    </row>
+    <row r="26" spans="1:15">
+      <c r="A26" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5">
+        <v>90.8</v>
+      </c>
+      <c r="D26" s="4"/>
+      <c r="E26" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F26" s="7">
+        <v>173000</v>
+      </c>
+      <c r="G26" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H26" s="7">
+        <v>3</v>
+      </c>
+      <c r="I26" s="7">
+        <v>10500</v>
+      </c>
+      <c r="J26" s="5">
+        <v>61.6</v>
+      </c>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="5"/>
+      <c r="O26" s="4"/>
+    </row>
+    <row r="27" spans="1:15">
+      <c r="A27" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="D27" s="4"/>
+      <c r="E27" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F27" s="7">
+        <v>631000</v>
+      </c>
+      <c r="G27" s="7">
+        <v>21000</v>
+      </c>
+      <c r="H27" s="7">
+        <v>3</v>
+      </c>
+      <c r="I27" s="7">
+        <v>29500</v>
+      </c>
+      <c r="J27" s="5">
+        <v>61.3</v>
+      </c>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
+      <c r="M27" s="7"/>
+      <c r="N27" s="5"/>
+      <c r="O27" s="4"/>
+    </row>
+    <row r="28" spans="1:15">
+      <c r="A28" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5">
+        <v>83.3</v>
+      </c>
+      <c r="D28" s="4"/>
+      <c r="E28" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F28" s="7">
+        <v>448000</v>
+      </c>
+      <c r="G28" s="7">
+        <v>25000</v>
+      </c>
+      <c r="H28" s="7">
+        <v>3</v>
+      </c>
+      <c r="I28" s="7">
+        <v>26000</v>
+      </c>
+      <c r="J28" s="5">
+        <v>61.3</v>
+      </c>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
+      <c r="M28" s="7"/>
+      <c r="N28" s="5"/>
+      <c r="O28" s="4"/>
+    </row>
+    <row r="29" spans="1:15">
+      <c r="A29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B29" s="5"/>
+      <c r="C29" s="5">
+        <v>77.7</v>
+      </c>
+      <c r="D29" s="4"/>
+      <c r="E29" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F29" s="7">
+        <v>430000</v>
+      </c>
+      <c r="G29" s="7">
+        <v>25000</v>
+      </c>
+      <c r="H29" s="7">
+        <v>3</v>
+      </c>
+      <c r="I29" s="7">
+        <v>37500</v>
+      </c>
+      <c r="J29" s="5">
+        <v>61.1</v>
+      </c>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="7"/>
+      <c r="N29" s="5"/>
+      <c r="O29" s="4"/>
+    </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="B30" s="5"/>
+      <c r="C30" s="5">
+        <v>90</v>
+      </c>
+      <c r="D30" s="4"/>
+      <c r="E30" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F30" s="7">
+        <v>166000</v>
+      </c>
+      <c r="G30" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H30" s="7">
+        <v>3</v>
+      </c>
+      <c r="I30" s="7">
+        <v>10500</v>
+      </c>
+      <c r="J30" s="5">
+        <v>61.1</v>
+      </c>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4"/>
+      <c r="M30" s="7"/>
+      <c r="N30" s="5"/>
+      <c r="O30" s="4"/>
+    </row>
+    <row r="31" spans="1:15">
+      <c r="A31" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B31" s="5"/>
+      <c r="C31" s="5">
+        <v>88.5</v>
+      </c>
+      <c r="D31" s="4"/>
+      <c r="E31" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F31" s="7">
+        <v>184000</v>
+      </c>
+      <c r="G31" s="7">
+        <v>11000</v>
+      </c>
+      <c r="H31" s="7">
+        <v>3</v>
+      </c>
+      <c r="I31" s="7">
+        <v>11500</v>
+      </c>
+      <c r="J31" s="5">
+        <v>60.6</v>
+      </c>
+      <c r="K31" s="4"/>
+      <c r="L31" s="4"/>
+      <c r="M31" s="7"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="4"/>
+    </row>
+    <row r="32" spans="1:15">
+      <c r="A32" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="5"/>
+      <c r="C32" s="5">
+        <v>86.3</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F32" s="7">
+        <v>189000</v>
+      </c>
+      <c r="G32" s="7">
+        <v>17000</v>
+      </c>
+      <c r="H32" s="7">
+        <v>3</v>
+      </c>
+      <c r="I32" s="7">
+        <v>16000</v>
+      </c>
+      <c r="J32" s="5">
+        <v>60.5</v>
+      </c>
+      <c r="K32" s="4"/>
+      <c r="L32" s="4"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="5"/>
+      <c r="O32" s="4"/>
+    </row>
+    <row r="33" spans="1:15">
+      <c r="A33" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" s="5"/>
+      <c r="C33" s="5">
+        <v>90</v>
+      </c>
+      <c r="D33" s="4"/>
+      <c r="E33" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="7">
+        <v>147000</v>
+      </c>
+      <c r="G33" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H33" s="7">
+        <v>3</v>
+      </c>
+      <c r="I33" s="7">
+        <v>7000</v>
+      </c>
+      <c r="J33" s="5">
+        <v>60.3</v>
+      </c>
+      <c r="K33" s="4"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="5"/>
+      <c r="O33" s="4"/>
+    </row>
+    <row r="34" spans="1:15">
+      <c r="A34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="5"/>
+      <c r="C34" s="5">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F34" s="7">
+        <v>103000</v>
+      </c>
+      <c r="G34" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H34" s="7">
+        <v>3</v>
+      </c>
+      <c r="I34" s="7">
+        <v>8000</v>
+      </c>
+      <c r="J34" s="5">
+        <v>60.3</v>
+      </c>
+      <c r="K34" s="4"/>
+      <c r="L34" s="4"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="5"/>
+      <c r="O34" s="4"/>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B35" s="5"/>
+      <c r="C35" s="5">
+        <v>80.2</v>
+      </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F35" s="7">
+        <v>903000</v>
+      </c>
+      <c r="G35" s="7">
+        <v>26000</v>
+      </c>
+      <c r="H35" s="7">
+        <v>3</v>
+      </c>
+      <c r="I35" s="7">
+        <v>28500</v>
+      </c>
+      <c r="J35" s="5">
+        <v>60.2</v>
+      </c>
+      <c r="K35" s="4"/>
+      <c r="L35" s="4"/>
+      <c r="M35" s="7"/>
+      <c r="N35" s="5"/>
+      <c r="O35" s="4"/>
+    </row>
+    <row r="36" spans="1:15">
+      <c r="A36" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="5"/>
+      <c r="C36" s="5">
+        <v>87.5</v>
+      </c>
+      <c r="D36" s="4"/>
+      <c r="E36" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F36" s="7">
+        <v>454000</v>
+      </c>
+      <c r="G36" s="7">
+        <v>0</v>
+      </c>
+      <c r="H36" s="7">
+        <v>3</v>
+      </c>
+      <c r="I36" s="7">
+        <v>11500</v>
+      </c>
+      <c r="J36" s="5">
+        <v>60</v>
+      </c>
+      <c r="K36" s="4"/>
+      <c r="L36" s="4"/>
+      <c r="M36" s="7"/>
+      <c r="N36" s="5"/>
+      <c r="O36" s="4"/>
+    </row>
+    <row r="37" spans="1:15">
+      <c r="A37" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5">
+        <v>88.5</v>
+      </c>
+      <c r="D37" s="4"/>
+      <c r="E37" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F37" s="7">
+        <v>118000</v>
+      </c>
+      <c r="G37" s="7">
+        <v>8000</v>
+      </c>
+      <c r="H37" s="7">
+        <v>3</v>
+      </c>
+      <c r="I37" s="7">
+        <v>7500</v>
+      </c>
+      <c r="J37" s="5">
+        <v>59.6</v>
+      </c>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="7"/>
+      <c r="N37" s="5"/>
+      <c r="O37" s="4"/>
+    </row>
+    <row r="38" spans="1:15">
+      <c r="A38" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5">
+        <v>86.7</v>
+      </c>
+      <c r="D38" s="4"/>
+      <c r="E38" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F38" s="7">
+        <v>122000</v>
+      </c>
+      <c r="G38" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H38" s="7">
+        <v>3</v>
+      </c>
+      <c r="I38" s="7">
+        <v>11000</v>
+      </c>
+      <c r="J38" s="5">
+        <v>59.4</v>
+      </c>
+      <c r="K38" s="4"/>
+      <c r="L38" s="4"/>
+      <c r="M38" s="7"/>
+      <c r="N38" s="5"/>
+      <c r="O38" s="4"/>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="A39" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5">
+        <v>87.2</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F39" s="7">
+        <v>130000</v>
+      </c>
+      <c r="G39" s="7">
+        <v>10000</v>
+      </c>
+      <c r="H39" s="7">
+        <v>3</v>
+      </c>
+      <c r="I39" s="7">
+        <v>9500</v>
+      </c>
+      <c r="J39" s="5">
+        <v>59.3</v>
+      </c>
+      <c r="K39" s="4"/>
+      <c r="L39" s="4"/>
+      <c r="M39" s="7"/>
+      <c r="N39" s="5"/>
+      <c r="O39" s="4"/>
+    </row>
+    <row r="40" spans="1:15">
+      <c r="A40" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5">
+        <v>81.2</v>
+      </c>
+      <c r="D40" s="4"/>
+      <c r="E40" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F40" s="7">
+        <v>244000</v>
+      </c>
+      <c r="G40" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H40" s="7">
+        <v>3</v>
+      </c>
+      <c r="I40" s="7">
+        <v>22000</v>
+      </c>
+      <c r="J40" s="5">
+        <v>59.2</v>
+      </c>
+      <c r="K40" s="4"/>
+      <c r="L40" s="4"/>
+      <c r="M40" s="7"/>
+      <c r="N40" s="5"/>
+      <c r="O40" s="4"/>
+    </row>
+    <row r="41" spans="1:15">
+      <c r="A41" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="5"/>
+      <c r="C41" s="5">
+        <v>87.90000000000001</v>
+      </c>
+      <c r="D41" s="4"/>
+      <c r="E41" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F41" s="7">
+        <v>314000</v>
+      </c>
+      <c r="G41" s="7">
+        <v>4000</v>
+      </c>
+      <c r="H41" s="7">
+        <v>3</v>
+      </c>
+      <c r="I41" s="7">
+        <v>7000</v>
+      </c>
+      <c r="J41" s="5">
+        <v>59.1</v>
+      </c>
+      <c r="K41" s="4"/>
+      <c r="L41" s="4"/>
+      <c r="M41" s="7"/>
+      <c r="N41" s="5"/>
+      <c r="O41" s="4"/>
+    </row>
+    <row r="42" spans="1:15">
+      <c r="A42" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B42" s="5"/>
+      <c r="C42" s="5">
+        <v>81.5</v>
+      </c>
+      <c r="D42" s="4"/>
+      <c r="E42" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F42" s="7">
+        <v>375000</v>
+      </c>
+      <c r="G42" s="7">
+        <v>16000</v>
+      </c>
+      <c r="H42" s="7">
+        <v>3</v>
+      </c>
+      <c r="I42" s="7">
+        <v>20500</v>
+      </c>
+      <c r="J42" s="5">
+        <v>59</v>
+      </c>
+      <c r="K42" s="4"/>
+      <c r="L42" s="4"/>
+      <c r="M42" s="7"/>
+      <c r="N42" s="5"/>
+      <c r="O42" s="4"/>
+    </row>
+    <row r="43" spans="1:15">
+      <c r="A43" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="B43" s="5"/>
+      <c r="C43" s="5">
+        <v>81.59999999999999</v>
+      </c>
+      <c r="D43" s="4"/>
+      <c r="E43" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F43" s="7">
+        <v>280000</v>
+      </c>
+      <c r="G43" s="7">
+        <v>20000</v>
+      </c>
+      <c r="H43" s="7">
+        <v>3</v>
+      </c>
+      <c r="I43" s="7">
+        <v>20500</v>
+      </c>
+      <c r="J43" s="5">
+        <v>59</v>
+      </c>
+      <c r="K43" s="4"/>
+      <c r="L43" s="4"/>
+      <c r="M43" s="7"/>
+      <c r="N43" s="5"/>
+      <c r="O43" s="4"/>
+    </row>
+    <row r="44" spans="1:15">
+      <c r="A44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="5"/>
+      <c r="C44" s="5">
+        <v>82</v>
+      </c>
+      <c r="D44" s="4"/>
+      <c r="E44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F44" s="7">
+        <v>1232000</v>
+      </c>
+      <c r="G44" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H44" s="7">
+        <v>3</v>
+      </c>
+      <c r="I44" s="7">
+        <v>19000</v>
+      </c>
+      <c r="J44" s="5">
+        <v>58.9</v>
+      </c>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
+      <c r="M44" s="7"/>
+      <c r="N44" s="5"/>
+      <c r="O44" s="4"/>
+    </row>
+    <row r="45" spans="1:15">
+      <c r="A45" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B45" s="5"/>
+      <c r="C45" s="5">
+        <v>75.2</v>
+      </c>
+      <c r="D45" s="4"/>
+      <c r="E45" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F45" s="7">
+        <v>336000</v>
+      </c>
+      <c r="G45" s="7">
+        <v>33000</v>
+      </c>
+      <c r="H45" s="7">
+        <v>3</v>
+      </c>
+      <c r="I45" s="7">
+        <v>34000</v>
+      </c>
+      <c r="J45" s="5">
+        <v>58.9</v>
+      </c>
+      <c r="K45" s="4"/>
+      <c r="L45" s="4"/>
+      <c r="M45" s="7"/>
+      <c r="N45" s="5"/>
+      <c r="O45" s="4"/>
+    </row>
+    <row r="46" spans="1:15">
+      <c r="A46" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B46" s="5"/>
+      <c r="C46" s="5">
+        <v>86.09999999999999</v>
+      </c>
+      <c r="D46" s="4"/>
+      <c r="E46" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F46" s="7">
+        <v>135000</v>
+      </c>
+      <c r="G46" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H46" s="7">
+        <v>3</v>
+      </c>
+      <c r="I46" s="7">
+        <v>8500</v>
+      </c>
+      <c r="J46" s="5">
+        <v>58.5</v>
+      </c>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4"/>
+      <c r="M46" s="7"/>
+      <c r="N46" s="5"/>
+      <c r="O46" s="4"/>
+    </row>
+    <row r="47" spans="1:15">
+      <c r="A47" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="B47" s="5"/>
+      <c r="C47" s="5">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F47" s="7">
+        <v>127000</v>
+      </c>
+      <c r="G47" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H47" s="7">
+        <v>3</v>
+      </c>
+      <c r="I47" s="7">
+        <v>15000</v>
+      </c>
+      <c r="J47" s="5">
+        <v>58.5</v>
+      </c>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="7"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="4"/>
+    </row>
+    <row r="48" spans="1:15">
+      <c r="A48" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5">
+        <v>84.3</v>
+      </c>
+      <c r="D48" s="4"/>
+      <c r="E48" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F48" s="7">
+        <v>120000</v>
+      </c>
+      <c r="G48" s="7">
+        <v>9000</v>
+      </c>
+      <c r="H48" s="7">
+        <v>3</v>
+      </c>
+      <c r="I48" s="7">
+        <v>12500</v>
+      </c>
+      <c r="J48" s="5">
+        <v>58.5</v>
+      </c>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="7"/>
+      <c r="N48" s="5"/>
+      <c r="O48" s="4"/>
+    </row>
+    <row r="49" spans="1:15">
+      <c r="A49" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="B49" s="5"/>
+      <c r="C49" s="5">
+        <v>86.90000000000001</v>
+      </c>
+      <c r="D49" s="4"/>
+      <c r="E49" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F49" s="7">
+        <v>154000</v>
+      </c>
+      <c r="G49" s="7">
+        <v>4000</v>
+      </c>
+      <c r="H49" s="7">
+        <v>3</v>
+      </c>
+      <c r="I49" s="7">
+        <v>6500</v>
+      </c>
+      <c r="J49" s="5">
+        <v>58.4</v>
+      </c>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="7"/>
+      <c r="N49" s="5"/>
+      <c r="O49" s="4"/>
+    </row>
+    <row r="50" spans="1:15">
+      <c r="A50" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B50" s="5">
+        <v>9</v>
+      </c>
+      <c r="C50" s="5">
+        <v>86.3</v>
+      </c>
+      <c r="D50" s="4"/>
+      <c r="E50" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F50" s="7">
+        <v>195000</v>
+      </c>
+      <c r="G50" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H50" s="7">
+        <v>3</v>
+      </c>
+      <c r="I50" s="7">
+        <v>6500</v>
+      </c>
+      <c r="J50" s="5">
+        <v>58.1</v>
+      </c>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="7"/>
+      <c r="N50" s="5"/>
+      <c r="O50" s="4"/>
+    </row>
+    <row r="51" spans="1:15">
+      <c r="A51" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="B51" s="5"/>
+      <c r="C51" s="5">
+        <v>80.90000000000001</v>
+      </c>
+      <c r="D51" s="4"/>
+      <c r="E51" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F51" s="7">
+        <v>472000</v>
+      </c>
+      <c r="G51" s="7">
+        <v>19000</v>
+      </c>
+      <c r="H51" s="7">
+        <v>3</v>
+      </c>
+      <c r="I51" s="7">
+        <v>17500</v>
+      </c>
+      <c r="J51" s="5">
+        <v>57.9</v>
+      </c>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="7"/>
+      <c r="N51" s="5"/>
+      <c r="O51" s="4"/>
+    </row>
+    <row r="52" spans="1:15">
+      <c r="A52" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="5"/>
+      <c r="C52" s="5">
+        <v>85.8</v>
+      </c>
+      <c r="D52" s="4"/>
+      <c r="E52" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F52" s="7">
+        <v>270000</v>
+      </c>
+      <c r="G52" s="7">
+        <v>3000</v>
+      </c>
+      <c r="H52" s="7">
+        <v>3</v>
+      </c>
+      <c r="I52" s="7">
+        <v>6500</v>
+      </c>
+      <c r="J52" s="5">
+        <v>57.8</v>
+      </c>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="7"/>
+      <c r="N52" s="5"/>
+      <c r="O52" s="4"/>
+    </row>
+    <row r="53" spans="1:15">
+      <c r="A53" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5">
+        <v>87.09999999999999</v>
+      </c>
+      <c r="D53" s="4"/>
+      <c r="E53" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F53" s="7">
+        <v>131000</v>
+      </c>
+      <c r="G53" s="7">
+        <v>6000</v>
+      </c>
+      <c r="H53" s="7">
+        <v>3</v>
+      </c>
+      <c r="I53" s="7">
+        <v>3500</v>
+      </c>
+      <c r="J53" s="5">
+        <v>57.8</v>
+      </c>
+      <c r="K53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="7"/>
+      <c r="N53" s="5"/>
+      <c r="O53" s="4"/>
+    </row>
+    <row r="54" spans="1:15">
+      <c r="A54" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="5"/>
+      <c r="C54" s="5">
+        <v>86.3</v>
+      </c>
+      <c r="D54" s="4"/>
+      <c r="E54" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F54" s="7">
+        <v>111000</v>
+      </c>
+      <c r="G54" s="7">
+        <v>8000</v>
+      </c>
+      <c r="H54" s="7">
+        <v>3</v>
+      </c>
+      <c r="I54" s="7">
+        <v>5000</v>
+      </c>
+      <c r="J54" s="5">
+        <v>57.7</v>
+      </c>
+      <c r="K54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="7"/>
+      <c r="N54" s="5"/>
+      <c r="O54" s="4"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:O5"/>
+  <autoFilter ref="A4:O54"/>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E5" r:id="rId1"/>
+    <hyperlink ref="E6" r:id="rId2"/>
+    <hyperlink ref="E7" r:id="rId3"/>
+    <hyperlink ref="E8" r:id="rId4"/>
+    <hyperlink ref="E9" r:id="rId5"/>
+    <hyperlink ref="E10" r:id="rId6"/>
+    <hyperlink ref="E11" r:id="rId7"/>
+    <hyperlink ref="E12" r:id="rId8"/>
+    <hyperlink ref="E13" r:id="rId9"/>
+    <hyperlink ref="E14" r:id="rId10"/>
+    <hyperlink ref="E15" r:id="rId11"/>
+    <hyperlink ref="E16" r:id="rId12"/>
+    <hyperlink ref="E17" r:id="rId13"/>
+    <hyperlink ref="E18" r:id="rId14"/>
+    <hyperlink ref="E19" r:id="rId15"/>
+    <hyperlink ref="E20" r:id="rId16"/>
+    <hyperlink ref="E21" r:id="rId17"/>
+    <hyperlink ref="E22" r:id="rId18"/>
+    <hyperlink ref="E23" r:id="rId19"/>
+    <hyperlink ref="E24" r:id="rId20"/>
+    <hyperlink ref="E25" r:id="rId21"/>
+    <hyperlink ref="E26" r:id="rId22"/>
+    <hyperlink ref="E27" r:id="rId23"/>
+    <hyperlink ref="E28" r:id="rId24"/>
+    <hyperlink ref="E29" r:id="rId25"/>
+    <hyperlink ref="E30" r:id="rId26"/>
+    <hyperlink ref="E31" r:id="rId27"/>
+    <hyperlink ref="E32" r:id="rId28"/>
+    <hyperlink ref="E33" r:id="rId29"/>
+    <hyperlink ref="E34" r:id="rId30"/>
+    <hyperlink ref="E35" r:id="rId31"/>
+    <hyperlink ref="E36" r:id="rId32"/>
+    <hyperlink ref="E37" r:id="rId33"/>
+    <hyperlink ref="E38" r:id="rId34"/>
+    <hyperlink ref="E39" r:id="rId35"/>
+    <hyperlink ref="E40" r:id="rId36"/>
+    <hyperlink ref="E41" r:id="rId37"/>
+    <hyperlink ref="E42" r:id="rId38"/>
+    <hyperlink ref="E43" r:id="rId39"/>
+    <hyperlink ref="E44" r:id="rId40"/>
+    <hyperlink ref="E45" r:id="rId41"/>
+    <hyperlink ref="E46" r:id="rId42"/>
+    <hyperlink ref="E47" r:id="rId43"/>
+    <hyperlink ref="E48" r:id="rId44"/>
+    <hyperlink ref="E49" r:id="rId45"/>
+    <hyperlink ref="E50" r:id="rId46"/>
+    <hyperlink ref="E51" r:id="rId47"/>
+    <hyperlink ref="E52" r:id="rId48"/>
+    <hyperlink ref="E53" r:id="rId49"/>
+    <hyperlink ref="E54" r:id="rId50"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-16T04:31:27+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-17T04:37:06+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>游走神话时代，开局拜师道门天师</t>
+  </si>
+  <si>
+    <t>武侠网游，开局三个神级词条</t>
+  </si>
+  <si>
     <t>规则怪谈：无所谓，系统会出手</t>
   </si>
   <si>
-    <t>游走神话时代，开局拜师道门天师</t>
-  </si>
-  <si>
-    <t>武侠网游，开局三个神级词条</t>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
+    <t>西游：大圣闹地府！始皇长生啦</t>
   </si>
   <si>
     <t>无声1937</t>
   </si>
   <si>
+    <t>名义：刚提名省服，你让我退休？</t>
+  </si>
+  <si>
+    <t>我一写网文的，你让我混娱乐圈？</t>
+  </si>
+  <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
+    <t>死刑当天，修仙者夺舍了我</t>
+  </si>
+  <si>
     <t>火影：扉间问谁断后，我当三代！</t>
   </si>
   <si>
+    <t>我都永生了，会亿点技能很合理吧</t>
+  </si>
+  <si>
+    <t>灵气复苏？前世女帝老婆也复苏了</t>
+  </si>
+  <si>
+    <t>一毛一天修为，我靠直播氪穿宇宙</t>
+  </si>
+  <si>
+    <t>宿舍求生：糯米可镇不住我们太久</t>
+  </si>
+  <si>
+    <t>魏家孽种成首辅，全族跪求我认祖</t>
+  </si>
+  <si>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
+    <t>命格通神，我的悟性可以无限叠加</t>
+  </si>
+  <si>
+    <t>重生八零渔村，带仨前妻赶海暴富</t>
+  </si>
+  <si>
+    <t>无职：验牌洛琪希，牌没有问题？</t>
+  </si>
+  <si>
+    <t>开局魅骨词条，我成了宇智波团宠</t>
+  </si>
+  <si>
+    <t>穿越70，我被身边的人宠坏了</t>
+  </si>
+  <si>
+    <t>综漫：表白被拒就变强？</t>
+  </si>
+  <si>
+    <t>洪荒：我十凶天角蚁，躺平就变强</t>
+  </si>
+  <si>
+    <t>打卡双人骑行圈，开局拿捏假名媛</t>
+  </si>
+  <si>
+    <t>奥特：天蝎座第一道光</t>
+  </si>
+  <si>
+    <t>从金丹仙族开始的老祖之路！</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>大唐：不是诗仙，但是真剑仙！</t>
+  </si>
+  <si>
+    <t>末世：我开局拥有一艘驱逐舰</t>
+  </si>
+  <si>
+    <t>穿越黄毛，女主们把我当白月光了</t>
+  </si>
+  <si>
+    <t>模拟未来：我是叛徒？请世家赴死</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>惊悚世界，我的小弟有亿点多</t>
+  </si>
+  <si>
+    <t>祖上十八鬼帝，你让我恐怖求生？</t>
+  </si>
+  <si>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>一心求死，反倒成为千古一帝？</t>
+  </si>
+  <si>
+    <t>斩神师兄太我清道德天尊社恐反差</t>
+  </si>
+  <si>
     <t>刚穿越洪荒，就要被弑神枪钉死了</t>
   </si>
   <si>
-    <t>魏家孽种成首辅，全族跪求我认祖</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>穿越成国公，咋就是封建余孽了？</t>
-  </si>
-  <si>
-    <t>我一写网文的，你让我混娱乐圈？</t>
-  </si>
-  <si>
-    <t>西游：大圣闹地府！始皇长生啦</t>
-  </si>
-  <si>
-    <t>死刑当天，修仙者夺舍了我</t>
-  </si>
-  <si>
-    <t>我都永生了，会亿点技能很合理吧</t>
-  </si>
-  <si>
-    <t>人在高中，香火证道什么鬼？</t>
-  </si>
-  <si>
-    <t>综漫：表白被拒就变强？</t>
-  </si>
-  <si>
     <t>无敌江湖后，我隐退于世</t>
   </si>
   <si>
-    <t>奥特：天蝎座第一道光</t>
-  </si>
-  <si>
-    <t>重生八零渔村，带仨前妻赶海暴富</t>
-  </si>
-  <si>
-    <t>无职：验牌洛琪希，牌没有问题？</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>末世：我开局拥有一艘驱逐舰</t>
-  </si>
-  <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>一心求死，反倒成为千古一帝？</t>
-  </si>
-  <si>
-    <t>娱乐圈在线吃瓜，嘎嘎吃瓜嘎嘎香</t>
-  </si>
-  <si>
-    <t>洪荒：我十凶天角蚁，躺平就变强</t>
-  </si>
-  <si>
-    <t>斩神师兄太我清道德天尊社恐反差</t>
-  </si>
-  <si>
-    <t>从零开始，打造华夏首支特种部队</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
-  </si>
-  <si>
-    <t>模拟未来：我是叛徒？请世家赴死</t>
-  </si>
-  <si>
-    <t>西游降临：开局拜师通天教主！</t>
-  </si>
-  <si>
-    <t>打卡双人骑行圈，开局拿捏假名媛</t>
-  </si>
-  <si>
-    <t>一毛一天修为，我靠直播氪穿宇宙</t>
-  </si>
-  <si>
-    <t>诡异世界，我的神通无限升级！</t>
-  </si>
-  <si>
-    <t>穿越黄毛，女主们把我当白月光了</t>
-  </si>
-  <si>
-    <t>灵气复苏？前世女帝老婆也复苏了</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
+    <t>玄幻：多管闲事，成人间武圣</t>
+  </si>
+  <si>
+    <t>青梅是天命之女？可我既是天命！</t>
+  </si>
+  <si>
+    <t>给员工发超跑，你当死士养呢？</t>
+  </si>
+  <si>
+    <t>重生三岁被捡，成了杨老板亲弟</t>
+  </si>
+  <si>
+    <t>分手后，她们变得不对劲了！</t>
+  </si>
+  <si>
+    <t>全民英雄协会：开局招募一拳光头</t>
+  </si>
+  <si>
+    <t>刚进宗门，就睡出个绝美师尊老婆</t>
+  </si>
+  <si>
+    <t>爱情公寓：开局拿下林妙妙</t>
   </si>
   <si>
     <t>别人穿四合院，我为啥上战场</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>天渊</t>
-  </si>
-  <si>
-    <t>玄幻：多管闲事，成人间武圣</t>
-  </si>
-  <si>
-    <t>不是，啥叫世界会自主更新版本？</t>
-  </si>
-  <si>
-    <t>分手后，她们变得不对劲了！</t>
-  </si>
-  <si>
-    <t>刚上大一，哪来五个病娇未婚妻？</t>
-  </si>
-  <si>
-    <t>老师，男生也能报考魔女学院吗？</t>
-  </si>
-  <si>
-    <t>青梅是天命之女？可我既是天命！</t>
-  </si>
-  <si>
-    <t>名义，汉东刘长生，谁与争锋！</t>
-  </si>
-  <si>
-    <t>爱情公寓：开局拿下林妙妙</t>
-  </si>
-  <si>
-    <t>楼层求生：从垃圾场开始变废为宝</t>
-  </si>
-  <si>
-    <t>列车求生：我的乘员提供暴击结算</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>848000</v>
+        <v>894000</v>
       </c>
       <c r="G5" s="7">
-        <v>81000</v>
+        <v>46000</v>
       </c>
       <c r="H5" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I5" s="7">
-        <v>86000</v>
+        <v>72667</v>
       </c>
       <c r="J5" s="5">
-        <v>85.5</v>
+        <v>82.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1549000</v>
+        <v>295000</v>
       </c>
       <c r="G6" s="7">
-        <v>67000</v>
+        <v>49000</v>
       </c>
       <c r="H6" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I6" s="7">
-        <v>74000</v>
+        <v>42667</v>
       </c>
       <c r="J6" s="5">
-        <v>74</v>
+        <v>77.7</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -832,19 +832,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>246000</v>
+        <v>197000</v>
       </c>
       <c r="G7" s="7">
-        <v>41000</v>
+        <v>42000</v>
       </c>
       <c r="H7" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I7" s="7">
-        <v>39500</v>
+        <v>33333</v>
       </c>
       <c r="J7" s="5">
-        <v>73.90000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>83.2</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>155000</v>
+        <v>1596000</v>
       </c>
       <c r="G8" s="7">
-        <v>32000</v>
+        <v>47000</v>
       </c>
       <c r="H8" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="7">
-        <v>29000</v>
+        <v>65000</v>
       </c>
       <c r="J8" s="5">
-        <v>71.2</v>
+        <v>74</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>89.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>384000</v>
+        <v>1580000</v>
       </c>
       <c r="G9" s="7">
-        <v>40000</v>
+        <v>63000</v>
       </c>
       <c r="H9" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="7">
-        <v>43500</v>
+        <v>51333</v>
       </c>
       <c r="J9" s="5">
-        <v>69.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -931,19 +931,19 @@
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>344000</v>
+        <v>149000</v>
       </c>
       <c r="G10" s="7">
-        <v>26000</v>
+        <v>20000</v>
       </c>
       <c r="H10" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="7">
-        <v>26000</v>
+        <v>20333</v>
       </c>
       <c r="J10" s="5">
-        <v>68.2</v>
+        <v>69.8</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>100</v>
+        <v>86.2</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>131000</v>
+        <v>415000</v>
       </c>
       <c r="G11" s="7">
-        <v>18000</v>
+        <v>31000</v>
       </c>
       <c r="H11" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="7">
-        <v>13000</v>
+        <v>39333</v>
       </c>
       <c r="J11" s="5">
-        <v>67.2</v>
+        <v>69.2</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>88.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>421000</v>
+        <v>223000</v>
       </c>
       <c r="G12" s="7">
-        <v>68000</v>
+        <v>24000</v>
       </c>
       <c r="H12" s="7">
         <v>3</v>
       </c>
       <c r="I12" s="7">
-        <v>37500</v>
+        <v>24500</v>
       </c>
       <c r="J12" s="5">
-        <v>66.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>83</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>1517000</v>
+        <v>933000</v>
       </c>
       <c r="G13" s="7">
-        <v>31000</v>
+        <v>39000</v>
       </c>
       <c r="H13" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I13" s="7">
-        <v>45500</v>
+        <v>40000</v>
       </c>
       <c r="J13" s="5">
-        <v>66</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>99</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>220000</v>
+        <v>585000</v>
       </c>
       <c r="G14" s="7">
-        <v>24000</v>
+        <v>36000</v>
       </c>
       <c r="H14" s="7">
         <v>3</v>
       </c>
       <c r="I14" s="7">
-        <v>6000</v>
+        <v>48500</v>
       </c>
       <c r="J14" s="5">
-        <v>65</v>
+        <v>66.7</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>83</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>894000</v>
+        <v>309000</v>
       </c>
       <c r="G15" s="7">
-        <v>35000</v>
+        <v>34000</v>
       </c>
       <c r="H15" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I15" s="7">
-        <v>40500</v>
+        <v>30667</v>
       </c>
       <c r="J15" s="5">
-        <v>64.8</v>
+        <v>66.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>91.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>129000</v>
+        <v>352000</v>
       </c>
       <c r="G16" s="7">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="H16" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7">
-        <v>20500</v>
+        <v>20000</v>
       </c>
       <c r="J16" s="5">
-        <v>64.40000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>86.8</v>
+        <v>81.2</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>275000</v>
+        <v>442000</v>
       </c>
       <c r="G17" s="7">
-        <v>35000</v>
+        <v>39000</v>
       </c>
       <c r="H17" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I17" s="7">
-        <v>29000</v>
+        <v>36667</v>
       </c>
       <c r="J17" s="5">
-        <v>64</v>
+        <v>65.8</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>82.8</v>
+        <v>86.2</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>403000</v>
+        <v>274000</v>
       </c>
       <c r="G18" s="7">
-        <v>44000</v>
+        <v>30000</v>
       </c>
       <c r="H18" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I18" s="7">
-        <v>35500</v>
+        <v>24667</v>
       </c>
       <c r="J18" s="5">
-        <v>63.4</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>89.59999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>199000</v>
+        <v>131000</v>
       </c>
       <c r="G19" s="7">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="H19" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
-        <v>19500</v>
+        <v>9333</v>
       </c>
       <c r="J19" s="5">
-        <v>63.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>92.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>181000</v>
+        <v>106000</v>
       </c>
       <c r="G20" s="7">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="H20" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="7">
-        <v>12500</v>
+        <v>11333</v>
       </c>
       <c r="J20" s="5">
-        <v>63.2</v>
+        <v>65.2</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>93.59999999999999</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>105000</v>
+        <v>446000</v>
       </c>
       <c r="G21" s="7">
-        <v>9000</v>
+        <v>25000</v>
       </c>
       <c r="H21" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I21" s="7">
-        <v>10000</v>
+        <v>33333</v>
       </c>
       <c r="J21" s="5">
-        <v>63</v>
+        <v>64.8</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>83.2</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>282000</v>
+        <v>156000</v>
       </c>
       <c r="G22" s="7">
-        <v>20000</v>
+        <v>9000</v>
       </c>
       <c r="H22" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I22" s="7">
-        <v>32000</v>
+        <v>7667</v>
       </c>
       <c r="J22" s="5">
-        <v>62.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>91.8</v>
+        <v>90.3</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>162000</v>
+        <v>100000</v>
       </c>
       <c r="G23" s="7">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="7">
-        <v>12000</v>
+        <v>11333</v>
       </c>
       <c r="J23" s="5">
-        <v>62.5</v>
+        <v>64.5</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>85.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>213000</v>
+        <v>171000</v>
       </c>
       <c r="G24" s="7">
-        <v>22000</v>
+        <v>9000</v>
       </c>
       <c r="H24" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="7">
-        <v>23500</v>
+        <v>11000</v>
       </c>
       <c r="J24" s="5">
-        <v>62</v>
+        <v>64.3</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>88.8</v>
+        <v>84.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>423000</v>
+        <v>234000</v>
       </c>
       <c r="G25" s="7">
-        <v>3000</v>
+        <v>21000</v>
       </c>
       <c r="H25" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I25" s="7">
-        <v>16000</v>
+        <v>22667</v>
       </c>
       <c r="J25" s="5">
-        <v>61.8</v>
+        <v>64</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>90.8</v>
+        <v>93.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>173000</v>
+        <v>181000</v>
       </c>
       <c r="G26" s="7">
-        <v>9000</v>
+        <v>16000</v>
       </c>
       <c r="H26" s="7">
         <v>3</v>
       </c>
       <c r="I26" s="7">
-        <v>10500</v>
+        <v>14000</v>
       </c>
       <c r="J26" s="5">
-        <v>61.6</v>
+        <v>63.9</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>81.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>631000</v>
+        <v>230000</v>
       </c>
       <c r="G27" s="7">
-        <v>21000</v>
+        <v>27000</v>
       </c>
       <c r="H27" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I27" s="7">
-        <v>29500</v>
+        <v>25000</v>
       </c>
       <c r="J27" s="5">
-        <v>61.3</v>
+        <v>63.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>83.3</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>448000</v>
+        <v>191000</v>
       </c>
       <c r="G28" s="7">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="H28" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="7">
-        <v>26000</v>
+        <v>11667</v>
       </c>
       <c r="J28" s="5">
-        <v>61.3</v>
+        <v>63.6</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>77.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>430000</v>
+        <v>174000</v>
       </c>
       <c r="G29" s="7">
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="H29" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="7">
-        <v>37500</v>
+        <v>9667</v>
       </c>
       <c r="J29" s="5">
-        <v>61.1</v>
+        <v>63.6</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>166000</v>
+        <v>461000</v>
       </c>
       <c r="G30" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H30" s="7">
+        <v>4</v>
+      </c>
+      <c r="I30" s="7">
         <v>10000</v>
       </c>
-      <c r="H30" s="7">
-        <v>3</v>
-      </c>
-      <c r="I30" s="7">
-        <v>10500</v>
-      </c>
       <c r="J30" s="5">
-        <v>61.1</v>
+        <v>63.5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>88.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>184000</v>
+        <v>298000</v>
       </c>
       <c r="G31" s="7">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="H31" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I31" s="7">
-        <v>11500</v>
+        <v>26667</v>
       </c>
       <c r="J31" s="5">
-        <v>60.6</v>
+        <v>63.4</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>86.3</v>
+        <v>81.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>189000</v>
+        <v>650000</v>
       </c>
       <c r="G32" s="7">
-        <v>17000</v>
+        <v>19000</v>
       </c>
       <c r="H32" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I32" s="7">
-        <v>16000</v>
+        <v>26000</v>
       </c>
       <c r="J32" s="5">
-        <v>60.5</v>
+        <v>63.2</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>90</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>147000</v>
+        <v>323000</v>
       </c>
       <c r="G33" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H33" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="7">
-        <v>7000</v>
+        <v>7667</v>
       </c>
       <c r="J33" s="5">
-        <v>60.3</v>
+        <v>63.2</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>89.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>103000</v>
+        <v>105000</v>
       </c>
       <c r="G34" s="7">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H34" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="7">
-        <v>8000</v>
+        <v>6333</v>
       </c>
       <c r="J34" s="5">
-        <v>60.3</v>
+        <v>63.2</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>80.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>903000</v>
+        <v>179000</v>
       </c>
       <c r="G35" s="7">
-        <v>26000</v>
+        <v>6000</v>
       </c>
       <c r="H35" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I35" s="7">
-        <v>28500</v>
+        <v>9000</v>
       </c>
       <c r="J35" s="5">
-        <v>60.2</v>
+        <v>63.1</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>87.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>454000</v>
+        <v>141000</v>
       </c>
       <c r="G36" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H36" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I36" s="7">
-        <v>11500</v>
+        <v>10000</v>
       </c>
       <c r="J36" s="5">
-        <v>60</v>
+        <v>63.1</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>88.5</v>
+        <v>89</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>118000</v>
+        <v>112000</v>
       </c>
       <c r="G37" s="7">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="H37" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="7">
-        <v>7500</v>
+        <v>8333</v>
       </c>
       <c r="J37" s="5">
-        <v>59.6</v>
+        <v>63</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>86.7</v>
+        <v>82.2</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>122000</v>
+        <v>305000</v>
       </c>
       <c r="G38" s="7">
-        <v>9000</v>
+        <v>25000</v>
       </c>
       <c r="H38" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I38" s="7">
-        <v>11000</v>
+        <v>22000</v>
       </c>
       <c r="J38" s="5">
-        <v>59.4</v>
+        <v>62.7</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>87.2</v>
+        <v>79.5</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>130000</v>
+        <v>322000</v>
       </c>
       <c r="G39" s="7">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="H39" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I39" s="7">
-        <v>9500</v>
+        <v>27667</v>
       </c>
       <c r="J39" s="5">
-        <v>59.3</v>
+        <v>62.6</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>81.2</v>
+        <v>88.7</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>244000</v>
+        <v>104000</v>
       </c>
       <c r="G40" s="7">
-        <v>19000</v>
+        <v>6000</v>
       </c>
       <c r="H40" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>22000</v>
+        <v>6000</v>
       </c>
       <c r="J40" s="5">
-        <v>59.2</v>
+        <v>62.3</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>87.90000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>314000</v>
+        <v>203000</v>
       </c>
       <c r="G41" s="7">
-        <v>4000</v>
+        <v>14000</v>
       </c>
       <c r="H41" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="7">
-        <v>7000</v>
+        <v>15333</v>
       </c>
       <c r="J41" s="5">
-        <v>59.1</v>
+        <v>62</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>81.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>375000</v>
+        <v>462000</v>
       </c>
       <c r="G42" s="7">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="H42" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I42" s="7">
-        <v>20500</v>
+        <v>22000</v>
       </c>
       <c r="J42" s="5">
-        <v>59</v>
+        <v>61.8</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>81.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>280000</v>
+        <v>192000</v>
       </c>
       <c r="G43" s="7">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="H43" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I43" s="7">
-        <v>20500</v>
+        <v>10333</v>
       </c>
       <c r="J43" s="5">
-        <v>59</v>
+        <v>61.8</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>82</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>1232000</v>
+        <v>132000</v>
       </c>
       <c r="G44" s="7">
-        <v>19000</v>
+        <v>1000</v>
       </c>
       <c r="H44" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" s="7">
-        <v>19000</v>
+        <v>9000</v>
       </c>
       <c r="J44" s="5">
-        <v>58.9</v>
+        <v>61.8</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>75.2</v>
+        <v>86.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>336000</v>
+        <v>107000</v>
       </c>
       <c r="G45" s="7">
-        <v>33000</v>
+        <v>2000</v>
       </c>
       <c r="H45" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
-        <v>34000</v>
+        <v>7333</v>
       </c>
       <c r="J45" s="5">
-        <v>58.9</v>
+        <v>61.2</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>86.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>135000</v>
+        <v>368000</v>
       </c>
       <c r="G46" s="7">
-        <v>7000</v>
+        <v>32000</v>
       </c>
       <c r="H46" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7">
-        <v>8500</v>
+        <v>33333</v>
       </c>
       <c r="J46" s="5">
-        <v>58.5</v>
+        <v>61</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2143,28 +2143,30 @@
       <c r="A47" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="5"/>
+      <c r="B47" s="5">
+        <v>9</v>
+      </c>
       <c r="C47" s="5">
-        <v>83.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>127000</v>
+        <v>198000</v>
       </c>
       <c r="G47" s="7">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="H47" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="7">
-        <v>15000</v>
+        <v>5333</v>
       </c>
       <c r="J47" s="5">
-        <v>58.5</v>
+        <v>60.9</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>84.3</v>
+        <v>76.3</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>120000</v>
+        <v>361000</v>
       </c>
       <c r="G48" s="7">
-        <v>9000</v>
+        <v>23000</v>
       </c>
       <c r="H48" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48" s="7">
-        <v>12500</v>
+        <v>27000</v>
       </c>
       <c r="J48" s="5">
-        <v>58.5</v>
+        <v>60.7</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>86.90000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>154000</v>
+        <v>166000</v>
       </c>
       <c r="G49" s="7">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="H49" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I49" s="7">
-        <v>6500</v>
+        <v>7333</v>
       </c>
       <c r="J49" s="5">
-        <v>58.4</v>
+        <v>60.7</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2242,30 +2244,28 @@
       <c r="A50" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="B50" s="5">
-        <v>9</v>
-      </c>
+      <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>86.3</v>
+        <v>82.8</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>195000</v>
+        <v>135000</v>
       </c>
       <c r="G50" s="7">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="H50" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I50" s="7">
-        <v>6500</v>
+        <v>12667</v>
       </c>
       <c r="J50" s="5">
-        <v>58.1</v>
+        <v>60.7</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>80.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>472000</v>
+        <v>173000</v>
       </c>
       <c r="G51" s="7">
-        <v>19000</v>
+        <v>5000</v>
       </c>
       <c r="H51" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I51" s="7">
-        <v>17500</v>
+        <v>3667</v>
       </c>
       <c r="J51" s="5">
-        <v>57.9</v>
+        <v>60.6</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>85.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>270000</v>
+        <v>106000</v>
       </c>
       <c r="G52" s="7">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="H52" s="7">
         <v>3</v>
       </c>
       <c r="I52" s="7">
-        <v>6500</v>
+        <v>10000</v>
       </c>
       <c r="J52" s="5">
-        <v>57.8</v>
+        <v>60.5</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>87.09999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>131000</v>
+        <v>269000</v>
       </c>
       <c r="G53" s="7">
-        <v>6000</v>
+        <v>-1000</v>
       </c>
       <c r="H53" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I53" s="7">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="J53" s="5">
-        <v>57.8</v>
+        <v>60.2</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>86.3</v>
+        <v>79.8</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>111000</v>
+        <v>385000</v>
       </c>
       <c r="G54" s="7">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H54" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="J54" s="5">
-        <v>57.7</v>
+        <v>60.1</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-17T04:37:06+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-18T04:22:25+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>都重生了，谁还装富二代啊</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>点子王行动哥随便弟，三人行很刑</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
     <t>游走神话时代，开局拜师道门天师</t>
   </si>
   <si>
     <t>武侠网游，开局三个神级词条</t>
   </si>
   <si>
+    <t>纨绔大少是邪神，眷属全部是美女</t>
+  </si>
+  <si>
     <t>规则怪谈：无所谓，系统会出手</t>
   </si>
   <si>
+    <t>年代赶山：打猎娶媳妇养大姨子</t>
+  </si>
+  <si>
     <t>系统想害我，我选择上交国家</t>
   </si>
   <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
+    <t>火影：扉间问谁断后，我当三代！</t>
+  </si>
+  <si>
+    <t>名义：刚提名省服，你让我退休？</t>
+  </si>
+  <si>
+    <t>综漫：表白被拒就变强？</t>
+  </si>
+  <si>
+    <t>我一写网文的，你让我混娱乐圈？</t>
+  </si>
+  <si>
+    <t>无声1937</t>
+  </si>
+  <si>
+    <t>死刑当天，修仙者夺舍了我</t>
+  </si>
+  <si>
     <t>西游：大圣闹地府！始皇长生啦</t>
   </si>
   <si>
-    <t>无声1937</t>
-  </si>
-  <si>
-    <t>名义：刚提名省服，你让我退休？</t>
-  </si>
-  <si>
-    <t>我一写网文的，你让我混娱乐圈？</t>
-  </si>
-  <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
-    <t>死刑当天，修仙者夺舍了我</t>
-  </si>
-  <si>
-    <t>火影：扉间问谁断后，我当三代！</t>
-  </si>
-  <si>
     <t>我都永生了，会亿点技能很合理吧</t>
   </si>
   <si>
+    <t>末世：我开局拥有一艘驱逐舰</t>
+  </si>
+  <si>
     <t>灵气复苏？前世女帝老婆也复苏了</t>
   </si>
   <si>
+    <t>宿舍求生：糯米可镇不住我们太久</t>
+  </si>
+  <si>
+    <t>首富，从功夫女足开始！</t>
+  </si>
+  <si>
+    <t>奥特：天蝎座第一道光</t>
+  </si>
+  <si>
+    <t>模拟未来：我是叛徒？请世家赴死</t>
+  </si>
+  <si>
+    <t>重生八零渔村，带仨前妻赶海暴富</t>
+  </si>
+  <si>
+    <t>打卡双人骑行圈，开局拿捏假名媛</t>
+  </si>
+  <si>
+    <t>魏家孽种成首辅，全族跪求我认祖</t>
+  </si>
+  <si>
+    <t>开局魅骨词条，我成了宇智波团宠</t>
+  </si>
+  <si>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>无职：验牌洛琪希，牌没有问题？</t>
+  </si>
+  <si>
+    <t>无敌江湖后，我隐退于世</t>
+  </si>
+  <si>
+    <t>玄幻：多管闲事，成人间武圣</t>
+  </si>
+  <si>
+    <t>洪荒：我十凶天角蚁，躺平就变强</t>
+  </si>
+  <si>
+    <t>领证三天，我被未婚妻杀死</t>
+  </si>
+  <si>
+    <t>命格通神，我的悟性可以无限叠加</t>
+  </si>
+  <si>
+    <t>飓风战魂：我的陀螺竟是谱尼？！</t>
+  </si>
+  <si>
+    <t>惊悚世界，我的小弟有亿点多</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>大唐：不是诗仙，但是真剑仙！</t>
+  </si>
+  <si>
+    <t>斩神师兄太我清道德天尊社恐反差</t>
+  </si>
+  <si>
+    <t>楼层求生：从垃圾场开始变废为宝</t>
+  </si>
+  <si>
+    <t>从金丹仙族开始的老祖之路！</t>
+  </si>
+  <si>
+    <t>全民英雄协会：开局招募一拳光头</t>
+  </si>
+  <si>
     <t>一毛一天修为，我靠直播氪穿宇宙</t>
   </si>
   <si>
-    <t>宿舍求生：糯米可镇不住我们太久</t>
-  </si>
-  <si>
-    <t>魏家孽种成首辅，全族跪求我认祖</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
-  </si>
-  <si>
-    <t>命格通神，我的悟性可以无限叠加</t>
-  </si>
-  <si>
-    <t>重生八零渔村，带仨前妻赶海暴富</t>
-  </si>
-  <si>
-    <t>无职：验牌洛琪希，牌没有问题？</t>
-  </si>
-  <si>
-    <t>开局魅骨词条，我成了宇智波团宠</t>
-  </si>
-  <si>
-    <t>穿越70，我被身边的人宠坏了</t>
-  </si>
-  <si>
-    <t>综漫：表白被拒就变强？</t>
-  </si>
-  <si>
-    <t>洪荒：我十凶天角蚁，躺平就变强</t>
-  </si>
-  <si>
-    <t>打卡双人骑行圈，开局拿捏假名媛</t>
-  </si>
-  <si>
-    <t>奥特：天蝎座第一道光</t>
-  </si>
-  <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>大唐：不是诗仙，但是真剑仙！</t>
-  </si>
-  <si>
-    <t>末世：我开局拥有一艘驱逐舰</t>
-  </si>
-  <si>
-    <t>穿越黄毛，女主们把我当白月光了</t>
-  </si>
-  <si>
-    <t>模拟未来：我是叛徒？请世家赴死</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>惊悚世界，我的小弟有亿点多</t>
-  </si>
-  <si>
     <t>祖上十八鬼帝，你让我恐怖求生？</t>
   </si>
   <si>
-    <t>从零开始，打造华夏首支特种部队</t>
+    <t>给员工发超跑，你当死士养呢？</t>
+  </si>
+  <si>
+    <t>重生三岁被捡，成了杨老板亲弟</t>
+  </si>
+  <si>
+    <t>海洋求生，上船两个要求，大萝莉</t>
+  </si>
+  <si>
+    <t>分手后，她们变得不对劲了！</t>
   </si>
   <si>
     <t>一心求死，反倒成为千古一帝？</t>
-  </si>
-  <si>
-    <t>斩神师兄太我清道德天尊社恐反差</t>
-  </si>
-  <si>
-    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
-  </si>
-  <si>
-    <t>无敌江湖后，我隐退于世</t>
-  </si>
-  <si>
-    <t>玄幻：多管闲事，成人间武圣</t>
-  </si>
-  <si>
-    <t>青梅是天命之女？可我既是天命！</t>
-  </si>
-  <si>
-    <t>给员工发超跑，你当死士养呢？</t>
-  </si>
-  <si>
-    <t>重生三岁被捡，成了杨老板亲弟</t>
-  </si>
-  <si>
-    <t>分手后，她们变得不对劲了！</t>
-  </si>
-  <si>
-    <t>全民英雄协会：开局招募一拳光头</t>
-  </si>
-  <si>
-    <t>刚进宗门，就睡出个绝美师尊老婆</t>
-  </si>
-  <si>
-    <t>爱情公寓：开局拿下林妙妙</t>
-  </si>
-  <si>
-    <t>别人穿四合院，我为啥上战场</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>95.2</v>
+        <v>93.7</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>894000</v>
+        <v>814000</v>
       </c>
       <c r="G5" s="7">
-        <v>46000</v>
+        <v>309000</v>
       </c>
       <c r="H5" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I5" s="7">
-        <v>72667</v>
+        <v>172000</v>
       </c>
       <c r="J5" s="5">
-        <v>82.5</v>
+        <v>85.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>295000</v>
+        <v>936000</v>
       </c>
       <c r="G6" s="7">
-        <v>49000</v>
+        <v>42000</v>
       </c>
       <c r="H6" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I6" s="7">
-        <v>42667</v>
+        <v>65000</v>
       </c>
       <c r="J6" s="5">
-        <v>77.7</v>
+        <v>83.3</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>197000</v>
+        <v>327000</v>
       </c>
       <c r="G7" s="7">
-        <v>42000</v>
+        <v>32000</v>
       </c>
       <c r="H7" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I7" s="7">
-        <v>33333</v>
+        <v>40000</v>
       </c>
       <c r="J7" s="5">
-        <v>75.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>83.2</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>1596000</v>
+        <v>242000</v>
       </c>
       <c r="G8" s="7">
-        <v>47000</v>
+        <v>45000</v>
       </c>
       <c r="H8" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I8" s="7">
-        <v>65000</v>
+        <v>36250</v>
       </c>
       <c r="J8" s="5">
-        <v>74</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>85.09999999999999</v>
+        <v>84</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>1580000</v>
+        <v>676000</v>
       </c>
       <c r="G9" s="7">
-        <v>63000</v>
+        <v>70000</v>
       </c>
       <c r="H9" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I9" s="7">
-        <v>51333</v>
+        <v>76000</v>
       </c>
       <c r="J9" s="5">
-        <v>71.59999999999999</v>
+        <v>74.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>95.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>149000</v>
+        <v>1613000</v>
       </c>
       <c r="G10" s="7">
-        <v>20000</v>
+        <v>17000</v>
       </c>
       <c r="H10" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7">
-        <v>20333</v>
+        <v>53000</v>
       </c>
       <c r="J10" s="5">
-        <v>69.8</v>
+        <v>73</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>86.2</v>
+        <v>97.8</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>415000</v>
+        <v>117000</v>
       </c>
       <c r="G11" s="7">
-        <v>31000</v>
+        <v>20000</v>
       </c>
       <c r="H11" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
-        <v>39333</v>
+        <v>15750</v>
       </c>
       <c r="J11" s="5">
-        <v>69.2</v>
+        <v>72.7</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>96.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>223000</v>
+        <v>1613000</v>
       </c>
       <c r="G12" s="7">
-        <v>24000</v>
+        <v>33000</v>
       </c>
       <c r="H12" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7">
-        <v>24500</v>
+        <v>46750</v>
       </c>
       <c r="J12" s="5">
-        <v>68.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>83.40000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>933000</v>
+        <v>634000</v>
       </c>
       <c r="G13" s="7">
-        <v>39000</v>
+        <v>49000</v>
       </c>
       <c r="H13" s="7">
         <v>4</v>
       </c>
       <c r="I13" s="7">
-        <v>40000</v>
+        <v>48667</v>
       </c>
       <c r="J13" s="5">
-        <v>67.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>82.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>585000</v>
+        <v>369000</v>
       </c>
       <c r="G14" s="7">
-        <v>36000</v>
+        <v>17000</v>
       </c>
       <c r="H14" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I14" s="7">
-        <v>48500</v>
+        <v>19250</v>
       </c>
       <c r="J14" s="5">
-        <v>66.7</v>
+        <v>70.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>85.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>309000</v>
+        <v>245000</v>
       </c>
       <c r="G15" s="7">
-        <v>34000</v>
+        <v>22000</v>
       </c>
       <c r="H15" s="7">
         <v>4</v>
       </c>
       <c r="I15" s="7">
-        <v>30667</v>
+        <v>23667</v>
       </c>
       <c r="J15" s="5">
-        <v>66.7</v>
+        <v>69.8</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>90.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>352000</v>
+        <v>209000</v>
       </c>
       <c r="G16" s="7">
-        <v>8000</v>
+        <v>18000</v>
       </c>
       <c r="H16" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="7">
-        <v>20000</v>
+        <v>13250</v>
       </c>
       <c r="J16" s="5">
-        <v>66.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>81.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>442000</v>
+        <v>957000</v>
       </c>
       <c r="G17" s="7">
-        <v>39000</v>
+        <v>24000</v>
       </c>
       <c r="H17" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="7">
-        <v>36667</v>
+        <v>36000</v>
       </c>
       <c r="J17" s="5">
-        <v>65.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>86.2</v>
+        <v>81.8</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>274000</v>
+        <v>430000</v>
       </c>
       <c r="G18" s="7">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="H18" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="7">
-        <v>24667</v>
+        <v>33250</v>
       </c>
       <c r="J18" s="5">
-        <v>65.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>93.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>131000</v>
+        <v>331000</v>
       </c>
       <c r="G19" s="7">
-        <v>13000</v>
+        <v>22000</v>
       </c>
       <c r="H19" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
-        <v>9333</v>
+        <v>28500</v>
       </c>
       <c r="J19" s="5">
-        <v>65.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>91.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>106000</v>
+        <v>157000</v>
       </c>
       <c r="G20" s="7">
-        <v>13000</v>
+        <v>8000</v>
       </c>
       <c r="H20" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I20" s="7">
-        <v>11333</v>
+        <v>17250</v>
       </c>
       <c r="J20" s="5">
-        <v>65.2</v>
+        <v>67.7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>80.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>446000</v>
+        <v>475000</v>
       </c>
       <c r="G21" s="7">
-        <v>25000</v>
+        <v>33000</v>
       </c>
       <c r="H21" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="7">
-        <v>33333</v>
+        <v>35750</v>
       </c>
       <c r="J21" s="5">
-        <v>64.8</v>
+        <v>67.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>92.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>156000</v>
+        <v>188000</v>
       </c>
       <c r="G22" s="7">
         <v>9000</v>
       </c>
       <c r="H22" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I22" s="7">
-        <v>7667</v>
+        <v>9000</v>
       </c>
       <c r="J22" s="5">
-        <v>64.59999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>90.3</v>
+        <v>83.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>100000</v>
+        <v>299000</v>
       </c>
       <c r="G23" s="7">
-        <v>12000</v>
+        <v>25000</v>
       </c>
       <c r="H23" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="7">
-        <v>11333</v>
+        <v>24750</v>
       </c>
       <c r="J23" s="5">
-        <v>64.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>90.09999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>171000</v>
+        <v>118000</v>
       </c>
       <c r="G24" s="7">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="H24" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" s="7">
-        <v>11000</v>
+        <v>11500</v>
       </c>
       <c r="J24" s="5">
-        <v>64.3</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>84.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>234000</v>
+        <v>101000</v>
       </c>
       <c r="G25" s="7">
-        <v>21000</v>
+        <v>7000</v>
       </c>
       <c r="H25" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="7">
-        <v>22667</v>
+        <v>6250</v>
       </c>
       <c r="J25" s="5">
-        <v>64</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>93.5</v>
+        <v>83</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>181000</v>
+        <v>317000</v>
       </c>
       <c r="G26" s="7">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="H26" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I26" s="7">
-        <v>14000</v>
+        <v>24750</v>
       </c>
       <c r="J26" s="5">
-        <v>63.9</v>
+        <v>66.8</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>82.59999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>230000</v>
+        <v>122000</v>
       </c>
       <c r="G27" s="7">
-        <v>27000</v>
+        <v>10000</v>
       </c>
       <c r="H27" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I27" s="7">
-        <v>25000</v>
+        <v>8750</v>
       </c>
       <c r="J27" s="5">
-        <v>63.7</v>
+        <v>66.8</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>88.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>191000</v>
+        <v>178000</v>
       </c>
       <c r="G28" s="7">
+        <v>7000</v>
+      </c>
+      <c r="H28" s="7">
+        <v>5</v>
+      </c>
+      <c r="I28" s="7">
         <v>10000</v>
       </c>
-      <c r="H28" s="7">
-        <v>4</v>
-      </c>
-      <c r="I28" s="7">
-        <v>11667</v>
-      </c>
       <c r="J28" s="5">
-        <v>63.6</v>
+        <v>66.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>89.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>174000</v>
+        <v>469000</v>
       </c>
       <c r="G29" s="7">
         <v>8000</v>
       </c>
       <c r="H29" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" s="7">
-        <v>9667</v>
+        <v>9500</v>
       </c>
       <c r="J29" s="5">
-        <v>63.6</v>
+        <v>66.5</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89</v>
+        <v>79.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>461000</v>
+        <v>465000</v>
       </c>
       <c r="G30" s="7">
-        <v>7000</v>
+        <v>19000</v>
       </c>
       <c r="H30" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>10000</v>
+        <v>29750</v>
       </c>
       <c r="J30" s="5">
-        <v>63.5</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>81.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>298000</v>
+        <v>195000</v>
       </c>
       <c r="G31" s="7">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="H31" s="7">
         <v>4</v>
       </c>
       <c r="I31" s="7">
-        <v>26667</v>
+        <v>14000</v>
       </c>
       <c r="J31" s="5">
-        <v>63.4</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>81.2</v>
+        <v>89.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>650000</v>
+        <v>161000</v>
       </c>
       <c r="G32" s="7">
-        <v>19000</v>
+        <v>5000</v>
       </c>
       <c r="H32" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" s="7">
-        <v>26000</v>
+        <v>7000</v>
       </c>
       <c r="J32" s="5">
-        <v>63.2</v>
+        <v>65.8</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>89.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>323000</v>
+        <v>326000</v>
       </c>
       <c r="G33" s="7">
-        <v>9000</v>
+        <v>21000</v>
       </c>
       <c r="H33" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>7667</v>
+        <v>21750</v>
       </c>
       <c r="J33" s="5">
-        <v>63.2</v>
+        <v>65.5</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>90.3</v>
+        <v>81.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>105000</v>
+        <v>251000</v>
       </c>
       <c r="G34" s="7">
-        <v>6000</v>
+        <v>17000</v>
       </c>
       <c r="H34" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" s="7">
-        <v>6333</v>
+        <v>21250</v>
       </c>
       <c r="J34" s="5">
-        <v>63.2</v>
+        <v>65.3</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>88.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>179000</v>
+        <v>112000</v>
       </c>
       <c r="G35" s="7">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="H35" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I35" s="7">
-        <v>9000</v>
+        <v>6750</v>
       </c>
       <c r="J35" s="5">
-        <v>63.1</v>
+        <v>65.3</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>88.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>141000</v>
+        <v>399000</v>
       </c>
       <c r="G36" s="7">
-        <v>11000</v>
+        <v>31000</v>
       </c>
       <c r="H36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36" s="7">
-        <v>10000</v>
+        <v>32750</v>
       </c>
       <c r="J36" s="5">
-        <v>63.1</v>
+        <v>65.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>89</v>
+        <v>87.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>112000</v>
+        <v>179000</v>
       </c>
       <c r="G37" s="7">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="H37" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" s="7">
-        <v>8333</v>
+        <v>8500</v>
       </c>
       <c r="J37" s="5">
-        <v>63</v>
+        <v>65.2</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>82.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>305000</v>
+        <v>115000</v>
       </c>
       <c r="G38" s="7">
-        <v>25000</v>
+        <v>21000</v>
       </c>
       <c r="H38" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I38" s="7">
-        <v>22000</v>
+        <v>5750</v>
       </c>
       <c r="J38" s="5">
-        <v>62.7</v>
+        <v>65.2</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>79.5</v>
+        <v>86</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>322000</v>
+        <v>110000</v>
       </c>
       <c r="G39" s="7">
-        <v>30000</v>
+        <v>10000</v>
       </c>
       <c r="H39" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I39" s="7">
-        <v>27667</v>
+        <v>11000</v>
       </c>
       <c r="J39" s="5">
-        <v>62.6</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>88.7</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>104000</v>
+        <v>152000</v>
       </c>
       <c r="G40" s="7">
-        <v>6000</v>
+        <v>12000</v>
       </c>
       <c r="H40" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I40" s="7">
-        <v>6000</v>
+        <v>9750</v>
       </c>
       <c r="J40" s="5">
-        <v>62.3</v>
+        <v>64.8</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>83.90000000000001</v>
+        <v>77.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>203000</v>
+        <v>349000</v>
       </c>
       <c r="G41" s="7">
-        <v>14000</v>
+        <v>27000</v>
       </c>
       <c r="H41" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>15333</v>
+        <v>27500</v>
       </c>
       <c r="J41" s="5">
-        <v>62</v>
+        <v>64.7</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>80.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>462000</v>
+        <v>325000</v>
       </c>
       <c r="G42" s="7">
-        <v>14000</v>
+        <v>2000</v>
       </c>
       <c r="H42" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I42" s="7">
-        <v>22000</v>
+        <v>6250</v>
       </c>
       <c r="J42" s="5">
-        <v>61.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>85.8</v>
+        <v>87.2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>192000</v>
+        <v>108000</v>
       </c>
       <c r="G43" s="7">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="H43" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43" s="7">
-        <v>10333</v>
+        <v>5500</v>
       </c>
       <c r="J43" s="5">
-        <v>61.8</v>
+        <v>64.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>132000</v>
+        <v>199000</v>
       </c>
       <c r="G44" s="7">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="H44" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" s="7">
-        <v>9000</v>
+        <v>9500</v>
       </c>
       <c r="J44" s="5">
-        <v>61.8</v>
+        <v>64.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>86.2</v>
+        <v>87.7</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>107000</v>
+        <v>140000</v>
       </c>
       <c r="G45" s="7">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H45" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I45" s="7">
-        <v>7333</v>
+        <v>4000</v>
       </c>
       <c r="J45" s="5">
-        <v>61.2</v>
+        <v>64.2</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>74</v>
+        <v>79.5</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>368000</v>
+        <v>658000</v>
       </c>
       <c r="G46" s="7">
-        <v>32000</v>
+        <v>8000</v>
       </c>
       <c r="H46" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I46" s="7">
-        <v>33333</v>
+        <v>21500</v>
       </c>
       <c r="J46" s="5">
-        <v>61</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2143,30 +2143,28 @@
       <c r="A47" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="5">
-        <v>9</v>
-      </c>
+      <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>86.40000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>198000</v>
+        <v>179000</v>
       </c>
       <c r="G47" s="7">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H47" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="7">
-        <v>5333</v>
+        <v>4250</v>
       </c>
       <c r="J47" s="5">
-        <v>60.9</v>
+        <v>64</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>76.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>361000</v>
+        <v>135000</v>
       </c>
       <c r="G48" s="7">
-        <v>23000</v>
+        <v>4000</v>
       </c>
       <c r="H48" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I48" s="7">
-        <v>27000</v>
+        <v>8000</v>
       </c>
       <c r="J48" s="5">
-        <v>60.7</v>
+        <v>64</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>85.3</v>
+        <v>86.5</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>166000</v>
+        <v>108000</v>
       </c>
       <c r="G49" s="7">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="H49" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I49" s="7">
-        <v>7333</v>
+        <v>5500</v>
       </c>
       <c r="J49" s="5">
-        <v>60.7</v>
+        <v>64</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>82.8</v>
+        <v>76.5</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>135000</v>
+        <v>386000</v>
       </c>
       <c r="G50" s="7">
-        <v>8000</v>
+        <v>25000</v>
       </c>
       <c r="H50" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" s="7">
-        <v>12667</v>
+        <v>26500</v>
       </c>
       <c r="J50" s="5">
-        <v>60.7</v>
+        <v>63.7</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>86.7</v>
+        <v>85.2</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>173000</v>
+        <v>174000</v>
       </c>
       <c r="G51" s="7">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="H51" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I51" s="7">
-        <v>3667</v>
+        <v>7500</v>
       </c>
       <c r="J51" s="5">
-        <v>60.6</v>
+        <v>63.7</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>89.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>106000</v>
+        <v>135000</v>
       </c>
       <c r="G52" s="7">
-        <v>8000</v>
+        <v>11000</v>
       </c>
       <c r="H52" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I52" s="7">
-        <v>10000</v>
+        <v>6667</v>
       </c>
       <c r="J52" s="5">
-        <v>60.5</v>
+        <v>63.4</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>85.90000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>269000</v>
+        <v>144000</v>
       </c>
       <c r="G53" s="7">
-        <v>-1000</v>
+        <v>9000</v>
       </c>
       <c r="H53" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7">
-        <v>4000</v>
+        <v>11750</v>
       </c>
       <c r="J53" s="5">
-        <v>60.2</v>
+        <v>63.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>79.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>385000</v>
+        <v>467000</v>
       </c>
       <c r="G54" s="7">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H54" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I54" s="7">
-        <v>17000</v>
+        <v>17750</v>
       </c>
       <c r="J54" s="5">
-        <v>60.1</v>
+        <v>63.1</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-18T04:22:25+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-19T04:18:55+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
-    <t>都重生了，谁还装富二代啊</t>
+    <t>游走神话时代，开局拜师道门天师</t>
   </si>
   <si>
     <t>打开作品</t>
   </si>
   <si>
+    <t>武侠网游，开局三个神级词条</t>
+  </si>
+  <si>
     <t>点子王行动哥随便弟，三人行很刑</t>
   </si>
   <si>
-    <t>游走神话时代，开局拜师道门天师</t>
-  </si>
-  <si>
-    <t>武侠网游，开局三个神级词条</t>
-  </si>
-  <si>
     <t>纨绔大少是邪神，眷属全部是美女</t>
   </si>
   <si>
+    <t>凤流高手</t>
+  </si>
+  <si>
+    <t>系统想害我，我选择上交国家</t>
+  </si>
+  <si>
     <t>规则怪谈：无所谓，系统会出手</t>
   </si>
   <si>
-    <t>年代赶山：打猎娶媳妇养大姨子</t>
-  </si>
-  <si>
-    <t>系统想害我，我选择上交国家</t>
+    <t>综漫：表白被拒就变强？</t>
+  </si>
+  <si>
+    <t>带着渡劫修为，重回高中时代</t>
+  </si>
+  <si>
+    <t>火影：扉间问谁断后，我当三代！</t>
+  </si>
+  <si>
+    <t>宿舍求生：糯米可镇不住我们太久</t>
   </si>
   <si>
     <t>说好造桥游戏，打穿天山什么鬼？</t>
   </si>
   <si>
-    <t>火影：扉间问谁断后，我当三代！</t>
+    <t>西游：大圣闹地府！始皇长生啦</t>
+  </si>
+  <si>
+    <t>国运三角洲，开局航天堵桥</t>
+  </si>
+  <si>
+    <t>人在高中，香火证道什么鬼？</t>
+  </si>
+  <si>
+    <t>我一写网文的，你让我混娱乐圈？</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>死刑当天，修仙者夺舍了我</t>
   </si>
   <si>
     <t>名义：刚提名省服，你让我退休？</t>
   </si>
   <si>
-    <t>综漫：表白被拒就变强？</t>
-  </si>
-  <si>
-    <t>我一写网文的，你让我混娱乐圈？</t>
+    <t>县城：女友出国要我卖房，给脸了</t>
+  </si>
+  <si>
+    <t>神女录：开局契约外冷内齁裴玉寒</t>
+  </si>
+  <si>
+    <t>末世：我开局拥有一艘驱逐舰</t>
+  </si>
+  <si>
+    <t>她未上岸提分手，我结婚她破防了</t>
+  </si>
+  <si>
+    <t>打卡双人骑行圈，开局拿捏假名媛</t>
+  </si>
+  <si>
+    <t>我都永生了，会亿点技能很合理吧</t>
   </si>
   <si>
     <t>无声1937</t>
   </si>
   <si>
-    <t>死刑当天，修仙者夺舍了我</t>
-  </si>
-  <si>
-    <t>西游：大圣闹地府！始皇长生啦</t>
-  </si>
-  <si>
-    <t>我都永生了，会亿点技能很合理吧</t>
-  </si>
-  <si>
-    <t>末世：我开局拥有一艘驱逐舰</t>
+    <t>飓风战魂：我的陀螺竟是谱尼？！</t>
   </si>
   <si>
     <t>灵气复苏？前世女帝老婆也复苏了</t>
   </si>
   <si>
-    <t>宿舍求生：糯米可镇不住我们太久</t>
-  </si>
-  <si>
-    <t>首富，从功夫女足开始！</t>
+    <t>重生八零渔村，带仨前妻赶海暴富</t>
+  </si>
+  <si>
+    <t>命格通神，我的悟性可以无限叠加</t>
   </si>
   <si>
     <t>奥特：天蝎座第一道光</t>
   </si>
   <si>
+    <t>全民英雄协会：开局招募一拳光头</t>
+  </si>
+  <si>
+    <t>刚进宗门，就睡出个绝美师尊老婆</t>
+  </si>
+  <si>
+    <t>三次入伍，我只想退伍进体制</t>
+  </si>
+  <si>
+    <t>退休勇者买下魔王当女仆</t>
+  </si>
+  <si>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
+    <t>分手后，她们变得不对劲了！</t>
+  </si>
+  <si>
+    <t>开局魅骨词条，我成了宇智波团宠</t>
+  </si>
+  <si>
+    <t>玄幻：多管闲事，成人间武圣</t>
+  </si>
+  <si>
+    <t>无职：验牌洛琪希，牌没有问题？</t>
+  </si>
+  <si>
+    <t>惊悚世界，我的小弟有亿点多</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>觉醒伪神，神明弃我，我自为神</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>祖上十八鬼帝，你让我恐怖求生？</t>
+  </si>
+  <si>
+    <t>从金丹仙族开始的老祖之路！</t>
+  </si>
+  <si>
     <t>模拟未来：我是叛徒？请世家赴死</t>
   </si>
   <si>
-    <t>重生八零渔村，带仨前妻赶海暴富</t>
-  </si>
-  <si>
-    <t>打卡双人骑行圈，开局拿捏假名媛</t>
-  </si>
-  <si>
-    <t>魏家孽种成首辅，全族跪求我认祖</t>
-  </si>
-  <si>
-    <t>开局魅骨词条，我成了宇智波团宠</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>无职：验牌洛琪希，牌没有问题？</t>
-  </si>
-  <si>
-    <t>无敌江湖后，我隐退于世</t>
-  </si>
-  <si>
-    <t>玄幻：多管闲事，成人间武圣</t>
-  </si>
-  <si>
-    <t>洪荒：我十凶天角蚁，躺平就变强</t>
-  </si>
-  <si>
-    <t>领证三天，我被未婚妻杀死</t>
-  </si>
-  <si>
-    <t>命格通神，我的悟性可以无限叠加</t>
-  </si>
-  <si>
-    <t>飓风战魂：我的陀螺竟是谱尼？！</t>
-  </si>
-  <si>
-    <t>惊悚世界，我的小弟有亿点多</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>大唐：不是诗仙，但是真剑仙！</t>
-  </si>
-  <si>
-    <t>斩神师兄太我清道德天尊社恐反差</t>
+    <t>重生三岁被捡，成了杨老板亲弟</t>
   </si>
   <si>
     <t>楼层求生：从垃圾场开始变废为宝</t>
   </si>
   <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>全民英雄协会：开局招募一拳光头</t>
-  </si>
-  <si>
-    <t>一毛一天修为，我靠直播氪穿宇宙</t>
-  </si>
-  <si>
-    <t>祖上十八鬼帝，你让我恐怖求生？</t>
-  </si>
-  <si>
-    <t>给员工发超跑，你当死士养呢？</t>
-  </si>
-  <si>
-    <t>重生三岁被捡，成了杨老板亲弟</t>
-  </si>
-  <si>
-    <t>海洋求生，上船两个要求，大萝莉</t>
-  </si>
-  <si>
-    <t>分手后，她们变得不对劲了！</t>
-  </si>
-  <si>
-    <t>一心求死，反倒成为千古一帝？</t>
+    <t>诡异世界，我的神通无限升级！</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>93.7</v>
+        <v>98.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>814000</v>
+        <v>361000</v>
       </c>
       <c r="G5" s="7">
-        <v>309000</v>
+        <v>34000</v>
       </c>
       <c r="H5" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
-        <v>172000</v>
+        <v>38800</v>
       </c>
       <c r="J5" s="5">
-        <v>85.5</v>
+        <v>81.7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>94.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>936000</v>
+        <v>263000</v>
       </c>
       <c r="G6" s="7">
-        <v>42000</v>
+        <v>21000</v>
       </c>
       <c r="H6" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I6" s="7">
-        <v>65000</v>
+        <v>33200</v>
       </c>
       <c r="J6" s="5">
-        <v>83.3</v>
+        <v>79</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>98.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>327000</v>
+        <v>947000</v>
       </c>
       <c r="G7" s="7">
-        <v>32000</v>
+        <v>11000</v>
       </c>
       <c r="H7" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="7">
-        <v>40000</v>
+        <v>54200</v>
       </c>
       <c r="J7" s="5">
-        <v>79.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>242000</v>
+        <v>739000</v>
       </c>
       <c r="G8" s="7">
-        <v>45000</v>
+        <v>63000</v>
       </c>
       <c r="H8" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I8" s="7">
-        <v>36250</v>
+        <v>71667</v>
       </c>
       <c r="J8" s="5">
-        <v>79.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>676000</v>
+        <v>107000</v>
       </c>
       <c r="G9" s="7">
-        <v>70000</v>
+        <v>15000</v>
       </c>
       <c r="H9" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>76000</v>
+        <v>14600</v>
       </c>
       <c r="J9" s="5">
-        <v>74.2</v>
+        <v>74.5</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>81.3</v>
+        <v>82.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>1613000</v>
+        <v>1641000</v>
       </c>
       <c r="G10" s="7">
-        <v>17000</v>
+        <v>28000</v>
       </c>
       <c r="H10" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>53000</v>
+        <v>43000</v>
       </c>
       <c r="J10" s="5">
-        <v>73</v>
+        <v>74.3</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>97.8</v>
+        <v>80.8</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>117000</v>
+        <v>1622000</v>
       </c>
       <c r="G11" s="7">
-        <v>20000</v>
+        <v>9000</v>
       </c>
       <c r="H11" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" s="7">
-        <v>15750</v>
+        <v>44200</v>
       </c>
       <c r="J11" s="5">
-        <v>72.7</v>
+        <v>73.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>83.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>1613000</v>
+        <v>228000</v>
       </c>
       <c r="G12" s="7">
-        <v>33000</v>
+        <v>19000</v>
       </c>
       <c r="H12" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="7">
-        <v>46750</v>
+        <v>14400</v>
       </c>
       <c r="J12" s="5">
-        <v>72.40000000000001</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>85.7</v>
+        <v>95</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>634000</v>
+        <v>110000</v>
       </c>
       <c r="G13" s="7">
-        <v>49000</v>
+        <v>12000</v>
       </c>
       <c r="H13" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>48667</v>
+        <v>10000</v>
       </c>
       <c r="J13" s="5">
-        <v>71.3</v>
+        <v>72.8</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>92.7</v>
+        <v>90</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>369000</v>
+        <v>377000</v>
       </c>
       <c r="G14" s="7">
+        <v>8000</v>
+      </c>
+      <c r="H14" s="7">
+        <v>6</v>
+      </c>
+      <c r="I14" s="7">
         <v>17000</v>
       </c>
-      <c r="H14" s="7">
-        <v>5</v>
-      </c>
-      <c r="I14" s="7">
-        <v>19250</v>
-      </c>
       <c r="J14" s="5">
-        <v>70.8</v>
+        <v>71.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94.3</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>245000</v>
+        <v>130000</v>
       </c>
       <c r="G15" s="7">
-        <v>22000</v>
+        <v>12000</v>
       </c>
       <c r="H15" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I15" s="7">
-        <v>23667</v>
+        <v>11600</v>
       </c>
       <c r="J15" s="5">
-        <v>69.8</v>
+        <v>71.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>209000</v>
+        <v>666000</v>
       </c>
       <c r="G16" s="7">
-        <v>18000</v>
+        <v>32000</v>
       </c>
       <c r="H16" s="7">
         <v>5</v>
       </c>
       <c r="I16" s="7">
-        <v>13250</v>
+        <v>44500</v>
       </c>
       <c r="J16" s="5">
-        <v>69.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>81.59999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>957000</v>
+        <v>165000</v>
       </c>
       <c r="G17" s="7">
-        <v>24000</v>
+        <v>8000</v>
       </c>
       <c r="H17" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>36000</v>
+        <v>15400</v>
       </c>
       <c r="J17" s="5">
-        <v>68.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>81.8</v>
+        <v>92.8</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>430000</v>
+        <v>101000</v>
       </c>
       <c r="G18" s="7">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="H18" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="7">
-        <v>33250</v>
+        <v>8400</v>
       </c>
       <c r="J18" s="5">
-        <v>68.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>83.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>331000</v>
+        <v>212000</v>
       </c>
       <c r="G19" s="7">
-        <v>22000</v>
+        <v>15000</v>
       </c>
       <c r="H19" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19" s="7">
-        <v>28500</v>
+        <v>10400</v>
       </c>
       <c r="J19" s="5">
-        <v>68.3</v>
+        <v>71</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>88</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>157000</v>
+        <v>974000</v>
       </c>
       <c r="G20" s="7">
-        <v>8000</v>
+        <v>17000</v>
       </c>
       <c r="H20" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
-        <v>17250</v>
+        <v>32200</v>
       </c>
       <c r="J20" s="5">
-        <v>67.7</v>
+        <v>70.5</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>79.2</v>
+        <v>93.7</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>475000</v>
+        <v>410000</v>
       </c>
       <c r="G21" s="7">
-        <v>33000</v>
+        <v>22000</v>
       </c>
       <c r="H21" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" s="7">
-        <v>35750</v>
+        <v>3800</v>
       </c>
       <c r="J21" s="5">
-        <v>67.5</v>
+        <v>70.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>90.59999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>188000</v>
+        <v>352000</v>
       </c>
       <c r="G22" s="7">
-        <v>9000</v>
+        <v>21000</v>
       </c>
       <c r="H22" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I22" s="7">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="J22" s="5">
-        <v>67.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>83.2</v>
+        <v>90.3</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>299000</v>
+        <v>257000</v>
       </c>
       <c r="G23" s="7">
-        <v>25000</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="7">
         <v>5</v>
       </c>
       <c r="I23" s="7">
-        <v>24750</v>
+        <v>20750</v>
       </c>
       <c r="J23" s="5">
-        <v>66.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>89.2</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>118000</v>
+        <v>322000</v>
       </c>
       <c r="G24" s="7">
-        <v>12000</v>
+        <v>42000</v>
       </c>
       <c r="H24" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I24" s="7">
-        <v>11500</v>
+        <v>10000</v>
       </c>
       <c r="J24" s="5">
-        <v>66.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>91.59999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>101000</v>
+        <v>104000</v>
       </c>
       <c r="G25" s="7">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="H25" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" s="7">
-        <v>6250</v>
+        <v>5600</v>
       </c>
       <c r="J25" s="5">
-        <v>66.90000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>83</v>
+        <v>88.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>317000</v>
+        <v>194000</v>
       </c>
       <c r="G26" s="7">
-        <v>19000</v>
+        <v>6000</v>
       </c>
       <c r="H26" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" s="7">
-        <v>24750</v>
+        <v>8400</v>
       </c>
       <c r="J26" s="5">
-        <v>66.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>90.2</v>
+        <v>88.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>122000</v>
+        <v>106000</v>
       </c>
       <c r="G27" s="7">
-        <v>10000</v>
+        <v>28000</v>
       </c>
       <c r="H27" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="7">
-        <v>8750</v>
+        <v>8400</v>
       </c>
       <c r="J27" s="5">
-        <v>66.8</v>
+        <v>68.8</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>89.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>178000</v>
+        <v>470000</v>
       </c>
       <c r="G28" s="7">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="H28" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I28" s="7">
-        <v>10000</v>
+        <v>7800</v>
       </c>
       <c r="J28" s="5">
-        <v>66.7</v>
+        <v>68.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>89.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>469000</v>
+        <v>499000</v>
       </c>
       <c r="G29" s="7">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="H29" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I29" s="7">
-        <v>9500</v>
+        <v>33400</v>
       </c>
       <c r="J29" s="5">
-        <v>66.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>79.3</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>465000</v>
+        <v>435000</v>
       </c>
       <c r="G30" s="7">
-        <v>19000</v>
+        <v>5000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>29750</v>
+        <v>27600</v>
       </c>
       <c r="J30" s="5">
-        <v>66.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>91.7</v>
+        <v>87</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>195000</v>
+        <v>166000</v>
       </c>
       <c r="G31" s="7">
         <v>14000</v>
       </c>
       <c r="H31" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I31" s="7">
-        <v>14000</v>
+        <v>10600</v>
       </c>
       <c r="J31" s="5">
-        <v>65.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>89.2</v>
+        <v>80.8</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>161000</v>
+        <v>314000</v>
       </c>
       <c r="G32" s="7">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="H32" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I32" s="7">
-        <v>7000</v>
+        <v>22800</v>
       </c>
       <c r="J32" s="5">
-        <v>65.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>82</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>326000</v>
+        <v>181000</v>
       </c>
       <c r="G33" s="7">
-        <v>21000</v>
+        <v>3000</v>
       </c>
       <c r="H33" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I33" s="7">
-        <v>21750</v>
+        <v>8600</v>
       </c>
       <c r="J33" s="5">
-        <v>65.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>81.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>251000</v>
+        <v>119000</v>
       </c>
       <c r="G34" s="7">
-        <v>17000</v>
+        <v>9000</v>
       </c>
       <c r="H34" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>21250</v>
+        <v>10600</v>
       </c>
       <c r="J34" s="5">
-        <v>65.3</v>
+        <v>68</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>88.3</v>
+        <v>80.5</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>112000</v>
+        <v>329000</v>
       </c>
       <c r="G35" s="7">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="H35" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>6750</v>
+        <v>22200</v>
       </c>
       <c r="J35" s="5">
-        <v>65.3</v>
+        <v>67.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>76.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>399000</v>
+        <v>187000</v>
       </c>
       <c r="G36" s="7">
-        <v>31000</v>
+        <v>8000</v>
       </c>
       <c r="H36" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>32750</v>
+        <v>5000</v>
       </c>
       <c r="J36" s="5">
-        <v>65.2</v>
+        <v>67.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>87.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>179000</v>
+        <v>124000</v>
       </c>
       <c r="G37" s="7">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="H37" s="7">
         <v>5</v>
       </c>
       <c r="I37" s="7">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="J37" s="5">
-        <v>65.2</v>
+        <v>67.8</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>88.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>115000</v>
+        <v>105000</v>
       </c>
       <c r="G38" s="7">
-        <v>21000</v>
+        <v>10000</v>
       </c>
       <c r="H38" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>5750</v>
+        <v>8800</v>
       </c>
       <c r="J38" s="5">
-        <v>65.2</v>
+        <v>67.8</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>86</v>
+        <v>89.8</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>110000</v>
+        <v>168000</v>
       </c>
       <c r="G39" s="7">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H39" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I39" s="7">
-        <v>11000</v>
+        <v>600</v>
       </c>
       <c r="J39" s="5">
-        <v>65.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>152000</v>
+        <v>163000</v>
       </c>
       <c r="G40" s="7">
-        <v>12000</v>
+        <v>2000</v>
       </c>
       <c r="H40" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>9750</v>
+        <v>6000</v>
       </c>
       <c r="J40" s="5">
-        <v>64.8</v>
+        <v>67.5</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>77.8</v>
+        <v>84.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>349000</v>
+        <v>152000</v>
       </c>
       <c r="G41" s="7">
-        <v>27000</v>
+        <v>8000</v>
       </c>
       <c r="H41" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I41" s="7">
-        <v>27500</v>
+        <v>11000</v>
       </c>
       <c r="J41" s="5">
-        <v>64.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>87.3</v>
+        <v>89.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>325000</v>
+        <v>205000</v>
       </c>
       <c r="G42" s="7">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="H42" s="7">
         <v>5</v>
       </c>
       <c r="I42" s="7">
-        <v>6250</v>
+        <v>13000</v>
       </c>
       <c r="J42" s="5">
-        <v>64.59999999999999</v>
+        <v>67.3</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>87.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>108000</v>
+        <v>426000</v>
       </c>
       <c r="G43" s="7">
-        <v>3000</v>
+        <v>27000</v>
       </c>
       <c r="H43" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I43" s="7">
-        <v>5500</v>
+        <v>31600</v>
       </c>
       <c r="J43" s="5">
-        <v>64.3</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>85.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>199000</v>
+        <v>265000</v>
       </c>
       <c r="G44" s="7">
-        <v>7000</v>
+        <v>14000</v>
       </c>
       <c r="H44" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I44" s="7">
-        <v>9500</v>
+        <v>19800</v>
       </c>
       <c r="J44" s="5">
-        <v>64.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>87.7</v>
+        <v>76.7</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>140000</v>
+        <v>374000</v>
       </c>
       <c r="G45" s="7">
-        <v>6000</v>
+        <v>25000</v>
       </c>
       <c r="H45" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="7">
-        <v>4000</v>
+        <v>27000</v>
       </c>
       <c r="J45" s="5">
-        <v>64.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>79.5</v>
+        <v>86.7</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>658000</v>
+        <v>325000</v>
       </c>
       <c r="G46" s="7">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="H46" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I46" s="7">
-        <v>21500</v>
+        <v>5000</v>
       </c>
       <c r="J46" s="5">
-        <v>64.09999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>87.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>179000</v>
+        <v>791000</v>
       </c>
       <c r="G47" s="7">
-        <v>6000</v>
+        <v>31000</v>
       </c>
       <c r="H47" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I47" s="7">
-        <v>4250</v>
+        <v>20600</v>
       </c>
       <c r="J47" s="5">
-        <v>64</v>
+        <v>66.8</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>85.40000000000001</v>
+        <v>79.7</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>135000</v>
+        <v>338000</v>
       </c>
       <c r="G48" s="7">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="H48" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I48" s="7">
-        <v>8000</v>
+        <v>19800</v>
       </c>
       <c r="J48" s="5">
-        <v>64</v>
+        <v>66.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>86.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>108000</v>
+        <v>112000</v>
       </c>
       <c r="G49" s="7">
         <v>4000</v>
       </c>
       <c r="H49" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I49" s="7">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="J49" s="5">
-        <v>64</v>
+        <v>66.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>76.5</v>
+        <v>80</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>386000</v>
+        <v>664000</v>
       </c>
       <c r="G50" s="7">
-        <v>25000</v>
+        <v>6000</v>
       </c>
       <c r="H50" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I50" s="7">
-        <v>26500</v>
+        <v>18400</v>
       </c>
       <c r="J50" s="5">
-        <v>63.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.2</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>174000</v>
+        <v>126000</v>
       </c>
       <c r="G51" s="7">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="H51" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I51" s="7">
-        <v>7500</v>
+        <v>7800</v>
       </c>
       <c r="J51" s="5">
-        <v>63.7</v>
+        <v>66.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>90.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>135000</v>
+        <v>180000</v>
       </c>
       <c r="G52" s="7">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="H52" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I52" s="7">
-        <v>6667</v>
+        <v>7200</v>
       </c>
       <c r="J52" s="5">
-        <v>63.4</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>82.5</v>
+        <v>86.3</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>144000</v>
+        <v>143000</v>
       </c>
       <c r="G53" s="7">
-        <v>9000</v>
+        <v>3000</v>
       </c>
       <c r="H53" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I53" s="7">
-        <v>11750</v>
+        <v>3800</v>
       </c>
       <c r="J53" s="5">
-        <v>63.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>79.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>467000</v>
+        <v>137000</v>
       </c>
       <c r="G54" s="7">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H54" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I54" s="7">
-        <v>17750</v>
+        <v>7400</v>
       </c>
       <c r="J54" s="5">
-        <v>63.1</v>
+        <v>66.3</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-19T04:18:55+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-20T04:37:41+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>武侠网游，开局三个神级词条</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>游走神话时代，开局拜师道门天师</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>武侠网游，开局三个神级词条</t>
+    <t>纨绔大少是邪神，眷属全部是美女</t>
+  </si>
+  <si>
+    <t>她未上岸提分手，我结婚她破防了</t>
+  </si>
+  <si>
+    <t>综漫：表白被拒就变强？</t>
+  </si>
+  <si>
+    <t>带着渡劫修为，重回高中时代</t>
+  </si>
+  <si>
+    <t>火影：扉间问谁断后，我当三代！</t>
+  </si>
+  <si>
+    <t>宿舍求生：糯米可镇不住我们太久</t>
+  </si>
+  <si>
+    <t>死刑当天，修仙者夺舍了我</t>
   </si>
   <si>
     <t>点子王行动哥随便弟，三人行很刑</t>
   </si>
   <si>
-    <t>纨绔大少是邪神，眷属全部是美女</t>
+    <t>名义：刚提名省服，你让我退休？</t>
+  </si>
+  <si>
+    <t>人在高中，香火证道什么鬼？</t>
+  </si>
+  <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>白娘子：你不能娶我妹妹小青</t>
+  </si>
+  <si>
+    <t>西游：大圣闹地府！始皇长生啦</t>
+  </si>
+  <si>
+    <t>县城：女友出国要我卖房，给脸了</t>
+  </si>
+  <si>
+    <t>我一写网文的，你让我混娱乐圈？</t>
+  </si>
+  <si>
+    <t>重生八零渔村，带仨前妻赶海暴富</t>
   </si>
   <si>
     <t>凤流高手</t>
   </si>
   <si>
-    <t>系统想害我，我选择上交国家</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>综漫：表白被拒就变强？</t>
-  </si>
-  <si>
-    <t>带着渡劫修为，重回高中时代</t>
-  </si>
-  <si>
-    <t>火影：扉间问谁断后，我当三代！</t>
-  </si>
-  <si>
-    <t>宿舍求生：糯米可镇不住我们太久</t>
-  </si>
-  <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
-    <t>西游：大圣闹地府！始皇长生啦</t>
+    <t>无敌江湖后，我隐退于世</t>
+  </si>
+  <si>
+    <t>祖上十八鬼帝，你让我恐怖求生？</t>
+  </si>
+  <si>
+    <t>三次入伍，我只想退伍进体制</t>
+  </si>
+  <si>
+    <t>惊悚世界，我的小弟有亿点多</t>
+  </si>
+  <si>
+    <t>我都永生了，会亿点技能很合理吧</t>
+  </si>
+  <si>
+    <t>开局魅骨词条，我成了宇智波团宠</t>
+  </si>
+  <si>
+    <t>觉醒伪神，神明弃我，我自为神</t>
+  </si>
+  <si>
+    <t>无声1937</t>
+  </si>
+  <si>
+    <t>灵气复苏？前世女帝老婆也复苏了</t>
+  </si>
+  <si>
+    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
+  </si>
+  <si>
+    <t>聊天群：混沌魔神？万界该溜子</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>退休勇者买下魔王当女仆</t>
+  </si>
+  <si>
+    <t>神女录：开局契约外冷内齁裴玉寒</t>
+  </si>
+  <si>
+    <t>奥特：天蝎座第一道光</t>
   </si>
   <si>
     <t>国运三角洲，开局航天堵桥</t>
   </si>
   <si>
-    <t>人在高中，香火证道什么鬼？</t>
-  </si>
-  <si>
-    <t>我一写网文的，你让我混娱乐圈？</t>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
+    <t>命格通神，我的悟性可以无限叠加</t>
+  </si>
+  <si>
+    <t>诡异世界，我的神通无限升级！</t>
+  </si>
+  <si>
+    <t>打卡双人骑行圈，开局拿捏假名媛</t>
   </si>
   <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
-    <t>死刑当天，修仙者夺舍了我</t>
-  </si>
-  <si>
-    <t>名义：刚提名省服，你让我退休？</t>
-  </si>
-  <si>
-    <t>县城：女友出国要我卖房，给脸了</t>
-  </si>
-  <si>
-    <t>神女录：开局契约外冷内齁裴玉寒</t>
-  </si>
-  <si>
-    <t>末世：我开局拥有一艘驱逐舰</t>
-  </si>
-  <si>
-    <t>她未上岸提分手，我结婚她破防了</t>
-  </si>
-  <si>
-    <t>打卡双人骑行圈，开局拿捏假名媛</t>
-  </si>
-  <si>
-    <t>我都永生了，会亿点技能很合理吧</t>
-  </si>
-  <si>
-    <t>无声1937</t>
+    <t>分手后，她们变得不对劲了！</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>我，暗影君王，拥有亿万召唤兽！</t>
+  </si>
+  <si>
+    <t>斩神师兄太我清道德天尊社恐反差</t>
+  </si>
+  <si>
+    <t>开局九转玄功，我炼体很合理吧？</t>
+  </si>
+  <si>
+    <t>模拟未来：我是叛徒？请世家赴死</t>
+  </si>
+  <si>
+    <t>无职：验牌洛琪希，牌没有问题？</t>
   </si>
   <si>
     <t>飓风战魂：我的陀螺竟是谱尼？！</t>
   </si>
   <si>
-    <t>灵气复苏？前世女帝老婆也复苏了</t>
-  </si>
-  <si>
-    <t>重生八零渔村，带仨前妻赶海暴富</t>
-  </si>
-  <si>
-    <t>命格通神，我的悟性可以无限叠加</t>
-  </si>
-  <si>
-    <t>奥特：天蝎座第一道光</t>
-  </si>
-  <si>
-    <t>全民英雄协会：开局招募一拳光头</t>
-  </si>
-  <si>
-    <t>刚进宗门，就睡出个绝美师尊老婆</t>
-  </si>
-  <si>
-    <t>三次入伍，我只想退伍进体制</t>
-  </si>
-  <si>
-    <t>退休勇者买下魔王当女仆</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
-  </si>
-  <si>
-    <t>分手后，她们变得不对劲了！</t>
-  </si>
-  <si>
-    <t>开局魅骨词条，我成了宇智波团宠</t>
-  </si>
-  <si>
-    <t>玄幻：多管闲事，成人间武圣</t>
-  </si>
-  <si>
-    <t>无职：验牌洛琪希，牌没有问题？</t>
-  </si>
-  <si>
-    <t>惊悚世界，我的小弟有亿点多</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>觉醒伪神，神明弃我，我自为神</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>祖上十八鬼帝，你让我恐怖求生？</t>
-  </si>
-  <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>模拟未来：我是叛徒？请世家赴死</t>
-  </si>
-  <si>
-    <t>重生三岁被捡，成了杨老板亲弟</t>
-  </si>
-  <si>
-    <t>楼层求生：从垃圾场开始变废为宝</t>
-  </si>
-  <si>
-    <t>诡异世界，我的神通无限升级！</t>
+    <t>因为太无敌，我被重生者抢破头？</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>98.2</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>361000</v>
+        <v>313000</v>
       </c>
       <c r="G5" s="7">
-        <v>34000</v>
+        <v>50000</v>
       </c>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="7">
-        <v>38800</v>
+        <v>36000</v>
       </c>
       <c r="J5" s="5">
-        <v>81.7</v>
+        <v>84</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>95.8</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>263000</v>
+        <v>394000</v>
       </c>
       <c r="G6" s="7">
-        <v>21000</v>
+        <v>33000</v>
       </c>
       <c r="H6" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>33200</v>
+        <v>37833</v>
       </c>
       <c r="J6" s="5">
-        <v>79</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>79.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>947000</v>
+        <v>789000</v>
       </c>
       <c r="G7" s="7">
-        <v>11000</v>
+        <v>50000</v>
       </c>
       <c r="H7" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" s="7">
-        <v>54200</v>
+        <v>66250</v>
       </c>
       <c r="J7" s="5">
-        <v>75.2</v>
+        <v>76.3</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>82</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>739000</v>
+        <v>129000</v>
       </c>
       <c r="G8" s="7">
-        <v>63000</v>
+        <v>23000</v>
       </c>
       <c r="H8" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>71667</v>
+        <v>10833</v>
       </c>
       <c r="J8" s="5">
-        <v>75</v>
+        <v>75.7</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>96</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>107000</v>
+        <v>248000</v>
       </c>
       <c r="G9" s="7">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>14600</v>
+        <v>15333</v>
       </c>
       <c r="J9" s="5">
-        <v>74.5</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>82.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>1641000</v>
+        <v>121000</v>
       </c>
       <c r="G10" s="7">
-        <v>28000</v>
+        <v>11000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="7">
-        <v>43000</v>
+        <v>10167</v>
       </c>
       <c r="J10" s="5">
-        <v>74.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>80.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>1622000</v>
+        <v>387000</v>
       </c>
       <c r="G11" s="7">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="H11" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>44200</v>
+        <v>15833</v>
       </c>
       <c r="J11" s="5">
-        <v>73.5</v>
+        <v>73.8</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>94.2</v>
+        <v>92.5</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>228000</v>
+        <v>142000</v>
       </c>
       <c r="G12" s="7">
-        <v>19000</v>
+        <v>12000</v>
       </c>
       <c r="H12" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>14400</v>
+        <v>11667</v>
       </c>
       <c r="J12" s="5">
-        <v>73.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>95</v>
+        <v>85.3</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>110000</v>
+        <v>381000</v>
       </c>
       <c r="G13" s="7">
-        <v>12000</v>
+        <v>29000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>10000</v>
+        <v>27333</v>
       </c>
       <c r="J13" s="5">
-        <v>72.8</v>
+        <v>73.7</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>90</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>377000</v>
+        <v>937000</v>
       </c>
       <c r="G14" s="7">
-        <v>8000</v>
+        <v>-10000</v>
       </c>
       <c r="H14" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>17000</v>
+        <v>43500</v>
       </c>
       <c r="J14" s="5">
-        <v>71.8</v>
+        <v>73.3</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>91.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>130000</v>
+        <v>271000</v>
       </c>
       <c r="G15" s="7">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="H15" s="7">
         <v>6</v>
       </c>
       <c r="I15" s="7">
-        <v>11600</v>
+        <v>19400</v>
       </c>
       <c r="J15" s="5">
-        <v>71.3</v>
+        <v>73.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>81.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>666000</v>
+        <v>226000</v>
       </c>
       <c r="G16" s="7">
-        <v>32000</v>
+        <v>14000</v>
       </c>
       <c r="H16" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I16" s="7">
-        <v>44500</v>
+        <v>11000</v>
       </c>
       <c r="J16" s="5">
-        <v>71.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>89.5</v>
+        <v>80.5</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>165000</v>
+        <v>691000</v>
       </c>
       <c r="G17" s="7">
-        <v>8000</v>
+        <v>25000</v>
       </c>
       <c r="H17" s="7">
         <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>15400</v>
+        <v>40600</v>
       </c>
       <c r="J17" s="5">
-        <v>71.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>92.8</v>
+        <v>79.3</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>101000</v>
+        <v>1607000</v>
       </c>
       <c r="G18" s="7">
-        <v>8000</v>
+        <v>-15000</v>
       </c>
       <c r="H18" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="7">
-        <v>8400</v>
+        <v>34333</v>
       </c>
       <c r="J18" s="5">
-        <v>71.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>91.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>212000</v>
+        <v>107000</v>
       </c>
       <c r="G19" s="7">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="H19" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
-        <v>10400</v>
+        <v>14250</v>
       </c>
       <c r="J19" s="5">
-        <v>71</v>
+        <v>72.2</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>80.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>974000</v>
+        <v>169000</v>
       </c>
       <c r="G20" s="7">
-        <v>17000</v>
+        <v>4000</v>
       </c>
       <c r="H20" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20" s="7">
-        <v>32200</v>
+        <v>13500</v>
       </c>
       <c r="J20" s="5">
-        <v>70.5</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>93.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>410000</v>
+        <v>360000</v>
       </c>
       <c r="G21" s="7">
-        <v>22000</v>
+        <v>38000</v>
       </c>
       <c r="H21" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>3800</v>
+        <v>14667</v>
       </c>
       <c r="J21" s="5">
-        <v>70.5</v>
+        <v>72</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>83.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>352000</v>
+        <v>991000</v>
       </c>
       <c r="G22" s="7">
-        <v>21000</v>
+        <v>17000</v>
       </c>
       <c r="H22" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>27000</v>
+        <v>29667</v>
       </c>
       <c r="J22" s="5">
-        <v>70.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>90.3</v>
+        <v>89.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>257000</v>
+        <v>187000</v>
       </c>
       <c r="G23" s="7">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="H23" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>20750</v>
+        <v>8167</v>
       </c>
       <c r="J23" s="5">
-        <v>69.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>88.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>322000</v>
+        <v>110000</v>
       </c>
       <c r="G24" s="7">
-        <v>42000</v>
+        <v>3000</v>
       </c>
       <c r="H24" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="7">
-        <v>10000</v>
+        <v>12667</v>
       </c>
       <c r="J24" s="5">
-        <v>69.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>90.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>104000</v>
+        <v>120000</v>
       </c>
       <c r="G25" s="7">
         <v>6000</v>
       </c>
       <c r="H25" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>5600</v>
+        <v>5833</v>
       </c>
       <c r="J25" s="5">
-        <v>69.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>88.8</v>
+        <v>89</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>194000</v>
+        <v>118000</v>
       </c>
       <c r="G26" s="7">
         <v>6000</v>
       </c>
       <c r="H26" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" s="7">
-        <v>8400</v>
+        <v>5333</v>
       </c>
       <c r="J26" s="5">
-        <v>68.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>88.5</v>
+        <v>87.3</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>106000</v>
+        <v>115000</v>
       </c>
       <c r="G27" s="7">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="H27" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I27" s="7">
-        <v>8400</v>
+        <v>9000</v>
       </c>
       <c r="J27" s="5">
-        <v>68.8</v>
+        <v>70.3</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>88.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>470000</v>
+        <v>402000</v>
       </c>
       <c r="G28" s="7">
-        <v>1000</v>
+        <v>28000</v>
       </c>
       <c r="H28" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>7800</v>
+        <v>27167</v>
       </c>
       <c r="J28" s="5">
-        <v>68.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>76.90000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>499000</v>
+        <v>522000</v>
       </c>
       <c r="G29" s="7">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="H29" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>33400</v>
+        <v>31667</v>
       </c>
       <c r="J29" s="5">
-        <v>68.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>79.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>435000</v>
+        <v>215000</v>
       </c>
       <c r="G30" s="7">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="H30" s="7">
         <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>27600</v>
+        <v>12400</v>
       </c>
       <c r="J30" s="5">
-        <v>68.59999999999999</v>
+        <v>70</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>87</v>
+        <v>80.2</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>166000</v>
+        <v>822000</v>
       </c>
       <c r="G31" s="7">
-        <v>14000</v>
+        <v>31000</v>
       </c>
       <c r="H31" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" s="7">
-        <v>10600</v>
+        <v>22333</v>
       </c>
       <c r="J31" s="5">
-        <v>68.5</v>
+        <v>69.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>80.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>314000</v>
+        <v>440000</v>
       </c>
       <c r="G32" s="7">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="H32" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I32" s="7">
-        <v>22800</v>
+        <v>23833</v>
       </c>
       <c r="J32" s="5">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>87.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>181000</v>
+        <v>328000</v>
       </c>
       <c r="G33" s="7">
-        <v>3000</v>
+        <v>14000</v>
       </c>
       <c r="H33" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I33" s="7">
-        <v>8600</v>
+        <v>21333</v>
       </c>
       <c r="J33" s="5">
-        <v>68.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>86.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>119000</v>
+        <v>132000</v>
       </c>
       <c r="G34" s="7">
-        <v>9000</v>
+        <v>4000</v>
       </c>
       <c r="H34" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I34" s="7">
-        <v>10600</v>
+        <v>4500</v>
       </c>
       <c r="J34" s="5">
-        <v>68</v>
+        <v>69.5</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>80.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>329000</v>
+        <v>109000</v>
       </c>
       <c r="G35" s="7">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="H35" s="7">
         <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>22200</v>
+        <v>8800</v>
       </c>
       <c r="J35" s="5">
-        <v>67.8</v>
+        <v>69.5</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>88.3</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>187000</v>
+        <v>355000</v>
       </c>
       <c r="G36" s="7">
-        <v>8000</v>
+        <v>17000</v>
       </c>
       <c r="H36" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" s="7">
-        <v>5000</v>
+        <v>19333</v>
       </c>
       <c r="J36" s="5">
-        <v>67.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>91.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>124000</v>
+        <v>173000</v>
       </c>
       <c r="G37" s="7">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="H37" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>9500</v>
+        <v>1333</v>
       </c>
       <c r="J37" s="5">
-        <v>67.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>86.5</v>
+        <v>87.2</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>105000</v>
+        <v>107000</v>
       </c>
       <c r="G38" s="7">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I38" s="7">
-        <v>8800</v>
+        <v>5167</v>
       </c>
       <c r="J38" s="5">
-        <v>67.8</v>
+        <v>69.3</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>89.8</v>
+        <v>80.2</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>168000</v>
+        <v>340000</v>
       </c>
       <c r="G39" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H39" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>600</v>
+        <v>20333</v>
       </c>
       <c r="J39" s="5">
-        <v>67.5</v>
+        <v>69.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>87.3</v>
+        <v>86.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>163000</v>
+        <v>103000</v>
       </c>
       <c r="G40" s="7">
         <v>2000</v>
       </c>
       <c r="H40" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>6000</v>
+        <v>7333</v>
       </c>
       <c r="J40" s="5">
-        <v>67.5</v>
+        <v>69.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>84.8</v>
+        <v>86.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>152000</v>
+        <v>164000</v>
       </c>
       <c r="G41" s="7">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="H41" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41" s="7">
-        <v>11000</v>
+        <v>5167</v>
       </c>
       <c r="J41" s="5">
-        <v>67.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>89.2</v>
+        <v>84.7</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>205000</v>
+        <v>124000</v>
       </c>
       <c r="G42" s="7">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H42" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>13000</v>
+        <v>9667</v>
       </c>
       <c r="J42" s="5">
-        <v>67.3</v>
+        <v>69</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>74.90000000000001</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>426000</v>
+        <v>140000</v>
       </c>
       <c r="G43" s="7">
-        <v>27000</v>
+        <v>3000</v>
       </c>
       <c r="H43" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="7">
-        <v>31600</v>
+        <v>6667</v>
       </c>
       <c r="J43" s="5">
-        <v>67.09999999999999</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>80.2</v>
+        <v>86</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>265000</v>
+        <v>459000</v>
       </c>
       <c r="G44" s="7">
-        <v>14000</v>
+        <v>-11000</v>
       </c>
       <c r="H44" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I44" s="7">
-        <v>19800</v>
+        <v>4667</v>
       </c>
       <c r="J44" s="5">
-        <v>67.09999999999999</v>
+        <v>68.5</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>76.7</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>374000</v>
+        <v>406000</v>
       </c>
       <c r="G45" s="7">
-        <v>25000</v>
+        <v>-4000</v>
       </c>
       <c r="H45" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I45" s="7">
-        <v>27000</v>
+        <v>2500</v>
       </c>
       <c r="J45" s="5">
-        <v>66.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>86.7</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>325000</v>
+        <v>159000</v>
       </c>
       <c r="G46" s="7">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H46" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I46" s="7">
-        <v>5000</v>
+        <v>10333</v>
       </c>
       <c r="J46" s="5">
-        <v>66.90000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>79.40000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>791000</v>
+        <v>1145000</v>
       </c>
       <c r="G47" s="7">
-        <v>31000</v>
+        <v>22000</v>
       </c>
       <c r="H47" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I47" s="7">
-        <v>20600</v>
+        <v>13667</v>
       </c>
       <c r="J47" s="5">
-        <v>66.8</v>
+        <v>68.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>79.7</v>
+        <v>92.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>338000</v>
+        <v>100000</v>
       </c>
       <c r="G48" s="7">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="H48" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I48" s="7">
-        <v>19800</v>
+        <v>8250</v>
       </c>
       <c r="J48" s="5">
-        <v>66.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>86.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>112000</v>
+        <v>197000</v>
       </c>
       <c r="G49" s="7">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H49" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I49" s="7">
-        <v>5200</v>
+        <v>6000</v>
       </c>
       <c r="J49" s="5">
-        <v>66.8</v>
+        <v>67.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>80</v>
+        <v>85.5</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>664000</v>
+        <v>147000</v>
       </c>
       <c r="G50" s="7">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="H50" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I50" s="7">
-        <v>18400</v>
+        <v>3000</v>
       </c>
       <c r="J50" s="5">
-        <v>66.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>84.59999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>126000</v>
+        <v>129000</v>
       </c>
       <c r="G51" s="7">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="H51" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I51" s="7">
-        <v>7800</v>
+        <v>7000</v>
       </c>
       <c r="J51" s="5">
-        <v>66.5</v>
+        <v>67.8</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84.7</v>
+        <v>78.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>180000</v>
+        <v>275000</v>
       </c>
       <c r="G52" s="7">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="H52" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" s="7">
-        <v>7200</v>
+        <v>18167</v>
       </c>
       <c r="J52" s="5">
-        <v>66.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>86.3</v>
+        <v>82.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>143000</v>
+        <v>167000</v>
       </c>
       <c r="G53" s="7">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="H53" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I53" s="7">
-        <v>3800</v>
+        <v>9000</v>
       </c>
       <c r="J53" s="5">
-        <v>66.40000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>84.40000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>137000</v>
+        <v>116000</v>
       </c>
       <c r="G54" s="7">
-        <v>6000</v>
+        <v>19000</v>
       </c>
       <c r="H54" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>7400</v>
+        <v>16333</v>
       </c>
       <c r="J54" s="5">
-        <v>66.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-20T04:37:41+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-21T04:35:39+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -82,145 +82,145 @@
     <t>纨绔大少是邪神，眷属全部是美女</t>
   </si>
   <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>名义：刚提名省服，你让我退休？</t>
+  </si>
+  <si>
+    <t>白娘子：你不能娶我妹妹小青</t>
+  </si>
+  <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>综漫：表白被拒就变强？</t>
+  </si>
+  <si>
+    <t>县城：女友出国要我卖房，给脸了</t>
+  </si>
+  <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
+    <t>死刑当天，修仙者夺舍了我</t>
+  </si>
+  <si>
     <t>她未上岸提分手，我结婚她破防了</t>
   </si>
   <si>
-    <t>综漫：表白被拒就变强？</t>
-  </si>
-  <si>
     <t>带着渡劫修为，重回高中时代</t>
   </si>
   <si>
+    <t>因为太无敌，我被重生者抢破头？</t>
+  </si>
+  <si>
+    <t>聊天群：混沌魔神？万界该溜子</t>
+  </si>
+  <si>
     <t>火影：扉间问谁断后，我当三代！</t>
   </si>
   <si>
+    <t>西游：大圣闹地府！始皇长生啦</t>
+  </si>
+  <si>
+    <t>开局魅骨词条，我成了宇智波团宠</t>
+  </si>
+  <si>
     <t>宿舍求生：糯米可镇不住我们太久</t>
   </si>
   <si>
-    <t>死刑当天，修仙者夺舍了我</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>名义：刚提名省服，你让我退休？</t>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>我一写网文的，你让我混娱乐圈？</t>
   </si>
   <si>
     <t>人在高中，香火证道什么鬼？</t>
   </si>
   <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>白娘子：你不能娶我妹妹小青</t>
-  </si>
-  <si>
-    <t>西游：大圣闹地府！始皇长生啦</t>
-  </si>
-  <si>
-    <t>县城：女友出国要我卖房，给脸了</t>
-  </si>
-  <si>
-    <t>我一写网文的，你让我混娱乐圈？</t>
+    <t>祖上十八鬼帝，你让我恐怖求生？</t>
+  </si>
+  <si>
+    <t>凤流高手</t>
+  </si>
+  <si>
+    <t>觉醒伪神，神明弃我，我自为神</t>
+  </si>
+  <si>
+    <t>惊悚世界，我的小弟有亿点多</t>
+  </si>
+  <si>
+    <t>无声1937</t>
+  </si>
+  <si>
+    <t>海洋求生，上船两个要求，大萝莉</t>
+  </si>
+  <si>
+    <t>一毛一天修为，我靠直播氪穿宇宙</t>
   </si>
   <si>
     <t>重生八零渔村，带仨前妻赶海暴富</t>
   </si>
   <si>
-    <t>凤流高手</t>
-  </si>
-  <si>
-    <t>无敌江湖后，我隐退于世</t>
-  </si>
-  <si>
-    <t>祖上十八鬼帝，你让我恐怖求生？</t>
+    <t>我都永生了，会亿点技能很合理吧</t>
+  </si>
+  <si>
+    <t>奥特：天蝎座第一道光</t>
+  </si>
+  <si>
+    <t>三角洲：手游主播的我误入巅峰赛</t>
+  </si>
+  <si>
+    <t>灵气复苏？前世女帝老婆也复苏了</t>
+  </si>
+  <si>
+    <t>退休勇者买下魔王当女仆</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
   </si>
   <si>
     <t>三次入伍，我只想退伍进体制</t>
   </si>
   <si>
-    <t>惊悚世界，我的小弟有亿点多</t>
-  </si>
-  <si>
-    <t>我都永生了，会亿点技能很合理吧</t>
-  </si>
-  <si>
-    <t>开局魅骨词条，我成了宇智波团宠</t>
-  </si>
-  <si>
-    <t>觉醒伪神，神明弃我，我自为神</t>
-  </si>
-  <si>
-    <t>无声1937</t>
-  </si>
-  <si>
-    <t>灵气复苏？前世女帝老婆也复苏了</t>
-  </si>
-  <si>
-    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
-  </si>
-  <si>
-    <t>聊天群：混沌魔神？万界该溜子</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>退休勇者买下魔王当女仆</t>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>玄幻：多管闲事，成人间武圣</t>
+  </si>
+  <si>
+    <t>开了无敌秒杀外挂的我横推多元</t>
+  </si>
+  <si>
+    <t>飓风战魂：我的陀螺竟是谱尼？！</t>
+  </si>
+  <si>
+    <t>开局九转玄功，我炼体很合理吧？</t>
+  </si>
+  <si>
+    <t>模拟未来：我是叛徒？请世家赴死</t>
+  </si>
+  <si>
+    <t>国运三角洲，开局航天堵桥</t>
+  </si>
+  <si>
+    <t>从金丹仙族开始的老祖之路！</t>
   </si>
   <si>
     <t>神女录：开局契约外冷内齁裴玉寒</t>
   </si>
   <si>
-    <t>奥特：天蝎座第一道光</t>
-  </si>
-  <si>
-    <t>国运三角洲，开局航天堵桥</t>
+    <t>诡异世界，我的神通无限升级！</t>
+  </si>
+  <si>
+    <t>穿越黄毛，女主们把我当白月光了</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
   </si>
   <si>
     <t>要当总统了，你跟我说系统来了？</t>
-  </si>
-  <si>
-    <t>命格通神，我的悟性可以无限叠加</t>
-  </si>
-  <si>
-    <t>诡异世界，我的神通无限升级！</t>
-  </si>
-  <si>
-    <t>打卡双人骑行圈，开局拿捏假名媛</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>分手后，她们变得不对劲了！</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>我，暗影君王，拥有亿万召唤兽！</t>
-  </si>
-  <si>
-    <t>斩神师兄太我清道德天尊社恐反差</t>
-  </si>
-  <si>
-    <t>开局九转玄功，我炼体很合理吧？</t>
-  </si>
-  <si>
-    <t>模拟未来：我是叛徒？请世家赴死</t>
-  </si>
-  <si>
-    <t>无职：验牌洛琪希，牌没有问题？</t>
-  </si>
-  <si>
-    <t>飓风战魂：我的陀螺竟是谱尼？！</t>
-  </si>
-  <si>
-    <t>因为太无敌，我被重生者抢破头？</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>313000</v>
+        <v>347000</v>
       </c>
       <c r="G5" s="7">
-        <v>50000</v>
+        <v>34000</v>
       </c>
       <c r="H5" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>36000</v>
+        <v>35714</v>
       </c>
       <c r="J5" s="5">
-        <v>84</v>
+        <v>83.2</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>97.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>394000</v>
+        <v>425000</v>
       </c>
       <c r="G6" s="7">
-        <v>33000</v>
+        <v>31000</v>
       </c>
       <c r="H6" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="7">
-        <v>37833</v>
+        <v>36857</v>
       </c>
       <c r="J6" s="5">
-        <v>82.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>81.3</v>
+        <v>80.5</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>789000</v>
+        <v>829000</v>
       </c>
       <c r="G7" s="7">
-        <v>50000</v>
+        <v>40000</v>
       </c>
       <c r="H7" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="7">
-        <v>66250</v>
+        <v>61000</v>
       </c>
       <c r="J7" s="5">
-        <v>76.3</v>
+        <v>77.5</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>96.40000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>129000</v>
+        <v>114000</v>
       </c>
       <c r="G8" s="7">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="H8" s="7">
         <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>10833</v>
+        <v>13833</v>
       </c>
       <c r="J8" s="5">
-        <v>75.7</v>
+        <v>77.2</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>94.09999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>248000</v>
+        <v>290000</v>
       </c>
       <c r="G9" s="7">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="H9" s="7">
         <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>15333</v>
+        <v>19333</v>
       </c>
       <c r="J9" s="5">
-        <v>75.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>94.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>121000</v>
+        <v>122000</v>
       </c>
       <c r="G10" s="7">
-        <v>11000</v>
+        <v>15000</v>
       </c>
       <c r="H10" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>10167</v>
+        <v>14400</v>
       </c>
       <c r="J10" s="5">
-        <v>74.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>90.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>387000</v>
+        <v>966000</v>
       </c>
       <c r="G11" s="7">
-        <v>10000</v>
+        <v>29000</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I11" s="7">
-        <v>15833</v>
+        <v>41429</v>
       </c>
       <c r="J11" s="5">
-        <v>73.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>92.5</v>
+        <v>92.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>142000</v>
+        <v>264000</v>
       </c>
       <c r="G12" s="7">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" s="7">
-        <v>11667</v>
+        <v>15429</v>
       </c>
       <c r="J12" s="5">
-        <v>73.8</v>
+        <v>74.8</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>85.3</v>
+        <v>89.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>381000</v>
+        <v>411000</v>
       </c>
       <c r="G13" s="7">
-        <v>29000</v>
+        <v>51000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>27333</v>
+        <v>19857</v>
       </c>
       <c r="J13" s="5">
-        <v>73.7</v>
+        <v>74.3</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>77.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>937000</v>
+        <v>715000</v>
       </c>
       <c r="G14" s="7">
-        <v>-10000</v>
+        <v>24000</v>
       </c>
       <c r="H14" s="7">
         <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>43500</v>
+        <v>37833</v>
       </c>
       <c r="J14" s="5">
-        <v>73.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>91.8</v>
+        <v>84.8</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>271000</v>
+        <v>410000</v>
       </c>
       <c r="G15" s="7">
-        <v>14000</v>
+        <v>29000</v>
       </c>
       <c r="H15" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>19400</v>
+        <v>27571</v>
       </c>
       <c r="J15" s="5">
-        <v>73.3</v>
+        <v>73.5</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>90.90000000000001</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>226000</v>
+        <v>144000</v>
       </c>
       <c r="G16" s="7">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="H16" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I16" s="7">
-        <v>11000</v>
+        <v>11429</v>
       </c>
       <c r="J16" s="5">
-        <v>72.7</v>
+        <v>73.2</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>80.5</v>
+        <v>92.2</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>691000</v>
+        <v>130000</v>
       </c>
       <c r="G17" s="7">
-        <v>25000</v>
+        <v>9000</v>
       </c>
       <c r="H17" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>40600</v>
+        <v>10000</v>
       </c>
       <c r="J17" s="5">
-        <v>72.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>79.3</v>
+        <v>96.5</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>1607000</v>
+        <v>134000</v>
       </c>
       <c r="G18" s="7">
-        <v>-15000</v>
+        <v>18000</v>
       </c>
       <c r="H18" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I18" s="7">
-        <v>34333</v>
+        <v>16750</v>
       </c>
       <c r="J18" s="5">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,23 +1221,23 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>97.59999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>107000</v>
+        <v>121000</v>
       </c>
       <c r="G19" s="7">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="H19" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>14250</v>
+        <v>9333</v>
       </c>
       <c r="J19" s="5">
         <v>72.2</v>
@@ -1254,23 +1254,23 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>88.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>169000</v>
+        <v>389000</v>
       </c>
       <c r="G20" s="7">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H20" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" s="7">
-        <v>13500</v>
+        <v>13857</v>
       </c>
       <c r="J20" s="5">
         <v>72.09999999999999</v>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>87.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>360000</v>
+        <v>174000</v>
       </c>
       <c r="G21" s="7">
-        <v>38000</v>
+        <v>5000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>14667</v>
+        <v>12286</v>
       </c>
       <c r="J21" s="5">
-        <v>72</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>80.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>991000</v>
+        <v>223000</v>
       </c>
       <c r="G22" s="7">
-        <v>17000</v>
+        <v>8000</v>
       </c>
       <c r="H22" s="7">
         <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>29667</v>
+        <v>11667</v>
       </c>
       <c r="J22" s="5">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>89.7</v>
+        <v>88.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>187000</v>
+        <v>152000</v>
       </c>
       <c r="G23" s="7">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I23" s="7">
-        <v>8167</v>
+        <v>11429</v>
       </c>
       <c r="J23" s="5">
-        <v>71.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>86.3</v>
+        <v>80.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>110000</v>
+        <v>1607000</v>
       </c>
       <c r="G24" s="7">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H24" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I24" s="7">
-        <v>12667</v>
+        <v>29429</v>
       </c>
       <c r="J24" s="5">
-        <v>70.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>120000</v>
+        <v>1005000</v>
       </c>
       <c r="G25" s="7">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I25" s="7">
-        <v>5833</v>
+        <v>27429</v>
       </c>
       <c r="J25" s="5">
-        <v>70.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>89</v>
+        <v>87.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>118000</v>
+        <v>232000</v>
       </c>
       <c r="G26" s="7">
         <v>6000</v>
       </c>
       <c r="H26" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>5333</v>
+        <v>10286</v>
       </c>
       <c r="J26" s="5">
-        <v>70.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>87.3</v>
+        <v>89.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>115000</v>
+        <v>125000</v>
       </c>
       <c r="G27" s="7">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="H27" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I27" s="7">
-        <v>9000</v>
+        <v>5571</v>
       </c>
       <c r="J27" s="5">
-        <v>70.3</v>
+        <v>70.8</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>78.8</v>
+        <v>86.3</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>402000</v>
+        <v>113000</v>
       </c>
       <c r="G28" s="7">
-        <v>28000</v>
+        <v>3000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>27167</v>
+        <v>11286</v>
       </c>
       <c r="J28" s="5">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,23 +1551,23 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>76.5</v>
+        <v>80.2</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>522000</v>
+        <v>854000</v>
       </c>
       <c r="G29" s="7">
-        <v>23000</v>
+        <v>32000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>31667</v>
+        <v>23714</v>
       </c>
       <c r="J29" s="5">
         <v>70</v>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89</v>
+        <v>78.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>215000</v>
+        <v>429000</v>
       </c>
       <c r="G30" s="7">
-        <v>10000</v>
+        <v>27000</v>
       </c>
       <c r="H30" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I30" s="7">
-        <v>12400</v>
+        <v>27143</v>
       </c>
       <c r="J30" s="5">
-        <v>70</v>
+        <v>69.8</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,23 +1617,23 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>80.2</v>
+        <v>80.5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>822000</v>
+        <v>450000</v>
       </c>
       <c r="G31" s="7">
-        <v>31000</v>
+        <v>10000</v>
       </c>
       <c r="H31" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" s="7">
-        <v>22333</v>
+        <v>21857</v>
       </c>
       <c r="J31" s="5">
         <v>69.7</v>
@@ -1650,23 +1650,23 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>79.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>440000</v>
+        <v>146000</v>
       </c>
       <c r="G32" s="7">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H32" s="7">
         <v>7</v>
       </c>
       <c r="I32" s="7">
-        <v>23833</v>
+        <v>5167</v>
       </c>
       <c r="J32" s="5">
         <v>69.59999999999999</v>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>80.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>328000</v>
+        <v>137000</v>
       </c>
       <c r="G33" s="7">
-        <v>14000</v>
+        <v>7000</v>
       </c>
       <c r="H33" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I33" s="7">
-        <v>21333</v>
+        <v>4857</v>
       </c>
       <c r="J33" s="5">
-        <v>69.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>87.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>132000</v>
+        <v>187000</v>
       </c>
       <c r="G34" s="7">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="H34" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I34" s="7">
-        <v>4500</v>
+        <v>7000</v>
       </c>
       <c r="J34" s="5">
-        <v>69.5</v>
+        <v>69.3</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>89.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>109000</v>
+        <v>539000</v>
       </c>
       <c r="G35" s="7">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="H35" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I35" s="7">
-        <v>8800</v>
+        <v>29571</v>
       </c>
       <c r="J35" s="5">
-        <v>69.5</v>
+        <v>69.2</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>81.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>355000</v>
+        <v>353000</v>
       </c>
       <c r="G36" s="7">
-        <v>17000</v>
+        <v>13000</v>
       </c>
       <c r="H36" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>19333</v>
+        <v>19286</v>
       </c>
       <c r="J36" s="5">
-        <v>69.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>89.2</v>
+        <v>96.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>173000</v>
+        <v>101000</v>
       </c>
       <c r="G37" s="7">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="H37" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I37" s="7">
-        <v>1333</v>
+        <v>15000</v>
       </c>
       <c r="J37" s="5">
-        <v>69.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>87.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>107000</v>
+        <v>340000</v>
       </c>
       <c r="G38" s="7">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="H38" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I38" s="7">
-        <v>5167</v>
+        <v>20000</v>
       </c>
       <c r="J38" s="5">
-        <v>69.3</v>
+        <v>68.8</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>80.2</v>
+        <v>88</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>340000</v>
+        <v>176000</v>
       </c>
       <c r="G39" s="7">
-        <v>11000</v>
+        <v>3000</v>
       </c>
       <c r="H39" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I39" s="7">
-        <v>20333</v>
+        <v>1571</v>
       </c>
       <c r="J39" s="5">
-        <v>69.2</v>
+        <v>68.8</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>103000</v>
+        <v>369000</v>
       </c>
       <c r="G40" s="7">
-        <v>2000</v>
+        <v>14000</v>
       </c>
       <c r="H40" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I40" s="7">
-        <v>7333</v>
+        <v>18571</v>
       </c>
       <c r="J40" s="5">
-        <v>69.2</v>
+        <v>68.7</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>86.7</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>164000</v>
+        <v>123000</v>
       </c>
       <c r="G41" s="7">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="H41" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I41" s="7">
-        <v>5167</v>
+        <v>8857</v>
       </c>
       <c r="J41" s="5">
-        <v>69</v>
+        <v>68.5</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>84.7</v>
+        <v>81.3</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>124000</v>
+        <v>1166000</v>
       </c>
       <c r="G42" s="7">
-        <v>5000</v>
+        <v>21000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I42" s="7">
-        <v>9667</v>
+        <v>14714</v>
       </c>
       <c r="J42" s="5">
-        <v>69</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>85.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>140000</v>
+        <v>468000</v>
       </c>
       <c r="G43" s="7">
-        <v>3000</v>
+        <v>19000</v>
       </c>
       <c r="H43" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" s="7">
-        <v>6667</v>
+        <v>28571</v>
       </c>
       <c r="J43" s="5">
-        <v>68.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86</v>
+        <v>86.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>459000</v>
+        <v>120000</v>
       </c>
       <c r="G44" s="7">
-        <v>-11000</v>
+        <v>9000</v>
       </c>
       <c r="H44" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I44" s="7">
-        <v>4667</v>
+        <v>9800</v>
       </c>
       <c r="J44" s="5">
-        <v>68.5</v>
+        <v>68.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>87.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>406000</v>
+        <v>169000</v>
       </c>
       <c r="G45" s="7">
-        <v>-4000</v>
+        <v>2000</v>
       </c>
       <c r="H45" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I45" s="7">
-        <v>2500</v>
+        <v>8000</v>
       </c>
       <c r="J45" s="5">
-        <v>68.5</v>
+        <v>67.8</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>83.09999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>159000</v>
+        <v>149000</v>
       </c>
       <c r="G46" s="7">
-        <v>7000</v>
+        <v>2000</v>
       </c>
       <c r="H46" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I46" s="7">
-        <v>10333</v>
+        <v>2857</v>
       </c>
       <c r="J46" s="5">
-        <v>68.3</v>
+        <v>67.8</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>81.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>1145000</v>
+        <v>133000</v>
       </c>
       <c r="G47" s="7">
-        <v>22000</v>
+        <v>4000</v>
       </c>
       <c r="H47" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I47" s="7">
-        <v>13667</v>
+        <v>6571</v>
       </c>
       <c r="J47" s="5">
-        <v>68.2</v>
+        <v>67.7</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>92.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>100000</v>
+        <v>104000</v>
       </c>
       <c r="G48" s="7">
-        <v>16000</v>
+        <v>1000</v>
       </c>
       <c r="H48" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I48" s="7">
-        <v>8250</v>
+        <v>6429</v>
       </c>
       <c r="J48" s="5">
-        <v>67.90000000000001</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>84.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>197000</v>
+        <v>671000</v>
       </c>
       <c r="G49" s="7">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="H49" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I49" s="7">
-        <v>6000</v>
+        <v>14143</v>
       </c>
       <c r="J49" s="5">
-        <v>67.8</v>
+        <v>67.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>85.5</v>
+        <v>84.3</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>147000</v>
+        <v>107000</v>
       </c>
       <c r="G50" s="7">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="H50" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I50" s="7">
-        <v>3000</v>
+        <v>4429</v>
       </c>
       <c r="J50" s="5">
-        <v>67.8</v>
+        <v>67.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>83.8</v>
+        <v>83.2</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>129000</v>
+        <v>140000</v>
       </c>
       <c r="G51" s="7">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H51" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51" s="7">
-        <v>7000</v>
+        <v>5714</v>
       </c>
       <c r="J51" s="5">
-        <v>67.8</v>
+        <v>67.2</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>78.5</v>
+        <v>83.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>275000</v>
+        <v>142000</v>
       </c>
       <c r="G52" s="7">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="H52" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I52" s="7">
-        <v>18167</v>
+        <v>4429</v>
       </c>
       <c r="J52" s="5">
-        <v>67.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>82.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>167000</v>
+        <v>253000</v>
       </c>
       <c r="G53" s="7">
-        <v>1000</v>
+        <v>21000</v>
       </c>
       <c r="H53" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I53" s="7">
-        <v>9000</v>
+        <v>3857</v>
       </c>
       <c r="J53" s="5">
-        <v>67.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>93.7</v>
+        <v>83</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>116000</v>
+        <v>159000</v>
       </c>
       <c r="G54" s="7">
-        <v>19000</v>
+        <v>-5000</v>
       </c>
       <c r="H54" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I54" s="7">
-        <v>16333</v>
+        <v>3714</v>
       </c>
       <c r="J54" s="5">
-        <v>67.59999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-21T04:35:39+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-22T04:31:43+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>纨绔大少是邪神，眷属全部是美女</t>
+  </si>
+  <si>
+    <t>白娘子：你不能娶我妹妹小青</t>
+  </si>
+  <si>
     <t>游走神话时代，开局拜师道门天师</t>
   </si>
   <si>
-    <t>纨绔大少是邪神，眷属全部是美女</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
+    <t>衰神气运逆转，回老家享受生活</t>
+  </si>
+  <si>
+    <t>凤流高手</t>
+  </si>
+  <si>
+    <t>死刑当天，修仙者夺舍了我</t>
   </si>
   <si>
     <t>名义：刚提名省服，你让我退休？</t>
   </si>
   <si>
-    <t>白娘子：你不能娶我妹妹小青</t>
+    <t>综漫：表白被拒就变强？</t>
   </si>
   <si>
     <t>点子王行动哥随便弟，三人行很刑</t>
   </si>
   <si>
-    <t>综漫：表白被拒就变强？</t>
+    <t>全民领主：我的兵营来自战锤</t>
+  </si>
+  <si>
+    <t>带着渡劫修为，重回高中时代</t>
+  </si>
+  <si>
+    <t>全民英雄协会：开局招募一拳光头</t>
+  </si>
+  <si>
+    <t>她未上岸提分手，我结婚她破防了</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>聊天群：混沌魔神？万界该溜子</t>
+  </si>
+  <si>
+    <t>重生八零渔村，带仨前妻赶海暴富</t>
+  </si>
+  <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
   </si>
   <si>
     <t>县城：女友出国要我卖房，给脸了</t>
   </si>
   <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
-    <t>死刑当天，修仙者夺舍了我</t>
-  </si>
-  <si>
-    <t>她未上岸提分手，我结婚她破防了</t>
-  </si>
-  <si>
-    <t>带着渡劫修为，重回高中时代</t>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>宿舍求生：糯米可镇不住我们太久</t>
   </si>
   <si>
     <t>因为太无敌，我被重生者抢破头？</t>
   </si>
   <si>
-    <t>聊天群：混沌魔神？万界该溜子</t>
-  </si>
-  <si>
-    <t>火影：扉间问谁断后，我当三代！</t>
+    <t>三角洲：手游主播的我误入巅峰赛</t>
+  </si>
+  <si>
+    <t>名义：谁还不是个汉大帮</t>
+  </si>
+  <si>
+    <t>美恐：天真珈百璃，正在开始狩猎</t>
+  </si>
+  <si>
+    <t>海洋求生，上船两个要求，大萝莉</t>
+  </si>
+  <si>
+    <t>惊悚世界，我的小弟有亿点多</t>
   </si>
   <si>
     <t>西游：大圣闹地府！始皇长生啦</t>
   </si>
   <si>
-    <t>开局魅骨词条，我成了宇智波团宠</t>
-  </si>
-  <si>
-    <t>宿舍求生：糯米可镇不住我们太久</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
+    <t>机甲武神：从矿星开始</t>
   </si>
   <si>
     <t>我一写网文的，你让我混娱乐圈？</t>
   </si>
   <si>
-    <t>人在高中，香火证道什么鬼？</t>
-  </si>
-  <si>
     <t>祖上十八鬼帝，你让我恐怖求生？</t>
   </si>
   <si>
-    <t>凤流高手</t>
+    <t>三次入伍，我只想退伍进体制</t>
+  </si>
+  <si>
+    <t>无声1937</t>
   </si>
   <si>
     <t>觉醒伪神，神明弃我，我自为神</t>
   </si>
   <si>
-    <t>惊悚世界，我的小弟有亿点多</t>
-  </si>
-  <si>
-    <t>无声1937</t>
-  </si>
-  <si>
-    <t>海洋求生，上船两个要求，大萝莉</t>
+    <t>植物大战僵尸恐怖版开局获得电大</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>我，暗影君王，拥有亿万召唤兽！</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
+  </si>
+  <si>
+    <t>不会踢球？却成了足球巨星！</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
+  </si>
+  <si>
+    <t>诡异世界，我的神通无限升级！</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>老师，男生也能报考魔女学院吗？</t>
   </si>
   <si>
     <t>一毛一天修为，我靠直播氪穿宇宙</t>
   </si>
   <si>
-    <t>重生八零渔村，带仨前妻赶海暴富</t>
+    <t>奥特：天蝎座第一道光</t>
+  </si>
+  <si>
+    <t>飓风战魂：我的陀螺竟是谱尼？！</t>
+  </si>
+  <si>
+    <t>穿越黄毛，女主们把我当白月光了</t>
   </si>
   <si>
     <t>我都永生了，会亿点技能很合理吧</t>
   </si>
   <si>
-    <t>奥特：天蝎座第一道光</t>
-  </si>
-  <si>
-    <t>三角洲：手游主播的我误入巅峰赛</t>
-  </si>
-  <si>
     <t>灵气复苏？前世女帝老婆也复苏了</t>
-  </si>
-  <si>
-    <t>退休勇者买下魔王当女仆</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>三次入伍，我只想退伍进体制</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>玄幻：多管闲事，成人间武圣</t>
-  </si>
-  <si>
-    <t>开了无敌秒杀外挂的我横推多元</t>
-  </si>
-  <si>
-    <t>飓风战魂：我的陀螺竟是谱尼？！</t>
-  </si>
-  <si>
-    <t>开局九转玄功，我炼体很合理吧？</t>
-  </si>
-  <si>
-    <t>模拟未来：我是叛徒？请世家赴死</t>
-  </si>
-  <si>
-    <t>国运三角洲，开局航天堵桥</t>
-  </si>
-  <si>
-    <t>从金丹仙族开始的老祖之路！</t>
-  </si>
-  <si>
-    <t>神女录：开局契约外冷内齁裴玉寒</t>
-  </si>
-  <si>
-    <t>诡异世界，我的神通无限升级！</t>
-  </si>
-  <si>
-    <t>穿越黄毛，女主们把我当白月光了</t>
-  </si>
-  <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>98.59999999999999</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>347000</v>
+        <v>374000</v>
       </c>
       <c r="G5" s="7">
-        <v>34000</v>
+        <v>27000</v>
       </c>
       <c r="H5" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="7">
-        <v>35714</v>
+        <v>34625</v>
       </c>
       <c r="J5" s="5">
-        <v>83.2</v>
+        <v>81.2</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>96</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>425000</v>
+        <v>139000</v>
       </c>
       <c r="G6" s="7">
-        <v>31000</v>
+        <v>25000</v>
       </c>
       <c r="H6" s="7">
         <v>8</v>
       </c>
       <c r="I6" s="7">
-        <v>36857</v>
+        <v>15429</v>
       </c>
       <c r="J6" s="5">
-        <v>82</v>
+        <v>78.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>80.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>829000</v>
+        <v>867000</v>
       </c>
       <c r="G7" s="7">
-        <v>40000</v>
+        <v>38000</v>
       </c>
       <c r="H7" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>61000</v>
+        <v>57167</v>
       </c>
       <c r="J7" s="5">
-        <v>77.5</v>
+        <v>78.3</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>97.8</v>
+        <v>98</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>114000</v>
+        <v>137000</v>
       </c>
       <c r="G8" s="7">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="H8" s="7">
         <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>13833</v>
+        <v>14500</v>
       </c>
       <c r="J8" s="5">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>94.3</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>290000</v>
+        <v>427000</v>
       </c>
       <c r="G9" s="7">
-        <v>19000</v>
+        <v>2000</v>
       </c>
       <c r="H9" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7">
-        <v>19333</v>
+        <v>32500</v>
       </c>
       <c r="J9" s="5">
-        <v>76.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>122000</v>
+        <v>217000</v>
       </c>
       <c r="G10" s="7">
-        <v>15000</v>
+        <v>55000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I10" s="7">
-        <v>14400</v>
+        <v>51500</v>
       </c>
       <c r="J10" s="5">
-        <v>75.40000000000001</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>81.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>966000</v>
+        <v>126000</v>
       </c>
       <c r="G11" s="7">
-        <v>29000</v>
+        <v>13000</v>
       </c>
       <c r="H11" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="7">
-        <v>41429</v>
+        <v>11500</v>
       </c>
       <c r="J11" s="5">
-        <v>75.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>92.7</v>
+        <v>86.8</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>264000</v>
+        <v>445000</v>
       </c>
       <c r="G12" s="7">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="H12" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I12" s="7">
-        <v>15429</v>
+        <v>28500</v>
       </c>
       <c r="J12" s="5">
-        <v>74.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>89.7</v>
+        <v>90.5</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>411000</v>
+        <v>299000</v>
       </c>
       <c r="G13" s="7">
-        <v>51000</v>
+        <v>9000</v>
       </c>
       <c r="H13" s="7">
         <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>19857</v>
+        <v>17857</v>
       </c>
       <c r="J13" s="5">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>80.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>715000</v>
+        <v>276000</v>
       </c>
       <c r="G14" s="7">
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I14" s="7">
-        <v>37833</v>
+        <v>15000</v>
       </c>
       <c r="J14" s="5">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>84.8</v>
+        <v>79.5</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>410000</v>
+        <v>978000</v>
       </c>
       <c r="G15" s="7">
-        <v>29000</v>
+        <v>12000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7">
-        <v>27571</v>
+        <v>37750</v>
       </c>
       <c r="J15" s="5">
-        <v>73.5</v>
+        <v>73.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,23 +1122,23 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>91.59999999999999</v>
+        <v>96.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>144000</v>
+        <v>133000</v>
       </c>
       <c r="G16" s="7">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H16" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I16" s="7">
-        <v>11429</v>
+        <v>8600</v>
       </c>
       <c r="J16" s="5">
         <v>73.2</v>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>92.2</v>
+        <v>91.8</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>130000</v>
+        <v>139000</v>
       </c>
       <c r="G17" s="7">
         <v>9000</v>
       </c>
       <c r="H17" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="7">
-        <v>10000</v>
+        <v>9875</v>
       </c>
       <c r="J17" s="5">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>96.5</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>134000</v>
+        <v>192000</v>
       </c>
       <c r="G18" s="7">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="H18" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7">
-        <v>16750</v>
+        <v>3750</v>
       </c>
       <c r="J18" s="5">
-        <v>72.3</v>
+        <v>72.7</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>90.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>121000</v>
+        <v>153000</v>
       </c>
       <c r="G19" s="7">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="H19" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I19" s="7">
-        <v>9333</v>
+        <v>11125</v>
       </c>
       <c r="J19" s="5">
-        <v>72.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>88.5</v>
+        <v>82</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>389000</v>
+        <v>1635000</v>
       </c>
       <c r="G20" s="7">
-        <v>2000</v>
+        <v>28000</v>
       </c>
       <c r="H20" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>13857</v>
+        <v>29250</v>
       </c>
       <c r="J20" s="5">
-        <v>72.09999999999999</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89.2</v>
+        <v>90.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>174000</v>
+        <v>134000</v>
       </c>
       <c r="G21" s="7">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="H21" s="7">
         <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>12286</v>
+        <v>9857</v>
       </c>
       <c r="J21" s="5">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>88.8</v>
+        <v>91.3</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>223000</v>
+        <v>196000</v>
       </c>
       <c r="G22" s="7">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="H22" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I22" s="7">
-        <v>11667</v>
+        <v>7250</v>
       </c>
       <c r="J22" s="5">
-        <v>71.8</v>
+        <v>72</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88.8</v>
+        <v>78.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>152000</v>
+        <v>729000</v>
       </c>
       <c r="G23" s="7">
-        <v>10000</v>
+        <v>14000</v>
       </c>
       <c r="H23" s="7">
         <v>8</v>
       </c>
       <c r="I23" s="7">
-        <v>11429</v>
+        <v>34429</v>
       </c>
       <c r="J23" s="5">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>80.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>1607000</v>
+        <v>440000</v>
       </c>
       <c r="G24" s="7">
-        <v>0</v>
+        <v>29000</v>
       </c>
       <c r="H24" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" s="7">
-        <v>29429</v>
+        <v>21000</v>
       </c>
       <c r="J24" s="5">
-        <v>71.5</v>
+        <v>71.7</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>80.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>1005000</v>
+        <v>333000</v>
       </c>
       <c r="G25" s="7">
-        <v>14000</v>
+        <v>41000</v>
       </c>
       <c r="H25" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I25" s="7">
-        <v>27429</v>
+        <v>14750</v>
       </c>
       <c r="J25" s="5">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>87.8</v>
+        <v>88.3</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>232000</v>
+        <v>158000</v>
       </c>
       <c r="G26" s="7">
         <v>6000</v>
       </c>
       <c r="H26" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I26" s="7">
-        <v>10286</v>
+        <v>10750</v>
       </c>
       <c r="J26" s="5">
-        <v>70.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>125000</v>
+        <v>144000</v>
       </c>
       <c r="G27" s="7">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="H27" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I27" s="7">
-        <v>5571</v>
+        <v>15400</v>
       </c>
       <c r="J27" s="5">
-        <v>70.8</v>
+        <v>71.3</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>86.3</v>
+        <v>95.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
@@ -1528,16 +1528,16 @@
         <v>113000</v>
       </c>
       <c r="G28" s="7">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I28" s="7">
-        <v>11286</v>
+        <v>14250</v>
       </c>
       <c r="J28" s="5">
-        <v>70.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>80.2</v>
+        <v>88</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>854000</v>
+        <v>174000</v>
       </c>
       <c r="G29" s="7">
-        <v>32000</v>
+        <v>11000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>23714</v>
+        <v>9667</v>
       </c>
       <c r="J29" s="5">
-        <v>70</v>
+        <v>70.8</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>78.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>429000</v>
+        <v>108000</v>
       </c>
       <c r="G30" s="7">
-        <v>27000</v>
+        <v>13000</v>
       </c>
       <c r="H30" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>27143</v>
+        <v>9750</v>
       </c>
       <c r="J30" s="5">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>80.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>450000</v>
+        <v>154000</v>
       </c>
       <c r="G31" s="7">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="H31" s="7">
         <v>8</v>
       </c>
       <c r="I31" s="7">
-        <v>21857</v>
+        <v>5571</v>
       </c>
       <c r="J31" s="5">
-        <v>69.7</v>
+        <v>70.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>87.8</v>
+        <v>78.8</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>146000</v>
+        <v>456000</v>
       </c>
       <c r="G32" s="7">
-        <v>4000</v>
+        <v>27000</v>
       </c>
       <c r="H32" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I32" s="7">
-        <v>5167</v>
+        <v>27125</v>
       </c>
       <c r="J32" s="5">
-        <v>69.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>87.7</v>
+        <v>86.2</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>137000</v>
+        <v>174000</v>
       </c>
       <c r="G33" s="7">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="H33" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I33" s="7">
-        <v>4857</v>
+        <v>10750</v>
       </c>
       <c r="J33" s="5">
-        <v>69.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>86.40000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>187000</v>
+        <v>295000</v>
       </c>
       <c r="G34" s="7">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="H34" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I34" s="7">
-        <v>7000</v>
+        <v>44500</v>
       </c>
       <c r="J34" s="5">
-        <v>69.3</v>
+        <v>70</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>76.09999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>539000</v>
+        <v>1008000</v>
       </c>
       <c r="G35" s="7">
-        <v>17000</v>
+        <v>3000</v>
       </c>
       <c r="H35" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>29571</v>
+        <v>24375</v>
       </c>
       <c r="J35" s="5">
-        <v>69.2</v>
+        <v>69.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>80.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>353000</v>
+        <v>130000</v>
       </c>
       <c r="G36" s="7">
-        <v>13000</v>
+        <v>5000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I36" s="7">
-        <v>19286</v>
+        <v>5500</v>
       </c>
       <c r="J36" s="5">
-        <v>69.2</v>
+        <v>69.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>96.7</v>
+        <v>86.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>101000</v>
+        <v>130000</v>
       </c>
       <c r="G37" s="7">
-        <v>17000</v>
+        <v>7000</v>
       </c>
       <c r="H37" s="7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I37" s="7">
-        <v>15000</v>
+        <v>8625</v>
       </c>
       <c r="J37" s="5">
-        <v>68.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>79.59999999999999</v>
+        <v>80.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>340000</v>
+        <v>460000</v>
       </c>
       <c r="G38" s="7">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="H38" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I38" s="7">
-        <v>20000</v>
+        <v>20375</v>
       </c>
       <c r="J38" s="5">
-        <v>68.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>88</v>
+        <v>78.8</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>176000</v>
+        <v>875000</v>
       </c>
       <c r="G39" s="7">
-        <v>3000</v>
+        <v>21000</v>
       </c>
       <c r="H39" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39" s="7">
-        <v>1571</v>
+        <v>23375</v>
       </c>
       <c r="J39" s="5">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>80.09999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>369000</v>
+        <v>153000</v>
       </c>
       <c r="G40" s="7">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="H40" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>18571</v>
+        <v>11400</v>
       </c>
       <c r="J40" s="5">
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>84.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>123000</v>
+        <v>256000</v>
       </c>
       <c r="G41" s="7">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H41" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41" s="7">
-        <v>8857</v>
+        <v>250</v>
       </c>
       <c r="J41" s="5">
-        <v>68.5</v>
+        <v>69</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>81.3</v>
+        <v>85</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>1166000</v>
+        <v>120000</v>
       </c>
       <c r="G42" s="7">
-        <v>21000</v>
+        <v>8000</v>
       </c>
       <c r="H42" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>14714</v>
+        <v>8833</v>
       </c>
       <c r="J42" s="5">
-        <v>68.40000000000001</v>
+        <v>69</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>75.09999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>468000</v>
+        <v>281000</v>
       </c>
       <c r="G43" s="7">
-        <v>19000</v>
+        <v>28000</v>
       </c>
       <c r="H43" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I43" s="7">
-        <v>28571</v>
+        <v>6875</v>
       </c>
       <c r="J43" s="5">
-        <v>68.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.8</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>120000</v>
+        <v>111000</v>
       </c>
       <c r="G44" s="7">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H44" s="7">
         <v>6</v>
       </c>
       <c r="I44" s="7">
-        <v>9800</v>
+        <v>8000</v>
       </c>
       <c r="J44" s="5">
-        <v>68.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>83.2</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>169000</v>
+        <v>281000</v>
       </c>
       <c r="G45" s="7">
-        <v>2000</v>
+        <v>39000</v>
       </c>
       <c r="H45" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I45" s="7">
-        <v>8000</v>
+        <v>10500</v>
       </c>
       <c r="J45" s="5">
-        <v>67.8</v>
+        <v>68.3</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>85.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>149000</v>
+        <v>143000</v>
       </c>
       <c r="G46" s="7">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="H46" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I46" s="7">
-        <v>2857</v>
+        <v>5375</v>
       </c>
       <c r="J46" s="5">
-        <v>67.8</v>
+        <v>68.3</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>83.7</v>
+        <v>79.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>133000</v>
+        <v>381000</v>
       </c>
       <c r="G47" s="7">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="H47" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
-        <v>6571</v>
+        <v>17750</v>
       </c>
       <c r="J47" s="5">
-        <v>67.7</v>
+        <v>68.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>83.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>104000</v>
+        <v>141000</v>
       </c>
       <c r="G48" s="7">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="H48" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>6429</v>
+        <v>0</v>
       </c>
       <c r="J48" s="5">
-        <v>67.59999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>79.90000000000001</v>
+        <v>85.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>671000</v>
+        <v>142000</v>
       </c>
       <c r="G49" s="7">
         <v>5000</v>
       </c>
       <c r="H49" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I49" s="7">
-        <v>14143</v>
+        <v>4875</v>
       </c>
       <c r="J49" s="5">
-        <v>67.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>84.3</v>
+        <v>79.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>107000</v>
+        <v>361000</v>
       </c>
       <c r="G50" s="7">
-        <v>0</v>
+        <v>8000</v>
       </c>
       <c r="H50" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I50" s="7">
-        <v>4429</v>
+        <v>17875</v>
       </c>
       <c r="J50" s="5">
-        <v>67.5</v>
+        <v>68</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>83.2</v>
+        <v>84</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>140000</v>
+        <v>171000</v>
       </c>
       <c r="G51" s="7">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H51" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I51" s="7">
-        <v>5714</v>
+        <v>7250</v>
       </c>
       <c r="J51" s="5">
-        <v>67.2</v>
+        <v>68</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>83.7</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>142000</v>
+        <v>145000</v>
       </c>
       <c r="G52" s="7">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="H52" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I52" s="7">
-        <v>4429</v>
+        <v>4250</v>
       </c>
       <c r="J52" s="5">
-        <v>67.09999999999999</v>
+        <v>68</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>83.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>253000</v>
+        <v>546000</v>
       </c>
       <c r="G53" s="7">
-        <v>21000</v>
+        <v>7000</v>
       </c>
       <c r="H53" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I53" s="7">
-        <v>3857</v>
+        <v>26750</v>
       </c>
       <c r="J53" s="5">
-        <v>66.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>83</v>
+        <v>78.7</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>159000</v>
+        <v>349000</v>
       </c>
       <c r="G54" s="7">
-        <v>-5000</v>
+        <v>9000</v>
       </c>
       <c r="H54" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I54" s="7">
-        <v>3714</v>
+        <v>18625</v>
       </c>
       <c r="J54" s="5">
-        <v>66.59999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-22T04:31:43+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-23T04:28:21+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>综漫：表白被拒就变强？</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
     <t>武侠网游，开局三个神级词条</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
-  </si>
-  <si>
     <t>纨绔大少是邪神，眷属全部是美女</t>
   </si>
   <si>
+    <t>死刑当天，修仙者夺舍了我</t>
+  </si>
+  <si>
+    <t>全三国重生，我老六身份藏不住了</t>
+  </si>
+  <si>
+    <t>凤流高手</t>
+  </si>
+  <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
     <t>白娘子：你不能娶我妹妹小青</t>
   </si>
   <si>
     <t>游走神话时代，开局拜师道门天师</t>
   </si>
   <si>
-    <t>衰神气运逆转，回老家享受生活</t>
-  </si>
-  <si>
-    <t>凤流高手</t>
-  </si>
-  <si>
-    <t>死刑当天，修仙者夺舍了我</t>
-  </si>
-  <si>
     <t>名义：刚提名省服，你让我退休？</t>
   </si>
   <si>
-    <t>综漫：表白被拒就变强？</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
+    <t>她未上岸提分手，我结婚她破防了</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>不拱火我来汉东干什么？</t>
   </si>
   <si>
     <t>全民领主：我的兵营来自战锤</t>
   </si>
   <si>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>因为太无敌，我被重生者抢破头？</t>
+  </si>
+  <si>
     <t>带着渡劫修为，重回高中时代</t>
   </si>
   <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>宿舍求生：糯米可镇不住我们太久</t>
+  </si>
+  <si>
+    <t>名义：谁还不是个汉大帮</t>
+  </si>
+  <si>
+    <t>三角洲：手游主播的我误入巅峰赛</t>
+  </si>
+  <si>
     <t>全民英雄协会：开局招募一拳光头</t>
   </si>
   <si>
-    <t>她未上岸提分手，我结婚她破防了</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>聊天群：混沌魔神？万界该溜子</t>
+    <t>植物大战僵尸恐怖版开局获得电大</t>
+  </si>
+  <si>
+    <t>我，暗影君王，拥有亿万召唤兽！</t>
+  </si>
+  <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
   </si>
   <si>
     <t>重生八零渔村，带仨前妻赶海暴富</t>
   </si>
   <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
-    <t>县城：女友出国要我卖房，给脸了</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>宿舍求生：糯米可镇不住我们太久</t>
-  </si>
-  <si>
-    <t>因为太无敌，我被重生者抢破头？</t>
-  </si>
-  <si>
-    <t>三角洲：手游主播的我误入巅峰赛</t>
-  </si>
-  <si>
-    <t>名义：谁还不是个汉大帮</t>
-  </si>
-  <si>
     <t>美恐：天真珈百璃，正在开始狩猎</t>
   </si>
   <si>
+    <t>四合院1948亿万富翁躺平生活</t>
+  </si>
+  <si>
+    <t>不会踢球？却成了足球巨星！</t>
+  </si>
+  <si>
+    <t>机甲武神：从矿星开始</t>
+  </si>
+  <si>
+    <t>开了无敌秒杀外挂的我横推多元</t>
+  </si>
+  <si>
+    <t>开局魅骨词条，我成了宇智波团宠</t>
+  </si>
+  <si>
+    <t>惊悚世界，我的小弟有亿点多</t>
+  </si>
+  <si>
+    <t>无声1937</t>
+  </si>
+  <si>
+    <t>老师，男生也能报考魔女学院吗？</t>
+  </si>
+  <si>
+    <t>西游：大圣闹地府！始皇长生啦</t>
+  </si>
+  <si>
+    <t>领证三天，我被未婚妻杀死</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
+  </si>
+  <si>
+    <t>全员悍匪：你管这叫正经公司？</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
+  </si>
+  <si>
+    <t>三次入伍，我只想退伍进体制</t>
+  </si>
+  <si>
+    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
+  </si>
+  <si>
     <t>海洋求生，上船两个要求，大萝莉</t>
   </si>
   <si>
-    <t>惊悚世界，我的小弟有亿点多</t>
-  </si>
-  <si>
-    <t>西游：大圣闹地府！始皇长生啦</t>
-  </si>
-  <si>
-    <t>机甲武神：从矿星开始</t>
-  </si>
-  <si>
-    <t>我一写网文的，你让我混娱乐圈？</t>
-  </si>
-  <si>
-    <t>祖上十八鬼帝，你让我恐怖求生？</t>
-  </si>
-  <si>
-    <t>三次入伍，我只想退伍进体制</t>
-  </si>
-  <si>
-    <t>无声1937</t>
-  </si>
-  <si>
-    <t>觉醒伪神，神明弃我，我自为神</t>
-  </si>
-  <si>
-    <t>植物大战僵尸恐怖版开局获得电大</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>我，暗影君王，拥有亿万召唤兽！</t>
-  </si>
-  <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>不会踢球？却成了足球巨星！</t>
-  </si>
-  <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
+    <t>让你去救赎，双生校花怎么恶堕了</t>
   </si>
   <si>
     <t>诡异世界，我的神通无限升级！</t>
   </si>
   <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>老师，男生也能报考魔女学院吗？</t>
-  </si>
-  <si>
-    <t>一毛一天修为，我靠直播氪穿宇宙</t>
-  </si>
-  <si>
-    <t>奥特：天蝎座第一道光</t>
-  </si>
-  <si>
-    <t>飓风战魂：我的陀螺竟是谱尼？！</t>
-  </si>
-  <si>
-    <t>穿越黄毛，女主们把我当白月光了</t>
-  </si>
-  <si>
     <t>我都永生了，会亿点技能很合理吧</t>
   </si>
   <si>
-    <t>灵气复苏？前世女帝老婆也复苏了</t>
+    <t>当泰拉上国家来到蓝星</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>95.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>374000</v>
+        <v>313000</v>
       </c>
       <c r="G5" s="7">
-        <v>27000</v>
+        <v>37000</v>
       </c>
       <c r="H5" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="7">
-        <v>34625</v>
+        <v>17444</v>
       </c>
       <c r="J5" s="5">
-        <v>81.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>139000</v>
+        <v>161000</v>
       </c>
       <c r="G6" s="7">
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="H6" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="7">
-        <v>15429</v>
+        <v>16250</v>
       </c>
       <c r="J6" s="5">
-        <v>78.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>80.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>867000</v>
+        <v>391000</v>
       </c>
       <c r="G7" s="7">
-        <v>38000</v>
+        <v>17000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7">
-        <v>57167</v>
+        <v>32667</v>
       </c>
       <c r="J7" s="5">
-        <v>78.3</v>
+        <v>79</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>98</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>137000</v>
+        <v>907000</v>
       </c>
       <c r="G8" s="7">
-        <v>15000</v>
+        <v>40000</v>
       </c>
       <c r="H8" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7">
-        <v>14500</v>
+        <v>54714</v>
       </c>
       <c r="J8" s="5">
-        <v>77.5</v>
+        <v>78.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>88.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>427000</v>
+        <v>503000</v>
       </c>
       <c r="G9" s="7">
-        <v>2000</v>
+        <v>58000</v>
       </c>
       <c r="H9" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I9" s="7">
-        <v>32500</v>
+        <v>31778</v>
       </c>
       <c r="J9" s="5">
-        <v>76.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,23 +924,23 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>99.5</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>217000</v>
+        <v>114000</v>
       </c>
       <c r="G10" s="7">
-        <v>55000</v>
+        <v>15000</v>
       </c>
       <c r="H10" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I10" s="7">
-        <v>51500</v>
+        <v>8667</v>
       </c>
       <c r="J10" s="5">
         <v>76.90000000000001</v>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>95.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>126000</v>
+        <v>143000</v>
       </c>
       <c r="G11" s="7">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="H11" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I11" s="7">
-        <v>11500</v>
+        <v>12111</v>
       </c>
       <c r="J11" s="5">
-        <v>75.3</v>
+        <v>76.7</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>86.8</v>
+        <v>83.2</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>445000</v>
+        <v>1017000</v>
       </c>
       <c r="G12" s="7">
-        <v>35000</v>
+        <v>39000</v>
       </c>
       <c r="H12" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>28500</v>
+        <v>37889</v>
       </c>
       <c r="J12" s="5">
-        <v>74.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>90.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>299000</v>
+        <v>148000</v>
       </c>
       <c r="G13" s="7">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="H13" s="7">
         <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>17857</v>
+        <v>14000</v>
       </c>
       <c r="J13" s="5">
-        <v>74.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>90.90000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>276000</v>
+        <v>421000</v>
       </c>
       <c r="G14" s="7">
-        <v>12000</v>
+        <v>-6000</v>
       </c>
       <c r="H14" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I14" s="7">
-        <v>15000</v>
+        <v>28222</v>
       </c>
       <c r="J14" s="5">
-        <v>73.7</v>
+        <v>74.7</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,14 +1089,14 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>79.5</v>
+        <v>91.5</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>978000</v>
+        <v>311000</v>
       </c>
       <c r="G15" s="7">
         <v>12000</v>
@@ -1105,10 +1105,10 @@
         <v>9</v>
       </c>
       <c r="I15" s="7">
-        <v>37750</v>
+        <v>17125</v>
       </c>
       <c r="J15" s="5">
-        <v>73.2</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>96.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>133000</v>
+        <v>165000</v>
       </c>
       <c r="G16" s="7">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="H16" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I16" s="7">
-        <v>8600</v>
+        <v>11222</v>
       </c>
       <c r="J16" s="5">
-        <v>73.2</v>
+        <v>74</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>91.8</v>
+        <v>83.2</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>139000</v>
+        <v>1683000</v>
       </c>
       <c r="G17" s="7">
-        <v>9000</v>
+        <v>48000</v>
       </c>
       <c r="H17" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" s="7">
-        <v>9875</v>
+        <v>31333</v>
       </c>
       <c r="J17" s="5">
-        <v>73</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>94.09999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>192000</v>
+        <v>286000</v>
       </c>
       <c r="G18" s="7">
-        <v>15000</v>
+        <v>34000</v>
       </c>
       <c r="H18" s="7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I18" s="7">
-        <v>3750</v>
+        <v>38500</v>
       </c>
       <c r="J18" s="5">
-        <v>72.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>90.5</v>
+        <v>93</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>153000</v>
+        <v>147000</v>
       </c>
       <c r="G19" s="7">
-        <v>9000</v>
+        <v>14000</v>
       </c>
       <c r="H19" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>11125</v>
+        <v>9500</v>
       </c>
       <c r="J19" s="5">
-        <v>72.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>82</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>1635000</v>
+        <v>269000</v>
       </c>
       <c r="G20" s="7">
-        <v>28000</v>
+        <v>33000</v>
       </c>
       <c r="H20" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I20" s="7">
-        <v>29250</v>
+        <v>12444</v>
       </c>
       <c r="J20" s="5">
-        <v>72.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>90.5</v>
+        <v>89.8</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>134000</v>
+        <v>152000</v>
       </c>
       <c r="G21" s="7">
-        <v>13000</v>
+        <v>8000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>9857</v>
+        <v>14167</v>
       </c>
       <c r="J21" s="5">
-        <v>72.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>91.3</v>
+        <v>90.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>196000</v>
+        <v>147000</v>
       </c>
       <c r="G22" s="7">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="H22" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I22" s="7">
-        <v>7250</v>
+        <v>9667</v>
       </c>
       <c r="J22" s="5">
-        <v>72</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>78.8</v>
+        <v>86.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>729000</v>
+        <v>379000</v>
       </c>
       <c r="G23" s="7">
-        <v>14000</v>
+        <v>46000</v>
       </c>
       <c r="H23" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I23" s="7">
-        <v>34429</v>
+        <v>18222</v>
       </c>
       <c r="J23" s="5">
-        <v>71.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>84.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>440000</v>
+        <v>167000</v>
       </c>
       <c r="G24" s="7">
-        <v>29000</v>
+        <v>9000</v>
       </c>
       <c r="H24" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I24" s="7">
-        <v>21000</v>
+        <v>10556</v>
       </c>
       <c r="J24" s="5">
-        <v>71.7</v>
+        <v>72.2</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>86.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>333000</v>
+        <v>188000</v>
       </c>
       <c r="G25" s="7">
-        <v>41000</v>
+        <v>14000</v>
       </c>
       <c r="H25" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I25" s="7">
-        <v>14750</v>
+        <v>10286</v>
       </c>
       <c r="J25" s="5">
-        <v>71.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>88.3</v>
+        <v>91.7</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>158000</v>
+        <v>122000</v>
       </c>
       <c r="G26" s="7">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="H26" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I26" s="7">
-        <v>10750</v>
+        <v>13200</v>
       </c>
       <c r="J26" s="5">
-        <v>71.3</v>
+        <v>71.7</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>89.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>144000</v>
+        <v>203000</v>
       </c>
       <c r="G27" s="7">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="H27" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>15400</v>
+        <v>4556</v>
       </c>
       <c r="J27" s="5">
-        <v>71.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>95.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>113000</v>
+        <v>163000</v>
       </c>
       <c r="G28" s="7">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="H28" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>14250</v>
+        <v>11167</v>
       </c>
       <c r="J28" s="5">
-        <v>71.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>88</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>174000</v>
+        <v>130000</v>
       </c>
       <c r="G29" s="7">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>9667</v>
+        <v>9000</v>
       </c>
       <c r="J29" s="5">
-        <v>70.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>96.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>108000</v>
+        <v>739000</v>
       </c>
       <c r="G30" s="7">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I30" s="7">
-        <v>9750</v>
+        <v>31375</v>
       </c>
       <c r="J30" s="5">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>88.90000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>154000</v>
+        <v>327000</v>
       </c>
       <c r="G31" s="7">
-        <v>8000</v>
+        <v>46000</v>
       </c>
       <c r="H31" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I31" s="7">
-        <v>5571</v>
+        <v>14444</v>
       </c>
       <c r="J31" s="5">
-        <v>70.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>78.8</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>456000</v>
+        <v>201000</v>
       </c>
       <c r="G32" s="7">
-        <v>27000</v>
+        <v>5000</v>
       </c>
       <c r="H32" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I32" s="7">
-        <v>27125</v>
+        <v>7000</v>
       </c>
       <c r="J32" s="5">
-        <v>70.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>86.2</v>
+        <v>91.2</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>174000</v>
+        <v>117000</v>
       </c>
       <c r="G33" s="7">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="H33" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I33" s="7">
-        <v>10750</v>
+        <v>9600</v>
       </c>
       <c r="J33" s="5">
-        <v>70.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,23 +1716,23 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>90.7</v>
+        <v>95.5</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>295000</v>
+        <v>185000</v>
       </c>
       <c r="G34" s="7">
-        <v>44000</v>
+        <v>29000</v>
       </c>
       <c r="H34" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="7">
-        <v>44500</v>
+        <v>22000</v>
       </c>
       <c r="J34" s="5">
         <v>70</v>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>79.5</v>
+        <v>87.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>1008000</v>
+        <v>116000</v>
       </c>
       <c r="G35" s="7">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H35" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>24375</v>
+        <v>7500</v>
       </c>
       <c r="J35" s="5">
-        <v>69.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>87.90000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>130000</v>
+        <v>328000</v>
       </c>
       <c r="G36" s="7">
-        <v>5000</v>
+        <v>33000</v>
       </c>
       <c r="H36" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I36" s="7">
-        <v>5500</v>
+        <v>40667</v>
       </c>
       <c r="J36" s="5">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,7 +1815,7 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>86.3</v>
+        <v>86.2</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
@@ -1825,16 +1825,16 @@
         <v>130000</v>
       </c>
       <c r="G37" s="7">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="H37" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I37" s="7">
-        <v>8625</v>
+        <v>8429</v>
       </c>
       <c r="J37" s="5">
-        <v>69.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>80.5</v>
+        <v>85.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>460000</v>
+        <v>218000</v>
       </c>
       <c r="G38" s="7">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H38" s="7">
         <v>9</v>
       </c>
       <c r="I38" s="7">
-        <v>20375</v>
+        <v>8125</v>
       </c>
       <c r="J38" s="5">
-        <v>69.40000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>78.8</v>
+        <v>77.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>875000</v>
+        <v>474000</v>
       </c>
       <c r="G39" s="7">
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="H39" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39" s="7">
-        <v>23375</v>
+        <v>26111</v>
       </c>
       <c r="J39" s="5">
-        <v>69.2</v>
+        <v>69</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>87.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>153000</v>
+        <v>469000</v>
       </c>
       <c r="G40" s="7">
-        <v>10000</v>
+        <v>9000</v>
       </c>
       <c r="H40" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I40" s="7">
-        <v>11400</v>
+        <v>19111</v>
       </c>
       <c r="J40" s="5">
-        <v>69.2</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>89</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>256000</v>
+        <v>147000</v>
       </c>
       <c r="G41" s="7">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H41" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I41" s="7">
-        <v>250</v>
+        <v>667</v>
       </c>
       <c r="J41" s="5">
-        <v>69</v>
+        <v>68.8</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>120000</v>
+        <v>171000</v>
       </c>
       <c r="G42" s="7">
-        <v>8000</v>
+        <v>-3000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I42" s="7">
-        <v>8833</v>
+        <v>9222</v>
       </c>
       <c r="J42" s="5">
-        <v>69</v>
+        <v>68.7</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>85.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>281000</v>
+        <v>139000</v>
       </c>
       <c r="G43" s="7">
-        <v>28000</v>
+        <v>14000</v>
       </c>
       <c r="H43" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I43" s="7">
-        <v>6875</v>
+        <v>5222</v>
       </c>
       <c r="J43" s="5">
-        <v>68.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,23 +2046,23 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>88.40000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>111000</v>
+        <v>241000</v>
       </c>
       <c r="G44" s="7">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="H44" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I44" s="7">
-        <v>8000</v>
+        <v>13500</v>
       </c>
       <c r="J44" s="5">
         <v>68.59999999999999</v>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>83.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>281000</v>
+        <v>298000</v>
       </c>
       <c r="G45" s="7">
-        <v>39000</v>
+        <v>20000</v>
       </c>
       <c r="H45" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I45" s="7">
-        <v>10500</v>
+        <v>17000</v>
       </c>
       <c r="J45" s="5">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,23 +2112,23 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>85.40000000000001</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>143000</v>
+        <v>304000</v>
       </c>
       <c r="G46" s="7">
-        <v>3000</v>
+        <v>23000</v>
       </c>
       <c r="H46" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I46" s="7">
-        <v>5375</v>
+        <v>8667</v>
       </c>
       <c r="J46" s="5">
         <v>68.3</v>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>79.5</v>
+        <v>83.8</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>381000</v>
+        <v>133000</v>
       </c>
       <c r="G47" s="7">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="H47" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I47" s="7">
-        <v>17750</v>
+        <v>8000</v>
       </c>
       <c r="J47" s="5">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.59999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>141000</v>
+        <v>111000</v>
       </c>
       <c r="G48" s="7">
-        <v>7000</v>
+        <v>3000</v>
       </c>
       <c r="H48" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I48" s="7">
-        <v>0</v>
+        <v>667</v>
       </c>
       <c r="J48" s="5">
-        <v>68.2</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>85.2</v>
+        <v>84.8</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>142000</v>
+        <v>156000</v>
       </c>
       <c r="G49" s="7">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H49" s="7">
         <v>9</v>
       </c>
       <c r="I49" s="7">
-        <v>4875</v>
+        <v>5125</v>
       </c>
       <c r="J49" s="5">
-        <v>68.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>79.2</v>
+        <v>86</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>361000</v>
+        <v>155000</v>
       </c>
       <c r="G50" s="7">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="H50" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I50" s="7">
-        <v>17875</v>
+        <v>2444</v>
       </c>
       <c r="J50" s="5">
-        <v>68</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>84</v>
+        <v>84.3</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>171000</v>
+        <v>110000</v>
       </c>
       <c r="G51" s="7">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H51" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I51" s="7">
-        <v>7250</v>
+        <v>6143</v>
       </c>
       <c r="J51" s="5">
-        <v>68</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>85.40000000000001</v>
+        <v>84.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
@@ -2320,16 +2320,16 @@
         <v>145000</v>
       </c>
       <c r="G52" s="7">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H52" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I52" s="7">
-        <v>4250</v>
+        <v>5000</v>
       </c>
       <c r="J52" s="5">
-        <v>68</v>
+        <v>67.8</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>75</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>546000</v>
+        <v>555000</v>
       </c>
       <c r="G53" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H53" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I53" s="7">
-        <v>26750</v>
+        <v>24778</v>
       </c>
       <c r="J53" s="5">
-        <v>67.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>78.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>349000</v>
+        <v>207000</v>
       </c>
       <c r="G54" s="7">
-        <v>9000</v>
+        <v>18000</v>
       </c>
       <c r="H54" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>18625</v>
+        <v>17000</v>
       </c>
       <c r="J54" s="5">
-        <v>67.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-23T04:28:21+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-24T04:25:20+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>武侠网游，开局三个神级词条</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>凤流高手</t>
+  </si>
+  <si>
+    <t>纨绔大少是邪神，眷属全部是美女</t>
+  </si>
+  <si>
     <t>综漫：表白被拒就变强？</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
-  </si>
-  <si>
-    <t>武侠网游，开局三个神级词条</t>
-  </si>
-  <si>
-    <t>纨绔大少是邪神，眷属全部是美女</t>
-  </si>
-  <si>
-    <t>死刑当天，修仙者夺舍了我</t>
+    <t>抗美援朝：什么叫这是四合院世界</t>
+  </si>
+  <si>
+    <t>封神：开局反出西岐，我死守渑池</t>
+  </si>
+  <si>
+    <t>带着渡劫修为，重回高中时代</t>
+  </si>
+  <si>
+    <t>三角洲：手游主播的我误入巅峰赛</t>
+  </si>
+  <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>名义：刚提名省服，你让我退休？</t>
+  </si>
+  <si>
+    <t>四合院1948亿万富翁躺平生活</t>
+  </si>
+  <si>
+    <t>游走神话时代，开局拜师道门天师</t>
+  </si>
+  <si>
+    <t>我，原始首徒，封神开局整顿阐教</t>
+  </si>
+  <si>
+    <t>不拱火我来汉东干什么？</t>
+  </si>
+  <si>
+    <t>白娘子：你不能娶我妹妹小青</t>
   </si>
   <si>
     <t>全三国重生，我老六身份藏不住了</t>
   </si>
   <si>
-    <t>凤流高手</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>白娘子：你不能娶我妹妹小青</t>
-  </si>
-  <si>
-    <t>游走神话时代，开局拜师道门天师</t>
-  </si>
-  <si>
-    <t>名义：刚提名省服，你让我退休？</t>
-  </si>
-  <si>
-    <t>她未上岸提分手，我结婚她破防了</t>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
   </si>
   <si>
     <t>规则怪谈：无所谓，系统会出手</t>
   </si>
   <si>
-    <t>不拱火我来汉东干什么？</t>
-  </si>
-  <si>
-    <t>全民领主：我的兵营来自战锤</t>
+    <t>聊天群：混沌魔神？万界该溜子</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
   </si>
   <si>
     <t>从零开始，打造华夏首支特种部队</t>
   </si>
   <si>
+    <t>美恐：天真珈百璃，正在开始狩猎</t>
+  </si>
+  <si>
+    <t>宿舍求生：糯米可镇不住我们太久</t>
+  </si>
+  <si>
+    <t>植物大战僵尸恐怖版开局获得电大</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
+  </si>
+  <si>
+    <t>西游：大圣闹地府！始皇长生啦</t>
+  </si>
+  <si>
+    <t>说好造桥游戏，打穿天山什么鬼？</t>
+  </si>
+  <si>
+    <t>名义：谁还不是个汉大帮</t>
+  </si>
+  <si>
+    <t>不会踢球？却成了足球巨星！</t>
+  </si>
+  <si>
+    <t>选择求生：只有我能看到正确答案</t>
+  </si>
+  <si>
+    <t>老师，男生也能报考魔女学院吗？</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
+  </si>
+  <si>
+    <t>开局魅骨词条，我成了宇智波团宠</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>机甲武神：从矿星开始</t>
+  </si>
+  <si>
+    <t>天幕让你当废物班长你独断万古？</t>
+  </si>
+  <si>
     <t>因为太无敌，我被重生者抢破头？</t>
   </si>
   <si>
-    <t>带着渡劫修为，重回高中时代</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>宿舍求生：糯米可镇不住我们太久</t>
-  </si>
-  <si>
-    <t>名义：谁还不是个汉大帮</t>
-  </si>
-  <si>
-    <t>三角洲：手游主播的我误入巅峰赛</t>
-  </si>
-  <si>
-    <t>全民英雄协会：开局招募一拳光头</t>
-  </si>
-  <si>
-    <t>植物大战僵尸恐怖版开局获得电大</t>
-  </si>
-  <si>
-    <t>我，暗影君王，拥有亿万召唤兽！</t>
-  </si>
-  <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>很野很欲，楼下的蔷薇正飘香！</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>让你去救赎，双生校花怎么恶堕了</t>
+  </si>
+  <si>
+    <t>从修仙回到都市，坏消息修为没了</t>
+  </si>
+  <si>
+    <t>无声1937</t>
+  </si>
+  <si>
+    <t>穿越黄毛，女主们把我当白月光了</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>灵气复苏？前世女帝老婆也复苏了</t>
   </si>
   <si>
     <t>重生八零渔村，带仨前妻赶海暴富</t>
   </si>
   <si>
-    <t>美恐：天真珈百璃，正在开始狩猎</t>
-  </si>
-  <si>
-    <t>四合院1948亿万富翁躺平生活</t>
-  </si>
-  <si>
-    <t>不会踢球？却成了足球巨星！</t>
-  </si>
-  <si>
-    <t>机甲武神：从矿星开始</t>
-  </si>
-  <si>
-    <t>开了无敌秒杀外挂的我横推多元</t>
-  </si>
-  <si>
-    <t>开局魅骨词条，我成了宇智波团宠</t>
-  </si>
-  <si>
-    <t>惊悚世界，我的小弟有亿点多</t>
-  </si>
-  <si>
-    <t>无声1937</t>
-  </si>
-  <si>
-    <t>老师，男生也能报考魔女学院吗？</t>
-  </si>
-  <si>
-    <t>西游：大圣闹地府！始皇长生啦</t>
-  </si>
-  <si>
     <t>领证三天，我被未婚妻杀死</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
-  </si>
-  <si>
-    <t>全员悍匪：你管这叫正经公司？</t>
-  </si>
-  <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>三次入伍，我只想退伍进体制</t>
-  </si>
-  <si>
-    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
-  </si>
-  <si>
-    <t>海洋求生，上船两个要求，大萝莉</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
-  </si>
-  <si>
-    <t>让你去救赎，双生校花怎么恶堕了</t>
-  </si>
-  <si>
-    <t>诡异世界，我的神通无限升级！</t>
-  </si>
-  <si>
-    <t>我都永生了，会亿点技能很合理吧</t>
-  </si>
-  <si>
-    <t>当泰拉上国家来到蓝星</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>313000</v>
+        <v>414000</v>
       </c>
       <c r="G5" s="7">
-        <v>37000</v>
+        <v>23000</v>
       </c>
       <c r="H5" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="7">
-        <v>17444</v>
+        <v>31700</v>
       </c>
       <c r="J5" s="5">
-        <v>79.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>161000</v>
+        <v>187000</v>
       </c>
       <c r="G6" s="7">
-        <v>22000</v>
+        <v>26000</v>
       </c>
       <c r="H6" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="7">
-        <v>16250</v>
+        <v>17333</v>
       </c>
       <c r="J6" s="5">
-        <v>79.09999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>391000</v>
+        <v>169000</v>
       </c>
       <c r="G7" s="7">
-        <v>17000</v>
+        <v>26000</v>
       </c>
       <c r="H7" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I7" s="7">
-        <v>32667</v>
+        <v>13500</v>
       </c>
       <c r="J7" s="5">
-        <v>79</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>81.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>907000</v>
+        <v>940000</v>
       </c>
       <c r="G8" s="7">
-        <v>40000</v>
+        <v>33000</v>
       </c>
       <c r="H8" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="7">
-        <v>54714</v>
+        <v>52000</v>
       </c>
       <c r="J8" s="5">
-        <v>78.3</v>
+        <v>78</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>91.5</v>
+        <v>96.8</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>503000</v>
+        <v>344000</v>
       </c>
       <c r="G9" s="7">
-        <v>58000</v>
+        <v>31000</v>
       </c>
       <c r="H9" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I9" s="7">
-        <v>31778</v>
+        <v>18800</v>
       </c>
       <c r="J9" s="5">
-        <v>78.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>99.5</v>
+        <v>99.2</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>114000</v>
+        <v>100000</v>
       </c>
       <c r="G10" s="7">
-        <v>15000</v>
+        <v>30000</v>
       </c>
       <c r="H10" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I10" s="7">
-        <v>8667</v>
+        <v>10857</v>
       </c>
       <c r="J10" s="5">
-        <v>76.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>97.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>143000</v>
+        <v>793000</v>
       </c>
       <c r="G11" s="7">
-        <v>17000</v>
+        <v>77000</v>
       </c>
       <c r="H11" s="7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I11" s="7">
-        <v>12111</v>
+        <v>78000</v>
       </c>
       <c r="J11" s="5">
-        <v>76.7</v>
+        <v>76.8</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>83.2</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>1017000</v>
+        <v>166000</v>
       </c>
       <c r="G12" s="7">
-        <v>39000</v>
+        <v>19000</v>
       </c>
       <c r="H12" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I12" s="7">
-        <v>37889</v>
+        <v>10600</v>
       </c>
       <c r="J12" s="5">
-        <v>75.2</v>
+        <v>76.2</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>93.90000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>148000</v>
+        <v>136000</v>
       </c>
       <c r="G13" s="7">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="H13" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>14000</v>
+        <v>13333</v>
       </c>
       <c r="J13" s="5">
-        <v>75.09999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>86.7</v>
+        <v>83.3</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>421000</v>
+        <v>1058000</v>
       </c>
       <c r="G14" s="7">
-        <v>-6000</v>
+        <v>41000</v>
       </c>
       <c r="H14" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7">
-        <v>28222</v>
+        <v>38200</v>
       </c>
       <c r="J14" s="5">
-        <v>74.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>91.5</v>
+        <v>93</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>311000</v>
+        <v>328000</v>
       </c>
       <c r="G15" s="7">
-        <v>12000</v>
+        <v>17000</v>
       </c>
       <c r="H15" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I15" s="7">
-        <v>17125</v>
+        <v>17111</v>
       </c>
       <c r="J15" s="5">
-        <v>74.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>93.09999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>165000</v>
+        <v>217000</v>
       </c>
       <c r="G16" s="7">
-        <v>12000</v>
+        <v>32000</v>
       </c>
       <c r="H16" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I16" s="7">
-        <v>11222</v>
+        <v>24500</v>
       </c>
       <c r="J16" s="5">
-        <v>74</v>
+        <v>75.2</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>83.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>1683000</v>
+        <v>419000</v>
       </c>
       <c r="G17" s="7">
-        <v>48000</v>
+        <v>-2000</v>
       </c>
       <c r="H17" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="7">
-        <v>31333</v>
+        <v>25200</v>
       </c>
       <c r="J17" s="5">
-        <v>73.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,23 +1188,23 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>99.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>286000</v>
+        <v>108000</v>
       </c>
       <c r="G18" s="7">
-        <v>34000</v>
+        <v>13000</v>
       </c>
       <c r="H18" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I18" s="7">
-        <v>38500</v>
+        <v>10200</v>
       </c>
       <c r="J18" s="5">
         <v>73.59999999999999</v>
@@ -1221,23 +1221,23 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>93</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>147000</v>
+        <v>313000</v>
       </c>
       <c r="G19" s="7">
-        <v>14000</v>
+        <v>27000</v>
       </c>
       <c r="H19" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
-        <v>9500</v>
+        <v>34667</v>
       </c>
       <c r="J19" s="5">
         <v>73.5</v>
@@ -1254,23 +1254,23 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>91.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>269000</v>
+        <v>155000</v>
       </c>
       <c r="G20" s="7">
-        <v>33000</v>
+        <v>7000</v>
       </c>
       <c r="H20" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>12444</v>
+        <v>13125</v>
       </c>
       <c r="J20" s="5">
         <v>73.2</v>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>152000</v>
+        <v>122000</v>
       </c>
       <c r="G21" s="7">
         <v>8000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>14167</v>
+        <v>8571</v>
       </c>
       <c r="J21" s="5">
-        <v>72.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>90.8</v>
+        <v>90.3</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>147000</v>
+        <v>360000</v>
       </c>
       <c r="G22" s="7">
-        <v>8000</v>
+        <v>80000</v>
       </c>
       <c r="H22" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="7">
-        <v>9667</v>
+        <v>13000</v>
       </c>
       <c r="J22" s="5">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>86.7</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>379000</v>
+        <v>123000</v>
       </c>
       <c r="G23" s="7">
-        <v>46000</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="7">
-        <v>18222</v>
+        <v>1800</v>
       </c>
       <c r="J23" s="5">
-        <v>72.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,23 +1386,23 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>90.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>167000</v>
+        <v>1700000</v>
       </c>
       <c r="G24" s="7">
-        <v>9000</v>
+        <v>17000</v>
       </c>
       <c r="H24" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I24" s="7">
-        <v>10556</v>
+        <v>29900</v>
       </c>
       <c r="J24" s="5">
         <v>72.2</v>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>188000</v>
+        <v>141000</v>
       </c>
       <c r="G25" s="7">
-        <v>14000</v>
+        <v>11000</v>
       </c>
       <c r="H25" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I25" s="7">
-        <v>10286</v>
+        <v>8444</v>
       </c>
       <c r="J25" s="5">
-        <v>71.7</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>91.7</v>
+        <v>86.2</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>122000</v>
+        <v>382000</v>
       </c>
       <c r="G26" s="7">
-        <v>9000</v>
+        <v>55000</v>
       </c>
       <c r="H26" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I26" s="7">
-        <v>13200</v>
+        <v>18500</v>
       </c>
       <c r="J26" s="5">
-        <v>71.7</v>
+        <v>72</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>91.40000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>203000</v>
+        <v>298000</v>
       </c>
       <c r="G27" s="7">
-        <v>11000</v>
+        <v>29000</v>
       </c>
       <c r="H27" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="7">
-        <v>4556</v>
+        <v>14100</v>
       </c>
       <c r="J27" s="5">
-        <v>71.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>88.40000000000001</v>
+        <v>89.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>163000</v>
+        <v>125000</v>
       </c>
       <c r="G28" s="7">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="H28" s="7">
         <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>11167</v>
+        <v>9333</v>
       </c>
       <c r="J28" s="5">
-        <v>71.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>88.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>130000</v>
+        <v>174000</v>
       </c>
       <c r="G29" s="7">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I29" s="7">
-        <v>9000</v>
+        <v>10200</v>
       </c>
       <c r="J29" s="5">
-        <v>71.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>78.2</v>
+        <v>88.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>739000</v>
+        <v>173000</v>
       </c>
       <c r="G30" s="7">
         <v>10000</v>
       </c>
       <c r="H30" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I30" s="7">
-        <v>31375</v>
+        <v>11000</v>
       </c>
       <c r="J30" s="5">
-        <v>70.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,23 +1617,23 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>85.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>327000</v>
+        <v>341000</v>
       </c>
       <c r="G31" s="7">
-        <v>46000</v>
+        <v>37000</v>
       </c>
       <c r="H31" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I31" s="7">
-        <v>14444</v>
+        <v>11500</v>
       </c>
       <c r="J31" s="5">
         <v>70.90000000000001</v>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>89.09999999999999</v>
+        <v>88</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>201000</v>
+        <v>174000</v>
       </c>
       <c r="G32" s="7">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H32" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="7">
-        <v>7000</v>
+        <v>8600</v>
       </c>
       <c r="J32" s="5">
-        <v>70.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>91.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>117000</v>
+        <v>750000</v>
       </c>
       <c r="G33" s="7">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="H33" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I33" s="7">
-        <v>9600</v>
+        <v>29111</v>
       </c>
       <c r="J33" s="5">
-        <v>70.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>95.5</v>
+        <v>86.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>185000</v>
+        <v>198000</v>
       </c>
       <c r="G34" s="7">
-        <v>29000</v>
+        <v>10000</v>
       </c>
       <c r="H34" s="7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I34" s="7">
-        <v>22000</v>
+        <v>10250</v>
       </c>
       <c r="J34" s="5">
-        <v>70</v>
+        <v>70.3</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>87.3</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>116000</v>
+        <v>122000</v>
       </c>
       <c r="G35" s="7">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H35" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I35" s="7">
-        <v>7500</v>
+        <v>7286</v>
       </c>
       <c r="J35" s="5">
-        <v>69.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>86.3</v>
+        <v>95.2</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>328000</v>
+        <v>108000</v>
       </c>
       <c r="G36" s="7">
-        <v>33000</v>
+        <v>16000</v>
       </c>
       <c r="H36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36" s="7">
-        <v>40667</v>
+        <v>11250</v>
       </c>
       <c r="J36" s="5">
-        <v>69.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>86.2</v>
+        <v>90.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>130000</v>
+        <v>157000</v>
       </c>
       <c r="G37" s="7">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="H37" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I37" s="7">
-        <v>8429</v>
+        <v>1600</v>
       </c>
       <c r="J37" s="5">
-        <v>69.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>85.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>218000</v>
+        <v>249000</v>
       </c>
       <c r="G38" s="7">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="H38" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>8125</v>
+        <v>12400</v>
       </c>
       <c r="J38" s="5">
-        <v>69.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>77.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>474000</v>
+        <v>222000</v>
       </c>
       <c r="G39" s="7">
-        <v>18000</v>
+        <v>4000</v>
       </c>
       <c r="H39" s="7">
         <v>10</v>
       </c>
       <c r="I39" s="7">
-        <v>26111</v>
+        <v>7667</v>
       </c>
       <c r="J39" s="5">
-        <v>69</v>
+        <v>69.7</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>80.3</v>
+        <v>81.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>469000</v>
+        <v>413000</v>
       </c>
       <c r="G40" s="7">
-        <v>9000</v>
+        <v>34000</v>
       </c>
       <c r="H40" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I40" s="7">
-        <v>19111</v>
+        <v>19800</v>
       </c>
       <c r="J40" s="5">
-        <v>68.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>88.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>147000</v>
+        <v>350000</v>
       </c>
       <c r="G41" s="7">
-        <v>6000</v>
+        <v>22000</v>
       </c>
       <c r="H41" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>667</v>
+        <v>36000</v>
       </c>
       <c r="J41" s="5">
-        <v>68.8</v>
+        <v>69.5</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>84.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>171000</v>
+        <v>472000</v>
       </c>
       <c r="G42" s="7">
-        <v>-3000</v>
+        <v>32000</v>
       </c>
       <c r="H42" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>9222</v>
+        <v>29167</v>
       </c>
       <c r="J42" s="5">
-        <v>68.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>86.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>139000</v>
+        <v>152000</v>
       </c>
       <c r="G43" s="7">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I43" s="7">
-        <v>5222</v>
+        <v>12143</v>
       </c>
       <c r="J43" s="5">
-        <v>68.7</v>
+        <v>69.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>91.40000000000001</v>
+        <v>86.3</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>241000</v>
+        <v>181000</v>
       </c>
       <c r="G44" s="7">
-        <v>14000</v>
+        <v>35000</v>
       </c>
       <c r="H44" s="7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I44" s="7">
-        <v>13500</v>
+        <v>5400</v>
       </c>
       <c r="J44" s="5">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>80.40000000000001</v>
+        <v>93</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>298000</v>
+        <v>124000</v>
       </c>
       <c r="G45" s="7">
-        <v>20000</v>
+        <v>13000</v>
       </c>
       <c r="H45" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I45" s="7">
-        <v>17000</v>
+        <v>10500</v>
       </c>
       <c r="J45" s="5">
-        <v>68.5</v>
+        <v>68.8</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>83.90000000000001</v>
+        <v>88.2</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>304000</v>
+        <v>256000</v>
       </c>
       <c r="G46" s="7">
-        <v>23000</v>
+        <v>3000</v>
       </c>
       <c r="H46" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I46" s="7">
-        <v>8667</v>
+        <v>200</v>
       </c>
       <c r="J46" s="5">
-        <v>68.3</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>83.8</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>133000</v>
+        <v>116000</v>
       </c>
       <c r="G47" s="7">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H47" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
-        <v>8000</v>
+        <v>6125</v>
       </c>
       <c r="J47" s="5">
-        <v>68.09999999999999</v>
+        <v>68.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,23 +2178,23 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.2</v>
+        <v>81.7</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>111000</v>
+        <v>201000</v>
       </c>
       <c r="G48" s="7">
-        <v>3000</v>
+        <v>24000</v>
       </c>
       <c r="H48" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I48" s="7">
-        <v>667</v>
+        <v>12571</v>
       </c>
       <c r="J48" s="5">
         <v>68.09999999999999</v>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>84.8</v>
+        <v>79.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>156000</v>
+        <v>473000</v>
       </c>
       <c r="G49" s="7">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="H49" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I49" s="7">
-        <v>5125</v>
+        <v>17600</v>
       </c>
       <c r="J49" s="5">
-        <v>67.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>86</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>155000</v>
+        <v>149000</v>
       </c>
       <c r="G50" s="7">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H50" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I50" s="7">
-        <v>2444</v>
+        <v>3800</v>
       </c>
       <c r="J50" s="5">
-        <v>67.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>84.3</v>
+        <v>79.7</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>110000</v>
+        <v>398000</v>
       </c>
       <c r="G51" s="7">
-        <v>6000</v>
+        <v>13000</v>
       </c>
       <c r="H51" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I51" s="7">
-        <v>6143</v>
+        <v>15900</v>
       </c>
       <c r="J51" s="5">
-        <v>67.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84.7</v>
+        <v>79.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>145000</v>
+        <v>364000</v>
       </c>
       <c r="G52" s="7">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="H52" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I52" s="7">
-        <v>5000</v>
+        <v>16400</v>
       </c>
       <c r="J52" s="5">
-        <v>67.8</v>
+        <v>67.7</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,23 +2343,23 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>75.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>555000</v>
+        <v>196000</v>
       </c>
       <c r="G53" s="7">
-        <v>9000</v>
+        <v>-5000</v>
       </c>
       <c r="H53" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I53" s="7">
-        <v>24778</v>
+        <v>5800</v>
       </c>
       <c r="J53" s="5">
         <v>67.7</v>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>93.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>207000</v>
+        <v>151000</v>
       </c>
       <c r="G54" s="7">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="H54" s="7">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I54" s="7">
-        <v>17000</v>
+        <v>5900</v>
       </c>
       <c r="J54" s="5">
-        <v>67.7</v>
+        <v>67.5</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-24T04:25:20+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-25T04:36:34+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>封神：开局反出西岐，我死守渑池</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>凤流高手</t>
+  </si>
+  <si>
     <t>武侠网游，开局三个神级词条</t>
   </si>
   <si>
-    <t>打开作品</t>
+    <t>游走神话时代，开局拜师道门天师</t>
+  </si>
+  <si>
+    <t>抗美援朝：什么叫这是四合院世界</t>
   </si>
   <si>
     <t>什么叫我成了灭世级怪谈？</t>
   </si>
   <si>
-    <t>凤流高手</t>
+    <t>综漫：表白被拒就变强？</t>
+  </si>
+  <si>
+    <t>十天寿命，买个神话级武魂合理吧</t>
+  </si>
+  <si>
+    <t>不拱火我来汉东干什么？</t>
+  </si>
+  <si>
+    <t>三角洲：手游主播的我误入巅峰赛</t>
   </si>
   <si>
     <t>纨绔大少是邪神，眷属全部是美女</t>
   </si>
   <si>
-    <t>综漫：表白被拒就变强？</t>
-  </si>
-  <si>
-    <t>抗美援朝：什么叫这是四合院世界</t>
-  </si>
-  <si>
-    <t>封神：开局反出西岐，我死守渑池</t>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>白娘子：你不能娶我妹妹小青</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>聊天群：混沌魔神？万界该溜子</t>
+  </si>
+  <si>
+    <t>很野很欲，楼下的蔷薇正飘香！</t>
+  </si>
+  <si>
+    <t>名义：刚提名省服，你让我退休？</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>选择求生：只有我能看到正确答案</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
   </si>
   <si>
     <t>带着渡劫修为，重回高中时代</t>
   </si>
   <si>
-    <t>三角洲：手游主播的我误入巅峰赛</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>名义：刚提名省服，你让我退休？</t>
+    <t>老师，男生也能报考魔女学院吗？</t>
+  </si>
+  <si>
+    <t>美恐：天真珈百璃，正在开始狩猎</t>
+  </si>
+  <si>
+    <t>全三国重生，我老六身份藏不住了</t>
+  </si>
+  <si>
+    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
+  </si>
+  <si>
+    <t>不会踢球？却成了足球巨星！</t>
+  </si>
+  <si>
+    <t>植物大战僵尸恐怖版开局获得电大</t>
+  </si>
+  <si>
+    <t>都市剧：这个世界没有好玩的游戏</t>
+  </si>
+  <si>
+    <t>从修仙回到都市，坏消息修为没了</t>
+  </si>
+  <si>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>我，原始首徒，封神开局整顿阐教</t>
   </si>
   <si>
     <t>四合院1948亿万富翁躺平生活</t>
   </si>
   <si>
-    <t>游走神话时代，开局拜师道门天师</t>
-  </si>
-  <si>
-    <t>我，原始首徒，封神开局整顿阐教</t>
-  </si>
-  <si>
-    <t>不拱火我来汉东干什么？</t>
-  </si>
-  <si>
-    <t>白娘子：你不能娶我妹妹小青</t>
-  </si>
-  <si>
-    <t>全三国重生，我老六身份藏不住了</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
+    <t>因为太无敌，我被重生者抢破头？</t>
+  </si>
+  <si>
+    <t>西游：大圣闹地府！始皇长生啦</t>
+  </si>
+  <si>
+    <t>洪荒八景宫中有逆徒</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
+  </si>
+  <si>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>机甲武神：从矿星开始</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
   </si>
   <si>
     <t>规则怪谈：无所谓，系统会出手</t>
   </si>
   <si>
-    <t>聊天群：混沌魔神？万界该溜子</t>
-  </si>
-  <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
-  </si>
-  <si>
-    <t>从零开始，打造华夏首支特种部队</t>
-  </si>
-  <si>
-    <t>美恐：天真珈百璃，正在开始狩猎</t>
+    <t>火影：扉间问谁断后，我当三代！</t>
   </si>
   <si>
     <t>宿舍求生：糯米可镇不住我们太久</t>
   </si>
   <si>
-    <t>植物大战僵尸恐怖版开局获得电大</t>
-  </si>
-  <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>西游：大圣闹地府！始皇长生啦</t>
+    <t>无声1937</t>
+  </si>
+  <si>
+    <t>穿越黄毛，女主们把我当白月光了</t>
   </si>
   <si>
     <t>说好造桥游戏，打穿天山什么鬼？</t>
   </si>
   <si>
-    <t>名义：谁还不是个汉大帮</t>
-  </si>
-  <si>
-    <t>不会踢球？却成了足球巨星！</t>
-  </si>
-  <si>
-    <t>选择求生：只有我能看到正确答案</t>
-  </si>
-  <si>
-    <t>老师，男生也能报考魔女学院吗？</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
-  </si>
-  <si>
-    <t>开局魅骨词条，我成了宇智波团宠</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>机甲武神：从矿星开始</t>
+    <t>当泰拉上国家来到蓝星</t>
+  </si>
+  <si>
+    <t>斩神：谁说热武器不能斩神</t>
   </si>
   <si>
     <t>天幕让你当废物班长你独断万古？</t>
   </si>
   <si>
-    <t>因为太无敌，我被重生者抢破头？</t>
-  </si>
-  <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>很野很欲，楼下的蔷薇正飘香！</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>让你去救赎，双生校花怎么恶堕了</t>
-  </si>
-  <si>
-    <t>从修仙回到都市，坏消息修为没了</t>
-  </si>
-  <si>
-    <t>无声1937</t>
-  </si>
-  <si>
-    <t>穿越黄毛，女主们把我当白月光了</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>灵气复苏？前世女帝老婆也复苏了</t>
-  </si>
-  <si>
-    <t>重生八零渔村，带仨前妻赶海暴富</t>
-  </si>
-  <si>
-    <t>领证三天，我被未婚妻杀死</t>
+    <t>模拟：少年缺悟性吗？借个脑子吧</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>94</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>414000</v>
+        <v>879000</v>
       </c>
       <c r="G5" s="7">
-        <v>23000</v>
+        <v>86000</v>
       </c>
       <c r="H5" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I5" s="7">
-        <v>31700</v>
+        <v>80667</v>
       </c>
       <c r="J5" s="5">
-        <v>79.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>187000</v>
+        <v>196000</v>
       </c>
       <c r="G6" s="7">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="H6" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I6" s="7">
-        <v>17333</v>
+        <v>14727</v>
       </c>
       <c r="J6" s="5">
-        <v>79.3</v>
+        <v>78.7</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>92.5</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>169000</v>
+        <v>432000</v>
       </c>
       <c r="G7" s="7">
-        <v>26000</v>
+        <v>18000</v>
       </c>
       <c r="H7" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I7" s="7">
-        <v>13500</v>
+        <v>30455</v>
       </c>
       <c r="J7" s="5">
-        <v>78.40000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>81.8</v>
+        <v>94.7</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>940000</v>
+        <v>446000</v>
       </c>
       <c r="G8" s="7">
-        <v>33000</v>
+        <v>27000</v>
       </c>
       <c r="H8" s="7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I8" s="7">
-        <v>52000</v>
+        <v>25364</v>
       </c>
       <c r="J8" s="5">
-        <v>78</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,23 +891,23 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>96.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>344000</v>
+        <v>124000</v>
       </c>
       <c r="G9" s="7">
-        <v>31000</v>
+        <v>24000</v>
       </c>
       <c r="H9" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7">
-        <v>18800</v>
+        <v>12500</v>
       </c>
       <c r="J9" s="5">
         <v>77.90000000000001</v>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>99.2</v>
+        <v>97</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>100000</v>
+        <v>208000</v>
       </c>
       <c r="G10" s="7">
-        <v>30000</v>
+        <v>21000</v>
       </c>
       <c r="H10" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I10" s="7">
-        <v>10857</v>
+        <v>17700</v>
       </c>
       <c r="J10" s="5">
-        <v>77.3</v>
+        <v>77.8</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>87.8</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>793000</v>
+        <v>370000</v>
       </c>
       <c r="G11" s="7">
-        <v>77000</v>
+        <v>26000</v>
       </c>
       <c r="H11" s="7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I11" s="7">
-        <v>78000</v>
+        <v>19455</v>
       </c>
       <c r="J11" s="5">
-        <v>76.8</v>
+        <v>77.3</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>97.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>166000</v>
+        <v>138000</v>
       </c>
       <c r="G12" s="7">
         <v>19000</v>
       </c>
       <c r="H12" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>10600</v>
+        <v>11833</v>
       </c>
       <c r="J12" s="5">
-        <v>76.2</v>
+        <v>77</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>95.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>136000</v>
+        <v>343000</v>
       </c>
       <c r="G13" s="7">
-        <v>14000</v>
+        <v>30000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I13" s="7">
-        <v>13333</v>
+        <v>33500</v>
       </c>
       <c r="J13" s="5">
-        <v>75.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>83.3</v>
+        <v>95.3</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>1058000</v>
+        <v>151000</v>
       </c>
       <c r="G14" s="7">
-        <v>41000</v>
+        <v>15000</v>
       </c>
       <c r="H14" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I14" s="7">
-        <v>38200</v>
+        <v>13571</v>
       </c>
       <c r="J14" s="5">
-        <v>75.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>93</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>328000</v>
+        <v>942000</v>
       </c>
       <c r="G15" s="7">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="H15" s="7">
         <v>10</v>
       </c>
       <c r="I15" s="7">
-        <v>17111</v>
+        <v>46444</v>
       </c>
       <c r="J15" s="5">
-        <v>75.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>98.3</v>
+        <v>81.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>217000</v>
+        <v>1081000</v>
       </c>
       <c r="G16" s="7">
-        <v>32000</v>
+        <v>23000</v>
       </c>
       <c r="H16" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I16" s="7">
-        <v>24500</v>
+        <v>36818</v>
       </c>
       <c r="J16" s="5">
-        <v>75.2</v>
+        <v>74</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>87.59999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>419000</v>
+        <v>164000</v>
       </c>
       <c r="G17" s="7">
-        <v>-2000</v>
+        <v>9000</v>
       </c>
       <c r="H17" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I17" s="7">
-        <v>25200</v>
+        <v>12667</v>
       </c>
       <c r="J17" s="5">
-        <v>74.5</v>
+        <v>73.7</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>96.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>108000</v>
+        <v>402000</v>
       </c>
       <c r="G18" s="7">
-        <v>13000</v>
+        <v>42000</v>
       </c>
       <c r="H18" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I18" s="7">
-        <v>10200</v>
+        <v>15636</v>
       </c>
       <c r="J18" s="5">
-        <v>73.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>96.09999999999999</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>313000</v>
+        <v>153000</v>
       </c>
       <c r="G19" s="7">
-        <v>27000</v>
+        <v>12000</v>
       </c>
       <c r="H19" s="7">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I19" s="7">
-        <v>34667</v>
+        <v>8800</v>
       </c>
       <c r="J19" s="5">
-        <v>73.5</v>
+        <v>72.3</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>90.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>155000</v>
+        <v>139000</v>
       </c>
       <c r="G20" s="7">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H20" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
-        <v>13125</v>
+        <v>11400</v>
       </c>
       <c r="J20" s="5">
-        <v>73.2</v>
+        <v>72.3</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>92.40000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>122000</v>
+        <v>329000</v>
       </c>
       <c r="G21" s="7">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I21" s="7">
-        <v>8571</v>
+        <v>15500</v>
       </c>
       <c r="J21" s="5">
-        <v>73</v>
+        <v>72.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>90.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>360000</v>
+        <v>454000</v>
       </c>
       <c r="G22" s="7">
-        <v>80000</v>
+        <v>41000</v>
       </c>
       <c r="H22" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I22" s="7">
-        <v>13000</v>
+        <v>21727</v>
       </c>
       <c r="J22" s="5">
-        <v>72.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>95.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>123000</v>
+        <v>120000</v>
       </c>
       <c r="G23" s="7">
         <v>12000</v>
       </c>
       <c r="H23" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I23" s="7">
-        <v>1800</v>
+        <v>11400</v>
       </c>
       <c r="J23" s="5">
-        <v>72.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>81.3</v>
+        <v>88.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>1700000</v>
+        <v>256000</v>
       </c>
       <c r="G24" s="7">
-        <v>17000</v>
+        <v>7000</v>
       </c>
       <c r="H24" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I24" s="7">
-        <v>29900</v>
+        <v>11500</v>
       </c>
       <c r="J24" s="5">
-        <v>72.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>90.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>141000</v>
+        <v>172000</v>
       </c>
       <c r="G25" s="7">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="H25" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I25" s="7">
-        <v>8444</v>
+        <v>10182</v>
       </c>
       <c r="J25" s="5">
-        <v>72.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>86.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>382000</v>
+        <v>167000</v>
       </c>
       <c r="G26" s="7">
-        <v>55000</v>
+        <v>10000</v>
       </c>
       <c r="H26" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" s="7">
-        <v>18500</v>
+        <v>2364</v>
       </c>
       <c r="J26" s="5">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>88.2</v>
+        <v>88.7</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>298000</v>
+        <v>132000</v>
       </c>
       <c r="G27" s="7">
-        <v>29000</v>
+        <v>7000</v>
       </c>
       <c r="H27" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I27" s="7">
-        <v>14100</v>
+        <v>9000</v>
       </c>
       <c r="J27" s="5">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>89.8</v>
+        <v>88.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>125000</v>
+        <v>127000</v>
       </c>
       <c r="G28" s="7">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I28" s="7">
-        <v>9333</v>
+        <v>8125</v>
       </c>
       <c r="J28" s="5">
-        <v>71.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>88.7</v>
+        <v>91.3</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>174000</v>
+        <v>132000</v>
       </c>
       <c r="G29" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H29" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I29" s="7">
-        <v>10200</v>
+        <v>2455</v>
       </c>
       <c r="J29" s="5">
-        <v>71.3</v>
+        <v>70.8</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>88.2</v>
+        <v>82.8</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>173000</v>
+        <v>422000</v>
       </c>
       <c r="G30" s="7">
-        <v>10000</v>
+        <v>40000</v>
       </c>
       <c r="H30" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I30" s="7">
-        <v>11000</v>
+        <v>20455</v>
       </c>
       <c r="J30" s="5">
-        <v>71.3</v>
+        <v>70.7</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>87.3</v>
+        <v>88.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>341000</v>
+        <v>129000</v>
       </c>
       <c r="G31" s="7">
-        <v>37000</v>
+        <v>7000</v>
       </c>
       <c r="H31" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I31" s="7">
-        <v>11500</v>
+        <v>7250</v>
       </c>
       <c r="J31" s="5">
-        <v>70.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>174000</v>
+        <v>180000</v>
       </c>
       <c r="G32" s="7">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="H32" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I32" s="7">
-        <v>8600</v>
+        <v>10500</v>
       </c>
       <c r="J32" s="5">
-        <v>70.59999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>78.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>750000</v>
+        <v>334000</v>
       </c>
       <c r="G33" s="7">
-        <v>11000</v>
+        <v>19000</v>
       </c>
       <c r="H33" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I33" s="7">
-        <v>29111</v>
+        <v>26200</v>
       </c>
       <c r="J33" s="5">
-        <v>70.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>86.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>198000</v>
+        <v>244000</v>
       </c>
       <c r="G34" s="7">
-        <v>10000</v>
+        <v>43000</v>
       </c>
       <c r="H34" s="7">
         <v>9</v>
       </c>
       <c r="I34" s="7">
-        <v>10250</v>
+        <v>16375</v>
       </c>
       <c r="J34" s="5">
-        <v>70.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>88.09999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>122000</v>
+        <v>210000</v>
       </c>
       <c r="G35" s="7">
-        <v>6000</v>
+        <v>29000</v>
       </c>
       <c r="H35" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I35" s="7">
-        <v>7286</v>
+        <v>7545</v>
       </c>
       <c r="J35" s="5">
-        <v>70.3</v>
+        <v>70</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>95.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>108000</v>
+        <v>112000</v>
       </c>
       <c r="G36" s="7">
-        <v>16000</v>
+        <v>4000</v>
       </c>
       <c r="H36" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I36" s="7">
-        <v>11250</v>
+        <v>9167</v>
       </c>
       <c r="J36" s="5">
-        <v>70.2</v>
+        <v>69.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>90.3</v>
+        <v>84.8</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>157000</v>
+        <v>220000</v>
       </c>
       <c r="G37" s="7">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="H37" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I37" s="7">
-        <v>1600</v>
+        <v>20200</v>
       </c>
       <c r="J37" s="5">
-        <v>70.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>88.59999999999999</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>249000</v>
+        <v>152000</v>
       </c>
       <c r="G38" s="7">
-        <v>8000</v>
+        <v>0</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I38" s="7">
-        <v>12400</v>
+        <v>10625</v>
       </c>
       <c r="J38" s="5">
-        <v>69.8</v>
+        <v>69.5</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>86.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>222000</v>
+        <v>174000</v>
       </c>
       <c r="G39" s="7">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="H39" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I39" s="7">
-        <v>7667</v>
+        <v>7818</v>
       </c>
       <c r="J39" s="5">
-        <v>69.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>81.2</v>
+        <v>97.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>413000</v>
+        <v>136000</v>
       </c>
       <c r="G40" s="7">
-        <v>34000</v>
+        <v>15000</v>
       </c>
       <c r="H40" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>19800</v>
+        <v>15667</v>
       </c>
       <c r="J40" s="5">
-        <v>69.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>82.8</v>
+        <v>83.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>350000</v>
+        <v>369000</v>
       </c>
       <c r="G41" s="7">
-        <v>22000</v>
+        <v>28000</v>
       </c>
       <c r="H41" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I41" s="7">
-        <v>36000</v>
+        <v>13000</v>
       </c>
       <c r="J41" s="5">
-        <v>69.5</v>
+        <v>69.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>76.5</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>472000</v>
+        <v>314000</v>
       </c>
       <c r="G42" s="7">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I42" s="7">
-        <v>29167</v>
+        <v>14273</v>
       </c>
       <c r="J42" s="5">
-        <v>69.40000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>84.2</v>
+        <v>78.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>152000</v>
+        <v>364000</v>
       </c>
       <c r="G43" s="7">
-        <v>0</v>
+        <v>14000</v>
       </c>
       <c r="H43" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I43" s="7">
-        <v>12143</v>
+        <v>31600</v>
       </c>
       <c r="J43" s="5">
-        <v>69.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.3</v>
+        <v>89</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>181000</v>
+        <v>261000</v>
       </c>
       <c r="G44" s="7">
-        <v>35000</v>
+        <v>5000</v>
       </c>
       <c r="H44" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I44" s="7">
-        <v>5400</v>
+        <v>636</v>
       </c>
       <c r="J44" s="5">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>93</v>
+        <v>78.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>124000</v>
+        <v>1664000</v>
       </c>
       <c r="G45" s="7">
-        <v>13000</v>
+        <v>-36000</v>
       </c>
       <c r="H45" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I45" s="7">
-        <v>10500</v>
+        <v>23909</v>
       </c>
       <c r="J45" s="5">
-        <v>68.8</v>
+        <v>69</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>88.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>256000</v>
+        <v>296000</v>
       </c>
       <c r="G46" s="7">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="H46" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I46" s="7">
-        <v>200</v>
+        <v>364</v>
       </c>
       <c r="J46" s="5">
-        <v>68.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>84.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>116000</v>
+        <v>172000</v>
       </c>
       <c r="G47" s="7">
-        <v>6000</v>
+        <v>-2000</v>
       </c>
       <c r="H47" s="7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I47" s="7">
-        <v>6125</v>
+        <v>9091</v>
       </c>
       <c r="J47" s="5">
-        <v>68.2</v>
+        <v>69</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>81.7</v>
+        <v>81</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>201000</v>
+        <v>485000</v>
       </c>
       <c r="G48" s="7">
-        <v>24000</v>
+        <v>12000</v>
       </c>
       <c r="H48" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I48" s="7">
-        <v>12571</v>
+        <v>17091</v>
       </c>
       <c r="J48" s="5">
-        <v>68.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>79.2</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>473000</v>
+        <v>153000</v>
       </c>
       <c r="G49" s="7">
         <v>4000</v>
       </c>
       <c r="H49" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I49" s="7">
-        <v>17600</v>
+        <v>3818</v>
       </c>
       <c r="J49" s="5">
-        <v>68</v>
+        <v>68.7</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>85.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>149000</v>
+        <v>748000</v>
       </c>
       <c r="G50" s="7">
-        <v>2000</v>
+        <v>-2000</v>
       </c>
       <c r="H50" s="7">
         <v>11</v>
       </c>
       <c r="I50" s="7">
-        <v>3800</v>
+        <v>26000</v>
       </c>
       <c r="J50" s="5">
-        <v>68</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>79.7</v>
+        <v>86.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>398000</v>
+        <v>212000</v>
       </c>
       <c r="G51" s="7">
-        <v>13000</v>
+        <v>5000</v>
       </c>
       <c r="H51" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I51" s="7">
-        <v>15900</v>
+        <v>11200</v>
       </c>
       <c r="J51" s="5">
-        <v>67.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>79.2</v>
+        <v>84</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>364000</v>
+        <v>157000</v>
       </c>
       <c r="G52" s="7">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="H52" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I52" s="7">
-        <v>16400</v>
+        <v>7833</v>
       </c>
       <c r="J52" s="5">
-        <v>67.7</v>
+        <v>68.2</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>84</v>
+        <v>73.3</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>196000</v>
+        <v>495000</v>
       </c>
       <c r="G53" s="7">
-        <v>-5000</v>
+        <v>23000</v>
       </c>
       <c r="H53" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I53" s="7">
-        <v>5800</v>
+        <v>28286</v>
       </c>
       <c r="J53" s="5">
-        <v>67.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>83.7</v>
+        <v>85.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>151000</v>
+        <v>101000</v>
       </c>
       <c r="G54" s="7">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="H54" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I54" s="7">
-        <v>5900</v>
+        <v>1636</v>
       </c>
       <c r="J54" s="5">
-        <v>67.5</v>
+        <v>67.3</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-25T04:36:34+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-26T04:40:38+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>不拱火我来汉东干什么？</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
     <t>凤流高手</t>
   </si>
   <si>
+    <t>综漫：表白被拒就变强？</t>
+  </si>
+  <si>
+    <t>抗美援朝：什么叫这是四合院世界</t>
+  </si>
+  <si>
+    <t>很野很欲，楼下的蔷薇正飘香！</t>
+  </si>
+  <si>
+    <t>十天寿命，买个神话级武魂合理吧</t>
+  </si>
+  <si>
+    <t>选择求生：只有我能看到正确答案</t>
+  </si>
+  <si>
+    <t>游走神话时代，开局拜师道门天师</t>
+  </si>
+  <si>
+    <t>纨绔大少是邪神，眷属全部是美女</t>
+  </si>
+  <si>
+    <t>三角洲：手游主播的我误入巅峰赛</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>洪荒八景宫中有逆徒</t>
+  </si>
+  <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
+  </si>
+  <si>
+    <t>老师，男生也能报考魔女学院吗？</t>
+  </si>
+  <si>
+    <t>火影：越豪越强？胜你无需第二剑</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>白娘子：你不能娶我妹妹小青</t>
+  </si>
+  <si>
+    <t>名义：刚提名省服，你让我退休？</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>全三国重生，我老六身份藏不住了</t>
+  </si>
+  <si>
+    <t>四合院1948亿万富翁躺平生活</t>
+  </si>
+  <si>
+    <t>斩神：零号病人，是死之执政</t>
+  </si>
+  <si>
+    <t>聊天群：混沌魔神？万界该溜子</t>
+  </si>
+  <si>
+    <t>不会踢球？却成了足球巨星！</t>
+  </si>
+  <si>
+    <t>我在红楼世界玩修仙游戏！</t>
+  </si>
+  <si>
+    <t>机甲武神：从矿星开始</t>
+  </si>
+  <si>
+    <t>美恐：天真珈百璃，正在开始狩猎</t>
+  </si>
+  <si>
+    <t>每天一万潜能点，只能给大专生？</t>
+  </si>
+  <si>
     <t>武侠网游，开局三个神级词条</t>
   </si>
   <si>
-    <t>游走神话时代，开局拜师道门天师</t>
-  </si>
-  <si>
-    <t>抗美援朝：什么叫这是四合院世界</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
-  </si>
-  <si>
-    <t>综漫：表白被拒就变强？</t>
-  </si>
-  <si>
-    <t>十天寿命，买个神话级武魂合理吧</t>
-  </si>
-  <si>
-    <t>不拱火我来汉东干什么？</t>
-  </si>
-  <si>
-    <t>三角洲：手游主播的我误入巅峰赛</t>
-  </si>
-  <si>
-    <t>纨绔大少是邪神，眷属全部是美女</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>白娘子：你不能娶我妹妹小青</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>聊天群：混沌魔神？万界该溜子</t>
-  </si>
-  <si>
-    <t>很野很欲，楼下的蔷薇正飘香！</t>
-  </si>
-  <si>
-    <t>名义：刚提名省服，你让我退休？</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>选择求生：只有我能看到正确答案</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
+    <t>当泰拉上国家来到蓝星</t>
+  </si>
+  <si>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
   </si>
   <si>
     <t>带着渡劫修为，重回高中时代</t>
   </si>
   <si>
-    <t>老师，男生也能报考魔女学院吗？</t>
-  </si>
-  <si>
-    <t>美恐：天真珈百璃，正在开始狩猎</t>
-  </si>
-  <si>
-    <t>全三国重生，我老六身份藏不住了</t>
-  </si>
-  <si>
-    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
+    <t>都市剧：这个世界没有好玩的游戏</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>火影：扉间问谁断后，我当三代！</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
   </si>
   <si>
     <t>我跟大明太子摊牌了：要么听我的</t>
   </si>
   <si>
-    <t>不会踢球？却成了足球巨星！</t>
+    <t>穿越黄毛，女主们把我当白月光了</t>
+  </si>
+  <si>
+    <t>要当总统了，你跟我说系统来了？</t>
+  </si>
+  <si>
+    <t>我，原始首徒，封神开局整顿阐教</t>
+  </si>
+  <si>
+    <t>西游：大圣闹地府！始皇长生啦</t>
+  </si>
+  <si>
+    <t>直播我和徐妙云，老朱全家破防了</t>
   </si>
   <si>
     <t>植物大战僵尸恐怖版开局获得电大</t>
   </si>
   <si>
-    <t>都市剧：这个世界没有好玩的游戏</t>
-  </si>
-  <si>
-    <t>从修仙回到都市，坏消息修为没了</t>
-  </si>
-  <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>我，原始首徒，封神开局整顿阐教</t>
-  </si>
-  <si>
-    <t>四合院1948亿万富翁躺平生活</t>
-  </si>
-  <si>
-    <t>因为太无敌，我被重生者抢破头？</t>
-  </si>
-  <si>
-    <t>西游：大圣闹地府！始皇长生啦</t>
-  </si>
-  <si>
-    <t>洪荒八景宫中有逆徒</t>
-  </si>
-  <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>从零开始，打造华夏首支特种部队</t>
-  </si>
-  <si>
-    <t>机甲武神：从矿星开始</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>火影：扉间问谁断后，我当三代！</t>
-  </si>
-  <si>
-    <t>宿舍求生：糯米可镇不住我们太久</t>
-  </si>
-  <si>
-    <t>无声1937</t>
-  </si>
-  <si>
-    <t>穿越黄毛，女主们把我当白月光了</t>
-  </si>
-  <si>
-    <t>说好造桥游戏，打穿天山什么鬼？</t>
-  </si>
-  <si>
-    <t>当泰拉上国家来到蓝星</t>
-  </si>
-  <si>
-    <t>斩神：谁说热武器不能斩神</t>
-  </si>
-  <si>
-    <t>天幕让你当废物班长你独断万古？</t>
-  </si>
-  <si>
-    <t>模拟：少年缺悟性吗？借个脑子吧</t>
+    <t>开局假冒亡牌飞行员，旱地拔葱！</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>88.90000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>879000</v>
+        <v>993000</v>
       </c>
       <c r="G5" s="7">
-        <v>86000</v>
+        <v>114000</v>
       </c>
       <c r="H5" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="7">
-        <v>80667</v>
+        <v>89000</v>
       </c>
       <c r="J5" s="5">
-        <v>81.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>196000</v>
+        <v>381000</v>
       </c>
       <c r="G6" s="7">
-        <v>27000</v>
+        <v>38000</v>
       </c>
       <c r="H6" s="7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I6" s="7">
-        <v>14727</v>
+        <v>34400</v>
       </c>
       <c r="J6" s="5">
-        <v>78.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>432000</v>
+        <v>239000</v>
       </c>
       <c r="G7" s="7">
-        <v>18000</v>
+        <v>31000</v>
       </c>
       <c r="H7" s="7">
         <v>12</v>
       </c>
       <c r="I7" s="7">
-        <v>30455</v>
+        <v>18909</v>
       </c>
       <c r="J7" s="5">
-        <v>78.5</v>
+        <v>79.7</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>446000</v>
+        <v>232000</v>
       </c>
       <c r="G8" s="7">
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="H8" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I8" s="7">
-        <v>25364</v>
+        <v>16500</v>
       </c>
       <c r="J8" s="5">
-        <v>78.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>124000</v>
+        <v>403000</v>
       </c>
       <c r="G9" s="7">
-        <v>24000</v>
+        <v>33000</v>
       </c>
       <c r="H9" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I9" s="7">
-        <v>12500</v>
+        <v>20583</v>
       </c>
       <c r="J9" s="5">
-        <v>77.90000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>208000</v>
+        <v>146000</v>
       </c>
       <c r="G10" s="7">
-        <v>21000</v>
+        <v>22000</v>
       </c>
       <c r="H10" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I10" s="7">
-        <v>17700</v>
+        <v>13556</v>
       </c>
       <c r="J10" s="5">
-        <v>77.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>95.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>370000</v>
+        <v>161000</v>
       </c>
       <c r="G11" s="7">
-        <v>26000</v>
+        <v>22000</v>
       </c>
       <c r="H11" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>19455</v>
+        <v>13167</v>
       </c>
       <c r="J11" s="5">
-        <v>77.3</v>
+        <v>77.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -997,19 +997,19 @@
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>138000</v>
+        <v>156000</v>
       </c>
       <c r="G12" s="7">
-        <v>19000</v>
+        <v>18000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" s="7">
-        <v>11833</v>
+        <v>12714</v>
       </c>
       <c r="J12" s="5">
-        <v>77</v>
+        <v>77.2</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>96.40000000000001</v>
+        <v>95.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>343000</v>
+        <v>136000</v>
       </c>
       <c r="G13" s="7">
-        <v>30000</v>
+        <v>16000</v>
       </c>
       <c r="H13" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>33500</v>
+        <v>12167</v>
       </c>
       <c r="J13" s="5">
-        <v>76.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>95.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>151000</v>
+        <v>454000</v>
       </c>
       <c r="G14" s="7">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="H14" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I14" s="7">
-        <v>13571</v>
+        <v>23917</v>
       </c>
       <c r="J14" s="5">
-        <v>75.8</v>
+        <v>75.5</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>78.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>942000</v>
+        <v>965000</v>
       </c>
       <c r="G15" s="7">
-        <v>2000</v>
+        <v>23000</v>
       </c>
       <c r="H15" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="7">
-        <v>46444</v>
+        <v>44100</v>
       </c>
       <c r="J15" s="5">
-        <v>74.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>81.5</v>
+        <v>94.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>1081000</v>
+        <v>165000</v>
       </c>
       <c r="G16" s="7">
-        <v>23000</v>
+        <v>14000</v>
       </c>
       <c r="H16" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>36818</v>
+        <v>13625</v>
       </c>
       <c r="J16" s="5">
-        <v>74</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>91.90000000000001</v>
+        <v>90</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>164000</v>
+        <v>459000</v>
       </c>
       <c r="G17" s="7">
-        <v>9000</v>
+        <v>57000</v>
       </c>
       <c r="H17" s="7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I17" s="7">
-        <v>12667</v>
+        <v>19083</v>
       </c>
       <c r="J17" s="5">
-        <v>73.7</v>
+        <v>74.3</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>88</v>
+        <v>99.8</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>402000</v>
+        <v>156000</v>
       </c>
       <c r="G18" s="7">
-        <v>42000</v>
+        <v>20000</v>
       </c>
       <c r="H18" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I18" s="7">
-        <v>15636</v>
+        <v>16750</v>
       </c>
       <c r="J18" s="5">
-        <v>72.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>91.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>153000</v>
+        <v>1104000</v>
       </c>
       <c r="G19" s="7">
-        <v>12000</v>
+        <v>23000</v>
       </c>
       <c r="H19" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I19" s="7">
-        <v>8800</v>
+        <v>35667</v>
       </c>
       <c r="J19" s="5">
-        <v>72.3</v>
+        <v>73.7</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>93.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>139000</v>
+        <v>571000</v>
       </c>
       <c r="G20" s="7">
-        <v>15000</v>
+        <v>103000</v>
       </c>
       <c r="H20" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I20" s="7">
-        <v>11400</v>
+        <v>18500</v>
       </c>
       <c r="J20" s="5">
-        <v>72.3</v>
+        <v>73</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>87.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>329000</v>
+        <v>269000</v>
       </c>
       <c r="G21" s="7">
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="H21" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>15500</v>
+        <v>11714</v>
       </c>
       <c r="J21" s="5">
-        <v>72.2</v>
+        <v>72.8</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>84.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>454000</v>
+        <v>182000</v>
       </c>
       <c r="G22" s="7">
-        <v>41000</v>
+        <v>15000</v>
       </c>
       <c r="H22" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I22" s="7">
-        <v>21727</v>
+        <v>3417</v>
       </c>
       <c r="J22" s="5">
-        <v>72.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>93.2</v>
+        <v>96.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>120000</v>
+        <v>188000</v>
       </c>
       <c r="G23" s="7">
-        <v>12000</v>
+        <v>24000</v>
       </c>
       <c r="H23" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23" s="7">
-        <v>11400</v>
+        <v>17500</v>
       </c>
       <c r="J23" s="5">
-        <v>72.09999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>88.2</v>
+        <v>94.5</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>256000</v>
+        <v>280000</v>
       </c>
       <c r="G24" s="7">
-        <v>7000</v>
+        <v>19000</v>
       </c>
       <c r="H24" s="7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I24" s="7">
-        <v>11500</v>
+        <v>2167</v>
       </c>
       <c r="J24" s="5">
-        <v>71.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>88.09999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>172000</v>
+        <v>170000</v>
       </c>
       <c r="G25" s="7">
         <v>6000</v>
       </c>
       <c r="H25" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I25" s="7">
-        <v>10182</v>
+        <v>12000</v>
       </c>
       <c r="J25" s="5">
-        <v>71</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>91.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>167000</v>
+        <v>332000</v>
       </c>
       <c r="G26" s="7">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="H26" s="7">
         <v>12</v>
       </c>
       <c r="I26" s="7">
-        <v>2364</v>
+        <v>14364</v>
       </c>
       <c r="J26" s="5">
-        <v>71</v>
+        <v>72.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>88.7</v>
+        <v>84.2</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>132000</v>
+        <v>495000</v>
       </c>
       <c r="G27" s="7">
-        <v>7000</v>
+        <v>41000</v>
       </c>
       <c r="H27" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I27" s="7">
-        <v>9000</v>
+        <v>23333</v>
       </c>
       <c r="J27" s="5">
-        <v>71</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>88.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>127000</v>
+        <v>134000</v>
       </c>
       <c r="G28" s="7">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="H28" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I28" s="7">
-        <v>8125</v>
+        <v>8000</v>
       </c>
       <c r="J28" s="5">
-        <v>70.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>91.3</v>
+        <v>85.8</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>132000</v>
+        <v>227000</v>
       </c>
       <c r="G29" s="7">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="H29" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>2455</v>
+        <v>18000</v>
       </c>
       <c r="J29" s="5">
-        <v>70.8</v>
+        <v>71.7</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>82.8</v>
+        <v>89.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>422000</v>
+        <v>169000</v>
       </c>
       <c r="G30" s="7">
-        <v>40000</v>
+        <v>15000</v>
       </c>
       <c r="H30" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I30" s="7">
-        <v>20455</v>
+        <v>9333</v>
       </c>
       <c r="J30" s="5">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>88.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>129000</v>
+        <v>162000</v>
       </c>
       <c r="G31" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H31" s="7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I31" s="7">
-        <v>7250</v>
+        <v>8818</v>
       </c>
       <c r="J31" s="5">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>87</v>
+        <v>90.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>180000</v>
+        <v>137000</v>
       </c>
       <c r="G32" s="7">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="H32" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I32" s="7">
-        <v>10500</v>
+        <v>7333</v>
       </c>
       <c r="J32" s="5">
-        <v>70.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>82.8</v>
+        <v>90.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>334000</v>
+        <v>106000</v>
       </c>
       <c r="G33" s="7">
-        <v>19000</v>
+        <v>7000</v>
       </c>
       <c r="H33" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I33" s="7">
-        <v>26200</v>
+        <v>6500</v>
       </c>
       <c r="J33" s="5">
-        <v>70.09999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>83.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>244000</v>
+        <v>383000</v>
       </c>
       <c r="G34" s="7">
-        <v>43000</v>
+        <v>19000</v>
       </c>
       <c r="H34" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I34" s="7">
-        <v>16375</v>
+        <v>29500</v>
       </c>
       <c r="J34" s="5">
-        <v>70.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>87.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>210000</v>
+        <v>140000</v>
       </c>
       <c r="G35" s="7">
-        <v>29000</v>
+        <v>8000</v>
       </c>
       <c r="H35" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>7545</v>
+        <v>8875</v>
       </c>
       <c r="J35" s="5">
-        <v>70</v>
+        <v>71.3</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>86.40000000000001</v>
+        <v>94.3</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>112000</v>
+        <v>166000</v>
       </c>
       <c r="G36" s="7">
-        <v>4000</v>
+        <v>16000</v>
       </c>
       <c r="H36" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I36" s="7">
-        <v>9167</v>
+        <v>17250</v>
       </c>
       <c r="J36" s="5">
-        <v>69.8</v>
+        <v>71.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>84.8</v>
+        <v>79.8</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>220000</v>
+        <v>439000</v>
       </c>
       <c r="G37" s="7">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="H37" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I37" s="7">
-        <v>20200</v>
+        <v>28500</v>
       </c>
       <c r="J37" s="5">
-        <v>69.7</v>
+        <v>71</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>85.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>152000</v>
+        <v>219000</v>
       </c>
       <c r="G38" s="7">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="H38" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I38" s="7">
-        <v>10625</v>
+        <v>10500</v>
       </c>
       <c r="J38" s="5">
-        <v>69.5</v>
+        <v>70.8</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>86.2</v>
+        <v>85.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>174000</v>
+        <v>338000</v>
       </c>
       <c r="G39" s="7">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="H39" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I39" s="7">
-        <v>7818</v>
+        <v>15083</v>
       </c>
       <c r="J39" s="5">
-        <v>69.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>97.2</v>
+        <v>87.8</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>136000</v>
+        <v>242000</v>
       </c>
       <c r="G40" s="7">
-        <v>15000</v>
+        <v>32000</v>
       </c>
       <c r="H40" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I40" s="7">
-        <v>15667</v>
+        <v>9583</v>
       </c>
       <c r="J40" s="5">
-        <v>69.40000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>83.5</v>
+        <v>90.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>369000</v>
+        <v>142000</v>
       </c>
       <c r="G41" s="7">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="H41" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I41" s="7">
-        <v>13000</v>
+        <v>3083</v>
       </c>
       <c r="J41" s="5">
-        <v>69.2</v>
+        <v>70.7</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>82.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>314000</v>
+        <v>177000</v>
       </c>
       <c r="G42" s="7">
-        <v>16000</v>
+        <v>5000</v>
       </c>
       <c r="H42" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I42" s="7">
-        <v>14273</v>
+        <v>9750</v>
       </c>
       <c r="J42" s="5">
-        <v>69.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>78.5</v>
+        <v>80.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>364000</v>
+        <v>346000</v>
       </c>
       <c r="G43" s="7">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="H43" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="7">
-        <v>31600</v>
+        <v>23833</v>
       </c>
       <c r="J43" s="5">
-        <v>69.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>89</v>
+        <v>80.5</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>261000</v>
+        <v>1668000</v>
       </c>
       <c r="G44" s="7">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H44" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I44" s="7">
-        <v>636</v>
+        <v>22250</v>
       </c>
       <c r="J44" s="5">
-        <v>69.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>78.2</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>1664000</v>
+        <v>305000</v>
       </c>
       <c r="G45" s="7">
-        <v>-36000</v>
+        <v>9000</v>
       </c>
       <c r="H45" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I45" s="7">
-        <v>23909</v>
+        <v>1083</v>
       </c>
       <c r="J45" s="5">
-        <v>69</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>88.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>296000</v>
+        <v>397000</v>
       </c>
       <c r="G46" s="7">
-        <v>7000</v>
+        <v>28000</v>
       </c>
       <c r="H46" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I46" s="7">
-        <v>364</v>
+        <v>14250</v>
       </c>
       <c r="J46" s="5">
-        <v>69</v>
+        <v>69.3</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>85</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>172000</v>
+        <v>450000</v>
       </c>
       <c r="G47" s="7">
-        <v>-2000</v>
+        <v>28000</v>
       </c>
       <c r="H47" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I47" s="7">
-        <v>9091</v>
+        <v>21083</v>
       </c>
       <c r="J47" s="5">
-        <v>69</v>
+        <v>69.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>81</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>485000</v>
+        <v>158000</v>
       </c>
       <c r="G48" s="7">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="H48" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I48" s="7">
-        <v>17091</v>
+        <v>3917</v>
       </c>
       <c r="J48" s="5">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>86.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>153000</v>
+        <v>154000</v>
       </c>
       <c r="G49" s="7">
         <v>4000</v>
       </c>
       <c r="H49" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I49" s="7">
-        <v>3818</v>
+        <v>1750</v>
       </c>
       <c r="J49" s="5">
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>76.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>748000</v>
+        <v>114000</v>
       </c>
       <c r="G50" s="7">
-        <v>-2000</v>
+        <v>2000</v>
       </c>
       <c r="H50" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I50" s="7">
-        <v>26000</v>
+        <v>8143</v>
       </c>
       <c r="J50" s="5">
-        <v>68.59999999999999</v>
+        <v>69</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>86.5</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>212000</v>
+        <v>173000</v>
       </c>
       <c r="G51" s="7">
-        <v>5000</v>
+        <v>-1000</v>
       </c>
       <c r="H51" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I51" s="7">
-        <v>11200</v>
+        <v>7083</v>
       </c>
       <c r="J51" s="5">
-        <v>68.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84</v>
+        <v>81.8</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>157000</v>
+        <v>707000</v>
       </c>
       <c r="G52" s="7">
-        <v>7000</v>
+        <v>39000</v>
       </c>
       <c r="H52" s="7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I52" s="7">
-        <v>7833</v>
+        <v>14417</v>
       </c>
       <c r="J52" s="5">
-        <v>68.2</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>73.3</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>495000</v>
+        <v>182000</v>
       </c>
       <c r="G53" s="7">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="H53" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I53" s="7">
-        <v>28286</v>
+        <v>9556</v>
       </c>
       <c r="J53" s="5">
-        <v>67.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>85.2</v>
+        <v>88.8</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>101000</v>
+        <v>173000</v>
       </c>
       <c r="G54" s="7">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="H54" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I54" s="7">
-        <v>1636</v>
+        <v>18250</v>
       </c>
       <c r="J54" s="5">
-        <v>67.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-26T04:40:38+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-27T05:00:21+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -82,145 +82,145 @@
     <t>什么叫我成了灭世级怪谈？</t>
   </si>
   <si>
+    <t>抗美援朝：什么叫这是四合院世界</t>
+  </si>
+  <si>
     <t>凤流高手</t>
   </si>
   <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
     <t>综漫：表白被拒就变强？</t>
   </si>
   <si>
-    <t>抗美援朝：什么叫这是四合院世界</t>
-  </si>
-  <si>
     <t>很野很欲，楼下的蔷薇正飘香！</t>
   </si>
   <si>
+    <t>我在新西兰当牧场大佬</t>
+  </si>
+  <si>
+    <t>火影：越豪越强？胜你无需第二剑</t>
+  </si>
+  <si>
+    <t>三角洲：手游主播的我误入巅峰赛</t>
+  </si>
+  <si>
+    <t>选择求生：只有我能看到正确答案</t>
+  </si>
+  <si>
+    <t>洪荒八景宫中有逆徒</t>
+  </si>
+  <si>
+    <t>盗墓：八岁创雷法，震惊张海琪</t>
+  </si>
+  <si>
+    <t>纨绔大少是邪神，眷属全部是美女</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>游走神话时代，开局拜师道门天师</t>
+  </si>
+  <si>
     <t>十天寿命，买个神话级武魂合理吧</t>
   </si>
   <si>
-    <t>选择求生：只有我能看到正确答案</t>
-  </si>
-  <si>
-    <t>游走神话时代，开局拜师道门天师</t>
-  </si>
-  <si>
-    <t>纨绔大少是邪神，眷属全部是美女</t>
-  </si>
-  <si>
-    <t>三角洲：手游主播的我误入巅峰赛</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>洪荒八景宫中有逆徒</t>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>斩神：零号病人，是死之执政</t>
+  </si>
+  <si>
+    <t>每天一万潜能点，只能给大专生？</t>
+  </si>
+  <si>
+    <t>让你去养老大队，你破惊天奇案？</t>
+  </si>
+  <si>
+    <t>老师，男生也能报考魔女学院吗？</t>
+  </si>
+  <si>
+    <t>旧日余烬</t>
+  </si>
+  <si>
+    <t>开局假冒亡牌飞行员，旱地拔葱！</t>
+  </si>
+  <si>
+    <t>不会踢球？却成了足球巨星！</t>
+  </si>
+  <si>
+    <t>分家只给破木船？我靠赶海赚麻了</t>
+  </si>
+  <si>
+    <t>四合院1948亿万富翁躺平生活</t>
+  </si>
+  <si>
+    <t>跑男：系统过于抽象，还好我也是</t>
+  </si>
+  <si>
+    <t>我在红楼世界玩修仙游戏！</t>
+  </si>
+  <si>
+    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>名义：刚提名省服，你让我退休？</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>白娘子：你不能娶我妹妹小青</t>
+  </si>
+  <si>
+    <t>机甲武神：从矿星开始</t>
   </si>
   <si>
     <t>点子王行动哥随便弟，三人行很刑</t>
   </si>
   <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
-  </si>
-  <si>
-    <t>老师，男生也能报考魔女学院吗？</t>
-  </si>
-  <si>
-    <t>火影：越豪越强？胜你无需第二剑</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>白娘子：你不能娶我妹妹小青</t>
-  </si>
-  <si>
-    <t>名义：刚提名省服，你让我退休？</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>美恐：天真珈百璃，正在开始狩猎</t>
+  </si>
+  <si>
+    <t>抗战：我黄埔元老开局打爆小鬼子</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
   </si>
   <si>
     <t>全三国重生，我老六身份藏不住了</t>
   </si>
   <si>
-    <t>四合院1948亿万富翁躺平生活</t>
-  </si>
-  <si>
-    <t>斩神：零号病人，是死之执政</t>
-  </si>
-  <si>
     <t>聊天群：混沌魔神？万界该溜子</t>
   </si>
   <si>
-    <t>不会踢球？却成了足球巨星！</t>
-  </si>
-  <si>
-    <t>我在红楼世界玩修仙游戏！</t>
-  </si>
-  <si>
-    <t>机甲武神：从矿星开始</t>
-  </si>
-  <si>
-    <t>美恐：天真珈百璃，正在开始狩猎</t>
-  </si>
-  <si>
-    <t>每天一万潜能点，只能给大专生？</t>
-  </si>
-  <si>
-    <t>武侠网游，开局三个神级词条</t>
-  </si>
-  <si>
-    <t>当泰拉上国家来到蓝星</t>
-  </si>
-  <si>
-    <t>从零开始，打造华夏首支特种部队</t>
+    <t>都市剧：这个世界没有好玩的游戏</t>
   </si>
   <si>
     <t>综漫：异种族评鉴指南</t>
   </si>
   <si>
-    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
-  </si>
-  <si>
     <t>带着渡劫修为，重回高中时代</t>
   </si>
   <si>
-    <t>都市剧：这个世界没有好玩的游戏</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
     <t>火影：扉间问谁断后，我当三代！</t>
   </si>
   <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
-  </si>
-  <si>
-    <t>穿越黄毛，女主们把我当白月光了</t>
-  </si>
-  <si>
-    <t>要当总统了，你跟我说系统来了？</t>
-  </si>
-  <si>
-    <t>我，原始首徒，封神开局整顿阐教</t>
-  </si>
-  <si>
-    <t>西游：大圣闹地府！始皇长生啦</t>
-  </si>
-  <si>
-    <t>直播我和徐妙云，老朱全家破防了</t>
-  </si>
-  <si>
-    <t>植物大战僵尸恐怖版开局获得电大</t>
-  </si>
-  <si>
-    <t>开局假冒亡牌飞行员，旱地拔葱！</t>
+    <t>点赞送系统，开局请关圣帝君斩诡</t>
+  </si>
+  <si>
+    <t>被富婆女粉抓住后，我财富自由了</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>91.3</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>993000</v>
+        <v>1057000</v>
       </c>
       <c r="G5" s="7">
-        <v>114000</v>
+        <v>64000</v>
       </c>
       <c r="H5" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
-        <v>89000</v>
+        <v>84000</v>
       </c>
       <c r="J5" s="5">
-        <v>87.5</v>
+        <v>85.7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>98.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>381000</v>
+        <v>420000</v>
       </c>
       <c r="G6" s="7">
-        <v>38000</v>
+        <v>39000</v>
       </c>
       <c r="H6" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>34400</v>
+        <v>35167</v>
       </c>
       <c r="J6" s="5">
-        <v>80.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>239000</v>
+        <v>267000</v>
       </c>
       <c r="G7" s="7">
-        <v>31000</v>
+        <v>28000</v>
       </c>
       <c r="H7" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I7" s="7">
-        <v>18909</v>
+        <v>19667</v>
       </c>
       <c r="J7" s="5">
-        <v>79.7</v>
+        <v>78.8</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>232000</v>
+        <v>166000</v>
       </c>
       <c r="G8" s="7">
-        <v>36000</v>
+        <v>20000</v>
       </c>
       <c r="H8" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I8" s="7">
-        <v>16500</v>
+        <v>14200</v>
       </c>
       <c r="J8" s="5">
-        <v>79.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>96.90000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>403000</v>
+        <v>258000</v>
       </c>
       <c r="G9" s="7">
-        <v>33000</v>
+        <v>26000</v>
       </c>
       <c r="H9" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I9" s="7">
-        <v>20583</v>
+        <v>17231</v>
       </c>
       <c r="J9" s="5">
-        <v>78.40000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>146000</v>
+        <v>700000</v>
       </c>
       <c r="G10" s="7">
-        <v>22000</v>
+        <v>129000</v>
       </c>
       <c r="H10" s="7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I10" s="7">
-        <v>13556</v>
+        <v>27000</v>
       </c>
       <c r="J10" s="5">
-        <v>78.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>98.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>161000</v>
+        <v>428000</v>
       </c>
       <c r="G11" s="7">
-        <v>22000</v>
+        <v>25000</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I11" s="7">
-        <v>13167</v>
+        <v>20923</v>
       </c>
       <c r="J11" s="5">
-        <v>77.5</v>
+        <v>77.2</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>98.2</v>
+        <v>97</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>156000</v>
+        <v>181000</v>
       </c>
       <c r="G12" s="7">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="H12" s="7">
         <v>8</v>
       </c>
       <c r="I12" s="7">
-        <v>12714</v>
+        <v>14143</v>
       </c>
       <c r="J12" s="5">
-        <v>77.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>95.7</v>
+        <v>99</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>136000</v>
+        <v>110000</v>
       </c>
       <c r="G13" s="7">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I13" s="7">
-        <v>12167</v>
+        <v>5400</v>
       </c>
       <c r="J13" s="5">
-        <v>75.7</v>
+        <v>75.8</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>90.09999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>454000</v>
+        <v>212000</v>
       </c>
       <c r="G14" s="7">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="H14" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>23917</v>
+        <v>18800</v>
       </c>
       <c r="J14" s="5">
-        <v>75.5</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>80.7</v>
+        <v>93.5</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>965000</v>
+        <v>177000</v>
       </c>
       <c r="G15" s="7">
-        <v>23000</v>
+        <v>12000</v>
       </c>
       <c r="H15" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I15" s="7">
-        <v>44100</v>
+        <v>13444</v>
       </c>
       <c r="J15" s="5">
-        <v>75.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>94.5</v>
+        <v>93.8</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>165000</v>
+        <v>148000</v>
       </c>
       <c r="G16" s="7">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="H16" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I16" s="7">
-        <v>13625</v>
+        <v>12143</v>
       </c>
       <c r="J16" s="5">
-        <v>75.40000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>90</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>459000</v>
+        <v>171000</v>
       </c>
       <c r="G17" s="7">
-        <v>57000</v>
+        <v>15000</v>
       </c>
       <c r="H17" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>19083</v>
+        <v>16400</v>
       </c>
       <c r="J17" s="5">
         <v>74.3</v>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>99.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>156000</v>
+        <v>102000</v>
       </c>
       <c r="G18" s="7">
-        <v>20000</v>
+        <v>9000</v>
       </c>
       <c r="H18" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I18" s="7">
-        <v>16750</v>
+        <v>9333</v>
       </c>
       <c r="J18" s="5">
-        <v>74.09999999999999</v>
+        <v>74</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>81.5</v>
+        <v>78.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>1104000</v>
+        <v>967000</v>
       </c>
       <c r="G19" s="7">
-        <v>23000</v>
+        <v>2000</v>
       </c>
       <c r="H19" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I19" s="7">
-        <v>35667</v>
+        <v>40273</v>
       </c>
       <c r="J19" s="5">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>87.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>571000</v>
+        <v>502000</v>
       </c>
       <c r="G20" s="7">
-        <v>103000</v>
+        <v>43000</v>
       </c>
       <c r="H20" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I20" s="7">
-        <v>18500</v>
+        <v>20923</v>
       </c>
       <c r="J20" s="5">
-        <v>73</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>90.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>269000</v>
+        <v>446000</v>
       </c>
       <c r="G21" s="7">
-        <v>13000</v>
+        <v>-8000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I21" s="7">
-        <v>11714</v>
+        <v>21462</v>
       </c>
       <c r="J21" s="5">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,23 +1320,23 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>94.40000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>182000</v>
+        <v>164000</v>
       </c>
       <c r="G22" s="7">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="H22" s="7">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I22" s="7">
-        <v>3417</v>
+        <v>12125</v>
       </c>
       <c r="J22" s="5">
         <v>72.8</v>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>96.8</v>
+        <v>94.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>188000</v>
+        <v>299000</v>
       </c>
       <c r="G23" s="7">
-        <v>24000</v>
+        <v>19000</v>
       </c>
       <c r="H23" s="7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I23" s="7">
-        <v>17500</v>
+        <v>3462</v>
       </c>
       <c r="J23" s="5">
-        <v>72.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>94.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>280000</v>
+        <v>186000</v>
       </c>
       <c r="G24" s="7">
-        <v>19000</v>
+        <v>17000</v>
       </c>
       <c r="H24" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I24" s="7">
-        <v>2167</v>
+        <v>10429</v>
       </c>
       <c r="J24" s="5">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,23 +1419,23 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89.8</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>170000</v>
+        <v>180000</v>
       </c>
       <c r="G25" s="7">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="H25" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I25" s="7">
-        <v>12000</v>
+        <v>16600</v>
       </c>
       <c r="J25" s="5">
         <v>72.40000000000001</v>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>88.5</v>
+        <v>92.3</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>332000</v>
+        <v>104000</v>
       </c>
       <c r="G26" s="7">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="H26" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I26" s="7">
-        <v>14364</v>
+        <v>5615</v>
       </c>
       <c r="J26" s="5">
-        <v>72.3</v>
+        <v>72.2</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,23 +1485,23 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>84.2</v>
+        <v>92.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>495000</v>
+        <v>195000</v>
       </c>
       <c r="G27" s="7">
-        <v>41000</v>
+        <v>13000</v>
       </c>
       <c r="H27" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I27" s="7">
-        <v>23333</v>
+        <v>4154</v>
       </c>
       <c r="J27" s="5">
         <v>72.09999999999999</v>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>91.09999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>134000</v>
+        <v>118000</v>
       </c>
       <c r="G28" s="7">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H28" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>8000</v>
+        <v>7833</v>
       </c>
       <c r="J28" s="5">
-        <v>72.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>85.8</v>
+        <v>90.2</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>227000</v>
+        <v>184000</v>
       </c>
       <c r="G29" s="7">
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I29" s="7">
-        <v>18000</v>
+        <v>16800</v>
       </c>
       <c r="J29" s="5">
-        <v>71.7</v>
+        <v>71.8</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89.2</v>
+        <v>90.8</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>169000</v>
+        <v>145000</v>
       </c>
       <c r="G30" s="7">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="H30" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I30" s="7">
-        <v>9333</v>
+        <v>7400</v>
       </c>
       <c r="J30" s="5">
-        <v>71.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>89.40000000000001</v>
+        <v>92</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>162000</v>
+        <v>100000</v>
       </c>
       <c r="G31" s="7">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="H31" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I31" s="7">
-        <v>8818</v>
+        <v>5000</v>
       </c>
       <c r="J31" s="5">
-        <v>71.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>90.2</v>
+        <v>86.5</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>137000</v>
+        <v>232000</v>
       </c>
       <c r="G32" s="7">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H32" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>7333</v>
+        <v>16143</v>
       </c>
       <c r="J32" s="5">
-        <v>71.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,23 +1683,23 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>90.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>106000</v>
+        <v>168000</v>
       </c>
       <c r="G33" s="7">
-        <v>7000</v>
+        <v>14000</v>
       </c>
       <c r="H33" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I33" s="7">
-        <v>6500</v>
+        <v>13000</v>
       </c>
       <c r="J33" s="5">
         <v>71.40000000000001</v>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>79.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>383000</v>
+        <v>112000</v>
       </c>
       <c r="G34" s="7">
-        <v>19000</v>
+        <v>6000</v>
       </c>
       <c r="H34" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I34" s="7">
-        <v>29500</v>
+        <v>6455</v>
       </c>
       <c r="J34" s="5">
-        <v>71.3</v>
+        <v>71.2</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>89.3</v>
+        <v>91.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>140000</v>
+        <v>152000</v>
       </c>
       <c r="G35" s="7">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H35" s="7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I35" s="7">
-        <v>8875</v>
+        <v>3615</v>
       </c>
       <c r="J35" s="5">
-        <v>71.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>94.3</v>
+        <v>81.8</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>166000</v>
+        <v>519000</v>
       </c>
       <c r="G36" s="7">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="H36" s="7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I36" s="7">
-        <v>17250</v>
+        <v>23385</v>
       </c>
       <c r="J36" s="5">
-        <v>71.2</v>
+        <v>70.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>79.8</v>
+        <v>86.2</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>439000</v>
+        <v>330000</v>
       </c>
       <c r="G37" s="7">
-        <v>7000</v>
+        <v>-2000</v>
       </c>
       <c r="H37" s="7">
         <v>13</v>
       </c>
       <c r="I37" s="7">
-        <v>28500</v>
+        <v>13000</v>
       </c>
       <c r="J37" s="5">
-        <v>71</v>
+        <v>70.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>87.5</v>
+        <v>82</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>219000</v>
+        <v>481000</v>
       </c>
       <c r="G38" s="7">
-        <v>7000</v>
+        <v>31000</v>
       </c>
       <c r="H38" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I38" s="7">
-        <v>10500</v>
+        <v>21846</v>
       </c>
       <c r="J38" s="5">
-        <v>70.8</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>85.3</v>
+        <v>81.7</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>338000</v>
+        <v>1692000</v>
       </c>
       <c r="G39" s="7">
         <v>24000</v>
       </c>
       <c r="H39" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I39" s="7">
-        <v>15083</v>
+        <v>22385</v>
       </c>
       <c r="J39" s="5">
-        <v>70.7</v>
+        <v>70.5</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>87.8</v>
+        <v>86.8</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>242000</v>
+        <v>171000</v>
       </c>
       <c r="G40" s="7">
-        <v>32000</v>
+        <v>1000</v>
       </c>
       <c r="H40" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I40" s="7">
-        <v>9583</v>
+        <v>11000</v>
       </c>
       <c r="J40" s="5">
-        <v>70.7</v>
+        <v>70.5</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>90.8</v>
+        <v>78.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>142000</v>
+        <v>399000</v>
       </c>
       <c r="G41" s="7">
-        <v>10000</v>
+        <v>16000</v>
       </c>
       <c r="H41" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I41" s="7">
-        <v>3083</v>
+        <v>27571</v>
       </c>
       <c r="J41" s="5">
-        <v>70.7</v>
+        <v>70.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>87.5</v>
+        <v>76.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>177000</v>
+        <v>1073000</v>
       </c>
       <c r="G42" s="7">
-        <v>5000</v>
+        <v>-31000</v>
       </c>
       <c r="H42" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I42" s="7">
-        <v>9750</v>
+        <v>30538</v>
       </c>
       <c r="J42" s="5">
-        <v>70.59999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>80.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>346000</v>
+        <v>357000</v>
       </c>
       <c r="G43" s="7">
-        <v>12000</v>
+        <v>19000</v>
       </c>
       <c r="H43" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I43" s="7">
-        <v>23833</v>
+        <v>15385</v>
       </c>
       <c r="J43" s="5">
-        <v>70.2</v>
+        <v>69.7</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>80.5</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>1668000</v>
+        <v>144000</v>
       </c>
       <c r="G44" s="7">
         <v>4000</v>
       </c>
       <c r="H44" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I44" s="7">
-        <v>22250</v>
+        <v>8333</v>
       </c>
       <c r="J44" s="5">
-        <v>69.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>89.59999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>305000</v>
+        <v>107000</v>
       </c>
       <c r="G45" s="7">
-        <v>9000</v>
+        <v>16000</v>
       </c>
       <c r="H45" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
-        <v>1083</v>
+        <v>16667</v>
       </c>
       <c r="J45" s="5">
-        <v>69.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,23 +2112,23 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>83.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>397000</v>
+        <v>422000</v>
       </c>
       <c r="G46" s="7">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="H46" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I46" s="7">
-        <v>14250</v>
+        <v>15077</v>
       </c>
       <c r="J46" s="5">
         <v>69.3</v>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>79.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>450000</v>
+        <v>135000</v>
       </c>
       <c r="G47" s="7">
-        <v>28000</v>
+        <v>1000</v>
       </c>
       <c r="H47" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I47" s="7">
-        <v>21083</v>
+        <v>7300</v>
       </c>
       <c r="J47" s="5">
-        <v>69.2</v>
+        <v>69.3</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.59999999999999</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>158000</v>
+        <v>165000</v>
       </c>
       <c r="G48" s="7">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H48" s="7">
         <v>13</v>
       </c>
       <c r="I48" s="7">
-        <v>3917</v>
+        <v>8333</v>
       </c>
       <c r="J48" s="5">
-        <v>69.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>88.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>154000</v>
+        <v>353000</v>
       </c>
       <c r="G49" s="7">
-        <v>4000</v>
+        <v>7000</v>
       </c>
       <c r="H49" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I49" s="7">
-        <v>1750</v>
+        <v>21429</v>
       </c>
       <c r="J49" s="5">
-        <v>69.2</v>
+        <v>68.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>85.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>114000</v>
+        <v>266000</v>
       </c>
       <c r="G50" s="7">
-        <v>2000</v>
+        <v>24000</v>
       </c>
       <c r="H50" s="7">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I50" s="7">
-        <v>8143</v>
+        <v>10692</v>
       </c>
       <c r="J50" s="5">
-        <v>69</v>
+        <v>68.7</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.59999999999999</v>
+        <v>84</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>173000</v>
+        <v>176000</v>
       </c>
       <c r="G51" s="7">
         <v>-1000</v>
       </c>
       <c r="H51" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I51" s="7">
-        <v>7083</v>
+        <v>8923</v>
       </c>
       <c r="J51" s="5">
-        <v>68.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>81.8</v>
+        <v>87.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>707000</v>
+        <v>307000</v>
       </c>
       <c r="G52" s="7">
-        <v>39000</v>
+        <v>2000</v>
       </c>
       <c r="H52" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I52" s="7">
-        <v>14417</v>
+        <v>1154</v>
       </c>
       <c r="J52" s="5">
-        <v>68.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>84.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>182000</v>
+        <v>334000</v>
       </c>
       <c r="G53" s="7">
-        <v>2000</v>
+        <v>23000</v>
       </c>
       <c r="H53" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I53" s="7">
-        <v>9556</v>
+        <v>21333</v>
       </c>
       <c r="J53" s="5">
-        <v>68.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>88.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>173000</v>
+        <v>213000</v>
       </c>
       <c r="G54" s="7">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="H54" s="7">
         <v>5</v>
       </c>
       <c r="I54" s="7">
-        <v>18250</v>
+        <v>14250</v>
       </c>
       <c r="J54" s="5">
-        <v>68.40000000000001</v>
+        <v>68</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-27T05:00:21+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-28T05:01:53+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>不拱火我来汉东干什么？</t>
   </si>
   <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>火影：越豪越强？胜你无需第二剑</t>
+  </si>
+  <si>
     <t>什么叫我成了灭世级怪谈？</t>
   </si>
   <si>
     <t>抗美援朝：什么叫这是四合院世界</t>
   </si>
   <si>
+    <t>很野很欲，楼下的蔷薇正飘香！</t>
+  </si>
+  <si>
+    <t>我，原始首徒，封神开局整顿阐教</t>
+  </si>
+  <si>
     <t>凤流高手</t>
   </si>
   <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>综漫：表白被拒就变强？</t>
-  </si>
-  <si>
-    <t>很野很欲，楼下的蔷薇正飘香！</t>
-  </si>
-  <si>
-    <t>我在新西兰当牧场大佬</t>
-  </si>
-  <si>
-    <t>火影：越豪越强？胜你无需第二剑</t>
+    <t>选择求生：只有我能看到正确答案</t>
   </si>
   <si>
     <t>三角洲：手游主播的我误入巅峰赛</t>
   </si>
   <si>
-    <t>选择求生：只有我能看到正确答案</t>
+    <t>盗墓：八岁创雷法，震惊张海琪</t>
+  </si>
+  <si>
+    <t>重生：躺平的低调人生</t>
+  </si>
+  <si>
+    <t>游走神话时代，开局拜师道门天师</t>
+  </si>
+  <si>
+    <t>每天一万潜能点，只能给大专生？</t>
+  </si>
+  <si>
+    <t>抗战：我黄埔元老开局打爆小鬼子</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>四合院：整顿家风，从我妈开始</t>
+  </si>
+  <si>
+    <t>跑男：系统过于抽象，还好我也是</t>
+  </si>
+  <si>
+    <t>分家只给破木船？我靠赶海赚麻了</t>
+  </si>
+  <si>
+    <t>让你去养老大队，你破惊天奇案？</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>四合院1948亿万富翁躺平生活</t>
+  </si>
+  <si>
+    <t>开局假冒亡牌飞行员，旱地拔葱！</t>
+  </si>
+  <si>
+    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
+  </si>
+  <si>
+    <t>我在红楼世界玩修仙游戏！</t>
+  </si>
+  <si>
+    <t>主角死后，未婚妻跟反派的我享福</t>
+  </si>
+  <si>
+    <t>斩神：零号病人，是死之执政</t>
+  </si>
+  <si>
+    <t>都市剧：这个世界没有好玩的游戏</t>
+  </si>
+  <si>
+    <t>衰神气运逆转，回老家享受生活</t>
+  </si>
+  <si>
+    <t>接待意难平的古人，老祖宗全看着</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>纨绔大少是邪神，眷属全部是美女</t>
+  </si>
+  <si>
+    <t>旧日余烬</t>
+  </si>
+  <si>
+    <t>带着渡劫修为，重回高中时代</t>
+  </si>
+  <si>
+    <t>疯掉后，我的故事让全国人痛哭</t>
+  </si>
+  <si>
+    <t>机甲武神：从矿星开始</t>
+  </si>
+  <si>
+    <t>女尊：你们快放开我男朋友！</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>全民穿越！我在末日世界养城兽</t>
+  </si>
+  <si>
+    <t>宿舍求生：糯米可镇不住我们太久</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
+  </si>
+  <si>
+    <t>不会踢球？却成了足球巨星！</t>
+  </si>
+  <si>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>直播见证神话：从鳌太线走蛟开始</t>
+  </si>
+  <si>
+    <t>直播我和徐妙云，老朱全家破防了</t>
   </si>
   <si>
     <t>洪荒八景宫中有逆徒</t>
   </si>
   <si>
-    <t>盗墓：八岁创雷法，震惊张海琪</t>
-  </si>
-  <si>
-    <t>纨绔大少是邪神，眷属全部是美女</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>游走神话时代，开局拜师道门天师</t>
-  </si>
-  <si>
-    <t>十天寿命，买个神话级武魂合理吧</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>斩神：零号病人，是死之执政</t>
-  </si>
-  <si>
-    <t>每天一万潜能点，只能给大专生？</t>
-  </si>
-  <si>
-    <t>让你去养老大队，你破惊天奇案？</t>
-  </si>
-  <si>
-    <t>老师，男生也能报考魔女学院吗？</t>
-  </si>
-  <si>
-    <t>旧日余烬</t>
-  </si>
-  <si>
-    <t>开局假冒亡牌飞行员，旱地拔葱！</t>
-  </si>
-  <si>
-    <t>不会踢球？却成了足球巨星！</t>
-  </si>
-  <si>
-    <t>分家只给破木船？我靠赶海赚麻了</t>
-  </si>
-  <si>
-    <t>四合院1948亿万富翁躺平生活</t>
-  </si>
-  <si>
-    <t>跑男：系统过于抽象，还好我也是</t>
-  </si>
-  <si>
-    <t>我在红楼世界玩修仙游戏！</t>
-  </si>
-  <si>
-    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>名义：刚提名省服，你让我退休？</t>
-  </si>
-  <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>白娘子：你不能娶我妹妹小青</t>
-  </si>
-  <si>
-    <t>机甲武神：从矿星开始</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>从零开始，打造华夏首支特种部队</t>
-  </si>
-  <si>
-    <t>美恐：天真珈百璃，正在开始狩猎</t>
-  </si>
-  <si>
-    <t>抗战：我黄埔元老开局打爆小鬼子</t>
-  </si>
-  <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
     <t>全三国重生，我老六身份藏不住了</t>
-  </si>
-  <si>
-    <t>聊天群：混沌魔神？万界该溜子</t>
-  </si>
-  <si>
-    <t>都市剧：这个世界没有好玩的游戏</t>
-  </si>
-  <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>带着渡劫修为，重回高中时代</t>
-  </si>
-  <si>
-    <t>火影：扉间问谁断后，我当三代！</t>
-  </si>
-  <si>
-    <t>点赞送系统，开局请关圣帝君斩诡</t>
-  </si>
-  <si>
-    <t>被富婆女粉抓住后，我财富自由了</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>84.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1057000</v>
+        <v>1133000</v>
       </c>
       <c r="G5" s="7">
-        <v>64000</v>
+        <v>76000</v>
       </c>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="7">
-        <v>84000</v>
+        <v>82667</v>
       </c>
       <c r="J5" s="5">
-        <v>85.7</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>98.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>420000</v>
+        <v>466000</v>
       </c>
       <c r="G6" s="7">
-        <v>39000</v>
+        <v>46000</v>
       </c>
       <c r="H6" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="7">
-        <v>35167</v>
+        <v>36714</v>
       </c>
       <c r="J6" s="5">
-        <v>82.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>98</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>267000</v>
+        <v>809000</v>
       </c>
       <c r="G7" s="7">
-        <v>28000</v>
+        <v>109000</v>
       </c>
       <c r="H7" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I7" s="7">
-        <v>19667</v>
+        <v>32857</v>
       </c>
       <c r="J7" s="5">
-        <v>78.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>166000</v>
+        <v>232000</v>
       </c>
       <c r="G8" s="7">
         <v>20000</v>
       </c>
       <c r="H8" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>14200</v>
+        <v>19000</v>
       </c>
       <c r="J8" s="5">
-        <v>78</v>
+        <v>77.2</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>97.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>258000</v>
+        <v>289000</v>
       </c>
       <c r="G9" s="7">
-        <v>26000</v>
+        <v>22000</v>
       </c>
       <c r="H9" s="7">
         <v>14</v>
       </c>
       <c r="I9" s="7">
-        <v>17231</v>
+        <v>19846</v>
       </c>
       <c r="J9" s="5">
-        <v>77.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>91.7</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>700000</v>
+        <v>183000</v>
       </c>
       <c r="G10" s="7">
-        <v>129000</v>
+        <v>17000</v>
       </c>
       <c r="H10" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I10" s="7">
-        <v>27000</v>
+        <v>14455</v>
       </c>
       <c r="J10" s="5">
-        <v>77.2</v>
+        <v>76.7</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>94.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>428000</v>
+        <v>200000</v>
       </c>
       <c r="G11" s="7">
-        <v>25000</v>
+        <v>19000</v>
       </c>
       <c r="H11" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I11" s="7">
-        <v>20923</v>
+        <v>14750</v>
       </c>
       <c r="J11" s="5">
-        <v>77.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>97</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>181000</v>
+        <v>130000</v>
       </c>
       <c r="G12" s="7">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="H12" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>14143</v>
+        <v>8111</v>
       </c>
       <c r="J12" s="5">
-        <v>76.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>99</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>110000</v>
+        <v>274000</v>
       </c>
       <c r="G13" s="7">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="H13" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I13" s="7">
-        <v>5400</v>
+        <v>17143</v>
       </c>
       <c r="J13" s="5">
-        <v>75.8</v>
+        <v>75.2</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>95.2</v>
+        <v>94</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>212000</v>
+        <v>161000</v>
       </c>
       <c r="G14" s="7">
-        <v>24000</v>
+        <v>13000</v>
       </c>
       <c r="H14" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I14" s="7">
-        <v>18800</v>
+        <v>12250</v>
       </c>
       <c r="J14" s="5">
-        <v>75.09999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>93.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>177000</v>
+        <v>188000</v>
       </c>
       <c r="G15" s="7">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="H15" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="7">
-        <v>13444</v>
+        <v>13200</v>
       </c>
       <c r="J15" s="5">
-        <v>74.8</v>
+        <v>74.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>93.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>148000</v>
+        <v>111000</v>
       </c>
       <c r="G16" s="7">
-        <v>12000</v>
+        <v>9000</v>
       </c>
       <c r="H16" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I16" s="7">
-        <v>12143</v>
+        <v>9300</v>
       </c>
       <c r="J16" s="5">
-        <v>74.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>94.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>171000</v>
+        <v>111000</v>
       </c>
       <c r="G17" s="7">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="H17" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" s="7">
-        <v>16400</v>
+        <v>17500</v>
       </c>
       <c r="J17" s="5">
-        <v>74.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>93.90000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>102000</v>
+        <v>443000</v>
       </c>
       <c r="G18" s="7">
-        <v>9000</v>
+        <v>-3000</v>
       </c>
       <c r="H18" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I18" s="7">
-        <v>9333</v>
+        <v>19714</v>
       </c>
       <c r="J18" s="5">
-        <v>74</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>78.5</v>
+        <v>89.2</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>967000</v>
+        <v>191000</v>
       </c>
       <c r="G19" s="7">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="H19" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>40273</v>
+        <v>15667</v>
       </c>
       <c r="J19" s="5">
-        <v>73.2</v>
+        <v>73</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>87</v>
+        <v>97.8</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>502000</v>
+        <v>122000</v>
       </c>
       <c r="G20" s="7">
-        <v>43000</v>
+        <v>15000</v>
       </c>
       <c r="H20" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I20" s="7">
-        <v>20923</v>
+        <v>16250</v>
       </c>
       <c r="J20" s="5">
-        <v>73.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>86.5</v>
+        <v>86</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>446000</v>
+        <v>539000</v>
       </c>
       <c r="G21" s="7">
-        <v>-8000</v>
+        <v>37000</v>
       </c>
       <c r="H21" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I21" s="7">
-        <v>21462</v>
+        <v>22071</v>
       </c>
       <c r="J21" s="5">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,23 +1320,23 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>90.40000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>164000</v>
+        <v>272000</v>
       </c>
       <c r="G22" s="7">
-        <v>8000</v>
+        <v>30000</v>
       </c>
       <c r="H22" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I22" s="7">
-        <v>12125</v>
+        <v>27667</v>
       </c>
       <c r="J22" s="5">
         <v>72.8</v>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>94.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>299000</v>
+        <v>179000</v>
       </c>
       <c r="G23" s="7">
-        <v>19000</v>
+        <v>11000</v>
       </c>
       <c r="H23" s="7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>3462</v>
+        <v>12667</v>
       </c>
       <c r="J23" s="5">
-        <v>72.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>90.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>186000</v>
+        <v>108000</v>
       </c>
       <c r="G24" s="7">
-        <v>17000</v>
+        <v>8000</v>
       </c>
       <c r="H24" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I24" s="7">
-        <v>10429</v>
+        <v>5214</v>
       </c>
       <c r="J24" s="5">
-        <v>72.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>91.40000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>180000</v>
+        <v>111000</v>
       </c>
       <c r="G25" s="7">
-        <v>14000</v>
+        <v>7000</v>
       </c>
       <c r="H25" s="7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I25" s="7">
-        <v>16600</v>
+        <v>5714</v>
       </c>
       <c r="J25" s="5">
-        <v>72.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>92.3</v>
+        <v>91.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>104000</v>
+        <v>311000</v>
       </c>
       <c r="G26" s="7">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H26" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I26" s="7">
-        <v>5615</v>
+        <v>4071</v>
       </c>
       <c r="J26" s="5">
-        <v>72.2</v>
+        <v>71.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>92.8</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>195000</v>
+        <v>236000</v>
       </c>
       <c r="G27" s="7">
-        <v>13000</v>
+        <v>4000</v>
       </c>
       <c r="H27" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I27" s="7">
-        <v>4154</v>
+        <v>14625</v>
       </c>
       <c r="J27" s="5">
-        <v>72.09999999999999</v>
+        <v>71</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>90.8</v>
+        <v>85.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>118000</v>
+        <v>187000</v>
       </c>
       <c r="G28" s="7">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="H28" s="7">
         <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>7833</v>
+        <v>14500</v>
       </c>
       <c r="J28" s="5">
-        <v>71.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90.2</v>
+        <v>90.3</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>184000</v>
+        <v>161000</v>
       </c>
       <c r="G29" s="7">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="H29" s="7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I29" s="7">
-        <v>16800</v>
+        <v>4000</v>
       </c>
       <c r="J29" s="5">
-        <v>71.8</v>
+        <v>70.7</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>90.8</v>
+        <v>89</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>145000</v>
+        <v>117000</v>
       </c>
       <c r="G30" s="7">
-        <v>8000</v>
+        <v>5000</v>
       </c>
       <c r="H30" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I30" s="7">
-        <v>7400</v>
+        <v>6333</v>
       </c>
       <c r="J30" s="5">
-        <v>71.8</v>
+        <v>70.5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>92</v>
+        <v>97.3</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>100000</v>
+        <v>206000</v>
       </c>
       <c r="G31" s="7">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="H31" s="7">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I31" s="7">
-        <v>5000</v>
+        <v>19000</v>
       </c>
       <c r="J31" s="5">
-        <v>71.8</v>
+        <v>70.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>86.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>232000</v>
+        <v>197000</v>
       </c>
       <c r="G32" s="7">
-        <v>5000</v>
+        <v>11000</v>
       </c>
       <c r="H32" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I32" s="7">
-        <v>16143</v>
+        <v>10500</v>
       </c>
       <c r="J32" s="5">
-        <v>71.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>91.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>168000</v>
+        <v>366000</v>
       </c>
       <c r="G33" s="7">
-        <v>14000</v>
+        <v>13000</v>
       </c>
       <c r="H33" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I33" s="7">
-        <v>13000</v>
+        <v>20375</v>
       </c>
       <c r="J33" s="5">
-        <v>71.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>90.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>112000</v>
+        <v>322000</v>
       </c>
       <c r="G34" s="7">
-        <v>6000</v>
+        <v>16000</v>
       </c>
       <c r="H34" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I34" s="7">
-        <v>6455</v>
+        <v>15250</v>
       </c>
       <c r="J34" s="5">
-        <v>71.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>91.3</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>152000</v>
+        <v>110000</v>
       </c>
       <c r="G35" s="7">
-        <v>10000</v>
+        <v>8000</v>
       </c>
       <c r="H35" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>3615</v>
+        <v>6400</v>
       </c>
       <c r="J35" s="5">
-        <v>71.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>81.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>519000</v>
+        <v>535000</v>
       </c>
       <c r="G36" s="7">
-        <v>24000</v>
+        <v>16000</v>
       </c>
       <c r="H36" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I36" s="7">
-        <v>23385</v>
+        <v>22857</v>
       </c>
       <c r="J36" s="5">
-        <v>70.8</v>
+        <v>69.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>86.2</v>
+        <v>74.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>330000</v>
+        <v>931000</v>
       </c>
       <c r="G37" s="7">
-        <v>-2000</v>
+        <v>-36000</v>
       </c>
       <c r="H37" s="7">
         <v>13</v>
       </c>
       <c r="I37" s="7">
-        <v>13000</v>
+        <v>33917</v>
       </c>
       <c r="J37" s="5">
-        <v>70.7</v>
+        <v>69.5</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>82</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>481000</v>
+        <v>125000</v>
       </c>
       <c r="G38" s="7">
-        <v>31000</v>
+        <v>7000</v>
       </c>
       <c r="H38" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I38" s="7">
-        <v>21846</v>
+        <v>7714</v>
       </c>
       <c r="J38" s="5">
-        <v>70.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>81.7</v>
+        <v>85.7</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>1692000</v>
+        <v>178000</v>
       </c>
       <c r="G39" s="7">
-        <v>24000</v>
+        <v>2000</v>
       </c>
       <c r="H39" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I39" s="7">
-        <v>22385</v>
+        <v>8429</v>
       </c>
       <c r="J39" s="5">
-        <v>70.5</v>
+        <v>69.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86.8</v>
+        <v>87</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>171000</v>
+        <v>119000</v>
       </c>
       <c r="G40" s="7">
-        <v>1000</v>
+        <v>14000</v>
       </c>
       <c r="H40" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>11000</v>
+        <v>5500</v>
       </c>
       <c r="J40" s="5">
-        <v>70.5</v>
+        <v>69.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>78.8</v>
+        <v>77.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>399000</v>
+        <v>411000</v>
       </c>
       <c r="G41" s="7">
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="H41" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41" s="7">
-        <v>27571</v>
+        <v>25625</v>
       </c>
       <c r="J41" s="5">
-        <v>70.2</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>76.5</v>
+        <v>88.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>1073000</v>
+        <v>101000</v>
       </c>
       <c r="G42" s="7">
-        <v>-31000</v>
+        <v>10000</v>
       </c>
       <c r="H42" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I42" s="7">
-        <v>30538</v>
+        <v>9600</v>
       </c>
       <c r="J42" s="5">
-        <v>69.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>83.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>357000</v>
+        <v>1686000</v>
       </c>
       <c r="G43" s="7">
-        <v>19000</v>
+        <v>-6000</v>
       </c>
       <c r="H43" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I43" s="7">
-        <v>15385</v>
+        <v>20357</v>
       </c>
       <c r="J43" s="5">
-        <v>69.7</v>
+        <v>69</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>144000</v>
+        <v>371000</v>
       </c>
       <c r="G44" s="7">
-        <v>4000</v>
+        <v>14000</v>
       </c>
       <c r="H44" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I44" s="7">
-        <v>8333</v>
+        <v>15286</v>
       </c>
       <c r="J44" s="5">
-        <v>69.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>96.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>107000</v>
+        <v>237000</v>
       </c>
       <c r="G45" s="7">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="H45" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I45" s="7">
-        <v>16667</v>
+        <v>20400</v>
       </c>
       <c r="J45" s="5">
-        <v>69.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>82.8</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>422000</v>
+        <v>153000</v>
       </c>
       <c r="G46" s="7">
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="H46" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I46" s="7">
-        <v>15077</v>
+        <v>5786</v>
       </c>
       <c r="J46" s="5">
-        <v>69.3</v>
+        <v>68.7</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>86.40000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>135000</v>
+        <v>500000</v>
       </c>
       <c r="G47" s="7">
-        <v>1000</v>
+        <v>19000</v>
       </c>
       <c r="H47" s="7">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="I47" s="7">
-        <v>7300</v>
+        <v>21643</v>
       </c>
       <c r="J47" s="5">
-        <v>69.3</v>
+        <v>68.5</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>85.40000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>165000</v>
+        <v>438000</v>
       </c>
       <c r="G48" s="7">
-        <v>3000</v>
+        <v>16000</v>
       </c>
       <c r="H48" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I48" s="7">
-        <v>8333</v>
+        <v>15143</v>
       </c>
       <c r="J48" s="5">
-        <v>69.09999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>78.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>353000</v>
+        <v>145000</v>
       </c>
       <c r="G49" s="7">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I49" s="7">
-        <v>21429</v>
+        <v>6727</v>
       </c>
       <c r="J49" s="5">
-        <v>68.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>83.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>266000</v>
+        <v>289000</v>
       </c>
       <c r="G50" s="7">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="H50" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I50" s="7">
-        <v>10692</v>
+        <v>11571</v>
       </c>
       <c r="J50" s="5">
-        <v>68.7</v>
+        <v>68.3</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>84</v>
+        <v>83.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>176000</v>
+        <v>393000</v>
       </c>
       <c r="G51" s="7">
-        <v>-1000</v>
+        <v>68000</v>
       </c>
       <c r="H51" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I51" s="7">
-        <v>8923</v>
+        <v>28250</v>
       </c>
       <c r="J51" s="5">
-        <v>68.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>87.3</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>307000</v>
+        <v>743000</v>
       </c>
       <c r="G52" s="7">
-        <v>2000</v>
+        <v>16000</v>
       </c>
       <c r="H52" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I52" s="7">
-        <v>1154</v>
+        <v>14929</v>
       </c>
       <c r="J52" s="5">
-        <v>68.3</v>
+        <v>67.7</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>77.5</v>
+        <v>81</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>334000</v>
+        <v>162000</v>
       </c>
       <c r="G53" s="7">
-        <v>23000</v>
+        <v>-9000</v>
       </c>
       <c r="H53" s="7">
         <v>7</v>
       </c>
       <c r="I53" s="7">
-        <v>21333</v>
+        <v>12167</v>
       </c>
       <c r="J53" s="5">
-        <v>68</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>89.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>213000</v>
+        <v>132000</v>
       </c>
       <c r="G54" s="7">
-        <v>10000</v>
+        <v>-3000</v>
       </c>
       <c r="H54" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I54" s="7">
-        <v>14250</v>
+        <v>6364</v>
       </c>
       <c r="J54" s="5">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-28T05:01:53+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-29T05:26:56+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>不拱火我来汉东干什么？</t>
   </si>
   <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
     <t>火影：越豪越强？胜你无需第二剑</t>
   </si>
   <si>
-    <t>什么叫我成了灭世级怪谈？</t>
+    <t>玩家都说我是赛博女鬼？</t>
+  </si>
+  <si>
+    <t>抗战：我黄埔元老开局打爆小鬼子</t>
+  </si>
+  <si>
+    <t>很野很欲，楼下的蔷薇正飘香！</t>
+  </si>
+  <si>
+    <t>选择求生：只有我能看到正确答案</t>
+  </si>
+  <si>
+    <t>四合院：整顿家风，从我妈开始</t>
+  </si>
+  <si>
+    <t>接待意难平的古人，老祖宗全看着</t>
+  </si>
+  <si>
+    <t>刚出马，就被国家收编了</t>
+  </si>
+  <si>
+    <t>盗墓：八岁创雷法，震惊张海琪</t>
+  </si>
+  <si>
+    <t>三角洲：手游主播的我误入巅峰赛</t>
+  </si>
+  <si>
+    <t>凤流高手</t>
+  </si>
+  <si>
+    <t>人在都市，词条成神</t>
+  </si>
+  <si>
+    <t>女尊：你们快放开我男朋友！</t>
+  </si>
+  <si>
+    <t>游走神话时代，开局拜师道门天师</t>
+  </si>
+  <si>
+    <t>衰神气运逆转，回老家享受生活</t>
+  </si>
+  <si>
+    <t>九门：天与暴君模板，震惊陈皮</t>
+  </si>
+  <si>
+    <t>退伍上大学，教官竟是我带的兵</t>
+  </si>
+  <si>
+    <t>我的沪上野妻</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>让你去养老大队，你破惊天奇案？</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>主角死后，未婚妻跟反派的我享福</t>
+  </si>
+  <si>
+    <t>我，原始首徒，封神开局整顿阐教</t>
+  </si>
+  <si>
+    <t>九子夺嫡：开局签到陆地神仙！</t>
+  </si>
+  <si>
+    <t>高武，万法同修，一证永证</t>
+  </si>
+  <si>
+    <t>直播见证神话：从鳌太线走蛟开始</t>
+  </si>
+  <si>
+    <t>全民穿越！我在末日世界养城兽</t>
+  </si>
+  <si>
+    <t>四合院1948亿万富翁躺平生活</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
+  </si>
+  <si>
+    <t>带着渡劫修为，重回高中时代</t>
+  </si>
+  <si>
+    <t>都市剧：这个世界没有好玩的游戏</t>
+  </si>
+  <si>
+    <t>被富婆女粉抓住后，我财富自由了</t>
+  </si>
+  <si>
+    <t>斩神：零号病人，是死之执政</t>
+  </si>
+  <si>
+    <t>洪荒八景宫中有逆徒</t>
+  </si>
+  <si>
+    <t>老师，男生也能报考魔女学院吗？</t>
+  </si>
+  <si>
+    <t>我，老头，永远比校花高四个境界</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
+  </si>
+  <si>
+    <t>植物大战僵尸恐怖版开局获得电大</t>
+  </si>
+  <si>
+    <t>机甲武神：从矿星开始</t>
+  </si>
+  <si>
+    <t>我的直播通武侠，开局整垮少林寺</t>
   </si>
   <si>
     <t>抗美援朝：什么叫这是四合院世界</t>
   </si>
   <si>
-    <t>很野很欲，楼下的蔷薇正飘香！</t>
-  </si>
-  <si>
-    <t>我，原始首徒，封神开局整顿阐教</t>
-  </si>
-  <si>
-    <t>凤流高手</t>
-  </si>
-  <si>
-    <t>选择求生：只有我能看到正确答案</t>
-  </si>
-  <si>
-    <t>三角洲：手游主播的我误入巅峰赛</t>
-  </si>
-  <si>
-    <t>盗墓：八岁创雷法，震惊张海琪</t>
-  </si>
-  <si>
-    <t>重生：躺平的低调人生</t>
-  </si>
-  <si>
-    <t>游走神话时代，开局拜师道门天师</t>
-  </si>
-  <si>
-    <t>每天一万潜能点，只能给大专生？</t>
-  </si>
-  <si>
-    <t>抗战：我黄埔元老开局打爆小鬼子</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>四合院：整顿家风，从我妈开始</t>
+    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
   </si>
   <si>
     <t>跑男：系统过于抽象，还好我也是</t>
   </si>
   <si>
-    <t>分家只给破木船？我靠赶海赚麻了</t>
-  </si>
-  <si>
-    <t>让你去养老大队，你破惊天奇案？</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>四合院1948亿万富翁躺平生活</t>
-  </si>
-  <si>
-    <t>开局假冒亡牌飞行员，旱地拔葱！</t>
-  </si>
-  <si>
-    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
-  </si>
-  <si>
-    <t>我在红楼世界玩修仙游戏！</t>
-  </si>
-  <si>
-    <t>主角死后，未婚妻跟反派的我享福</t>
-  </si>
-  <si>
-    <t>斩神：零号病人，是死之执政</t>
-  </si>
-  <si>
-    <t>都市剧：这个世界没有好玩的游戏</t>
-  </si>
-  <si>
-    <t>衰神气运逆转，回老家享受生活</t>
-  </si>
-  <si>
-    <t>接待意难平的古人，老祖宗全看着</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>纨绔大少是邪神，眷属全部是美女</t>
-  </si>
-  <si>
     <t>旧日余烬</t>
   </si>
   <si>
-    <t>带着渡劫修为，重回高中时代</t>
-  </si>
-  <si>
-    <t>疯掉后，我的故事让全国人痛哭</t>
-  </si>
-  <si>
-    <t>机甲武神：从矿星开始</t>
-  </si>
-  <si>
-    <t>女尊：你们快放开我男朋友！</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>从零开始，打造华夏首支特种部队</t>
-  </si>
-  <si>
-    <t>全民穿越！我在末日世界养城兽</t>
-  </si>
-  <si>
-    <t>宿舍求生：糯米可镇不住我们太久</t>
-  </si>
-  <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
-  </si>
-  <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>不会踢球？却成了足球巨星！</t>
-  </si>
-  <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>直播见证神话：从鳌太线走蛟开始</t>
-  </si>
-  <si>
-    <t>直播我和徐妙云，老朱全家破防了</t>
-  </si>
-  <si>
-    <t>洪荒八景宫中有逆徒</t>
-  </si>
-  <si>
-    <t>全三国重生，我老六身份藏不住了</t>
+    <t>搭讪就有奖，加满5000个好友</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>85.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1133000</v>
+        <v>1208000</v>
       </c>
       <c r="G5" s="7">
-        <v>76000</v>
+        <v>75000</v>
       </c>
       <c r="H5" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>82667</v>
+        <v>81571</v>
       </c>
       <c r="J5" s="5">
-        <v>87.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>99.3</v>
+        <v>97.3</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>466000</v>
+        <v>507000</v>
       </c>
       <c r="G6" s="7">
-        <v>46000</v>
+        <v>41000</v>
       </c>
       <c r="H6" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="7">
-        <v>36714</v>
+        <v>37250</v>
       </c>
       <c r="J6" s="5">
-        <v>83.8</v>
+        <v>82.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>90.40000000000001</v>
+        <v>97.8</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>809000</v>
+        <v>321000</v>
       </c>
       <c r="G7" s="7">
-        <v>109000</v>
+        <v>32000</v>
       </c>
       <c r="H7" s="7">
         <v>15</v>
       </c>
       <c r="I7" s="7">
-        <v>32857</v>
+        <v>20714</v>
       </c>
       <c r="J7" s="5">
-        <v>77.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>95.40000000000001</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>232000</v>
+        <v>903000</v>
       </c>
       <c r="G8" s="7">
-        <v>20000</v>
+        <v>94000</v>
       </c>
       <c r="H8" s="7">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I8" s="7">
-        <v>19000</v>
+        <v>36933</v>
       </c>
       <c r="J8" s="5">
-        <v>77.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>94.7</v>
+        <v>95.2</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>289000</v>
+        <v>253000</v>
       </c>
       <c r="G9" s="7">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="H9" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I9" s="7">
-        <v>19846</v>
+        <v>19286</v>
       </c>
       <c r="J9" s="5">
-        <v>77</v>
+        <v>77.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>96.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>183000</v>
+        <v>322000</v>
       </c>
       <c r="G10" s="7">
-        <v>17000</v>
+        <v>43000</v>
       </c>
       <c r="H10" s="7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>14455</v>
+        <v>11600</v>
       </c>
       <c r="J10" s="5">
-        <v>76.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>95.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>200000</v>
+        <v>138000</v>
       </c>
       <c r="G11" s="7">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H11" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I11" s="7">
-        <v>14750</v>
+        <v>16200</v>
       </c>
       <c r="J11" s="5">
-        <v>76.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>98.09999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>130000</v>
+        <v>216000</v>
       </c>
       <c r="G12" s="7">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="H12" s="7">
         <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>8111</v>
+        <v>14889</v>
       </c>
       <c r="J12" s="5">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>92.59999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>274000</v>
+        <v>173000</v>
       </c>
       <c r="G13" s="7">
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="H13" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I13" s="7">
-        <v>17143</v>
+        <v>12222</v>
       </c>
       <c r="J13" s="5">
-        <v>75.2</v>
+        <v>74.5</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>94</v>
+        <v>95.3</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>161000</v>
+        <v>296000</v>
       </c>
       <c r="G14" s="7">
-        <v>13000</v>
+        <v>24000</v>
       </c>
       <c r="H14" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I14" s="7">
-        <v>12250</v>
+        <v>26750</v>
       </c>
       <c r="J14" s="5">
-        <v>74.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>92.59999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>188000</v>
+        <v>121000</v>
       </c>
       <c r="G15" s="7">
         <v>11000</v>
       </c>
       <c r="H15" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>13200</v>
+        <v>7167</v>
       </c>
       <c r="J15" s="5">
-        <v>74.2</v>
+        <v>73.8</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>94.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>111000</v>
+        <v>103000</v>
       </c>
       <c r="G16" s="7">
         <v>9000</v>
       </c>
       <c r="H16" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I16" s="7">
-        <v>9300</v>
+        <v>8444</v>
       </c>
       <c r="J16" s="5">
-        <v>74.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>98.5</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>111000</v>
+        <v>119000</v>
       </c>
       <c r="G17" s="7">
-        <v>13000</v>
+        <v>8000</v>
       </c>
       <c r="H17" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I17" s="7">
-        <v>17500</v>
+        <v>9182</v>
       </c>
       <c r="J17" s="5">
-        <v>73.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,23 +1188,23 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>87.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>443000</v>
+        <v>196000</v>
       </c>
       <c r="G18" s="7">
-        <v>-3000</v>
+        <v>8000</v>
       </c>
       <c r="H18" s="7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I18" s="7">
-        <v>19714</v>
+        <v>12727</v>
       </c>
       <c r="J18" s="5">
         <v>73.09999999999999</v>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>89.2</v>
+        <v>88.2</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>191000</v>
+        <v>279000</v>
       </c>
       <c r="G19" s="7">
-        <v>11000</v>
+        <v>5000</v>
       </c>
       <c r="H19" s="7">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I19" s="7">
-        <v>15667</v>
+        <v>16333</v>
       </c>
       <c r="J19" s="5">
-        <v>73</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>97.8</v>
+        <v>98.2</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>122000</v>
+        <v>135000</v>
       </c>
       <c r="G20" s="7">
-        <v>15000</v>
+        <v>19000</v>
       </c>
       <c r="H20" s="7">
         <v>5</v>
       </c>
       <c r="I20" s="7">
-        <v>16250</v>
+        <v>13000</v>
       </c>
       <c r="J20" s="5">
-        <v>72.90000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>86</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>539000</v>
+        <v>109000</v>
       </c>
       <c r="G21" s="7">
-        <v>37000</v>
+        <v>8000</v>
       </c>
       <c r="H21" s="7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>22071</v>
+        <v>9333</v>
       </c>
       <c r="J21" s="5">
-        <v>72.8</v>
+        <v>72.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>97.90000000000001</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>272000</v>
+        <v>436000</v>
       </c>
       <c r="G22" s="7">
-        <v>30000</v>
+        <v>-7000</v>
       </c>
       <c r="H22" s="7">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="I22" s="7">
-        <v>27667</v>
+        <v>17933</v>
       </c>
       <c r="J22" s="5">
-        <v>72.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>179000</v>
+        <v>335000</v>
       </c>
       <c r="G23" s="7">
-        <v>11000</v>
+        <v>13000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I23" s="7">
-        <v>12667</v>
+        <v>14800</v>
       </c>
       <c r="J23" s="5">
-        <v>71.90000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.5</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>108000</v>
+        <v>100000</v>
       </c>
       <c r="G24" s="7">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="H24" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I24" s="7">
-        <v>5214</v>
+        <v>6778</v>
       </c>
       <c r="J24" s="5">
-        <v>71.59999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>91.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>111000</v>
+        <v>105000</v>
       </c>
       <c r="G25" s="7">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H25" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I25" s="7">
-        <v>5714</v>
+        <v>11250</v>
       </c>
       <c r="J25" s="5">
-        <v>71.5</v>
+        <v>71.7</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>91.5</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>311000</v>
+        <v>644000</v>
       </c>
       <c r="G26" s="7">
-        <v>12000</v>
+        <v>64000</v>
       </c>
       <c r="H26" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I26" s="7">
-        <v>4071</v>
+        <v>11733</v>
       </c>
       <c r="J26" s="5">
-        <v>71.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>86.09999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>236000</v>
+        <v>560000</v>
       </c>
       <c r="G27" s="7">
-        <v>4000</v>
+        <v>25000</v>
       </c>
       <c r="H27" s="7">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I27" s="7">
-        <v>14625</v>
+        <v>23000</v>
       </c>
       <c r="J27" s="5">
-        <v>71</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>85.5</v>
+        <v>90.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>187000</v>
+        <v>118000</v>
       </c>
       <c r="G28" s="7">
-        <v>3000</v>
+        <v>7000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I28" s="7">
-        <v>14500</v>
+        <v>5800</v>
       </c>
       <c r="J28" s="5">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90.3</v>
+        <v>83</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>161000</v>
+        <v>562000</v>
       </c>
       <c r="G29" s="7">
-        <v>9000</v>
+        <v>23000</v>
       </c>
       <c r="H29" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" s="7">
-        <v>4000</v>
+        <v>22133</v>
       </c>
       <c r="J29" s="5">
-        <v>70.7</v>
+        <v>71.2</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>117000</v>
+        <v>221000</v>
       </c>
       <c r="G30" s="7">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="H30" s="7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>6333</v>
+        <v>18000</v>
       </c>
       <c r="J30" s="5">
-        <v>70.5</v>
+        <v>71.2</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>97.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>206000</v>
+        <v>138000</v>
       </c>
       <c r="G31" s="7">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="H31" s="7">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I31" s="7">
-        <v>19000</v>
+        <v>8100</v>
       </c>
       <c r="J31" s="5">
-        <v>70.3</v>
+        <v>71.2</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>86.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>197000</v>
+        <v>106000</v>
       </c>
       <c r="G32" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H32" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I32" s="7">
-        <v>10500</v>
+        <v>7333</v>
       </c>
       <c r="J32" s="5">
-        <v>70.3</v>
+        <v>71.2</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1681,28 +1681,30 @@
       <c r="A33" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="5"/>
+      <c r="B33" s="5">
+        <v>6.7</v>
+      </c>
       <c r="C33" s="5">
-        <v>81.5</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>366000</v>
+        <v>145000</v>
       </c>
       <c r="G33" s="7">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="H33" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>20375</v>
+        <v>11750</v>
       </c>
       <c r="J33" s="5">
-        <v>69.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>92.8</v>
+        <v>81.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>322000</v>
+        <v>444000</v>
       </c>
       <c r="G34" s="7">
-        <v>16000</v>
+        <v>51000</v>
       </c>
       <c r="H34" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>15250</v>
+        <v>32800</v>
       </c>
       <c r="J34" s="5">
-        <v>69.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>91.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>110000</v>
+        <v>260000</v>
       </c>
       <c r="G35" s="7">
-        <v>8000</v>
+        <v>23000</v>
       </c>
       <c r="H35" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>6400</v>
+        <v>20833</v>
       </c>
       <c r="J35" s="5">
-        <v>69.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>80.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>535000</v>
+        <v>238000</v>
       </c>
       <c r="G36" s="7">
-        <v>16000</v>
+        <v>2000</v>
       </c>
       <c r="H36" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I36" s="7">
-        <v>22857</v>
+        <v>13222</v>
       </c>
       <c r="J36" s="5">
-        <v>69.8</v>
+        <v>70.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>74.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>931000</v>
+        <v>521000</v>
       </c>
       <c r="G37" s="7">
-        <v>-36000</v>
+        <v>21000</v>
       </c>
       <c r="H37" s="7">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="I37" s="7">
-        <v>33917</v>
+        <v>21600</v>
       </c>
       <c r="J37" s="5">
-        <v>69.5</v>
+        <v>70</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>86.40000000000001</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>125000</v>
+        <v>182000</v>
       </c>
       <c r="G38" s="7">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="H38" s="7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I38" s="7">
-        <v>7714</v>
+        <v>8133</v>
       </c>
       <c r="J38" s="5">
-        <v>69.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>85.7</v>
+        <v>81.2</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>178000</v>
+        <v>378000</v>
       </c>
       <c r="G39" s="7">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="H39" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I39" s="7">
-        <v>8429</v>
+        <v>19444</v>
       </c>
       <c r="J39" s="5">
-        <v>69.2</v>
+        <v>69.5</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>87</v>
+        <v>87.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>119000</v>
+        <v>194000</v>
       </c>
       <c r="G40" s="7">
-        <v>14000</v>
+        <v>3000</v>
       </c>
       <c r="H40" s="7">
         <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>5500</v>
+        <v>6333</v>
       </c>
       <c r="J40" s="5">
-        <v>69.2</v>
+        <v>69.5</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>77.7</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>411000</v>
+        <v>202000</v>
       </c>
       <c r="G41" s="7">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="H41" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I41" s="7">
-        <v>25625</v>
+        <v>9889</v>
       </c>
       <c r="J41" s="5">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>88.5</v>
+        <v>84.8</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>101000</v>
+        <v>160000</v>
       </c>
       <c r="G42" s="7">
-        <v>10000</v>
+        <v>-2000</v>
       </c>
       <c r="H42" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I42" s="7">
-        <v>9600</v>
+        <v>10143</v>
       </c>
       <c r="J42" s="5">
-        <v>69.09999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>79.90000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>1686000</v>
+        <v>194000</v>
       </c>
       <c r="G43" s="7">
-        <v>-6000</v>
+        <v>4000</v>
       </c>
       <c r="H43" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I43" s="7">
-        <v>20357</v>
+        <v>3533</v>
       </c>
       <c r="J43" s="5">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>81.8</v>
+        <v>94.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>371000</v>
+        <v>136000</v>
       </c>
       <c r="G44" s="7">
-        <v>14000</v>
+        <v>21000</v>
       </c>
       <c r="H44" s="7">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I44" s="7">
-        <v>15286</v>
+        <v>19667</v>
       </c>
       <c r="J44" s="5">
-        <v>68.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>82.90000000000001</v>
+        <v>80.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>237000</v>
+        <v>1684000</v>
       </c>
       <c r="G45" s="7">
-        <v>22000</v>
+        <v>-2000</v>
       </c>
       <c r="H45" s="7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I45" s="7">
-        <v>20400</v>
+        <v>18867</v>
       </c>
       <c r="J45" s="5">
-        <v>68.7</v>
+        <v>68.8</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>85.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>153000</v>
+        <v>457000</v>
       </c>
       <c r="G46" s="7">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="H46" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I46" s="7">
-        <v>5786</v>
+        <v>15400</v>
       </c>
       <c r="J46" s="5">
-        <v>68.7</v>
+        <v>68.8</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>78.3</v>
+        <v>85.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>500000</v>
+        <v>179000</v>
       </c>
       <c r="G47" s="7">
-        <v>19000</v>
+        <v>3000</v>
       </c>
       <c r="H47" s="7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I47" s="7">
-        <v>21643</v>
+        <v>6917</v>
       </c>
       <c r="J47" s="5">
-        <v>68.5</v>
+        <v>68.8</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>81.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>438000</v>
+        <v>419000</v>
       </c>
       <c r="G48" s="7">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="H48" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I48" s="7">
-        <v>15143</v>
+        <v>23667</v>
       </c>
       <c r="J48" s="5">
-        <v>68.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>85</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>145000</v>
+        <v>312000</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="H49" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I49" s="7">
-        <v>6727</v>
+        <v>17500</v>
       </c>
       <c r="J49" s="5">
-        <v>68.40000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>289000</v>
+        <v>176000</v>
       </c>
       <c r="G50" s="7">
-        <v>23000</v>
+        <v>-7000</v>
       </c>
       <c r="H50" s="7">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I50" s="7">
-        <v>11571</v>
+        <v>12667</v>
       </c>
       <c r="J50" s="5">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>83.8</v>
+        <v>86.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>393000</v>
+        <v>163000</v>
       </c>
       <c r="G51" s="7">
-        <v>68000</v>
+        <v>2000</v>
       </c>
       <c r="H51" s="7">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I51" s="7">
-        <v>28250</v>
+        <v>3867</v>
       </c>
       <c r="J51" s="5">
-        <v>68.2</v>
+        <v>68.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>79.90000000000001</v>
+        <v>83.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>743000</v>
+        <v>178000</v>
       </c>
       <c r="G52" s="7">
-        <v>16000</v>
+        <v>-1000</v>
       </c>
       <c r="H52" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I52" s="7">
-        <v>14929</v>
+        <v>10714</v>
       </c>
       <c r="J52" s="5">
-        <v>67.7</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>81</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>162000</v>
+        <v>130000</v>
       </c>
       <c r="G53" s="7">
-        <v>-9000</v>
+        <v>5000</v>
       </c>
       <c r="H53" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I53" s="7">
-        <v>12167</v>
+        <v>7375</v>
       </c>
       <c r="J53" s="5">
-        <v>67.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2374,28 +2376,30 @@
       <c r="A54" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="5"/>
+      <c r="B54" s="5">
+        <v>6.5</v>
+      </c>
       <c r="C54" s="5">
-        <v>83.40000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>132000</v>
+        <v>169000</v>
       </c>
       <c r="G54" s="7">
-        <v>-3000</v>
+        <v>10000</v>
       </c>
       <c r="H54" s="7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I54" s="7">
-        <v>6364</v>
+        <v>8800</v>
       </c>
       <c r="J54" s="5">
-        <v>67.5</v>
+        <v>68.3</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-29T05:26:56+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-09-30T05:14:53+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -85,142 +85,142 @@
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
+    <t>高武，万法同修，一证永证</t>
+  </si>
+  <si>
+    <t>四合院：整顿家风，从我妈开始</t>
+  </si>
+  <si>
+    <t>从修仙回到都市，坏消息修为没了</t>
+  </si>
+  <si>
+    <t>直播见证神话：从鳌太线走蛟开始</t>
+  </si>
+  <si>
+    <t>退伍上大学，教官竟是我带的兵</t>
+  </si>
+  <si>
     <t>火影：越豪越强？胜你无需第二剑</t>
   </si>
   <si>
     <t>玩家都说我是赛博女鬼？</t>
   </si>
   <si>
+    <t>人在都市，词条成神</t>
+  </si>
+  <si>
+    <t>我的沪上野妻</t>
+  </si>
+  <si>
+    <t>盗墓：八岁创雷法，震惊张海琪</t>
+  </si>
+  <si>
+    <t>朱标私生子，老朱逼我当皇帝！</t>
+  </si>
+  <si>
+    <t>开箱必出神话级，阁下如何应对？</t>
+  </si>
+  <si>
+    <t>三角洲：手游主播的我误入巅峰赛</t>
+  </si>
+  <si>
     <t>抗战：我黄埔元老开局打爆小鬼子</t>
   </si>
   <si>
+    <t>衰神气运逆转，回老家享受生活</t>
+  </si>
+  <si>
+    <t>老师，男生也能报考魔女学院吗？</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>凤流高手</t>
+  </si>
+  <si>
+    <t>接待意难平的古人，老祖宗全看着</t>
+  </si>
+  <si>
+    <t>九门：天与暴君模板，震惊陈皮</t>
+  </si>
+  <si>
+    <t>主角死后，未婚妻跟反派的我享福</t>
+  </si>
+  <si>
+    <t>海吞天</t>
+  </si>
+  <si>
+    <t>我，老头，永远比校花高四个境界</t>
+  </si>
+  <si>
+    <t>全民穿越！我在末日世界养城兽</t>
+  </si>
+  <si>
+    <t>洪荒：我十凶天角蚁，躺平就变强</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>游走神话时代，开局拜师道门天师</t>
+  </si>
+  <si>
+    <t>星铁观影，曝光虚照就是欢愉星神</t>
+  </si>
+  <si>
+    <t>模拟：少年缺悟性吗？借个脑子吧</t>
+  </si>
+  <si>
+    <t>抗美援朝：什么叫这是四合院世界</t>
+  </si>
+  <si>
+    <t>选择求生：只有我能看到正确答案</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>搭讪就有奖，加满5000个好友</t>
+  </si>
+  <si>
+    <t>疯掉后，我的故事让全国人痛哭</t>
+  </si>
+  <si>
+    <t>让你去养老大队，你破惊天奇案？</t>
+  </si>
+  <si>
+    <t>女尊：你们快放开我男朋友！</t>
+  </si>
+  <si>
+    <t>年代：一分钟一块钱，创业当首富</t>
+  </si>
+  <si>
+    <t>全民航海：古神对我的船重度依赖</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>跑男：系统过于抽象，还好我也是</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
+  </si>
+  <si>
     <t>很野很欲，楼下的蔷薇正飘香！</t>
   </si>
   <si>
-    <t>选择求生：只有我能看到正确答案</t>
-  </si>
-  <si>
-    <t>四合院：整顿家风，从我妈开始</t>
-  </si>
-  <si>
-    <t>接待意难平的古人，老祖宗全看着</t>
-  </si>
-  <si>
-    <t>刚出马，就被国家收编了</t>
-  </si>
-  <si>
-    <t>盗墓：八岁创雷法，震惊张海琪</t>
-  </si>
-  <si>
-    <t>三角洲：手游主播的我误入巅峰赛</t>
-  </si>
-  <si>
-    <t>凤流高手</t>
-  </si>
-  <si>
-    <t>人在都市，词条成神</t>
-  </si>
-  <si>
-    <t>女尊：你们快放开我男朋友！</t>
-  </si>
-  <si>
-    <t>游走神话时代，开局拜师道门天师</t>
-  </si>
-  <si>
-    <t>衰神气运逆转，回老家享受生活</t>
-  </si>
-  <si>
-    <t>九门：天与暴君模板，震惊陈皮</t>
-  </si>
-  <si>
-    <t>退伍上大学，教官竟是我带的兵</t>
-  </si>
-  <si>
-    <t>我的沪上野妻</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>让你去养老大队，你破惊天奇案？</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>主角死后，未婚妻跟反派的我享福</t>
-  </si>
-  <si>
-    <t>我，原始首徒，封神开局整顿阐教</t>
-  </si>
-  <si>
-    <t>九子夺嫡：开局签到陆地神仙！</t>
-  </si>
-  <si>
-    <t>高武，万法同修，一证永证</t>
-  </si>
-  <si>
-    <t>直播见证神话：从鳌太线走蛟开始</t>
-  </si>
-  <si>
-    <t>全民穿越！我在末日世界养城兽</t>
-  </si>
-  <si>
-    <t>四合院1948亿万富翁躺平生活</t>
-  </si>
-  <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
-  </si>
-  <si>
-    <t>带着渡劫修为，重回高中时代</t>
-  </si>
-  <si>
-    <t>都市剧：这个世界没有好玩的游戏</t>
+    <t>龙族：我的强化每月刷新</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>我的直播通武侠，开局整垮少林寺</t>
   </si>
   <si>
     <t>被富婆女粉抓住后，我财富自由了</t>
-  </si>
-  <si>
-    <t>斩神：零号病人，是死之执政</t>
-  </si>
-  <si>
-    <t>洪荒八景宫中有逆徒</t>
-  </si>
-  <si>
-    <t>老师，男生也能报考魔女学院吗？</t>
-  </si>
-  <si>
-    <t>我，老头，永远比校花高四个境界</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>植物大战僵尸恐怖版开局获得电大</t>
-  </si>
-  <si>
-    <t>机甲武神：从矿星开始</t>
-  </si>
-  <si>
-    <t>我的直播通武侠，开局整垮少林寺</t>
-  </si>
-  <si>
-    <t>抗美援朝：什么叫这是四合院世界</t>
-  </si>
-  <si>
-    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
-  </si>
-  <si>
-    <t>跑男：系统过于抽象，还好我也是</t>
-  </si>
-  <si>
-    <t>旧日余烬</t>
-  </si>
-  <si>
-    <t>搭讪就有奖，加满5000个好友</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>85.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1208000</v>
+        <v>1264000</v>
       </c>
       <c r="G5" s="7">
-        <v>75000</v>
+        <v>56000</v>
       </c>
       <c r="H5" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="7">
-        <v>81571</v>
+        <v>78375</v>
       </c>
       <c r="J5" s="5">
-        <v>87.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>97.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>507000</v>
+        <v>552000</v>
       </c>
       <c r="G6" s="7">
-        <v>41000</v>
+        <v>45000</v>
       </c>
       <c r="H6" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="7">
-        <v>37250</v>
+        <v>38111</v>
       </c>
       <c r="J6" s="5">
-        <v>82.8</v>
+        <v>83.2</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>97.8</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>321000</v>
+        <v>352000</v>
       </c>
       <c r="G7" s="7">
-        <v>32000</v>
+        <v>31000</v>
       </c>
       <c r="H7" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" s="7">
-        <v>20714</v>
+        <v>21400</v>
       </c>
       <c r="J7" s="5">
-        <v>79</v>
+        <v>78.5</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>88.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>903000</v>
+        <v>993000</v>
       </c>
       <c r="G8" s="7">
-        <v>94000</v>
+        <v>90000</v>
       </c>
       <c r="H8" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" s="7">
-        <v>36933</v>
+        <v>40250</v>
       </c>
       <c r="J8" s="5">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -889,28 +889,30 @@
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="5"/>
+      <c r="B9" s="5">
+        <v>6.7</v>
+      </c>
       <c r="C9" s="5">
-        <v>95.2</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>253000</v>
+        <v>190000</v>
       </c>
       <c r="G9" s="7">
-        <v>21000</v>
+        <v>45000</v>
       </c>
       <c r="H9" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>19286</v>
+        <v>18400</v>
       </c>
       <c r="J9" s="5">
-        <v>77.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +926,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>322000</v>
+        <v>316000</v>
       </c>
       <c r="G10" s="7">
-        <v>43000</v>
+        <v>20000</v>
       </c>
       <c r="H10" s="7">
         <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>11600</v>
+        <v>25400</v>
       </c>
       <c r="J10" s="5">
-        <v>75.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,23 +959,23 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>97.09999999999999</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>138000</v>
+        <v>530000</v>
       </c>
       <c r="G11" s="7">
-        <v>16000</v>
+        <v>74000</v>
       </c>
       <c r="H11" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I11" s="7">
-        <v>16200</v>
+        <v>48000</v>
       </c>
       <c r="J11" s="5">
         <v>75.5</v>
@@ -990,26 +992,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>93.8</v>
+        <v>84.3</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>216000</v>
+        <v>492000</v>
       </c>
       <c r="G12" s="7">
-        <v>16000</v>
+        <v>48000</v>
       </c>
       <c r="H12" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>14889</v>
+        <v>35333</v>
       </c>
       <c r="J12" s="5">
-        <v>75.3</v>
+        <v>75.2</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1025,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>93.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>173000</v>
+        <v>119000</v>
       </c>
       <c r="G13" s="7">
-        <v>12000</v>
+        <v>14000</v>
       </c>
       <c r="H13" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>12222</v>
+        <v>11800</v>
       </c>
       <c r="J13" s="5">
-        <v>74.5</v>
+        <v>75.2</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1058,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>95.3</v>
+        <v>91.5</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>296000</v>
+        <v>264000</v>
       </c>
       <c r="G14" s="7">
-        <v>24000</v>
+        <v>11000</v>
       </c>
       <c r="H14" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I14" s="7">
-        <v>26750</v>
+        <v>18250</v>
       </c>
       <c r="J14" s="5">
-        <v>74.09999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1091,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>121000</v>
+        <v>340000</v>
       </c>
       <c r="G15" s="7">
-        <v>11000</v>
+        <v>18000</v>
       </c>
       <c r="H15" s="7">
         <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>7167</v>
+        <v>12667</v>
       </c>
       <c r="J15" s="5">
-        <v>73.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1124,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>93</v>
+        <v>95.2</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>103000</v>
+        <v>152000</v>
       </c>
       <c r="G16" s="7">
-        <v>9000</v>
+        <v>17000</v>
       </c>
       <c r="H16" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I16" s="7">
-        <v>8444</v>
+        <v>13800</v>
       </c>
       <c r="J16" s="5">
-        <v>73.3</v>
+        <v>73.8</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1157,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>92.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>119000</v>
+        <v>719000</v>
       </c>
       <c r="G17" s="7">
-        <v>8000</v>
+        <v>75000</v>
       </c>
       <c r="H17" s="7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I17" s="7">
-        <v>9182</v>
+        <v>15688</v>
       </c>
       <c r="J17" s="5">
-        <v>73.2</v>
+        <v>73.5</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1190,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>90.7</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>196000</v>
+        <v>128000</v>
       </c>
       <c r="G18" s="7">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="H18" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I18" s="7">
-        <v>12727</v>
+        <v>9167</v>
       </c>
       <c r="J18" s="5">
-        <v>73.09999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1223,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>88.2</v>
+        <v>86.3</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>279000</v>
+        <v>388000</v>
       </c>
       <c r="G19" s="7">
-        <v>5000</v>
+        <v>65000</v>
       </c>
       <c r="H19" s="7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
-        <v>16333</v>
+        <v>43000</v>
       </c>
       <c r="J19" s="5">
-        <v>72.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1256,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>98.2</v>
+        <v>93.3</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>135000</v>
+        <v>157000</v>
       </c>
       <c r="G20" s="7">
-        <v>19000</v>
+        <v>14000</v>
       </c>
       <c r="H20" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I20" s="7">
-        <v>13000</v>
+        <v>6286</v>
       </c>
       <c r="J20" s="5">
-        <v>72.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1289,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>90.59999999999999</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>109000</v>
+        <v>202000</v>
       </c>
       <c r="G21" s="7">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I21" s="7">
-        <v>9333</v>
+        <v>12167</v>
       </c>
       <c r="J21" s="5">
-        <v>72.2</v>
+        <v>72.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1322,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>86.59999999999999</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>436000</v>
+        <v>143000</v>
       </c>
       <c r="G22" s="7">
-        <v>-7000</v>
+        <v>5000</v>
       </c>
       <c r="H22" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>17933</v>
+        <v>14333</v>
       </c>
       <c r="J22" s="5">
-        <v>72.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,23 +1355,23 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>91.7</v>
+        <v>88.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>335000</v>
+        <v>339000</v>
       </c>
       <c r="G23" s="7">
+        <v>4000</v>
+      </c>
+      <c r="H23" s="7">
+        <v>7</v>
+      </c>
+      <c r="I23" s="7">
         <v>13000</v>
-      </c>
-      <c r="H23" s="7">
-        <v>6</v>
-      </c>
-      <c r="I23" s="7">
-        <v>14800</v>
       </c>
       <c r="J23" s="5">
         <v>72.09999999999999</v>
@@ -1386,23 +1388,23 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>100000</v>
+        <v>206000</v>
       </c>
       <c r="G24" s="7">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="H24" s="7">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I24" s="7">
-        <v>6778</v>
+        <v>4062</v>
       </c>
       <c r="J24" s="5">
         <v>72.09999999999999</v>
@@ -1419,26 +1421,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>105000</v>
+        <v>589000</v>
       </c>
       <c r="G25" s="7">
-        <v>12000</v>
+        <v>29000</v>
       </c>
       <c r="H25" s="7">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I25" s="7">
-        <v>11250</v>
+        <v>23375</v>
       </c>
       <c r="J25" s="5">
-        <v>71.7</v>
+        <v>72</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1454,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>88.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>644000</v>
+        <v>282000</v>
       </c>
       <c r="G26" s="7">
-        <v>64000</v>
+        <v>3000</v>
       </c>
       <c r="H26" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" s="7">
-        <v>11733</v>
+        <v>15500</v>
       </c>
       <c r="J26" s="5">
-        <v>71.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1487,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>83.40000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>560000</v>
+        <v>128000</v>
       </c>
       <c r="G27" s="7">
-        <v>25000</v>
+        <v>7000</v>
       </c>
       <c r="H27" s="7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I27" s="7">
-        <v>23000</v>
+        <v>7143</v>
       </c>
       <c r="J27" s="5">
-        <v>71.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1520,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>90.8</v>
+        <v>90.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>118000</v>
+        <v>108000</v>
       </c>
       <c r="G28" s="7">
-        <v>7000</v>
+        <v>8000</v>
       </c>
       <c r="H28" s="7">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I28" s="7">
-        <v>5800</v>
+        <v>6900</v>
       </c>
       <c r="J28" s="5">
-        <v>71.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1553,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>562000</v>
+        <v>228000</v>
       </c>
       <c r="G29" s="7">
-        <v>23000</v>
+        <v>7000</v>
       </c>
       <c r="H29" s="7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I29" s="7">
-        <v>22133</v>
+        <v>15800</v>
       </c>
       <c r="J29" s="5">
-        <v>71.2</v>
+        <v>71.5</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1586,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>94</v>
+        <v>90.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>221000</v>
+        <v>100000</v>
       </c>
       <c r="G30" s="7">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I30" s="7">
-        <v>18000</v>
+        <v>7400</v>
       </c>
       <c r="J30" s="5">
-        <v>71.2</v>
+        <v>71.5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1619,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>89.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>138000</v>
+        <v>152000</v>
       </c>
       <c r="G31" s="7">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="H31" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I31" s="7">
-        <v>8100</v>
+        <v>18750</v>
       </c>
       <c r="J31" s="5">
-        <v>71.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1652,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>89.7</v>
+        <v>82.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>106000</v>
+        <v>285000</v>
       </c>
       <c r="G32" s="7">
-        <v>7000</v>
+        <v>25000</v>
       </c>
       <c r="H32" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>7333</v>
+        <v>21429</v>
       </c>
       <c r="J32" s="5">
-        <v>71.2</v>
+        <v>70.8</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1681,30 +1683,28 @@
       <c r="A33" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="5">
-        <v>6.7</v>
-      </c>
+      <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>96.59999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>145000</v>
+        <v>146000</v>
       </c>
       <c r="G33" s="7">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="H33" s="7">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I33" s="7">
-        <v>11750</v>
+        <v>62</v>
       </c>
       <c r="J33" s="5">
-        <v>71.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>81.2</v>
+        <v>82.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>444000</v>
+        <v>581000</v>
       </c>
       <c r="G34" s="7">
-        <v>51000</v>
+        <v>19000</v>
       </c>
       <c r="H34" s="7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I34" s="7">
-        <v>32800</v>
+        <v>21938</v>
       </c>
       <c r="J34" s="5">
-        <v>70.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>82.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>260000</v>
+        <v>422000</v>
       </c>
       <c r="G35" s="7">
-        <v>23000</v>
+        <v>-14000</v>
       </c>
       <c r="H35" s="7">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I35" s="7">
-        <v>20833</v>
+        <v>15938</v>
       </c>
       <c r="J35" s="5">
-        <v>70.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>85.2</v>
+        <v>93.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>238000</v>
+        <v>160000</v>
       </c>
       <c r="G36" s="7">
-        <v>2000</v>
+        <v>18000</v>
       </c>
       <c r="H36" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I36" s="7">
-        <v>13222</v>
+        <v>16250</v>
       </c>
       <c r="J36" s="5">
-        <v>70.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>81.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>521000</v>
+        <v>115000</v>
       </c>
       <c r="G37" s="7">
-        <v>21000</v>
+        <v>10000</v>
       </c>
       <c r="H37" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I37" s="7">
-        <v>21600</v>
+        <v>2000</v>
       </c>
       <c r="J37" s="5">
-        <v>70</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>86.90000000000001</v>
+        <v>86.2</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>182000</v>
+        <v>176000</v>
       </c>
       <c r="G38" s="7">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="H38" s="7">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I38" s="7">
-        <v>8133</v>
+        <v>11692</v>
       </c>
       <c r="J38" s="5">
-        <v>69.8</v>
+        <v>70.3</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>81.2</v>
+        <v>86.2</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>378000</v>
+        <v>173000</v>
       </c>
       <c r="G39" s="7">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="H39" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I39" s="7">
-        <v>19444</v>
+        <v>11000</v>
       </c>
       <c r="J39" s="5">
-        <v>69.5</v>
+        <v>70.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>87.2</v>
+        <v>88.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>194000</v>
+        <v>491000</v>
       </c>
       <c r="G40" s="7">
-        <v>3000</v>
+        <v>47000</v>
       </c>
       <c r="H40" s="7">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I40" s="7">
-        <v>6333</v>
+        <v>6250</v>
       </c>
       <c r="J40" s="5">
-        <v>69.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,28 +1947,30 @@
       <c r="A41" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="5"/>
+      <c r="B41" s="5">
+        <v>6.5</v>
+      </c>
       <c r="C41" s="5">
-        <v>84.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>202000</v>
+        <v>176000</v>
       </c>
       <c r="G41" s="7">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="H41" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I41" s="7">
-        <v>9889</v>
+        <v>8500</v>
       </c>
       <c r="J41" s="5">
-        <v>69.2</v>
+        <v>70</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1984,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>84.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>160000</v>
+        <v>143000</v>
       </c>
       <c r="G42" s="7">
-        <v>-2000</v>
+        <v>12000</v>
       </c>
       <c r="H42" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I42" s="7">
-        <v>10143</v>
+        <v>7125</v>
       </c>
       <c r="J42" s="5">
-        <v>69.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2017,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>87.7</v>
+        <v>88</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>194000</v>
+        <v>122000</v>
       </c>
       <c r="G43" s="7">
         <v>4000</v>
       </c>
       <c r="H43" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I43" s="7">
-        <v>3533</v>
+        <v>5688</v>
       </c>
       <c r="J43" s="5">
-        <v>69.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2050,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>94.8</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>136000</v>
+        <v>113000</v>
       </c>
       <c r="G44" s="7">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="H44" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I44" s="7">
-        <v>19667</v>
+        <v>8571</v>
       </c>
       <c r="J44" s="5">
-        <v>69.09999999999999</v>
+        <v>69.7</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2083,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>80.2</v>
+        <v>95.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>1684000</v>
+        <v>103000</v>
       </c>
       <c r="G45" s="7">
-        <v>-2000</v>
+        <v>10000</v>
       </c>
       <c r="H45" s="7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I45" s="7">
-        <v>18867</v>
+        <v>8000</v>
       </c>
       <c r="J45" s="5">
-        <v>68.8</v>
+        <v>69.7</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2116,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>81.8</v>
+        <v>94.2</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>457000</v>
+        <v>102000</v>
       </c>
       <c r="G46" s="7">
-        <v>19000</v>
+        <v>10000</v>
       </c>
       <c r="H46" s="7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I46" s="7">
-        <v>15400</v>
+        <v>11500</v>
       </c>
       <c r="J46" s="5">
-        <v>68.8</v>
+        <v>69.7</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2149,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>85.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>179000</v>
+        <v>181000</v>
       </c>
       <c r="G47" s="7">
-        <v>3000</v>
+        <v>21000</v>
       </c>
       <c r="H47" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I47" s="7">
-        <v>6917</v>
+        <v>21000</v>
       </c>
       <c r="J47" s="5">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2182,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>77.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>419000</v>
+        <v>180000</v>
       </c>
       <c r="G48" s="7">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="H48" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>23667</v>
+        <v>9625</v>
       </c>
       <c r="J48" s="5">
-        <v>68.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2215,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>80.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>312000</v>
+        <v>533000</v>
       </c>
       <c r="G49" s="7">
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="H49" s="7">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="I49" s="7">
-        <v>17500</v>
+        <v>21000</v>
       </c>
       <c r="J49" s="5">
-        <v>68.59999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2248,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>82.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>176000</v>
+        <v>210000</v>
       </c>
       <c r="G50" s="7">
-        <v>-7000</v>
+        <v>-6000</v>
       </c>
       <c r="H50" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I50" s="7">
-        <v>12667</v>
+        <v>12800</v>
       </c>
       <c r="J50" s="5">
-        <v>68.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2281,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>86.5</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>163000</v>
+        <v>192000</v>
       </c>
       <c r="G51" s="7">
-        <v>2000</v>
+        <v>29000</v>
       </c>
       <c r="H51" s="7">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="I51" s="7">
-        <v>3867</v>
+        <v>32500</v>
       </c>
       <c r="J51" s="5">
-        <v>68.5</v>
+        <v>68.8</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2314,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>83.2</v>
+        <v>80.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>178000</v>
+        <v>1683000</v>
       </c>
       <c r="G52" s="7">
         <v>-1000</v>
       </c>
       <c r="H52" s="7">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I52" s="7">
-        <v>10714</v>
+        <v>17625</v>
       </c>
       <c r="J52" s="5">
-        <v>68.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2347,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>84.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>130000</v>
+        <v>325000</v>
       </c>
       <c r="G53" s="7">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="H53" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I53" s="7">
-        <v>7375</v>
+        <v>17000</v>
       </c>
       <c r="J53" s="5">
-        <v>68.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,27 +2378,25 @@
       <c r="A54" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="B54" s="5">
-        <v>6.5</v>
-      </c>
+      <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>87.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>169000</v>
+        <v>195000</v>
       </c>
       <c r="G54" s="7">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H54" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I54" s="7">
-        <v>8800</v>
+        <v>5571</v>
       </c>
       <c r="J54" s="5">
         <v>68.3</v>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-09-30T05:14:53+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-01T05:29:57+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>不拱火我来汉东干什么？</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>不拱火我来汉东干什么？</t>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>高武，万法同修，一证永证</t>
+  </si>
+  <si>
+    <t>红楼：勋门儒将</t>
   </si>
   <si>
     <t>什么叫我成了灭世级怪谈？</t>
   </si>
   <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>高武，万法同修，一证永证</t>
+    <t>直播见证神话：从鳌太线走蛟开始</t>
+  </si>
+  <si>
+    <t>四合院1948亿万富翁躺平生活</t>
   </si>
   <si>
     <t>四合院：整顿家风，从我妈开始</t>
   </si>
   <si>
+    <t>人在都市，词条成神</t>
+  </si>
+  <si>
+    <t>退伍上大学，教官竟是我带的兵</t>
+  </si>
+  <si>
+    <t>开箱必出神话级，阁下如何应对？</t>
+  </si>
+  <si>
     <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
-    <t>直播见证神话：从鳌太线走蛟开始</t>
-  </si>
-  <si>
-    <t>退伍上大学，教官竟是我带的兵</t>
+    <t>抗战：我黄埔元老开局打爆小鬼子</t>
+  </si>
+  <si>
+    <t>全三国重生，我老六身份藏不住了</t>
+  </si>
+  <si>
+    <t>朱标私生子，老朱逼我当皇帝！</t>
+  </si>
+  <si>
+    <t>我，老头，永远比校花高四个境界</t>
+  </si>
+  <si>
+    <t>玩家都说我是赛博女鬼？</t>
   </si>
   <si>
     <t>火影：越豪越强？胜你无需第二剑</t>
   </si>
   <si>
-    <t>玩家都说我是赛博女鬼？</t>
-  </si>
-  <si>
-    <t>人在都市，词条成神</t>
+    <t>镇国杀神：从拯救落难母女开始</t>
+  </si>
+  <si>
+    <t>凤流高手</t>
   </si>
   <si>
     <t>我的沪上野妻</t>
   </si>
   <si>
+    <t>让你配主题曲，你唱终会与你同行</t>
+  </si>
+  <si>
+    <t>主角死后，未婚妻跟反派的我享福</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>洪荒：截教逆徒，截胡的截！</t>
+  </si>
+  <si>
+    <t>洪荒：我十凶天角蚁，躺平就变强</t>
+  </si>
+  <si>
+    <t>老师，男生也能报考魔女学院吗？</t>
+  </si>
+  <si>
+    <t>星铁观影，曝光虚照就是欢愉星神</t>
+  </si>
+  <si>
+    <t>女尊：我的大号老婆占有欲爆棚！</t>
+  </si>
+  <si>
+    <t>龙族：我的强化每月刷新</t>
+  </si>
+  <si>
+    <t>西游：百眼魔君，一口道钟炼万物</t>
+  </si>
+  <si>
+    <t>全民穿越！我在末日世界养城兽</t>
+  </si>
+  <si>
+    <t>模拟：少年缺悟性吗？借个脑子吧</t>
+  </si>
+  <si>
+    <t>抗美援朝：什么叫这是四合院世界</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
+  </si>
+  <si>
+    <t>海吞天</t>
+  </si>
+  <si>
+    <t>疯掉后，我的故事让全国人痛哭</t>
+  </si>
+  <si>
     <t>盗墓：八岁创雷法，震惊张海琪</t>
   </si>
   <si>
-    <t>朱标私生子，老朱逼我当皇帝！</t>
-  </si>
-  <si>
-    <t>开箱必出神话级，阁下如何应对？</t>
-  </si>
-  <si>
     <t>三角洲：手游主播的我误入巅峰赛</t>
   </si>
   <si>
-    <t>抗战：我黄埔元老开局打爆小鬼子</t>
-  </si>
-  <si>
-    <t>衰神气运逆转，回老家享受生活</t>
-  </si>
-  <si>
-    <t>老师，男生也能报考魔女学院吗？</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>凤流高手</t>
+    <t>女尊：你们快放开我男朋友！</t>
+  </si>
+  <si>
+    <t>大秦：祖龙惊呆，扶苏竟是暴君！</t>
+  </si>
+  <si>
+    <t>很野很欲，楼下的蔷薇正飘香！</t>
+  </si>
+  <si>
+    <t>选择求生：只有我能看到正确答案</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>我的直播通武侠，开局整垮少林寺</t>
   </si>
   <si>
     <t>接待意难平的古人，老祖宗全看着</t>
-  </si>
-  <si>
-    <t>九门：天与暴君模板，震惊陈皮</t>
-  </si>
-  <si>
-    <t>主角死后，未婚妻跟反派的我享福</t>
-  </si>
-  <si>
-    <t>海吞天</t>
-  </si>
-  <si>
-    <t>我，老头，永远比校花高四个境界</t>
-  </si>
-  <si>
-    <t>全民穿越！我在末日世界养城兽</t>
-  </si>
-  <si>
-    <t>洪荒：我十凶天角蚁，躺平就变强</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>游走神话时代，开局拜师道门天师</t>
-  </si>
-  <si>
-    <t>星铁观影，曝光虚照就是欢愉星神</t>
-  </si>
-  <si>
-    <t>模拟：少年缺悟性吗？借个脑子吧</t>
-  </si>
-  <si>
-    <t>抗美援朝：什么叫这是四合院世界</t>
-  </si>
-  <si>
-    <t>选择求生：只有我能看到正确答案</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>搭讪就有奖，加满5000个好友</t>
-  </si>
-  <si>
-    <t>疯掉后，我的故事让全国人痛哭</t>
-  </si>
-  <si>
-    <t>让你去养老大队，你破惊天奇案？</t>
-  </si>
-  <si>
-    <t>女尊：你们快放开我男朋友！</t>
-  </si>
-  <si>
-    <t>年代：一分钟一块钱，创业当首富</t>
-  </si>
-  <si>
-    <t>全民航海：古神对我的船重度依赖</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
-    <t>跑男：系统过于抽象，还好我也是</t>
-  </si>
-  <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
-  </si>
-  <si>
-    <t>很野很欲，楼下的蔷薇正飘香！</t>
-  </si>
-  <si>
-    <t>龙族：我的强化每月刷新</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>我的直播通武侠，开局整垮少林寺</t>
-  </si>
-  <si>
-    <t>被富婆女粉抓住后，我财富自由了</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>84.3</v>
+        <v>95.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1264000</v>
+        <v>587000</v>
       </c>
       <c r="G5" s="7">
-        <v>56000</v>
+        <v>35000</v>
       </c>
       <c r="H5" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I5" s="7">
-        <v>78375</v>
+        <v>37800</v>
       </c>
       <c r="J5" s="5">
-        <v>86</v>
+        <v>81.8</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>97.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>552000</v>
+        <v>1251000</v>
       </c>
       <c r="G6" s="7">
-        <v>45000</v>
+        <v>-13000</v>
       </c>
       <c r="H6" s="7">
         <v>10</v>
       </c>
       <c r="I6" s="7">
-        <v>38111</v>
+        <v>68222</v>
       </c>
       <c r="J6" s="5">
-        <v>83.2</v>
+        <v>80.3</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>96.59999999999999</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>352000</v>
+        <v>1083000</v>
       </c>
       <c r="G7" s="7">
-        <v>31000</v>
+        <v>90000</v>
       </c>
       <c r="H7" s="7">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="I7" s="7">
-        <v>21400</v>
+        <v>43176</v>
       </c>
       <c r="J7" s="5">
-        <v>78.5</v>
+        <v>79</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -856,28 +856,30 @@
       <c r="A8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="5"/>
+      <c r="B8" s="5">
+        <v>6.7</v>
+      </c>
       <c r="C8" s="5">
-        <v>87.5</v>
+        <v>96.3</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>993000</v>
+        <v>210000</v>
       </c>
       <c r="G8" s="7">
-        <v>90000</v>
+        <v>20000</v>
       </c>
       <c r="H8" s="7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>40250</v>
+        <v>18667</v>
       </c>
       <c r="J8" s="5">
-        <v>78.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -889,9 +891,7 @@
       <c r="A9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="5">
-        <v>6.7</v>
-      </c>
+      <c r="B9" s="5"/>
       <c r="C9" s="5">
         <v>100</v>
       </c>
@@ -900,16 +900,16 @@
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>190000</v>
+        <v>108000</v>
       </c>
       <c r="G9" s="7">
-        <v>45000</v>
+        <v>17000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7">
-        <v>18400</v>
+        <v>10250</v>
       </c>
       <c r="J9" s="5">
         <v>77.59999999999999</v>
@@ -926,26 +926,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>93.40000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>316000</v>
+        <v>379000</v>
       </c>
       <c r="G10" s="7">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I10" s="7">
-        <v>25400</v>
+        <v>21750</v>
       </c>
       <c r="J10" s="5">
-        <v>75.7</v>
+        <v>77.5</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -959,26 +959,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>93.59999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>530000</v>
+        <v>542000</v>
       </c>
       <c r="G11" s="7">
-        <v>74000</v>
+        <v>50000</v>
       </c>
       <c r="H11" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I11" s="7">
-        <v>48000</v>
+        <v>37429</v>
       </c>
       <c r="J11" s="5">
-        <v>75.5</v>
+        <v>76.8</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -992,26 +992,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>84.3</v>
+        <v>97</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>492000</v>
+        <v>260000</v>
       </c>
       <c r="G12" s="7">
-        <v>48000</v>
+        <v>27000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I12" s="7">
-        <v>35333</v>
+        <v>12818</v>
       </c>
       <c r="J12" s="5">
-        <v>75.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1025,26 +1025,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>98.7</v>
+        <v>91.8</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>119000</v>
+        <v>332000</v>
       </c>
       <c r="G13" s="7">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>11800</v>
+        <v>23833</v>
       </c>
       <c r="J13" s="5">
-        <v>75.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1058,26 +1058,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>91.5</v>
+        <v>95.3</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>264000</v>
+        <v>171000</v>
       </c>
       <c r="G14" s="7">
-        <v>11000</v>
+        <v>19000</v>
       </c>
       <c r="H14" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>18250</v>
+        <v>14667</v>
       </c>
       <c r="J14" s="5">
-        <v>74.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1091,26 +1091,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>93.2</v>
+        <v>95.7</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>340000</v>
+        <v>131000</v>
       </c>
       <c r="G15" s="7">
-        <v>18000</v>
+        <v>12000</v>
       </c>
       <c r="H15" s="7">
         <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>12667</v>
+        <v>11833</v>
       </c>
       <c r="J15" s="5">
-        <v>74.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1124,26 +1124,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>95.2</v>
+        <v>96.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>152000</v>
+        <v>177000</v>
       </c>
       <c r="G16" s="7">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="H16" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>13800</v>
+        <v>8000</v>
       </c>
       <c r="J16" s="5">
-        <v>73.8</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1157,26 +1157,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>90.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>719000</v>
+        <v>575000</v>
       </c>
       <c r="G17" s="7">
-        <v>75000</v>
+        <v>45000</v>
       </c>
       <c r="H17" s="7">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I17" s="7">
-        <v>15688</v>
+        <v>47250</v>
       </c>
       <c r="J17" s="5">
-        <v>73.5</v>
+        <v>74.8</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1190,26 +1190,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>93.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>128000</v>
+        <v>153000</v>
       </c>
       <c r="G18" s="7">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="H18" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I18" s="7">
-        <v>9167</v>
+        <v>13714</v>
       </c>
       <c r="J18" s="5">
-        <v>73.5</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1223,26 +1223,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>86.3</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>388000</v>
+        <v>129000</v>
       </c>
       <c r="G19" s="7">
-        <v>65000</v>
+        <v>13000</v>
       </c>
       <c r="H19" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I19" s="7">
-        <v>43000</v>
+        <v>4786</v>
       </c>
       <c r="J19" s="5">
-        <v>73.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1256,26 +1256,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>93.3</v>
+        <v>82.2</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>157000</v>
+        <v>423000</v>
       </c>
       <c r="G20" s="7">
-        <v>14000</v>
+        <v>35000</v>
       </c>
       <c r="H20" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
-        <v>6286</v>
+        <v>41400</v>
       </c>
       <c r="J20" s="5">
-        <v>72.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1289,26 +1289,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>202000</v>
+        <v>168000</v>
       </c>
       <c r="G21" s="7">
-        <v>6000</v>
+        <v>16000</v>
       </c>
       <c r="H21" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I21" s="7">
-        <v>12167</v>
+        <v>18200</v>
       </c>
       <c r="J21" s="5">
-        <v>72.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1322,26 +1322,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>88.59999999999999</v>
+        <v>91</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>143000</v>
+        <v>351000</v>
       </c>
       <c r="G22" s="7">
-        <v>5000</v>
+        <v>11000</v>
       </c>
       <c r="H22" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>14333</v>
+        <v>12429</v>
       </c>
       <c r="J22" s="5">
-        <v>72.3</v>
+        <v>73.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1355,26 +1355,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88.8</v>
+        <v>88.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>339000</v>
+        <v>268000</v>
       </c>
       <c r="G23" s="7">
         <v>4000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I23" s="7">
-        <v>13000</v>
+        <v>16667</v>
       </c>
       <c r="J23" s="5">
-        <v>72.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1388,26 +1388,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>92.8</v>
+        <v>88.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>206000</v>
+        <v>331000</v>
       </c>
       <c r="G24" s="7">
-        <v>12000</v>
+        <v>42000</v>
       </c>
       <c r="H24" s="7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I24" s="7">
-        <v>4062</v>
+        <v>16333</v>
       </c>
       <c r="J24" s="5">
-        <v>72.09999999999999</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1421,26 +1421,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>84</v>
+        <v>89.3</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>589000</v>
+        <v>290000</v>
       </c>
       <c r="G25" s="7">
-        <v>29000</v>
+        <v>8000</v>
       </c>
       <c r="H25" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I25" s="7">
-        <v>23375</v>
+        <v>15059</v>
       </c>
       <c r="J25" s="5">
-        <v>72</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1454,26 +1454,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>87.5</v>
+        <v>87.2</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>282000</v>
+        <v>775000</v>
       </c>
       <c r="G26" s="7">
-        <v>3000</v>
+        <v>56000</v>
       </c>
       <c r="H26" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I26" s="7">
-        <v>15500</v>
+        <v>18059</v>
       </c>
       <c r="J26" s="5">
-        <v>72</v>
+        <v>72.5</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1487,26 +1487,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>91.3</v>
+        <v>95.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>128000</v>
+        <v>223000</v>
       </c>
       <c r="G27" s="7">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="H27" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I27" s="7">
-        <v>7143</v>
+        <v>18250</v>
       </c>
       <c r="J27" s="5">
-        <v>72</v>
+        <v>72.3</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1520,26 +1520,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>90.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>108000</v>
+        <v>232000</v>
       </c>
       <c r="G28" s="7">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="H28" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>6900</v>
+        <v>13833</v>
       </c>
       <c r="J28" s="5">
-        <v>71.59999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1553,26 +1553,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90</v>
+        <v>90.3</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>228000</v>
+        <v>548000</v>
       </c>
       <c r="G29" s="7">
-        <v>7000</v>
+        <v>57000</v>
       </c>
       <c r="H29" s="7">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I29" s="7">
-        <v>15800</v>
+        <v>9235</v>
       </c>
       <c r="J29" s="5">
-        <v>71.5</v>
+        <v>72</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1586,26 +1586,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>90.3</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>100000</v>
+        <v>197000</v>
       </c>
       <c r="G30" s="7">
-        <v>5000</v>
+        <v>16000</v>
       </c>
       <c r="H30" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>7400</v>
+        <v>19750</v>
       </c>
       <c r="J30" s="5">
-        <v>71.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1619,26 +1619,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>93.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>152000</v>
+        <v>107000</v>
       </c>
       <c r="G31" s="7">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="H31" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I31" s="7">
-        <v>18750</v>
+        <v>8167</v>
       </c>
       <c r="J31" s="5">
-        <v>71.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1652,26 +1652,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>82.7</v>
+        <v>92.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>285000</v>
+        <v>157000</v>
       </c>
       <c r="G32" s="7">
-        <v>25000</v>
+        <v>11000</v>
       </c>
       <c r="H32" s="7">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I32" s="7">
-        <v>21429</v>
+        <v>706</v>
       </c>
       <c r="J32" s="5">
-        <v>70.8</v>
+        <v>71.2</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1685,26 +1685,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.3</v>
+        <v>91</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>146000</v>
+        <v>215000</v>
       </c>
       <c r="G33" s="7">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="H33" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I33" s="7">
-        <v>62</v>
+        <v>4353</v>
       </c>
       <c r="J33" s="5">
-        <v>70.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>82.2</v>
+        <v>89.5</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>581000</v>
+        <v>172000</v>
       </c>
       <c r="G34" s="7">
-        <v>19000</v>
+        <v>12000</v>
       </c>
       <c r="H34" s="7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>21938</v>
+        <v>15400</v>
       </c>
       <c r="J34" s="5">
-        <v>70.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>84.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>422000</v>
+        <v>118000</v>
       </c>
       <c r="G35" s="7">
-        <v>-14000</v>
+        <v>45000</v>
       </c>
       <c r="H35" s="7">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I35" s="7">
-        <v>15938</v>
+        <v>18667</v>
       </c>
       <c r="J35" s="5">
-        <v>70.7</v>
+        <v>71</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>93.7</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>160000</v>
+        <v>214000</v>
       </c>
       <c r="G36" s="7">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="H36" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I36" s="7">
-        <v>16250</v>
+        <v>29000</v>
       </c>
       <c r="J36" s="5">
-        <v>70.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>90.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>115000</v>
+        <v>105000</v>
       </c>
       <c r="G37" s="7">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="H37" s="7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I37" s="7">
-        <v>2000</v>
+        <v>7778</v>
       </c>
       <c r="J37" s="5">
-        <v>70.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>86.2</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>176000</v>
+        <v>310000</v>
       </c>
       <c r="G38" s="7">
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="H38" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I38" s="7">
-        <v>11692</v>
+        <v>21875</v>
       </c>
       <c r="J38" s="5">
-        <v>70.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>86.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>173000</v>
+        <v>126000</v>
       </c>
       <c r="G39" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H39" s="7">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="I39" s="7">
-        <v>11000</v>
+        <v>2529</v>
       </c>
       <c r="J39" s="5">
-        <v>70.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>88.2</v>
+        <v>86.8</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>491000</v>
+        <v>177000</v>
       </c>
       <c r="G40" s="7">
-        <v>47000</v>
+        <v>1000</v>
       </c>
       <c r="H40" s="7">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I40" s="7">
-        <v>6250</v>
+        <v>10929</v>
       </c>
       <c r="J40" s="5">
-        <v>70.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,30 +1947,28 @@
       <c r="A41" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B41" s="5">
-        <v>6.5</v>
-      </c>
+      <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>87</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>176000</v>
+        <v>602000</v>
       </c>
       <c r="G41" s="7">
-        <v>7000</v>
+        <v>13000</v>
       </c>
       <c r="H41" s="7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I41" s="7">
-        <v>8500</v>
+        <v>22765</v>
       </c>
       <c r="J41" s="5">
-        <v>70</v>
+        <v>70.3</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1984,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>87.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>143000</v>
+        <v>597000</v>
       </c>
       <c r="G42" s="7">
-        <v>12000</v>
+        <v>16000</v>
       </c>
       <c r="H42" s="7">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I42" s="7">
-        <v>7125</v>
+        <v>21588</v>
       </c>
       <c r="J42" s="5">
-        <v>69.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2017,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>88</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>122000</v>
+        <v>158000</v>
       </c>
       <c r="G43" s="7">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H43" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I43" s="7">
-        <v>5688</v>
+        <v>3118</v>
       </c>
       <c r="J43" s="5">
-        <v>69.8</v>
+        <v>70.2</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2050,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>113000</v>
+        <v>103000</v>
       </c>
       <c r="G44" s="7">
-        <v>4000</v>
+        <v>3000</v>
       </c>
       <c r="H44" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I44" s="7">
-        <v>8571</v>
+        <v>7000</v>
       </c>
       <c r="J44" s="5">
-        <v>69.7</v>
+        <v>70.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2083,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>95.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>103000</v>
+        <v>153000</v>
       </c>
       <c r="G45" s="7">
         <v>10000</v>
       </c>
       <c r="H45" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I45" s="7">
-        <v>8000</v>
+        <v>7444</v>
       </c>
       <c r="J45" s="5">
-        <v>69.7</v>
+        <v>69.8</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2116,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>94.2</v>
+        <v>86.3</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>102000</v>
+        <v>129000</v>
       </c>
       <c r="G46" s="7">
-        <v>10000</v>
+        <v>1000</v>
       </c>
       <c r="H46" s="7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I46" s="7">
-        <v>11500</v>
+        <v>8538</v>
       </c>
       <c r="J46" s="5">
-        <v>69.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2149,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>94.40000000000001</v>
+        <v>85</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>181000</v>
+        <v>199000</v>
       </c>
       <c r="G47" s="7">
-        <v>21000</v>
+        <v>-3000</v>
       </c>
       <c r="H47" s="7">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I47" s="7">
-        <v>21000</v>
+        <v>11000</v>
       </c>
       <c r="J47" s="5">
-        <v>69.2</v>
+        <v>69.5</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2182,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>84.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>180000</v>
+        <v>117000</v>
       </c>
       <c r="G48" s="7">
-        <v>2000</v>
+        <v>4000</v>
       </c>
       <c r="H48" s="7">
         <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>9625</v>
+        <v>8000</v>
       </c>
       <c r="J48" s="5">
-        <v>69.09999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2215,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>79.3</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>533000</v>
+        <v>106000</v>
       </c>
       <c r="G49" s="7">
-        <v>12000</v>
+        <v>27000</v>
       </c>
       <c r="H49" s="7">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I49" s="7">
-        <v>21000</v>
+        <v>26500</v>
       </c>
       <c r="J49" s="5">
-        <v>68.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2248,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>83</v>
+        <v>84.3</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>210000</v>
+        <v>207000</v>
       </c>
       <c r="G50" s="7">
-        <v>-6000</v>
+        <v>-3000</v>
       </c>
       <c r="H50" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I50" s="7">
-        <v>12800</v>
+        <v>11364</v>
       </c>
       <c r="J50" s="5">
-        <v>68.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2281,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>93.90000000000001</v>
+        <v>85</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>192000</v>
+        <v>171000</v>
       </c>
       <c r="G51" s="7">
-        <v>29000</v>
+        <v>-2000</v>
       </c>
       <c r="H51" s="7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I51" s="7">
-        <v>32500</v>
+        <v>9818</v>
       </c>
       <c r="J51" s="5">
-        <v>68.8</v>
+        <v>69.2</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2314,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>80.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>1683000</v>
+        <v>617000</v>
       </c>
       <c r="G52" s="7">
-        <v>-1000</v>
+        <v>73000</v>
       </c>
       <c r="H52" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I52" s="7">
-        <v>17625</v>
+        <v>9588</v>
       </c>
       <c r="J52" s="5">
-        <v>68.5</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2347,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>80.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>325000</v>
+        <v>343000</v>
       </c>
       <c r="G53" s="7">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="H53" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I53" s="7">
-        <v>17000</v>
+        <v>17100</v>
       </c>
       <c r="J53" s="5">
-        <v>68.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2380,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>85.3</v>
+        <v>86.3</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>195000</v>
+        <v>129000</v>
       </c>
       <c r="G54" s="7">
         <v>1000</v>
       </c>
       <c r="H54" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I54" s="7">
-        <v>5571</v>
+        <v>6375</v>
       </c>
       <c r="J54" s="5">
-        <v>68.3</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-01T05:29:57+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-02T05:16:16+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
-    <t>不拱火我来汉东干什么？</t>
+    <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
     <t>打开作品</t>
   </si>
   <si>
-    <t>封神：开局反出西岐，我死守渑池</t>
-  </si>
-  <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
-    <t>高武，万法同修，一证永证</t>
-  </si>
-  <si>
-    <t>红楼：勋门儒将</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
+    <t>朱标私生子，老朱逼我当皇帝！</t>
+  </si>
+  <si>
+    <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
     <t>直播见证神话：从鳌太线走蛟开始</t>
   </si>
   <si>
-    <t>四合院1948亿万富翁躺平生活</t>
-  </si>
-  <si>
-    <t>四合院：整顿家风，从我妈开始</t>
-  </si>
-  <si>
-    <t>人在都市，词条成神</t>
-  </si>
-  <si>
-    <t>退伍上大学，教官竟是我带的兵</t>
-  </si>
-  <si>
-    <t>开箱必出神话级，阁下如何应对？</t>
-  </si>
-  <si>
-    <t>从修仙回到都市，坏消息修为没了</t>
-  </si>
-  <si>
-    <t>抗战：我黄埔元老开局打爆小鬼子</t>
-  </si>
-  <si>
-    <t>全三国重生，我老六身份藏不住了</t>
-  </si>
-  <si>
-    <t>朱标私生子，老朱逼我当皇帝！</t>
-  </si>
-  <si>
-    <t>我，老头，永远比校花高四个境界</t>
-  </si>
-  <si>
-    <t>玩家都说我是赛博女鬼？</t>
-  </si>
-  <si>
-    <t>火影：越豪越强？胜你无需第二剑</t>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>我的沪上野妻</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>地球不允许我这么牛逼的存在！</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>网游：我的药剂永久持续</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
+  </si>
+  <si>
+    <t>系统延迟一坤年，我成了全球股东</t>
   </si>
   <si>
     <t>镇国杀神：从拯救落难母女开始</t>
   </si>
   <si>
-    <t>凤流高手</t>
-  </si>
-  <si>
-    <t>我的沪上野妻</t>
-  </si>
-  <si>
-    <t>让你配主题曲，你唱终会与你同行</t>
-  </si>
-  <si>
-    <t>主角死后，未婚妻跟反派的我享福</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
-    <t>洪荒：截教逆徒，截胡的截！</t>
-  </si>
-  <si>
-    <t>洪荒：我十凶天角蚁，躺平就变强</t>
-  </si>
-  <si>
-    <t>老师，男生也能报考魔女学院吗？</t>
-  </si>
-  <si>
-    <t>星铁观影，曝光虚照就是欢愉星神</t>
-  </si>
-  <si>
-    <t>女尊：我的大号老婆占有欲爆棚！</t>
-  </si>
-  <si>
-    <t>龙族：我的强化每月刷新</t>
-  </si>
-  <si>
-    <t>西游：百眼魔君，一口道钟炼万物</t>
-  </si>
-  <si>
     <t>全民穿越！我在末日世界养城兽</t>
   </si>
   <si>
-    <t>模拟：少年缺悟性吗？借个脑子吧</t>
-  </si>
-  <si>
-    <t>抗美援朝：什么叫这是四合院世界</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>刚穿越洪荒，就要被弑神枪钉死了</t>
-  </si>
-  <si>
-    <t>海吞天</t>
-  </si>
-  <si>
-    <t>疯掉后，我的故事让全国人痛哭</t>
-  </si>
-  <si>
-    <t>盗墓：八岁创雷法，震惊张海琪</t>
-  </si>
-  <si>
-    <t>三角洲：手游主播的我误入巅峰赛</t>
-  </si>
-  <si>
-    <t>女尊：你们快放开我男朋友！</t>
-  </si>
-  <si>
-    <t>大秦：祖龙惊呆，扶苏竟是暴君！</t>
-  </si>
-  <si>
-    <t>很野很欲，楼下的蔷薇正飘香！</t>
-  </si>
-  <si>
-    <t>选择求生：只有我能看到正确答案</t>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>我的直播通武侠，开局整垮少林寺</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
+  </si>
+  <si>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>四合院：老易有了个天才孤儿侄子</t>
+  </si>
+  <si>
+    <t>直播我和徐妙云，老朱全家破防了</t>
   </si>
   <si>
     <t>我都宇宙之主了，你们还在地球？</t>
   </si>
   <si>
-    <t>我的直播通武侠，开局整垮少林寺</t>
-  </si>
-  <si>
-    <t>接待意难平的古人，老祖宗全看着</t>
+    <t>天灾末世：我能提取神话词条</t>
+  </si>
+  <si>
+    <t>文臣尽头是武斗？我在朝堂横着走</t>
+  </si>
+  <si>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>抗战：把父亲捧成将星</t>
+  </si>
+  <si>
+    <t>四合院：从李云龙战友开始</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>三角洲：我有1哈夫币秒杀系统！</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>完美犯罪？在我的眼里全是破绽！</t>
+  </si>
+  <si>
+    <t>点星九藏</t>
+  </si>
+  <si>
+    <t>村花的傻子老公</t>
+  </si>
+  <si>
+    <t>县城：女友出国要我卖房，给脸了</t>
+  </si>
+  <si>
+    <t>穿越神祇：我提取词条碾压诸神</t>
+  </si>
+  <si>
+    <t>机甲武神：从矿星开始</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>天渊</t>
+  </si>
+  <si>
+    <t>扛着棺材去修仙</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>聚宝仙盆</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>末日生存方案供应商</t>
+  </si>
+  <si>
+    <t>猎魔人小姐，我真不是血族</t>
+  </si>
+  <si>
+    <t>全民公路求生：我的房车无限进化</t>
+  </si>
+  <si>
+    <t>罪案现场，那些轰动全国的大案</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>95.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>587000</v>
+        <v>1275000</v>
       </c>
       <c r="G5" s="7">
-        <v>35000</v>
+        <v>24000</v>
       </c>
       <c r="H5" s="7">
         <v>11</v>
       </c>
       <c r="I5" s="7">
-        <v>37800</v>
+        <v>63800</v>
       </c>
       <c r="J5" s="5">
-        <v>81.8</v>
+        <v>80.8</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>78.59999999999999</v>
+        <v>87</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1251000</v>
+        <v>1173000</v>
       </c>
       <c r="G6" s="7">
-        <v>-13000</v>
+        <v>90000</v>
       </c>
       <c r="H6" s="7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I6" s="7">
-        <v>68222</v>
+        <v>45778</v>
       </c>
       <c r="J6" s="5">
-        <v>80.3</v>
+        <v>79.3</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>87.59999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1083000</v>
+        <v>465000</v>
       </c>
       <c r="G7" s="7">
-        <v>90000</v>
+        <v>42000</v>
       </c>
       <c r="H7" s="7">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>43176</v>
+        <v>41500</v>
       </c>
       <c r="J7" s="5">
-        <v>79</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -856,30 +856,28 @@
       <c r="A8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="5">
-        <v>6.7</v>
-      </c>
+      <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>96.3</v>
+        <v>85.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>210000</v>
+        <v>613000</v>
       </c>
       <c r="G8" s="7">
-        <v>20000</v>
+        <v>38000</v>
       </c>
       <c r="H8" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I8" s="7">
-        <v>18667</v>
+        <v>45400</v>
       </c>
       <c r="J8" s="5">
-        <v>77.59999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -893,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>108000</v>
+        <v>562000</v>
       </c>
       <c r="G9" s="7">
-        <v>17000</v>
+        <v>20000</v>
       </c>
       <c r="H9" s="7">
         <v>9</v>
       </c>
       <c r="I9" s="7">
-        <v>10250</v>
+        <v>35250</v>
       </c>
       <c r="J9" s="5">
-        <v>77.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -926,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>94.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>379000</v>
+        <v>608000</v>
       </c>
       <c r="G10" s="7">
-        <v>27000</v>
+        <v>60000</v>
       </c>
       <c r="H10" s="7">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I10" s="7">
-        <v>21750</v>
+        <v>12056</v>
       </c>
       <c r="J10" s="5">
-        <v>77.5</v>
+        <v>72.5</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -959,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>86.3</v>
+        <v>84.2</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>542000</v>
+        <v>811000</v>
       </c>
       <c r="G11" s="7">
-        <v>50000</v>
+        <v>36000</v>
       </c>
       <c r="H11" s="7">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I11" s="7">
-        <v>37429</v>
+        <v>19056</v>
       </c>
       <c r="J11" s="5">
-        <v>76.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -992,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>260000</v>
+        <v>620000</v>
       </c>
       <c r="G12" s="7">
-        <v>27000</v>
+        <v>18000</v>
       </c>
       <c r="H12" s="7">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I12" s="7">
-        <v>12818</v>
+        <v>22500</v>
       </c>
       <c r="J12" s="5">
-        <v>76.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1025,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>91.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>332000</v>
+        <v>313000</v>
       </c>
       <c r="G13" s="7">
-        <v>16000</v>
+        <v>29000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>23833</v>
+        <v>24000</v>
       </c>
       <c r="J13" s="5">
-        <v>76.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1058,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>95.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>171000</v>
+        <v>613000</v>
       </c>
       <c r="G14" s="7">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I14" s="7">
-        <v>14667</v>
+        <v>21278</v>
       </c>
       <c r="J14" s="5">
-        <v>76.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1091,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>95.7</v>
+        <v>86.5</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>131000</v>
+        <v>221000</v>
       </c>
       <c r="G15" s="7">
-        <v>12000</v>
+        <v>27000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I15" s="7">
-        <v>11833</v>
+        <v>6455</v>
       </c>
       <c r="J15" s="5">
-        <v>75.59999999999999</v>
+        <v>69.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1124,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>96.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>177000</v>
+        <v>550000</v>
       </c>
       <c r="G16" s="7">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="H16" s="7">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I16" s="7">
-        <v>8000</v>
+        <v>19611</v>
       </c>
       <c r="J16" s="5">
-        <v>75.09999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1157,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>87.3</v>
+        <v>80</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>575000</v>
+        <v>484000</v>
       </c>
       <c r="G17" s="7">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="H17" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I17" s="7">
-        <v>47250</v>
+        <v>18889</v>
       </c>
       <c r="J17" s="5">
-        <v>74.8</v>
+        <v>68.7</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1190,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>92.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>153000</v>
+        <v>350000</v>
       </c>
       <c r="G18" s="7">
-        <v>10000</v>
+        <v>19000</v>
       </c>
       <c r="H18" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I18" s="7">
-        <v>13714</v>
+        <v>16600</v>
       </c>
       <c r="J18" s="5">
-        <v>74.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1223,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>95.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>129000</v>
+        <v>327000</v>
       </c>
       <c r="G19" s="7">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="H19" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I19" s="7">
-        <v>4786</v>
+        <v>21333</v>
       </c>
       <c r="J19" s="5">
-        <v>73.90000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1256,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>82.2</v>
+        <v>80.5</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>423000</v>
+        <v>499000</v>
       </c>
       <c r="G20" s="7">
-        <v>35000</v>
+        <v>29000</v>
       </c>
       <c r="H20" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I20" s="7">
-        <v>41400</v>
+        <v>16273</v>
       </c>
       <c r="J20" s="5">
-        <v>73.59999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1289,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>92.5</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>168000</v>
+        <v>354000</v>
       </c>
       <c r="G21" s="7">
-        <v>16000</v>
+        <v>11000</v>
       </c>
       <c r="H21" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I21" s="7">
-        <v>18200</v>
+        <v>16545</v>
       </c>
       <c r="J21" s="5">
-        <v>73.40000000000001</v>
+        <v>68.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1322,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>91</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>351000</v>
+        <v>499000</v>
       </c>
       <c r="G22" s="7">
-        <v>11000</v>
+        <v>17000</v>
       </c>
       <c r="H22" s="7">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I22" s="7">
-        <v>12429</v>
+        <v>15167</v>
       </c>
       <c r="J22" s="5">
-        <v>73.2</v>
+        <v>68</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1355,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>88.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>268000</v>
+        <v>355000</v>
       </c>
       <c r="G23" s="7">
-        <v>4000</v>
+        <v>16000</v>
       </c>
       <c r="H23" s="7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I23" s="7">
-        <v>16667</v>
+        <v>12667</v>
       </c>
       <c r="J23" s="5">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1388,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>88.8</v>
+        <v>80.3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>331000</v>
+        <v>1669000</v>
       </c>
       <c r="G24" s="7">
-        <v>42000</v>
+        <v>1000</v>
       </c>
       <c r="H24" s="7">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="I24" s="7">
-        <v>16333</v>
+        <v>14889</v>
       </c>
       <c r="J24" s="5">
-        <v>72.90000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1421,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89.3</v>
+        <v>79.8</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>290000</v>
+        <v>376000</v>
       </c>
       <c r="G25" s="7">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="H25" s="7">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>15059</v>
+        <v>15667</v>
       </c>
       <c r="J25" s="5">
-        <v>72.90000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1454,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>87.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>775000</v>
+        <v>806000</v>
       </c>
       <c r="G26" s="7">
-        <v>56000</v>
+        <v>7000</v>
       </c>
       <c r="H26" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I26" s="7">
-        <v>18059</v>
+        <v>15111</v>
       </c>
       <c r="J26" s="5">
-        <v>72.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1487,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>95.8</v>
+        <v>81</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>223000</v>
+        <v>675000</v>
       </c>
       <c r="G27" s="7">
-        <v>20000</v>
+        <v>58000</v>
       </c>
       <c r="H27" s="7">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I27" s="7">
-        <v>18250</v>
+        <v>12278</v>
       </c>
       <c r="J27" s="5">
-        <v>72.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1520,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>88.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>232000</v>
+        <v>319000</v>
       </c>
       <c r="G28" s="7">
-        <v>4000</v>
+        <v>24000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I28" s="7">
-        <v>13833</v>
+        <v>20800</v>
       </c>
       <c r="J28" s="5">
-        <v>72.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1553,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90.3</v>
+        <v>78.8</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>548000</v>
+        <v>446000</v>
       </c>
       <c r="G29" s="7">
-        <v>57000</v>
+        <v>20000</v>
       </c>
       <c r="H29" s="7">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>9235</v>
+        <v>15000</v>
       </c>
       <c r="J29" s="5">
-        <v>72</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1586,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>93.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>197000</v>
+        <v>389000</v>
       </c>
       <c r="G30" s="7">
-        <v>16000</v>
+        <v>4000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I30" s="7">
-        <v>19750</v>
+        <v>12889</v>
       </c>
       <c r="J30" s="5">
-        <v>71.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1619,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>89.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>107000</v>
+        <v>206000</v>
       </c>
       <c r="G31" s="7">
-        <v>10000</v>
+        <v>20000</v>
       </c>
       <c r="H31" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I31" s="7">
-        <v>8167</v>
+        <v>11125</v>
       </c>
       <c r="J31" s="5">
-        <v>71.3</v>
+        <v>66.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1652,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>92.7</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>157000</v>
+        <v>307000</v>
       </c>
       <c r="G32" s="7">
-        <v>11000</v>
+        <v>34000</v>
       </c>
       <c r="H32" s="7">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I32" s="7">
-        <v>706</v>
+        <v>38000</v>
       </c>
       <c r="J32" s="5">
-        <v>71.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1685,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>91</v>
+        <v>81.7</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>215000</v>
+        <v>233000</v>
       </c>
       <c r="G33" s="7">
-        <v>9000</v>
+        <v>24000</v>
       </c>
       <c r="H33" s="7">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I33" s="7">
-        <v>4353</v>
+        <v>6400</v>
       </c>
       <c r="J33" s="5">
-        <v>71.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>89.5</v>
+        <v>77.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>172000</v>
+        <v>331000</v>
       </c>
       <c r="G34" s="7">
+        <v>6000</v>
+      </c>
+      <c r="H34" s="7">
+        <v>12</v>
+      </c>
+      <c r="I34" s="7">
         <v>12000</v>
       </c>
-      <c r="H34" s="7">
-        <v>6</v>
-      </c>
-      <c r="I34" s="7">
-        <v>15400</v>
-      </c>
       <c r="J34" s="5">
-        <v>71.09999999999999</v>
+        <v>65.8</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>98.7</v>
+        <v>82.7</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>118000</v>
+        <v>354000</v>
       </c>
       <c r="G35" s="7">
-        <v>45000</v>
+        <v>50000</v>
       </c>
       <c r="H35" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I35" s="7">
-        <v>18667</v>
+        <v>44500</v>
       </c>
       <c r="J35" s="5">
-        <v>71</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>93.90000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>214000</v>
+        <v>288000</v>
       </c>
       <c r="G36" s="7">
-        <v>22000</v>
+        <v>14000</v>
       </c>
       <c r="H36" s="7">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I36" s="7">
-        <v>29000</v>
+        <v>2000</v>
       </c>
       <c r="J36" s="5">
-        <v>70.90000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>88.90000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>105000</v>
+        <v>292000</v>
       </c>
       <c r="G37" s="7">
         <v>7000</v>
       </c>
       <c r="H37" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" s="7">
-        <v>7778</v>
+        <v>14200</v>
       </c>
       <c r="J37" s="5">
-        <v>70.8</v>
+        <v>64.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>82.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>310000</v>
+        <v>359000</v>
       </c>
       <c r="G38" s="7">
-        <v>25000</v>
+        <v>13000</v>
       </c>
       <c r="H38" s="7">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I38" s="7">
-        <v>21875</v>
+        <v>1000</v>
       </c>
       <c r="J38" s="5">
-        <v>70.59999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>90.90000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>126000</v>
+        <v>451000</v>
       </c>
       <c r="G39" s="7">
-        <v>11000</v>
+        <v>-9000</v>
       </c>
       <c r="H39" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I39" s="7">
-        <v>2529</v>
+        <v>9944</v>
       </c>
       <c r="J39" s="5">
-        <v>70.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86.8</v>
+        <v>75.5</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>177000</v>
+        <v>681000</v>
       </c>
       <c r="G40" s="7">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="H40" s="7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="I40" s="7">
-        <v>10929</v>
+        <v>11222</v>
       </c>
       <c r="J40" s="5">
-        <v>70.5</v>
+        <v>64.3</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>81.09999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>602000</v>
+        <v>403000</v>
       </c>
       <c r="G41" s="7">
-        <v>13000</v>
+        <v>-10000</v>
       </c>
       <c r="H41" s="7">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I41" s="7">
-        <v>22765</v>
+        <v>16417</v>
       </c>
       <c r="J41" s="5">
-        <v>70.3</v>
+        <v>64.3</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>81.59999999999999</v>
+        <v>76.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>597000</v>
+        <v>400000</v>
       </c>
       <c r="G42" s="7">
-        <v>16000</v>
+        <v>-6000</v>
       </c>
       <c r="H42" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I42" s="7">
-        <v>21588</v>
+        <v>8944</v>
       </c>
       <c r="J42" s="5">
-        <v>70.3</v>
+        <v>64.3</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>89.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>158000</v>
+        <v>352000</v>
       </c>
       <c r="G43" s="7">
-        <v>6000</v>
+        <v>29000</v>
       </c>
       <c r="H43" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I43" s="7">
-        <v>3118</v>
+        <v>2889</v>
       </c>
       <c r="J43" s="5">
-        <v>70.2</v>
+        <v>64.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>88.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>103000</v>
+        <v>1212000</v>
       </c>
       <c r="G44" s="7">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="H44" s="7">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I44" s="7">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="J44" s="5">
-        <v>70.2</v>
+        <v>64.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>87.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>153000</v>
+        <v>218000</v>
       </c>
       <c r="G45" s="7">
-        <v>10000</v>
+        <v>45000</v>
       </c>
       <c r="H45" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
-        <v>7444</v>
+        <v>22667</v>
       </c>
       <c r="J45" s="5">
-        <v>69.8</v>
+        <v>64</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>86.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>129000</v>
+        <v>505000</v>
       </c>
       <c r="G46" s="7">
-        <v>1000</v>
+        <v>26000</v>
       </c>
       <c r="H46" s="7">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I46" s="7">
-        <v>8538</v>
+        <v>2056</v>
       </c>
       <c r="J46" s="5">
-        <v>69.59999999999999</v>
+        <v>63.9</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>85</v>
+        <v>77.7</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>199000</v>
+        <v>451000</v>
       </c>
       <c r="G47" s="7">
-        <v>-3000</v>
+        <v>5000</v>
       </c>
       <c r="H47" s="7">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I47" s="7">
-        <v>11000</v>
+        <v>4278</v>
       </c>
       <c r="J47" s="5">
-        <v>69.5</v>
+        <v>63.8</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>86.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>117000</v>
+        <v>1106000</v>
       </c>
       <c r="G48" s="7">
-        <v>4000</v>
+        <v>-2000</v>
       </c>
       <c r="H48" s="7">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I48" s="7">
-        <v>8000</v>
+        <v>2389</v>
       </c>
       <c r="J48" s="5">
-        <v>69.5</v>
+        <v>63.7</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>97.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>106000</v>
+        <v>792000</v>
       </c>
       <c r="G49" s="7">
-        <v>27000</v>
+        <v>-12000</v>
       </c>
       <c r="H49" s="7">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="I49" s="7">
-        <v>26500</v>
+        <v>6444</v>
       </c>
       <c r="J49" s="5">
-        <v>69.3</v>
+        <v>63.6</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>84.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>207000</v>
+        <v>542000</v>
       </c>
       <c r="G50" s="7">
-        <v>-3000</v>
+        <v>4000</v>
       </c>
       <c r="H50" s="7">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I50" s="7">
-        <v>11364</v>
+        <v>1333</v>
       </c>
       <c r="J50" s="5">
-        <v>69.2</v>
+        <v>63.6</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>171000</v>
+        <v>406000</v>
       </c>
       <c r="G51" s="7">
-        <v>-2000</v>
+        <v>42000</v>
       </c>
       <c r="H51" s="7">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I51" s="7">
-        <v>9818</v>
+        <v>8444</v>
       </c>
       <c r="J51" s="5">
-        <v>69.2</v>
+        <v>63.6</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84.90000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>617000</v>
+        <v>369000</v>
       </c>
       <c r="G52" s="7">
-        <v>73000</v>
+        <v>3000</v>
       </c>
       <c r="H52" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I52" s="7">
-        <v>9588</v>
+        <v>1056</v>
       </c>
       <c r="J52" s="5">
-        <v>69.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>81.5</v>
+        <v>76.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>343000</v>
+        <v>145000</v>
       </c>
       <c r="G53" s="7">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="H53" s="7">
         <v>11</v>
       </c>
       <c r="I53" s="7">
-        <v>17100</v>
+        <v>5500</v>
       </c>
       <c r="J53" s="5">
-        <v>69.09999999999999</v>
+        <v>63.5</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>86.3</v>
+        <v>77.3</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>129000</v>
+        <v>185000</v>
       </c>
       <c r="G54" s="7">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="H54" s="7">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I54" s="7">
-        <v>6375</v>
+        <v>2167</v>
       </c>
       <c r="J54" s="5">
-        <v>69.09999999999999</v>
+        <v>63.1</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-02T05:16:16+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-03T05:00:28+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
+    <t>从修仙回到都市，坏消息修为没了</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>魏家孽种成首辅，全族跪求我认祖</t>
   </si>
   <si>
     <t>朱标私生子，老朱逼我当皇帝！</t>
   </si>
   <si>
-    <t>从修仙回到都市，坏消息修为没了</t>
-  </si>
-  <si>
     <t>直播见证神话：从鳌太线走蛟开始</t>
   </si>
   <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>系统延迟一坤年，我成了全球股东</t>
+  </si>
+  <si>
+    <t>地球不允许我这么牛逼的存在！</t>
+  </si>
+  <si>
+    <t>天灾末世：我能提取神话词条</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
   </si>
   <si>
     <t>我的沪上野妻</t>
   </si>
   <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>地球不允许我这么牛逼的存在！</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
+  </si>
+  <si>
+    <t>镇国杀神：从拯救落难母女开始</t>
+  </si>
+  <si>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
     <t>网游：我的药剂永久持续</t>
   </si>
   <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
-  </si>
-  <si>
-    <t>系统延迟一坤年，我成了全球股东</t>
-  </si>
-  <si>
-    <t>镇国杀神：从拯救落难母女开始</t>
+    <t>抗战：把父亲捧成将星</t>
+  </si>
+  <si>
+    <t>直播我和徐妙云，老朱全家破防了</t>
+  </si>
+  <si>
+    <t>三角洲：我有1哈夫币秒杀系统！</t>
+  </si>
+  <si>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>四合院：老易有了个天才孤儿侄子</t>
   </si>
   <si>
     <t>全民穿越！我在末日世界养城兽</t>
   </si>
   <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>扛着棺材去修仙</t>
   </si>
   <si>
     <t>我的直播通武侠，开局整垮少林寺</t>
   </si>
   <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>四合院：老易有了个天才孤儿侄子</t>
-  </si>
-  <si>
-    <t>直播我和徐妙云，老朱全家破防了</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>天灾末世：我能提取神话词条</t>
+    <t>重生之我卖的真是高压锅</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>村花的傻子老公</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>穿越神祇：我提取词条碾压诸神</t>
+  </si>
+  <si>
+    <t>全民公路求生：我的房车无限进化</t>
+  </si>
+  <si>
+    <t>完美犯罪？在我的眼里全是破绽！</t>
+  </si>
+  <si>
+    <t>全民神祇时代：我的词条每日刷新</t>
+  </si>
+  <si>
+    <t>人在成龙，我有一个老乡聊天群！</t>
   </si>
   <si>
     <t>文臣尽头是武斗？我在朝堂横着走</t>
   </si>
   <si>
-    <t>从零开始，打造华夏首支特种部队</t>
-  </si>
-  <si>
-    <t>抗战：把父亲捧成将星</t>
+    <t>神雕：全真出了个记仇真人！</t>
+  </si>
+  <si>
+    <t>谍战：这个外科医生潜伏得很深</t>
+  </si>
+  <si>
+    <t>末日生存方案供应商</t>
   </si>
   <si>
     <t>四合院：从李云龙战友开始</t>
   </si>
   <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>三角洲：我有1哈夫币秒杀系统！</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>完美犯罪？在我的眼里全是破绽！</t>
-  </si>
-  <si>
-    <t>点星九藏</t>
-  </si>
-  <si>
-    <t>村花的傻子老公</t>
-  </si>
-  <si>
-    <t>县城：女友出国要我卖房，给脸了</t>
-  </si>
-  <si>
-    <t>穿越神祇：我提取词条碾压诸神</t>
-  </si>
-  <si>
-    <t>机甲武神：从矿星开始</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>天渊</t>
-  </si>
-  <si>
-    <t>扛着棺材去修仙</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
   </si>
   <si>
     <t>聚宝仙盆</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>末日生存方案供应商</t>
-  </si>
-  <si>
-    <t>猎魔人小姐，我真不是血族</t>
-  </si>
-  <si>
-    <t>全民公路求生：我的房车无限进化</t>
-  </si>
-  <si>
-    <t>罪案现场，那些轰动全国的大案</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>81.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1275000</v>
+        <v>1278000</v>
       </c>
       <c r="G5" s="7">
-        <v>24000</v>
+        <v>105000</v>
       </c>
       <c r="H5" s="7">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I5" s="7">
-        <v>63800</v>
+        <v>48895</v>
       </c>
       <c r="J5" s="5">
-        <v>80.8</v>
+        <v>80.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>87</v>
+        <v>81.8</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1173000</v>
+        <v>1301000</v>
       </c>
       <c r="G6" s="7">
-        <v>90000</v>
+        <v>26000</v>
       </c>
       <c r="H6" s="7">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I6" s="7">
-        <v>45778</v>
+        <v>60364</v>
       </c>
       <c r="J6" s="5">
-        <v>79.3</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>84.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>465000</v>
+        <v>664000</v>
       </c>
       <c r="G7" s="7">
-        <v>42000</v>
+        <v>51000</v>
       </c>
       <c r="H7" s="7">
         <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>41500</v>
+        <v>46333</v>
       </c>
       <c r="J7" s="5">
-        <v>77.09999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>85.5</v>
+        <v>88</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>613000</v>
+        <v>662000</v>
       </c>
       <c r="G8" s="7">
-        <v>38000</v>
+        <v>54000</v>
       </c>
       <c r="H8" s="7">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I8" s="7">
-        <v>45400</v>
+        <v>14263</v>
       </c>
       <c r="J8" s="5">
-        <v>76.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>79.90000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>562000</v>
+        <v>473000</v>
       </c>
       <c r="G9" s="7">
-        <v>20000</v>
+        <v>72000</v>
       </c>
       <c r="H9" s="7">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="I9" s="7">
-        <v>35250</v>
+        <v>6684</v>
       </c>
       <c r="J9" s="5">
-        <v>72.8</v>
+        <v>71.7</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>89.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>608000</v>
+        <v>473000</v>
       </c>
       <c r="G10" s="7">
-        <v>60000</v>
+        <v>8000</v>
       </c>
       <c r="H10" s="7">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I10" s="7">
-        <v>12056</v>
+        <v>36714</v>
       </c>
       <c r="J10" s="5">
-        <v>72.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>84.2</v>
+        <v>77.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>811000</v>
+        <v>570000</v>
       </c>
       <c r="G11" s="7">
-        <v>36000</v>
+        <v>8000</v>
       </c>
       <c r="H11" s="7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I11" s="7">
-        <v>19056</v>
+        <v>32222</v>
       </c>
       <c r="J11" s="5">
-        <v>71.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>82</v>
+        <v>81.8</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>620000</v>
+        <v>637000</v>
       </c>
       <c r="G12" s="7">
-        <v>18000</v>
+        <v>17000</v>
       </c>
       <c r="H12" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I12" s="7">
-        <v>22500</v>
+        <v>22211</v>
       </c>
       <c r="J12" s="5">
-        <v>70.7</v>
+        <v>70.5</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>84.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>313000</v>
+        <v>520000</v>
       </c>
       <c r="G13" s="7">
-        <v>29000</v>
+        <v>36000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I13" s="7">
-        <v>24000</v>
+        <v>20600</v>
       </c>
       <c r="J13" s="5">
-        <v>70.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>81.59999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>613000</v>
+        <v>332000</v>
       </c>
       <c r="G14" s="7">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="H14" s="7">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>21278</v>
+        <v>23167</v>
       </c>
       <c r="J14" s="5">
-        <v>70.2</v>
+        <v>70</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>86.5</v>
+        <v>81</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>221000</v>
+        <v>343000</v>
       </c>
       <c r="G15" s="7">
-        <v>27000</v>
+        <v>24000</v>
       </c>
       <c r="H15" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>6455</v>
+        <v>21333</v>
       </c>
       <c r="J15" s="5">
-        <v>69.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>79.90000000000001</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>550000</v>
+        <v>625000</v>
       </c>
       <c r="G16" s="7">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="H16" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I16" s="7">
-        <v>19611</v>
+        <v>20789</v>
       </c>
       <c r="J16" s="5">
-        <v>68.8</v>
+        <v>69.7</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>80</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>484000</v>
+        <v>532000</v>
       </c>
       <c r="G17" s="7">
-        <v>30000</v>
+        <v>33000</v>
       </c>
       <c r="H17" s="7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I17" s="7">
-        <v>18889</v>
+        <v>17667</v>
       </c>
       <c r="J17" s="5">
-        <v>68.7</v>
+        <v>69.5</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,23 +1188,23 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>81</v>
+        <v>81.5</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>350000</v>
+        <v>522000</v>
       </c>
       <c r="G18" s="7">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="H18" s="7">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I18" s="7">
-        <v>16600</v>
+        <v>15579</v>
       </c>
       <c r="J18" s="5">
         <v>68.7</v>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>78.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>327000</v>
+        <v>814000</v>
       </c>
       <c r="G19" s="7">
-        <v>17000</v>
+        <v>3000</v>
       </c>
       <c r="H19" s="7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I19" s="7">
-        <v>21333</v>
+        <v>18211</v>
       </c>
       <c r="J19" s="5">
-        <v>68.7</v>
+        <v>68.5</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,23 +1254,23 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>80.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>499000</v>
+        <v>723000</v>
       </c>
       <c r="G20" s="7">
-        <v>29000</v>
+        <v>48000</v>
       </c>
       <c r="H20" s="7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I20" s="7">
-        <v>16273</v>
+        <v>14158</v>
       </c>
       <c r="J20" s="5">
         <v>68.3</v>
@@ -1287,23 +1287,23 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>80.09999999999999</v>
+        <v>79</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>354000</v>
+        <v>556000</v>
       </c>
       <c r="G21" s="7">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="H21" s="7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I21" s="7">
-        <v>16545</v>
+        <v>18895</v>
       </c>
       <c r="J21" s="5">
         <v>68.2</v>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>80.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>499000</v>
+        <v>364000</v>
       </c>
       <c r="G22" s="7">
-        <v>17000</v>
+        <v>14000</v>
       </c>
       <c r="H22" s="7">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="I22" s="7">
-        <v>15167</v>
+        <v>16364</v>
       </c>
       <c r="J22" s="5">
-        <v>68</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>81.59999999999999</v>
+        <v>81.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>355000</v>
+        <v>367000</v>
       </c>
       <c r="G23" s="7">
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I23" s="7">
-        <v>12667</v>
+        <v>12632</v>
       </c>
       <c r="J23" s="5">
-        <v>68</v>
+        <v>67.8</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>80.3</v>
+        <v>80</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>1669000</v>
+        <v>1665000</v>
       </c>
       <c r="G24" s="7">
-        <v>1000</v>
+        <v>-4000</v>
       </c>
       <c r="H24" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I24" s="7">
-        <v>14889</v>
+        <v>13895</v>
       </c>
       <c r="J24" s="5">
-        <v>67.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>79.8</v>
+        <v>81.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>376000</v>
+        <v>395000</v>
       </c>
       <c r="G25" s="7">
-        <v>7000</v>
+        <v>41000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I25" s="7">
-        <v>15667</v>
+        <v>43333</v>
       </c>
       <c r="J25" s="5">
-        <v>67.8</v>
+        <v>67.5</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>79.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>806000</v>
+        <v>243000</v>
       </c>
       <c r="G26" s="7">
-        <v>7000</v>
+        <v>22000</v>
       </c>
       <c r="H26" s="7">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I26" s="7">
-        <v>15111</v>
+        <v>7750</v>
       </c>
       <c r="J26" s="5">
-        <v>67.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>81</v>
+        <v>80.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>675000</v>
+        <v>223000</v>
       </c>
       <c r="G27" s="7">
-        <v>58000</v>
+        <v>17000</v>
       </c>
       <c r="H27" s="7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>12278</v>
+        <v>11778</v>
       </c>
       <c r="J27" s="5">
-        <v>67.59999999999999</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>80.7</v>
+        <v>78.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>319000</v>
+        <v>806000</v>
       </c>
       <c r="G28" s="7">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="H28" s="7">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I28" s="7">
-        <v>20800</v>
+        <v>14316</v>
       </c>
       <c r="J28" s="5">
-        <v>67.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>78.8</v>
+        <v>79</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>446000</v>
+        <v>341000</v>
       </c>
       <c r="G29" s="7">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I29" s="7">
-        <v>15000</v>
+        <v>11833</v>
       </c>
       <c r="J29" s="5">
-        <v>67.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>79</v>
+        <v>78.5</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>389000</v>
+        <v>391000</v>
       </c>
       <c r="G30" s="7">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="H30" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I30" s="7">
-        <v>12889</v>
+        <v>12316</v>
       </c>
       <c r="J30" s="5">
-        <v>66.7</v>
+        <v>66.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>79.8</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>206000</v>
+        <v>377000</v>
       </c>
       <c r="G31" s="7">
-        <v>20000</v>
+        <v>1000</v>
       </c>
       <c r="H31" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I31" s="7">
-        <v>11125</v>
+        <v>13571</v>
       </c>
       <c r="J31" s="5">
-        <v>66.7</v>
+        <v>66.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>87.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>307000</v>
+        <v>335000</v>
       </c>
       <c r="G32" s="7">
-        <v>34000</v>
+        <v>8000</v>
       </c>
       <c r="H32" s="7">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I32" s="7">
-        <v>38000</v>
+        <v>20000</v>
       </c>
       <c r="J32" s="5">
-        <v>66.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>81.7</v>
+        <v>79.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>233000</v>
+        <v>406000</v>
       </c>
       <c r="G33" s="7">
-        <v>24000</v>
+        <v>6000</v>
       </c>
       <c r="H33" s="7">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I33" s="7">
-        <v>6400</v>
+        <v>8789</v>
       </c>
       <c r="J33" s="5">
-        <v>66.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>77.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>331000</v>
+        <v>1654000</v>
       </c>
       <c r="G34" s="7">
-        <v>6000</v>
+        <v>17000</v>
       </c>
       <c r="H34" s="7">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="I34" s="7">
-        <v>12000</v>
+        <v>842</v>
       </c>
       <c r="J34" s="5">
-        <v>65.8</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>82.7</v>
+        <v>80.7</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>354000</v>
+        <v>239000</v>
       </c>
       <c r="G35" s="7">
-        <v>50000</v>
+        <v>21000</v>
       </c>
       <c r="H35" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I35" s="7">
-        <v>44500</v>
+        <v>22250</v>
       </c>
       <c r="J35" s="5">
-        <v>65.59999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>80.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>288000</v>
+        <v>346000</v>
       </c>
       <c r="G36" s="7">
-        <v>14000</v>
+        <v>-8000</v>
       </c>
       <c r="H36" s="7">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I36" s="7">
-        <v>2000</v>
+        <v>14500</v>
       </c>
       <c r="J36" s="5">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>74.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>292000</v>
+        <v>350000</v>
       </c>
       <c r="G37" s="7">
-        <v>7000</v>
+        <v>24000</v>
       </c>
       <c r="H37" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I37" s="7">
-        <v>14200</v>
+        <v>26667</v>
       </c>
       <c r="J37" s="5">
-        <v>64.7</v>
+        <v>64.5</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>80.7</v>
+        <v>79.2</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>359000</v>
+        <v>533000</v>
       </c>
       <c r="G38" s="7">
-        <v>13000</v>
+        <v>28000</v>
       </c>
       <c r="H38" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I38" s="7">
-        <v>1000</v>
+        <v>3421</v>
       </c>
       <c r="J38" s="5">
-        <v>64.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>76.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>451000</v>
+        <v>248000</v>
       </c>
       <c r="G39" s="7">
-        <v>-9000</v>
+        <v>15000</v>
       </c>
       <c r="H39" s="7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I39" s="7">
-        <v>9944</v>
+        <v>6938</v>
       </c>
       <c r="J39" s="5">
-        <v>64.5</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>75.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>681000</v>
+        <v>381000</v>
       </c>
       <c r="G40" s="7">
-        <v>9000</v>
+        <v>29000</v>
       </c>
       <c r="H40" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I40" s="7">
-        <v>11222</v>
+        <v>4263</v>
       </c>
       <c r="J40" s="5">
         <v>64.3</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>73.09999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>403000</v>
+        <v>369000</v>
       </c>
       <c r="G41" s="7">
-        <v>-10000</v>
+        <v>10000</v>
       </c>
       <c r="H41" s="7">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="I41" s="7">
-        <v>16417</v>
+        <v>1474</v>
       </c>
       <c r="J41" s="5">
         <v>64.3</v>
@@ -1980,23 +1980,23 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>76.5</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>400000</v>
+        <v>195000</v>
       </c>
       <c r="G42" s="7">
-        <v>-6000</v>
+        <v>10000</v>
       </c>
       <c r="H42" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I42" s="7">
-        <v>8944</v>
+        <v>2579</v>
       </c>
       <c r="J42" s="5">
         <v>64.3</v>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>79.2</v>
+        <v>75</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>352000</v>
+        <v>692000</v>
       </c>
       <c r="G43" s="7">
-        <v>29000</v>
+        <v>11000</v>
       </c>
       <c r="H43" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I43" s="7">
-        <v>2889</v>
+        <v>11211</v>
       </c>
       <c r="J43" s="5">
-        <v>64.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>79.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>1212000</v>
+        <v>374000</v>
       </c>
       <c r="G44" s="7">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H44" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I44" s="7">
-        <v>1000</v>
+        <v>1263</v>
       </c>
       <c r="J44" s="5">
-        <v>64.2</v>
+        <v>63.9</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>84.2</v>
+        <v>78.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>218000</v>
+        <v>297000</v>
       </c>
       <c r="G45" s="7">
-        <v>45000</v>
+        <v>9000</v>
       </c>
       <c r="H45" s="7">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="I45" s="7">
-        <v>22667</v>
+        <v>2368</v>
       </c>
       <c r="J45" s="5">
-        <v>64</v>
+        <v>63.9</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>78.90000000000001</v>
+        <v>78</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>505000</v>
+        <v>402000</v>
       </c>
       <c r="G46" s="7">
-        <v>26000</v>
+        <v>74000</v>
       </c>
       <c r="H46" s="7">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="I46" s="7">
-        <v>2056</v>
+        <v>3700</v>
       </c>
       <c r="J46" s="5">
-        <v>63.9</v>
+        <v>63.8</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,23 +2145,23 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>77.7</v>
+        <v>77.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>451000</v>
+        <v>201000</v>
       </c>
       <c r="G47" s="7">
-        <v>5000</v>
+        <v>11000</v>
       </c>
       <c r="H47" s="7">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I47" s="7">
-        <v>4278</v>
+        <v>5062</v>
       </c>
       <c r="J47" s="5">
         <v>63.8</v>
@@ -2178,23 +2178,23 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>78.40000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>1106000</v>
+        <v>447000</v>
       </c>
       <c r="G48" s="7">
-        <v>-2000</v>
+        <v>1000</v>
       </c>
       <c r="H48" s="7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>2389</v>
+        <v>13250</v>
       </c>
       <c r="J48" s="5">
         <v>63.7</v>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>76.3</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>792000</v>
+        <v>316000</v>
       </c>
       <c r="G49" s="7">
-        <v>-12000</v>
+        <v>15000</v>
       </c>
       <c r="H49" s="7">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="I49" s="7">
-        <v>6444</v>
+        <v>600</v>
       </c>
       <c r="J49" s="5">
-        <v>63.6</v>
+        <v>63.7</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,23 +2244,23 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>78.59999999999999</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>542000</v>
+        <v>251000</v>
       </c>
       <c r="G50" s="7">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H50" s="7">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="I50" s="7">
-        <v>1333</v>
+        <v>5333</v>
       </c>
       <c r="J50" s="5">
         <v>63.6</v>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>75.40000000000001</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>406000</v>
+        <v>545000</v>
       </c>
       <c r="G51" s="7">
-        <v>42000</v>
+        <v>3000</v>
       </c>
       <c r="H51" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I51" s="7">
-        <v>8444</v>
+        <v>1421</v>
       </c>
       <c r="J51" s="5">
-        <v>63.6</v>
+        <v>63.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,23 +2310,23 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>78.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>369000</v>
+        <v>322000</v>
       </c>
       <c r="G52" s="7">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="H52" s="7">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I52" s="7">
-        <v>1056</v>
+        <v>30333</v>
       </c>
       <c r="J52" s="5">
         <v>63.5</v>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>76.5</v>
+        <v>78</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>145000</v>
+        <v>1100000</v>
       </c>
       <c r="G53" s="7">
-        <v>13000</v>
+        <v>-6000</v>
       </c>
       <c r="H53" s="7">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I53" s="7">
-        <v>5500</v>
+        <v>1947</v>
       </c>
       <c r="J53" s="5">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>77.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>185000</v>
+        <v>453000</v>
       </c>
       <c r="G54" s="7">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="H54" s="7">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I54" s="7">
-        <v>2167</v>
+        <v>4158</v>
       </c>
       <c r="J54" s="5">
-        <v>63.1</v>
+        <v>63.4</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-03T05:00:28+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-04T05:33:16+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>封神：开局反出西岐，我死守渑池</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>封神：开局反出西岐，我死守渑池</t>
-  </si>
-  <si>
     <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
+    <t>系统延迟一坤年，我成了全球股东</t>
+  </si>
+  <si>
+    <t>朱标私生子，老朱逼我当皇帝！</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>天灾末世：我能提取神话词条</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
     <t>魏家孽种成首辅，全族跪求我认祖</t>
   </si>
   <si>
-    <t>朱标私生子，老朱逼我当皇帝！</t>
+    <t>网游：我的药剂永久持续</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>我的沪上野妻</t>
+  </si>
+  <si>
+    <t>梦境杀怪爆属性，现实肉身成圣人</t>
   </si>
   <si>
     <t>直播见证神话：从鳌太线走蛟开始</t>
   </si>
   <si>
+    <t>镇国杀神：从拯救落难母女开始</t>
+  </si>
+  <si>
     <t>全国没几个正常人？朕要杀疯了</t>
   </si>
   <si>
-    <t>系统延迟一坤年，我成了全球股东</t>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>直播我和徐妙云，老朱全家破防了</t>
+  </si>
+  <si>
+    <t>我跟大明太子摊牌了：要么听我的</t>
+  </si>
+  <si>
+    <t>全民神祇时代：我的词条每日刷新</t>
   </si>
   <si>
     <t>地球不允许我这么牛逼的存在！</t>
   </si>
   <si>
-    <t>天灾末世：我能提取神话词条</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>我的沪上野妻</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
-  </si>
-  <si>
-    <t>镇国杀神：从拯救落难母女开始</t>
-  </si>
-  <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>网游：我的药剂永久持续</t>
-  </si>
-  <si>
     <t>抗战：把父亲捧成将星</t>
   </si>
   <si>
-    <t>直播我和徐妙云，老朱全家破防了</t>
+    <t>四合院：老易有了个天才孤儿侄子</t>
+  </si>
+  <si>
+    <t>重生之我卖的真是高压锅</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>全民穿越！我在末日世界养城兽</t>
+  </si>
+  <si>
+    <t>四合院：从李云龙战友开始</t>
+  </si>
+  <si>
+    <t>同学们都选阐教，我选截教杀疯了</t>
+  </si>
+  <si>
+    <t>我的直播通武侠，开局整垮少林寺</t>
+  </si>
+  <si>
+    <t>全民公路求生：我的房车无限进化</t>
+  </si>
+  <si>
+    <t>神雕：全真出了个记仇真人！</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>谍战：这个外科医生潜伏得很深</t>
+  </si>
+  <si>
+    <t>人在成龙，我有一个老乡聊天群！</t>
+  </si>
+  <si>
+    <t>魂穿刘关张，诸侯们被整麻了</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>穿越神祇：我提取词条碾压诸神</t>
+  </si>
+  <si>
+    <t>末日生存方案供应商</t>
+  </si>
+  <si>
+    <t>村花的傻子老公</t>
+  </si>
+  <si>
+    <t>死亡列车：开局SSS级天赋！</t>
+  </si>
+  <si>
+    <t>聚宝仙盆</t>
   </si>
   <si>
     <t>三角洲：我有1哈夫币秒杀系统！</t>
-  </si>
-  <si>
-    <t>从零开始，打造华夏首支特种部队</t>
-  </si>
-  <si>
-    <t>四合院：老易有了个天才孤儿侄子</t>
-  </si>
-  <si>
-    <t>全民穿越！我在末日世界养城兽</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>扛着棺材去修仙</t>
-  </si>
-  <si>
-    <t>我的直播通武侠，开局整垮少林寺</t>
-  </si>
-  <si>
-    <t>重生之我卖的真是高压锅</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>村花的傻子老公</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>穿越神祇：我提取词条碾压诸神</t>
-  </si>
-  <si>
-    <t>全民公路求生：我的房车无限进化</t>
-  </si>
-  <si>
-    <t>完美犯罪？在我的眼里全是破绽！</t>
-  </si>
-  <si>
-    <t>全民神祇时代：我的词条每日刷新</t>
-  </si>
-  <si>
-    <t>人在成龙，我有一个老乡聊天群！</t>
-  </si>
-  <si>
-    <t>文臣尽头是武斗？我在朝堂横着走</t>
-  </si>
-  <si>
-    <t>神雕：全真出了个记仇真人！</t>
-  </si>
-  <si>
-    <t>谍战：这个外科医生潜伏得很深</t>
-  </si>
-  <si>
-    <t>末日生存方案供应商</t>
-  </si>
-  <si>
-    <t>四合院：从李云龙战友开始</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>聚宝仙盆</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>87.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1278000</v>
+        <v>1505000</v>
       </c>
       <c r="G5" s="7">
-        <v>105000</v>
+        <v>204000</v>
       </c>
       <c r="H5" s="7">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I5" s="7">
-        <v>48895</v>
+        <v>72333</v>
       </c>
       <c r="J5" s="5">
-        <v>80.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>81.8</v>
+        <v>86</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1301000</v>
+        <v>1367000</v>
       </c>
       <c r="G6" s="7">
-        <v>26000</v>
+        <v>89000</v>
       </c>
       <c r="H6" s="7">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I6" s="7">
-        <v>60364</v>
+        <v>50900</v>
       </c>
       <c r="J6" s="5">
-        <v>80.09999999999999</v>
+        <v>80</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>87.40000000000001</v>
+        <v>84.3</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>664000</v>
+        <v>698000</v>
       </c>
       <c r="G7" s="7">
-        <v>51000</v>
+        <v>34000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>46333</v>
+        <v>44571</v>
       </c>
       <c r="J7" s="5">
-        <v>79.7</v>
+        <v>77.5</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -865,19 +865,19 @@
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>662000</v>
+        <v>720000</v>
       </c>
       <c r="G8" s="7">
-        <v>54000</v>
+        <v>58000</v>
       </c>
       <c r="H8" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I8" s="7">
-        <v>14263</v>
+        <v>16450</v>
       </c>
       <c r="J8" s="5">
-        <v>72</v>
+        <v>72.5</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>90.90000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>473000</v>
+        <v>556000</v>
       </c>
       <c r="G9" s="7">
-        <v>72000</v>
+        <v>36000</v>
       </c>
       <c r="H9" s="7">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I9" s="7">
-        <v>6684</v>
+        <v>22000</v>
       </c>
       <c r="J9" s="5">
-        <v>71.7</v>
+        <v>70.8</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>76.8</v>
+        <v>76.3</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>473000</v>
+        <v>479000</v>
       </c>
       <c r="G10" s="7">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="H10" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="7">
-        <v>36714</v>
+        <v>32875</v>
       </c>
       <c r="J10" s="5">
-        <v>71.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>77.7</v>
+        <v>82.3</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>570000</v>
+        <v>564000</v>
       </c>
       <c r="G11" s="7">
-        <v>8000</v>
+        <v>32000</v>
       </c>
       <c r="H11" s="7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I11" s="7">
-        <v>32222</v>
+        <v>18769</v>
       </c>
       <c r="J11" s="5">
-        <v>70.8</v>
+        <v>70</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>81.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>637000</v>
+        <v>365000</v>
       </c>
       <c r="G12" s="7">
-        <v>17000</v>
+        <v>22000</v>
       </c>
       <c r="H12" s="7">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I12" s="7">
-        <v>22211</v>
+        <v>21429</v>
       </c>
       <c r="J12" s="5">
-        <v>70.5</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>81.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>520000</v>
+        <v>432000</v>
       </c>
       <c r="G13" s="7">
-        <v>36000</v>
+        <v>37000</v>
       </c>
       <c r="H13" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I13" s="7">
-        <v>20600</v>
+        <v>41750</v>
       </c>
       <c r="J13" s="5">
-        <v>70.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>332000</v>
+        <v>634000</v>
       </c>
       <c r="G14" s="7">
-        <v>19000</v>
+        <v>9000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I14" s="7">
-        <v>23167</v>
+        <v>20200</v>
       </c>
       <c r="J14" s="5">
-        <v>70</v>
+        <v>69.3</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>81</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>343000</v>
+        <v>518000</v>
       </c>
       <c r="G15" s="7">
-        <v>24000</v>
+        <v>45000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I15" s="7">
-        <v>21333</v>
+        <v>8600</v>
       </c>
       <c r="J15" s="5">
-        <v>69.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>80.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>625000</v>
+        <v>270000</v>
       </c>
       <c r="G16" s="7">
-        <v>12000</v>
+        <v>27000</v>
       </c>
       <c r="H16" s="7">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I16" s="7">
-        <v>20789</v>
+        <v>9231</v>
       </c>
       <c r="J16" s="5">
-        <v>69.7</v>
+        <v>69</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>81.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>532000</v>
+        <v>769000</v>
       </c>
       <c r="G17" s="7">
-        <v>33000</v>
+        <v>46000</v>
       </c>
       <c r="H17" s="7">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I17" s="7">
-        <v>17667</v>
+        <v>15750</v>
       </c>
       <c r="J17" s="5">
-        <v>69.5</v>
+        <v>68.8</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>81.5</v>
+        <v>80.3</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>522000</v>
+        <v>820000</v>
       </c>
       <c r="G18" s="7">
-        <v>23000</v>
+        <v>6000</v>
       </c>
       <c r="H18" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I18" s="7">
-        <v>15579</v>
+        <v>17600</v>
       </c>
       <c r="J18" s="5">
-        <v>68.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>79.90000000000001</v>
+        <v>81.2</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>814000</v>
+        <v>544000</v>
       </c>
       <c r="G19" s="7">
-        <v>3000</v>
+        <v>22000</v>
       </c>
       <c r="H19" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I19" s="7">
-        <v>18211</v>
+        <v>15900</v>
       </c>
       <c r="J19" s="5">
-        <v>68.5</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>81.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>723000</v>
+        <v>564000</v>
       </c>
       <c r="G20" s="7">
-        <v>48000</v>
+        <v>-6000</v>
       </c>
       <c r="H20" s="7">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I20" s="7">
-        <v>14158</v>
+        <v>28400</v>
       </c>
       <c r="J20" s="5">
-        <v>68.3</v>
+        <v>68.5</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>79</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>556000</v>
+        <v>377000</v>
       </c>
       <c r="G21" s="7">
-        <v>6000</v>
+        <v>13000</v>
       </c>
       <c r="H21" s="7">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I21" s="7">
-        <v>18895</v>
+        <v>16083</v>
       </c>
       <c r="J21" s="5">
-        <v>68.2</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>80.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>364000</v>
+        <v>633000</v>
       </c>
       <c r="G22" s="7">
-        <v>14000</v>
+        <v>-4000</v>
       </c>
       <c r="H22" s="7">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="I22" s="7">
-        <v>16364</v>
+        <v>20900</v>
       </c>
       <c r="J22" s="5">
-        <v>68.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1360,16 +1360,16 @@
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>367000</v>
+        <v>379000</v>
       </c>
       <c r="G23" s="7">
         <v>12000</v>
       </c>
       <c r="H23" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I23" s="7">
-        <v>12632</v>
+        <v>12600</v>
       </c>
       <c r="J23" s="5">
         <v>67.8</v>
@@ -1386,23 +1386,23 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>80</v>
+        <v>80.3</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>1665000</v>
+        <v>1666000</v>
       </c>
       <c r="G24" s="7">
-        <v>-4000</v>
+        <v>1000</v>
       </c>
       <c r="H24" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I24" s="7">
-        <v>13895</v>
+        <v>13250</v>
       </c>
       <c r="J24" s="5">
         <v>67.5</v>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>81.2</v>
+        <v>82.5</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>395000</v>
+        <v>214000</v>
       </c>
       <c r="G25" s="7">
-        <v>41000</v>
+        <v>51000</v>
       </c>
       <c r="H25" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I25" s="7">
-        <v>43333</v>
+        <v>16200</v>
       </c>
       <c r="J25" s="5">
-        <v>67.5</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>82.7</v>
+        <v>79.7</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>243000</v>
+        <v>814000</v>
       </c>
       <c r="G26" s="7">
-        <v>22000</v>
+        <v>8000</v>
       </c>
       <c r="H26" s="7">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I26" s="7">
-        <v>7750</v>
+        <v>14000</v>
       </c>
       <c r="J26" s="5">
-        <v>67.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>80.8</v>
+        <v>76.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>223000</v>
+        <v>550000</v>
       </c>
       <c r="G27" s="7">
-        <v>17000</v>
+        <v>-6000</v>
       </c>
       <c r="H27" s="7">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I27" s="7">
-        <v>11778</v>
+        <v>17650</v>
       </c>
       <c r="J27" s="5">
-        <v>67.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>78.7</v>
+        <v>80.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>806000</v>
+        <v>459000</v>
       </c>
       <c r="G28" s="7">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="H28" s="7">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="I28" s="7">
-        <v>14316</v>
+        <v>8545</v>
       </c>
       <c r="J28" s="5">
-        <v>66.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,23 +1551,23 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>79</v>
+        <v>75.2</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>341000</v>
+        <v>335000</v>
       </c>
       <c r="G29" s="7">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="H29" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>11833</v>
+        <v>20286</v>
       </c>
       <c r="J29" s="5">
         <v>66.40000000000001</v>
@@ -1584,23 +1584,23 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>78.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>391000</v>
+        <v>235000</v>
       </c>
       <c r="G30" s="7">
-        <v>2000</v>
+        <v>12000</v>
       </c>
       <c r="H30" s="7">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I30" s="7">
-        <v>12316</v>
+        <v>11800</v>
       </c>
       <c r="J30" s="5">
         <v>66.3</v>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>78.09999999999999</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>377000</v>
+        <v>379000</v>
       </c>
       <c r="G31" s="7">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H31" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="7">
-        <v>13571</v>
+        <v>12125</v>
       </c>
       <c r="J31" s="5">
-        <v>66.3</v>
+        <v>66.2</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>75.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>335000</v>
+        <v>369000</v>
       </c>
       <c r="G32" s="7">
-        <v>8000</v>
+        <v>19000</v>
       </c>
       <c r="H32" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I32" s="7">
-        <v>20000</v>
+        <v>24750</v>
       </c>
       <c r="J32" s="5">
-        <v>66.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>79.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>406000</v>
+        <v>1675000</v>
       </c>
       <c r="G33" s="7">
-        <v>6000</v>
+        <v>21000</v>
       </c>
       <c r="H33" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I33" s="7">
-        <v>8789</v>
+        <v>1850</v>
       </c>
       <c r="J33" s="5">
-        <v>65.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>82.09999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>1654000</v>
+        <v>412000</v>
       </c>
       <c r="G34" s="7">
-        <v>17000</v>
+        <v>31000</v>
       </c>
       <c r="H34" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I34" s="7">
-        <v>842</v>
+        <v>5600</v>
       </c>
       <c r="J34" s="5">
-        <v>65.40000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>80.7</v>
+        <v>79</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>239000</v>
+        <v>410000</v>
       </c>
       <c r="G35" s="7">
-        <v>21000</v>
+        <v>4000</v>
       </c>
       <c r="H35" s="7">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="I35" s="7">
-        <v>22250</v>
+        <v>8550</v>
       </c>
       <c r="J35" s="5">
-        <v>64.90000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>74.59999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>346000</v>
+        <v>390000</v>
       </c>
       <c r="G36" s="7">
-        <v>-8000</v>
+        <v>-1000</v>
       </c>
       <c r="H36" s="7">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I36" s="7">
-        <v>14500</v>
+        <v>11650</v>
       </c>
       <c r="J36" s="5">
-        <v>64.7</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>83.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>350000</v>
+        <v>340000</v>
       </c>
       <c r="G37" s="7">
-        <v>24000</v>
+        <v>5000</v>
       </c>
       <c r="H37" s="7">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I37" s="7">
-        <v>26667</v>
+        <v>18636</v>
       </c>
       <c r="J37" s="5">
-        <v>64.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>533000</v>
+        <v>332000</v>
       </c>
       <c r="G38" s="7">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="H38" s="7">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I38" s="7">
-        <v>3421</v>
+        <v>25250</v>
       </c>
       <c r="J38" s="5">
-        <v>64.40000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>77.59999999999999</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>248000</v>
+        <v>557000</v>
       </c>
       <c r="G39" s="7">
-        <v>15000</v>
+        <v>24000</v>
       </c>
       <c r="H39" s="7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I39" s="7">
-        <v>6938</v>
+        <v>4450</v>
       </c>
       <c r="J39" s="5">
-        <v>64.40000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>78.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>381000</v>
+        <v>340000</v>
       </c>
       <c r="G40" s="7">
-        <v>29000</v>
+        <v>-6000</v>
       </c>
       <c r="H40" s="7">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I40" s="7">
-        <v>4263</v>
+        <v>12923</v>
       </c>
       <c r="J40" s="5">
-        <v>64.3</v>
+        <v>64.5</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1954,16 +1954,16 @@
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>369000</v>
+        <v>381000</v>
       </c>
       <c r="G41" s="7">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="H41" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I41" s="7">
-        <v>1474</v>
+        <v>1550</v>
       </c>
       <c r="J41" s="5">
         <v>64.3</v>
@@ -1980,23 +1980,23 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>79.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>195000</v>
+        <v>331000</v>
       </c>
       <c r="G42" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="H42" s="7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I42" s="7">
-        <v>2579</v>
+        <v>1500</v>
       </c>
       <c r="J42" s="5">
         <v>64.3</v>
@@ -2013,23 +2013,23 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>75</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>692000</v>
+        <v>260000</v>
       </c>
       <c r="G43" s="7">
-        <v>11000</v>
+        <v>12000</v>
       </c>
       <c r="H43" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I43" s="7">
-        <v>11211</v>
+        <v>7235</v>
       </c>
       <c r="J43" s="5">
         <v>64.09999999999999</v>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>79.2</v>
+        <v>77.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>374000</v>
+        <v>257000</v>
       </c>
       <c r="G44" s="7">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H44" s="7">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="I44" s="7">
-        <v>1263</v>
+        <v>5429</v>
       </c>
       <c r="J44" s="5">
-        <v>63.9</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,23 +2079,23 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>78.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>297000</v>
+        <v>211000</v>
       </c>
       <c r="G45" s="7">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="H45" s="7">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I45" s="7">
-        <v>2368</v>
+        <v>5353</v>
       </c>
       <c r="J45" s="5">
         <v>63.9</v>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>78</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>402000</v>
+        <v>211000</v>
       </c>
       <c r="G46" s="7">
-        <v>74000</v>
+        <v>17000</v>
       </c>
       <c r="H46" s="7">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="I46" s="7">
-        <v>3700</v>
+        <v>5154</v>
       </c>
       <c r="J46" s="5">
-        <v>63.8</v>
+        <v>63.7</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>77.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>201000</v>
+        <v>203000</v>
       </c>
       <c r="G47" s="7">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="H47" s="7">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I47" s="7">
-        <v>5062</v>
+        <v>2850</v>
       </c>
       <c r="J47" s="5">
-        <v>63.8</v>
+        <v>63.7</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>73.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>447000</v>
+        <v>1099000</v>
       </c>
       <c r="G48" s="7">
-        <v>1000</v>
+        <v>-1000</v>
       </c>
       <c r="H48" s="7">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I48" s="7">
-        <v>13250</v>
+        <v>1800</v>
       </c>
       <c r="J48" s="5">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>79.09999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>316000</v>
+        <v>698000</v>
       </c>
       <c r="G49" s="7">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="H49" s="7">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I49" s="7">
-        <v>600</v>
+        <v>10950</v>
       </c>
       <c r="J49" s="5">
-        <v>63.7</v>
+        <v>63.6</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,23 +2244,23 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>76.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>251000</v>
+        <v>549000</v>
       </c>
       <c r="G50" s="7">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="H50" s="7">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="I50" s="7">
-        <v>5333</v>
+        <v>1550</v>
       </c>
       <c r="J50" s="5">
         <v>63.6</v>
@@ -2284,16 +2284,16 @@
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>545000</v>
+        <v>374000</v>
       </c>
       <c r="G51" s="7">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H51" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I51" s="7">
-        <v>1421</v>
+        <v>1650</v>
       </c>
       <c r="J51" s="5">
         <v>63.5</v>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>79.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>322000</v>
+        <v>199000</v>
       </c>
       <c r="G52" s="7">
         <v>15000</v>
       </c>
       <c r="H52" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I52" s="7">
-        <v>30333</v>
+        <v>12000</v>
       </c>
       <c r="J52" s="5">
-        <v>63.5</v>
+        <v>63.4</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>78</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>1100000</v>
+        <v>453000</v>
       </c>
       <c r="G53" s="7">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="H53" s="7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I53" s="7">
-        <v>1947</v>
+        <v>3950</v>
       </c>
       <c r="J53" s="5">
-        <v>63.4</v>
+        <v>63.1</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>77.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>453000</v>
+        <v>333000</v>
       </c>
       <c r="G54" s="7">
-        <v>2000</v>
+        <v>-8000</v>
       </c>
       <c r="H54" s="7">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="I54" s="7">
-        <v>4158</v>
+        <v>10308</v>
       </c>
       <c r="J54" s="5">
-        <v>63.4</v>
+        <v>63.1</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-04T05:33:16+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-05T05:42:45+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -82,145 +82,145 @@
     <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
+    <t>高武：看不起斩魄刀，流刃若火呢</t>
+  </si>
+  <si>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>朱标私生子，老朱逼我当皇帝！</t>
+  </si>
+  <si>
     <t>系统延迟一坤年，我成了全球股东</t>
   </si>
   <si>
-    <t>朱标私生子，老朱逼我当皇帝！</t>
+    <t>刚上大一，抽到财阀身份被曝光</t>
+  </si>
+  <si>
+    <t>我的沪上野妻</t>
   </si>
   <si>
     <t>穿书反派，把阴湿女主养成病娇了</t>
   </si>
   <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
     <t>天灾末世：我能提取神话词条</t>
   </si>
   <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
+    <t>网游：我的药剂永久持续</t>
+  </si>
+  <si>
+    <t>直播见证神话：从鳌太线走蛟开始</t>
   </si>
   <si>
     <t>我是皇帝我怕谁？</t>
   </si>
   <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
     <t>魏家孽种成首辅，全族跪求我认祖</t>
   </si>
   <si>
-    <t>网游：我的药剂永久持续</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>我的沪上野妻</t>
+    <t>四合院：从李云龙战友开始</t>
+  </si>
+  <si>
+    <t>重生之我卖的真是高压锅</t>
+  </si>
+  <si>
+    <t>我合成了全世界</t>
+  </si>
+  <si>
+    <t>全国没几个正常人？朕要杀疯了</t>
+  </si>
+  <si>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>死亡列车：开局SSS级天赋！</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>直播我和徐妙云，老朱全家破防了</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>抗战：把父亲捧成将星</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>全民神祇时代：我的词条每日刷新</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>给员工发超跑，你当死士养呢？</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>精灵：杀穿超古代的我只想退休</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
   </si>
   <si>
     <t>梦境杀怪爆属性，现实肉身成圣人</t>
   </si>
   <si>
-    <t>直播见证神话：从鳌太线走蛟开始</t>
-  </si>
-  <si>
-    <t>镇国杀神：从拯救落难母女开始</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>全民地仙：开局紫金葫芦辟福地</t>
-  </si>
-  <si>
-    <t>直播我和徐妙云，老朱全家破防了</t>
+    <t>抗美援朝：什么叫这是四合院世界</t>
+  </si>
+  <si>
+    <t>开局九选四，生来便是误闯天家</t>
+  </si>
+  <si>
+    <t>从零开始，打造华夏首支特种部队</t>
+  </si>
+  <si>
+    <t>穿书后，我把女主养成病娇了</t>
+  </si>
+  <si>
+    <t>全民穿越！我在末日世界养城兽</t>
+  </si>
+  <si>
+    <t>四合院：老易有了个天才孤儿侄子</t>
+  </si>
+  <si>
+    <t>地球不允许我这么牛逼的存在！</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>答应联姻，冰山女总裁咋成病娇了</t>
   </si>
   <si>
     <t>我跟大明太子摊牌了：要么听我的</t>
-  </si>
-  <si>
-    <t>全民神祇时代：我的词条每日刷新</t>
-  </si>
-  <si>
-    <t>地球不允许我这么牛逼的存在！</t>
-  </si>
-  <si>
-    <t>抗战：把父亲捧成将星</t>
-  </si>
-  <si>
-    <t>四合院：老易有了个天才孤儿侄子</t>
-  </si>
-  <si>
-    <t>重生之我卖的真是高压锅</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>从零开始，打造华夏首支特种部队</t>
-  </si>
-  <si>
-    <t>全民穿越！我在末日世界养城兽</t>
-  </si>
-  <si>
-    <t>四合院：从李云龙战友开始</t>
-  </si>
-  <si>
-    <t>同学们都选阐教，我选截教杀疯了</t>
-  </si>
-  <si>
-    <t>我的直播通武侠，开局整垮少林寺</t>
-  </si>
-  <si>
-    <t>全民公路求生：我的房车无限进化</t>
-  </si>
-  <si>
-    <t>神雕：全真出了个记仇真人！</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>谍战：这个外科医生潜伏得很深</t>
-  </si>
-  <si>
-    <t>人在成龙，我有一个老乡聊天群！</t>
-  </si>
-  <si>
-    <t>魂穿刘关张，诸侯们被整麻了</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>穿越神祇：我提取词条碾压诸神</t>
-  </si>
-  <si>
-    <t>末日生存方案供应商</t>
-  </si>
-  <si>
-    <t>村花的傻子老公</t>
-  </si>
-  <si>
-    <t>死亡列车：开局SSS级天赋！</t>
-  </si>
-  <si>
-    <t>聚宝仙盆</t>
-  </si>
-  <si>
-    <t>三角洲：我有1哈夫币秒杀系统！</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>95.09999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1505000</v>
+        <v>1643000</v>
       </c>
       <c r="G5" s="7">
-        <v>204000</v>
+        <v>138000</v>
       </c>
       <c r="H5" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="7">
-        <v>72333</v>
+        <v>77385</v>
       </c>
       <c r="J5" s="5">
-        <v>90.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>86</v>
+        <v>86.7</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1367000</v>
+        <v>1470000</v>
       </c>
       <c r="G6" s="7">
-        <v>89000</v>
+        <v>103000</v>
       </c>
       <c r="H6" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I6" s="7">
-        <v>50900</v>
+        <v>53381</v>
       </c>
       <c r="J6" s="5">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>84.3</v>
+        <v>84.5</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>698000</v>
+        <v>734000</v>
       </c>
       <c r="G7" s="7">
-        <v>34000</v>
+        <v>36000</v>
       </c>
       <c r="H7" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="7">
-        <v>44571</v>
+        <v>43500</v>
       </c>
       <c r="J7" s="5">
-        <v>77.5</v>
+        <v>77.3</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>88</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>720000</v>
+        <v>476000</v>
       </c>
       <c r="G8" s="7">
-        <v>58000</v>
+        <v>44000</v>
       </c>
       <c r="H8" s="7">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I8" s="7">
-        <v>16450</v>
+        <v>42200</v>
       </c>
       <c r="J8" s="5">
-        <v>72.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>82.3</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>556000</v>
+        <v>782000</v>
       </c>
       <c r="G9" s="7">
-        <v>36000</v>
+        <v>62000</v>
       </c>
       <c r="H9" s="7">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I9" s="7">
-        <v>22000</v>
+        <v>18619</v>
       </c>
       <c r="J9" s="5">
-        <v>70.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>76.3</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>479000</v>
+        <v>304000</v>
       </c>
       <c r="G10" s="7">
-        <v>6000</v>
+        <v>63000</v>
       </c>
       <c r="H10" s="7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I10" s="7">
-        <v>32875</v>
+        <v>34500</v>
       </c>
       <c r="J10" s="5">
-        <v>70.2</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>82.3</v>
+        <v>86.2</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>564000</v>
+        <v>257000</v>
       </c>
       <c r="G11" s="7">
-        <v>32000</v>
+        <v>43000</v>
       </c>
       <c r="H11" s="7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>18769</v>
+        <v>20667</v>
       </c>
       <c r="J11" s="5">
-        <v>70</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>80.90000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>365000</v>
+        <v>498000</v>
       </c>
       <c r="G12" s="7">
-        <v>22000</v>
+        <v>19000</v>
       </c>
       <c r="H12" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>21429</v>
+        <v>31333</v>
       </c>
       <c r="J12" s="5">
-        <v>69.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>80</v>
+        <v>82.3</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>432000</v>
+        <v>589000</v>
       </c>
       <c r="G13" s="7">
-        <v>37000</v>
+        <v>33000</v>
       </c>
       <c r="H13" s="7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I13" s="7">
-        <v>41750</v>
+        <v>22917</v>
       </c>
       <c r="J13" s="5">
-        <v>69.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>80.5</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>634000</v>
+        <v>203000</v>
       </c>
       <c r="G14" s="7">
-        <v>9000</v>
+        <v>25000</v>
       </c>
       <c r="H14" s="7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I14" s="7">
-        <v>20200</v>
+        <v>31500</v>
       </c>
       <c r="J14" s="5">
-        <v>69.3</v>
+        <v>70.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>85.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>518000</v>
+        <v>853000</v>
       </c>
       <c r="G15" s="7">
-        <v>45000</v>
+        <v>33000</v>
       </c>
       <c r="H15" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I15" s="7">
-        <v>8600</v>
+        <v>18333</v>
       </c>
       <c r="J15" s="5">
-        <v>69.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>84.90000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>270000</v>
+        <v>600000</v>
       </c>
       <c r="G16" s="7">
-        <v>27000</v>
+        <v>36000</v>
       </c>
       <c r="H16" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I16" s="7">
-        <v>9231</v>
+        <v>20000</v>
       </c>
       <c r="J16" s="5">
-        <v>69</v>
+        <v>70.5</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>81.59999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>769000</v>
+        <v>825000</v>
       </c>
       <c r="G17" s="7">
-        <v>46000</v>
+        <v>56000</v>
       </c>
       <c r="H17" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I17" s="7">
-        <v>15750</v>
+        <v>17667</v>
       </c>
       <c r="J17" s="5">
-        <v>68.8</v>
+        <v>70.3</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>80.3</v>
+        <v>81.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>820000</v>
+        <v>388000</v>
       </c>
       <c r="G18" s="7">
-        <v>6000</v>
+        <v>23000</v>
       </c>
       <c r="H18" s="7">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7">
-        <v>17600</v>
+        <v>21625</v>
       </c>
       <c r="J18" s="5">
-        <v>68.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>81.2</v>
+        <v>86.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>544000</v>
+        <v>297000</v>
       </c>
       <c r="G19" s="7">
-        <v>22000</v>
+        <v>27000</v>
       </c>
       <c r="H19" s="7">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="I19" s="7">
-        <v>15900</v>
+        <v>10500</v>
       </c>
       <c r="J19" s="5">
-        <v>68.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>75.2</v>
+        <v>78.7</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>564000</v>
+        <v>582000</v>
       </c>
       <c r="G20" s="7">
-        <v>-6000</v>
+        <v>18000</v>
       </c>
       <c r="H20" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I20" s="7">
-        <v>28400</v>
+        <v>27455</v>
       </c>
       <c r="J20" s="5">
-        <v>68.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>80.59999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>377000</v>
+        <v>648000</v>
       </c>
       <c r="G21" s="7">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="H21" s="7">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I21" s="7">
-        <v>16083</v>
+        <v>19905</v>
       </c>
       <c r="J21" s="5">
-        <v>68.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>78.40000000000001</v>
+        <v>89.3</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>633000</v>
+        <v>476000</v>
       </c>
       <c r="G22" s="7">
-        <v>-4000</v>
+        <v>47000</v>
       </c>
       <c r="H22" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I22" s="7">
-        <v>20900</v>
+        <v>1429</v>
       </c>
       <c r="J22" s="5">
-        <v>68.3</v>
+        <v>69.5</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>81.2</v>
+        <v>85</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>379000</v>
+        <v>555000</v>
       </c>
       <c r="G23" s="7">
-        <v>12000</v>
+        <v>37000</v>
       </c>
       <c r="H23" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I23" s="7">
-        <v>12600</v>
+        <v>9952</v>
       </c>
       <c r="J23" s="5">
-        <v>67.8</v>
+        <v>69.2</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>80.3</v>
+        <v>82</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>1666000</v>
+        <v>349000</v>
       </c>
       <c r="G24" s="7">
-        <v>1000</v>
+        <v>17000</v>
       </c>
       <c r="H24" s="7">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I24" s="7">
-        <v>13250</v>
+        <v>23600</v>
       </c>
       <c r="J24" s="5">
-        <v>67.5</v>
+        <v>69</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>82.5</v>
+        <v>82</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>214000</v>
+        <v>384000</v>
       </c>
       <c r="G25" s="7">
-        <v>51000</v>
+        <v>15000</v>
       </c>
       <c r="H25" s="7">
         <v>6</v>
       </c>
       <c r="I25" s="7">
-        <v>16200</v>
+        <v>22800</v>
       </c>
       <c r="J25" s="5">
-        <v>67.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>79.7</v>
+        <v>86</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>814000</v>
+        <v>237000</v>
       </c>
       <c r="G26" s="7">
-        <v>8000</v>
+        <v>39000</v>
       </c>
       <c r="H26" s="7">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I26" s="7">
-        <v>14000</v>
+        <v>24250</v>
       </c>
       <c r="J26" s="5">
-        <v>67.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>76.8</v>
+        <v>78.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>550000</v>
+        <v>632000</v>
       </c>
       <c r="G27" s="7">
-        <v>-6000</v>
+        <v>-1000</v>
       </c>
       <c r="H27" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I27" s="7">
-        <v>17650</v>
+        <v>19857</v>
       </c>
       <c r="J27" s="5">
-        <v>66.7</v>
+        <v>68.3</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>80.8</v>
+        <v>81.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>459000</v>
+        <v>393000</v>
       </c>
       <c r="G28" s="7">
-        <v>57000</v>
+        <v>14000</v>
       </c>
       <c r="H28" s="7">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I28" s="7">
-        <v>8545</v>
+        <v>12667</v>
       </c>
       <c r="J28" s="5">
-        <v>66.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>75.2</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>335000</v>
+        <v>220000</v>
       </c>
       <c r="G29" s="7">
-        <v>3000</v>
+        <v>21000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>20286</v>
+        <v>13500</v>
       </c>
       <c r="J29" s="5">
-        <v>66.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>78.90000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>235000</v>
+        <v>1670000</v>
       </c>
       <c r="G30" s="7">
-        <v>12000</v>
+        <v>4000</v>
       </c>
       <c r="H30" s="7">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I30" s="7">
-        <v>11800</v>
+        <v>12810</v>
       </c>
       <c r="J30" s="5">
-        <v>66.3</v>
+        <v>67.5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>78.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>379000</v>
+        <v>824000</v>
       </c>
       <c r="G31" s="7">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="H31" s="7">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I31" s="7">
-        <v>12125</v>
+        <v>13810</v>
       </c>
       <c r="J31" s="5">
-        <v>66.2</v>
+        <v>67.5</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>81.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>369000</v>
+        <v>504000</v>
       </c>
       <c r="G32" s="7">
-        <v>19000</v>
+        <v>25000</v>
       </c>
       <c r="H32" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I32" s="7">
-        <v>24750</v>
+        <v>28000</v>
       </c>
       <c r="J32" s="5">
-        <v>66.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>82.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>1675000</v>
+        <v>248000</v>
       </c>
       <c r="G33" s="7">
-        <v>21000</v>
+        <v>13000</v>
       </c>
       <c r="H33" s="7">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="I33" s="7">
-        <v>1850</v>
+        <v>11909</v>
       </c>
       <c r="J33" s="5">
-        <v>65.8</v>
+        <v>67</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>80.40000000000001</v>
+        <v>95.3</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>412000</v>
+        <v>281000</v>
       </c>
       <c r="G34" s="7">
-        <v>31000</v>
+        <v>23000</v>
       </c>
       <c r="H34" s="7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I34" s="7">
-        <v>5600</v>
+        <v>22000</v>
       </c>
       <c r="J34" s="5">
-        <v>65.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>79</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>410000</v>
+        <v>510000</v>
       </c>
       <c r="G35" s="7">
-        <v>4000</v>
+        <v>51000</v>
       </c>
       <c r="H35" s="7">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I35" s="7">
-        <v>8550</v>
+        <v>12083</v>
       </c>
       <c r="J35" s="5">
-        <v>65.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>77.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>390000</v>
+        <v>422000</v>
       </c>
       <c r="G36" s="7">
-        <v>-1000</v>
+        <v>12000</v>
       </c>
       <c r="H36" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I36" s="7">
-        <v>11650</v>
+        <v>8714</v>
       </c>
       <c r="J36" s="5">
-        <v>65.59999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>74.09999999999999</v>
+        <v>81.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>340000</v>
+        <v>450000</v>
       </c>
       <c r="G37" s="7">
-        <v>5000</v>
+        <v>38000</v>
       </c>
       <c r="H37" s="7">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="I37" s="7">
-        <v>18636</v>
+        <v>7143</v>
       </c>
       <c r="J37" s="5">
-        <v>65.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>79</v>
+        <v>84.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>332000</v>
+        <v>2053000</v>
       </c>
       <c r="G38" s="7">
-        <v>10000</v>
+        <v>55000</v>
       </c>
       <c r="H38" s="7">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I38" s="7">
-        <v>25250</v>
+        <v>1048</v>
       </c>
       <c r="J38" s="5">
-        <v>64.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>79.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>557000</v>
+        <v>356000</v>
       </c>
       <c r="G39" s="7">
-        <v>24000</v>
+        <v>85000</v>
       </c>
       <c r="H39" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I39" s="7">
-        <v>4450</v>
+        <v>3619</v>
       </c>
       <c r="J39" s="5">
-        <v>64.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>75.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>340000</v>
+        <v>1703000</v>
       </c>
       <c r="G40" s="7">
-        <v>-6000</v>
+        <v>28000</v>
       </c>
       <c r="H40" s="7">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I40" s="7">
-        <v>12923</v>
+        <v>3095</v>
       </c>
       <c r="J40" s="5">
-        <v>64.5</v>
+        <v>66.3</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>79.8</v>
+        <v>96.2</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>381000</v>
+        <v>213000</v>
       </c>
       <c r="G41" s="7">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="H41" s="7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I41" s="7">
-        <v>1550</v>
+        <v>17500</v>
       </c>
       <c r="J41" s="5">
-        <v>64.3</v>
+        <v>66.3</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>79.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>331000</v>
+        <v>317000</v>
       </c>
       <c r="G42" s="7">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H42" s="7">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I42" s="7">
-        <v>1500</v>
+        <v>25000</v>
       </c>
       <c r="J42" s="5">
-        <v>64.3</v>
+        <v>66.2</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>76.90000000000001</v>
+        <v>77</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>260000</v>
+        <v>544000</v>
       </c>
       <c r="G43" s="7">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I43" s="7">
-        <v>7235</v>
+        <v>15143</v>
       </c>
       <c r="J43" s="5">
-        <v>64.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>77.8</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>257000</v>
+        <v>220000</v>
       </c>
       <c r="G44" s="7">
-        <v>6000</v>
+        <v>17000</v>
       </c>
       <c r="H44" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I44" s="7">
-        <v>5429</v>
+        <v>19000</v>
       </c>
       <c r="J44" s="5">
-        <v>64.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>77.40000000000001</v>
+        <v>94</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>211000</v>
+        <v>134000</v>
       </c>
       <c r="G45" s="7">
-        <v>10000</v>
+        <v>25000</v>
       </c>
       <c r="H45" s="7">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="I45" s="7">
-        <v>5353</v>
+        <v>21500</v>
       </c>
       <c r="J45" s="5">
-        <v>63.9</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>77.09999999999999</v>
+        <v>78</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>211000</v>
+        <v>390000</v>
       </c>
       <c r="G46" s="7">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="H46" s="7">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I46" s="7">
-        <v>5154</v>
+        <v>11095</v>
       </c>
       <c r="J46" s="5">
-        <v>63.7</v>
+        <v>65.7</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>78.09999999999999</v>
+        <v>96.8</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>203000</v>
+        <v>133000</v>
       </c>
       <c r="G47" s="7">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="H47" s="7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I47" s="7">
-        <v>2850</v>
+        <v>14000</v>
       </c>
       <c r="J47" s="5">
-        <v>63.7</v>
+        <v>65.7</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>78.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>1099000</v>
+        <v>345000</v>
       </c>
       <c r="G48" s="7">
-        <v>-1000</v>
+        <v>5000</v>
       </c>
       <c r="H48" s="7">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I48" s="7">
-        <v>1800</v>
+        <v>17500</v>
       </c>
       <c r="J48" s="5">
-        <v>63.6</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>74.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>698000</v>
+        <v>378000</v>
       </c>
       <c r="G49" s="7">
-        <v>6000</v>
+        <v>-1000</v>
       </c>
       <c r="H49" s="7">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I49" s="7">
-        <v>10950</v>
+        <v>10667</v>
       </c>
       <c r="J49" s="5">
-        <v>63.6</v>
+        <v>65.3</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>78.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>549000</v>
+        <v>335000</v>
       </c>
       <c r="G50" s="7">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="H50" s="7">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I50" s="7">
-        <v>1550</v>
+        <v>17750</v>
       </c>
       <c r="J50" s="5">
-        <v>63.6</v>
+        <v>65.3</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>78.40000000000001</v>
+        <v>78.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>374000</v>
+        <v>277000</v>
       </c>
       <c r="G51" s="7">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="H51" s="7">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I51" s="7">
-        <v>1650</v>
+        <v>7778</v>
       </c>
       <c r="J51" s="5">
-        <v>63.5</v>
+        <v>65.3</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>77.09999999999999</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>199000</v>
+        <v>216000</v>
       </c>
       <c r="G52" s="7">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="H52" s="7">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="I52" s="7">
-        <v>12000</v>
+        <v>3333</v>
       </c>
       <c r="J52" s="5">
-        <v>63.4</v>
+        <v>65.2</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>76.59999999999999</v>
+        <v>95.8</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>453000</v>
+        <v>125000</v>
       </c>
       <c r="G53" s="7">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H53" s="7">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="I53" s="7">
-        <v>3950</v>
+        <v>14000</v>
       </c>
       <c r="J53" s="5">
-        <v>63.1</v>
+        <v>65.2</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>73.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>333000</v>
+        <v>540000</v>
       </c>
       <c r="G54" s="7">
-        <v>-8000</v>
+        <v>-10000</v>
       </c>
       <c r="H54" s="7">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="I54" s="7">
-        <v>10308</v>
+        <v>16333</v>
       </c>
       <c r="J54" s="5">
-        <v>63.1</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-05T05:42:45+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-06T06:01:30+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>都重生了，谁还装富二代啊</t>
+  </si>
+  <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
+    <t>高武：看不起斩魄刀，流刃若火呢</t>
+  </si>
+  <si>
+    <t>开局九选四，生来便是误闯天家</t>
+  </si>
+  <si>
     <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
     <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
+    <t>我合成了全世界</t>
+  </si>
+  <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
-    <t>高武：看不起斩魄刀，流刃若火呢</t>
+    <t>四合院：从李云龙战友开始</t>
   </si>
   <si>
     <t>全民地仙：开局紫金葫芦辟福地</t>
   </si>
   <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>系统延迟一坤年，我成了全球股东</t>
+  </si>
+  <si>
     <t>朱标私生子，老朱逼我当皇帝！</t>
   </si>
   <si>
-    <t>系统延迟一坤年，我成了全球股东</t>
+    <t>莫欺老年穷：我一个铜板一年功力</t>
+  </si>
+  <si>
+    <t>我是皇帝我怕谁？</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>我的沪上野妻</t>
+  </si>
+  <si>
+    <t>天灾末世：我能提取神话词条</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
   </si>
   <si>
     <t>刚上大一，抽到财阀身份被曝光</t>
   </si>
   <si>
-    <t>我的沪上野妻</t>
-  </si>
-  <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
+    <t>魏家孽种成首辅，全族跪求我认祖</t>
+  </si>
+  <si>
+    <t>重生之我卖的真是高压锅</t>
+  </si>
+  <si>
+    <t>精灵：杀穿超古代的我只想退休</t>
   </si>
   <si>
     <t>我都宇宙之主了，你们还在地球？</t>
   </si>
   <si>
-    <t>天灾末世：我能提取神话词条</t>
+    <t>李承乾拥兵百万，三千剑仙逼宫！</t>
+  </si>
+  <si>
+    <t>直播见证神话：从鳌太线走蛟开始</t>
+  </si>
+  <si>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
+    <t>大明国舅：开局赐婚徐妙云</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>成龙历险记，不过我是斯卡蒂</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>神通者</t>
   </si>
   <si>
     <t>网游：我的药剂永久持续</t>
   </si>
   <si>
-    <t>直播见证神话：从鳌太线走蛟开始</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>魏家孽种成首辅，全族跪求我认祖</t>
-  </si>
-  <si>
-    <t>四合院：从李云龙战友开始</t>
-  </si>
-  <si>
-    <t>重生之我卖的真是高压锅</t>
-  </si>
-  <si>
-    <t>我合成了全世界</t>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>死亡列车：开局SSS级天赋！</t>
+  </si>
+  <si>
+    <t>给员工发超跑，你当死士养呢？</t>
+  </si>
+  <si>
+    <t>让你守破道观，你咋真修仙了？</t>
+  </si>
+  <si>
+    <t>直播我和徐妙云，老朱全家破防了</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
+  </si>
+  <si>
+    <t>规则怪谈：无所谓，系统会出手</t>
+  </si>
+  <si>
+    <t>开箱必出神话级，阁下如何应对？</t>
+  </si>
+  <si>
+    <t>答应联姻，冰山女总裁咋成病娇了</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
   </si>
   <si>
     <t>全国没几个正常人？朕要杀疯了</t>
   </si>
   <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>死亡列车：开局SSS级天赋！</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>直播我和徐妙云，老朱全家破防了</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
-  </si>
-  <si>
-    <t>抗战：把父亲捧成将星</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
+    <t>四合院：大家一起做禽兽</t>
+  </si>
+  <si>
+    <t>穿书后，我把女主养成病娇了</t>
+  </si>
+  <si>
+    <t>停下吧苏总，国家已经兜不住了！</t>
   </si>
   <si>
     <t>全民神祇时代：我的词条每日刷新</t>
   </si>
   <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>神通者</t>
-  </si>
-  <si>
-    <t>给员工发超跑，你当死士养呢？</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>精灵：杀穿超古代的我只想退休</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
-  </si>
-  <si>
-    <t>梦境杀怪爆属性，现实肉身成圣人</t>
-  </si>
-  <si>
-    <t>抗美援朝：什么叫这是四合院世界</t>
-  </si>
-  <si>
-    <t>开局九选四，生来便是误闯天家</t>
-  </si>
-  <si>
-    <t>从零开始，打造华夏首支特种部队</t>
-  </si>
-  <si>
-    <t>穿书后，我把女主养成病娇了</t>
-  </si>
-  <si>
-    <t>全民穿越！我在末日世界养城兽</t>
-  </si>
-  <si>
-    <t>四合院：老易有了个天才孤儿侄子</t>
-  </si>
-  <si>
-    <t>地球不允许我这么牛逼的存在！</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>答应联姻，冰山女总裁咋成病娇了</t>
-  </si>
-  <si>
-    <t>我跟大明太子摊牌了：要么听我的</t>
+    <t>龙族：我的强化每月刷新</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>89.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1643000</v>
+        <v>1713000</v>
       </c>
       <c r="G5" s="7">
-        <v>138000</v>
+        <v>70000</v>
       </c>
       <c r="H5" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="7">
-        <v>77385</v>
+        <v>76857</v>
       </c>
       <c r="J5" s="5">
-        <v>88.5</v>
+        <v>85.7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>86.7</v>
+        <v>90.5</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1470000</v>
+        <v>578000</v>
       </c>
       <c r="G6" s="7">
-        <v>103000</v>
+        <v>248000</v>
       </c>
       <c r="H6" s="7">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="I6" s="7">
-        <v>53381</v>
+        <v>107500</v>
       </c>
       <c r="J6" s="5">
-        <v>81</v>
+        <v>83.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>84.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>734000</v>
+        <v>1584000</v>
       </c>
       <c r="G7" s="7">
-        <v>36000</v>
+        <v>114000</v>
       </c>
       <c r="H7" s="7">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I7" s="7">
-        <v>43500</v>
+        <v>56136</v>
       </c>
       <c r="J7" s="5">
-        <v>77.3</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>81.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>476000</v>
+        <v>358000</v>
       </c>
       <c r="G8" s="7">
-        <v>44000</v>
+        <v>54000</v>
       </c>
       <c r="H8" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I8" s="7">
-        <v>42200</v>
+        <v>41000</v>
       </c>
       <c r="J8" s="5">
-        <v>73.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>88.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>782000</v>
+        <v>203000</v>
       </c>
       <c r="G9" s="7">
-        <v>62000</v>
+        <v>69000</v>
       </c>
       <c r="H9" s="7">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I9" s="7">
-        <v>18619</v>
+        <v>37333</v>
       </c>
       <c r="J9" s="5">
-        <v>73.09999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>82.7</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>304000</v>
+        <v>758000</v>
       </c>
       <c r="G10" s="7">
-        <v>63000</v>
+        <v>24000</v>
       </c>
       <c r="H10" s="7">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="I10" s="7">
-        <v>34500</v>
+        <v>41333</v>
       </c>
       <c r="J10" s="5">
-        <v>72.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>86.2</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>257000</v>
+        <v>509000</v>
       </c>
       <c r="G11" s="7">
-        <v>43000</v>
+        <v>33000</v>
       </c>
       <c r="H11" s="7">
         <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>20667</v>
+        <v>40667</v>
       </c>
       <c r="J11" s="5">
-        <v>72.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>79.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>498000</v>
+        <v>284000</v>
       </c>
       <c r="G12" s="7">
-        <v>19000</v>
+        <v>47000</v>
       </c>
       <c r="H12" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I12" s="7">
-        <v>31333</v>
+        <v>28800</v>
       </c>
       <c r="J12" s="5">
-        <v>71.3</v>
+        <v>73.2</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>82.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>589000</v>
+        <v>837000</v>
       </c>
       <c r="G13" s="7">
-        <v>33000</v>
+        <v>55000</v>
       </c>
       <c r="H13" s="7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I13" s="7">
-        <v>22917</v>
+        <v>20273</v>
       </c>
       <c r="J13" s="5">
-        <v>71</v>
+        <v>72.7</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>98.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>203000</v>
+        <v>372000</v>
       </c>
       <c r="G14" s="7">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="H14" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>31500</v>
+        <v>23500</v>
       </c>
       <c r="J14" s="5">
-        <v>70.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>83.7</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>853000</v>
+        <v>289000</v>
       </c>
       <c r="G15" s="7">
-        <v>33000</v>
+        <v>32000</v>
       </c>
       <c r="H15" s="7">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>18333</v>
+        <v>22286</v>
       </c>
       <c r="J15" s="5">
-        <v>70.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>82.8</v>
+        <v>84</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>600000</v>
+        <v>645000</v>
       </c>
       <c r="G16" s="7">
-        <v>36000</v>
+        <v>45000</v>
       </c>
       <c r="H16" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I16" s="7">
-        <v>20000</v>
+        <v>21667</v>
       </c>
       <c r="J16" s="5">
-        <v>70.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>83.5</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>825000</v>
+        <v>619000</v>
       </c>
       <c r="G17" s="7">
-        <v>56000</v>
+        <v>30000</v>
       </c>
       <c r="H17" s="7">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I17" s="7">
-        <v>17667</v>
+        <v>23462</v>
       </c>
       <c r="J17" s="5">
-        <v>70.3</v>
+        <v>70.7</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>81.7</v>
+        <v>77.8</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>388000</v>
+        <v>511000</v>
       </c>
       <c r="G18" s="7">
-        <v>23000</v>
+        <v>13000</v>
       </c>
       <c r="H18" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I18" s="7">
-        <v>21625</v>
+        <v>29500</v>
       </c>
       <c r="J18" s="5">
-        <v>70.3</v>
+        <v>70.2</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>86.5</v>
+        <v>97.2</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>297000</v>
+        <v>157000</v>
       </c>
       <c r="G19" s="7">
-        <v>27000</v>
+        <v>20000</v>
       </c>
       <c r="H19" s="7">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
-        <v>10500</v>
+        <v>18667</v>
       </c>
       <c r="J19" s="5">
-        <v>70.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>78.7</v>
+        <v>81.3</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>582000</v>
+        <v>662000</v>
       </c>
       <c r="G20" s="7">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="H20" s="7">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I20" s="7">
-        <v>27455</v>
+        <v>19636</v>
       </c>
       <c r="J20" s="5">
-        <v>70.09999999999999</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>81.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>648000</v>
+        <v>524000</v>
       </c>
       <c r="G21" s="7">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="H21" s="7">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I21" s="7">
-        <v>19905</v>
+        <v>25333</v>
       </c>
       <c r="J21" s="5">
-        <v>69.7</v>
+        <v>69.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>89.3</v>
+        <v>81.2</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>476000</v>
+        <v>866000</v>
       </c>
       <c r="G22" s="7">
-        <v>47000</v>
+        <v>13000</v>
       </c>
       <c r="H22" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I22" s="7">
-        <v>1429</v>
+        <v>18091</v>
       </c>
       <c r="J22" s="5">
-        <v>69.5</v>
+        <v>69.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,23 +1353,23 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>85</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>555000</v>
+        <v>405000</v>
       </c>
       <c r="G23" s="7">
-        <v>37000</v>
+        <v>17000</v>
       </c>
       <c r="H23" s="7">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="I23" s="7">
-        <v>9952</v>
+        <v>21111</v>
       </c>
       <c r="J23" s="5">
         <v>69.2</v>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>82</v>
+        <v>87.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>349000</v>
+        <v>520000</v>
       </c>
       <c r="G24" s="7">
-        <v>17000</v>
+        <v>44000</v>
       </c>
       <c r="H24" s="7">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I24" s="7">
-        <v>23600</v>
+        <v>3364</v>
       </c>
       <c r="J24" s="5">
-        <v>69</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>82</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>384000</v>
+        <v>218000</v>
       </c>
       <c r="G25" s="7">
         <v>15000</v>
       </c>
       <c r="H25" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I25" s="7">
-        <v>22800</v>
+        <v>26000</v>
       </c>
       <c r="J25" s="5">
-        <v>68.8</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>86</v>
+        <v>83.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>237000</v>
+        <v>587000</v>
       </c>
       <c r="G26" s="7">
-        <v>39000</v>
+        <v>32000</v>
       </c>
       <c r="H26" s="7">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="I26" s="7">
-        <v>24250</v>
+        <v>10955</v>
       </c>
       <c r="J26" s="5">
-        <v>68.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>78.8</v>
+        <v>79.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>632000</v>
+        <v>390000</v>
       </c>
       <c r="G27" s="7">
-        <v>-1000</v>
+        <v>6000</v>
       </c>
       <c r="H27" s="7">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I27" s="7">
-        <v>19857</v>
+        <v>20000</v>
       </c>
       <c r="J27" s="5">
-        <v>68.3</v>
+        <v>68.7</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>81.7</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>393000</v>
+        <v>232000</v>
       </c>
       <c r="G28" s="7">
-        <v>14000</v>
+        <v>19000</v>
       </c>
       <c r="H28" s="7">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I28" s="7">
-        <v>12667</v>
+        <v>18000</v>
       </c>
       <c r="J28" s="5">
-        <v>68.09999999999999</v>
+        <v>68.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>80.59999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>220000</v>
+        <v>856000</v>
       </c>
       <c r="G29" s="7">
-        <v>21000</v>
+        <v>31000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I29" s="7">
-        <v>13500</v>
+        <v>18273</v>
       </c>
       <c r="J29" s="5">
-        <v>67.7</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>80.5</v>
+        <v>99.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>1670000</v>
+        <v>104000</v>
       </c>
       <c r="G30" s="7">
-        <v>4000</v>
+        <v>15000</v>
       </c>
       <c r="H30" s="7">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I30" s="7">
-        <v>12810</v>
+        <v>7667</v>
       </c>
       <c r="J30" s="5">
-        <v>67.5</v>
+        <v>68.5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>80</v>
+        <v>76.2</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>824000</v>
+        <v>586000</v>
       </c>
       <c r="G31" s="7">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="H31" s="7">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I31" s="7">
-        <v>13810</v>
+        <v>25500</v>
       </c>
       <c r="J31" s="5">
-        <v>67.5</v>
+        <v>68.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>93.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>504000</v>
+        <v>407000</v>
       </c>
       <c r="G32" s="7">
-        <v>25000</v>
+        <v>14000</v>
       </c>
       <c r="H32" s="7">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I32" s="7">
-        <v>28000</v>
+        <v>12727</v>
       </c>
       <c r="J32" s="5">
-        <v>67.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>80</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>248000</v>
+        <v>103000</v>
       </c>
       <c r="G33" s="7">
-        <v>13000</v>
+        <v>16000</v>
       </c>
       <c r="H33" s="7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I33" s="7">
-        <v>11909</v>
+        <v>20000</v>
       </c>
       <c r="J33" s="5">
-        <v>67</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>95.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>281000</v>
+        <v>298000</v>
       </c>
       <c r="G34" s="7">
-        <v>23000</v>
+        <v>17000</v>
       </c>
       <c r="H34" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="7">
-        <v>22000</v>
+        <v>20333</v>
       </c>
       <c r="J34" s="5">
-        <v>66.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>79.59999999999999</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>510000</v>
+        <v>196000</v>
       </c>
       <c r="G35" s="7">
-        <v>51000</v>
+        <v>21000</v>
       </c>
       <c r="H35" s="7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I35" s="7">
-        <v>12083</v>
+        <v>26000</v>
       </c>
       <c r="J35" s="5">
-        <v>66.8</v>
+        <v>67.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>81.09999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>422000</v>
+        <v>440000</v>
       </c>
       <c r="G36" s="7">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="H36" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I36" s="7">
-        <v>8714</v>
+        <v>9136</v>
       </c>
       <c r="J36" s="5">
-        <v>66.8</v>
+        <v>67.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>81.7</v>
+        <v>84.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>450000</v>
+        <v>2117000</v>
       </c>
       <c r="G37" s="7">
-        <v>38000</v>
+        <v>64000</v>
       </c>
       <c r="H37" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I37" s="7">
-        <v>7143</v>
+        <v>3909</v>
       </c>
       <c r="J37" s="5">
-        <v>66.7</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>84.3</v>
+        <v>81.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>2053000</v>
+        <v>312000</v>
       </c>
       <c r="G38" s="7">
-        <v>55000</v>
+        <v>15000</v>
       </c>
       <c r="H38" s="7">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="I38" s="7">
-        <v>1048</v>
+        <v>10800</v>
       </c>
       <c r="J38" s="5">
-        <v>66.59999999999999</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>82.8</v>
+        <v>82</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>356000</v>
+        <v>492000</v>
       </c>
       <c r="G39" s="7">
-        <v>85000</v>
+        <v>42000</v>
       </c>
       <c r="H39" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I39" s="7">
-        <v>3619</v>
+        <v>8727</v>
       </c>
       <c r="J39" s="5">
-        <v>66.40000000000001</v>
+        <v>67.3</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>82.8</v>
+        <v>79.3</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>1703000</v>
+        <v>240000</v>
       </c>
       <c r="G40" s="7">
-        <v>28000</v>
+        <v>20000</v>
       </c>
       <c r="H40" s="7">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I40" s="7">
-        <v>3095</v>
+        <v>14429</v>
       </c>
       <c r="J40" s="5">
-        <v>66.3</v>
+        <v>67.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>96.2</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>213000</v>
+        <v>403000</v>
       </c>
       <c r="G41" s="7">
-        <v>20000</v>
+        <v>47000</v>
       </c>
       <c r="H41" s="7">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I41" s="7">
-        <v>17500</v>
+        <v>5591</v>
       </c>
       <c r="J41" s="5">
-        <v>66.3</v>
+        <v>67</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>92.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>317000</v>
+        <v>300000</v>
       </c>
       <c r="G42" s="7">
-        <v>20000</v>
+        <v>23000</v>
       </c>
       <c r="H42" s="7">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I42" s="7">
-        <v>25000</v>
+        <v>8579</v>
       </c>
       <c r="J42" s="5">
-        <v>66.2</v>
+        <v>67</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>77</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>544000</v>
+        <v>825000</v>
       </c>
       <c r="G43" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H43" s="7">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I43" s="7">
-        <v>15143</v>
+        <v>13227</v>
       </c>
       <c r="J43" s="5">
-        <v>66.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>95.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>220000</v>
+        <v>328000</v>
       </c>
       <c r="G44" s="7">
-        <v>17000</v>
+        <v>11000</v>
       </c>
       <c r="H44" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" s="7">
-        <v>19000</v>
+        <v>20333</v>
       </c>
       <c r="J44" s="5">
-        <v>66.09999999999999</v>
+        <v>66.7</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>94</v>
+        <v>79.5</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>134000</v>
+        <v>1658000</v>
       </c>
       <c r="G45" s="7">
-        <v>25000</v>
+        <v>-12000</v>
       </c>
       <c r="H45" s="7">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="I45" s="7">
-        <v>21500</v>
+        <v>11682</v>
       </c>
       <c r="J45" s="5">
-        <v>66.09999999999999</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>390000</v>
+        <v>259000</v>
       </c>
       <c r="G46" s="7">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="H46" s="7">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7">
-        <v>11095</v>
+        <v>16000</v>
       </c>
       <c r="J46" s="5">
-        <v>65.7</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>96.8</v>
+        <v>92.8</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>133000</v>
+        <v>138000</v>
       </c>
       <c r="G47" s="7">
-        <v>16000</v>
+        <v>13000</v>
       </c>
       <c r="H47" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I47" s="7">
-        <v>14000</v>
+        <v>13667</v>
       </c>
       <c r="J47" s="5">
-        <v>65.7</v>
+        <v>66.5</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>75</v>
+        <v>82.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>345000</v>
+        <v>1726000</v>
       </c>
       <c r="G48" s="7">
-        <v>5000</v>
+        <v>23000</v>
       </c>
       <c r="H48" s="7">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="I48" s="7">
-        <v>17500</v>
+        <v>4000</v>
       </c>
       <c r="J48" s="5">
-        <v>65.59999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>77.59999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>378000</v>
+        <v>614000</v>
       </c>
       <c r="G49" s="7">
-        <v>-1000</v>
+        <v>-18000</v>
       </c>
       <c r="H49" s="7">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="I49" s="7">
-        <v>10667</v>
+        <v>18136</v>
       </c>
       <c r="J49" s="5">
-        <v>65.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>74.3</v>
+        <v>89.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>335000</v>
+        <v>165000</v>
       </c>
       <c r="G50" s="7">
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="H50" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I50" s="7">
-        <v>17750</v>
+        <v>20667</v>
       </c>
       <c r="J50" s="5">
-        <v>65.3</v>
+        <v>66.2</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>78.8</v>
+        <v>92.3</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>277000</v>
+        <v>145000</v>
       </c>
       <c r="G51" s="7">
-        <v>17000</v>
+        <v>12000</v>
       </c>
       <c r="H51" s="7">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="I51" s="7">
-        <v>7778</v>
+        <v>13333</v>
       </c>
       <c r="J51" s="5">
-        <v>65.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>80.59999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>216000</v>
+        <v>169000</v>
       </c>
       <c r="G52" s="7">
-        <v>13000</v>
+        <v>10000</v>
       </c>
       <c r="H52" s="7">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I52" s="7">
-        <v>3333</v>
+        <v>11667</v>
       </c>
       <c r="J52" s="5">
-        <v>65.2</v>
+        <v>65.7</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>95.8</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>125000</v>
+        <v>548000</v>
       </c>
       <c r="G53" s="7">
-        <v>15000</v>
+        <v>38000</v>
       </c>
       <c r="H53" s="7">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I53" s="7">
-        <v>14000</v>
+        <v>14077</v>
       </c>
       <c r="J53" s="5">
-        <v>65.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>74.3</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>540000</v>
+        <v>325000</v>
       </c>
       <c r="G54" s="7">
-        <v>-10000</v>
+        <v>13000</v>
       </c>
       <c r="H54" s="7">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>16333</v>
+        <v>15333</v>
       </c>
       <c r="J54" s="5">
-        <v>64.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-06T06:01:30+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-07T05:35:40+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,13 +70,16 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>都重生了，谁还装富二代啊</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>都重生了，谁还装富二代啊</t>
+    <t>开局九选四，生来便是误闯天家</t>
   </si>
   <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
@@ -85,142 +88,139 @@
     <t>高武：看不起斩魄刀，流刃若火呢</t>
   </si>
   <si>
-    <t>开局九选四，生来便是误闯天家</t>
+    <t>精灵：杀穿超古代的我只想退休</t>
   </si>
   <si>
     <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
+    <t>李承乾拥兵百万，三千剑仙逼宫！</t>
+  </si>
+  <si>
+    <t>全球修仙：只有我商城降价十亿倍</t>
+  </si>
+  <si>
+    <t>大明：开局政变，请洪武赴死！</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>大一开学300斤，减一斤一个亿</t>
+  </si>
+  <si>
     <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
-    <t>我合成了全世界</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
+    <t>1955，归国带飞国家工业</t>
+  </si>
+  <si>
+    <t>停下吧苏总，国家已经兜不住了！</t>
+  </si>
+  <si>
+    <t>末日海上求生，开局SSS级天赋</t>
+  </si>
+  <si>
+    <t>莫欺老年穷：我一个铜板一年功力</t>
+  </si>
+  <si>
+    <t>光门连通淞户，大国倾国以赴</t>
+  </si>
+  <si>
+    <t>大明国舅：开局赐婚徐妙云</t>
   </si>
   <si>
     <t>四合院：从李云龙战友开始</t>
   </si>
   <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
+  </si>
+  <si>
+    <t>系统延迟一坤年，我成了全球股东</t>
+  </si>
+  <si>
     <t>全民地仙：开局紫金葫芦辟福地</t>
   </si>
   <si>
     <t>穿书反派，把阴湿女主养成病娇了</t>
   </si>
   <si>
-    <t>系统延迟一坤年，我成了全球股东</t>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>奥特综漫直播：什么叫人类灭绝了</t>
+  </si>
+  <si>
+    <t>回到二战，我成了美国大兵</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>穿书后，我把女主养成病娇了</t>
+  </si>
+  <si>
+    <t>重生之我卖的真是高压锅</t>
+  </si>
+  <si>
+    <t>刚上大一，抽到财阀身份被曝光</t>
+  </si>
+  <si>
+    <t>四合院：大家一起做禽兽</t>
+  </si>
+  <si>
+    <t>我的沪上野妻</t>
   </si>
   <si>
     <t>朱标私生子，老朱逼我当皇帝！</t>
   </si>
   <si>
-    <t>莫欺老年穷：我一个铜板一年功力</t>
+    <t>魏家孽种成首辅，全族跪求我认祖</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>末世死考：开局天使魅魔三选一</t>
+  </si>
+  <si>
+    <t>洪荒：截教逆徒，截胡的截！</t>
+  </si>
+  <si>
+    <t>龙族：我的强化每月刷新</t>
+  </si>
+  <si>
+    <t>成龙历险记，不过我是斯卡蒂</t>
+  </si>
+  <si>
+    <t>序列车队：我能无限升级奇物</t>
   </si>
   <si>
     <t>我是皇帝我怕谁？</t>
   </si>
   <si>
-    <t>什么叫我成了灭世级怪谈？</t>
-  </si>
-  <si>
-    <t>我的沪上野妻</t>
-  </si>
-  <si>
-    <t>天灾末世：我能提取神话词条</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>刚上大一，抽到财阀身份被曝光</t>
-  </si>
-  <si>
-    <t>魏家孽种成首辅，全族跪求我认祖</t>
-  </si>
-  <si>
-    <t>重生之我卖的真是高压锅</t>
-  </si>
-  <si>
-    <t>精灵：杀穿超古代的我只想退休</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>李承乾拥兵百万，三千剑仙逼宫！</t>
+    <t>兄弟托孤，让我做好爸爸？</t>
   </si>
   <si>
     <t>直播见证神话：从鳌太线走蛟开始</t>
   </si>
   <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>大明国舅：开局赐婚徐妙云</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
-    <t>成龙历险记，不过我是斯卡蒂</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
+    <t>给员工发超跑，你当死士养呢？</t>
+  </si>
+  <si>
+    <t>原神：尼伯龙根转世，女皇大孝子</t>
+  </si>
+  <si>
+    <t>我的密法天赋没有上限</t>
   </si>
   <si>
     <t>神通者</t>
-  </si>
-  <si>
-    <t>网游：我的药剂永久持续</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>死亡列车：开局SSS级天赋！</t>
-  </si>
-  <si>
-    <t>给员工发超跑，你当死士养呢？</t>
-  </si>
-  <si>
-    <t>让你守破道观，你咋真修仙了？</t>
-  </si>
-  <si>
-    <t>直播我和徐妙云，老朱全家破防了</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
-  </si>
-  <si>
-    <t>规则怪谈：无所谓，系统会出手</t>
-  </si>
-  <si>
-    <t>开箱必出神话级，阁下如何应对？</t>
-  </si>
-  <si>
-    <t>答应联姻，冰山女总裁咋成病娇了</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>全国没几个正常人？朕要杀疯了</t>
-  </si>
-  <si>
-    <t>四合院：大家一起做禽兽</t>
-  </si>
-  <si>
-    <t>穿书后，我把女主养成病娇了</t>
-  </si>
-  <si>
-    <t>停下吧苏总，国家已经兜不住了！</t>
-  </si>
-  <si>
-    <t>全民神祇时代：我的词条每日刷新</t>
-  </si>
-  <si>
-    <t>龙族：我的强化每月刷新</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>84.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1713000</v>
+        <v>738000</v>
       </c>
       <c r="G5" s="7">
-        <v>70000</v>
+        <v>160000</v>
       </c>
       <c r="H5" s="7">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I5" s="7">
-        <v>76857</v>
+        <v>125000</v>
       </c>
       <c r="J5" s="5">
-        <v>85.7</v>
+        <v>88</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>90.5</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>578000</v>
+        <v>1770000</v>
       </c>
       <c r="G6" s="7">
-        <v>248000</v>
+        <v>57000</v>
       </c>
       <c r="H6" s="7">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I6" s="7">
-        <v>107500</v>
+        <v>75533</v>
       </c>
       <c r="J6" s="5">
-        <v>83.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1584000</v>
+        <v>306000</v>
       </c>
       <c r="G7" s="7">
-        <v>114000</v>
+        <v>103000</v>
       </c>
       <c r="H7" s="7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I7" s="7">
-        <v>56136</v>
+        <v>53750</v>
       </c>
       <c r="J7" s="5">
-        <v>81.90000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>358000</v>
+        <v>1688000</v>
       </c>
       <c r="G8" s="7">
-        <v>54000</v>
+        <v>104000</v>
       </c>
       <c r="H8" s="7">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I8" s="7">
-        <v>41000</v>
+        <v>58217</v>
       </c>
       <c r="J8" s="5">
-        <v>77.2</v>
+        <v>82.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -898,19 +898,19 @@
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>203000</v>
+        <v>404000</v>
       </c>
       <c r="G9" s="7">
-        <v>69000</v>
+        <v>46000</v>
       </c>
       <c r="H9" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="7">
-        <v>37333</v>
+        <v>42250</v>
       </c>
       <c r="J9" s="5">
-        <v>76.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>82.7</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>758000</v>
+        <v>285000</v>
       </c>
       <c r="G10" s="7">
-        <v>24000</v>
+        <v>53000</v>
       </c>
       <c r="H10" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7">
-        <v>41333</v>
+        <v>26750</v>
       </c>
       <c r="J10" s="5">
-        <v>75.8</v>
+        <v>76.7</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>79.59999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>509000</v>
+        <v>781000</v>
       </c>
       <c r="G11" s="7">
-        <v>33000</v>
+        <v>23000</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I11" s="7">
-        <v>40667</v>
+        <v>39500</v>
       </c>
       <c r="J11" s="5">
-        <v>73.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>87.3</v>
+        <v>100</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>284000</v>
+        <v>160000</v>
       </c>
       <c r="G12" s="7">
-        <v>47000</v>
+        <v>56000</v>
       </c>
       <c r="H12" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7">
-        <v>28800</v>
+        <v>19750</v>
       </c>
       <c r="J12" s="5">
-        <v>73.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>86.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>837000</v>
+        <v>166000</v>
       </c>
       <c r="G13" s="7">
-        <v>55000</v>
+        <v>64000</v>
       </c>
       <c r="H13" s="7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I13" s="7">
-        <v>20273</v>
+        <v>22000</v>
       </c>
       <c r="J13" s="5">
-        <v>72.7</v>
+        <v>74.3</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>83.59999999999999</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>372000</v>
+        <v>109000</v>
       </c>
       <c r="G14" s="7">
-        <v>23000</v>
+        <v>14000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I14" s="7">
-        <v>23500</v>
+        <v>19000</v>
       </c>
       <c r="J14" s="5">
-        <v>71.90000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>83.90000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>289000</v>
+        <v>556000</v>
       </c>
       <c r="G15" s="7">
         <v>32000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I15" s="7">
-        <v>22286</v>
+        <v>27000</v>
       </c>
       <c r="J15" s="5">
-        <v>71.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>84</v>
+        <v>97.2</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>645000</v>
+        <v>190000</v>
       </c>
       <c r="G16" s="7">
-        <v>45000</v>
+        <v>47000</v>
       </c>
       <c r="H16" s="7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I16" s="7">
-        <v>21667</v>
+        <v>20000</v>
       </c>
       <c r="J16" s="5">
-        <v>71.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>81.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>619000</v>
+        <v>538000</v>
       </c>
       <c r="G17" s="7">
-        <v>30000</v>
+        <v>29000</v>
       </c>
       <c r="H17" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>23462</v>
+        <v>39000</v>
       </c>
       <c r="J17" s="5">
-        <v>70.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>77.8</v>
+        <v>97.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>511000</v>
+        <v>232000</v>
       </c>
       <c r="G18" s="7">
-        <v>13000</v>
+        <v>36000</v>
       </c>
       <c r="H18" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I18" s="7">
-        <v>29500</v>
+        <v>18500</v>
       </c>
       <c r="J18" s="5">
-        <v>70.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>97.2</v>
+        <v>98.8</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>157000</v>
+        <v>190000</v>
       </c>
       <c r="G19" s="7">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="H19" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
-        <v>18667</v>
+        <v>14000</v>
       </c>
       <c r="J19" s="5">
-        <v>70.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>81.3</v>
+        <v>97.7</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>662000</v>
+        <v>113000</v>
       </c>
       <c r="G20" s="7">
         <v>14000</v>
       </c>
       <c r="H20" s="7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I20" s="7">
-        <v>19636</v>
+        <v>12000</v>
       </c>
       <c r="J20" s="5">
-        <v>69.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>92.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>524000</v>
+        <v>174000</v>
       </c>
       <c r="G21" s="7">
-        <v>20000</v>
+        <v>17000</v>
       </c>
       <c r="H21" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" s="7">
-        <v>25333</v>
+        <v>18250</v>
       </c>
       <c r="J21" s="5">
-        <v>69.3</v>
+        <v>71.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>81.2</v>
+        <v>97.2</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>866000</v>
+        <v>129000</v>
       </c>
       <c r="G22" s="7">
-        <v>13000</v>
+        <v>19000</v>
       </c>
       <c r="H22" s="7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I22" s="7">
-        <v>18091</v>
+        <v>11750</v>
       </c>
       <c r="J22" s="5">
-        <v>69.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>79.90000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>405000</v>
+        <v>119000</v>
       </c>
       <c r="G23" s="7">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="H23" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I23" s="7">
-        <v>21111</v>
+        <v>18667</v>
       </c>
       <c r="J23" s="5">
-        <v>69.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>87.8</v>
+        <v>82.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>520000</v>
+        <v>390000</v>
       </c>
       <c r="G24" s="7">
-        <v>44000</v>
+        <v>18000</v>
       </c>
       <c r="H24" s="7">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I24" s="7">
-        <v>3364</v>
+        <v>22714</v>
       </c>
       <c r="J24" s="5">
-        <v>69.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>91.59999999999999</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>218000</v>
+        <v>314000</v>
       </c>
       <c r="G25" s="7">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="H25" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="7">
-        <v>26000</v>
+        <v>19250</v>
       </c>
       <c r="J25" s="5">
-        <v>68.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>83.8</v>
+        <v>92.3</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>587000</v>
+        <v>346000</v>
       </c>
       <c r="G26" s="7">
-        <v>32000</v>
+        <v>18000</v>
       </c>
       <c r="H26" s="7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I26" s="7">
-        <v>10955</v>
+        <v>19750</v>
       </c>
       <c r="J26" s="5">
-        <v>68.8</v>
+        <v>70.7</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>79.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>390000</v>
+        <v>642000</v>
       </c>
       <c r="G27" s="7">
-        <v>6000</v>
+        <v>23000</v>
       </c>
       <c r="H27" s="7">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I27" s="7">
-        <v>20000</v>
+        <v>23429</v>
       </c>
       <c r="J27" s="5">
-        <v>68.7</v>
+        <v>70.5</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>94.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>232000</v>
+        <v>313000</v>
       </c>
       <c r="G28" s="7">
-        <v>19000</v>
+        <v>24000</v>
       </c>
       <c r="H28" s="7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I28" s="7">
-        <v>18000</v>
+        <v>22500</v>
       </c>
       <c r="J28" s="5">
-        <v>68.7</v>
+        <v>70.5</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>80.09999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>856000</v>
+        <v>676000</v>
       </c>
       <c r="G29" s="7">
         <v>31000</v>
       </c>
       <c r="H29" s="7">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="I29" s="7">
-        <v>18273</v>
+        <v>22250</v>
       </c>
       <c r="J29" s="5">
-        <v>68.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>99.3</v>
+        <v>89</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>104000</v>
+        <v>573000</v>
       </c>
       <c r="G30" s="7">
-        <v>15000</v>
+        <v>53000</v>
       </c>
       <c r="H30" s="7">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I30" s="7">
-        <v>7667</v>
+        <v>5522</v>
       </c>
       <c r="J30" s="5">
-        <v>68.5</v>
+        <v>70.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>76.2</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>586000</v>
+        <v>222000</v>
       </c>
       <c r="G31" s="7">
-        <v>4000</v>
+        <v>23000</v>
       </c>
       <c r="H31" s="7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I31" s="7">
-        <v>25500</v>
+        <v>32500</v>
       </c>
       <c r="J31" s="5">
-        <v>68.3</v>
+        <v>70.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>81.59999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>407000</v>
+        <v>139000</v>
       </c>
       <c r="G32" s="7">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="H32" s="7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I32" s="7">
-        <v>12727</v>
+        <v>9750</v>
       </c>
       <c r="J32" s="5">
-        <v>68.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>98.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>103000</v>
+        <v>904000</v>
       </c>
       <c r="G33" s="7">
-        <v>16000</v>
+        <v>48000</v>
       </c>
       <c r="H33" s="7">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I33" s="7">
-        <v>20000</v>
+        <v>19565</v>
       </c>
       <c r="J33" s="5">
-        <v>68.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>92.59999999999999</v>
+        <v>93.7</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>298000</v>
+        <v>180000</v>
       </c>
       <c r="G34" s="7">
-        <v>17000</v>
+        <v>21000</v>
       </c>
       <c r="H34" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" s="7">
-        <v>20333</v>
+        <v>13000</v>
       </c>
       <c r="J34" s="5">
-        <v>68</v>
+        <v>69.8</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>95.09999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>196000</v>
+        <v>159000</v>
       </c>
       <c r="G35" s="7">
-        <v>21000</v>
+        <v>14000</v>
       </c>
       <c r="H35" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I35" s="7">
-        <v>26000</v>
+        <v>13500</v>
       </c>
       <c r="J35" s="5">
-        <v>67.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>82.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>440000</v>
+        <v>403000</v>
       </c>
       <c r="G36" s="7">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="H36" s="7">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>9136</v>
+        <v>19000</v>
       </c>
       <c r="J36" s="5">
-        <v>67.7</v>
+        <v>69.5</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>84.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>2117000</v>
+        <v>228000</v>
       </c>
       <c r="G37" s="7">
-        <v>64000</v>
+        <v>10000</v>
       </c>
       <c r="H37" s="7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I37" s="7">
-        <v>3909</v>
+        <v>22000</v>
       </c>
       <c r="J37" s="5">
-        <v>67.59999999999999</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>81.7</v>
+        <v>89.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>312000</v>
+        <v>183000</v>
       </c>
       <c r="G38" s="7">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="H38" s="7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I38" s="7">
-        <v>10800</v>
+        <v>20000</v>
       </c>
       <c r="J38" s="5">
-        <v>67.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>82</v>
+        <v>81.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>492000</v>
+        <v>880000</v>
       </c>
       <c r="G39" s="7">
-        <v>42000</v>
+        <v>14000</v>
       </c>
       <c r="H39" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I39" s="7">
-        <v>8727</v>
+        <v>17913</v>
       </c>
       <c r="J39" s="5">
-        <v>67.3</v>
+        <v>69.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>79.3</v>
+        <v>77</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>240000</v>
+        <v>516000</v>
       </c>
       <c r="G40" s="7">
-        <v>20000</v>
+        <v>5000</v>
       </c>
       <c r="H40" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I40" s="7">
-        <v>14429</v>
+        <v>27273</v>
       </c>
       <c r="J40" s="5">
-        <v>67.2</v>
+        <v>69.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>82.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>403000</v>
+        <v>615000</v>
       </c>
       <c r="G41" s="7">
-        <v>47000</v>
+        <v>28000</v>
       </c>
       <c r="H41" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I41" s="7">
-        <v>5591</v>
+        <v>11696</v>
       </c>
       <c r="J41" s="5">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>81.5</v>
+        <v>84.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>300000</v>
+        <v>467000</v>
       </c>
       <c r="G42" s="7">
-        <v>23000</v>
+        <v>27000</v>
       </c>
       <c r="H42" s="7">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I42" s="7">
-        <v>8579</v>
+        <v>9913</v>
       </c>
       <c r="J42" s="5">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>78.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>825000</v>
+        <v>124000</v>
       </c>
       <c r="G43" s="7">
-        <v>1000</v>
+        <v>11000</v>
       </c>
       <c r="H43" s="7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I43" s="7">
-        <v>13227</v>
+        <v>12000</v>
       </c>
       <c r="J43" s="5">
-        <v>66.7</v>
+        <v>69</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>90.2</v>
+        <v>92.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>328000</v>
+        <v>159000</v>
       </c>
       <c r="G44" s="7">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="H44" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I44" s="7">
-        <v>20333</v>
+        <v>12750</v>
       </c>
       <c r="J44" s="5">
-        <v>66.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>79.5</v>
+        <v>90.3</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>1658000</v>
+        <v>339000</v>
       </c>
       <c r="G45" s="7">
-        <v>-12000</v>
+        <v>14000</v>
       </c>
       <c r="H45" s="7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I45" s="7">
-        <v>11682</v>
+        <v>15000</v>
       </c>
       <c r="J45" s="5">
-        <v>66.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,14 +2112,14 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>92</v>
+        <v>92.3</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>259000</v>
+        <v>212000</v>
       </c>
       <c r="G46" s="7">
         <v>16000</v>
@@ -2128,10 +2128,10 @@
         <v>4</v>
       </c>
       <c r="I46" s="7">
-        <v>16000</v>
+        <v>22667</v>
       </c>
       <c r="J46" s="5">
-        <v>66.59999999999999</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>92.8</v>
+        <v>93.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>138000</v>
+        <v>108000</v>
       </c>
       <c r="G47" s="7">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="H47" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I47" s="7">
-        <v>13667</v>
+        <v>7750</v>
       </c>
       <c r="J47" s="5">
-        <v>66.5</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>82.5</v>
+        <v>79.3</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>1726000</v>
+        <v>663000</v>
       </c>
       <c r="G48" s="7">
-        <v>23000</v>
+        <v>1000</v>
       </c>
       <c r="H48" s="7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I48" s="7">
-        <v>4000</v>
+        <v>18826</v>
       </c>
       <c r="J48" s="5">
-        <v>66.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>76.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>614000</v>
+        <v>103000</v>
       </c>
       <c r="G49" s="7">
-        <v>-18000</v>
+        <v>13000</v>
       </c>
       <c r="H49" s="7">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="I49" s="7">
-        <v>18136</v>
+        <v>11000</v>
       </c>
       <c r="J49" s="5">
-        <v>66.40000000000001</v>
+        <v>68.3</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>89.2</v>
+        <v>76.7</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>165000</v>
+        <v>593000</v>
       </c>
       <c r="G50" s="7">
-        <v>17000</v>
+        <v>7000</v>
       </c>
       <c r="H50" s="7">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I50" s="7">
-        <v>20667</v>
+        <v>24077</v>
       </c>
       <c r="J50" s="5">
-        <v>66.2</v>
+        <v>68.2</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>92.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>145000</v>
+        <v>456000</v>
       </c>
       <c r="G51" s="7">
-        <v>12000</v>
+        <v>53000</v>
       </c>
       <c r="H51" s="7">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I51" s="7">
-        <v>13333</v>
+        <v>7652</v>
       </c>
       <c r="J51" s="5">
-        <v>66.09999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>92.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>169000</v>
+        <v>195000</v>
       </c>
       <c r="G52" s="7">
-        <v>10000</v>
+        <v>17000</v>
       </c>
       <c r="H52" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I52" s="7">
-        <v>11667</v>
+        <v>9750</v>
       </c>
       <c r="J52" s="5">
-        <v>65.7</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>76.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>548000</v>
+        <v>131000</v>
       </c>
       <c r="G53" s="7">
-        <v>38000</v>
+        <v>17000</v>
       </c>
       <c r="H53" s="7">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I53" s="7">
-        <v>14077</v>
+        <v>13000</v>
       </c>
       <c r="J53" s="5">
-        <v>65.40000000000001</v>
+        <v>67.8</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>90.09999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>325000</v>
+        <v>2168000</v>
       </c>
       <c r="G54" s="7">
-        <v>13000</v>
+        <v>51000</v>
       </c>
       <c r="H54" s="7">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I54" s="7">
-        <v>15333</v>
+        <v>5957</v>
       </c>
       <c r="J54" s="5">
-        <v>65.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-07T05:35:40+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-08T05:44:04+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>开局九选四，生来便是误闯天家</t>
+  </si>
+  <si>
     <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
-    <t>开局九选四，生来便是误闯天家</t>
-  </si>
-  <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
+    <t>全球修仙：只有我商城降价十亿倍</t>
+  </si>
+  <si>
+    <t>精灵：杀穿超古代的我只想退休</t>
+  </si>
+  <si>
     <t>高武：看不起斩魄刀，流刃若火呢</t>
   </si>
   <si>
-    <t>精灵：杀穿超古代的我只想退休</t>
+    <t>李承乾拥兵百万，三千剑仙逼宫！</t>
+  </si>
+  <si>
+    <t>1955，归国带飞国家工业</t>
+  </si>
+  <si>
+    <t>末世死考：开局天使魅魔三选一</t>
+  </si>
+  <si>
+    <t>大明：开局政变，请洪武赴死！</t>
+  </si>
+  <si>
+    <t>光门连通淞户，大国倾国以赴</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>停下吧苏总，国家已经兜不住了！</t>
+  </si>
+  <si>
+    <t>莫欺老年穷：我一个铜板一年功力</t>
+  </si>
+  <si>
+    <t>穿书后，我把女主养成病娇了</t>
+  </si>
+  <si>
+    <t>大明第一国舅，开局治好朱雄英！</t>
   </si>
   <si>
     <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
-    <t>李承乾拥兵百万，三千剑仙逼宫！</t>
-  </si>
-  <si>
-    <t>全球修仙：只有我商城降价十亿倍</t>
-  </si>
-  <si>
-    <t>大明：开局政变，请洪武赴死！</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
+    <t>法庭暴君：从反杀讹诈犯开始</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
+  </si>
+  <si>
+    <t>序列车队：我能无限升级奇物</t>
+  </si>
+  <si>
+    <t>末日海上求生，开局SSS级天赋</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>四合院：大家一起做禽兽</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>公路求生：刷新重卡一级一节车厢</t>
+  </si>
+  <si>
+    <t>洪荒：唯一金乌一心只想拐婆娘</t>
+  </si>
+  <si>
+    <t>大明国舅：开局赐婚徐妙云</t>
+  </si>
+  <si>
+    <t>洪荒：截教逆徒，截胡的截！</t>
+  </si>
+  <si>
+    <t>三角洲：能恋与洲，谁还打职业啊</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>饥荒求生，国运垫底咋饱荒了？</t>
+  </si>
+  <si>
+    <t>四合院：从李云龙战友开始</t>
+  </si>
+  <si>
+    <t>回到二战，我成了美国大兵</t>
+  </si>
+  <si>
+    <t>报告，美少女后桌又拿臭脚熏我！</t>
+  </si>
+  <si>
+    <t>全民副本：我能打造九九八十一难</t>
+  </si>
+  <si>
+    <t>啊？我是背景通天的大佬？</t>
+  </si>
+  <si>
+    <t>朱标私生子，老朱逼我当皇帝！</t>
   </si>
   <si>
     <t>大一开学300斤，减一斤一个亿</t>
   </si>
   <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>1955，归国带飞国家工业</t>
-  </si>
-  <si>
-    <t>停下吧苏总，国家已经兜不住了！</t>
-  </si>
-  <si>
-    <t>末日海上求生，开局SSS级天赋</t>
-  </si>
-  <si>
-    <t>莫欺老年穷：我一个铜板一年功力</t>
-  </si>
-  <si>
-    <t>光门连通淞户，大国倾国以赴</t>
-  </si>
-  <si>
-    <t>大明国舅：开局赐婚徐妙云</t>
-  </si>
-  <si>
-    <t>四合院：从李云龙战友开始</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
-  </si>
-  <si>
-    <t>系统延迟一坤年，我成了全球股东</t>
-  </si>
-  <si>
     <t>全民地仙：开局紫金葫芦辟福地</t>
   </si>
   <si>
+    <t>规则怪谈：我穿越成了F级诡异</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>原神：尼伯龙根转世，女皇大孝子</t>
+  </si>
+  <si>
+    <t>我的密法天赋没有上限</t>
+  </si>
+  <si>
+    <t>国运求生：我的幸运值拉满了</t>
+  </si>
+  <si>
+    <t>全民航海：古神对我的船重度依赖</t>
+  </si>
+  <si>
     <t>穿书反派，把阴湿女主养成病娇了</t>
   </si>
   <si>
     <t>人在诡异，靠第四天灾登顶至高</t>
   </si>
   <si>
-    <t>奥特综漫直播：什么叫人类灭绝了</t>
-  </si>
-  <si>
-    <t>回到二战，我成了美国大兵</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>穿书后，我把女主养成病娇了</t>
-  </si>
-  <si>
-    <t>重生之我卖的真是高压锅</t>
-  </si>
-  <si>
     <t>刚上大一，抽到财阀身份被曝光</t>
   </si>
   <si>
-    <t>四合院：大家一起做禽兽</t>
-  </si>
-  <si>
-    <t>我的沪上野妻</t>
-  </si>
-  <si>
-    <t>朱标私生子，老朱逼我当皇帝！</t>
-  </si>
-  <si>
-    <t>魏家孽种成首辅，全族跪求我认祖</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>末世死考：开局天使魅魔三选一</t>
-  </si>
-  <si>
-    <t>洪荒：截教逆徒，截胡的截！</t>
-  </si>
-  <si>
-    <t>龙族：我的强化每月刷新</t>
-  </si>
-  <si>
-    <t>成龙历险记，不过我是斯卡蒂</t>
-  </si>
-  <si>
-    <t>序列车队：我能无限升级奇物</t>
-  </si>
-  <si>
-    <t>我是皇帝我怕谁？</t>
-  </si>
-  <si>
-    <t>兄弟托孤，让我做好爸爸？</t>
-  </si>
-  <si>
-    <t>直播见证神话：从鳌太线走蛟开始</t>
-  </si>
-  <si>
-    <t>给员工发超跑，你当死士养呢？</t>
-  </si>
-  <si>
-    <t>原神：尼伯龙根转世，女皇大孝子</t>
-  </si>
-  <si>
-    <t>我的密法天赋没有上限</t>
-  </si>
-  <si>
-    <t>神通者</t>
+    <t>出门捡垃圾，我被美女总裁强推了</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>92.7</v>
+        <v>93.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>738000</v>
+        <v>844000</v>
       </c>
       <c r="G5" s="7">
-        <v>160000</v>
+        <v>106000</v>
       </c>
       <c r="H5" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="7">
-        <v>125000</v>
+        <v>120250</v>
       </c>
       <c r="J5" s="5">
-        <v>88</v>
+        <v>91.3</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>1770000</v>
+        <v>390000</v>
       </c>
       <c r="G6" s="7">
-        <v>57000</v>
+        <v>84000</v>
       </c>
       <c r="H6" s="7">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="I6" s="7">
-        <v>75533</v>
+        <v>59800</v>
       </c>
       <c r="J6" s="5">
-        <v>85.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>306000</v>
+        <v>1816000</v>
       </c>
       <c r="G7" s="7">
-        <v>103000</v>
+        <v>46000</v>
       </c>
       <c r="H7" s="7">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I7" s="7">
-        <v>53750</v>
+        <v>73688</v>
       </c>
       <c r="J7" s="5">
-        <v>83.40000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>86.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>1688000</v>
+        <v>1790000</v>
       </c>
       <c r="G8" s="7">
-        <v>104000</v>
+        <v>102000</v>
       </c>
       <c r="H8" s="7">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I8" s="7">
-        <v>58217</v>
+        <v>60042</v>
       </c>
       <c r="J8" s="5">
-        <v>82.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -898,19 +898,19 @@
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>404000</v>
+        <v>257000</v>
       </c>
       <c r="G9" s="7">
-        <v>46000</v>
+        <v>91000</v>
       </c>
       <c r="H9" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>42250</v>
+        <v>35800</v>
       </c>
       <c r="J9" s="5">
-        <v>80.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -931,19 +931,19 @@
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>285000</v>
+        <v>349000</v>
       </c>
       <c r="G10" s="7">
-        <v>53000</v>
+        <v>64000</v>
       </c>
       <c r="H10" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>26750</v>
+        <v>34200</v>
       </c>
       <c r="J10" s="5">
-        <v>76.7</v>
+        <v>81.5</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>82.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>781000</v>
+        <v>434000</v>
       </c>
       <c r="G11" s="7">
-        <v>23000</v>
+        <v>30000</v>
       </c>
       <c r="H11" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I11" s="7">
-        <v>39500</v>
+        <v>39800</v>
       </c>
       <c r="J11" s="5">
-        <v>75.2</v>
+        <v>80.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -997,19 +997,19 @@
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>160000</v>
+        <v>187000</v>
       </c>
       <c r="G12" s="7">
-        <v>56000</v>
+        <v>27000</v>
       </c>
       <c r="H12" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="7">
-        <v>19750</v>
+        <v>21200</v>
       </c>
       <c r="J12" s="5">
-        <v>74.90000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>97.8</v>
+        <v>98.8</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>166000</v>
+        <v>271000</v>
       </c>
       <c r="G13" s="7">
-        <v>64000</v>
+        <v>39000</v>
       </c>
       <c r="H13" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>22000</v>
+        <v>22600</v>
       </c>
       <c r="J13" s="5">
-        <v>74.3</v>
+        <v>78</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>99.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>109000</v>
+        <v>162000</v>
       </c>
       <c r="G14" s="7">
-        <v>14000</v>
+        <v>38000</v>
       </c>
       <c r="H14" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>19000</v>
+        <v>17200</v>
       </c>
       <c r="J14" s="5">
-        <v>74.3</v>
+        <v>77.3</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>556000</v>
+        <v>124000</v>
       </c>
       <c r="G15" s="7">
-        <v>32000</v>
+        <v>15000</v>
       </c>
       <c r="H15" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" s="7">
-        <v>27000</v>
+        <v>18200</v>
       </c>
       <c r="J15" s="5">
-        <v>73.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>97.2</v>
+        <v>99.3</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>190000</v>
+        <v>159000</v>
       </c>
       <c r="G16" s="7">
-        <v>47000</v>
+        <v>30000</v>
       </c>
       <c r="H16" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16" s="7">
-        <v>20000</v>
+        <v>15400</v>
       </c>
       <c r="J16" s="5">
-        <v>73.5</v>
+        <v>76.5</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>79.40000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>538000</v>
+        <v>576000</v>
       </c>
       <c r="G17" s="7">
-        <v>29000</v>
+        <v>20000</v>
       </c>
       <c r="H17" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>39000</v>
+        <v>25600</v>
       </c>
       <c r="J17" s="5">
-        <v>73.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>97.7</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>232000</v>
+        <v>210000</v>
       </c>
       <c r="G18" s="7">
-        <v>36000</v>
+        <v>20000</v>
       </c>
       <c r="H18" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="7">
-        <v>18500</v>
+        <v>15200</v>
       </c>
       <c r="J18" s="5">
-        <v>73.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>98.8</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>190000</v>
+        <v>194000</v>
       </c>
       <c r="G19" s="7">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="H19" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19" s="7">
-        <v>14000</v>
+        <v>18600</v>
       </c>
       <c r="J19" s="5">
-        <v>72.8</v>
+        <v>74.7</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>97.7</v>
+        <v>96.5</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>113000</v>
+        <v>178000</v>
       </c>
       <c r="G20" s="7">
-        <v>14000</v>
+        <v>19000</v>
       </c>
       <c r="H20" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
-        <v>12000</v>
+        <v>14600</v>
       </c>
       <c r="J20" s="5">
-        <v>71.7</v>
+        <v>74.7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>94.5</v>
+        <v>98.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>174000</v>
+        <v>110000</v>
       </c>
       <c r="G21" s="7">
-        <v>17000</v>
+        <v>23000</v>
       </c>
       <c r="H21" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I21" s="7">
-        <v>18250</v>
+        <v>8400</v>
       </c>
       <c r="J21" s="5">
-        <v>71.5</v>
+        <v>74.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>97.2</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>129000</v>
+        <v>797000</v>
       </c>
       <c r="G22" s="7">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H22" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I22" s="7">
-        <v>11750</v>
+        <v>37364</v>
       </c>
       <c r="J22" s="5">
-        <v>71.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>99.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>119000</v>
+        <v>139000</v>
       </c>
       <c r="G23" s="7">
-        <v>16000</v>
+        <v>34000</v>
       </c>
       <c r="H23" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I23" s="7">
-        <v>18667</v>
+        <v>10200</v>
       </c>
       <c r="J23" s="5">
-        <v>71.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>82.8</v>
+        <v>92.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>390000</v>
+        <v>366000</v>
       </c>
       <c r="G24" s="7">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="H24" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I24" s="7">
-        <v>22714</v>
+        <v>19800</v>
       </c>
       <c r="J24" s="5">
-        <v>71.2</v>
+        <v>74</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>92.90000000000001</v>
+        <v>97.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>314000</v>
+        <v>128000</v>
       </c>
       <c r="G25" s="7">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="H25" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I25" s="7">
-        <v>19250</v>
+        <v>10200</v>
       </c>
       <c r="J25" s="5">
-        <v>70.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>92.3</v>
+        <v>96.2</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>346000</v>
+        <v>126000</v>
       </c>
       <c r="G26" s="7">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="H26" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" s="7">
-        <v>19750</v>
+        <v>12200</v>
       </c>
       <c r="J26" s="5">
-        <v>70.7</v>
+        <v>74</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>81.09999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>642000</v>
+        <v>131000</v>
       </c>
       <c r="G27" s="7">
-        <v>23000</v>
+        <v>43000</v>
       </c>
       <c r="H27" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I27" s="7">
-        <v>23429</v>
+        <v>19500</v>
       </c>
       <c r="J27" s="5">
-        <v>70.5</v>
+        <v>73.8</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>81.59999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>313000</v>
+        <v>204000</v>
       </c>
       <c r="G28" s="7">
-        <v>24000</v>
+        <v>21000</v>
       </c>
       <c r="H28" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I28" s="7">
-        <v>22500</v>
+        <v>20200</v>
       </c>
       <c r="J28" s="5">
-        <v>70.5</v>
+        <v>73.3</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>81.5</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>676000</v>
+        <v>565000</v>
       </c>
       <c r="G29" s="7">
-        <v>31000</v>
+        <v>27000</v>
       </c>
       <c r="H29" s="7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I29" s="7">
-        <v>22250</v>
+        <v>37500</v>
       </c>
       <c r="J29" s="5">
-        <v>70.40000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>573000</v>
+        <v>102000</v>
       </c>
       <c r="G30" s="7">
-        <v>53000</v>
+        <v>19000</v>
       </c>
       <c r="H30" s="7">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>5522</v>
+        <v>10000</v>
       </c>
       <c r="J30" s="5">
-        <v>70.3</v>
+        <v>72.8</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>96.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>222000</v>
+        <v>103000</v>
       </c>
       <c r="G31" s="7">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="H31" s="7">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I31" s="7">
-        <v>32500</v>
+        <v>13750</v>
       </c>
       <c r="J31" s="5">
-        <v>70.3</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>96.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>139000</v>
+        <v>133000</v>
       </c>
       <c r="G32" s="7">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="H32" s="7">
         <v>5</v>
       </c>
       <c r="I32" s="7">
-        <v>9750</v>
+        <v>17500</v>
       </c>
       <c r="J32" s="5">
-        <v>70.3</v>
+        <v>72.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>82.09999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>904000</v>
+        <v>176000</v>
       </c>
       <c r="G33" s="7">
-        <v>48000</v>
+        <v>17000</v>
       </c>
       <c r="H33" s="7">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I33" s="7">
-        <v>19565</v>
+        <v>13600</v>
       </c>
       <c r="J33" s="5">
-        <v>70</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>93.7</v>
+        <v>94.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>180000</v>
+        <v>121000</v>
       </c>
       <c r="G34" s="7">
-        <v>21000</v>
+        <v>12000</v>
       </c>
       <c r="H34" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>13000</v>
+        <v>8800</v>
       </c>
       <c r="J34" s="5">
-        <v>69.8</v>
+        <v>72.3</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>93.2</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>159000</v>
+        <v>323000</v>
       </c>
       <c r="G35" s="7">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="H35" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>13500</v>
+        <v>17200</v>
       </c>
       <c r="J35" s="5">
-        <v>69.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>81.40000000000001</v>
+        <v>96</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>403000</v>
+        <v>114000</v>
       </c>
       <c r="G36" s="7">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>19000</v>
+        <v>4000</v>
       </c>
       <c r="J36" s="5">
-        <v>69.5</v>
+        <v>71.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>88.90000000000001</v>
+        <v>83.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>228000</v>
+        <v>411000</v>
       </c>
       <c r="G37" s="7">
-        <v>10000</v>
+        <v>21000</v>
       </c>
       <c r="H37" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I37" s="7">
-        <v>22000</v>
+        <v>22500</v>
       </c>
       <c r="J37" s="5">
-        <v>69.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>89.7</v>
+        <v>92.8</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>183000</v>
+        <v>152000</v>
       </c>
       <c r="G38" s="7">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="H38" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>20000</v>
+        <v>10400</v>
       </c>
       <c r="J38" s="5">
-        <v>69.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>81.3</v>
+        <v>93.5</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>880000</v>
+        <v>109000</v>
       </c>
       <c r="G39" s="7">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="H39" s="7">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I39" s="7">
-        <v>17913</v>
+        <v>8600</v>
       </c>
       <c r="J39" s="5">
-        <v>69.2</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>77</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>516000</v>
+        <v>123000</v>
       </c>
       <c r="G40" s="7">
-        <v>5000</v>
+        <v>25000</v>
       </c>
       <c r="H40" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I40" s="7">
-        <v>27273</v>
+        <v>15000</v>
       </c>
       <c r="J40" s="5">
-        <v>69.2</v>
+        <v>71.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>83.7</v>
+        <v>93.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>615000</v>
+        <v>112000</v>
       </c>
       <c r="G41" s="7">
-        <v>28000</v>
+        <v>14000</v>
       </c>
       <c r="H41" s="7">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I41" s="7">
-        <v>11696</v>
+        <v>6600</v>
       </c>
       <c r="J41" s="5">
-        <v>69</v>
+        <v>71.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>84.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>467000</v>
+        <v>538000</v>
       </c>
       <c r="G42" s="7">
-        <v>27000</v>
+        <v>22000</v>
       </c>
       <c r="H42" s="7">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="I42" s="7">
-        <v>9913</v>
+        <v>26833</v>
       </c>
       <c r="J42" s="5">
-        <v>69</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>92.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>124000</v>
+        <v>200000</v>
       </c>
       <c r="G43" s="7">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="H43" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I43" s="7">
-        <v>12000</v>
+        <v>18000</v>
       </c>
       <c r="J43" s="5">
-        <v>69</v>
+        <v>70.7</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>92.2</v>
+        <v>81.5</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>159000</v>
+        <v>333000</v>
       </c>
       <c r="G44" s="7">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="H44" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I44" s="7">
-        <v>12750</v>
+        <v>22222</v>
       </c>
       <c r="J44" s="5">
-        <v>68.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>90.3</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>339000</v>
+        <v>116000</v>
       </c>
       <c r="G45" s="7">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="H45" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="7">
-        <v>15000</v>
+        <v>6600</v>
       </c>
       <c r="J45" s="5">
-        <v>68.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>92.3</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>212000</v>
+        <v>942000</v>
       </c>
       <c r="G46" s="7">
-        <v>16000</v>
+        <v>38000</v>
       </c>
       <c r="H46" s="7">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I46" s="7">
-        <v>22667</v>
+        <v>20333</v>
       </c>
       <c r="J46" s="5">
-        <v>68.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>93.5</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>108000</v>
+        <v>208000</v>
       </c>
       <c r="G47" s="7">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="H47" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I47" s="7">
-        <v>7750</v>
+        <v>10400</v>
       </c>
       <c r="J47" s="5">
-        <v>68.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>79.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>663000</v>
+        <v>146000</v>
       </c>
       <c r="G48" s="7">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="H48" s="7">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I48" s="7">
-        <v>18826</v>
+        <v>13500</v>
       </c>
       <c r="J48" s="5">
-        <v>68.3</v>
+        <v>70</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>92</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>103000</v>
+        <v>141000</v>
       </c>
       <c r="G49" s="7">
-        <v>13000</v>
+        <v>26000</v>
       </c>
       <c r="H49" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I49" s="7">
-        <v>11000</v>
+        <v>19667</v>
       </c>
       <c r="J49" s="5">
-        <v>68.3</v>
+        <v>70</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>76.7</v>
+        <v>90.5</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>593000</v>
+        <v>165000</v>
       </c>
       <c r="G50" s="7">
         <v>7000</v>
       </c>
       <c r="H50" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I50" s="7">
-        <v>24077</v>
+        <v>8400</v>
       </c>
       <c r="J50" s="5">
-        <v>68.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>83.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>456000</v>
+        <v>701000</v>
       </c>
       <c r="G51" s="7">
-        <v>53000</v>
+        <v>25000</v>
       </c>
       <c r="H51" s="7">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="I51" s="7">
-        <v>7652</v>
+        <v>22412</v>
       </c>
       <c r="J51" s="5">
-        <v>68.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>91.8</v>
+        <v>87.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>195000</v>
+        <v>620000</v>
       </c>
       <c r="G52" s="7">
-        <v>17000</v>
+        <v>47000</v>
       </c>
       <c r="H52" s="7">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I52" s="7">
-        <v>9750</v>
+        <v>7250</v>
       </c>
       <c r="J52" s="5">
-        <v>67.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>95.5</v>
+        <v>86</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>131000</v>
+        <v>230000</v>
       </c>
       <c r="G53" s="7">
-        <v>17000</v>
+        <v>2000</v>
       </c>
       <c r="H53" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I53" s="7">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="J53" s="5">
-        <v>67.8</v>
+        <v>69.8</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>84.09999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>2168000</v>
+        <v>140000</v>
       </c>
       <c r="G54" s="7">
-        <v>51000</v>
+        <v>15000</v>
       </c>
       <c r="H54" s="7">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="I54" s="7">
-        <v>5957</v>
+        <v>7556</v>
       </c>
       <c r="J54" s="5">
-        <v>67.7</v>
+        <v>69.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-08T05:44:04+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-09T05:48:31+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>开局九选四，生来便是误闯天家</t>
   </si>
   <si>
+    <t>全球修仙：只有我商城降价十亿倍</t>
+  </si>
+  <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
     <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>全球修仙：只有我商城降价十亿倍</t>
-  </si>
-  <si>
     <t>精灵：杀穿超古代的我只想退休</t>
   </si>
   <si>
     <t>高武：看不起斩魄刀，流刃若火呢</t>
   </si>
   <si>
+    <t>1955，归国带飞国家工业</t>
+  </si>
+  <si>
+    <t>末世死考：开局天使魅魔三选一</t>
+  </si>
+  <si>
+    <t>大明：开局政变，请洪武赴死！</t>
+  </si>
+  <si>
+    <t>光门连通淞户，大国倾国以赴</t>
+  </si>
+  <si>
+    <t>法庭暴君：从反杀讹诈犯开始</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>序列车队：我能无限升级奇物</t>
+  </si>
+  <si>
+    <t>大明第一国舅，开局治好朱雄英！</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>莫欺老年穷：我一个铜板一年功力</t>
+  </si>
+  <si>
+    <t>全民副本：我能打造九九八十一难</t>
+  </si>
+  <si>
+    <t>停下吧苏总，国家已经兜不住了！</t>
+  </si>
+  <si>
     <t>李承乾拥兵百万，三千剑仙逼宫！</t>
   </si>
   <si>
-    <t>1955，归国带飞国家工业</t>
-  </si>
-  <si>
-    <t>末世死考：开局天使魅魔三选一</t>
-  </si>
-  <si>
-    <t>大明：开局政变，请洪武赴死！</t>
-  </si>
-  <si>
-    <t>光门连通淞户，大国倾国以赴</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
-  </si>
-  <si>
-    <t>停下吧苏总，国家已经兜不住了！</t>
-  </si>
-  <si>
-    <t>莫欺老年穷：我一个铜板一年功力</t>
-  </si>
-  <si>
-    <t>穿书后，我把女主养成病娇了</t>
-  </si>
-  <si>
-    <t>大明第一国舅，开局治好朱雄英！</t>
+    <t>公路求生：刷新重卡一级一节车厢</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>三角洲：能恋与洲，谁还打职业啊</t>
+  </si>
+  <si>
+    <t>洪荒：截教逆徒，截胡的截！</t>
+  </si>
+  <si>
+    <t>大明国舅：开局赐婚徐妙云</t>
+  </si>
+  <si>
+    <t>末日海上求生，开局SSS级天赋</t>
+  </si>
+  <si>
+    <t>啊？我是背景通天的大佬？</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>大唐：我娶你姐，李世民你兴奋啥</t>
+  </si>
+  <si>
+    <t>饥荒求生，国运垫底咋饱荒了？</t>
   </si>
   <si>
     <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
-    <t>法庭暴君：从反杀讹诈犯开始</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
-  </si>
-  <si>
-    <t>序列车队：我能无限升级奇物</t>
-  </si>
-  <si>
-    <t>末日海上求生，开局SSS级天赋</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
+    <t>我的密法天赋没有上限</t>
+  </si>
+  <si>
+    <t>出门捡垃圾，我被美女总裁强推了</t>
+  </si>
+  <si>
+    <t>我是赫萝大第38本书</t>
+  </si>
+  <si>
+    <t>大一开学300斤，减一斤一个亿</t>
   </si>
   <si>
     <t>四合院：大家一起做禽兽</t>
   </si>
   <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>公路求生：刷新重卡一级一节车厢</t>
-  </si>
-  <si>
-    <t>洪荒：唯一金乌一心只想拐婆娘</t>
-  </si>
-  <si>
-    <t>大明国舅：开局赐婚徐妙云</t>
-  </si>
-  <si>
-    <t>洪荒：截教逆徒，截胡的截！</t>
-  </si>
-  <si>
-    <t>三角洲：能恋与洲，谁还打职业啊</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
-    <t>饥荒求生，国运垫底咋饱荒了？</t>
+    <t>成龙历险记，不过我是斯卡蒂</t>
+  </si>
+  <si>
+    <t>洪荒：我十凶天角蚁，躺平就变强</t>
+  </si>
+  <si>
+    <t>国运求生：我的幸运值拉满了</t>
   </si>
   <si>
     <t>四合院：从李云龙战友开始</t>
   </si>
   <si>
-    <t>回到二战，我成了美国大兵</t>
-  </si>
-  <si>
-    <t>报告，美少女后桌又拿臭脚熏我！</t>
-  </si>
-  <si>
-    <t>全民副本：我能打造九九八十一难</t>
-  </si>
-  <si>
-    <t>啊？我是背景通天的大佬？</t>
+    <t>年代1958，从搬运工开始！</t>
+  </si>
+  <si>
+    <t>名义赵瑞龙，动点脑就骂我纨绔？</t>
+  </si>
+  <si>
+    <t>大劫将至，从边军开始马踏天下</t>
   </si>
   <si>
     <t>朱标私生子，老朱逼我当皇帝！</t>
   </si>
   <si>
-    <t>大一开学300斤，减一斤一个亿</t>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>刚上大一，抽到财阀身份被曝光</t>
   </si>
   <si>
     <t>全民地仙：开局紫金葫芦辟福地</t>
   </si>
   <si>
-    <t>规则怪谈：我穿越成了F级诡异</t>
-  </si>
-  <si>
     <t>我都宇宙之主了，你们还在地球？</t>
   </si>
   <si>
     <t>原神：尼伯龙根转世，女皇大孝子</t>
-  </si>
-  <si>
-    <t>我的密法天赋没有上限</t>
-  </si>
-  <si>
-    <t>国运求生：我的幸运值拉满了</t>
-  </si>
-  <si>
-    <t>全民航海：古神对我的船重度依赖</t>
-  </si>
-  <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>刚上大一，抽到财阀身份被曝光</t>
-  </si>
-  <si>
-    <t>出门捡垃圾，我被美女总裁强推了</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>93.2</v>
+        <v>90.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>844000</v>
+        <v>936000</v>
       </c>
       <c r="G5" s="7">
-        <v>106000</v>
+        <v>92000</v>
       </c>
       <c r="H5" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
-        <v>120250</v>
+        <v>114600</v>
       </c>
       <c r="J5" s="5">
-        <v>91.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>390000</v>
+        <v>446000</v>
       </c>
       <c r="G6" s="7">
-        <v>84000</v>
+        <v>56000</v>
       </c>
       <c r="H6" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>59800</v>
+        <v>59167</v>
       </c>
       <c r="J6" s="5">
-        <v>88</v>
+        <v>89.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1816000</v>
+        <v>332000</v>
       </c>
       <c r="G7" s="7">
-        <v>46000</v>
+        <v>75000</v>
       </c>
       <c r="H7" s="7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>73688</v>
+        <v>42333</v>
       </c>
       <c r="J7" s="5">
-        <v>84.59999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>86.5</v>
+        <v>87</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>1790000</v>
+        <v>1890000</v>
       </c>
       <c r="G8" s="7">
-        <v>102000</v>
+        <v>100000</v>
       </c>
       <c r="H8" s="7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I8" s="7">
-        <v>60042</v>
+        <v>61640</v>
       </c>
       <c r="J8" s="5">
-        <v>82.59999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>82.5</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>257000</v>
+        <v>1838000</v>
       </c>
       <c r="G9" s="7">
-        <v>91000</v>
+        <v>22000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="I9" s="7">
-        <v>35800</v>
+        <v>70647</v>
       </c>
       <c r="J9" s="5">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>349000</v>
+        <v>384000</v>
       </c>
       <c r="G10" s="7">
-        <v>64000</v>
+        <v>35000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I10" s="7">
-        <v>34200</v>
+        <v>34333</v>
       </c>
       <c r="J10" s="5">
-        <v>81.5</v>
+        <v>82.5</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>95.59999999999999</v>
+        <v>95</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>434000</v>
+        <v>463000</v>
       </c>
       <c r="G11" s="7">
-        <v>30000</v>
+        <v>29000</v>
       </c>
       <c r="H11" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>39800</v>
+        <v>38000</v>
       </c>
       <c r="J11" s="5">
-        <v>80.5</v>
+        <v>81.8</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>187000</v>
+        <v>308000</v>
       </c>
       <c r="G12" s="7">
-        <v>27000</v>
+        <v>37000</v>
       </c>
       <c r="H12" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>21200</v>
+        <v>25000</v>
       </c>
       <c r="J12" s="5">
-        <v>78.3</v>
+        <v>80.5</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>271000</v>
+        <v>188000</v>
       </c>
       <c r="G13" s="7">
-        <v>39000</v>
+        <v>26000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>22600</v>
+        <v>18667</v>
       </c>
       <c r="J13" s="5">
-        <v>78</v>
+        <v>79.7</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1063,19 +1063,19 @@
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>162000</v>
+        <v>143000</v>
       </c>
       <c r="G14" s="7">
-        <v>38000</v>
+        <v>19000</v>
       </c>
       <c r="H14" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>17200</v>
+        <v>18333</v>
       </c>
       <c r="J14" s="5">
-        <v>77.3</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>98.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>124000</v>
+        <v>184000</v>
       </c>
       <c r="G15" s="7">
-        <v>15000</v>
+        <v>25000</v>
       </c>
       <c r="H15" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>18200</v>
+        <v>17000</v>
       </c>
       <c r="J15" s="5">
-        <v>76.7</v>
+        <v>79.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>159000</v>
+        <v>173000</v>
       </c>
       <c r="G16" s="7">
-        <v>30000</v>
+        <v>34000</v>
       </c>
       <c r="H16" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" s="7">
-        <v>15400</v>
+        <v>14167</v>
       </c>
       <c r="J16" s="5">
-        <v>76.5</v>
+        <v>78.3</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>92.40000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>576000</v>
+        <v>161000</v>
       </c>
       <c r="G17" s="7">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="H17" s="7">
         <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>25600</v>
+        <v>21600</v>
       </c>
       <c r="J17" s="5">
-        <v>75.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>97.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>210000</v>
+        <v>155000</v>
       </c>
       <c r="G18" s="7">
-        <v>20000</v>
+        <v>27000</v>
       </c>
       <c r="H18" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="7">
-        <v>15200</v>
+        <v>13000</v>
       </c>
       <c r="J18" s="5">
-        <v>75.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>94.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>194000</v>
+        <v>127000</v>
       </c>
       <c r="G19" s="7">
-        <v>20000</v>
+        <v>17000</v>
       </c>
       <c r="H19" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>18600</v>
+        <v>9833</v>
       </c>
       <c r="J19" s="5">
-        <v>74.7</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>96.5</v>
+        <v>93.7</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>178000</v>
+        <v>390000</v>
       </c>
       <c r="G20" s="7">
-        <v>19000</v>
+        <v>24000</v>
       </c>
       <c r="H20" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20" s="7">
-        <v>14600</v>
+        <v>20500</v>
       </c>
       <c r="J20" s="5">
-        <v>74.7</v>
+        <v>76.7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>98.5</v>
+        <v>91.8</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>110000</v>
+        <v>593000</v>
       </c>
       <c r="G21" s="7">
-        <v>23000</v>
+        <v>17000</v>
       </c>
       <c r="H21" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>8400</v>
+        <v>24167</v>
       </c>
       <c r="J21" s="5">
-        <v>74.3</v>
+        <v>76.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>81.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>797000</v>
+        <v>210000</v>
       </c>
       <c r="G22" s="7">
         <v>16000</v>
       </c>
       <c r="H22" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>37364</v>
+        <v>18167</v>
       </c>
       <c r="J22" s="5">
-        <v>74.2</v>
+        <v>75.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>97.40000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>139000</v>
+        <v>150000</v>
       </c>
       <c r="G23" s="7">
-        <v>34000</v>
+        <v>27000</v>
       </c>
       <c r="H23" s="7">
         <v>6</v>
       </c>
       <c r="I23" s="7">
-        <v>10200</v>
+        <v>17400</v>
       </c>
       <c r="J23" s="5">
-        <v>74.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>92.8</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>366000</v>
+        <v>225000</v>
       </c>
       <c r="G24" s="7">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="H24" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I24" s="7">
-        <v>19800</v>
+        <v>15167</v>
       </c>
       <c r="J24" s="5">
-        <v>74</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>97.2</v>
+        <v>91.8</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>128000</v>
+        <v>197000</v>
       </c>
       <c r="G25" s="7">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="H25" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>10200</v>
+        <v>19333</v>
       </c>
       <c r="J25" s="5">
-        <v>74</v>
+        <v>75.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>96.2</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>126000</v>
+        <v>119000</v>
       </c>
       <c r="G26" s="7">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="H26" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" s="7">
-        <v>12200</v>
+        <v>11167</v>
       </c>
       <c r="J26" s="5">
-        <v>74</v>
+        <v>75.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>98.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>131000</v>
+        <v>339000</v>
       </c>
       <c r="G27" s="7">
-        <v>43000</v>
+        <v>16000</v>
       </c>
       <c r="H27" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I27" s="7">
-        <v>19500</v>
+        <v>17000</v>
       </c>
       <c r="J27" s="5">
-        <v>73.8</v>
+        <v>75.2</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>91.40000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>204000</v>
+        <v>135000</v>
       </c>
       <c r="G28" s="7">
-        <v>21000</v>
+        <v>14000</v>
       </c>
       <c r="H28" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>20200</v>
+        <v>9667</v>
       </c>
       <c r="J28" s="5">
-        <v>73.3</v>
+        <v>75</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>79.59999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>565000</v>
+        <v>195000</v>
       </c>
       <c r="G29" s="7">
-        <v>27000</v>
+        <v>19000</v>
       </c>
       <c r="H29" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>37500</v>
+        <v>14500</v>
       </c>
       <c r="J29" s="5">
-        <v>73.2</v>
+        <v>74.8</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>95</v>
+        <v>94.8</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>102000</v>
+        <v>146000</v>
       </c>
       <c r="G30" s="7">
-        <v>19000</v>
+        <v>13000</v>
       </c>
       <c r="H30" s="7">
         <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>10000</v>
+        <v>16600</v>
       </c>
       <c r="J30" s="5">
-        <v>72.8</v>
+        <v>74.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>98.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>103000</v>
+        <v>136000</v>
       </c>
       <c r="G31" s="7">
-        <v>20000</v>
+        <v>10000</v>
       </c>
       <c r="H31" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I31" s="7">
-        <v>13750</v>
+        <v>11833</v>
       </c>
       <c r="J31" s="5">
-        <v>72.59999999999999</v>
+        <v>74</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>96.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>133000</v>
+        <v>125000</v>
       </c>
       <c r="G32" s="7">
-        <v>14000</v>
+        <v>13000</v>
       </c>
       <c r="H32" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I32" s="7">
-        <v>17500</v>
+        <v>7667</v>
       </c>
       <c r="J32" s="5">
-        <v>72.5</v>
+        <v>73.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.8</v>
+        <v>79.7</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>176000</v>
+        <v>593000</v>
       </c>
       <c r="G33" s="7">
-        <v>17000</v>
+        <v>28000</v>
       </c>
       <c r="H33" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I33" s="7">
-        <v>13600</v>
+        <v>36444</v>
       </c>
       <c r="J33" s="5">
-        <v>72.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>94.8</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>121000</v>
+        <v>104000</v>
       </c>
       <c r="G34" s="7">
-        <v>12000</v>
+        <v>19000</v>
       </c>
       <c r="H34" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I34" s="7">
-        <v>8800</v>
+        <v>27000</v>
       </c>
       <c r="J34" s="5">
-        <v>72.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>90.40000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>323000</v>
+        <v>126000</v>
       </c>
       <c r="G35" s="7">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="H35" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>17200</v>
+        <v>5333</v>
       </c>
       <c r="J35" s="5">
-        <v>72</v>
+        <v>72.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>96</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>114000</v>
+        <v>802000</v>
       </c>
       <c r="G36" s="7">
-        <v>14000</v>
+        <v>5000</v>
       </c>
       <c r="H36" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I36" s="7">
-        <v>4000</v>
+        <v>34667</v>
       </c>
       <c r="J36" s="5">
-        <v>71.8</v>
+        <v>72.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>83.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>411000</v>
+        <v>160000</v>
       </c>
       <c r="G37" s="7">
-        <v>21000</v>
+        <v>14000</v>
       </c>
       <c r="H37" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I37" s="7">
-        <v>22500</v>
+        <v>13600</v>
       </c>
       <c r="J37" s="5">
-        <v>71.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>92.8</v>
+        <v>90.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>152000</v>
+        <v>181000</v>
       </c>
       <c r="G38" s="7">
-        <v>13000</v>
+        <v>41000</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I38" s="7">
-        <v>10400</v>
+        <v>10900</v>
       </c>
       <c r="J38" s="5">
-        <v>71.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>93.5</v>
+        <v>91.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>109000</v>
+        <v>120000</v>
       </c>
       <c r="G39" s="7">
-        <v>18000</v>
+        <v>11000</v>
       </c>
       <c r="H39" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>8600</v>
+        <v>9000</v>
       </c>
       <c r="J39" s="5">
-        <v>71.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>95.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>123000</v>
+        <v>209000</v>
       </c>
       <c r="G40" s="7">
-        <v>25000</v>
+        <v>9000</v>
       </c>
       <c r="H40" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>15000</v>
+        <v>16500</v>
       </c>
       <c r="J40" s="5">
-        <v>71.2</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>93.7</v>
+        <v>86.2</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>112000</v>
+        <v>215000</v>
       </c>
       <c r="G41" s="7">
-        <v>14000</v>
+        <v>11000</v>
       </c>
       <c r="H41" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41" s="7">
-        <v>6600</v>
+        <v>18667</v>
       </c>
       <c r="J41" s="5">
-        <v>71.2</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>80.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>538000</v>
+        <v>236000</v>
       </c>
       <c r="G42" s="7">
-        <v>22000</v>
+        <v>12000</v>
       </c>
       <c r="H42" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I42" s="7">
-        <v>26833</v>
+        <v>18400</v>
       </c>
       <c r="J42" s="5">
-        <v>70.90000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>87.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>200000</v>
+        <v>208000</v>
       </c>
       <c r="G43" s="7">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="H43" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I43" s="7">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="J43" s="5">
-        <v>70.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>81.5</v>
+        <v>94</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>333000</v>
+        <v>157000</v>
       </c>
       <c r="G44" s="7">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="H44" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I44" s="7">
-        <v>22222</v>
+        <v>18750</v>
       </c>
       <c r="J44" s="5">
-        <v>70.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>92.09999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>116000</v>
+        <v>430000</v>
       </c>
       <c r="G45" s="7">
-        <v>9000</v>
+        <v>19000</v>
       </c>
       <c r="H45" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I45" s="7">
-        <v>6600</v>
+        <v>22111</v>
       </c>
       <c r="J45" s="5">
-        <v>70.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>81.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>942000</v>
+        <v>324000</v>
       </c>
       <c r="G46" s="7">
-        <v>38000</v>
+        <v>43000</v>
       </c>
       <c r="H46" s="7">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7">
-        <v>20333</v>
+        <v>38333</v>
       </c>
       <c r="J46" s="5">
-        <v>70</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>89.90000000000001</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>208000</v>
+        <v>203000</v>
       </c>
       <c r="G47" s="7">
-        <v>13000</v>
+        <v>21000</v>
       </c>
       <c r="H47" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I47" s="7">
-        <v>10400</v>
+        <v>23500</v>
       </c>
       <c r="J47" s="5">
-        <v>70</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>93.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>146000</v>
+        <v>106000</v>
       </c>
       <c r="G48" s="7">
-        <v>15000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I48" s="7">
-        <v>13500</v>
+        <v>5833</v>
       </c>
       <c r="J48" s="5">
-        <v>70</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>96.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>141000</v>
+        <v>558000</v>
       </c>
       <c r="G49" s="7">
-        <v>26000</v>
+        <v>20000</v>
       </c>
       <c r="H49" s="7">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I49" s="7">
-        <v>19667</v>
+        <v>26308</v>
       </c>
       <c r="J49" s="5">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>90.5</v>
+        <v>92.5</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>165000</v>
+        <v>677000</v>
       </c>
       <c r="G50" s="7">
-        <v>7000</v>
+        <v>101000</v>
       </c>
       <c r="H50" s="7">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I50" s="7">
-        <v>8400</v>
+        <v>40</v>
       </c>
       <c r="J50" s="5">
-        <v>69.90000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>80.40000000000001</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>701000</v>
+        <v>231000</v>
       </c>
       <c r="G51" s="7">
-        <v>25000</v>
+        <v>1000</v>
       </c>
       <c r="H51" s="7">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="I51" s="7">
-        <v>22412</v>
+        <v>15167</v>
       </c>
       <c r="J51" s="5">
-        <v>69.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>87.2</v>
+        <v>82.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>620000</v>
+        <v>351000</v>
       </c>
       <c r="G52" s="7">
-        <v>47000</v>
+        <v>18000</v>
       </c>
       <c r="H52" s="7">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="I52" s="7">
-        <v>7250</v>
+        <v>21800</v>
       </c>
       <c r="J52" s="5">
-        <v>69.8</v>
+        <v>70.7</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>86</v>
+        <v>82.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>230000</v>
+        <v>979000</v>
       </c>
       <c r="G53" s="7">
-        <v>2000</v>
+        <v>37000</v>
       </c>
       <c r="H53" s="7">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="I53" s="7">
-        <v>18000</v>
+        <v>21000</v>
       </c>
       <c r="J53" s="5">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>86.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>140000</v>
+        <v>216000</v>
       </c>
       <c r="G54" s="7">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="H54" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I54" s="7">
-        <v>7556</v>
+        <v>10000</v>
       </c>
       <c r="J54" s="5">
-        <v>69.7</v>
+        <v>70.5</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-09T05:48:31+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-10T05:31:39+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,10 +76,13 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>全球修仙：只有我商城降价十亿倍</t>
+  </si>
+  <si>
     <t>开局九选四，生来便是误闯天家</t>
   </si>
   <si>
-    <t>全球修仙：只有我商城降价十亿倍</t>
+    <t>大一开学300斤，减一斤一个亿</t>
   </si>
   <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
@@ -88,139 +91,136 @@
     <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>1955，归国带飞国家工业</t>
+  </si>
+  <si>
     <t>精灵：杀穿超古代的我只想退休</t>
   </si>
   <si>
-    <t>高武：看不起斩魄刀，流刃若火呢</t>
-  </si>
-  <si>
-    <t>1955，归国带飞国家工业</t>
+    <t>序列车队：我能无限升级奇物</t>
+  </si>
+  <si>
+    <t>光门连通淞户，大国倾国以赴</t>
+  </si>
+  <si>
+    <t>大唐：我娶你姐，李世民你兴奋啥</t>
+  </si>
+  <si>
+    <t>全民副本：我能打造九九八十一难</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
+  </si>
+  <si>
+    <t>大明：开局政变，请洪武赴死！</t>
+  </si>
+  <si>
+    <t>大明第一国舅，开局治好朱雄英！</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>大明国舅：开局赐婚徐妙云</t>
+  </si>
+  <si>
+    <t>我的密法天赋没有上限</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>莫欺老年穷：我一个铜板一年功力</t>
+  </si>
+  <si>
+    <t>啊？我是背景通天的大佬？</t>
+  </si>
+  <si>
+    <t>九叔：让你请祖师，你请雷部天将</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>名义赵瑞龙，动点脑就骂我纨绔？</t>
+  </si>
+  <si>
+    <t>洪荒：截教逆徒，截胡的截！</t>
+  </si>
+  <si>
+    <t>出门捡垃圾，我被美女总裁强推了</t>
+  </si>
+  <si>
+    <t>成龙历险记，不过我是斯卡蒂</t>
+  </si>
+  <si>
+    <t>停下吧苏总，国家已经兜不住了！</t>
+  </si>
+  <si>
+    <t>开局最弱大帝，禁区至尊被逼疯了</t>
+  </si>
+  <si>
+    <t>末日海上求生，开局SSS级天赋</t>
+  </si>
+  <si>
+    <t>李承乾拥兵百万，三千剑仙逼宫！</t>
+  </si>
+  <si>
+    <t>法庭暴君：从反杀讹诈犯开始</t>
+  </si>
+  <si>
+    <t>国运求生：我的幸运值拉满了</t>
+  </si>
+  <si>
+    <t>生子就变强！开局拿捏丰腴女帝</t>
+  </si>
+  <si>
+    <t>奥特综漫直播：什么叫人类灭绝了</t>
+  </si>
+  <si>
+    <t>名义：搭档沙瑞金，让育良复婚！</t>
   </si>
   <si>
     <t>末世死考：开局天使魅魔三选一</t>
   </si>
   <si>
-    <t>大明：开局政变，请洪武赴死！</t>
-  </si>
-  <si>
-    <t>光门连通淞户，大国倾国以赴</t>
-  </si>
-  <si>
-    <t>法庭暴君：从反杀讹诈犯开始</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>序列车队：我能无限升级奇物</t>
-  </si>
-  <si>
-    <t>大明第一国舅，开局治好朱雄英！</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
-  </si>
-  <si>
-    <t>莫欺老年穷：我一个铜板一年功力</t>
-  </si>
-  <si>
-    <t>全民副本：我能打造九九八十一难</t>
-  </si>
-  <si>
-    <t>停下吧苏总，国家已经兜不住了！</t>
-  </si>
-  <si>
-    <t>李承乾拥兵百万，三千剑仙逼宫！</t>
-  </si>
-  <si>
-    <t>公路求生：刷新重卡一级一节车厢</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
     <t>三角洲：能恋与洲，谁还打职业啊</t>
   </si>
   <si>
-    <t>洪荒：截教逆徒，截胡的截！</t>
-  </si>
-  <si>
-    <t>大明国舅：开局赐婚徐妙云</t>
-  </si>
-  <si>
-    <t>末日海上求生，开局SSS级天赋</t>
-  </si>
-  <si>
-    <t>啊？我是背景通天的大佬？</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>大唐：我娶你姐，李世民你兴奋啥</t>
-  </si>
-  <si>
-    <t>饥荒求生，国运垫底咋饱荒了？</t>
-  </si>
-  <si>
-    <t>从修仙回到都市，坏消息修为没了</t>
-  </si>
-  <si>
-    <t>我的密法天赋没有上限</t>
-  </si>
-  <si>
-    <t>出门捡垃圾，我被美女总裁强推了</t>
-  </si>
-  <si>
-    <t>我是赫萝大第38本书</t>
-  </si>
-  <si>
-    <t>大一开学300斤，减一斤一个亿</t>
-  </si>
-  <si>
-    <t>四合院：大家一起做禽兽</t>
-  </si>
-  <si>
-    <t>成龙历险记，不过我是斯卡蒂</t>
-  </si>
-  <si>
-    <t>洪荒：我十凶天角蚁，躺平就变强</t>
-  </si>
-  <si>
-    <t>国运求生：我的幸运值拉满了</t>
+    <t>我都宇宙之主了，你们还在地球？</t>
   </si>
   <si>
     <t>四合院：从李云龙战友开始</t>
   </si>
   <si>
+    <t>中奖两个亿，我在县城当豪门！</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>年代：每日情报开局截胡女儿国王</t>
+  </si>
+  <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>四合院：顶替婚姻，淮茹悔断肠！</t>
+  </si>
+  <si>
+    <t>大劫将至，从边军开始马踏天下</t>
+  </si>
+  <si>
     <t>年代1958，从搬运工开始！</t>
   </si>
   <si>
-    <t>名义赵瑞龙，动点脑就骂我纨绔？</t>
-  </si>
-  <si>
-    <t>大劫将至，从边军开始马踏天下</t>
-  </si>
-  <si>
-    <t>朱标私生子，老朱逼我当皇帝！</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>刚上大一，抽到财阀身份被曝光</t>
-  </si>
-  <si>
-    <t>全民地仙：开局紫金葫芦辟福地</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>原神：尼伯龙根转世，女皇大孝子</t>
+    <t>女局长：扫黑之路</t>
+  </si>
+  <si>
+    <t>回到二战，我成了美国大兵</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>90.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>936000</v>
+        <v>1028000</v>
       </c>
       <c r="G5" s="7">
         <v>92000</v>
       </c>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="7">
-        <v>114600</v>
+        <v>110833</v>
       </c>
       <c r="J5" s="5">
-        <v>92.90000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>446000</v>
+        <v>407000</v>
       </c>
       <c r="G6" s="7">
-        <v>56000</v>
+        <v>75000</v>
       </c>
       <c r="H6" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="7">
-        <v>59167</v>
+        <v>47000</v>
       </c>
       <c r="J6" s="5">
-        <v>89.8</v>
+        <v>86.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>332000</v>
+        <v>464000</v>
       </c>
       <c r="G7" s="7">
-        <v>75000</v>
+        <v>18000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>42333</v>
+        <v>53286</v>
       </c>
       <c r="J7" s="5">
-        <v>85.59999999999999</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>1890000</v>
+        <v>314000</v>
       </c>
       <c r="G8" s="7">
-        <v>100000</v>
+        <v>105000</v>
       </c>
       <c r="H8" s="7">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7">
-        <v>61640</v>
+        <v>29143</v>
       </c>
       <c r="J8" s="5">
-        <v>83.3</v>
+        <v>82.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>82.5</v>
+        <v>84.2</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>1838000</v>
+        <v>1942000</v>
       </c>
       <c r="G9" s="7">
-        <v>22000</v>
+        <v>52000</v>
       </c>
       <c r="H9" s="7">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="I9" s="7">
-        <v>70647</v>
+        <v>61269</v>
       </c>
       <c r="J9" s="5">
-        <v>83</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>98</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>384000</v>
+        <v>1825000</v>
       </c>
       <c r="G10" s="7">
-        <v>35000</v>
+        <v>-13000</v>
       </c>
       <c r="H10" s="7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I10" s="7">
-        <v>34333</v>
+        <v>66000</v>
       </c>
       <c r="J10" s="5">
-        <v>82.5</v>
+        <v>80.8</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>463000</v>
+        <v>184000</v>
       </c>
       <c r="G11" s="7">
-        <v>29000</v>
+        <v>23000</v>
       </c>
       <c r="H11" s="7">
         <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>38000</v>
+        <v>21833</v>
       </c>
       <c r="J11" s="5">
-        <v>81.8</v>
+        <v>80.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>98.59999999999999</v>
+        <v>97.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>308000</v>
+        <v>344000</v>
       </c>
       <c r="G12" s="7">
-        <v>37000</v>
+        <v>36000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" s="7">
-        <v>25000</v>
+        <v>26571</v>
       </c>
       <c r="J12" s="5">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>188000</v>
+        <v>403000</v>
       </c>
       <c r="G13" s="7">
-        <v>26000</v>
+        <v>19000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>18667</v>
+        <v>32143</v>
       </c>
       <c r="J13" s="5">
-        <v>79.7</v>
+        <v>79.2</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1063,19 +1063,19 @@
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>143000</v>
+        <v>183000</v>
       </c>
       <c r="G14" s="7">
-        <v>19000</v>
+        <v>28000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="7">
-        <v>18333</v>
+        <v>15143</v>
       </c>
       <c r="J14" s="5">
-        <v>79.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>184000</v>
+        <v>203000</v>
       </c>
       <c r="G15" s="7">
-        <v>25000</v>
+        <v>19000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>17000</v>
+        <v>17286</v>
       </c>
       <c r="J15" s="5">
-        <v>79.2</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>99.5</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>173000</v>
+        <v>120000</v>
       </c>
       <c r="G16" s="7">
-        <v>34000</v>
+        <v>16000</v>
       </c>
       <c r="H16" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I16" s="7">
-        <v>14167</v>
+        <v>24250</v>
       </c>
       <c r="J16" s="5">
-        <v>78.3</v>
+        <v>75.8</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>98.5</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>161000</v>
+        <v>165000</v>
       </c>
       <c r="G17" s="7">
-        <v>30000</v>
+        <v>15000</v>
       </c>
       <c r="H17" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" s="7">
-        <v>21600</v>
+        <v>17000</v>
       </c>
       <c r="J17" s="5">
-        <v>77.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>97.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>155000</v>
+        <v>407000</v>
       </c>
       <c r="G18" s="7">
-        <v>27000</v>
+        <v>17000</v>
       </c>
       <c r="H18" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I18" s="7">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="J18" s="5">
-        <v>76.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>98.90000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>127000</v>
+        <v>153000</v>
       </c>
       <c r="G19" s="7">
-        <v>17000</v>
+        <v>10000</v>
       </c>
       <c r="H19" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" s="7">
-        <v>9833</v>
+        <v>17143</v>
       </c>
       <c r="J19" s="5">
-        <v>76.90000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>93.7</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>390000</v>
+        <v>142000</v>
       </c>
       <c r="G20" s="7">
-        <v>24000</v>
+        <v>15000</v>
       </c>
       <c r="H20" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" s="7">
-        <v>20500</v>
+        <v>10571</v>
       </c>
       <c r="J20" s="5">
-        <v>76.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>91.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>593000</v>
+        <v>602000</v>
       </c>
       <c r="G21" s="7">
-        <v>17000</v>
+        <v>9000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>24167</v>
+        <v>22000</v>
       </c>
       <c r="J21" s="5">
-        <v>76.5</v>
+        <v>75.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>93.2</v>
+        <v>92</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>210000</v>
+        <v>156000</v>
       </c>
       <c r="G22" s="7">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="H22" s="7">
         <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>18167</v>
+        <v>15500</v>
       </c>
       <c r="J22" s="5">
-        <v>75.8</v>
+        <v>74.5</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>96.7</v>
+        <v>92.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>150000</v>
+        <v>172000</v>
       </c>
       <c r="G23" s="7">
-        <v>27000</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>17400</v>
+        <v>13333</v>
       </c>
       <c r="J23" s="5">
-        <v>75.5</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>93.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>225000</v>
+        <v>627000</v>
       </c>
       <c r="G24" s="7">
-        <v>15000</v>
+        <v>34000</v>
       </c>
       <c r="H24" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I24" s="7">
-        <v>15167</v>
+        <v>36200</v>
       </c>
       <c r="J24" s="5">
-        <v>75.40000000000001</v>
+        <v>74.3</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>91.8</v>
+        <v>90.8</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>197000</v>
+        <v>222000</v>
       </c>
       <c r="G25" s="7">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I25" s="7">
-        <v>19333</v>
+        <v>17286</v>
       </c>
       <c r="J25" s="5">
-        <v>75.3</v>
+        <v>74.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>95.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>119000</v>
+        <v>140000</v>
       </c>
       <c r="G26" s="7">
-        <v>17000</v>
+        <v>15000</v>
       </c>
       <c r="H26" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>11167</v>
+        <v>8714</v>
       </c>
       <c r="J26" s="5">
-        <v>75.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>92.59999999999999</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>339000</v>
+        <v>162000</v>
       </c>
       <c r="G27" s="7">
-        <v>16000</v>
+        <v>30000</v>
       </c>
       <c r="H27" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I27" s="7">
-        <v>17000</v>
+        <v>29000</v>
       </c>
       <c r="J27" s="5">
-        <v>75.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>95.59999999999999</v>
+        <v>89.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>135000</v>
+        <v>346000</v>
       </c>
       <c r="G28" s="7">
-        <v>14000</v>
+        <v>7000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>9667</v>
+        <v>15571</v>
       </c>
       <c r="J28" s="5">
-        <v>75</v>
+        <v>73.3</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>93.09999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>195000</v>
+        <v>222000</v>
       </c>
       <c r="G29" s="7">
         <v>19000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I29" s="7">
-        <v>14500</v>
+        <v>22600</v>
       </c>
       <c r="J29" s="5">
-        <v>74.8</v>
+        <v>73.3</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>94.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>146000</v>
+        <v>209000</v>
       </c>
       <c r="G30" s="7">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="H30" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I30" s="7">
-        <v>16600</v>
+        <v>14429</v>
       </c>
       <c r="J30" s="5">
-        <v>74.3</v>
+        <v>73.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>92.8</v>
+        <v>90.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>136000</v>
+        <v>217000</v>
       </c>
       <c r="G31" s="7">
-        <v>10000</v>
+        <v>36000</v>
       </c>
       <c r="H31" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I31" s="7">
-        <v>11833</v>
+        <v>13182</v>
       </c>
       <c r="J31" s="5">
-        <v>74</v>
+        <v>73.2</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>93.8</v>
+        <v>88.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>125000</v>
+        <v>244000</v>
       </c>
       <c r="G32" s="7">
-        <v>13000</v>
+        <v>8000</v>
       </c>
       <c r="H32" s="7">
         <v>7</v>
       </c>
       <c r="I32" s="7">
-        <v>7667</v>
+        <v>16667</v>
       </c>
       <c r="J32" s="5">
-        <v>73.5</v>
+        <v>73</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>79.7</v>
+        <v>89.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>593000</v>
+        <v>231000</v>
       </c>
       <c r="G33" s="7">
-        <v>28000</v>
+        <v>6000</v>
       </c>
       <c r="H33" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I33" s="7">
-        <v>36444</v>
+        <v>13857</v>
       </c>
       <c r="J33" s="5">
-        <v>72.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>98.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>104000</v>
+        <v>206000</v>
       </c>
       <c r="G34" s="7">
-        <v>19000</v>
+        <v>35000</v>
       </c>
       <c r="H34" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I34" s="7">
-        <v>27000</v>
+        <v>40000</v>
       </c>
       <c r="J34" s="5">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>93.5</v>
+        <v>90.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>126000</v>
+        <v>142000</v>
       </c>
       <c r="G35" s="7">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="H35" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I35" s="7">
-        <v>5333</v>
+        <v>11000</v>
       </c>
       <c r="J35" s="5">
-        <v>72.8</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>80.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>802000</v>
+        <v>199000</v>
       </c>
       <c r="G36" s="7">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H36" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>34667</v>
+        <v>16857</v>
       </c>
       <c r="J36" s="5">
-        <v>72.7</v>
+        <v>72.3</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>93.09999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>160000</v>
+        <v>178000</v>
       </c>
       <c r="G37" s="7">
-        <v>14000</v>
+        <v>5000</v>
       </c>
       <c r="H37" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I37" s="7">
-        <v>13600</v>
+        <v>12857</v>
       </c>
       <c r="J37" s="5">
-        <v>72.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>90.5</v>
+        <v>90.2</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>181000</v>
+        <v>166000</v>
       </c>
       <c r="G38" s="7">
-        <v>41000</v>
+        <v>9000</v>
       </c>
       <c r="H38" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>10900</v>
+        <v>16800</v>
       </c>
       <c r="J38" s="5">
-        <v>72.5</v>
+        <v>71.8</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>91.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>120000</v>
+        <v>108000</v>
       </c>
       <c r="G39" s="7">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="H39" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I39" s="7">
-        <v>9000</v>
+        <v>6857</v>
       </c>
       <c r="J39" s="5">
-        <v>72.5</v>
+        <v>71.7</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>87.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>209000</v>
+        <v>254000</v>
       </c>
       <c r="G40" s="7">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H40" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>16500</v>
+        <v>19400</v>
       </c>
       <c r="J40" s="5">
-        <v>72.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>86.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>215000</v>
+        <v>248000</v>
       </c>
       <c r="G41" s="7">
-        <v>11000</v>
+        <v>16000</v>
       </c>
       <c r="H41" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I41" s="7">
-        <v>18667</v>
+        <v>10286</v>
       </c>
       <c r="J41" s="5">
-        <v>72.09999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>89.7</v>
+        <v>84.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>236000</v>
+        <v>220000</v>
       </c>
       <c r="G42" s="7">
-        <v>12000</v>
+        <v>32000</v>
       </c>
       <c r="H42" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I42" s="7">
-        <v>18400</v>
+        <v>20571</v>
       </c>
       <c r="J42" s="5">
-        <v>71.90000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>90.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>208000</v>
+        <v>141000</v>
       </c>
       <c r="G43" s="7">
-        <v>13000</v>
+        <v>6000</v>
       </c>
       <c r="H43" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I43" s="7">
-        <v>6000</v>
+        <v>9143</v>
       </c>
       <c r="J43" s="5">
-        <v>71.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>94</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>157000</v>
+        <v>1023000</v>
       </c>
       <c r="G44" s="7">
-        <v>16000</v>
+        <v>44000</v>
       </c>
       <c r="H44" s="7">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="I44" s="7">
-        <v>18750</v>
+        <v>21885</v>
       </c>
       <c r="J44" s="5">
-        <v>71.40000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,23 +2079,23 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>82.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>430000</v>
+        <v>450000</v>
       </c>
       <c r="G45" s="7">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="H45" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I45" s="7">
-        <v>22111</v>
+        <v>21900</v>
       </c>
       <c r="J45" s="5">
         <v>71.09999999999999</v>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>90.09999999999999</v>
+        <v>96.3</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>324000</v>
+        <v>183000</v>
       </c>
       <c r="G46" s="7">
-        <v>43000</v>
+        <v>25000</v>
       </c>
       <c r="H46" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I46" s="7">
-        <v>38333</v>
+        <v>34000</v>
       </c>
       <c r="J46" s="5">
-        <v>71.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>91.40000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>203000</v>
+        <v>1086000</v>
       </c>
       <c r="G47" s="7">
-        <v>21000</v>
+        <v>51000</v>
       </c>
       <c r="H47" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I47" s="7">
-        <v>23500</v>
+        <v>58500</v>
       </c>
       <c r="J47" s="5">
-        <v>71.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>90.3</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>106000</v>
+        <v>342000</v>
       </c>
       <c r="G48" s="7">
-        <v>6000</v>
+        <v>25000</v>
       </c>
       <c r="H48" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>5833</v>
+        <v>18875</v>
       </c>
       <c r="J48" s="5">
-        <v>71.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>80.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>558000</v>
+        <v>755000</v>
       </c>
       <c r="G49" s="7">
-        <v>20000</v>
+        <v>78000</v>
       </c>
       <c r="H49" s="7">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="I49" s="7">
-        <v>26308</v>
+        <v>3038</v>
       </c>
       <c r="J49" s="5">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>92.5</v>
+        <v>84.7</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>677000</v>
+        <v>209000</v>
       </c>
       <c r="G50" s="7">
-        <v>101000</v>
+        <v>11000</v>
       </c>
       <c r="H50" s="7">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="I50" s="7">
-        <v>40</v>
+        <v>14833</v>
       </c>
       <c r="J50" s="5">
-        <v>70.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.59999999999999</v>
+        <v>88</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>231000</v>
+        <v>109000</v>
       </c>
       <c r="G51" s="7">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="H51" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I51" s="7">
-        <v>15167</v>
+        <v>5429</v>
       </c>
       <c r="J51" s="5">
-        <v>70.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>82.3</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>351000</v>
+        <v>348000</v>
       </c>
       <c r="G52" s="7">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="H52" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I52" s="7">
-        <v>21800</v>
+        <v>34750</v>
       </c>
       <c r="J52" s="5">
-        <v>70.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>82.2</v>
+        <v>93.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>979000</v>
+        <v>114000</v>
       </c>
       <c r="G53" s="7">
-        <v>37000</v>
+        <v>13000</v>
       </c>
       <c r="H53" s="7">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7">
-        <v>21000</v>
+        <v>13500</v>
       </c>
       <c r="J53" s="5">
-        <v>70.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>87.2</v>
+        <v>86.3</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>216000</v>
+        <v>155000</v>
       </c>
       <c r="G54" s="7">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="H54" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I54" s="7">
-        <v>10000</v>
+        <v>7857</v>
       </c>
       <c r="J54" s="5">
-        <v>70.5</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-10T05:31:39+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-11T05:25:48+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>全球修仙：只有我商城降价十亿倍</t>
   </si>
   <si>
+    <t>大一开学300斤，减一斤一个亿</t>
+  </si>
+  <si>
     <t>开局九选四，生来便是误闯天家</t>
   </si>
   <si>
-    <t>大一开学300斤，减一斤一个亿</t>
+    <t>精灵：杀穿超古代的我只想退休</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
-    <t>封神：开局反出西岐，我死守渑池</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
     <t>1955，归国带飞国家工业</t>
   </si>
   <si>
-    <t>精灵：杀穿超古代的我只想退休</t>
+    <t>法庭暴君：从反杀讹诈犯开始</t>
   </si>
   <si>
     <t>序列车队：我能无限升级奇物</t>
   </si>
   <si>
-    <t>光门连通淞户，大国倾国以赴</t>
+    <t>九叔：让你请祖师，你请雷部天将</t>
+  </si>
+  <si>
+    <t>全民副本：我能打造九九八十一难</t>
+  </si>
+  <si>
+    <t>阴阳群芳谱</t>
+  </si>
+  <si>
+    <t>名义赵瑞龙，动点脑就骂我纨绔？</t>
+  </si>
+  <si>
+    <t>莫欺老年穷：我一个铜板一年功力</t>
+  </si>
+  <si>
+    <t>开局小破店，假名媛拿丝袜来回收</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>名义：汉东怼人王，创飞所有人</t>
+  </si>
+  <si>
+    <t>三角洲：能恋与洲，谁还打职业啊</t>
+  </si>
+  <si>
+    <t>开局最弱大帝，禁区至尊被逼疯了</t>
   </si>
   <si>
     <t>大唐：我娶你姐，李世民你兴奋啥</t>
   </si>
   <si>
-    <t>全民副本：我能打造九九八十一难</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
+    <t>变妹后，我成了联盟最恶女选手</t>
+  </si>
+  <si>
+    <t>年代1958，从搬运工开始！</t>
+  </si>
+  <si>
+    <t>奥特综漫直播：什么叫人类灭绝了</t>
+  </si>
+  <si>
+    <t>大明国舅：开局赐婚徐妙云</t>
+  </si>
+  <si>
+    <t>成龙历险记，不过我是斯卡蒂</t>
+  </si>
+  <si>
+    <t>啊？我是背景通天的大佬？</t>
+  </si>
+  <si>
+    <t>我落宝金钱五五开，吓傻六圣鸿钧</t>
+  </si>
+  <si>
+    <t>年代：每日情报开局截胡女儿国王</t>
+  </si>
+  <si>
+    <t>国运求生：我的幸运值拉满了</t>
   </si>
   <si>
     <t>大明：开局政变，请洪武赴死！</t>
   </si>
   <si>
-    <t>大明第一国舅，开局治好朱雄英！</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
-  </si>
-  <si>
-    <t>大明国舅：开局赐婚徐妙云</t>
+    <t>洪荒：截教逆徒，截胡的截！</t>
+  </si>
+  <si>
+    <t>末日海上求生，开局SSS级天赋</t>
+  </si>
+  <si>
+    <t>四合院：从李云龙战友开始</t>
+  </si>
+  <si>
+    <t>我就写个网文，真没想镇压文坛啊</t>
+  </si>
+  <si>
+    <t>我合成了全世界</t>
+  </si>
+  <si>
+    <t>中奖两个亿，我在县城当豪门！</t>
+  </si>
+  <si>
+    <t>全民游戏，我每天一个新天赋</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>名义：搭档沙瑞金，让育良复婚！</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
   </si>
   <si>
     <t>我的密法天赋没有上限</t>
   </si>
   <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>莫欺老年穷：我一个铜板一年功力</t>
-  </si>
-  <si>
-    <t>啊？我是背景通天的大佬？</t>
-  </si>
-  <si>
-    <t>九叔：让你请祖师，你请雷部天将</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
-    <t>名义赵瑞龙，动点脑就骂我纨绔？</t>
-  </si>
-  <si>
-    <t>洪荒：截教逆徒，截胡的截！</t>
-  </si>
-  <si>
-    <t>出门捡垃圾，我被美女总裁强推了</t>
-  </si>
-  <si>
-    <t>成龙历险记，不过我是斯卡蒂</t>
-  </si>
-  <si>
-    <t>停下吧苏总，国家已经兜不住了！</t>
-  </si>
-  <si>
-    <t>开局最弱大帝，禁区至尊被逼疯了</t>
-  </si>
-  <si>
-    <t>末日海上求生，开局SSS级天赋</t>
-  </si>
-  <si>
-    <t>李承乾拥兵百万，三千剑仙逼宫！</t>
-  </si>
-  <si>
-    <t>法庭暴君：从反杀讹诈犯开始</t>
-  </si>
-  <si>
-    <t>国运求生：我的幸运值拉满了</t>
-  </si>
-  <si>
     <t>生子就变强！开局拿捏丰腴女帝</t>
   </si>
   <si>
-    <t>奥特综漫直播：什么叫人类灭绝了</t>
-  </si>
-  <si>
-    <t>名义：搭档沙瑞金，让育良复婚！</t>
+    <t>入狱五年，归来仍是大佬</t>
   </si>
   <si>
     <t>末世死考：开局天使魅魔三选一</t>
   </si>
   <si>
-    <t>三角洲：能恋与洲，谁还打职业啊</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>四合院：从李云龙战友开始</t>
-  </si>
-  <si>
-    <t>中奖两个亿，我在县城当豪门！</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>年代：每日情报开局截胡女儿国王</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>四合院：顶替婚姻，淮茹悔断肠！</t>
-  </si>
-  <si>
-    <t>大劫将至，从边军开始马踏天下</t>
-  </si>
-  <si>
-    <t>年代1958，从搬运工开始！</t>
-  </si>
-  <si>
-    <t>女局长：扫黑之路</t>
-  </si>
-  <si>
     <t>回到二战，我成了美国大兵</t>
+  </si>
+  <si>
+    <t>饥荒求生，国运垫底咋饱荒了？</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>89.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1028000</v>
+        <v>1098000</v>
       </c>
       <c r="G5" s="7">
-        <v>92000</v>
+        <v>70000</v>
       </c>
       <c r="H5" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>110833</v>
+        <v>105000</v>
       </c>
       <c r="J5" s="5">
-        <v>94.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>407000</v>
+        <v>467000</v>
       </c>
       <c r="G6" s="7">
-        <v>75000</v>
+        <v>60000</v>
       </c>
       <c r="H6" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="7">
-        <v>47000</v>
+        <v>48625</v>
       </c>
       <c r="J6" s="5">
-        <v>86.8</v>
+        <v>87.2</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>92.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>464000</v>
+        <v>392000</v>
       </c>
       <c r="G7" s="7">
-        <v>18000</v>
+        <v>78000</v>
       </c>
       <c r="H7" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="7">
-        <v>53286</v>
+        <v>35250</v>
       </c>
       <c r="J7" s="5">
-        <v>84.09999999999999</v>
+        <v>83.8</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>314000</v>
+        <v>474000</v>
       </c>
       <c r="G8" s="7">
-        <v>105000</v>
+        <v>10000</v>
       </c>
       <c r="H8" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="7">
-        <v>29143</v>
+        <v>47875</v>
       </c>
       <c r="J8" s="5">
-        <v>82.3</v>
+        <v>81.7</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>84.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>1942000</v>
+        <v>436000</v>
       </c>
       <c r="G9" s="7">
-        <v>52000</v>
+        <v>33000</v>
       </c>
       <c r="H9" s="7">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7">
-        <v>61269</v>
+        <v>32250</v>
       </c>
       <c r="J9" s="5">
-        <v>81.59999999999999</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>80.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>1825000</v>
+        <v>222000</v>
       </c>
       <c r="G10" s="7">
-        <v>-13000</v>
+        <v>38000</v>
       </c>
       <c r="H10" s="7">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="I10" s="7">
-        <v>66000</v>
+        <v>24143</v>
       </c>
       <c r="J10" s="5">
-        <v>80.8</v>
+        <v>81</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>100</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>184000</v>
+        <v>1835000</v>
       </c>
       <c r="G11" s="7">
-        <v>23000</v>
+        <v>10000</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="I11" s="7">
-        <v>21833</v>
+        <v>63053</v>
       </c>
       <c r="J11" s="5">
-        <v>80.5</v>
+        <v>80.8</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>97.7</v>
+        <v>82.8</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>344000</v>
+        <v>1968000</v>
       </c>
       <c r="G12" s="7">
-        <v>36000</v>
+        <v>26000</v>
       </c>
       <c r="H12" s="7">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="I12" s="7">
-        <v>26571</v>
+        <v>59963</v>
       </c>
       <c r="J12" s="5">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>93</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>403000</v>
+        <v>379000</v>
       </c>
       <c r="G13" s="7">
-        <v>19000</v>
+        <v>35000</v>
       </c>
       <c r="H13" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="7">
-        <v>32143</v>
+        <v>27625</v>
       </c>
       <c r="J13" s="5">
-        <v>79.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>183000</v>
+        <v>203000</v>
       </c>
       <c r="G14" s="7">
-        <v>28000</v>
+        <v>25000</v>
       </c>
       <c r="H14" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="7">
-        <v>15143</v>
+        <v>14375</v>
       </c>
       <c r="J14" s="5">
-        <v>78.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>96.90000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>203000</v>
+        <v>206000</v>
       </c>
       <c r="G15" s="7">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7">
-        <v>17286</v>
+        <v>16125</v>
       </c>
       <c r="J15" s="5">
-        <v>77.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>99.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>120000</v>
+        <v>204000</v>
       </c>
       <c r="G16" s="7">
-        <v>16000</v>
+        <v>42000</v>
       </c>
       <c r="H16" s="7">
         <v>5</v>
       </c>
       <c r="I16" s="7">
-        <v>24250</v>
+        <v>32250</v>
       </c>
       <c r="J16" s="5">
-        <v>75.8</v>
+        <v>78</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>93.59999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>165000</v>
+        <v>185000</v>
       </c>
       <c r="G17" s="7">
-        <v>15000</v>
+        <v>20000</v>
       </c>
       <c r="H17" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>17000</v>
+        <v>17429</v>
       </c>
       <c r="J17" s="5">
-        <v>75.7</v>
+        <v>78</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>91.59999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>407000</v>
+        <v>127000</v>
       </c>
       <c r="G18" s="7">
-        <v>17000</v>
+        <v>33000</v>
       </c>
       <c r="H18" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7">
-        <v>20000</v>
+        <v>10750</v>
       </c>
       <c r="J18" s="5">
-        <v>75.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>92.90000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>153000</v>
+        <v>245000</v>
       </c>
       <c r="G19" s="7">
-        <v>10000</v>
+        <v>23000</v>
       </c>
       <c r="H19" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>17143</v>
+        <v>22667</v>
       </c>
       <c r="J19" s="5">
-        <v>75.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>95.90000000000001</v>
+        <v>93.3</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>142000</v>
+        <v>240000</v>
       </c>
       <c r="G20" s="7">
-        <v>15000</v>
+        <v>18000</v>
       </c>
       <c r="H20" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>10571</v>
+        <v>17375</v>
       </c>
       <c r="J20" s="5">
-        <v>75.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>90.40000000000001</v>
+        <v>97.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>602000</v>
+        <v>218000</v>
       </c>
       <c r="G21" s="7">
-        <v>9000</v>
+        <v>65000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I21" s="7">
-        <v>22000</v>
+        <v>51500</v>
       </c>
       <c r="J21" s="5">
-        <v>75.2</v>
+        <v>75.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>92</v>
+        <v>82.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>156000</v>
+        <v>666000</v>
       </c>
       <c r="G22" s="7">
-        <v>10000</v>
+        <v>39000</v>
       </c>
       <c r="H22" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I22" s="7">
-        <v>15500</v>
+        <v>36455</v>
       </c>
       <c r="J22" s="5">
-        <v>74.5</v>
+        <v>74.7</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>92.8</v>
+        <v>90.3</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>172000</v>
+        <v>610000</v>
       </c>
       <c r="G23" s="7">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I23" s="7">
-        <v>13333</v>
+        <v>20250</v>
       </c>
       <c r="J23" s="5">
-        <v>74.40000000000001</v>
+        <v>74.7</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>82.2</v>
+        <v>90.7</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>627000</v>
+        <v>421000</v>
       </c>
       <c r="G24" s="7">
-        <v>34000</v>
+        <v>14000</v>
       </c>
       <c r="H24" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I24" s="7">
-        <v>36200</v>
+        <v>19250</v>
       </c>
       <c r="J24" s="5">
-        <v>74.3</v>
+        <v>74.7</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,23 +1419,23 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>90.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>222000</v>
+        <v>153000</v>
       </c>
       <c r="G25" s="7">
         <v>12000</v>
       </c>
       <c r="H25" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I25" s="7">
-        <v>17286</v>
+        <v>9500</v>
       </c>
       <c r="J25" s="5">
         <v>74.3</v>
@@ -1452,23 +1452,23 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>94.40000000000001</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>140000</v>
+        <v>232000</v>
       </c>
       <c r="G26" s="7">
-        <v>15000</v>
+        <v>26000</v>
       </c>
       <c r="H26" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I26" s="7">
-        <v>8714</v>
+        <v>35333</v>
       </c>
       <c r="J26" s="5">
         <v>74.09999999999999</v>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>99.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>162000</v>
+        <v>129000</v>
       </c>
       <c r="G27" s="7">
-        <v>30000</v>
+        <v>9000</v>
       </c>
       <c r="H27" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I27" s="7">
-        <v>29000</v>
+        <v>21200</v>
       </c>
       <c r="J27" s="5">
-        <v>73.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>89.8</v>
+        <v>98</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>346000</v>
+        <v>124000</v>
       </c>
       <c r="G28" s="7">
-        <v>7000</v>
+        <v>21000</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I28" s="7">
-        <v>15571</v>
+        <v>19000</v>
       </c>
       <c r="J28" s="5">
-        <v>73.3</v>
+        <v>73.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>222000</v>
+        <v>377000</v>
       </c>
       <c r="G29" s="7">
-        <v>19000</v>
+        <v>29000</v>
       </c>
       <c r="H29" s="7">
         <v>6</v>
       </c>
       <c r="I29" s="7">
-        <v>22600</v>
+        <v>33600</v>
       </c>
       <c r="J29" s="5">
-        <v>73.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>90.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>209000</v>
+        <v>260000</v>
       </c>
       <c r="G30" s="7">
-        <v>14000</v>
+        <v>6000</v>
       </c>
       <c r="H30" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I30" s="7">
-        <v>14429</v>
+        <v>17167</v>
       </c>
       <c r="J30" s="5">
-        <v>73.3</v>
+        <v>73</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>90.8</v>
+        <v>89.7</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>217000</v>
+        <v>163000</v>
       </c>
       <c r="G31" s="7">
-        <v>36000</v>
+        <v>7000</v>
       </c>
       <c r="H31" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I31" s="7">
-        <v>13182</v>
+        <v>14286</v>
       </c>
       <c r="J31" s="5">
-        <v>73.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>88.7</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>244000</v>
+        <v>252000</v>
       </c>
       <c r="G32" s="7">
         <v>8000</v>
       </c>
       <c r="H32" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>16667</v>
+        <v>15429</v>
       </c>
       <c r="J32" s="5">
-        <v>73</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>89.5</v>
+        <v>91.3</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>231000</v>
+        <v>151000</v>
       </c>
       <c r="G33" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H33" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I33" s="7">
-        <v>13857</v>
+        <v>9000</v>
       </c>
       <c r="J33" s="5">
-        <v>72.7</v>
+        <v>72.5</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>97.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>206000</v>
+        <v>152000</v>
       </c>
       <c r="G34" s="7">
-        <v>35000</v>
+        <v>14000</v>
       </c>
       <c r="H34" s="7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I34" s="7">
-        <v>40000</v>
+        <v>9714</v>
       </c>
       <c r="J34" s="5">
-        <v>72.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>90.2</v>
+        <v>85</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>142000</v>
+        <v>372000</v>
       </c>
       <c r="G35" s="7">
-        <v>6000</v>
+        <v>30000</v>
       </c>
       <c r="H35" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I35" s="7">
-        <v>11000</v>
+        <v>20111</v>
       </c>
       <c r="J35" s="5">
-        <v>72.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>87.5</v>
+        <v>87.3</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>199000</v>
+        <v>172000</v>
       </c>
       <c r="G36" s="7">
-        <v>2000</v>
+        <v>6000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I36" s="7">
-        <v>16857</v>
+        <v>15000</v>
       </c>
       <c r="J36" s="5">
-        <v>72.3</v>
+        <v>71.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,23 +1815,23 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>88.3</v>
+        <v>87.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>178000</v>
+        <v>155000</v>
       </c>
       <c r="G37" s="7">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="H37" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I37" s="7">
-        <v>12857</v>
+        <v>15250</v>
       </c>
       <c r="J37" s="5">
         <v>71.8</v>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>90.2</v>
+        <v>87.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>166000</v>
+        <v>218000</v>
       </c>
       <c r="G38" s="7">
         <v>9000</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I38" s="7">
-        <v>16800</v>
+        <v>13750</v>
       </c>
       <c r="J38" s="5">
-        <v>71.8</v>
+        <v>71.7</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,23 +1881,23 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>90.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>108000</v>
+        <v>148000</v>
       </c>
       <c r="G39" s="7">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H39" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I39" s="7">
-        <v>6857</v>
+        <v>10375</v>
       </c>
       <c r="J39" s="5">
         <v>71.7</v>
@@ -1914,23 +1914,23 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>88.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>254000</v>
+        <v>474000</v>
       </c>
       <c r="G40" s="7">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="H40" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I40" s="7">
-        <v>19400</v>
+        <v>22091</v>
       </c>
       <c r="J40" s="5">
         <v>71.59999999999999</v>
@@ -1947,23 +1947,23 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>88.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>248000</v>
+        <v>461000</v>
       </c>
       <c r="G41" s="7">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="H41" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I41" s="7">
-        <v>10286</v>
+        <v>32167</v>
       </c>
       <c r="J41" s="5">
         <v>71.5</v>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>84.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>220000</v>
+        <v>520000</v>
       </c>
       <c r="G42" s="7">
-        <v>32000</v>
+        <v>45000</v>
       </c>
       <c r="H42" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I42" s="7">
-        <v>20571</v>
+        <v>47000</v>
       </c>
       <c r="J42" s="5">
-        <v>71.5</v>
+        <v>71.3</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>89.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>141000</v>
+        <v>206000</v>
       </c>
       <c r="G43" s="7">
-        <v>6000</v>
+        <v>23000</v>
       </c>
       <c r="H43" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I43" s="7">
-        <v>9143</v>
+        <v>30333</v>
       </c>
       <c r="J43" s="5">
-        <v>71.5</v>
+        <v>71.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>82.90000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>1023000</v>
+        <v>118000</v>
       </c>
       <c r="G44" s="7">
-        <v>44000</v>
+        <v>27000</v>
       </c>
       <c r="H44" s="7">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="I44" s="7">
-        <v>21885</v>
+        <v>25000</v>
       </c>
       <c r="J44" s="5">
-        <v>71.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,23 +2079,23 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>82.90000000000001</v>
+        <v>83.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>450000</v>
+        <v>1125000</v>
       </c>
       <c r="G45" s="7">
-        <v>20000</v>
+        <v>39000</v>
       </c>
       <c r="H45" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
-        <v>21900</v>
+        <v>52000</v>
       </c>
       <c r="J45" s="5">
         <v>71.09999999999999</v>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>96.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>183000</v>
+        <v>1065000</v>
       </c>
       <c r="G46" s="7">
-        <v>25000</v>
+        <v>42000</v>
       </c>
       <c r="H46" s="7">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="I46" s="7">
-        <v>34000</v>
+        <v>22630</v>
       </c>
       <c r="J46" s="5">
-        <v>70.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>85.09999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>1086000</v>
+        <v>260000</v>
       </c>
       <c r="G47" s="7">
-        <v>51000</v>
+        <v>12000</v>
       </c>
       <c r="H47" s="7">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
-        <v>58500</v>
+        <v>10500</v>
       </c>
       <c r="J47" s="5">
-        <v>70.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,7 +2178,7 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>83.09999999999999</v>
+        <v>85.7</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
@@ -2188,13 +2188,13 @@
         <v>342000</v>
       </c>
       <c r="G48" s="7">
-        <v>25000</v>
+        <v>-4000</v>
       </c>
       <c r="H48" s="7">
         <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>18875</v>
+        <v>13125</v>
       </c>
       <c r="J48" s="5">
         <v>70.40000000000001</v>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>90.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>755000</v>
+        <v>175000</v>
       </c>
       <c r="G49" s="7">
-        <v>78000</v>
+        <v>3000</v>
       </c>
       <c r="H49" s="7">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="I49" s="7">
-        <v>3038</v>
+        <v>11857</v>
       </c>
       <c r="J49" s="5">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>84.7</v>
+        <v>88.5</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>209000</v>
+        <v>115000</v>
       </c>
       <c r="G50" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H50" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I50" s="7">
-        <v>14833</v>
+        <v>6875</v>
       </c>
       <c r="J50" s="5">
-        <v>70.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>88</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>109000</v>
+        <v>127000</v>
       </c>
       <c r="G51" s="7">
-        <v>3000</v>
+        <v>25000</v>
       </c>
       <c r="H51" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I51" s="7">
-        <v>5429</v>
+        <v>13800</v>
       </c>
       <c r="J51" s="5">
-        <v>69.8</v>
+        <v>70.3</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>83.40000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>348000</v>
+        <v>245000</v>
       </c>
       <c r="G52" s="7">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="H52" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I52" s="7">
-        <v>34750</v>
+        <v>21125</v>
       </c>
       <c r="J52" s="5">
-        <v>69.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>93.2</v>
+        <v>87.8</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>114000</v>
+        <v>159000</v>
       </c>
       <c r="G53" s="7">
-        <v>13000</v>
+        <v>4000</v>
       </c>
       <c r="H53" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I53" s="7">
-        <v>13500</v>
+        <v>7375</v>
       </c>
       <c r="J53" s="5">
-        <v>69.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>86.3</v>
+        <v>88.7</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>155000</v>
+        <v>134000</v>
       </c>
       <c r="G54" s="7">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H54" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I54" s="7">
-        <v>7857</v>
+        <v>5000</v>
       </c>
       <c r="J54" s="5">
-        <v>69.40000000000001</v>
+        <v>70</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-11T05:25:48+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-12T05:37:46+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -82,145 +82,145 @@
     <t>大一开学300斤，减一斤一个亿</t>
   </si>
   <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>封神：开局反出西岐，我死守渑池</t>
+  </si>
+  <si>
+    <t>精灵：杀穿超古代的我只想退休</t>
+  </si>
+  <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
     <t>开局九选四，生来便是误闯天家</t>
   </si>
   <si>
-    <t>精灵：杀穿超古代的我只想退休</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>封神：开局反出西岐，我死守渑池</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
     <t>1955，归国带飞国家工业</t>
   </si>
   <si>
+    <t>九叔：让你请祖师，你请雷部天将</t>
+  </si>
+  <si>
     <t>法庭暴君：从反杀讹诈犯开始</t>
   </si>
   <si>
+    <t>开局小破店，假名媛拿丝袜来回收</t>
+  </si>
+  <si>
+    <t>开局最弱大帝，禁区至尊被逼疯了</t>
+  </si>
+  <si>
+    <t>阴阳群芳谱</t>
+  </si>
+  <si>
+    <t>变妹后，我成了联盟最恶女选手</t>
+  </si>
+  <si>
+    <t>高武：看不起斩魄刀，流刃若火呢</t>
+  </si>
+  <si>
+    <t>我就写个网文，真没想镇压文坛啊</t>
+  </si>
+  <si>
+    <t>什么叫我成了灭世级怪谈？</t>
+  </si>
+  <si>
+    <t>名义赵瑞龙，动点脑就骂我纨绔？</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>年代1958，从搬运工开始！</t>
+  </si>
+  <si>
     <t>序列车队：我能无限升级奇物</t>
   </si>
   <si>
-    <t>九叔：让你请祖师，你请雷部天将</t>
-  </si>
-  <si>
     <t>全民副本：我能打造九九八十一难</t>
   </si>
   <si>
-    <t>阴阳群芳谱</t>
-  </si>
-  <si>
-    <t>名义赵瑞龙，动点脑就骂我纨绔？</t>
+    <t>大唐：我娶你姐，李世民你兴奋啥</t>
+  </si>
+  <si>
+    <t>你管这叫警察？重炮都架租界口了</t>
+  </si>
+  <si>
+    <t>全民游戏，我每天一个新天赋</t>
+  </si>
+  <si>
+    <t>我落宝金钱五五开，吓傻六圣鸿钧</t>
   </si>
   <si>
     <t>莫欺老年穷：我一个铜板一年功力</t>
   </si>
   <si>
-    <t>开局小破店，假名媛拿丝袜来回收</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
+    <t>重回70美女班长跟我下乡</t>
+  </si>
+  <si>
+    <t>大明国舅：开局赐婚徐妙云</t>
+  </si>
+  <si>
+    <t>三角洲：能恋与洲，谁还打职业啊</t>
+  </si>
+  <si>
+    <t>我合成了全世界</t>
+  </si>
+  <si>
+    <t>啊？我是背景通天的大佬？</t>
   </si>
   <si>
     <t>名义：汉东怼人王，创飞所有人</t>
   </si>
   <si>
-    <t>三角洲：能恋与洲，谁还打职业啊</t>
-  </si>
-  <si>
-    <t>开局最弱大帝，禁区至尊被逼疯了</t>
-  </si>
-  <si>
-    <t>大唐：我娶你姐，李世民你兴奋啥</t>
-  </si>
-  <si>
-    <t>变妹后，我成了联盟最恶女选手</t>
-  </si>
-  <si>
-    <t>年代1958，从搬运工开始！</t>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>年代：每日情报开局截胡女儿国王</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
+    <t>中奖两个亿，我在县城当豪门！</t>
+  </si>
+  <si>
+    <t>大明：开局政变，请洪武赴死！</t>
   </si>
   <si>
     <t>奥特综漫直播：什么叫人类灭绝了</t>
   </si>
   <si>
-    <t>大明国舅：开局赐婚徐妙云</t>
-  </si>
-  <si>
-    <t>成龙历险记，不过我是斯卡蒂</t>
-  </si>
-  <si>
-    <t>啊？我是背景通天的大佬？</t>
-  </si>
-  <si>
-    <t>我落宝金钱五五开，吓傻六圣鸿钧</t>
-  </si>
-  <si>
-    <t>年代：每日情报开局截胡女儿国王</t>
+    <t>绝症留洋归乡？举国哭求我别死！</t>
   </si>
   <si>
     <t>国运求生：我的幸运值拉满了</t>
   </si>
   <si>
-    <t>大明：开局政变，请洪武赴死！</t>
-  </si>
-  <si>
-    <t>洪荒：截教逆徒，截胡的截！</t>
-  </si>
-  <si>
-    <t>末日海上求生，开局SSS级天赋</t>
-  </si>
-  <si>
-    <t>四合院：从李云龙战友开始</t>
-  </si>
-  <si>
-    <t>我就写个网文，真没想镇压文坛啊</t>
-  </si>
-  <si>
-    <t>我合成了全世界</t>
-  </si>
-  <si>
-    <t>中奖两个亿，我在县城当豪门！</t>
-  </si>
-  <si>
-    <t>全民游戏，我每天一个新天赋</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
+    <t>末世死考：开局天使魅魔三选一</t>
+  </si>
+  <si>
+    <t>名义：搭档沙瑞金，让育良复婚！</t>
+  </si>
+  <si>
+    <t>出门捡垃圾，我被美女总裁强推了</t>
+  </si>
+  <si>
+    <t>厉鬼，我真要适应你了！</t>
+  </si>
+  <si>
+    <t>双世：从冰灵根开始伪装天骄</t>
+  </si>
+  <si>
+    <t>回到二战，我成了美国大兵</t>
   </si>
   <si>
     <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>名义：搭档沙瑞金，让育良复婚！</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
-    <t>我的密法天赋没有上限</t>
-  </si>
-  <si>
-    <t>生子就变强！开局拿捏丰腴女帝</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
-  </si>
-  <si>
-    <t>末世死考：开局天使魅魔三选一</t>
-  </si>
-  <si>
-    <t>回到二战，我成了美国大兵</t>
-  </si>
-  <si>
-    <t>饥荒求生，国运垫底咋饱荒了？</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1098000</v>
+        <v>1172000</v>
       </c>
       <c r="G5" s="7">
-        <v>70000</v>
+        <v>74000</v>
       </c>
       <c r="H5" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="7">
-        <v>105000</v>
+        <v>101125</v>
       </c>
       <c r="J5" s="5">
-        <v>92.8</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>97.3</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>467000</v>
+        <v>508000</v>
       </c>
       <c r="G6" s="7">
-        <v>60000</v>
+        <v>41000</v>
       </c>
       <c r="H6" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I6" s="7">
-        <v>48625</v>
+        <v>47778</v>
       </c>
       <c r="J6" s="5">
-        <v>87.2</v>
+        <v>85.5</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -832,19 +832,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>392000</v>
+        <v>478000</v>
       </c>
       <c r="G7" s="7">
-        <v>78000</v>
+        <v>86000</v>
       </c>
       <c r="H7" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7">
-        <v>35250</v>
+        <v>40889</v>
       </c>
       <c r="J7" s="5">
-        <v>83.8</v>
+        <v>85.2</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>90.5</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>474000</v>
+        <v>275000</v>
       </c>
       <c r="G8" s="7">
-        <v>10000</v>
+        <v>53000</v>
       </c>
       <c r="H8" s="7">
         <v>9</v>
       </c>
       <c r="I8" s="7">
-        <v>47875</v>
+        <v>27750</v>
       </c>
       <c r="J8" s="5">
-        <v>81.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>96.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>436000</v>
+        <v>1873000</v>
       </c>
       <c r="G9" s="7">
-        <v>33000</v>
+        <v>38000</v>
       </c>
       <c r="H9" s="7">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="I9" s="7">
-        <v>32250</v>
+        <v>61800</v>
       </c>
       <c r="J9" s="5">
-        <v>81.09999999999999</v>
+        <v>81.3</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,23 +924,23 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>96.2</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>222000</v>
+        <v>470000</v>
       </c>
       <c r="G10" s="7">
-        <v>38000</v>
+        <v>34000</v>
       </c>
       <c r="H10" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I10" s="7">
-        <v>24143</v>
+        <v>32444</v>
       </c>
       <c r="J10" s="5">
         <v>81</v>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>81.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>1835000</v>
+        <v>2011000</v>
       </c>
       <c r="G11" s="7">
-        <v>10000</v>
+        <v>43000</v>
       </c>
       <c r="H11" s="7">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="I11" s="7">
-        <v>63053</v>
+        <v>59357</v>
       </c>
       <c r="J11" s="5">
-        <v>80.8</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>82.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>1968000</v>
+        <v>485000</v>
       </c>
       <c r="G12" s="7">
-        <v>26000</v>
+        <v>11000</v>
       </c>
       <c r="H12" s="7">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>59963</v>
+        <v>43778</v>
       </c>
       <c r="J12" s="5">
-        <v>80.5</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>96.40000000000001</v>
+        <v>96.2</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>379000</v>
+        <v>416000</v>
       </c>
       <c r="G13" s="7">
-        <v>35000</v>
+        <v>37000</v>
       </c>
       <c r="H13" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I13" s="7">
-        <v>27625</v>
+        <v>28667</v>
       </c>
       <c r="J13" s="5">
-        <v>79.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>99.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>203000</v>
+        <v>231000</v>
       </c>
       <c r="G14" s="7">
-        <v>25000</v>
+        <v>27000</v>
       </c>
       <c r="H14" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>14375</v>
+        <v>31200</v>
       </c>
       <c r="J14" s="5">
-        <v>78.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>98.3</v>
+        <v>100</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>206000</v>
+        <v>240000</v>
       </c>
       <c r="G15" s="7">
-        <v>23000</v>
+        <v>37000</v>
       </c>
       <c r="H15" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I15" s="7">
-        <v>16125</v>
+        <v>16889</v>
       </c>
       <c r="J15" s="5">
-        <v>78.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>99.90000000000001</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>204000</v>
+        <v>263000</v>
       </c>
       <c r="G16" s="7">
-        <v>42000</v>
+        <v>45000</v>
       </c>
       <c r="H16" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7">
-        <v>32250</v>
+        <v>49333</v>
       </c>
       <c r="J16" s="5">
-        <v>78</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>97.59999999999999</v>
+        <v>99.7</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>185000</v>
+        <v>265000</v>
       </c>
       <c r="G17" s="7">
-        <v>20000</v>
+        <v>33000</v>
       </c>
       <c r="H17" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I17" s="7">
-        <v>17429</v>
+        <v>34750</v>
       </c>
       <c r="J17" s="5">
-        <v>78</v>
+        <v>78.5</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>98.90000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>127000</v>
+        <v>150000</v>
       </c>
       <c r="G18" s="7">
-        <v>33000</v>
+        <v>23000</v>
       </c>
       <c r="H18" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="7">
-        <v>10750</v>
+        <v>12111</v>
       </c>
       <c r="J18" s="5">
-        <v>77.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>91.5</v>
+        <v>99.2</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>245000</v>
+        <v>147000</v>
       </c>
       <c r="G19" s="7">
         <v>23000</v>
       </c>
       <c r="H19" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I19" s="7">
-        <v>22667</v>
+        <v>19800</v>
       </c>
       <c r="J19" s="5">
-        <v>76</v>
+        <v>77.5</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>93.3</v>
+        <v>85.5</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>240000</v>
+        <v>609000</v>
       </c>
       <c r="G20" s="7">
-        <v>18000</v>
+        <v>79000</v>
       </c>
       <c r="H20" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I20" s="7">
-        <v>17375</v>
+        <v>41556</v>
       </c>
       <c r="J20" s="5">
-        <v>75.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>97.5</v>
+        <v>86</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>218000</v>
+        <v>526000</v>
       </c>
       <c r="G21" s="7">
         <v>65000</v>
       </c>
       <c r="H21" s="7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>51500</v>
+        <v>36857</v>
       </c>
       <c r="J21" s="5">
-        <v>75.5</v>
+        <v>76.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>82.8</v>
+        <v>92.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>666000</v>
+        <v>633000</v>
       </c>
       <c r="G22" s="7">
-        <v>39000</v>
+        <v>23000</v>
       </c>
       <c r="H22" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I22" s="7">
-        <v>36455</v>
+        <v>20556</v>
       </c>
       <c r="J22" s="5">
-        <v>74.7</v>
+        <v>76.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>90.3</v>
+        <v>91.5</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>610000</v>
+        <v>268000</v>
       </c>
       <c r="G23" s="7">
-        <v>8000</v>
+        <v>23000</v>
       </c>
       <c r="H23" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I23" s="7">
-        <v>20250</v>
+        <v>22714</v>
       </c>
       <c r="J23" s="5">
-        <v>74.7</v>
+        <v>76</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>90.7</v>
+        <v>84.5</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>421000</v>
+        <v>712000</v>
       </c>
       <c r="G24" s="7">
-        <v>14000</v>
+        <v>46000</v>
       </c>
       <c r="H24" s="7">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="I24" s="7">
-        <v>19250</v>
+        <v>37250</v>
       </c>
       <c r="J24" s="5">
-        <v>74.7</v>
+        <v>75.8</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>94.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>153000</v>
+        <v>410000</v>
       </c>
       <c r="G25" s="7">
-        <v>12000</v>
+        <v>33000</v>
       </c>
       <c r="H25" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>9500</v>
+        <v>33500</v>
       </c>
       <c r="J25" s="5">
-        <v>74.3</v>
+        <v>75.7</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>96.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>232000</v>
+        <v>222000</v>
       </c>
       <c r="G26" s="7">
-        <v>26000</v>
+        <v>16000</v>
       </c>
       <c r="H26" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I26" s="7">
-        <v>35333</v>
+        <v>16111</v>
       </c>
       <c r="J26" s="5">
-        <v>74.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>92.2</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>129000</v>
+        <v>196000</v>
       </c>
       <c r="G27" s="7">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="H27" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I27" s="7">
-        <v>21200</v>
+        <v>16625</v>
       </c>
       <c r="J27" s="5">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>98</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>124000</v>
+        <v>137000</v>
       </c>
       <c r="G28" s="7">
-        <v>21000</v>
+        <v>8000</v>
       </c>
       <c r="H28" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
         <v>19000</v>
       </c>
       <c r="J28" s="5">
-        <v>73.7</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>85.40000000000001</v>
+        <v>90.2</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>377000</v>
+        <v>234000</v>
       </c>
       <c r="G29" s="7">
-        <v>29000</v>
+        <v>35000</v>
       </c>
       <c r="H29" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>33600</v>
+        <v>20667</v>
       </c>
       <c r="J29" s="5">
-        <v>73.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>88.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>260000</v>
+        <v>141000</v>
       </c>
       <c r="G30" s="7">
-        <v>6000</v>
+        <v>23000</v>
       </c>
       <c r="H30" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>17167</v>
+        <v>24500</v>
       </c>
       <c r="J30" s="5">
-        <v>73</v>
+        <v>74.7</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>89.7</v>
+        <v>94.3</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>163000</v>
+        <v>172000</v>
       </c>
       <c r="G31" s="7">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="H31" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="7">
-        <v>14286</v>
+        <v>11000</v>
       </c>
       <c r="J31" s="5">
-        <v>72.90000000000001</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>88.59999999999999</v>
+        <v>91.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>252000</v>
+        <v>256000</v>
       </c>
       <c r="G32" s="7">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="H32" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I32" s="7">
-        <v>15429</v>
+        <v>17222</v>
       </c>
       <c r="J32" s="5">
-        <v>72.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>91.3</v>
+        <v>95.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>151000</v>
+        <v>103000</v>
       </c>
       <c r="G33" s="7">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="H33" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I33" s="7">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="J33" s="5">
-        <v>72.5</v>
+        <v>74.2</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>90.2</v>
+        <v>91.5</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>152000</v>
+        <v>173000</v>
       </c>
       <c r="G34" s="7">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="H34" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34" s="7">
-        <v>9714</v>
+        <v>13750</v>
       </c>
       <c r="J34" s="5">
-        <v>72</v>
+        <v>73.8</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>85</v>
+        <v>93.3</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>372000</v>
+        <v>164000</v>
       </c>
       <c r="G35" s="7">
-        <v>30000</v>
+        <v>11000</v>
       </c>
       <c r="H35" s="7">
         <v>10</v>
       </c>
       <c r="I35" s="7">
-        <v>20111</v>
+        <v>9667</v>
       </c>
       <c r="J35" s="5">
-        <v>71.8</v>
+        <v>73.7</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>87.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>172000</v>
+        <v>563000</v>
       </c>
       <c r="G36" s="7">
-        <v>6000</v>
+        <v>43000</v>
       </c>
       <c r="H36" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I36" s="7">
-        <v>15000</v>
+        <v>46000</v>
       </c>
       <c r="J36" s="5">
-        <v>71.8</v>
+        <v>73.5</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>87.3</v>
+        <v>93</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>155000</v>
+        <v>164000</v>
       </c>
       <c r="G37" s="7">
-        <v>2000</v>
+        <v>13000</v>
       </c>
       <c r="H37" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I37" s="7">
-        <v>15250</v>
+        <v>9444</v>
       </c>
       <c r="J37" s="5">
-        <v>71.8</v>
+        <v>73.5</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>87.7</v>
+        <v>88.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>218000</v>
+        <v>427000</v>
       </c>
       <c r="G38" s="7">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H38" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I38" s="7">
-        <v>13750</v>
+        <v>17778</v>
       </c>
       <c r="J38" s="5">
-        <v>71.7</v>
+        <v>73.2</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>89.2</v>
+        <v>90.7</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>148000</v>
+        <v>355000</v>
       </c>
       <c r="G39" s="7">
-        <v>6000</v>
+        <v>13000</v>
       </c>
       <c r="H39" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I39" s="7">
-        <v>10375</v>
+        <v>13111</v>
       </c>
       <c r="J39" s="5">
-        <v>71.7</v>
+        <v>73.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>83.7</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>474000</v>
+        <v>410000</v>
       </c>
       <c r="G40" s="7">
-        <v>24000</v>
+        <v>38000</v>
       </c>
       <c r="H40" s="7">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I40" s="7">
-        <v>22091</v>
+        <v>21900</v>
       </c>
       <c r="J40" s="5">
-        <v>71.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>79</v>
+        <v>83.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>461000</v>
+        <v>1161000</v>
       </c>
       <c r="G41" s="7">
-        <v>35000</v>
+        <v>36000</v>
       </c>
       <c r="H41" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>32167</v>
+        <v>48000</v>
       </c>
       <c r="J41" s="5">
-        <v>71.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>86.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>520000</v>
+        <v>151000</v>
       </c>
       <c r="G42" s="7">
-        <v>45000</v>
+        <v>24000</v>
       </c>
       <c r="H42" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>47000</v>
+        <v>15500</v>
       </c>
       <c r="J42" s="5">
-        <v>71.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>94.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>206000</v>
+        <v>226000</v>
       </c>
       <c r="G43" s="7">
-        <v>23000</v>
+        <v>20000</v>
       </c>
       <c r="H43" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43" s="7">
-        <v>30333</v>
+        <v>27750</v>
       </c>
       <c r="J43" s="5">
-        <v>71.3</v>
+        <v>72.7</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>96.2</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>118000</v>
+        <v>159000</v>
       </c>
       <c r="G44" s="7">
-        <v>27000</v>
+        <v>4000</v>
       </c>
       <c r="H44" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I44" s="7">
-        <v>25000</v>
+        <v>14000</v>
       </c>
       <c r="J44" s="5">
-        <v>71.2</v>
+        <v>72.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>83.8</v>
+        <v>87.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>1125000</v>
+        <v>264000</v>
       </c>
       <c r="G45" s="7">
-        <v>39000</v>
+        <v>4000</v>
       </c>
       <c r="H45" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I45" s="7">
-        <v>52000</v>
+        <v>15286</v>
       </c>
       <c r="J45" s="5">
-        <v>71.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>82.59999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>1065000</v>
+        <v>195000</v>
       </c>
       <c r="G46" s="7">
-        <v>42000</v>
+        <v>22000</v>
       </c>
       <c r="H46" s="7">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="I46" s="7">
-        <v>22630</v>
+        <v>23250</v>
       </c>
       <c r="J46" s="5">
-        <v>71.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>87.7</v>
+        <v>88.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>260000</v>
+        <v>177000</v>
       </c>
       <c r="G47" s="7">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="H47" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I47" s="7">
-        <v>10500</v>
+        <v>13571</v>
       </c>
       <c r="J47" s="5">
-        <v>70.90000000000001</v>
+        <v>72</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>85.7</v>
+        <v>84</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>342000</v>
+        <v>278000</v>
       </c>
       <c r="G48" s="7">
-        <v>-4000</v>
+        <v>33000</v>
       </c>
       <c r="H48" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I48" s="7">
-        <v>13125</v>
+        <v>22444</v>
       </c>
       <c r="J48" s="5">
-        <v>70.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>86.3</v>
+        <v>89.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>175000</v>
+        <v>276000</v>
       </c>
       <c r="G49" s="7">
-        <v>3000</v>
+        <v>16000</v>
       </c>
       <c r="H49" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I49" s="7">
-        <v>11857</v>
+        <v>11111</v>
       </c>
       <c r="J49" s="5">
-        <v>70.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>88.5</v>
+        <v>87</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>115000</v>
+        <v>257000</v>
       </c>
       <c r="G50" s="7">
-        <v>7000</v>
+        <v>25000</v>
       </c>
       <c r="H50" s="7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I50" s="7">
-        <v>6875</v>
+        <v>14231</v>
       </c>
       <c r="J50" s="5">
-        <v>70.40000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>88.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>127000</v>
+        <v>123000</v>
       </c>
       <c r="G51" s="7">
-        <v>25000</v>
+        <v>10000</v>
       </c>
       <c r="H51" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I51" s="7">
-        <v>13800</v>
+        <v>2556</v>
       </c>
       <c r="J51" s="5">
-        <v>70.3</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>81.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>245000</v>
+        <v>174000</v>
       </c>
       <c r="G52" s="7">
-        <v>25000</v>
+        <v>16000</v>
       </c>
       <c r="H52" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I52" s="7">
-        <v>21125</v>
+        <v>17750</v>
       </c>
       <c r="J52" s="5">
-        <v>70.2</v>
+        <v>71</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>87.8</v>
+        <v>89.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>159000</v>
+        <v>164000</v>
       </c>
       <c r="G53" s="7">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H53" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I53" s="7">
-        <v>7375</v>
+        <v>7111</v>
       </c>
       <c r="J53" s="5">
-        <v>70.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>88.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>134000</v>
+        <v>1098000</v>
       </c>
       <c r="G54" s="7">
-        <v>6000</v>
+        <v>33000</v>
       </c>
       <c r="H54" s="7">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="I54" s="7">
-        <v>5000</v>
+        <v>23000</v>
       </c>
       <c r="J54" s="5">
-        <v>70</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-12T05:37:46+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-13T06:32:35+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
-    <t>全球修仙：只有我商城降价十亿倍</t>
-  </si>
-  <si>
-    <t>大一开学300斤，减一斤一个亿</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
+    <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
     <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
-    <t>精灵：杀穿超古代的我只想退休</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>开局九选四，生来便是误闯天家</t>
-  </si>
-  <si>
-    <t>1955，归国带飞国家工业</t>
-  </si>
-  <si>
-    <t>九叔：让你请祖师，你请雷部天将</t>
-  </si>
-  <si>
-    <t>法庭暴君：从反杀讹诈犯开始</t>
-  </si>
-  <si>
-    <t>开局小破店，假名媛拿丝袜来回收</t>
-  </si>
-  <si>
-    <t>开局最弱大帝，禁区至尊被逼疯了</t>
-  </si>
-  <si>
-    <t>阴阳群芳谱</t>
-  </si>
-  <si>
-    <t>变妹后，我成了联盟最恶女选手</t>
+    <t>我合成了全世界</t>
+  </si>
+  <si>
+    <t>我就写个网文，真没想镇压文坛啊</t>
   </si>
   <si>
     <t>高武：看不起斩魄刀，流刃若火呢</t>
   </si>
   <si>
-    <t>我就写个网文，真没想镇压文坛啊</t>
-  </si>
-  <si>
-    <t>什么叫我成了灭世级怪谈？</t>
-  </si>
-  <si>
-    <t>名义赵瑞龙，动点脑就骂我纨绔？</t>
+    <t>你管这叫警察？重炮都架租界口了</t>
   </si>
   <si>
     <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
     <t>年代1958，从搬运工开始！</t>
   </si>
   <si>
-    <t>序列车队：我能无限升级奇物</t>
-  </si>
-  <si>
-    <t>全民副本：我能打造九九八十一难</t>
-  </si>
-  <si>
-    <t>大唐：我娶你姐，李世民你兴奋啥</t>
-  </si>
-  <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>全民游戏，我每天一个新天赋</t>
-  </si>
-  <si>
-    <t>我落宝金钱五五开，吓傻六圣鸿钧</t>
-  </si>
-  <si>
-    <t>莫欺老年穷：我一个铜板一年功力</t>
-  </si>
-  <si>
-    <t>重回70美女班长跟我下乡</t>
-  </si>
-  <si>
-    <t>大明国舅：开局赐婚徐妙云</t>
-  </si>
-  <si>
-    <t>三角洲：能恋与洲，谁还打职业啊</t>
-  </si>
-  <si>
-    <t>我合成了全世界</t>
-  </si>
-  <si>
-    <t>啊？我是背景通天的大佬？</t>
-  </si>
-  <si>
-    <t>名义：汉东怼人王，创飞所有人</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
+    <t>我靠风水中医术，养活六个妹妹</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
+    <t>伪人降临！我是全场唯一预言家</t>
+  </si>
+  <si>
+    <t>出门捡垃圾，我被美女总裁强推了</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>末世死考：开局天使魅魔三选一</t>
+  </si>
+  <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
     <t>年代：每日情报开局截胡女儿国王</t>
   </si>
   <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
-  </si>
-  <si>
-    <t>中奖两个亿，我在县城当豪门！</t>
-  </si>
-  <si>
-    <t>大明：开局政变，请洪武赴死！</t>
-  </si>
-  <si>
-    <t>奥特综漫直播：什么叫人类灭绝了</t>
-  </si>
-  <si>
-    <t>绝症留洋归乡？举国哭求我别死！</t>
-  </si>
-  <si>
-    <t>国运求生：我的幸运值拉满了</t>
-  </si>
-  <si>
-    <t>末世死考：开局天使魅魔三选一</t>
-  </si>
-  <si>
-    <t>名义：搭档沙瑞金，让育良复婚！</t>
-  </si>
-  <si>
-    <t>出门捡垃圾，我被美女总裁强推了</t>
-  </si>
-  <si>
-    <t>厉鬼，我真要适应你了！</t>
-  </si>
-  <si>
-    <t>双世：从冰灵根开始伪装天骄</t>
-  </si>
-  <si>
-    <t>回到二战，我成了美国大兵</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>重生年代：我怎么多了三个前妻</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>魏家孽种成首辅，全族跪求我认祖</t>
+  </si>
+  <si>
+    <t>网游：我的药剂永久持续</t>
+  </si>
+  <si>
+    <t>火影：人在木叶村，开局觉醒木遁</t>
+  </si>
+  <si>
+    <t>天灾末世：我能提取神话词条</t>
+  </si>
+  <si>
+    <t>四合院：大家一起做禽兽</t>
+  </si>
+  <si>
+    <t>全民神祇时代：我的词条每日刷新</t>
+  </si>
+  <si>
+    <t>朱标私生子，老朱逼我当皇帝！</t>
+  </si>
+  <si>
+    <t>末日逃亡：开局苍穹列车车长</t>
+  </si>
+  <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>重生之我卖的真是高压锅</t>
+  </si>
+  <si>
+    <t>死亡列车：开局SSS级天赋！</t>
+  </si>
+  <si>
+    <t>诡异乱世：大乾第一巡夜人</t>
+  </si>
+  <si>
+    <t>直播见证神话：从鳌太线走蛟开始</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>我在战锤抽词条，帝皇站起来了？</t>
+  </si>
+  <si>
+    <t>捕鱼大亨：从北海道小渔村开始</t>
+  </si>
+  <si>
+    <t>序列：吃神者</t>
+  </si>
+  <si>
+    <t>美综：谁说美剧没有人情世故？</t>
+  </si>
+  <si>
+    <t>我有一个女鬼催眠APP</t>
+  </si>
+  <si>
+    <t>退游六年，剑仙老婆现实找上门了</t>
+  </si>
+  <si>
+    <t>死亡游戏：开局欺诈师，假扮神明</t>
+  </si>
+  <si>
+    <t>我不是戏神</t>
+  </si>
+  <si>
+    <t>贵族大小姐下乡三年生七个跑路啦</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>一日破五境，人间太岁神！</t>
+  </si>
+  <si>
+    <t>全民公路求生：我的房车无限进化</t>
   </si>
 </sst>
 </file>
@@ -766,19 +766,19 @@
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1172000</v>
+        <v>1249000</v>
       </c>
       <c r="G5" s="7">
-        <v>74000</v>
+        <v>77000</v>
       </c>
       <c r="H5" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="7">
-        <v>101125</v>
+        <v>98444</v>
       </c>
       <c r="J5" s="5">
-        <v>92.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>97.3</v>
+        <v>84.8</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>508000</v>
+        <v>2076000</v>
       </c>
       <c r="G6" s="7">
-        <v>41000</v>
+        <v>65000</v>
       </c>
       <c r="H6" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I6" s="7">
-        <v>47778</v>
+        <v>59552</v>
       </c>
       <c r="J6" s="5">
-        <v>85.5</v>
+        <v>81.5</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>80.8</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>478000</v>
+        <v>1862000</v>
       </c>
       <c r="G7" s="7">
-        <v>86000</v>
+        <v>-11000</v>
       </c>
       <c r="H7" s="7">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="I7" s="7">
-        <v>40889</v>
+        <v>58333</v>
       </c>
       <c r="J7" s="5">
-        <v>85.2</v>
+        <v>79</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>88.8</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>275000</v>
+        <v>623000</v>
       </c>
       <c r="G8" s="7">
-        <v>53000</v>
+        <v>60000</v>
       </c>
       <c r="H8" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I8" s="7">
-        <v>27750</v>
+        <v>48800</v>
       </c>
       <c r="J8" s="5">
-        <v>81.90000000000001</v>
+        <v>79</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>83.40000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>1873000</v>
+        <v>599000</v>
       </c>
       <c r="G9" s="7">
-        <v>38000</v>
+        <v>73000</v>
       </c>
       <c r="H9" s="7">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7">
-        <v>61800</v>
+        <v>41375</v>
       </c>
       <c r="J9" s="5">
-        <v>81.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>96.2</v>
+        <v>85.5</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>470000</v>
+        <v>688000</v>
       </c>
       <c r="G10" s="7">
-        <v>34000</v>
+        <v>79000</v>
       </c>
       <c r="H10" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I10" s="7">
-        <v>32444</v>
+        <v>45300</v>
       </c>
       <c r="J10" s="5">
-        <v>81</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>83.7</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>2011000</v>
+        <v>281000</v>
       </c>
       <c r="G11" s="7">
-        <v>43000</v>
+        <v>47000</v>
       </c>
       <c r="H11" s="7">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="I11" s="7">
-        <v>59357</v>
+        <v>24429</v>
       </c>
       <c r="J11" s="5">
-        <v>80.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>89.90000000000001</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>485000</v>
+        <v>761000</v>
       </c>
       <c r="G12" s="7">
-        <v>11000</v>
+        <v>49000</v>
       </c>
       <c r="H12" s="7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I12" s="7">
-        <v>43778</v>
+        <v>38154</v>
       </c>
       <c r="J12" s="5">
-        <v>80.40000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>96.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>416000</v>
+        <v>1204000</v>
       </c>
       <c r="G13" s="7">
-        <v>37000</v>
+        <v>43000</v>
       </c>
       <c r="H13" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>28667</v>
+        <v>47000</v>
       </c>
       <c r="J13" s="5">
-        <v>80.09999999999999</v>
+        <v>76</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>98.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>231000</v>
+        <v>438000</v>
       </c>
       <c r="G14" s="7">
-        <v>27000</v>
+        <v>28000</v>
       </c>
       <c r="H14" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I14" s="7">
-        <v>31200</v>
+        <v>32714</v>
       </c>
       <c r="J14" s="5">
-        <v>79.90000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>100</v>
+        <v>89.8</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>240000</v>
+        <v>288000</v>
       </c>
       <c r="G15" s="7">
-        <v>37000</v>
+        <v>53000</v>
       </c>
       <c r="H15" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I15" s="7">
-        <v>16889</v>
+        <v>16200</v>
       </c>
       <c r="J15" s="5">
-        <v>79.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>99.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>263000</v>
+        <v>172000</v>
       </c>
       <c r="G16" s="7">
-        <v>45000</v>
+        <v>21000</v>
       </c>
       <c r="H16" s="7">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I16" s="7">
-        <v>49333</v>
+        <v>16286</v>
       </c>
       <c r="J16" s="5">
-        <v>79.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>99.7</v>
+        <v>80</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>265000</v>
+        <v>406000</v>
       </c>
       <c r="G17" s="7">
-        <v>33000</v>
+        <v>35000</v>
       </c>
       <c r="H17" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>34750</v>
+        <v>27429</v>
       </c>
       <c r="J17" s="5">
-        <v>78.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>99.2</v>
+        <v>85.8</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>150000</v>
+        <v>279000</v>
       </c>
       <c r="G18" s="7">
-        <v>23000</v>
+        <v>22000</v>
       </c>
       <c r="H18" s="7">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="I18" s="7">
-        <v>12111</v>
+        <v>14786</v>
       </c>
       <c r="J18" s="5">
-        <v>77.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>99.2</v>
+        <v>81.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>147000</v>
+        <v>1130000</v>
       </c>
       <c r="G19" s="7">
-        <v>23000</v>
+        <v>32000</v>
       </c>
       <c r="H19" s="7">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I19" s="7">
-        <v>19800</v>
+        <v>23310</v>
       </c>
       <c r="J19" s="5">
-        <v>77.5</v>
+        <v>70.7</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>85.5</v>
+        <v>81.3</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>609000</v>
+        <v>305000</v>
       </c>
       <c r="G20" s="7">
-        <v>79000</v>
+        <v>27000</v>
       </c>
       <c r="H20" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I20" s="7">
-        <v>41556</v>
+        <v>22900</v>
       </c>
       <c r="J20" s="5">
-        <v>77.40000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>86</v>
+        <v>84.8</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>526000</v>
+        <v>2459000</v>
       </c>
       <c r="G21" s="7">
-        <v>65000</v>
+        <v>67000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I21" s="7">
-        <v>36857</v>
+        <v>14759</v>
       </c>
       <c r="J21" s="5">
-        <v>76.5</v>
+        <v>70.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>92.8</v>
+        <v>80.5</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>633000</v>
+        <v>760000</v>
       </c>
       <c r="G22" s="7">
-        <v>23000</v>
+        <v>8000</v>
       </c>
       <c r="H22" s="7">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="I22" s="7">
-        <v>20556</v>
+        <v>23375</v>
       </c>
       <c r="J22" s="5">
-        <v>76.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>91.5</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>268000</v>
+        <v>429000</v>
       </c>
       <c r="G23" s="7">
-        <v>23000</v>
+        <v>19000</v>
       </c>
       <c r="H23" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I23" s="7">
-        <v>22714</v>
+        <v>21636</v>
       </c>
       <c r="J23" s="5">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>84.5</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>712000</v>
+        <v>397000</v>
       </c>
       <c r="G24" s="7">
-        <v>46000</v>
+        <v>18000</v>
       </c>
       <c r="H24" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I24" s="7">
-        <v>37250</v>
+        <v>18857</v>
       </c>
       <c r="J24" s="5">
-        <v>75.8</v>
+        <v>69.8</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>86</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>410000</v>
+        <v>326000</v>
       </c>
       <c r="G25" s="7">
-        <v>33000</v>
+        <v>27000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I25" s="7">
-        <v>33500</v>
+        <v>36250</v>
       </c>
       <c r="J25" s="5">
-        <v>75.7</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>93.7</v>
+        <v>84.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>222000</v>
+        <v>768000</v>
       </c>
       <c r="G26" s="7">
-        <v>16000</v>
+        <v>37000</v>
       </c>
       <c r="H26" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I26" s="7">
-        <v>16111</v>
+        <v>11103</v>
       </c>
       <c r="J26" s="5">
-        <v>75.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>92.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>196000</v>
+        <v>761000</v>
       </c>
       <c r="G27" s="7">
-        <v>11000</v>
+        <v>23000</v>
       </c>
       <c r="H27" s="7">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="I27" s="7">
-        <v>16625</v>
+        <v>14310</v>
       </c>
       <c r="J27" s="5">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>91.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>137000</v>
+        <v>385000</v>
       </c>
       <c r="G28" s="7">
-        <v>8000</v>
+        <v>22000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="I28" s="7">
-        <v>19000</v>
+        <v>10682</v>
       </c>
       <c r="J28" s="5">
-        <v>74.90000000000001</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90.2</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>234000</v>
+        <v>261000</v>
       </c>
       <c r="G29" s="7">
-        <v>35000</v>
+        <v>17000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I29" s="7">
-        <v>20667</v>
+        <v>11700</v>
       </c>
       <c r="J29" s="5">
-        <v>74.8</v>
+        <v>68.2</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>97.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>141000</v>
+        <v>538000</v>
       </c>
       <c r="G30" s="7">
-        <v>23000</v>
+        <v>31000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>24500</v>
+        <v>19400</v>
       </c>
       <c r="J30" s="5">
-        <v>74.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>94.3</v>
+        <v>79.7</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>172000</v>
+        <v>269000</v>
       </c>
       <c r="G31" s="7">
-        <v>20000</v>
+        <v>17000</v>
       </c>
       <c r="H31" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I31" s="7">
-        <v>11000</v>
+        <v>16600</v>
       </c>
       <c r="J31" s="5">
-        <v>74.59999999999999</v>
+        <v>68</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>91.2</v>
+        <v>77.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>256000</v>
+        <v>762000</v>
       </c>
       <c r="G32" s="7">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="H32" s="7">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I32" s="7">
-        <v>17222</v>
+        <v>19850</v>
       </c>
       <c r="J32" s="5">
-        <v>74.5</v>
+        <v>67.7</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>95.8</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>103000</v>
+        <v>555000</v>
       </c>
       <c r="G33" s="7">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="H33" s="7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I33" s="7">
-        <v>6000</v>
+        <v>19941</v>
       </c>
       <c r="J33" s="5">
-        <v>74.2</v>
+        <v>67.7</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>91.5</v>
+        <v>79</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>173000</v>
+        <v>284000</v>
       </c>
       <c r="G34" s="7">
-        <v>10000</v>
+        <v>22000</v>
       </c>
       <c r="H34" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>13750</v>
+        <v>24000</v>
       </c>
       <c r="J34" s="5">
-        <v>73.8</v>
+        <v>67.5</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>93.3</v>
+        <v>82.8</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>164000</v>
+        <v>867000</v>
       </c>
       <c r="G35" s="7">
-        <v>11000</v>
+        <v>33000</v>
       </c>
       <c r="H35" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I35" s="7">
-        <v>9667</v>
+        <v>6586</v>
       </c>
       <c r="J35" s="5">
-        <v>73.7</v>
+        <v>67.2</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>85.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>563000</v>
+        <v>744000</v>
       </c>
       <c r="G36" s="7">
-        <v>43000</v>
+        <v>1000</v>
       </c>
       <c r="H36" s="7">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="I36" s="7">
-        <v>46000</v>
+        <v>19273</v>
       </c>
       <c r="J36" s="5">
-        <v>73.5</v>
+        <v>67.2</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>93</v>
+        <v>78.8</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>164000</v>
+        <v>473000</v>
       </c>
       <c r="G37" s="7">
-        <v>13000</v>
+        <v>2000</v>
       </c>
       <c r="H37" s="7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I37" s="7">
-        <v>9444</v>
+        <v>15615</v>
       </c>
       <c r="J37" s="5">
-        <v>73.5</v>
+        <v>67.2</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>88.7</v>
+        <v>79.8</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>427000</v>
+        <v>384000</v>
       </c>
       <c r="G38" s="7">
-        <v>6000</v>
+        <v>22000</v>
       </c>
       <c r="H38" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>17778</v>
+        <v>21000</v>
       </c>
       <c r="J38" s="5">
-        <v>73.2</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>90.7</v>
+        <v>77</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>355000</v>
+        <v>437000</v>
       </c>
       <c r="G39" s="7">
-        <v>13000</v>
+        <v>26000</v>
       </c>
       <c r="H39" s="7">
         <v>10</v>
       </c>
       <c r="I39" s="7">
-        <v>13111</v>
+        <v>18444</v>
       </c>
       <c r="J39" s="5">
-        <v>73.2</v>
+        <v>67</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>86.59999999999999</v>
+        <v>76.3</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>410000</v>
+        <v>647000</v>
       </c>
       <c r="G40" s="7">
-        <v>38000</v>
+        <v>4000</v>
       </c>
       <c r="H40" s="7">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I40" s="7">
-        <v>21900</v>
+        <v>19316</v>
       </c>
       <c r="J40" s="5">
-        <v>73.09999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>83.5</v>
+        <v>81.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>1161000</v>
+        <v>1849000</v>
       </c>
       <c r="G41" s="7">
-        <v>36000</v>
+        <v>18000</v>
       </c>
       <c r="H41" s="7">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I41" s="7">
-        <v>48000</v>
+        <v>7276</v>
       </c>
       <c r="J41" s="5">
-        <v>72.90000000000001</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>89.2</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>151000</v>
+        <v>316000</v>
       </c>
       <c r="G42" s="7">
-        <v>24000</v>
+        <v>22000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="I42" s="7">
-        <v>15500</v>
+        <v>552</v>
       </c>
       <c r="J42" s="5">
-        <v>72.90000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>92.3</v>
+        <v>78.7</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>226000</v>
+        <v>304000</v>
       </c>
       <c r="G43" s="7">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="H43" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I43" s="7">
-        <v>27750</v>
+        <v>10636</v>
       </c>
       <c r="J43" s="5">
-        <v>72.7</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>88.59999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>159000</v>
+        <v>815000</v>
       </c>
       <c r="G44" s="7">
-        <v>4000</v>
+        <v>42000</v>
       </c>
       <c r="H44" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I44" s="7">
-        <v>14000</v>
+        <v>5379</v>
       </c>
       <c r="J44" s="5">
-        <v>72.2</v>
+        <v>65.8</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>87.8</v>
+        <v>80.5</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>264000</v>
+        <v>331000</v>
       </c>
       <c r="G45" s="7">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="H45" s="7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I45" s="7">
-        <v>15286</v>
+        <v>5333</v>
       </c>
       <c r="J45" s="5">
-        <v>72.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>93.3</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>195000</v>
+        <v>677000</v>
       </c>
       <c r="G46" s="7">
-        <v>22000</v>
+        <v>13000</v>
       </c>
       <c r="H46" s="7">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I46" s="7">
-        <v>23250</v>
+        <v>13000</v>
       </c>
       <c r="J46" s="5">
-        <v>72.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>88.3</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>177000</v>
+        <v>325000</v>
       </c>
       <c r="G47" s="7">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="H47" s="7">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="I47" s="7">
-        <v>13571</v>
+        <v>2621</v>
       </c>
       <c r="J47" s="5">
-        <v>72</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>84</v>
+        <v>77.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>278000</v>
+        <v>477000</v>
       </c>
       <c r="G48" s="7">
-        <v>33000</v>
+        <v>26000</v>
       </c>
       <c r="H48" s="7">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I48" s="7">
-        <v>22444</v>
+        <v>9706</v>
       </c>
       <c r="J48" s="5">
-        <v>71.8</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>89.2</v>
+        <v>81.5</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>276000</v>
+        <v>1808000</v>
       </c>
       <c r="G49" s="7">
-        <v>16000</v>
+        <v>3000</v>
       </c>
       <c r="H49" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I49" s="7">
-        <v>11111</v>
+        <v>828</v>
       </c>
       <c r="J49" s="5">
-        <v>71.8</v>
+        <v>65</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>87</v>
+        <v>78.5</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>257000</v>
+        <v>189000</v>
       </c>
       <c r="G50" s="7">
-        <v>25000</v>
+        <v>14000</v>
       </c>
       <c r="H50" s="7">
         <v>14</v>
       </c>
       <c r="I50" s="7">
-        <v>14231</v>
+        <v>6923</v>
       </c>
       <c r="J50" s="5">
-        <v>71.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>91.8</v>
+        <v>79.8</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>123000</v>
+        <v>1174000</v>
       </c>
       <c r="G51" s="7">
-        <v>10000</v>
+        <v>13000</v>
       </c>
       <c r="H51" s="7">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I51" s="7">
-        <v>2556</v>
+        <v>3828</v>
       </c>
       <c r="J51" s="5">
-        <v>71.09999999999999</v>
+        <v>64.8</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>93.8</v>
+        <v>79.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>174000</v>
+        <v>271000</v>
       </c>
       <c r="G52" s="7">
-        <v>16000</v>
+        <v>10000</v>
       </c>
       <c r="H52" s="7">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="I52" s="7">
-        <v>17750</v>
+        <v>4310</v>
       </c>
       <c r="J52" s="5">
-        <v>71</v>
+        <v>64.7</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>89.2</v>
+        <v>78.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>164000</v>
+        <v>228000</v>
       </c>
       <c r="G53" s="7">
-        <v>5000</v>
+        <v>17000</v>
       </c>
       <c r="H53" s="7">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I53" s="7">
-        <v>7111</v>
+        <v>6333</v>
       </c>
       <c r="J53" s="5">
-        <v>70.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>81.59999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>1098000</v>
+        <v>428000</v>
       </c>
       <c r="G54" s="7">
-        <v>33000</v>
+        <v>6000</v>
       </c>
       <c r="H54" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I54" s="7">
-        <v>23000</v>
+        <v>2690</v>
       </c>
       <c r="J54" s="5">
-        <v>70.59999999999999</v>
+        <v>64.5</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-13T06:32:35+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-14T04:35:02+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
+    <t>我合成了全世界</t>
+  </si>
+  <si>
     <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
-    <t>我合成了全世界</t>
+    <t>年代1958，从搬运工开始！</t>
+  </si>
+  <si>
+    <t>你管这叫警察？重炮都架租界口了</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
     <t>我就写个网文，真没想镇压文坛啊</t>
   </si>
   <si>
+    <t>重生年代：我怎么多了三个前妻</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
+    <t>出门捡垃圾，我被美女总裁强推了</t>
+  </si>
+  <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>魏家孽种成首辅，全族跪求我认祖</t>
+  </si>
+  <si>
     <t>高武：看不起斩魄刀，流刃若火呢</t>
   </si>
   <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>年代1958，从搬运工开始！</t>
-  </si>
-  <si>
-    <t>我靠风水中医术，养活六个妹妹</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
+    <t>死亡列车：开局SSS级天赋！</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>重生之我卖的真是高压锅</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
   </si>
   <si>
     <t>伪人降临！我是全场唯一预言家</t>
   </si>
   <si>
-    <t>出门捡垃圾，我被美女总裁强推了</t>
+    <t>直播见证神话：从鳌太线走蛟开始</t>
+  </si>
+  <si>
+    <t>年代：每日情报开局截胡女儿国王</t>
+  </si>
+  <si>
+    <t>四合院：大家一起做禽兽</t>
+  </si>
+  <si>
+    <t>末日逃亡：开局苍穹列车车长</t>
+  </si>
+  <si>
+    <t>火影：人在木叶村，开局觉醒木遁</t>
+  </si>
+  <si>
+    <t>全民神祇时代：我的词条每日刷新</t>
+  </si>
+  <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>末世死考：开局天使魅魔三选一</t>
   </si>
   <si>
     <t>我都宇宙之主了，你们还在地球？</t>
   </si>
   <si>
-    <t>末世死考：开局天使魅魔三选一</t>
-  </si>
-  <si>
-    <t>神通者</t>
-  </si>
-  <si>
     <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
-    <t>年代：每日情报开局截胡女儿国王</t>
-  </si>
-  <si>
-    <t>全民地仙：开局紫金葫芦辟福地</t>
-  </si>
-  <si>
-    <t>重生年代：我怎么多了三个前妻</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>魏家孽种成首辅，全族跪求我认祖</t>
+    <t>天灾末世：我能提取神话词条</t>
+  </si>
+  <si>
+    <t>诡异乱世：大乾第一巡夜人</t>
   </si>
   <si>
     <t>网游：我的药剂永久持续</t>
   </si>
   <si>
-    <t>火影：人在木叶村，开局觉醒木遁</t>
-  </si>
-  <si>
-    <t>天灾末世：我能提取神话词条</t>
-  </si>
-  <si>
-    <t>四合院：大家一起做禽兽</t>
-  </si>
-  <si>
-    <t>全民神祇时代：我的词条每日刷新</t>
+    <t>美综：谁说美剧没有人情世故？</t>
+  </si>
+  <si>
+    <t>捕鱼大亨：从北海道小渔村开始</t>
+  </si>
+  <si>
+    <t>百岁修仙：从觉醒天灵根开始</t>
+  </si>
+  <si>
+    <t>序列：吃神者</t>
+  </si>
+  <si>
+    <t>死亡游戏：开局欺诈师，假扮神明</t>
+  </si>
+  <si>
+    <t>公路求生：只有我能无限合成进化</t>
+  </si>
+  <si>
+    <t>我不是戏神</t>
+  </si>
+  <si>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
   </si>
   <si>
     <t>朱标私生子，老朱逼我当皇帝！</t>
   </si>
   <si>
-    <t>末日逃亡：开局苍穹列车车长</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>重生之我卖的真是高压锅</t>
-  </si>
-  <si>
-    <t>死亡列车：开局SSS级天赋！</t>
-  </si>
-  <si>
-    <t>诡异乱世：大乾第一巡夜人</t>
-  </si>
-  <si>
-    <t>直播见证神话：从鳌太线走蛟开始</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>我在战锤抽词条，帝皇站起来了？</t>
-  </si>
-  <si>
-    <t>捕鱼大亨：从北海道小渔村开始</t>
-  </si>
-  <si>
-    <t>序列：吃神者</t>
-  </si>
-  <si>
-    <t>美综：谁说美剧没有人情世故？</t>
-  </si>
-  <si>
     <t>我有一个女鬼催眠APP</t>
   </si>
   <si>
+    <t>魔女金词条？我反派先薅为敬！</t>
+  </si>
+  <si>
+    <t>90年港岛电影圈！我有即梦AI</t>
+  </si>
+  <si>
+    <t>我以狐仙镇百鬼</t>
+  </si>
+  <si>
+    <t>综漫：异种族评鉴指南</t>
+  </si>
+  <si>
     <t>退游六年，剑仙老婆现实找上门了</t>
-  </si>
-  <si>
-    <t>死亡游戏：开局欺诈师，假扮神明</t>
-  </si>
-  <si>
-    <t>我不是戏神</t>
-  </si>
-  <si>
-    <t>贵族大小姐下乡三年生七个跑路啦</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>一日破五境，人间太岁神！</t>
-  </si>
-  <si>
-    <t>全民公路求生：我的房车无限进化</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>87.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1249000</v>
+        <v>1333000</v>
       </c>
       <c r="G5" s="7">
-        <v>77000</v>
+        <v>84000</v>
       </c>
       <c r="H5" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I5" s="7">
-        <v>98444</v>
+        <v>97000</v>
       </c>
       <c r="J5" s="5">
-        <v>92.5</v>
+        <v>92.3</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,23 +792,23 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>84.8</v>
+        <v>84.7</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>2076000</v>
+        <v>2139000</v>
       </c>
       <c r="G6" s="7">
-        <v>65000</v>
+        <v>63000</v>
       </c>
       <c r="H6" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I6" s="7">
-        <v>59552</v>
+        <v>59667</v>
       </c>
       <c r="J6" s="5">
         <v>81.5</v>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>80.8</v>
+        <v>87.2</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1862000</v>
+        <v>678000</v>
       </c>
       <c r="G7" s="7">
-        <v>-11000</v>
+        <v>55000</v>
       </c>
       <c r="H7" s="7">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>58333</v>
+        <v>49833</v>
       </c>
       <c r="J7" s="5">
-        <v>79</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>88.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>623000</v>
+        <v>1832000</v>
       </c>
       <c r="G8" s="7">
-        <v>60000</v>
+        <v>-30000</v>
       </c>
       <c r="H8" s="7">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I8" s="7">
-        <v>48800</v>
+        <v>54318</v>
       </c>
       <c r="J8" s="5">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>87.8</v>
+        <v>85.5</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>599000</v>
+        <v>473000</v>
       </c>
       <c r="G9" s="7">
-        <v>73000</v>
+        <v>35000</v>
       </c>
       <c r="H9" s="7">
         <v>9</v>
       </c>
       <c r="I9" s="7">
-        <v>41375</v>
+        <v>33000</v>
       </c>
       <c r="J9" s="5">
-        <v>78.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>85.5</v>
+        <v>88.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>688000</v>
+        <v>315000</v>
       </c>
       <c r="G10" s="7">
-        <v>79000</v>
+        <v>34000</v>
       </c>
       <c r="H10" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I10" s="7">
-        <v>45300</v>
+        <v>25625</v>
       </c>
       <c r="J10" s="5">
-        <v>78.40000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>91.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>281000</v>
+        <v>798000</v>
       </c>
       <c r="G11" s="7">
-        <v>47000</v>
+        <v>37000</v>
       </c>
       <c r="H11" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I11" s="7">
-        <v>24429</v>
+        <v>38071</v>
       </c>
       <c r="J11" s="5">
-        <v>76.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>84.59999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>761000</v>
+        <v>639000</v>
       </c>
       <c r="G12" s="7">
-        <v>49000</v>
+        <v>40000</v>
       </c>
       <c r="H12" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>38154</v>
+        <v>41222</v>
       </c>
       <c r="J12" s="5">
-        <v>76.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>84.09999999999999</v>
+        <v>86</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>1204000</v>
+        <v>361000</v>
       </c>
       <c r="G13" s="7">
-        <v>43000</v>
+        <v>35000</v>
       </c>
       <c r="H13" s="7">
         <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>47000</v>
+        <v>36000</v>
       </c>
       <c r="J13" s="5">
-        <v>76</v>
+        <v>74.3</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>84.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>438000</v>
+        <v>1201000</v>
       </c>
       <c r="G14" s="7">
-        <v>28000</v>
+        <v>-3000</v>
       </c>
       <c r="H14" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>32714</v>
+        <v>38667</v>
       </c>
       <c r="J14" s="5">
-        <v>74.5</v>
+        <v>73.7</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>89.8</v>
+        <v>87</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>288000</v>
+        <v>193000</v>
       </c>
       <c r="G15" s="7">
-        <v>53000</v>
+        <v>21000</v>
       </c>
       <c r="H15" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7">
-        <v>16200</v>
+        <v>16875</v>
       </c>
       <c r="J15" s="5">
-        <v>73.40000000000001</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>88.40000000000001</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>172000</v>
+        <v>306000</v>
       </c>
       <c r="G16" s="7">
-        <v>21000</v>
+        <v>27000</v>
       </c>
       <c r="H16" s="7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I16" s="7">
-        <v>16286</v>
+        <v>15600</v>
       </c>
       <c r="J16" s="5">
-        <v>72.7</v>
+        <v>71.8</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>80</v>
+        <v>84.3</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>406000</v>
+        <v>2516000</v>
       </c>
       <c r="G17" s="7">
-        <v>35000</v>
+        <v>57000</v>
       </c>
       <c r="H17" s="7">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I17" s="7">
-        <v>27429</v>
+        <v>16167</v>
       </c>
       <c r="J17" s="5">
-        <v>70.90000000000001</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>85.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>279000</v>
+        <v>418000</v>
       </c>
       <c r="G18" s="7">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="H18" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I18" s="7">
-        <v>14786</v>
+        <v>19000</v>
       </c>
       <c r="J18" s="5">
-        <v>70.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>81.5</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>1130000</v>
+        <v>791000</v>
       </c>
       <c r="G19" s="7">
-        <v>32000</v>
+        <v>30000</v>
       </c>
       <c r="H19" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I19" s="7">
-        <v>23310</v>
+        <v>14833</v>
       </c>
       <c r="J19" s="5">
-        <v>70.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>81.3</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>305000</v>
+        <v>682000</v>
       </c>
       <c r="G20" s="7">
-        <v>27000</v>
+        <v>-6000</v>
       </c>
       <c r="H20" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I20" s="7">
-        <v>22900</v>
+        <v>40636</v>
       </c>
       <c r="J20" s="5">
-        <v>70.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>84.8</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>2459000</v>
+        <v>402000</v>
       </c>
       <c r="G21" s="7">
-        <v>67000</v>
+        <v>18000</v>
       </c>
       <c r="H21" s="7">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>14759</v>
+        <v>20500</v>
       </c>
       <c r="J21" s="5">
-        <v>70.3</v>
+        <v>68.8</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>80.5</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>760000</v>
+        <v>792000</v>
       </c>
       <c r="G22" s="7">
-        <v>8000</v>
+        <v>24000</v>
       </c>
       <c r="H22" s="7">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I22" s="7">
-        <v>23375</v>
+        <v>11533</v>
       </c>
       <c r="J22" s="5">
-        <v>70.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>81.09999999999999</v>
+        <v>80.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>429000</v>
+        <v>484000</v>
       </c>
       <c r="G23" s="7">
-        <v>19000</v>
+        <v>11000</v>
       </c>
       <c r="H23" s="7">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I23" s="7">
-        <v>21636</v>
+        <v>15286</v>
       </c>
       <c r="J23" s="5">
-        <v>70</v>
+        <v>68.2</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>81.90000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>397000</v>
+        <v>1890000</v>
       </c>
       <c r="G24" s="7">
-        <v>18000</v>
+        <v>41000</v>
       </c>
       <c r="H24" s="7">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="I24" s="7">
-        <v>18857</v>
+        <v>8400</v>
       </c>
       <c r="J24" s="5">
-        <v>69.8</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>82.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>326000</v>
+        <v>424000</v>
       </c>
       <c r="G25" s="7">
-        <v>27000</v>
+        <v>18000</v>
       </c>
       <c r="H25" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I25" s="7">
-        <v>36250</v>
+        <v>26250</v>
       </c>
       <c r="J25" s="5">
-        <v>69.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>84.5</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>768000</v>
+        <v>661000</v>
       </c>
       <c r="G26" s="7">
-        <v>37000</v>
+        <v>14000</v>
       </c>
       <c r="H26" s="7">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="I26" s="7">
-        <v>11103</v>
+        <v>19050</v>
       </c>
       <c r="J26" s="5">
-        <v>69.3</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>82.5</v>
+        <v>77.2</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>761000</v>
+        <v>432000</v>
       </c>
       <c r="G27" s="7">
-        <v>23000</v>
+        <v>3000</v>
       </c>
       <c r="H27" s="7">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I27" s="7">
-        <v>14310</v>
+        <v>20083</v>
       </c>
       <c r="J27" s="5">
-        <v>69</v>
+        <v>67.5</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>83.2</v>
+        <v>78.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>385000</v>
+        <v>284000</v>
       </c>
       <c r="G28" s="7">
-        <v>22000</v>
+        <v>15000</v>
       </c>
       <c r="H28" s="7">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="I28" s="7">
-        <v>10682</v>
+        <v>16455</v>
       </c>
       <c r="J28" s="5">
-        <v>68.40000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>82.40000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>261000</v>
+        <v>298000</v>
       </c>
       <c r="G29" s="7">
-        <v>17000</v>
+        <v>14000</v>
       </c>
       <c r="H29" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>11700</v>
+        <v>22333</v>
       </c>
       <c r="J29" s="5">
-        <v>68.2</v>
+        <v>67.2</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>82.3</v>
+        <v>80.5</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>538000</v>
+        <v>274000</v>
       </c>
       <c r="G30" s="7">
-        <v>31000</v>
+        <v>13000</v>
       </c>
       <c r="H30" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I30" s="7">
-        <v>19400</v>
+        <v>11818</v>
       </c>
       <c r="J30" s="5">
-        <v>68.09999999999999</v>
+        <v>67.2</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>79.7</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>269000</v>
+        <v>778000</v>
       </c>
       <c r="G31" s="7">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="H31" s="7">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I31" s="7">
-        <v>16600</v>
+        <v>19667</v>
       </c>
       <c r="J31" s="5">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>77.7</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>762000</v>
+        <v>893000</v>
       </c>
       <c r="G32" s="7">
-        <v>24000</v>
+        <v>26000</v>
       </c>
       <c r="H32" s="7">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="I32" s="7">
-        <v>19850</v>
+        <v>7233</v>
       </c>
       <c r="J32" s="5">
-        <v>67.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>77.59999999999999</v>
+        <v>77</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>555000</v>
+        <v>739000</v>
       </c>
       <c r="G33" s="7">
-        <v>3000</v>
+        <v>-5000</v>
       </c>
       <c r="H33" s="7">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I33" s="7">
-        <v>19941</v>
+        <v>18217</v>
       </c>
       <c r="J33" s="5">
-        <v>67.7</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>79</v>
+        <v>75.3</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>284000</v>
+        <v>316000</v>
       </c>
       <c r="G34" s="7">
-        <v>22000</v>
+        <v>11000</v>
       </c>
       <c r="H34" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I34" s="7">
-        <v>24000</v>
+        <v>21818</v>
       </c>
       <c r="J34" s="5">
-        <v>67.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>82.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>867000</v>
+        <v>1095000</v>
       </c>
       <c r="G35" s="7">
-        <v>33000</v>
+        <v>-35000</v>
       </c>
       <c r="H35" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I35" s="7">
-        <v>6586</v>
+        <v>21367</v>
       </c>
       <c r="J35" s="5">
-        <v>67.2</v>
+        <v>66.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>77</v>
+        <v>75.8</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>744000</v>
+        <v>733000</v>
       </c>
       <c r="G36" s="7">
-        <v>1000</v>
+        <v>-27000</v>
       </c>
       <c r="H36" s="7">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="I36" s="7">
-        <v>19273</v>
+        <v>20412</v>
       </c>
       <c r="J36" s="5">
-        <v>67.2</v>
+        <v>66.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>78.8</v>
+        <v>76.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>473000</v>
+        <v>540000</v>
       </c>
       <c r="G37" s="7">
         <v>2000</v>
       </c>
       <c r="H37" s="7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>15615</v>
+        <v>16500</v>
       </c>
       <c r="J37" s="5">
-        <v>67.2</v>
+        <v>66.2</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>79.8</v>
+        <v>75.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>384000</v>
+        <v>454000</v>
       </c>
       <c r="G38" s="7">
-        <v>22000</v>
+        <v>17000</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="I38" s="7">
-        <v>21000</v>
+        <v>18300</v>
       </c>
       <c r="J38" s="5">
-        <v>67.09999999999999</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>77</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>437000</v>
+        <v>390000</v>
       </c>
       <c r="G39" s="7">
-        <v>26000</v>
+        <v>5000</v>
       </c>
       <c r="H39" s="7">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I39" s="7">
-        <v>18444</v>
+        <v>10435</v>
       </c>
       <c r="J39" s="5">
-        <v>67</v>
+        <v>65.7</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>76.3</v>
+        <v>80.5</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>647000</v>
+        <v>343000</v>
       </c>
       <c r="G40" s="7">
-        <v>4000</v>
+        <v>12000</v>
       </c>
       <c r="H40" s="7">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I40" s="7">
-        <v>19316</v>
+        <v>5750</v>
       </c>
       <c r="J40" s="5">
-        <v>66.8</v>
+        <v>65.7</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>81.5</v>
+        <v>77.8</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>1849000</v>
+        <v>320000</v>
       </c>
       <c r="G41" s="7">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="H41" s="7">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="I41" s="7">
-        <v>7276</v>
+        <v>11083</v>
       </c>
       <c r="J41" s="5">
-        <v>66.59999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>84.09999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>316000</v>
+        <v>332000</v>
       </c>
       <c r="G42" s="7">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="H42" s="7">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="I42" s="7">
-        <v>552</v>
+        <v>5500</v>
       </c>
       <c r="J42" s="5">
-        <v>66.40000000000001</v>
+        <v>65.5</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>78.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>304000</v>
+        <v>849000</v>
       </c>
       <c r="G43" s="7">
-        <v>18000</v>
+        <v>34000</v>
       </c>
       <c r="H43" s="7">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="I43" s="7">
-        <v>10636</v>
+        <v>6333</v>
       </c>
       <c r="J43" s="5">
-        <v>65.90000000000001</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>80.8</v>
+        <v>77.5</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>815000</v>
+        <v>504000</v>
       </c>
       <c r="G44" s="7">
-        <v>42000</v>
+        <v>27000</v>
       </c>
       <c r="H44" s="7">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I44" s="7">
-        <v>5379</v>
+        <v>10667</v>
       </c>
       <c r="J44" s="5">
-        <v>65.8</v>
+        <v>65.3</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>80.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>331000</v>
+        <v>188000</v>
       </c>
       <c r="G45" s="7">
-        <v>12000</v>
+        <v>21000</v>
       </c>
       <c r="H45" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I45" s="7">
-        <v>5333</v>
+        <v>9333</v>
       </c>
       <c r="J45" s="5">
-        <v>65.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>76.90000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>677000</v>
+        <v>1812000</v>
       </c>
       <c r="G46" s="7">
-        <v>13000</v>
+        <v>4000</v>
       </c>
       <c r="H46" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I46" s="7">
-        <v>13000</v>
+        <v>933</v>
       </c>
       <c r="J46" s="5">
-        <v>65.5</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>81.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>325000</v>
+        <v>1187000</v>
       </c>
       <c r="G47" s="7">
-        <v>17000</v>
+        <v>13000</v>
       </c>
       <c r="H47" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I47" s="7">
-        <v>2621</v>
+        <v>4133</v>
       </c>
       <c r="J47" s="5">
-        <v>65.40000000000001</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>77.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>477000</v>
+        <v>536000</v>
       </c>
       <c r="G48" s="7">
-        <v>26000</v>
+        <v>-19000</v>
       </c>
       <c r="H48" s="7">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I48" s="7">
-        <v>9706</v>
+        <v>17778</v>
       </c>
       <c r="J48" s="5">
-        <v>65.09999999999999</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>81.5</v>
+        <v>75.7</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>1808000</v>
+        <v>682000</v>
       </c>
       <c r="G49" s="7">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H49" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I49" s="7">
-        <v>828</v>
+        <v>12733</v>
       </c>
       <c r="J49" s="5">
-        <v>65</v>
+        <v>64.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>78.5</v>
+        <v>79.3</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>189000</v>
+        <v>281000</v>
       </c>
       <c r="G50" s="7">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="H50" s="7">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="I50" s="7">
-        <v>6923</v>
+        <v>4500</v>
       </c>
       <c r="J50" s="5">
-        <v>64.90000000000001</v>
+        <v>64.7</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>79.8</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>1174000</v>
+        <v>361000</v>
       </c>
       <c r="G51" s="7">
-        <v>13000</v>
+        <v>39000</v>
       </c>
       <c r="H51" s="7">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="I51" s="7">
-        <v>3828</v>
+        <v>48000</v>
       </c>
       <c r="J51" s="5">
-        <v>64.8</v>
+        <v>64.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>79.3</v>
+        <v>80.3</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>271000</v>
+        <v>799000</v>
       </c>
       <c r="G52" s="7">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H52" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I52" s="7">
-        <v>4310</v>
+        <v>1133</v>
       </c>
       <c r="J52" s="5">
-        <v>64.7</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>78.2</v>
+        <v>77</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>228000</v>
+        <v>366000</v>
       </c>
       <c r="G53" s="7">
-        <v>17000</v>
+        <v>-3000</v>
       </c>
       <c r="H53" s="7">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="I53" s="7">
-        <v>6333</v>
+        <v>7967</v>
       </c>
       <c r="J53" s="5">
-        <v>64.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>79.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>428000</v>
+        <v>336000</v>
       </c>
       <c r="G54" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H54" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I54" s="7">
-        <v>2690</v>
+        <v>2900</v>
       </c>
       <c r="J54" s="5">
-        <v>64.5</v>
+        <v>64.3</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-14T04:35:02+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-15T04:17:38+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -82,145 +82,145 @@
     <t>我合成了全世界</t>
   </si>
   <si>
+    <t>重生年代：我怎么多了三个前妻</t>
+  </si>
+  <si>
     <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
     <t>年代1958，从搬运工开始！</t>
   </si>
   <si>
+    <t>我就写个网文，真没想镇压文坛啊</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
     <t>你管这叫警察？重炮都架租界口了</t>
   </si>
   <si>
     <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
-    <t>我就写个网文，真没想镇压文坛啊</t>
-  </si>
-  <si>
-    <t>重生年代：我怎么多了三个前妻</t>
-  </si>
-  <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
-    <t>入狱五年，归来仍是大佬</t>
+    <t>神通者</t>
   </si>
   <si>
     <t>出门捡垃圾，我被美女总裁强推了</t>
   </si>
   <si>
-    <t>神通者</t>
+    <t>末世死考：开局天使魅魔三选一</t>
+  </si>
+  <si>
+    <t>魏家孽种成首辅，全族跪求我认祖</t>
+  </si>
+  <si>
+    <t>四合院：大家一起做禽兽</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>伪人降临！我是全场唯一预言家</t>
+  </si>
+  <si>
+    <t>年代：每日情报开局截胡女儿国王</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>重生之我卖的真是高压锅</t>
+  </si>
+  <si>
+    <t>高武：看不起斩魄刀，流刃若火呢</t>
+  </si>
+  <si>
+    <t>死亡列车：开局SSS级天赋！</t>
   </si>
   <si>
     <t>全民地仙：开局紫金葫芦辟福地</t>
   </si>
   <si>
-    <t>魏家孽种成首辅，全族跪求我认祖</t>
-  </si>
-  <si>
-    <t>高武：看不起斩魄刀，流刃若火呢</t>
-  </si>
-  <si>
-    <t>死亡列车：开局SSS级天赋！</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
-    <t>重生之我卖的真是高压锅</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>伪人降临！我是全场唯一预言家</t>
+    <t>我都宇宙之主了，你们还在地球？</t>
+  </si>
+  <si>
+    <t>全民神祇时代：我的词条每日刷新</t>
+  </si>
+  <si>
+    <t>名义：高育良不装了，带同伟狂飙</t>
+  </si>
+  <si>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>末日逃亡：开局苍穹列车车长</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>火影：人在木叶村，开局觉醒木遁</t>
   </si>
   <si>
     <t>直播见证神话：从鳌太线走蛟开始</t>
   </si>
   <si>
-    <t>年代：每日情报开局截胡女儿国王</t>
-  </si>
-  <si>
-    <t>四合院：大家一起做禽兽</t>
-  </si>
-  <si>
-    <t>末日逃亡：开局苍穹列车车长</t>
-  </si>
-  <si>
-    <t>火影：人在木叶村，开局觉醒木遁</t>
-  </si>
-  <si>
-    <t>全民神祇时代：我的词条每日刷新</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>末世死考：开局天使魅魔三选一</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
     <t>从修仙回到都市，坏消息修为没了</t>
   </si>
   <si>
+    <t>朱标私生子，老朱逼我当皇帝！</t>
+  </si>
+  <si>
+    <t>序列：吃神者</t>
+  </si>
+  <si>
     <t>天灾末世：我能提取神话词条</t>
   </si>
   <si>
     <t>诡异乱世：大乾第一巡夜人</t>
   </si>
   <si>
+    <t>90年港岛电影圈！我有即梦AI</t>
+  </si>
+  <si>
+    <t>我不是戏神</t>
+  </si>
+  <si>
+    <t>东北鬼事1935</t>
+  </si>
+  <si>
+    <t>美综：谁说美剧没有人情世故？</t>
+  </si>
+  <si>
     <t>网游：我的药剂永久持续</t>
   </si>
   <si>
-    <t>美综：谁说美剧没有人情世故？</t>
-  </si>
-  <si>
-    <t>捕鱼大亨：从北海道小渔村开始</t>
-  </si>
-  <si>
     <t>百岁修仙：从觉醒天灵根开始</t>
   </si>
   <si>
-    <t>序列：吃神者</t>
+    <t>文字武侠：开局破庙夜会帮主夫人</t>
+  </si>
+  <si>
+    <t>我以狐仙镇百鬼</t>
+  </si>
+  <si>
+    <t>精灵女王审讯录</t>
   </si>
   <si>
     <t>死亡游戏：开局欺诈师，假扮神明</t>
   </si>
   <si>
-    <t>公路求生：只有我能无限合成进化</t>
-  </si>
-  <si>
-    <t>我不是戏神</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>朱标私生子，老朱逼我当皇帝！</t>
-  </si>
-  <si>
-    <t>我有一个女鬼催眠APP</t>
-  </si>
-  <si>
-    <t>魔女金词条？我反派先薅为敬！</t>
-  </si>
-  <si>
-    <t>90年港岛电影圈！我有即梦AI</t>
-  </si>
-  <si>
-    <t>我以狐仙镇百鬼</t>
-  </si>
-  <si>
-    <t>综漫：异种族评鉴指南</t>
-  </si>
-  <si>
-    <t>退游六年，剑仙老婆现实找上门了</t>
+    <t>红楼：庶子贾琮，开局收保护费</t>
+  </si>
+  <si>
+    <t>快穿诸天我有无限背包从药神开始</t>
+  </si>
+  <si>
+    <t>疯狂状元郎，系统逼我无恶不作</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>87.3</v>
+        <v>85.5</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1333000</v>
+        <v>1397000</v>
       </c>
       <c r="G5" s="7">
-        <v>84000</v>
+        <v>64000</v>
       </c>
       <c r="H5" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I5" s="7">
-        <v>97000</v>
+        <v>94000</v>
       </c>
       <c r="J5" s="5">
-        <v>92.3</v>
+        <v>90.5</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>84.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>2139000</v>
+        <v>2180000</v>
       </c>
       <c r="G6" s="7">
-        <v>63000</v>
+        <v>41000</v>
       </c>
       <c r="H6" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I6" s="7">
-        <v>59667</v>
+        <v>59065</v>
       </c>
       <c r="J6" s="5">
-        <v>81.5</v>
+        <v>80.7</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>87.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>678000</v>
+        <v>725000</v>
       </c>
       <c r="G7" s="7">
-        <v>55000</v>
+        <v>47000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>49833</v>
+        <v>49429</v>
       </c>
       <c r="J7" s="5">
-        <v>80.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>78.90000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>1832000</v>
+        <v>412000</v>
       </c>
       <c r="G8" s="7">
-        <v>-30000</v>
+        <v>51000</v>
       </c>
       <c r="H8" s="7">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>54318</v>
+        <v>38500</v>
       </c>
       <c r="J8" s="5">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>85.5</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>473000</v>
+        <v>1804000</v>
       </c>
       <c r="G9" s="7">
-        <v>35000</v>
+        <v>-28000</v>
       </c>
       <c r="H9" s="7">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="I9" s="7">
-        <v>33000</v>
+        <v>50739</v>
       </c>
       <c r="J9" s="5">
-        <v>75.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>88.8</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>315000</v>
+        <v>511000</v>
       </c>
       <c r="G10" s="7">
-        <v>34000</v>
+        <v>38000</v>
       </c>
       <c r="H10" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I10" s="7">
-        <v>25625</v>
+        <v>33556</v>
       </c>
       <c r="J10" s="5">
-        <v>75.2</v>
+        <v>76</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>82.7</v>
+        <v>81.2</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>798000</v>
+        <v>668000</v>
       </c>
       <c r="G11" s="7">
-        <v>37000</v>
+        <v>29000</v>
       </c>
       <c r="H11" s="7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I11" s="7">
-        <v>38071</v>
+        <v>40000</v>
       </c>
       <c r="J11" s="5">
-        <v>75</v>
+        <v>74.7</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>80.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>639000</v>
+        <v>224000</v>
       </c>
       <c r="G12" s="7">
-        <v>40000</v>
+        <v>31000</v>
       </c>
       <c r="H12" s="7">
         <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>41222</v>
+        <v>18444</v>
       </c>
       <c r="J12" s="5">
-        <v>74.7</v>
+        <v>74.2</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>86</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>361000</v>
+        <v>344000</v>
       </c>
       <c r="G13" s="7">
-        <v>35000</v>
+        <v>29000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I13" s="7">
-        <v>36000</v>
+        <v>26000</v>
       </c>
       <c r="J13" s="5">
-        <v>74.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>80.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>1201000</v>
+        <v>821000</v>
       </c>
       <c r="G14" s="7">
-        <v>-3000</v>
+        <v>23000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I14" s="7">
-        <v>38667</v>
+        <v>37067</v>
       </c>
       <c r="J14" s="5">
         <v>73.7</v>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>87</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>193000</v>
+        <v>1197000</v>
       </c>
       <c r="G15" s="7">
-        <v>21000</v>
+        <v>-4000</v>
       </c>
       <c r="H15" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>16875</v>
+        <v>32571</v>
       </c>
       <c r="J15" s="5">
-        <v>72.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>87.09999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>306000</v>
+        <v>2594000</v>
       </c>
       <c r="G16" s="7">
-        <v>27000</v>
+        <v>78000</v>
       </c>
       <c r="H16" s="7">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="I16" s="7">
-        <v>15600</v>
+        <v>18161</v>
       </c>
       <c r="J16" s="5">
-        <v>71.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>84.3</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>2516000</v>
+        <v>329000</v>
       </c>
       <c r="G17" s="7">
-        <v>57000</v>
+        <v>23000</v>
       </c>
       <c r="H17" s="7">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="I17" s="7">
-        <v>16167</v>
+        <v>16062</v>
       </c>
       <c r="J17" s="5">
-        <v>70.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>82.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>418000</v>
+        <v>343000</v>
       </c>
       <c r="G18" s="7">
-        <v>21000</v>
+        <v>27000</v>
       </c>
       <c r="H18" s="7">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I18" s="7">
-        <v>19000</v>
+        <v>22250</v>
       </c>
       <c r="J18" s="5">
-        <v>70.2</v>
+        <v>69.8</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>83.40000000000001</v>
+        <v>83</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>791000</v>
+        <v>818000</v>
       </c>
       <c r="G19" s="7">
-        <v>30000</v>
+        <v>27000</v>
       </c>
       <c r="H19" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I19" s="7">
-        <v>14833</v>
+        <v>15226</v>
       </c>
       <c r="J19" s="5">
-        <v>69.59999999999999</v>
+        <v>69.5</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>71.59999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>682000</v>
+        <v>300000</v>
       </c>
       <c r="G20" s="7">
-        <v>-6000</v>
+        <v>16000</v>
       </c>
       <c r="H20" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I20" s="7">
-        <v>40636</v>
+        <v>16417</v>
       </c>
       <c r="J20" s="5">
-        <v>69.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>79.40000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>402000</v>
+        <v>1933000</v>
       </c>
       <c r="G21" s="7">
-        <v>18000</v>
+        <v>43000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="I21" s="7">
-        <v>20500</v>
+        <v>9516</v>
       </c>
       <c r="J21" s="5">
-        <v>68.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>82.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>792000</v>
+        <v>445000</v>
       </c>
       <c r="G22" s="7">
-        <v>24000</v>
+        <v>21000</v>
       </c>
       <c r="H22" s="7">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I22" s="7">
-        <v>11533</v>
+        <v>25667</v>
       </c>
       <c r="J22" s="5">
-        <v>68.3</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>80.7</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>484000</v>
+        <v>441000</v>
       </c>
       <c r="G23" s="7">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="H23" s="7">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="I23" s="7">
-        <v>15286</v>
+        <v>19231</v>
       </c>
       <c r="J23" s="5">
-        <v>68.2</v>
+        <v>68</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>83.59999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>1890000</v>
+        <v>810000</v>
       </c>
       <c r="G24" s="7">
-        <v>41000</v>
+        <v>18000</v>
       </c>
       <c r="H24" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" s="7">
-        <v>8400</v>
+        <v>11742</v>
       </c>
       <c r="J24" s="5">
-        <v>68.09999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,23 +1419,23 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>75.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>424000</v>
+        <v>497000</v>
       </c>
       <c r="G25" s="7">
-        <v>18000</v>
+        <v>13000</v>
       </c>
       <c r="H25" s="7">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I25" s="7">
-        <v>26250</v>
+        <v>15133</v>
       </c>
       <c r="J25" s="5">
         <v>67.90000000000001</v>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>77.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>661000</v>
+        <v>673000</v>
       </c>
       <c r="G26" s="7">
-        <v>14000</v>
+        <v>-9000</v>
       </c>
       <c r="H26" s="7">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="I26" s="7">
-        <v>19050</v>
+        <v>36500</v>
       </c>
       <c r="J26" s="5">
-        <v>67.59999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>77.2</v>
+        <v>78</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>432000</v>
+        <v>415000</v>
       </c>
       <c r="G27" s="7">
-        <v>3000</v>
+        <v>13000</v>
       </c>
       <c r="H27" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I27" s="7">
-        <v>20083</v>
+        <v>19429</v>
       </c>
       <c r="J27" s="5">
-        <v>67.5</v>
+        <v>67.8</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>78.7</v>
+        <v>78.5</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>284000</v>
+        <v>423000</v>
       </c>
       <c r="G28" s="7">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="H28" s="7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I28" s="7">
-        <v>16455</v>
+        <v>18125</v>
       </c>
       <c r="J28" s="5">
-        <v>67.40000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,23 +1551,23 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>75.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>298000</v>
+        <v>1075000</v>
       </c>
       <c r="G29" s="7">
-        <v>14000</v>
+        <v>-20000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="I29" s="7">
-        <v>22333</v>
+        <v>20032</v>
       </c>
       <c r="J29" s="5">
         <v>67.2</v>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>80.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>274000</v>
+        <v>793000</v>
       </c>
       <c r="G30" s="7">
-        <v>13000</v>
+        <v>15000</v>
       </c>
       <c r="H30" s="7">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="I30" s="7">
-        <v>11818</v>
+        <v>19455</v>
       </c>
       <c r="J30" s="5">
-        <v>67.2</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>76.59999999999999</v>
+        <v>79.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>778000</v>
+        <v>285000</v>
       </c>
       <c r="G31" s="7">
-        <v>16000</v>
+        <v>22000</v>
       </c>
       <c r="H31" s="7">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="I31" s="7">
-        <v>19667</v>
+        <v>20000</v>
       </c>
       <c r="J31" s="5">
-        <v>67</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>81.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>893000</v>
+        <v>916000</v>
       </c>
       <c r="G32" s="7">
-        <v>26000</v>
+        <v>23000</v>
       </c>
       <c r="H32" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I32" s="7">
-        <v>7233</v>
+        <v>7742</v>
       </c>
       <c r="J32" s="5">
-        <v>66.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>77</v>
+        <v>75.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>739000</v>
+        <v>312000</v>
       </c>
       <c r="G33" s="7">
-        <v>-5000</v>
+        <v>14000</v>
       </c>
       <c r="H33" s="7">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="I33" s="7">
-        <v>18217</v>
+        <v>21143</v>
       </c>
       <c r="J33" s="5">
-        <v>66.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>75.3</v>
+        <v>76.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>316000</v>
+        <v>733000</v>
       </c>
       <c r="G34" s="7">
-        <v>11000</v>
+        <v>-6000</v>
       </c>
       <c r="H34" s="7">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="I34" s="7">
-        <v>21818</v>
+        <v>17208</v>
       </c>
       <c r="J34" s="5">
-        <v>66.90000000000001</v>
+        <v>66.5</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>75.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>1095000</v>
+        <v>284000</v>
       </c>
       <c r="G35" s="7">
-        <v>-35000</v>
+        <v>10000</v>
       </c>
       <c r="H35" s="7">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I35" s="7">
-        <v>21367</v>
+        <v>11667</v>
       </c>
       <c r="J35" s="5">
-        <v>66.8</v>
+        <v>66.5</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>75.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>733000</v>
+        <v>661000</v>
       </c>
       <c r="G36" s="7">
-        <v>-27000</v>
+        <v>0</v>
       </c>
       <c r="H36" s="7">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="I36" s="7">
-        <v>20412</v>
+        <v>18143</v>
       </c>
       <c r="J36" s="5">
-        <v>66.8</v>
+        <v>65.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>76.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>540000</v>
+        <v>701000</v>
       </c>
       <c r="G37" s="7">
-        <v>2000</v>
+        <v>-32000</v>
       </c>
       <c r="H37" s="7">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I37" s="7">
-        <v>16500</v>
+        <v>17500</v>
       </c>
       <c r="J37" s="5">
-        <v>66.2</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1855,19 +1855,19 @@
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>454000</v>
+        <v>528000</v>
       </c>
       <c r="G38" s="7">
-        <v>17000</v>
+        <v>-8000</v>
       </c>
       <c r="H38" s="7">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I38" s="7">
-        <v>18300</v>
+        <v>16421</v>
       </c>
       <c r="J38" s="5">
-        <v>66.09999999999999</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>78.40000000000001</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>390000</v>
+        <v>879000</v>
       </c>
       <c r="G39" s="7">
-        <v>5000</v>
+        <v>30000</v>
       </c>
       <c r="H39" s="7">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="I39" s="7">
-        <v>10435</v>
+        <v>7097</v>
       </c>
       <c r="J39" s="5">
-        <v>65.7</v>
+        <v>65.3</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>80.5</v>
+        <v>76</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>343000</v>
+        <v>539000</v>
       </c>
       <c r="G40" s="7">
-        <v>12000</v>
+        <v>-1000</v>
       </c>
       <c r="H40" s="7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I40" s="7">
-        <v>5750</v>
+        <v>14000</v>
       </c>
       <c r="J40" s="5">
-        <v>65.7</v>
+        <v>65.3</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>77.8</v>
+        <v>74.3</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>320000</v>
+        <v>462000</v>
       </c>
       <c r="G41" s="7">
-        <v>16000</v>
+        <v>8000</v>
       </c>
       <c r="H41" s="7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I41" s="7">
-        <v>11083</v>
+        <v>17364</v>
       </c>
       <c r="J41" s="5">
-        <v>65.59999999999999</v>
+        <v>65.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>80.2</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>332000</v>
+        <v>392000</v>
       </c>
       <c r="G42" s="7">
-        <v>16000</v>
+        <v>31000</v>
       </c>
       <c r="H42" s="7">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I42" s="7">
-        <v>5500</v>
+        <v>42333</v>
       </c>
       <c r="J42" s="5">
-        <v>65.5</v>
+        <v>65.2</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>79.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>849000</v>
+        <v>1815000</v>
       </c>
       <c r="G43" s="7">
-        <v>34000</v>
+        <v>3000</v>
       </c>
       <c r="H43" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I43" s="7">
-        <v>6333</v>
+        <v>1000</v>
       </c>
       <c r="J43" s="5">
-        <v>65.40000000000001</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>77.5</v>
+        <v>77.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>504000</v>
+        <v>213000</v>
       </c>
       <c r="G44" s="7">
-        <v>27000</v>
+        <v>14000</v>
       </c>
       <c r="H44" s="7">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="I44" s="7">
-        <v>10667</v>
+        <v>9417</v>
       </c>
       <c r="J44" s="5">
-        <v>65.3</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>78.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>188000</v>
+        <v>349000</v>
       </c>
       <c r="G45" s="7">
-        <v>21000</v>
+        <v>6000</v>
       </c>
       <c r="H45" s="7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I45" s="7">
-        <v>9333</v>
+        <v>5765</v>
       </c>
       <c r="J45" s="5">
-        <v>65.3</v>
+        <v>64.7</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>81.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>1812000</v>
+        <v>388000</v>
       </c>
       <c r="G46" s="7">
-        <v>4000</v>
+        <v>-2000</v>
       </c>
       <c r="H46" s="7">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="I46" s="7">
-        <v>933</v>
+        <v>9917</v>
       </c>
       <c r="J46" s="5">
-        <v>65.09999999999999</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>79.8</v>
+        <v>78.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>1187000</v>
+        <v>343000</v>
       </c>
       <c r="G47" s="7">
-        <v>13000</v>
+        <v>11000</v>
       </c>
       <c r="H47" s="7">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="I47" s="7">
-        <v>4133</v>
+        <v>5824</v>
       </c>
       <c r="J47" s="5">
-        <v>64.90000000000001</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>73.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>536000</v>
+        <v>1190000</v>
       </c>
       <c r="G48" s="7">
-        <v>-19000</v>
+        <v>3000</v>
       </c>
       <c r="H48" s="7">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="I48" s="7">
-        <v>17778</v>
+        <v>4097</v>
       </c>
       <c r="J48" s="5">
-        <v>64.90000000000001</v>
+        <v>64.5</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>75.7</v>
+        <v>80.3</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>682000</v>
+        <v>805000</v>
       </c>
       <c r="G49" s="7">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H49" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I49" s="7">
-        <v>12733</v>
+        <v>1290</v>
       </c>
       <c r="J49" s="5">
-        <v>64.8</v>
+        <v>64.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>79.3</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>281000</v>
+        <v>197000</v>
       </c>
       <c r="G50" s="7">
-        <v>10000</v>
+        <v>26000</v>
       </c>
       <c r="H50" s="7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I50" s="7">
-        <v>4500</v>
+        <v>21667</v>
       </c>
       <c r="J50" s="5">
-        <v>64.7</v>
+        <v>64.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>79.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>361000</v>
+        <v>522000</v>
       </c>
       <c r="G51" s="7">
-        <v>39000</v>
+        <v>18000</v>
       </c>
       <c r="H51" s="7">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="I51" s="7">
-        <v>48000</v>
+        <v>11053</v>
       </c>
       <c r="J51" s="5">
-        <v>64.5</v>
+        <v>64.3</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>80.3</v>
+        <v>84.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>799000</v>
+        <v>312000</v>
       </c>
       <c r="G52" s="7">
-        <v>6000</v>
+        <v>22000</v>
       </c>
       <c r="H52" s="7">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="I52" s="7">
-        <v>1133</v>
+        <v>24000</v>
       </c>
       <c r="J52" s="5">
-        <v>64.40000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>77</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>366000</v>
+        <v>288000</v>
       </c>
       <c r="G53" s="7">
-        <v>-3000</v>
+        <v>19000</v>
       </c>
       <c r="H53" s="7">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7">
-        <v>7967</v>
+        <v>21500</v>
       </c>
       <c r="J53" s="5">
-        <v>64.3</v>
+        <v>64</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>79.3</v>
+        <v>76.8</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>336000</v>
+        <v>433000</v>
       </c>
       <c r="G54" s="7">
-        <v>11000</v>
+        <v>25000</v>
       </c>
       <c r="H54" s="7">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="I54" s="7">
-        <v>2900</v>
+        <v>26500</v>
       </c>
       <c r="J54" s="5">
-        <v>64.3</v>
+        <v>63.9</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-15T04:17:38+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-16T04:13:08+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -82,145 +82,145 @@
     <t>我合成了全世界</t>
   </si>
   <si>
+    <t>辍学打工，你给我AK干嘛？</t>
+  </si>
+  <si>
+    <t>神雕杨过：我以九阴九阳压天下！</t>
+  </si>
+  <si>
+    <t>全民天赋，我每年融合一个自己</t>
+  </si>
+  <si>
+    <t>我就写个网文，真没想镇压文坛啊</t>
+  </si>
+  <si>
+    <t>封神：开局反出西岐，我死守渑池</t>
+  </si>
+  <si>
+    <t>西游：开局找黄狮精买功法</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>年代1958，从搬运工开始！</t>
+  </si>
+  <si>
+    <t>你管这叫警察？重炮都架租界口了</t>
+  </si>
+  <si>
+    <t>出门捡垃圾，我被美女总裁强推了</t>
+  </si>
+  <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>末世选择：开局一亿只美洲大蠊</t>
+  </si>
+  <si>
     <t>重生年代：我怎么多了三个前妻</t>
   </si>
   <si>
-    <t>封神：开局反出西岐，我死守渑池</t>
-  </si>
-  <si>
-    <t>年代1958，从搬运工开始！</t>
-  </si>
-  <si>
-    <t>我就写个网文，真没想镇压文坛啊</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
-  </si>
-  <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>神通者</t>
-  </si>
-  <si>
-    <t>出门捡垃圾，我被美女总裁强推了</t>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>开局最弱大帝，禁区至尊被逼疯了</t>
+  </si>
+  <si>
+    <t>名义：高育良不装了，带同伟狂飙</t>
+  </si>
+  <si>
+    <t>魏家孽种成首辅，全族跪求我认祖</t>
+  </si>
+  <si>
+    <t>扫黑风暴之怒海惊涛</t>
+  </si>
+  <si>
+    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+  </si>
+  <si>
+    <t>变妹后，我成了联盟最恶女选手</t>
+  </si>
+  <si>
+    <t>这个游戏不对劲，我挖矿成神！</t>
+  </si>
+  <si>
+    <t>四合院：大家一起做禽兽</t>
+  </si>
+  <si>
+    <t>武道通神：我的增益永久生效</t>
+  </si>
+  <si>
+    <t>我都成旧日了，诡秘才入侵现实？</t>
+  </si>
+  <si>
+    <t>见鬼！求生系统把我投放到80年</t>
+  </si>
+  <si>
+    <t>大唐：憨子别动手！有话好好说！</t>
   </si>
   <si>
     <t>末世死考：开局天使魅魔三选一</t>
   </si>
   <si>
-    <t>魏家孽种成首辅，全族跪求我认祖</t>
-  </si>
-  <si>
-    <t>四合院：大家一起做禽兽</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
+    <t>名义：取代沙瑞金，拿捏汉东全局</t>
+  </si>
+  <si>
+    <t>死亡列车：开局SSS级天赋！</t>
+  </si>
+  <si>
+    <t>全民地仙：开局紫金葫芦辟福地</t>
+  </si>
+  <si>
+    <t>人在诡异，靠第四天灾登顶至高</t>
+  </si>
+  <si>
+    <t>村女苏卉：离婚后的幸福人生</t>
+  </si>
+  <si>
+    <t>年代：每日情报开局截胡女儿国王</t>
+  </si>
+  <si>
+    <t>高武：看不起斩魄刀，流刃若火呢</t>
+  </si>
+  <si>
+    <t>全民游戏，我每天一个新天赋</t>
+  </si>
+  <si>
+    <t>穿书反派，把阴湿女主养成病娇了</t>
+  </si>
+  <si>
+    <t>红楼：庶子贾琮，开局收保护费</t>
+  </si>
+  <si>
+    <t>全民神祇时代：我的词条每日刷新</t>
+  </si>
+  <si>
+    <t>全球修仙：只有我商城降价十亿倍</t>
+  </si>
+  <si>
+    <t>直播见证神话：从鳌太线走蛟开始</t>
+  </si>
+  <si>
+    <t>我都宇宙之主了，你们还在地球？</t>
   </si>
   <si>
     <t>伪人降临！我是全场唯一预言家</t>
   </si>
   <si>
-    <t>年代：每日情报开局截胡女儿国王</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
+    <t>点子王行动哥随便弟，三人行很刑</t>
+  </si>
+  <si>
+    <t>大一开学300斤，减一斤一个亿</t>
   </si>
   <si>
     <t>重生之我卖的真是高压锅</t>
-  </si>
-  <si>
-    <t>高武：看不起斩魄刀，流刃若火呢</t>
-  </si>
-  <si>
-    <t>死亡列车：开局SSS级天赋！</t>
-  </si>
-  <si>
-    <t>全民地仙：开局紫金葫芦辟福地</t>
-  </si>
-  <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>全民神祇时代：我的词条每日刷新</t>
-  </si>
-  <si>
-    <t>名义：高育良不装了，带同伟狂飙</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>末日逃亡：开局苍穹列车车长</t>
-  </si>
-  <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>火影：人在木叶村，开局觉醒木遁</t>
-  </si>
-  <si>
-    <t>直播见证神话：从鳌太线走蛟开始</t>
-  </si>
-  <si>
-    <t>从修仙回到都市，坏消息修为没了</t>
-  </si>
-  <si>
-    <t>朱标私生子，老朱逼我当皇帝！</t>
-  </si>
-  <si>
-    <t>序列：吃神者</t>
-  </si>
-  <si>
-    <t>天灾末世：我能提取神话词条</t>
-  </si>
-  <si>
-    <t>诡异乱世：大乾第一巡夜人</t>
-  </si>
-  <si>
-    <t>90年港岛电影圈！我有即梦AI</t>
-  </si>
-  <si>
-    <t>我不是戏神</t>
-  </si>
-  <si>
-    <t>东北鬼事1935</t>
-  </si>
-  <si>
-    <t>美综：谁说美剧没有人情世故？</t>
-  </si>
-  <si>
-    <t>网游：我的药剂永久持续</t>
-  </si>
-  <si>
-    <t>百岁修仙：从觉醒天灵根开始</t>
-  </si>
-  <si>
-    <t>文字武侠：开局破庙夜会帮主夫人</t>
-  </si>
-  <si>
-    <t>我以狐仙镇百鬼</t>
-  </si>
-  <si>
-    <t>精灵女王审讯录</t>
-  </si>
-  <si>
-    <t>死亡游戏：开局欺诈师，假扮神明</t>
-  </si>
-  <si>
-    <t>红楼：庶子贾琮，开局收保护费</t>
-  </si>
-  <si>
-    <t>快穿诸天我有无限背包从药神开始</t>
-  </si>
-  <si>
-    <t>疯狂状元郎，系统逼我无恶不作</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>85.5</v>
+        <v>84.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1397000</v>
+        <v>1445000</v>
       </c>
       <c r="G5" s="7">
-        <v>64000</v>
+        <v>48000</v>
       </c>
       <c r="H5" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="7">
-        <v>94000</v>
+        <v>90167</v>
       </c>
       <c r="J5" s="5">
-        <v>90.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>83.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>2180000</v>
+        <v>2200000</v>
       </c>
       <c r="G6" s="7">
-        <v>41000</v>
+        <v>20000</v>
       </c>
       <c r="H6" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I6" s="7">
-        <v>59065</v>
+        <v>57844</v>
       </c>
       <c r="J6" s="5">
-        <v>80.7</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>85.40000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>725000</v>
+        <v>766000</v>
       </c>
       <c r="G7" s="7">
-        <v>47000</v>
+        <v>41000</v>
       </c>
       <c r="H7" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="7">
-        <v>49429</v>
+        <v>48375</v>
       </c>
       <c r="J7" s="5">
-        <v>79.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>89.7</v>
+        <v>98.8</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>412000</v>
+        <v>272000</v>
       </c>
       <c r="G8" s="7">
+        <v>36000</v>
+      </c>
+      <c r="H8" s="7">
+        <v>3</v>
+      </c>
+      <c r="I8" s="7">
         <v>51000</v>
       </c>
-      <c r="H8" s="7">
-        <v>7</v>
-      </c>
-      <c r="I8" s="7">
-        <v>38500</v>
-      </c>
       <c r="J8" s="5">
-        <v>79</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>78.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>1804000</v>
+        <v>426000</v>
       </c>
       <c r="G9" s="7">
-        <v>-28000</v>
+        <v>47000</v>
       </c>
       <c r="H9" s="7">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="I9" s="7">
-        <v>50739</v>
+        <v>47000</v>
       </c>
       <c r="J9" s="5">
-        <v>76.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>86.59999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>511000</v>
+        <v>202000</v>
       </c>
       <c r="G10" s="7">
-        <v>38000</v>
+        <v>36000</v>
       </c>
       <c r="H10" s="7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I10" s="7">
-        <v>33556</v>
+        <v>45500</v>
       </c>
       <c r="J10" s="5">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>81.2</v>
+        <v>81.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>668000</v>
+        <v>701000</v>
       </c>
       <c r="G11" s="7">
-        <v>29000</v>
+        <v>33000</v>
       </c>
       <c r="H11" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I11" s="7">
-        <v>40000</v>
+        <v>39364</v>
       </c>
       <c r="J11" s="5">
-        <v>74.7</v>
+        <v>74.8</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>90.09999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>224000</v>
+        <v>1762000</v>
       </c>
       <c r="G12" s="7">
-        <v>31000</v>
+        <v>-42000</v>
       </c>
       <c r="H12" s="7">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I12" s="7">
-        <v>18444</v>
+        <v>46875</v>
       </c>
       <c r="J12" s="5">
-        <v>74.2</v>
+        <v>74.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>86.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>344000</v>
+        <v>169000</v>
       </c>
       <c r="G13" s="7">
-        <v>29000</v>
+        <v>46000</v>
       </c>
       <c r="H13" s="7">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="I13" s="7">
-        <v>26000</v>
+        <v>38000</v>
       </c>
       <c r="J13" s="5">
-        <v>73.90000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>80.8</v>
+        <v>88.3</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>821000</v>
+        <v>253000</v>
       </c>
       <c r="G14" s="7">
-        <v>23000</v>
+        <v>29000</v>
       </c>
       <c r="H14" s="7">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7">
-        <v>37067</v>
+        <v>19500</v>
       </c>
       <c r="J14" s="5">
-        <v>73.7</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>80.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>1197000</v>
+        <v>840000</v>
       </c>
       <c r="G15" s="7">
-        <v>-4000</v>
+        <v>19000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I15" s="7">
-        <v>32571</v>
+        <v>35938</v>
       </c>
       <c r="J15" s="5">
-        <v>72.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>85.2</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>2594000</v>
+        <v>528000</v>
       </c>
       <c r="G16" s="7">
-        <v>78000</v>
+        <v>17000</v>
       </c>
       <c r="H16" s="7">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="I16" s="7">
-        <v>18161</v>
+        <v>31900</v>
       </c>
       <c r="J16" s="5">
-        <v>71.40000000000001</v>
+        <v>73</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>85.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>329000</v>
+        <v>358000</v>
       </c>
       <c r="G17" s="7">
-        <v>23000</v>
+        <v>14000</v>
       </c>
       <c r="H17" s="7">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="I17" s="7">
-        <v>16062</v>
+        <v>24800</v>
       </c>
       <c r="J17" s="5">
-        <v>70.8</v>
+        <v>71.2</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>80.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>343000</v>
+        <v>354000</v>
       </c>
       <c r="G18" s="7">
-        <v>27000</v>
+        <v>25000</v>
       </c>
       <c r="H18" s="7">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="I18" s="7">
-        <v>22250</v>
+        <v>16588</v>
       </c>
       <c r="J18" s="5">
-        <v>69.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>818000</v>
+        <v>2642000</v>
       </c>
       <c r="G19" s="7">
-        <v>27000</v>
+        <v>48000</v>
       </c>
       <c r="H19" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I19" s="7">
-        <v>15226</v>
+        <v>19094</v>
       </c>
       <c r="J19" s="5">
-        <v>69.5</v>
+        <v>71</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>81.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>300000</v>
+        <v>437000</v>
       </c>
       <c r="G20" s="7">
-        <v>16000</v>
+        <v>34000</v>
       </c>
       <c r="H20" s="7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I20" s="7">
-        <v>16417</v>
+        <v>35500</v>
       </c>
       <c r="J20" s="5">
-        <v>68.90000000000001</v>
+        <v>71</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>83.7</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>1933000</v>
+        <v>1182000</v>
       </c>
       <c r="G21" s="7">
-        <v>43000</v>
+        <v>-15000</v>
       </c>
       <c r="H21" s="7">
-        <v>32</v>
+        <v>9</v>
       </c>
       <c r="I21" s="7">
-        <v>9516</v>
+        <v>26625</v>
       </c>
       <c r="J21" s="5">
-        <v>68.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>445000</v>
+        <v>414000</v>
       </c>
       <c r="G22" s="7">
-        <v>21000</v>
+        <v>2000</v>
       </c>
       <c r="H22" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>25667</v>
+        <v>33286</v>
       </c>
       <c r="J22" s="5">
-        <v>68.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>78.59999999999999</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>441000</v>
+        <v>254000</v>
       </c>
       <c r="G23" s="7">
-        <v>9000</v>
+        <v>19000</v>
       </c>
       <c r="H23" s="7">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I23" s="7">
-        <v>19231</v>
+        <v>46000</v>
       </c>
       <c r="J23" s="5">
-        <v>68</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>81.8</v>
+        <v>94.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>810000</v>
+        <v>411000</v>
       </c>
       <c r="G24" s="7">
-        <v>18000</v>
+        <v>32000</v>
       </c>
       <c r="H24" s="7">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I24" s="7">
-        <v>11742</v>
+        <v>35500</v>
       </c>
       <c r="J24" s="5">
-        <v>67.90000000000001</v>
+        <v>70</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>80.3</v>
+        <v>81.2</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>497000</v>
+        <v>303000</v>
       </c>
       <c r="G25" s="7">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="H25" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>15133</v>
+        <v>19667</v>
       </c>
       <c r="J25" s="5">
-        <v>67.90000000000001</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>70.3</v>
+        <v>82.3</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>673000</v>
+        <v>840000</v>
       </c>
       <c r="G26" s="7">
-        <v>-9000</v>
+        <v>22000</v>
       </c>
       <c r="H26" s="7">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="I26" s="7">
-        <v>36500</v>
+        <v>15438</v>
       </c>
       <c r="J26" s="5">
-        <v>67.8</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>78</v>
+        <v>98.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>415000</v>
+        <v>161000</v>
       </c>
       <c r="G27" s="7">
-        <v>13000</v>
+        <v>27000</v>
       </c>
       <c r="H27" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I27" s="7">
-        <v>19429</v>
+        <v>22500</v>
       </c>
       <c r="J27" s="5">
-        <v>67.8</v>
+        <v>68.8</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>78.5</v>
+        <v>95.3</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>423000</v>
+        <v>332000</v>
       </c>
       <c r="G28" s="7">
-        <v>5000</v>
+        <v>26000</v>
       </c>
       <c r="H28" s="7">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="I28" s="7">
-        <v>18125</v>
+        <v>27500</v>
       </c>
       <c r="J28" s="5">
-        <v>67.7</v>
+        <v>68.3</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>76.7</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>1075000</v>
+        <v>227000</v>
       </c>
       <c r="G29" s="7">
-        <v>-20000</v>
+        <v>20000</v>
       </c>
       <c r="H29" s="7">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I29" s="7">
-        <v>20032</v>
+        <v>25000</v>
       </c>
       <c r="J29" s="5">
-        <v>67.2</v>
+        <v>68.3</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>76.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>793000</v>
+        <v>1950000</v>
       </c>
       <c r="G30" s="7">
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="H30" s="7">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="I30" s="7">
-        <v>19455</v>
+        <v>9750</v>
       </c>
       <c r="J30" s="5">
-        <v>66.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>79.8</v>
+        <v>79.5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>285000</v>
+        <v>311000</v>
       </c>
       <c r="G31" s="7">
-        <v>22000</v>
+        <v>11000</v>
       </c>
       <c r="H31" s="7">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I31" s="7">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="J31" s="5">
-        <v>66.90000000000001</v>
+        <v>67.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>81.59999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>916000</v>
+        <v>234000</v>
       </c>
       <c r="G32" s="7">
-        <v>23000</v>
+        <v>25000</v>
       </c>
       <c r="H32" s="7">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I32" s="7">
-        <v>7742</v>
+        <v>24000</v>
       </c>
       <c r="J32" s="5">
-        <v>66.8</v>
+        <v>67.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>75.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>312000</v>
+        <v>153000</v>
       </c>
       <c r="G33" s="7">
-        <v>14000</v>
+        <v>26000</v>
       </c>
       <c r="H33" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I33" s="7">
-        <v>21143</v>
+        <v>17500</v>
       </c>
       <c r="J33" s="5">
-        <v>66.8</v>
+        <v>67.5</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>76.8</v>
+        <v>96.5</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>733000</v>
+        <v>211000</v>
       </c>
       <c r="G34" s="7">
-        <v>-6000</v>
+        <v>19000</v>
       </c>
       <c r="H34" s="7">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I34" s="7">
-        <v>17208</v>
+        <v>21000</v>
       </c>
       <c r="J34" s="5">
-        <v>66.5</v>
+        <v>67.3</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>79.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>284000</v>
+        <v>172000</v>
       </c>
       <c r="G35" s="7">
-        <v>10000</v>
+        <v>17000</v>
       </c>
       <c r="H35" s="7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I35" s="7">
-        <v>11667</v>
+        <v>19500</v>
       </c>
       <c r="J35" s="5">
-        <v>66.5</v>
+        <v>67.3</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>74.90000000000001</v>
+        <v>76</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>661000</v>
+        <v>354000</v>
       </c>
       <c r="G36" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H36" s="7">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="I36" s="7">
-        <v>18143</v>
+        <v>21385</v>
       </c>
       <c r="J36" s="5">
-        <v>65.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>74.90000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>701000</v>
+        <v>295000</v>
       </c>
       <c r="G37" s="7">
-        <v>-32000</v>
+        <v>28000</v>
       </c>
       <c r="H37" s="7">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I37" s="7">
-        <v>17500</v>
+        <v>24500</v>
       </c>
       <c r="J37" s="5">
-        <v>65.59999999999999</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>75.5</v>
+        <v>77</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>528000</v>
+        <v>424000</v>
       </c>
       <c r="G38" s="7">
-        <v>-8000</v>
+        <v>9000</v>
       </c>
       <c r="H38" s="7">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="I38" s="7">
-        <v>16421</v>
+        <v>18125</v>
       </c>
       <c r="J38" s="5">
-        <v>65.59999999999999</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>79.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>879000</v>
+        <v>423000</v>
       </c>
       <c r="G39" s="7">
-        <v>30000</v>
+        <v>0</v>
       </c>
       <c r="H39" s="7">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="I39" s="7">
-        <v>7097</v>
+        <v>17059</v>
       </c>
       <c r="J39" s="5">
-        <v>65.3</v>
+        <v>66.8</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>76</v>
+        <v>79.8</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>539000</v>
+        <v>812000</v>
       </c>
       <c r="G40" s="7">
-        <v>-1000</v>
+        <v>2000</v>
       </c>
       <c r="H40" s="7">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="I40" s="7">
-        <v>14000</v>
+        <v>11438</v>
       </c>
       <c r="J40" s="5">
-        <v>65.3</v>
+        <v>66.7</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>74.3</v>
+        <v>91.5</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>462000</v>
+        <v>166000</v>
       </c>
       <c r="G41" s="7">
-        <v>8000</v>
+        <v>11000</v>
       </c>
       <c r="H41" s="7">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="I41" s="7">
-        <v>17364</v>
+        <v>29500</v>
       </c>
       <c r="J41" s="5">
-        <v>65.2</v>
+        <v>66.7</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>77.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>392000</v>
+        <v>441000</v>
       </c>
       <c r="G42" s="7">
-        <v>31000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I42" s="7">
-        <v>42333</v>
+        <v>17857</v>
       </c>
       <c r="J42" s="5">
-        <v>65.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>81.5</v>
+        <v>69.7</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>1815000</v>
+        <v>660000</v>
       </c>
       <c r="G43" s="7">
-        <v>3000</v>
+        <v>-13000</v>
       </c>
       <c r="H43" s="7">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I43" s="7">
-        <v>1000</v>
+        <v>32692</v>
       </c>
       <c r="J43" s="5">
-        <v>65.09999999999999</v>
+        <v>66.5</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>77.8</v>
+        <v>95.8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>213000</v>
+        <v>221000</v>
       </c>
       <c r="G44" s="7">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="H44" s="7">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I44" s="7">
-        <v>9417</v>
+        <v>19000</v>
       </c>
       <c r="J44" s="5">
-        <v>65.09999999999999</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>78.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>349000</v>
+        <v>727000</v>
       </c>
       <c r="G45" s="7">
-        <v>6000</v>
+        <v>-6000</v>
       </c>
       <c r="H45" s="7">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I45" s="7">
-        <v>5765</v>
+        <v>16280</v>
       </c>
       <c r="J45" s="5">
-        <v>64.7</v>
+        <v>66.3</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>76.59999999999999</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>388000</v>
+        <v>331000</v>
       </c>
       <c r="G46" s="7">
-        <v>-2000</v>
+        <v>19000</v>
       </c>
       <c r="H46" s="7">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="I46" s="7">
-        <v>9917</v>
+        <v>22750</v>
       </c>
       <c r="J46" s="5">
-        <v>64.59999999999999</v>
+        <v>66.3</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>78.5</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>343000</v>
+        <v>800000</v>
       </c>
       <c r="G47" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H47" s="7">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="I47" s="7">
-        <v>5824</v>
+        <v>18913</v>
       </c>
       <c r="J47" s="5">
-        <v>64.59999999999999</v>
+        <v>66.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>1190000</v>
+        <v>616000</v>
       </c>
       <c r="G48" s="7">
-        <v>3000</v>
+        <v>24000</v>
       </c>
       <c r="H48" s="7">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="I48" s="7">
-        <v>4097</v>
+        <v>24000</v>
       </c>
       <c r="J48" s="5">
-        <v>64.5</v>
+        <v>66.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>80.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>805000</v>
+        <v>665000</v>
       </c>
       <c r="G49" s="7">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="H49" s="7">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="I49" s="7">
-        <v>1290</v>
+        <v>17500</v>
       </c>
       <c r="J49" s="5">
-        <v>64.5</v>
+        <v>66</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>85.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>197000</v>
+        <v>1039000</v>
       </c>
       <c r="G50" s="7">
-        <v>26000</v>
+        <v>-36000</v>
       </c>
       <c r="H50" s="7">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="I50" s="7">
-        <v>21667</v>
+        <v>18281</v>
       </c>
       <c r="J50" s="5">
-        <v>64.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>75.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>522000</v>
+        <v>453000</v>
       </c>
       <c r="G51" s="7">
-        <v>18000</v>
+        <v>8000</v>
       </c>
       <c r="H51" s="7">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I51" s="7">
-        <v>11053</v>
+        <v>23900</v>
       </c>
       <c r="J51" s="5">
-        <v>64.3</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84.2</v>
+        <v>79.8</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>312000</v>
+        <v>923000</v>
       </c>
       <c r="G52" s="7">
-        <v>22000</v>
+        <v>7000</v>
       </c>
       <c r="H52" s="7">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="I52" s="7">
-        <v>24000</v>
+        <v>7719</v>
       </c>
       <c r="J52" s="5">
-        <v>64.3</v>
+        <v>65.8</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>79.40000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>288000</v>
+        <v>652000</v>
       </c>
       <c r="G53" s="7">
-        <v>19000</v>
+        <v>18000</v>
       </c>
       <c r="H53" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I53" s="7">
-        <v>21500</v>
+        <v>24500</v>
       </c>
       <c r="J53" s="5">
-        <v>64</v>
+        <v>65.7</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2383,19 +2383,19 @@
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>433000</v>
+        <v>493000</v>
       </c>
       <c r="G54" s="7">
-        <v>25000</v>
+        <v>-4000</v>
       </c>
       <c r="H54" s="7">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I54" s="7">
-        <v>26500</v>
+        <v>13938</v>
       </c>
       <c r="J54" s="5">
-        <v>63.9</v>
+        <v>65.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-16T04:13:08+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-17T04:03:39+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -82,145 +82,145 @@
     <t>我合成了全世界</t>
   </si>
   <si>
-    <t>辍学打工，你给我AK干嘛？</t>
+    <t>西游：开局找黄狮精买功法</t>
   </si>
   <si>
     <t>神雕杨过：我以九阴九阳压天下！</t>
   </si>
   <si>
+    <t>开局最弱大帝，禁区至尊被逼疯了</t>
+  </si>
+  <si>
+    <t>我就写个网文，真没想镇压文坛啊</t>
+  </si>
+  <si>
+    <t>年代1958，从搬运工开始！</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
+    <t>封神：开局反出西岐，我死守渑池</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>见鬼！求生系统把我投放到80年</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>武道通神：我的增益永久生效</t>
+  </si>
+  <si>
     <t>全民天赋，我每年融合一个自己</t>
   </si>
   <si>
-    <t>我就写个网文，真没想镇压文坛啊</t>
-  </si>
-  <si>
-    <t>封神：开局反出西岐，我死守渑池</t>
-  </si>
-  <si>
-    <t>西游：开局找黄狮精买功法</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>年代1958，从搬运工开始！</t>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>全民游戏，我每天一个新天赋</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>大唐：憨子别动手！有话好好说！</t>
+  </si>
+  <si>
+    <t>穿到六零，吃瓜看戏</t>
+  </si>
+  <si>
+    <t>扫黑风暴之怒海惊涛</t>
+  </si>
+  <si>
+    <t>出门捡垃圾，我被美女总裁强推了</t>
+  </si>
+  <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>序列车队：我能无限升级奇物</t>
+  </si>
+  <si>
+    <t>名义：取代沙瑞金，拿捏汉东全局</t>
+  </si>
+  <si>
+    <t>大一开学300斤，减一斤一个亿</t>
+  </si>
+  <si>
+    <t>1955，归国带飞国家工业</t>
   </si>
   <si>
     <t>你管这叫警察？重炮都架租界口了</t>
   </si>
   <si>
-    <t>出门捡垃圾，我被美女总裁强推了</t>
-  </si>
-  <si>
-    <t>神通者</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
+    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+  </si>
+  <si>
+    <t>阴阳美人谱</t>
+  </si>
+  <si>
+    <t>重生年代：我怎么多了三个前妻</t>
+  </si>
+  <si>
+    <t>名义：高育良不装了，带同伟狂飙</t>
+  </si>
+  <si>
+    <t>我都成旧日了，诡秘才入侵现实？</t>
+  </si>
+  <si>
+    <t>高武：看不起斩魄刀，流刃若火呢</t>
+  </si>
+  <si>
+    <t>全球修仙：只有我商城降价十亿倍</t>
+  </si>
+  <si>
+    <t>全民副本：我能打造九九八十一难</t>
+  </si>
+  <si>
+    <t>港综：给兄弟花钱，我百倍返还</t>
   </si>
   <si>
     <t>末世选择：开局一亿只美洲大蠊</t>
   </si>
   <si>
-    <t>重生年代：我怎么多了三个前妻</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>开局最弱大帝，禁区至尊被逼疯了</t>
-  </si>
-  <si>
-    <t>名义：高育良不装了，带同伟狂飙</t>
-  </si>
-  <si>
-    <t>魏家孽种成首辅，全族跪求我认祖</t>
-  </si>
-  <si>
-    <t>扫黑风暴之怒海惊涛</t>
-  </si>
-  <si>
-    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
-  </si>
-  <si>
     <t>变妹后，我成了联盟最恶女选手</t>
   </si>
   <si>
+    <t>伪人降临！我是全场唯一预言家</t>
+  </si>
+  <si>
+    <t>红楼：庶子贾琮，开局收保护费</t>
+  </si>
+  <si>
+    <t>精灵女王审讯录</t>
+  </si>
+  <si>
     <t>这个游戏不对劲，我挖矿成神！</t>
   </si>
   <si>
-    <t>四合院：大家一起做禽兽</t>
-  </si>
-  <si>
-    <t>武道通神：我的增益永久生效</t>
-  </si>
-  <si>
-    <t>我都成旧日了，诡秘才入侵现实？</t>
-  </si>
-  <si>
-    <t>见鬼！求生系统把我投放到80年</t>
-  </si>
-  <si>
-    <t>大唐：憨子别动手！有话好好说！</t>
-  </si>
-  <si>
-    <t>末世死考：开局天使魅魔三选一</t>
-  </si>
-  <si>
-    <t>名义：取代沙瑞金，拿捏汉东全局</t>
-  </si>
-  <si>
-    <t>死亡列车：开局SSS级天赋！</t>
-  </si>
-  <si>
-    <t>全民地仙：开局紫金葫芦辟福地</t>
-  </si>
-  <si>
-    <t>人在诡异，靠第四天灾登顶至高</t>
-  </si>
-  <si>
     <t>村女苏卉：离婚后的幸福人生</t>
   </si>
   <si>
-    <t>年代：每日情报开局截胡女儿国王</t>
-  </si>
-  <si>
-    <t>高武：看不起斩魄刀，流刃若火呢</t>
-  </si>
-  <si>
-    <t>全民游戏，我每天一个新天赋</t>
-  </si>
-  <si>
-    <t>穿书反派，把阴湿女主养成病娇了</t>
-  </si>
-  <si>
-    <t>红楼：庶子贾琮，开局收保护费</t>
-  </si>
-  <si>
-    <t>全民神祇时代：我的词条每日刷新</t>
-  </si>
-  <si>
-    <t>全球修仙：只有我商城降价十亿倍</t>
+    <t>一人：开局复制老天师满级金光咒</t>
+  </si>
+  <si>
+    <t>九叔：让你请祖师，你请雷部天将</t>
+  </si>
+  <si>
+    <t>每日签到：这个军医什么都会</t>
+  </si>
+  <si>
+    <t>天幕洛神赋，曹家父子社死</t>
   </si>
   <si>
     <t>直播见证神话：从鳌太线走蛟开始</t>
   </si>
   <si>
-    <t>我都宇宙之主了，你们还在地球？</t>
-  </si>
-  <si>
-    <t>伪人降临！我是全场唯一预言家</t>
-  </si>
-  <si>
-    <t>点子王行动哥随便弟，三人行很刑</t>
-  </si>
-  <si>
-    <t>大一开学300斤，减一斤一个亿</t>
-  </si>
-  <si>
-    <t>重生之我卖的真是高压锅</t>
+    <t>90年港岛电影圈！我有即梦AI</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>84.2</v>
+        <v>83.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1445000</v>
+        <v>1488000</v>
       </c>
       <c r="G5" s="7">
-        <v>48000</v>
+        <v>43000</v>
       </c>
       <c r="H5" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I5" s="7">
-        <v>90167</v>
+        <v>86538</v>
       </c>
       <c r="J5" s="5">
-        <v>88.90000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>82.59999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>2200000</v>
+        <v>2214000</v>
       </c>
       <c r="G6" s="7">
-        <v>20000</v>
+        <v>14000</v>
       </c>
       <c r="H6" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I6" s="7">
-        <v>57844</v>
+        <v>56515</v>
       </c>
       <c r="J6" s="5">
-        <v>79.90000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>84.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>766000</v>
+        <v>796000</v>
       </c>
       <c r="G7" s="7">
-        <v>41000</v>
+        <v>30000</v>
       </c>
       <c r="H7" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7">
-        <v>48375</v>
+        <v>46333</v>
       </c>
       <c r="J7" s="5">
-        <v>78.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>98.8</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>272000</v>
+        <v>203000</v>
       </c>
       <c r="G8" s="7">
-        <v>36000</v>
+        <v>34000</v>
       </c>
       <c r="H8" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="7">
-        <v>51000</v>
+        <v>36667</v>
       </c>
       <c r="J8" s="5">
-        <v>76.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99.7</v>
+        <v>95.8</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>426000</v>
+        <v>458000</v>
       </c>
       <c r="G9" s="7">
-        <v>47000</v>
+        <v>32000</v>
       </c>
       <c r="H9" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="7">
-        <v>47000</v>
+        <v>42000</v>
       </c>
       <c r="J9" s="5">
-        <v>75.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>99.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>202000</v>
+        <v>454000</v>
       </c>
       <c r="G10" s="7">
-        <v>36000</v>
+        <v>43000</v>
       </c>
       <c r="H10" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="7">
-        <v>45500</v>
+        <v>38000</v>
       </c>
       <c r="J10" s="5">
-        <v>75.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>81.7</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>701000</v>
+        <v>733000</v>
       </c>
       <c r="G11" s="7">
-        <v>33000</v>
+        <v>32000</v>
       </c>
       <c r="H11" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I11" s="7">
-        <v>39364</v>
+        <v>38750</v>
       </c>
       <c r="J11" s="5">
-        <v>74.8</v>
+        <v>74.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>78.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>1762000</v>
+        <v>558000</v>
       </c>
       <c r="G12" s="7">
-        <v>-42000</v>
+        <v>30000</v>
       </c>
       <c r="H12" s="7">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I12" s="7">
-        <v>46875</v>
+        <v>31727</v>
       </c>
       <c r="J12" s="5">
-        <v>74.7</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>100</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>169000</v>
+        <v>285000</v>
       </c>
       <c r="G13" s="7">
-        <v>46000</v>
+        <v>32000</v>
       </c>
       <c r="H13" s="7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I13" s="7">
-        <v>38000</v>
+        <v>20636</v>
       </c>
       <c r="J13" s="5">
-        <v>73.5</v>
+        <v>74.2</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>88.3</v>
+        <v>78</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>253000</v>
+        <v>1720000</v>
       </c>
       <c r="G14" s="7">
-        <v>29000</v>
+        <v>-42000</v>
       </c>
       <c r="H14" s="7">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I14" s="7">
-        <v>19500</v>
+        <v>43320</v>
       </c>
       <c r="J14" s="5">
-        <v>73.40000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>80.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>840000</v>
+        <v>848000</v>
       </c>
       <c r="G15" s="7">
-        <v>19000</v>
+        <v>8000</v>
       </c>
       <c r="H15" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I15" s="7">
-        <v>35938</v>
+        <v>34294</v>
       </c>
       <c r="J15" s="5">
-        <v>73.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>81.90000000000001</v>
+        <v>98.7</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>528000</v>
+        <v>236000</v>
       </c>
       <c r="G16" s="7">
-        <v>17000</v>
+        <v>25000</v>
       </c>
       <c r="H16" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7">
-        <v>31900</v>
+        <v>22333</v>
       </c>
       <c r="J16" s="5">
-        <v>73</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>81.8</v>
+        <v>94</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>358000</v>
+        <v>462000</v>
       </c>
       <c r="G17" s="7">
-        <v>14000</v>
+        <v>25000</v>
       </c>
       <c r="H17" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I17" s="7">
-        <v>24800</v>
+        <v>32000</v>
       </c>
       <c r="J17" s="5">
-        <v>71.2</v>
+        <v>71.7</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>85.3</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>354000</v>
+        <v>264000</v>
       </c>
       <c r="G18" s="7">
-        <v>25000</v>
+        <v>30000</v>
       </c>
       <c r="H18" s="7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I18" s="7">
-        <v>16588</v>
+        <v>26000</v>
       </c>
       <c r="J18" s="5">
-        <v>71.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>84</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>2642000</v>
+        <v>216000</v>
       </c>
       <c r="G19" s="7">
-        <v>48000</v>
+        <v>14000</v>
       </c>
       <c r="H19" s="7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="I19" s="7">
-        <v>19094</v>
+        <v>35000</v>
       </c>
       <c r="J19" s="5">
-        <v>71</v>
+        <v>71.3</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>96.59999999999999</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>437000</v>
+        <v>272000</v>
       </c>
       <c r="G20" s="7">
-        <v>34000</v>
+        <v>18000</v>
       </c>
       <c r="H20" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I20" s="7">
-        <v>35500</v>
+        <v>36667</v>
       </c>
       <c r="J20" s="5">
-        <v>71</v>
+        <v>71.2</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>79.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>1182000</v>
+        <v>244000</v>
       </c>
       <c r="G21" s="7">
-        <v>-15000</v>
+        <v>23000</v>
       </c>
       <c r="H21" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I21" s="7">
-        <v>26625</v>
+        <v>20333</v>
       </c>
       <c r="J21" s="5">
-        <v>70.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>76.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>414000</v>
+        <v>252000</v>
       </c>
       <c r="G22" s="7">
-        <v>2000</v>
+        <v>25000</v>
       </c>
       <c r="H22" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I22" s="7">
-        <v>33286</v>
+        <v>20333</v>
       </c>
       <c r="J22" s="5">
-        <v>70.2</v>
+        <v>70.5</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>90.09999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>254000</v>
+        <v>191000</v>
       </c>
       <c r="G23" s="7">
         <v>19000</v>
       </c>
       <c r="H23" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I23" s="7">
-        <v>46000</v>
+        <v>19333</v>
       </c>
       <c r="J23" s="5">
-        <v>70.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>94.8</v>
+        <v>96.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>411000</v>
+        <v>108000</v>
       </c>
       <c r="G24" s="7">
-        <v>32000</v>
+        <v>17000</v>
       </c>
       <c r="H24" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I24" s="7">
-        <v>35500</v>
+        <v>21000</v>
       </c>
       <c r="J24" s="5">
-        <v>70</v>
+        <v>70.5</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>81.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>303000</v>
+        <v>180000</v>
       </c>
       <c r="G25" s="7">
-        <v>18000</v>
+        <v>19000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I25" s="7">
-        <v>19667</v>
+        <v>21333</v>
       </c>
       <c r="J25" s="5">
-        <v>69.59999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>82.3</v>
+        <v>83.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>840000</v>
+        <v>374000</v>
       </c>
       <c r="G26" s="7">
-        <v>22000</v>
+        <v>20000</v>
       </c>
       <c r="H26" s="7">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="I26" s="7">
-        <v>15438</v>
+        <v>16778</v>
       </c>
       <c r="J26" s="5">
-        <v>69.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>98.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>161000</v>
+        <v>2649000</v>
       </c>
       <c r="G27" s="7">
-        <v>27000</v>
+        <v>7000</v>
       </c>
       <c r="H27" s="7">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="I27" s="7">
-        <v>22500</v>
+        <v>18727</v>
       </c>
       <c r="J27" s="5">
-        <v>68.8</v>
+        <v>70</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>95.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>332000</v>
+        <v>333000</v>
       </c>
       <c r="G28" s="7">
-        <v>26000</v>
+        <v>27000</v>
       </c>
       <c r="H28" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I28" s="7">
-        <v>27500</v>
+        <v>21333</v>
       </c>
       <c r="J28" s="5">
-        <v>68.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>96.40000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>227000</v>
+        <v>321000</v>
       </c>
       <c r="G29" s="7">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="H29" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I29" s="7">
         <v>25000</v>
       </c>
       <c r="J29" s="5">
-        <v>68.3</v>
+        <v>69.8</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>82.3</v>
+        <v>93</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>1950000</v>
+        <v>677000</v>
       </c>
       <c r="G30" s="7">
-        <v>17000</v>
+        <v>25000</v>
       </c>
       <c r="H30" s="7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="I30" s="7">
-        <v>9750</v>
+        <v>24667</v>
       </c>
       <c r="J30" s="5">
-        <v>67.7</v>
+        <v>69.3</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>79.5</v>
+        <v>93.7</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>311000</v>
+        <v>487000</v>
       </c>
       <c r="G31" s="7">
-        <v>11000</v>
+        <v>28000</v>
       </c>
       <c r="H31" s="7">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I31" s="7">
-        <v>16000</v>
+        <v>23000</v>
       </c>
       <c r="J31" s="5">
-        <v>67.7</v>
+        <v>69.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>95.5</v>
+        <v>79.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>234000</v>
+        <v>363000</v>
       </c>
       <c r="G32" s="7">
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="H32" s="7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I32" s="7">
-        <v>24000</v>
+        <v>23000</v>
       </c>
       <c r="J32" s="5">
-        <v>67.5</v>
+        <v>69.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>98.40000000000001</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>153000</v>
+        <v>352000</v>
       </c>
       <c r="G33" s="7">
-        <v>26000</v>
+        <v>20000</v>
       </c>
       <c r="H33" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I33" s="7">
-        <v>17500</v>
+        <v>25000</v>
       </c>
       <c r="J33" s="5">
-        <v>67.5</v>
+        <v>69.3</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>96.5</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>211000</v>
+        <v>252000</v>
       </c>
       <c r="G34" s="7">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="H34" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I34" s="7">
-        <v>21000</v>
+        <v>18333</v>
       </c>
       <c r="J34" s="5">
-        <v>67.3</v>
+        <v>69.2</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>97.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>172000</v>
+        <v>415000</v>
       </c>
       <c r="G35" s="7">
-        <v>17000</v>
+        <v>1000</v>
       </c>
       <c r="H35" s="7">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>19500</v>
+        <v>29250</v>
       </c>
       <c r="J35" s="5">
-        <v>67.3</v>
+        <v>69</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>76</v>
+        <v>80.5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>354000</v>
+        <v>317000</v>
       </c>
       <c r="G36" s="7">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="H36" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>21385</v>
+        <v>18857</v>
       </c>
       <c r="J36" s="5">
-        <v>67.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>94.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>295000</v>
+        <v>171000</v>
       </c>
       <c r="G37" s="7">
-        <v>28000</v>
+        <v>18000</v>
       </c>
       <c r="H37" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I37" s="7">
-        <v>24500</v>
+        <v>17667</v>
       </c>
       <c r="J37" s="5">
-        <v>67.09999999999999</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>77</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>424000</v>
+        <v>671000</v>
       </c>
       <c r="G38" s="7">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="H38" s="7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I38" s="7">
-        <v>18125</v>
+        <v>31143</v>
       </c>
       <c r="J38" s="5">
-        <v>66.90000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>77.3</v>
+        <v>92.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>423000</v>
+        <v>636000</v>
       </c>
       <c r="G39" s="7">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="H39" s="7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I39" s="7">
-        <v>17059</v>
+        <v>22667</v>
       </c>
       <c r="J39" s="5">
-        <v>66.8</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>79.8</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>812000</v>
+        <v>284000</v>
       </c>
       <c r="G40" s="7">
-        <v>2000</v>
+        <v>19000</v>
       </c>
       <c r="H40" s="7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>11438</v>
+        <v>17333</v>
       </c>
       <c r="J40" s="5">
-        <v>66.7</v>
+        <v>68.3</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>91.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>166000</v>
+        <v>317000</v>
       </c>
       <c r="G41" s="7">
-        <v>11000</v>
+        <v>26000</v>
       </c>
       <c r="H41" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I41" s="7">
-        <v>29500</v>
+        <v>20000</v>
       </c>
       <c r="J41" s="5">
-        <v>66.7</v>
+        <v>68.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>76.59999999999999</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>441000</v>
+        <v>1156000</v>
       </c>
       <c r="G42" s="7">
-        <v>0</v>
+        <v>-26000</v>
       </c>
       <c r="H42" s="7">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I42" s="7">
-        <v>17857</v>
+        <v>20778</v>
       </c>
       <c r="J42" s="5">
-        <v>66.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>69.7</v>
+        <v>92.2</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>660000</v>
+        <v>241000</v>
       </c>
       <c r="G43" s="7">
-        <v>-13000</v>
+        <v>14000</v>
       </c>
       <c r="H43" s="7">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I43" s="7">
-        <v>32692</v>
+        <v>21333</v>
       </c>
       <c r="J43" s="5">
-        <v>66.5</v>
+        <v>68</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>95.8</v>
+        <v>76.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>221000</v>
+        <v>477000</v>
       </c>
       <c r="G44" s="7">
-        <v>20000</v>
+        <v>24000</v>
       </c>
       <c r="H44" s="7">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I44" s="7">
-        <v>19000</v>
+        <v>23909</v>
       </c>
       <c r="J44" s="5">
-        <v>66.40000000000001</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>76.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>727000</v>
+        <v>345000</v>
       </c>
       <c r="G45" s="7">
-        <v>-6000</v>
+        <v>14000</v>
       </c>
       <c r="H45" s="7">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="I45" s="7">
-        <v>16280</v>
+        <v>21000</v>
       </c>
       <c r="J45" s="5">
-        <v>66.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>82.90000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>331000</v>
+        <v>227000</v>
       </c>
       <c r="G46" s="7">
+        <v>18000</v>
+      </c>
+      <c r="H46" s="7">
+        <v>6</v>
+      </c>
+      <c r="I46" s="7">
         <v>19000</v>
       </c>
-      <c r="H46" s="7">
-        <v>5</v>
-      </c>
-      <c r="I46" s="7">
-        <v>22750</v>
-      </c>
       <c r="J46" s="5">
-        <v>66.3</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>75.40000000000001</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>800000</v>
+        <v>1962000</v>
       </c>
       <c r="G47" s="7">
-        <v>7000</v>
+        <v>12000</v>
       </c>
       <c r="H47" s="7">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="I47" s="7">
-        <v>18913</v>
+        <v>9818</v>
       </c>
       <c r="J47" s="5">
-        <v>66.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>93</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>616000</v>
+        <v>177000</v>
       </c>
       <c r="G48" s="7">
-        <v>24000</v>
+        <v>11000</v>
       </c>
       <c r="H48" s="7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I48" s="7">
-        <v>24000</v>
+        <v>23333</v>
       </c>
       <c r="J48" s="5">
-        <v>66.2</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>75.59999999999999</v>
+        <v>95.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>665000</v>
+        <v>159000</v>
       </c>
       <c r="G49" s="7">
-        <v>4000</v>
+        <v>36000</v>
       </c>
       <c r="H49" s="7">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="I49" s="7">
-        <v>17500</v>
+        <v>12667</v>
       </c>
       <c r="J49" s="5">
-        <v>66</v>
+        <v>67.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>75.09999999999999</v>
+        <v>93.3</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>1039000</v>
+        <v>319000</v>
       </c>
       <c r="G50" s="7">
-        <v>-36000</v>
+        <v>22000</v>
       </c>
       <c r="H50" s="7">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="I50" s="7">
-        <v>18281</v>
+        <v>16333</v>
       </c>
       <c r="J50" s="5">
-        <v>65.90000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>72.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>453000</v>
+        <v>202000</v>
       </c>
       <c r="G51" s="7">
-        <v>8000</v>
+        <v>21000</v>
       </c>
       <c r="H51" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I51" s="7">
-        <v>23900</v>
+        <v>20333</v>
       </c>
       <c r="J51" s="5">
-        <v>65.90000000000001</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>79.8</v>
+        <v>80.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>923000</v>
+        <v>276000</v>
       </c>
       <c r="G52" s="7">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H52" s="7">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="I52" s="7">
-        <v>7719</v>
+        <v>18400</v>
       </c>
       <c r="J52" s="5">
-        <v>65.8</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>91.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>652000</v>
+        <v>679000</v>
       </c>
       <c r="G53" s="7">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="H53" s="7">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="I53" s="7">
-        <v>24500</v>
+        <v>17348</v>
       </c>
       <c r="J53" s="5">
-        <v>65.7</v>
+        <v>66.7</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>76.8</v>
+        <v>74.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>493000</v>
+        <v>423000</v>
       </c>
       <c r="G54" s="7">
-        <v>-4000</v>
+        <v>18000</v>
       </c>
       <c r="H54" s="7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I54" s="7">
-        <v>13938</v>
+        <v>31600</v>
       </c>
       <c r="J54" s="5">
-        <v>65.7</v>
+        <v>66.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-17T04:03:39+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-18T04:10:31+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
+    <t>神雕杨过：我以九阴九阳压天下！</t>
+  </si>
+  <si>
+    <t>重生年代：我怎么多了三个前妻</t>
+  </si>
+  <si>
+    <t>村女苏卉：离婚后的幸福人生</t>
+  </si>
+  <si>
+    <t>扫黑风暴之怒海惊涛</t>
+  </si>
+  <si>
+    <t>西游：开局找黄狮精买功法</t>
+  </si>
+  <si>
+    <t>见鬼！求生系统把我投放到80年</t>
+  </si>
+  <si>
+    <t>武道通神：我的增益永久生效</t>
+  </si>
+  <si>
+    <t>我都成旧日了，诡秘才入侵现实？</t>
+  </si>
+  <si>
     <t>我合成了全世界</t>
   </si>
   <si>
-    <t>西游：开局找黄狮精买功法</t>
-  </si>
-  <si>
-    <t>神雕杨过：我以九阴九阳压天下！</t>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>名义：取代沙瑞金，拿捏汉东全局</t>
+  </si>
+  <si>
+    <t>穿到六零，吃瓜看戏</t>
+  </si>
+  <si>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>我就写个网文，真没想镇压文坛啊</t>
+  </si>
+  <si>
+    <t>年代1958，从搬运工开始！</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>变妹后，我成了联盟最恶女选手</t>
+  </si>
+  <si>
+    <t>精灵女王审讯录</t>
+  </si>
+  <si>
+    <t>大唐：憨子别动手！有话好好说！</t>
+  </si>
+  <si>
+    <t>全球修仙：只有我商城降价十亿倍</t>
+  </si>
+  <si>
+    <t>序列车队：我能无限升级奇物</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
   </si>
   <si>
     <t>开局最弱大帝，禁区至尊被逼疯了</t>
   </si>
   <si>
-    <t>我就写个网文，真没想镇压文坛啊</t>
-  </si>
-  <si>
-    <t>年代1958，从搬运工开始！</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
+    <t>1955，归国带飞国家工业</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+  </si>
+  <si>
+    <t>伪人降临！我是全场唯一预言家</t>
+  </si>
+  <si>
+    <t>全民游戏，我每天一个新天赋</t>
+  </si>
+  <si>
+    <t>九叔：让你请祖师，你请雷部天将</t>
+  </si>
+  <si>
+    <t>一人：开局复制老天师满级金光咒</t>
+  </si>
+  <si>
+    <t>全民天赋，我每年融合一个自己</t>
+  </si>
+  <si>
+    <t>全民副本：我能打造九九八十一难</t>
+  </si>
+  <si>
+    <t>四合院：1948年开局暴富躺平</t>
+  </si>
+  <si>
+    <t>阴阳美人谱</t>
+  </si>
+  <si>
+    <t>神通者</t>
   </si>
   <si>
     <t>封神：开局反出西岐，我死守渑池</t>
   </si>
   <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>见鬼！求生系统把我投放到80年</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>武道通神：我的增益永久生效</t>
-  </si>
-  <si>
-    <t>全民天赋，我每年融合一个自己</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>全民游戏，我每天一个新天赋</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>大唐：憨子别动手！有话好好说！</t>
-  </si>
-  <si>
-    <t>穿到六零，吃瓜看戏</t>
-  </si>
-  <si>
-    <t>扫黑风暴之怒海惊涛</t>
-  </si>
-  <si>
-    <t>出门捡垃圾，我被美女总裁强推了</t>
-  </si>
-  <si>
-    <t>神通者</t>
-  </si>
-  <si>
-    <t>序列车队：我能无限升级奇物</t>
-  </si>
-  <si>
-    <t>名义：取代沙瑞金，拿捏汉东全局</t>
-  </si>
-  <si>
-    <t>大一开学300斤，减一斤一个亿</t>
-  </si>
-  <si>
-    <t>1955，归国带飞国家工业</t>
+    <t>港综：给兄弟花钱，我百倍返还</t>
+  </si>
+  <si>
+    <t>红楼：庶子贾琮，开局收保护费</t>
+  </si>
+  <si>
+    <t>修仙家族：从打下一片位面开始</t>
+  </si>
+  <si>
+    <t>型月：未婚妻露维亚，抽爆FGO</t>
+  </si>
+  <si>
+    <t>沉睡万年，逆徒皆成大帝</t>
   </si>
   <si>
     <t>你管这叫警察？重炮都架租界口了</t>
   </si>
   <si>
-    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
-  </si>
-  <si>
-    <t>阴阳美人谱</t>
-  </si>
-  <si>
-    <t>重生年代：我怎么多了三个前妻</t>
+    <t>大春不傻了，全村都慌了</t>
+  </si>
+  <si>
+    <t>辍学打工，你给我AK干嘛？</t>
+  </si>
+  <si>
+    <t>天幕洛神赋，曹家父子社死</t>
+  </si>
+  <si>
+    <t>村女赵秀丽</t>
   </si>
   <si>
     <t>名义：高育良不装了，带同伟狂飙</t>
   </si>
   <si>
-    <t>我都成旧日了，诡秘才入侵现实？</t>
-  </si>
-  <si>
-    <t>高武：看不起斩魄刀，流刃若火呢</t>
-  </si>
-  <si>
-    <t>全球修仙：只有我商城降价十亿倍</t>
-  </si>
-  <si>
-    <t>全民副本：我能打造九九八十一难</t>
-  </si>
-  <si>
-    <t>港综：给兄弟花钱，我百倍返还</t>
-  </si>
-  <si>
-    <t>末世选择：开局一亿只美洲大蠊</t>
-  </si>
-  <si>
-    <t>变妹后，我成了联盟最恶女选手</t>
-  </si>
-  <si>
-    <t>伪人降临！我是全场唯一预言家</t>
-  </si>
-  <si>
-    <t>红楼：庶子贾琮，开局收保护费</t>
-  </si>
-  <si>
-    <t>精灵女王审讯录</t>
-  </si>
-  <si>
-    <t>这个游戏不对劲，我挖矿成神！</t>
-  </si>
-  <si>
-    <t>村女苏卉：离婚后的幸福人生</t>
-  </si>
-  <si>
-    <t>一人：开局复制老天师满级金光咒</t>
-  </si>
-  <si>
-    <t>九叔：让你请祖师，你请雷部天将</t>
-  </si>
-  <si>
     <t>每日签到：这个军医什么都会</t>
-  </si>
-  <si>
-    <t>天幕洛神赋，曹家父子社死</t>
-  </si>
-  <si>
-    <t>直播见证神话：从鳌太线走蛟开始</t>
-  </si>
-  <si>
-    <t>90年港岛电影圈！我有即梦AI</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>83.8</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1488000</v>
+        <v>1521000</v>
       </c>
       <c r="G5" s="7">
-        <v>43000</v>
+        <v>33000</v>
       </c>
       <c r="H5" s="7">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="I5" s="7">
-        <v>86538</v>
+        <v>82714</v>
       </c>
       <c r="J5" s="5">
-        <v>87.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>82.40000000000001</v>
+        <v>82.5</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>2214000</v>
+        <v>2230000</v>
       </c>
       <c r="G6" s="7">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="H6" s="7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I6" s="7">
-        <v>56515</v>
+        <v>55324</v>
       </c>
       <c r="J6" s="5">
-        <v>79.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>82.59999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>796000</v>
+        <v>499000</v>
       </c>
       <c r="G7" s="7">
-        <v>30000</v>
+        <v>41000</v>
       </c>
       <c r="H7" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I7" s="7">
-        <v>46333</v>
+        <v>41750</v>
       </c>
       <c r="J7" s="5">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>88.7</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>203000</v>
+        <v>465000</v>
       </c>
       <c r="G8" s="7">
-        <v>34000</v>
+        <v>50000</v>
       </c>
       <c r="H8" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I8" s="7">
-        <v>36667</v>
+        <v>31556</v>
       </c>
       <c r="J8" s="5">
-        <v>76.2</v>
+        <v>76.7</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>458000</v>
+        <v>210000</v>
       </c>
       <c r="G9" s="7">
-        <v>32000</v>
+        <v>33000</v>
       </c>
       <c r="H9" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I9" s="7">
-        <v>42000</v>
+        <v>25750</v>
       </c>
       <c r="J9" s="5">
-        <v>75.2</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>97.09999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>454000</v>
+        <v>209000</v>
       </c>
       <c r="G10" s="7">
-        <v>43000</v>
+        <v>29000</v>
       </c>
       <c r="H10" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7">
-        <v>38000</v>
+        <v>23250</v>
       </c>
       <c r="J10" s="5">
-        <v>74.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>81.40000000000001</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>733000</v>
+        <v>219000</v>
       </c>
       <c r="G11" s="7">
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="H11" s="7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
-        <v>38750</v>
+        <v>31500</v>
       </c>
       <c r="J11" s="5">
-        <v>74.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>84.40000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>558000</v>
+        <v>262000</v>
       </c>
       <c r="G12" s="7">
-        <v>30000</v>
+        <v>26000</v>
       </c>
       <c r="H12" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7">
-        <v>31727</v>
+        <v>23250</v>
       </c>
       <c r="J12" s="5">
-        <v>74.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>89.09999999999999</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>285000</v>
+        <v>296000</v>
       </c>
       <c r="G13" s="7">
         <v>32000</v>
       </c>
       <c r="H13" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I13" s="7">
-        <v>20636</v>
+        <v>27500</v>
       </c>
       <c r="J13" s="5">
-        <v>74.2</v>
+        <v>74.7</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>1720000</v>
+        <v>198000</v>
       </c>
       <c r="G14" s="7">
-        <v>-42000</v>
+        <v>27000</v>
       </c>
       <c r="H14" s="7">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="I14" s="7">
-        <v>43320</v>
+        <v>20000</v>
       </c>
       <c r="J14" s="5">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>78.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>848000</v>
+        <v>803000</v>
       </c>
       <c r="G15" s="7">
-        <v>8000</v>
+        <v>7000</v>
       </c>
       <c r="H15" s="7">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="I15" s="7">
-        <v>34294</v>
+        <v>42400</v>
       </c>
       <c r="J15" s="5">
-        <v>72</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>98.7</v>
+        <v>97.5</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>236000</v>
+        <v>280000</v>
       </c>
       <c r="G16" s="7">
-        <v>25000</v>
+        <v>28000</v>
       </c>
       <c r="H16" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I16" s="7">
-        <v>22333</v>
+        <v>22250</v>
       </c>
       <c r="J16" s="5">
-        <v>71.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>94</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>462000</v>
+        <v>350000</v>
       </c>
       <c r="G17" s="7">
-        <v>25000</v>
+        <v>29000</v>
       </c>
       <c r="H17" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I17" s="7">
-        <v>32000</v>
+        <v>26000</v>
       </c>
       <c r="J17" s="5">
-        <v>71.7</v>
+        <v>73.8</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>96.59999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>264000</v>
+        <v>130000</v>
       </c>
       <c r="G18" s="7">
-        <v>30000</v>
+        <v>22000</v>
       </c>
       <c r="H18" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I18" s="7">
-        <v>26000</v>
+        <v>21250</v>
       </c>
       <c r="J18" s="5">
-        <v>71.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>91.90000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>216000</v>
+        <v>291000</v>
       </c>
       <c r="G19" s="7">
-        <v>14000</v>
+        <v>19000</v>
       </c>
       <c r="H19" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I19" s="7">
-        <v>35000</v>
+        <v>32250</v>
       </c>
       <c r="J19" s="5">
-        <v>71.3</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>90.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>272000</v>
+        <v>755000</v>
       </c>
       <c r="G20" s="7">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="H20" s="7">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I20" s="7">
-        <v>36667</v>
+        <v>37462</v>
       </c>
       <c r="J20" s="5">
-        <v>71.2</v>
+        <v>73.3</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>97.3</v>
+        <v>82.8</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>244000</v>
+        <v>580000</v>
       </c>
       <c r="G21" s="7">
-        <v>23000</v>
+        <v>22000</v>
       </c>
       <c r="H21" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I21" s="7">
-        <v>20333</v>
+        <v>30917</v>
       </c>
       <c r="J21" s="5">
-        <v>70.59999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>97.2</v>
+        <v>81</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>252000</v>
+        <v>873000</v>
       </c>
       <c r="G22" s="7">
         <v>25000</v>
       </c>
       <c r="H22" s="7">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="I22" s="7">
-        <v>20333</v>
+        <v>33778</v>
       </c>
       <c r="J22" s="5">
-        <v>70.5</v>
+        <v>73</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>97.5</v>
+        <v>95.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>191000</v>
+        <v>262000</v>
       </c>
       <c r="G23" s="7">
-        <v>19000</v>
+        <v>21000</v>
       </c>
       <c r="H23" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" s="7">
-        <v>19333</v>
+        <v>21250</v>
       </c>
       <c r="J23" s="5">
-        <v>70.5</v>
+        <v>73</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>96.8</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>108000</v>
+        <v>257000</v>
       </c>
       <c r="G24" s="7">
-        <v>17000</v>
+        <v>30000</v>
       </c>
       <c r="H24" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I24" s="7">
-        <v>21000</v>
+        <v>20833</v>
       </c>
       <c r="J24" s="5">
-        <v>70.5</v>
+        <v>73</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>96.40000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>180000</v>
+        <v>210000</v>
       </c>
       <c r="G25" s="7">
         <v>19000</v>
       </c>
       <c r="H25" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" s="7">
-        <v>21333</v>
+        <v>19250</v>
       </c>
       <c r="J25" s="5">
-        <v>70.40000000000001</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>83.5</v>
+        <v>93.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>374000</v>
+        <v>666000</v>
       </c>
       <c r="G26" s="7">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="H26" s="7">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="I26" s="7">
-        <v>16778</v>
+        <v>24500</v>
       </c>
       <c r="J26" s="5">
-        <v>70.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>82.40000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>2649000</v>
+        <v>358000</v>
       </c>
       <c r="G27" s="7">
-        <v>7000</v>
+        <v>25000</v>
       </c>
       <c r="H27" s="7">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="I27" s="7">
-        <v>18727</v>
+        <v>22250</v>
       </c>
       <c r="J27" s="5">
-        <v>70</v>
+        <v>72.5</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>95.59999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>333000</v>
+        <v>311000</v>
       </c>
       <c r="G28" s="7">
-        <v>27000</v>
+        <v>26000</v>
       </c>
       <c r="H28" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I28" s="7">
-        <v>21333</v>
+        <v>21083</v>
       </c>
       <c r="J28" s="5">
-        <v>69.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>93.8</v>
+        <v>89.5</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>321000</v>
+        <v>467000</v>
       </c>
       <c r="G29" s="7">
-        <v>26000</v>
+        <v>13000</v>
       </c>
       <c r="H29" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I29" s="7">
-        <v>25000</v>
+        <v>31750</v>
       </c>
       <c r="J29" s="5">
-        <v>69.8</v>
+        <v>72.2</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>93</v>
+        <v>93.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>677000</v>
+        <v>510000</v>
       </c>
       <c r="G30" s="7">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="H30" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>24667</v>
+        <v>23000</v>
       </c>
       <c r="J30" s="5">
-        <v>69.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>93.7</v>
+        <v>91.2</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>487000</v>
+        <v>475000</v>
       </c>
       <c r="G31" s="7">
-        <v>28000</v>
+        <v>13000</v>
       </c>
       <c r="H31" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I31" s="7">
-        <v>23000</v>
+        <v>27250</v>
       </c>
       <c r="J31" s="5">
-        <v>69.3</v>
+        <v>72</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>79.2</v>
+        <v>92.7</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>363000</v>
+        <v>372000</v>
       </c>
       <c r="G32" s="7">
-        <v>5000</v>
+        <v>20000</v>
       </c>
       <c r="H32" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I32" s="7">
-        <v>23000</v>
+        <v>23750</v>
       </c>
       <c r="J32" s="5">
-        <v>69.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.90000000000001</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>352000</v>
+        <v>523000</v>
       </c>
       <c r="G33" s="7">
-        <v>20000</v>
+        <v>46000</v>
       </c>
       <c r="H33" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I33" s="7">
-        <v>25000</v>
+        <v>25750</v>
       </c>
       <c r="J33" s="5">
-        <v>69.3</v>
+        <v>71.3</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>95.59999999999999</v>
+        <v>92.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>252000</v>
+        <v>260000</v>
       </c>
       <c r="G34" s="7">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="H34" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I34" s="7">
-        <v>18333</v>
+        <v>19250</v>
       </c>
       <c r="J34" s="5">
-        <v>69.2</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>75.8</v>
+        <v>93.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>415000</v>
+        <v>342000</v>
       </c>
       <c r="G35" s="7">
-        <v>1000</v>
+        <v>23000</v>
       </c>
       <c r="H35" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I35" s="7">
-        <v>29250</v>
+        <v>18000</v>
       </c>
       <c r="J35" s="5">
-        <v>69</v>
+        <v>70.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>80.5</v>
+        <v>94.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>317000</v>
+        <v>179000</v>
       </c>
       <c r="G36" s="7">
-        <v>14000</v>
+        <v>20000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I36" s="7">
-        <v>18857</v>
+        <v>14500</v>
       </c>
       <c r="J36" s="5">
-        <v>69</v>
+        <v>70.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>95.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>171000</v>
+        <v>223000</v>
       </c>
       <c r="G37" s="7">
-        <v>18000</v>
+        <v>7000</v>
       </c>
       <c r="H37" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I37" s="7">
-        <v>17667</v>
+        <v>28000</v>
       </c>
       <c r="J37" s="5">
-        <v>68.90000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>74.09999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>671000</v>
+        <v>299000</v>
       </c>
       <c r="G38" s="7">
-        <v>11000</v>
+        <v>15000</v>
       </c>
       <c r="H38" s="7">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="I38" s="7">
-        <v>31143</v>
+        <v>16750</v>
       </c>
       <c r="J38" s="5">
-        <v>68.5</v>
+        <v>70.2</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>92.3</v>
+        <v>94.7</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>636000</v>
+        <v>190000</v>
       </c>
       <c r="G39" s="7">
-        <v>20000</v>
+        <v>30000</v>
       </c>
       <c r="H39" s="7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I39" s="7">
-        <v>22667</v>
+        <v>36500</v>
       </c>
       <c r="J39" s="5">
-        <v>68.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>94.40000000000001</v>
+        <v>92.3</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>284000</v>
+        <v>265000</v>
       </c>
       <c r="G40" s="7">
-        <v>19000</v>
+        <v>13000</v>
       </c>
       <c r="H40" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I40" s="7">
-        <v>17333</v>
+        <v>17000</v>
       </c>
       <c r="J40" s="5">
-        <v>68.3</v>
+        <v>70</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>93.09999999999999</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>317000</v>
+        <v>2656000</v>
       </c>
       <c r="G41" s="7">
-        <v>26000</v>
+        <v>7000</v>
       </c>
       <c r="H41" s="7">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I41" s="7">
-        <v>20000</v>
+        <v>18382</v>
       </c>
       <c r="J41" s="5">
-        <v>68.2</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>78.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>1156000</v>
+        <v>1534000</v>
       </c>
       <c r="G42" s="7">
-        <v>-26000</v>
+        <v>-186000</v>
       </c>
       <c r="H42" s="7">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="I42" s="7">
-        <v>20778</v>
+        <v>34500</v>
       </c>
       <c r="J42" s="5">
-        <v>68.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>92.2</v>
+        <v>90.8</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>241000</v>
+        <v>335000</v>
       </c>
       <c r="G43" s="7">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="H43" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I43" s="7">
-        <v>21333</v>
+        <v>19500</v>
       </c>
       <c r="J43" s="5">
-        <v>68</v>
+        <v>69.8</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>76.2</v>
+        <v>81.3</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>477000</v>
+        <v>360000</v>
       </c>
       <c r="G44" s="7">
-        <v>24000</v>
+        <v>15000</v>
       </c>
       <c r="H44" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I44" s="7">
-        <v>23909</v>
+        <v>20000</v>
       </c>
       <c r="J44" s="5">
-        <v>67.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>81.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>345000</v>
+        <v>108000</v>
       </c>
       <c r="G45" s="7">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="H45" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I45" s="7">
-        <v>21000</v>
+        <v>7500</v>
       </c>
       <c r="J45" s="5">
-        <v>67.90000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>82.09999999999999</v>
+        <v>92.3</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>227000</v>
+        <v>157000</v>
       </c>
       <c r="G46" s="7">
         <v>18000</v>
       </c>
       <c r="H46" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I46" s="7">
-        <v>19000</v>
+        <v>14500</v>
       </c>
       <c r="J46" s="5">
-        <v>67.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>82.09999999999999</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>1962000</v>
+        <v>100000</v>
       </c>
       <c r="G47" s="7">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="H47" s="7">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="I47" s="7">
-        <v>9818</v>
+        <v>15000</v>
       </c>
       <c r="J47" s="5">
-        <v>67.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>90.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>177000</v>
+        <v>369000</v>
       </c>
       <c r="G48" s="7">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I48" s="7">
-        <v>23333</v>
+        <v>21583</v>
       </c>
       <c r="J48" s="5">
-        <v>67.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>95.2</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>159000</v>
+        <v>104000</v>
       </c>
       <c r="G49" s="7">
-        <v>36000</v>
+        <v>11000</v>
       </c>
       <c r="H49" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I49" s="7">
-        <v>12667</v>
+        <v>7750</v>
       </c>
       <c r="J49" s="5">
-        <v>67.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>93.3</v>
+        <v>77.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>319000</v>
+        <v>352000</v>
       </c>
       <c r="G50" s="7">
-        <v>22000</v>
+        <v>40000</v>
       </c>
       <c r="H50" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I50" s="7">
-        <v>16333</v>
+        <v>45500</v>
       </c>
       <c r="J50" s="5">
-        <v>67.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>91.5</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>202000</v>
+        <v>292000</v>
       </c>
       <c r="G51" s="7">
-        <v>21000</v>
+        <v>16000</v>
       </c>
       <c r="H51" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I51" s="7">
-        <v>20333</v>
+        <v>18000</v>
       </c>
       <c r="J51" s="5">
-        <v>67.40000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>80.5</v>
+        <v>96.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>276000</v>
+        <v>119000</v>
       </c>
       <c r="G52" s="7">
-        <v>15000</v>
+        <v>27000</v>
       </c>
       <c r="H52" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I52" s="7">
-        <v>18400</v>
+        <v>27500</v>
       </c>
       <c r="J52" s="5">
-        <v>66.90000000000001</v>
+        <v>68.8</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>77.09999999999999</v>
+        <v>80.3</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>679000</v>
+        <v>331000</v>
       </c>
       <c r="G53" s="7">
         <v>14000</v>
       </c>
       <c r="H53" s="7">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I53" s="7">
-        <v>17348</v>
+        <v>18250</v>
       </c>
       <c r="J53" s="5">
-        <v>66.7</v>
+        <v>68.7</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>74.2</v>
+        <v>88.8</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>423000</v>
+        <v>218000</v>
       </c>
       <c r="G54" s="7">
-        <v>18000</v>
+        <v>16000</v>
       </c>
       <c r="H54" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I54" s="7">
-        <v>31600</v>
+        <v>19250</v>
       </c>
       <c r="J54" s="5">
-        <v>66.7</v>
+        <v>68.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-18T04:10:31+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-19T04:19:50+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>神雕杨过：我以九阴九阳压天下！</t>
+  </si>
+  <si>
+    <t>重生年代：我怎么多了三个前妻</t>
+  </si>
+  <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
-    <t>神雕杨过：我以九阴九阳压天下！</t>
-  </si>
-  <si>
-    <t>重生年代：我怎么多了三个前妻</t>
+    <t>见鬼！求生系统把我投放到80年</t>
+  </si>
+  <si>
+    <t>型月：未婚妻露维亚，抽爆FGO</t>
+  </si>
+  <si>
+    <t>名义：取代沙瑞金，拿捏汉东全局</t>
+  </si>
+  <si>
+    <t>穿到六零，吃瓜看戏</t>
+  </si>
+  <si>
+    <t>全球修仙：只有我商城降价十亿倍</t>
+  </si>
+  <si>
+    <t>武道通神：我的增益永久生效</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>扫黑风暴之怒海惊涛</t>
+  </si>
+  <si>
+    <t>七零替妹下乡，我觉醒了万物图鉴</t>
+  </si>
+  <si>
+    <t>1955，归国带飞国家工业</t>
+  </si>
+  <si>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
+    <t>精灵女王审讯录</t>
+  </si>
+  <si>
+    <t>变妹后，我成了联盟最恶女选手</t>
+  </si>
+  <si>
+    <t>我都成旧日了，诡秘才入侵现实？</t>
+  </si>
+  <si>
+    <t>九叔：让你请祖师，你请雷部天将</t>
+  </si>
+  <si>
+    <t>序列车队：我能无限升级奇物</t>
+  </si>
+  <si>
+    <t>我就写个网文，真没想镇压文坛啊</t>
+  </si>
+  <si>
+    <t>我合成了全世界</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>红色人生模拟，我怎么成老干部了</t>
+  </si>
+  <si>
+    <t>年代1958，从搬运工开始！</t>
+  </si>
+  <si>
+    <t>开局最弱大帝，禁区至尊被逼疯了</t>
+  </si>
+  <si>
+    <t>全民天赋，我每年融合一个自己</t>
+  </si>
+  <si>
+    <t>大秦：只想活命，始皇却逼我登基</t>
+  </si>
+  <si>
+    <t>全民副本：我能打造九九八十一难</t>
+  </si>
+  <si>
+    <t>西游：开局找黄狮精买功法</t>
+  </si>
+  <si>
+    <t>四合院：1948年开局暴富躺平</t>
+  </si>
+  <si>
+    <t>全民游戏，我每天一个新天赋</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>饥荒求生，国运垫底咋饱荒了？</t>
+  </si>
+  <si>
+    <t>村女赵秀丽</t>
+  </si>
+  <si>
+    <t>财阀大小姐的恶毒男友重生了</t>
+  </si>
+  <si>
+    <t>天幕洛神赋，曹家父子社死</t>
+  </si>
+  <si>
+    <t>每日签到：这个军医什么都会</t>
+  </si>
+  <si>
+    <t>边军悍卒，绝色罪女天天求暖床</t>
+  </si>
+  <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>大明：我一个文官你给我武将系统</t>
   </si>
   <si>
     <t>村女苏卉：离婚后的幸福人生</t>
   </si>
   <si>
-    <t>扫黑风暴之怒海惊涛</t>
-  </si>
-  <si>
-    <t>西游：开局找黄狮精买功法</t>
-  </si>
-  <si>
-    <t>见鬼！求生系统把我投放到80年</t>
-  </si>
-  <si>
-    <t>武道通神：我的增益永久生效</t>
-  </si>
-  <si>
-    <t>我都成旧日了，诡秘才入侵现实？</t>
-  </si>
-  <si>
-    <t>我合成了全世界</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>名义：取代沙瑞金，拿捏汉东全局</t>
-  </si>
-  <si>
-    <t>穿到六零，吃瓜看戏</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>我就写个网文，真没想镇压文坛啊</t>
-  </si>
-  <si>
-    <t>年代1958，从搬运工开始！</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>变妹后，我成了联盟最恶女选手</t>
-  </si>
-  <si>
-    <t>精灵女王审讯录</t>
+    <t>儒道剑仙，苟在镇北王府当赘婿</t>
   </si>
   <si>
     <t>大唐：憨子别动手！有话好好说！</t>
   </si>
   <si>
-    <t>全球修仙：只有我商城降价十亿倍</t>
-  </si>
-  <si>
-    <t>序列车队：我能无限升级奇物</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
-  </si>
-  <si>
-    <t>开局最弱大帝，禁区至尊被逼疯了</t>
-  </si>
-  <si>
-    <t>1955，归国带飞国家工业</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+    <t>一人：你苦修功法？我直接加点！</t>
+  </si>
+  <si>
+    <t>沉睡万年，逆徒皆成大帝</t>
   </si>
   <si>
     <t>伪人降临！我是全场唯一预言家</t>
-  </si>
-  <si>
-    <t>全民游戏，我每天一个新天赋</t>
-  </si>
-  <si>
-    <t>九叔：让你请祖师，你请雷部天将</t>
-  </si>
-  <si>
-    <t>一人：开局复制老天师满级金光咒</t>
-  </si>
-  <si>
-    <t>全民天赋，我每年融合一个自己</t>
-  </si>
-  <si>
-    <t>全民副本：我能打造九九八十一难</t>
-  </si>
-  <si>
-    <t>四合院：1948年开局暴富躺平</t>
-  </si>
-  <si>
-    <t>阴阳美人谱</t>
-  </si>
-  <si>
-    <t>神通者</t>
-  </si>
-  <si>
-    <t>封神：开局反出西岐，我死守渑池</t>
-  </si>
-  <si>
-    <t>港综：给兄弟花钱，我百倍返还</t>
-  </si>
-  <si>
-    <t>红楼：庶子贾琮，开局收保护费</t>
-  </si>
-  <si>
-    <t>修仙家族：从打下一片位面开始</t>
-  </si>
-  <si>
-    <t>型月：未婚妻露维亚，抽爆FGO</t>
-  </si>
-  <si>
-    <t>沉睡万年，逆徒皆成大帝</t>
-  </si>
-  <si>
-    <t>你管这叫警察？重炮都架租界口了</t>
-  </si>
-  <si>
-    <t>大春不傻了，全村都慌了</t>
-  </si>
-  <si>
-    <t>辍学打工，你给我AK干嘛？</t>
-  </si>
-  <si>
-    <t>天幕洛神赋，曹家父子社死</t>
-  </si>
-  <si>
-    <t>村女赵秀丽</t>
-  </si>
-  <si>
-    <t>名义：高育良不装了，带同伟狂飙</t>
-  </si>
-  <si>
-    <t>每日签到：这个军医什么都会</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>83.09999999999999</v>
+        <v>83.5</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1521000</v>
+        <v>1559000</v>
       </c>
       <c r="G5" s="7">
-        <v>33000</v>
+        <v>38000</v>
       </c>
       <c r="H5" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" s="7">
-        <v>82714</v>
+        <v>79733</v>
       </c>
       <c r="J5" s="5">
-        <v>86.40000000000001</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>82.5</v>
+        <v>96.5</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>2230000</v>
+        <v>538000</v>
       </c>
       <c r="G6" s="7">
-        <v>16000</v>
+        <v>39000</v>
       </c>
       <c r="H6" s="7">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="I6" s="7">
-        <v>55324</v>
+        <v>41200</v>
       </c>
       <c r="J6" s="5">
-        <v>79.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>97.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>499000</v>
+        <v>543000</v>
       </c>
       <c r="G7" s="7">
-        <v>41000</v>
+        <v>78000</v>
       </c>
       <c r="H7" s="7">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="I7" s="7">
-        <v>41750</v>
+        <v>36200</v>
       </c>
       <c r="J7" s="5">
-        <v>79</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>88.7</v>
+        <v>81.7</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>465000</v>
+        <v>2230000</v>
       </c>
       <c r="G8" s="7">
-        <v>50000</v>
+        <v>0</v>
       </c>
       <c r="H8" s="7">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="I8" s="7">
-        <v>31556</v>
+        <v>53743</v>
       </c>
       <c r="J8" s="5">
-        <v>76.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>97.2</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>210000</v>
+        <v>288000</v>
       </c>
       <c r="G9" s="7">
-        <v>33000</v>
+        <v>26000</v>
       </c>
       <c r="H9" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>25750</v>
+        <v>23800</v>
       </c>
       <c r="J9" s="5">
-        <v>76.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>99.90000000000001</v>
+        <v>99</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>209000</v>
+        <v>196000</v>
       </c>
       <c r="G10" s="7">
-        <v>29000</v>
+        <v>39000</v>
       </c>
       <c r="H10" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>23250</v>
+        <v>19400</v>
       </c>
       <c r="J10" s="5">
-        <v>75.8</v>
+        <v>77.3</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>94.59999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>219000</v>
+        <v>377000</v>
       </c>
       <c r="G11" s="7">
-        <v>16000</v>
+        <v>27000</v>
       </c>
       <c r="H11" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" s="7">
-        <v>31500</v>
+        <v>26200</v>
       </c>
       <c r="J11" s="5">
-        <v>74.90000000000001</v>
+        <v>76.7</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>98.09999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>262000</v>
+        <v>146000</v>
       </c>
       <c r="G12" s="7">
-        <v>26000</v>
+        <v>16000</v>
       </c>
       <c r="H12" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I12" s="7">
-        <v>23250</v>
+        <v>20200</v>
       </c>
       <c r="J12" s="5">
-        <v>74.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>96.09999999999999</v>
+        <v>94.2</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>296000</v>
+        <v>699000</v>
       </c>
       <c r="G13" s="7">
-        <v>32000</v>
+        <v>33000</v>
       </c>
       <c r="H13" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>27500</v>
+        <v>26200</v>
       </c>
       <c r="J13" s="5">
-        <v>74.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>99</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>198000</v>
+        <v>321000</v>
       </c>
       <c r="G14" s="7">
+        <v>25000</v>
+      </c>
+      <c r="H14" s="7">
+        <v>6</v>
+      </c>
+      <c r="I14" s="7">
         <v>27000</v>
       </c>
-      <c r="H14" s="7">
-        <v>5</v>
-      </c>
-      <c r="I14" s="7">
-        <v>20000</v>
-      </c>
       <c r="J14" s="5">
-        <v>74.5</v>
+        <v>75.7</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>79.59999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>803000</v>
+        <v>301000</v>
       </c>
       <c r="G15" s="7">
-        <v>7000</v>
+        <v>21000</v>
       </c>
       <c r="H15" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I15" s="7">
-        <v>42400</v>
+        <v>22000</v>
       </c>
       <c r="J15" s="5">
-        <v>74.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>97.5</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>280000</v>
+        <v>394000</v>
       </c>
       <c r="G16" s="7">
-        <v>28000</v>
+        <v>22000</v>
       </c>
       <c r="H16" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I16" s="7">
-        <v>22250</v>
+        <v>23400</v>
       </c>
       <c r="J16" s="5">
-        <v>74.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>95.09999999999999</v>
+        <v>92</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>350000</v>
+        <v>492000</v>
       </c>
       <c r="G17" s="7">
-        <v>29000</v>
+        <v>17000</v>
       </c>
       <c r="H17" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>26000</v>
+        <v>25200</v>
       </c>
       <c r="J17" s="5">
-        <v>73.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>97.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>130000</v>
+        <v>225000</v>
       </c>
       <c r="G18" s="7">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="H18" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I18" s="7">
-        <v>21250</v>
+        <v>21800</v>
       </c>
       <c r="J18" s="5">
-        <v>73.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>91.8</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>291000</v>
+        <v>119000</v>
       </c>
       <c r="G19" s="7">
-        <v>19000</v>
+        <v>23000</v>
       </c>
       <c r="H19" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19" s="7">
-        <v>32250</v>
+        <v>17400</v>
       </c>
       <c r="J19" s="5">
-        <v>73.59999999999999</v>
+        <v>74.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>79.90000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>755000</v>
+        <v>531000</v>
       </c>
       <c r="G20" s="7">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="H20" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I20" s="7">
-        <v>37462</v>
+        <v>22600</v>
       </c>
       <c r="J20" s="5">
-        <v>73.3</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>82.8</v>
+        <v>89.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>580000</v>
+        <v>301000</v>
       </c>
       <c r="G21" s="7">
-        <v>22000</v>
+        <v>10000</v>
       </c>
       <c r="H21" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I21" s="7">
-        <v>30917</v>
+        <v>27800</v>
       </c>
       <c r="J21" s="5">
-        <v>73.3</v>
+        <v>74</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>81</v>
+        <v>87.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>873000</v>
+        <v>345000</v>
       </c>
       <c r="G22" s="7">
-        <v>25000</v>
+        <v>34000</v>
       </c>
       <c r="H22" s="7">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I22" s="7">
-        <v>33778</v>
+        <v>22077</v>
       </c>
       <c r="J22" s="5">
-        <v>73</v>
+        <v>73.8</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>95.8</v>
+        <v>87.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>262000</v>
+        <v>288000</v>
       </c>
       <c r="G23" s="7">
-        <v>21000</v>
+        <v>31000</v>
       </c>
       <c r="H23" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I23" s="7">
-        <v>21250</v>
+        <v>22286</v>
       </c>
       <c r="J23" s="5">
-        <v>73</v>
+        <v>73.8</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>86.90000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>257000</v>
+        <v>276000</v>
       </c>
       <c r="G24" s="7">
-        <v>30000</v>
+        <v>14000</v>
       </c>
       <c r="H24" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I24" s="7">
-        <v>20833</v>
+        <v>19800</v>
       </c>
       <c r="J24" s="5">
-        <v>73</v>
+        <v>73.8</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>96.59999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>210000</v>
+        <v>213000</v>
       </c>
       <c r="G25" s="7">
+        <v>15000</v>
+      </c>
+      <c r="H25" s="7">
+        <v>6</v>
+      </c>
+      <c r="I25" s="7">
         <v>19000</v>
       </c>
-      <c r="H25" s="7">
-        <v>5</v>
-      </c>
-      <c r="I25" s="7">
-        <v>19250</v>
-      </c>
       <c r="J25" s="5">
-        <v>72.90000000000001</v>
+        <v>73.7</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>93.8</v>
+        <v>92.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>666000</v>
+        <v>362000</v>
       </c>
       <c r="G26" s="7">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="H26" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" s="7">
-        <v>24500</v>
+        <v>18400</v>
       </c>
       <c r="J26" s="5">
-        <v>72.7</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>94.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>358000</v>
+        <v>373000</v>
       </c>
       <c r="G27" s="7">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="H27" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I27" s="7">
-        <v>22250</v>
+        <v>20800</v>
       </c>
       <c r="J27" s="5">
-        <v>72.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>85.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>311000</v>
+        <v>777000</v>
       </c>
       <c r="G28" s="7">
-        <v>26000</v>
+        <v>22000</v>
       </c>
       <c r="H28" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I28" s="7">
-        <v>21083</v>
+        <v>36357</v>
       </c>
       <c r="J28" s="5">
-        <v>72.5</v>
+        <v>73</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>89.5</v>
+        <v>78.7</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>467000</v>
+        <v>803000</v>
       </c>
       <c r="G29" s="7">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I29" s="7">
-        <v>31750</v>
+        <v>38545</v>
       </c>
       <c r="J29" s="5">
-        <v>72.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>93.3</v>
+        <v>93.8</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>510000</v>
+        <v>451000</v>
       </c>
       <c r="G30" s="7">
-        <v>23000</v>
+        <v>27000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>23000</v>
+        <v>12800</v>
       </c>
       <c r="J30" s="5">
-        <v>72.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>91.2</v>
+        <v>94.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>475000</v>
+        <v>145000</v>
       </c>
       <c r="G31" s="7">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="H31" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I31" s="7">
-        <v>27250</v>
+        <v>9800</v>
       </c>
       <c r="J31" s="5">
-        <v>72</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>92.7</v>
+        <v>81.8</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>372000</v>
+        <v>597000</v>
       </c>
       <c r="G32" s="7">
-        <v>20000</v>
+        <v>17000</v>
       </c>
       <c r="H32" s="7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I32" s="7">
-        <v>23750</v>
+        <v>29846</v>
       </c>
       <c r="J32" s="5">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>81.59999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>523000</v>
+        <v>470000</v>
       </c>
       <c r="G33" s="7">
-        <v>46000</v>
+        <v>3000</v>
       </c>
       <c r="H33" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I33" s="7">
-        <v>25750</v>
+        <v>26000</v>
       </c>
       <c r="J33" s="5">
-        <v>71.3</v>
+        <v>72.5</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>92.8</v>
+        <v>88.3</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>260000</v>
+        <v>230000</v>
       </c>
       <c r="G34" s="7">
-        <v>16000</v>
+        <v>7000</v>
       </c>
       <c r="H34" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>19250</v>
+        <v>23800</v>
       </c>
       <c r="J34" s="5">
-        <v>70.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>93.2</v>
+        <v>94</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>342000</v>
+        <v>120000</v>
       </c>
       <c r="G35" s="7">
-        <v>23000</v>
+        <v>12000</v>
       </c>
       <c r="H35" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>18000</v>
+        <v>10200</v>
       </c>
       <c r="J35" s="5">
-        <v>70.8</v>
+        <v>72.2</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>94.7</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>179000</v>
+        <v>310000</v>
       </c>
       <c r="G36" s="7">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="H36" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>14500</v>
+        <v>15600</v>
       </c>
       <c r="J36" s="5">
-        <v>70.7</v>
+        <v>72</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>88.3</v>
+        <v>86.7</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>223000</v>
+        <v>219000</v>
       </c>
       <c r="G37" s="7">
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I37" s="7">
-        <v>28000</v>
+        <v>25200</v>
       </c>
       <c r="J37" s="5">
-        <v>70.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>92.7</v>
+        <v>94.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>299000</v>
+        <v>214000</v>
       </c>
       <c r="G38" s="7">
-        <v>15000</v>
+        <v>24000</v>
       </c>
       <c r="H38" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I38" s="7">
-        <v>16750</v>
+        <v>32333</v>
       </c>
       <c r="J38" s="5">
-        <v>70.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>94.7</v>
+        <v>89.8</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>190000</v>
+        <v>269000</v>
       </c>
       <c r="G39" s="7">
-        <v>30000</v>
+        <v>9000</v>
       </c>
       <c r="H39" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I39" s="7">
-        <v>36500</v>
+        <v>17200</v>
       </c>
       <c r="J39" s="5">
-        <v>70.2</v>
+        <v>71.7</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>92.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>265000</v>
+        <v>880000</v>
       </c>
       <c r="G40" s="7">
-        <v>13000</v>
+        <v>7000</v>
       </c>
       <c r="H40" s="7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I40" s="7">
-        <v>17000</v>
+        <v>32368</v>
       </c>
       <c r="J40" s="5">
-        <v>70</v>
+        <v>71.5</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>82.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>2656000</v>
+        <v>161000</v>
       </c>
       <c r="G41" s="7">
-        <v>7000</v>
+        <v>14000</v>
       </c>
       <c r="H41" s="7">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="I41" s="7">
-        <v>18382</v>
+        <v>6800</v>
       </c>
       <c r="J41" s="5">
-        <v>69.90000000000001</v>
+        <v>71.3</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>75.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>1534000</v>
+        <v>136000</v>
       </c>
       <c r="G42" s="7">
-        <v>-186000</v>
+        <v>17000</v>
       </c>
       <c r="H42" s="7">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="I42" s="7">
-        <v>34500</v>
+        <v>24000</v>
       </c>
       <c r="J42" s="5">
-        <v>69.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>90.8</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>335000</v>
+        <v>454000</v>
       </c>
       <c r="G43" s="7">
-        <v>18000</v>
+        <v>46000</v>
       </c>
       <c r="H43" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I43" s="7">
-        <v>19500</v>
+        <v>19444</v>
       </c>
       <c r="J43" s="5">
-        <v>69.8</v>
+        <v>70.5</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>81.3</v>
+        <v>83</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>360000</v>
+        <v>313000</v>
       </c>
       <c r="G44" s="7">
-        <v>15000</v>
+        <v>21000</v>
       </c>
       <c r="H44" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I44" s="7">
-        <v>20000</v>
+        <v>18429</v>
       </c>
       <c r="J44" s="5">
-        <v>69.7</v>
+        <v>70.3</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>96</v>
+        <v>86.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>108000</v>
+        <v>229000</v>
       </c>
       <c r="G45" s="7">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="H45" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I45" s="7">
-        <v>7500</v>
+        <v>17600</v>
       </c>
       <c r="J45" s="5">
-        <v>69.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>92.3</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>157000</v>
+        <v>104000</v>
       </c>
       <c r="G46" s="7">
-        <v>18000</v>
+        <v>26000</v>
       </c>
       <c r="H46" s="7">
         <v>5</v>
       </c>
       <c r="I46" s="7">
-        <v>14500</v>
+        <v>11000</v>
       </c>
       <c r="J46" s="5">
-        <v>69.40000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>97.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>100000</v>
+        <v>2670000</v>
       </c>
       <c r="G47" s="7">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="H47" s="7">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="I47" s="7">
-        <v>15000</v>
+        <v>18257</v>
       </c>
       <c r="J47" s="5">
-        <v>69.3</v>
+        <v>70</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>79.5</v>
+        <v>90.3</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>369000</v>
+        <v>118000</v>
       </c>
       <c r="G48" s="7">
-        <v>6000</v>
+        <v>9000</v>
       </c>
       <c r="H48" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I48" s="7">
-        <v>21583</v>
+        <v>8800</v>
       </c>
       <c r="J48" s="5">
-        <v>69.09999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>94.40000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>104000</v>
+        <v>210000</v>
       </c>
       <c r="G49" s="7">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="H49" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I49" s="7">
-        <v>7750</v>
+        <v>20600</v>
       </c>
       <c r="J49" s="5">
-        <v>68.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>77.2</v>
+        <v>89</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>352000</v>
+        <v>237000</v>
       </c>
       <c r="G50" s="7">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="H50" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I50" s="7">
-        <v>45500</v>
+        <v>10400</v>
       </c>
       <c r="J50" s="5">
-        <v>68.8</v>
+        <v>69.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>80.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>292000</v>
+        <v>210000</v>
       </c>
       <c r="G51" s="7">
-        <v>16000</v>
+        <v>0</v>
       </c>
       <c r="H51" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I51" s="7">
-        <v>18000</v>
+        <v>15400</v>
       </c>
       <c r="J51" s="5">
-        <v>68.8</v>
+        <v>69.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>96.2</v>
+        <v>88.8</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>119000</v>
+        <v>197000</v>
       </c>
       <c r="G52" s="7">
-        <v>27000</v>
+        <v>12000</v>
       </c>
       <c r="H52" s="7">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I52" s="7">
-        <v>27500</v>
+        <v>10200</v>
       </c>
       <c r="J52" s="5">
-        <v>68.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>80.3</v>
+        <v>92.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>331000</v>
+        <v>109000</v>
       </c>
       <c r="G53" s="7">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="H53" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7">
-        <v>18250</v>
+        <v>13500</v>
       </c>
       <c r="J53" s="5">
-        <v>68.7</v>
+        <v>69.2</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>88.8</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>218000</v>
+        <v>551000</v>
       </c>
       <c r="G54" s="7">
-        <v>16000</v>
+        <v>28000</v>
       </c>
       <c r="H54" s="7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I54" s="7">
-        <v>19250</v>
+        <v>25923</v>
       </c>
       <c r="J54" s="5">
-        <v>68.7</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-19T04:19:50+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-20T04:31:24+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>大唐：憨子别动手！有话好好说！</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>西游：开局找黄狮精买功法</t>
+  </si>
+  <si>
+    <t>见鬼！求生系统把我投放到80年</t>
+  </si>
+  <si>
+    <t>型月：未婚妻露维亚，抽爆FGO</t>
+  </si>
+  <si>
     <t>都重生了，谁还装富二代啊</t>
   </si>
   <si>
-    <t>打开作品</t>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>穿到六零，吃瓜看戏</t>
+  </si>
+  <si>
+    <t>全球修仙：只有我商城降价十亿倍</t>
   </si>
   <si>
     <t>神雕杨过：我以九阴九阳压天下！</t>
   </si>
   <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>武道通神：我的增益永久生效</t>
+  </si>
+  <si>
+    <t>1955，归国带飞国家工业</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+  </si>
+  <si>
+    <t>天幕：进谏被罢官？那我回后世了</t>
+  </si>
+  <si>
+    <t>名义：取代沙瑞金，拿捏汉东全局</t>
+  </si>
+  <si>
+    <t>序列车队：我能无限升级奇物</t>
+  </si>
+  <si>
+    <t>扫黑风暴之怒海惊涛</t>
+  </si>
+  <si>
+    <t>全民副本：我能打造九九八十一难</t>
+  </si>
+  <si>
+    <t>觉醒死亡笔记，开局写下邪神名字</t>
+  </si>
+  <si>
+    <t>七零替妹下乡，我觉醒了万物图鉴</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>九叔：让你请祖师，你请雷部天将</t>
+  </si>
+  <si>
+    <t>我都成旧日了，诡秘才入侵现实？</t>
+  </si>
+  <si>
+    <t>边军悍卒，绝色罪女天天求暖床</t>
+  </si>
+  <si>
+    <t>全民游戏，我每天一个新天赋</t>
+  </si>
+  <si>
+    <t>亮剑：我和李云龙一起当警卫</t>
+  </si>
+  <si>
+    <t>四合院：1948年开局暴富躺平</t>
+  </si>
+  <si>
+    <t>说好的厌男，怎么全成病娇了</t>
+  </si>
+  <si>
+    <t>我就写个网文，真没想镇压文坛啊</t>
+  </si>
+  <si>
+    <t>全民天赋，我每年融合一个自己</t>
+  </si>
+  <si>
+    <t>饥荒求生，国运垫底咋饱荒了？</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
+    <t>儒道剑仙，苟在镇北王府当赘婿</t>
+  </si>
+  <si>
+    <t>开局最弱大帝，禁区至尊被逼疯了</t>
+  </si>
+  <si>
+    <t>港综：给兄弟花钱，我百倍返还</t>
+  </si>
+  <si>
+    <t>每日签到：这个军医什么都会</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
     <t>重生年代：我怎么多了三个前妻</t>
   </si>
   <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>见鬼！求生系统把我投放到80年</t>
-  </si>
-  <si>
-    <t>型月：未婚妻露维亚，抽爆FGO</t>
-  </si>
-  <si>
-    <t>名义：取代沙瑞金，拿捏汉东全局</t>
-  </si>
-  <si>
-    <t>穿到六零，吃瓜看戏</t>
-  </si>
-  <si>
-    <t>全球修仙：只有我商城降价十亿倍</t>
-  </si>
-  <si>
-    <t>武道通神：我的增益永久生效</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>扫黑风暴之怒海惊涛</t>
-  </si>
-  <si>
-    <t>七零替妹下乡，我觉醒了万物图鉴</t>
-  </si>
-  <si>
-    <t>1955，归国带飞国家工业</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
+    <t>大秦：只想活命，始皇却逼我登基</t>
+  </si>
+  <si>
+    <t>修仙家族：从打下一片位面开始</t>
+  </si>
+  <si>
+    <t>大梁最废纨绔，竟是最强世子爷</t>
   </si>
   <si>
     <t>精灵女王审讯录</t>
   </si>
   <si>
-    <t>变妹后，我成了联盟最恶女选手</t>
-  </si>
-  <si>
-    <t>我都成旧日了，诡秘才入侵现实？</t>
-  </si>
-  <si>
-    <t>九叔：让你请祖师，你请雷部天将</t>
-  </si>
-  <si>
-    <t>序列车队：我能无限升级奇物</t>
-  </si>
-  <si>
-    <t>我就写个网文，真没想镇压文坛啊</t>
-  </si>
-  <si>
-    <t>我合成了全世界</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
-    <t>红色人生模拟，我怎么成老干部了</t>
+    <t>四合院：我在1944是个败家子</t>
+  </si>
+  <si>
+    <t>大明：我一个文官你给我武将系统</t>
   </si>
   <si>
     <t>年代1958，从搬运工开始！</t>
   </si>
   <si>
-    <t>开局最弱大帝，禁区至尊被逼疯了</t>
-  </si>
-  <si>
-    <t>全民天赋，我每年融合一个自己</t>
-  </si>
-  <si>
-    <t>大秦：只想活命，始皇却逼我登基</t>
-  </si>
-  <si>
-    <t>全民副本：我能打造九九八十一难</t>
-  </si>
-  <si>
-    <t>西游：开局找黄狮精买功法</t>
-  </si>
-  <si>
-    <t>四合院：1948年开局暴富躺平</t>
-  </si>
-  <si>
-    <t>全民游戏，我每天一个新天赋</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>饥荒求生，国运垫底咋饱荒了？</t>
-  </si>
-  <si>
-    <t>村女赵秀丽</t>
-  </si>
-  <si>
-    <t>财阀大小姐的恶毒男友重生了</t>
-  </si>
-  <si>
-    <t>天幕洛神赋，曹家父子社死</t>
-  </si>
-  <si>
-    <t>每日签到：这个军医什么都会</t>
-  </si>
-  <si>
-    <t>边军悍卒，绝色罪女天天求暖床</t>
-  </si>
-  <si>
-    <t>神通者</t>
-  </si>
-  <si>
-    <t>大明：我一个文官你给我武将系统</t>
-  </si>
-  <si>
-    <t>村女苏卉：离婚后的幸福人生</t>
-  </si>
-  <si>
-    <t>儒道剑仙，苟在镇北王府当赘婿</t>
-  </si>
-  <si>
-    <t>大唐：憨子别动手！有话好好说！</t>
+    <t>精灵：杀穿超古代的我只想退休</t>
   </si>
   <si>
     <t>一人：你苦修功法？我直接加点！</t>
   </si>
   <si>
-    <t>沉睡万年，逆徒皆成大帝</t>
-  </si>
-  <si>
-    <t>伪人降临！我是全场唯一预言家</t>
+    <t>让你去救赎，双生校花怎么恶堕了</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>83.5</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>1559000</v>
+        <v>250000</v>
       </c>
       <c r="G5" s="7">
-        <v>38000</v>
+        <v>40000</v>
       </c>
       <c r="H5" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I5" s="7">
-        <v>79733</v>
+        <v>19500</v>
       </c>
       <c r="J5" s="5">
-        <v>85.90000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>96.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>538000</v>
+        <v>242000</v>
       </c>
       <c r="G6" s="7">
-        <v>39000</v>
+        <v>23000</v>
       </c>
       <c r="H6" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>41200</v>
+        <v>24833</v>
       </c>
       <c r="J6" s="5">
-        <v>81.40000000000001</v>
+        <v>79.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>92.8</v>
+        <v>97.2</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>543000</v>
+        <v>316000</v>
       </c>
       <c r="G7" s="7">
-        <v>78000</v>
+        <v>28000</v>
       </c>
       <c r="H7" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>36200</v>
+        <v>24500</v>
       </c>
       <c r="J7" s="5">
-        <v>80.09999999999999</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>81.7</v>
+        <v>97.3</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>2230000</v>
+        <v>220000</v>
       </c>
       <c r="G8" s="7">
-        <v>0</v>
+        <v>24000</v>
       </c>
       <c r="H8" s="7">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>53743</v>
+        <v>20167</v>
       </c>
       <c r="J8" s="5">
-        <v>78.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>97.2</v>
+        <v>75.8</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>288000</v>
+        <v>1418000</v>
       </c>
       <c r="G9" s="7">
-        <v>26000</v>
+        <v>-141000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I9" s="7">
-        <v>23800</v>
+        <v>65938</v>
       </c>
       <c r="J9" s="5">
-        <v>77.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>99</v>
+        <v>81.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>196000</v>
+        <v>2232000</v>
       </c>
       <c r="G10" s="7">
-        <v>39000</v>
+        <v>2000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="I10" s="7">
-        <v>19400</v>
+        <v>52306</v>
       </c>
       <c r="J10" s="5">
-        <v>77.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>94.8</v>
+        <v>95.5</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>377000</v>
+        <v>161000</v>
       </c>
       <c r="G11" s="7">
-        <v>27000</v>
+        <v>15000</v>
       </c>
       <c r="H11" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>26200</v>
+        <v>19333</v>
       </c>
       <c r="J11" s="5">
-        <v>76.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>97.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>146000</v>
+        <v>722000</v>
       </c>
       <c r="G12" s="7">
-        <v>16000</v>
+        <v>23000</v>
       </c>
       <c r="H12" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>20200</v>
+        <v>25667</v>
       </c>
       <c r="J12" s="5">
-        <v>76.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>94.2</v>
+        <v>85.5</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>699000</v>
+        <v>574000</v>
       </c>
       <c r="G13" s="7">
-        <v>33000</v>
+        <v>36000</v>
       </c>
       <c r="H13" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>26200</v>
+        <v>40333</v>
       </c>
       <c r="J13" s="5">
-        <v>76.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1063,19 +1063,19 @@
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>321000</v>
+        <v>512000</v>
       </c>
       <c r="G14" s="7">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="H14" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I14" s="7">
-        <v>27000</v>
+        <v>24333</v>
       </c>
       <c r="J14" s="5">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94.09999999999999</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>301000</v>
+        <v>341000</v>
       </c>
       <c r="G15" s="7">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="H15" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>22000</v>
+        <v>25833</v>
       </c>
       <c r="J15" s="5">
-        <v>75.3</v>
+        <v>76.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>93.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>394000</v>
+        <v>549000</v>
       </c>
       <c r="G16" s="7">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="H16" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I16" s="7">
-        <v>23400</v>
+        <v>21833</v>
       </c>
       <c r="J16" s="5">
-        <v>75.09999999999999</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>92</v>
+        <v>92.3</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>492000</v>
+        <v>318000</v>
       </c>
       <c r="G17" s="7">
         <v>17000</v>
       </c>
       <c r="H17" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I17" s="7">
-        <v>25200</v>
+        <v>21167</v>
       </c>
       <c r="J17" s="5">
-        <v>74.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>93.59999999999999</v>
+        <v>91.3</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>225000</v>
+        <v>410000</v>
       </c>
       <c r="G18" s="7">
         <v>16000</v>
       </c>
       <c r="H18" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I18" s="7">
-        <v>21800</v>
+        <v>22167</v>
       </c>
       <c r="J18" s="5">
-        <v>74.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>95.40000000000001</v>
+        <v>94.8</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>119000</v>
+        <v>263000</v>
       </c>
       <c r="G19" s="7">
-        <v>23000</v>
+        <v>28000</v>
       </c>
       <c r="H19" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>17400</v>
+        <v>14500</v>
       </c>
       <c r="J19" s="5">
-        <v>74.8</v>
+        <v>75.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>92.7</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>531000</v>
+        <v>387000</v>
       </c>
       <c r="G20" s="7">
-        <v>21000</v>
+        <v>10000</v>
       </c>
       <c r="H20" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I20" s="7">
-        <v>22600</v>
+        <v>23500</v>
       </c>
       <c r="J20" s="5">
-        <v>74.59999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>89.2</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>301000</v>
+        <v>388000</v>
       </c>
       <c r="G21" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="H21" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>27800</v>
+        <v>19833</v>
       </c>
       <c r="J21" s="5">
-        <v>74</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>87.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>345000</v>
+        <v>236000</v>
       </c>
       <c r="G22" s="7">
-        <v>34000</v>
+        <v>11000</v>
       </c>
       <c r="H22" s="7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>22077</v>
+        <v>20000</v>
       </c>
       <c r="J22" s="5">
-        <v>73.8</v>
+        <v>75</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>87.7</v>
+        <v>92.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>288000</v>
+        <v>326000</v>
       </c>
       <c r="G23" s="7">
-        <v>31000</v>
+        <v>16000</v>
       </c>
       <c r="H23" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>22286</v>
+        <v>15667</v>
       </c>
       <c r="J23" s="5">
-        <v>73.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>92.5</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>276000</v>
+        <v>128000</v>
       </c>
       <c r="G24" s="7">
-        <v>14000</v>
+        <v>19000</v>
       </c>
       <c r="H24" s="7">
         <v>6</v>
       </c>
       <c r="I24" s="7">
-        <v>19800</v>
+        <v>14400</v>
       </c>
       <c r="J24" s="5">
-        <v>73.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>92.59999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>213000</v>
+        <v>132000</v>
       </c>
       <c r="G25" s="7">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="H25" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>19000</v>
+        <v>16667</v>
       </c>
       <c r="J25" s="5">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>92.8</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>362000</v>
+        <v>473000</v>
       </c>
       <c r="G26" s="7">
-        <v>20000</v>
+        <v>22000</v>
       </c>
       <c r="H26" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I26" s="7">
-        <v>18400</v>
+        <v>14333</v>
       </c>
       <c r="J26" s="5">
-        <v>73.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>91.2</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>373000</v>
+        <v>306000</v>
       </c>
       <c r="G27" s="7">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="H27" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I27" s="7">
-        <v>20800</v>
+        <v>24000</v>
       </c>
       <c r="J27" s="5">
-        <v>73.40000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>79.90000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>777000</v>
+        <v>374000</v>
       </c>
       <c r="G28" s="7">
-        <v>22000</v>
+        <v>12000</v>
       </c>
       <c r="H28" s="7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>36357</v>
+        <v>17333</v>
       </c>
       <c r="J28" s="5">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>78.7</v>
+        <v>90.2</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>803000</v>
+        <v>224000</v>
       </c>
       <c r="G29" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H29" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>38545</v>
+        <v>17667</v>
       </c>
       <c r="J29" s="5">
-        <v>72.90000000000001</v>
+        <v>74</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>93.8</v>
+        <v>96.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>451000</v>
+        <v>121000</v>
       </c>
       <c r="G30" s="7">
-        <v>27000</v>
+        <v>17000</v>
       </c>
       <c r="H30" s="7">
         <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>12800</v>
+        <v>12200</v>
       </c>
       <c r="J30" s="5">
-        <v>72.8</v>
+        <v>74</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>94.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>145000</v>
+        <v>278000</v>
       </c>
       <c r="G31" s="7">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="H31" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I31" s="7">
-        <v>9800</v>
+        <v>15833</v>
       </c>
       <c r="J31" s="5">
-        <v>72.59999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>81.8</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>597000</v>
+        <v>104000</v>
       </c>
       <c r="G32" s="7">
-        <v>17000</v>
+        <v>10000</v>
       </c>
       <c r="H32" s="7">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="I32" s="7">
-        <v>29846</v>
+        <v>15200</v>
       </c>
       <c r="J32" s="5">
-        <v>72.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>87.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>470000</v>
+        <v>233000</v>
       </c>
       <c r="G33" s="7">
-        <v>3000</v>
+        <v>19000</v>
       </c>
       <c r="H33" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>26000</v>
+        <v>29000</v>
       </c>
       <c r="J33" s="5">
-        <v>72.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>88.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>230000</v>
+        <v>219000</v>
       </c>
       <c r="G34" s="7">
-        <v>7000</v>
+        <v>20000</v>
       </c>
       <c r="H34" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I34" s="7">
-        <v>23800</v>
+        <v>12333</v>
       </c>
       <c r="J34" s="5">
-        <v>72.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>94</v>
+        <v>79.7</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>120000</v>
+        <v>798000</v>
       </c>
       <c r="G35" s="7">
-        <v>12000</v>
+        <v>21000</v>
       </c>
       <c r="H35" s="7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I35" s="7">
-        <v>10200</v>
+        <v>35333</v>
       </c>
       <c r="J35" s="5">
-        <v>72.2</v>
+        <v>72.7</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>91.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>310000</v>
+        <v>233000</v>
       </c>
       <c r="G36" s="7">
-        <v>11000</v>
+        <v>3000</v>
       </c>
       <c r="H36" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" s="7">
-        <v>15600</v>
+        <v>20333</v>
       </c>
       <c r="J36" s="5">
-        <v>72</v>
+        <v>72.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>86.7</v>
+        <v>92.2</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>219000</v>
+        <v>172000</v>
       </c>
       <c r="G37" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H37" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>25200</v>
+        <v>7500</v>
       </c>
       <c r="J37" s="5">
-        <v>72</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,23 +1848,23 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>94.3</v>
+        <v>84.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>214000</v>
+        <v>370000</v>
       </c>
       <c r="G38" s="7">
-        <v>24000</v>
+        <v>25000</v>
       </c>
       <c r="H38" s="7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I38" s="7">
-        <v>32333</v>
+        <v>22286</v>
       </c>
       <c r="J38" s="5">
         <v>71.90000000000001</v>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>89.8</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>269000</v>
+        <v>244000</v>
       </c>
       <c r="G39" s="7">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="H39" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>17200</v>
+        <v>9833</v>
       </c>
       <c r="J39" s="5">
-        <v>71.7</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>78.90000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>880000</v>
+        <v>459000</v>
       </c>
       <c r="G40" s="7">
-        <v>7000</v>
+        <v>-11000</v>
       </c>
       <c r="H40" s="7">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>32368</v>
+        <v>19833</v>
       </c>
       <c r="J40" s="5">
-        <v>71.5</v>
+        <v>71.8</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>93.90000000000001</v>
+        <v>88</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>161000</v>
+        <v>339000</v>
       </c>
       <c r="G41" s="7">
-        <v>14000</v>
+        <v>4000</v>
       </c>
       <c r="H41" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I41" s="7">
-        <v>6800</v>
+        <v>13667</v>
       </c>
       <c r="J41" s="5">
-        <v>71.3</v>
+        <v>71.8</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>96.59999999999999</v>
+        <v>86.7</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>136000</v>
+        <v>240000</v>
       </c>
       <c r="G42" s="7">
-        <v>17000</v>
+        <v>11000</v>
       </c>
       <c r="H42" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>24000</v>
+        <v>16500</v>
       </c>
       <c r="J42" s="5">
-        <v>71.09999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>82.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>454000</v>
+        <v>891000</v>
       </c>
       <c r="G43" s="7">
-        <v>46000</v>
+        <v>11000</v>
       </c>
       <c r="H43" s="7">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="I43" s="7">
-        <v>19444</v>
+        <v>31300</v>
       </c>
       <c r="J43" s="5">
-        <v>70.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>83</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>313000</v>
+        <v>546000</v>
       </c>
       <c r="G44" s="7">
-        <v>21000</v>
+        <v>3000</v>
       </c>
       <c r="H44" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I44" s="7">
-        <v>18429</v>
+        <v>33182</v>
       </c>
       <c r="J44" s="5">
-        <v>70.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>86.8</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>229000</v>
+        <v>127000</v>
       </c>
       <c r="G45" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H45" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I45" s="7">
-        <v>17600</v>
+        <v>9667</v>
       </c>
       <c r="J45" s="5">
-        <v>70.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>95.09999999999999</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>104000</v>
+        <v>119000</v>
       </c>
       <c r="G46" s="7">
-        <v>26000</v>
+        <v>6000</v>
       </c>
       <c r="H46" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I46" s="7">
-        <v>11000</v>
+        <v>6833</v>
       </c>
       <c r="J46" s="5">
-        <v>70.09999999999999</v>
+        <v>71.2</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>82.7</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>2670000</v>
+        <v>112000</v>
       </c>
       <c r="G47" s="7">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="H47" s="7">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="I47" s="7">
-        <v>18257</v>
+        <v>7833</v>
       </c>
       <c r="J47" s="5">
-        <v>70</v>
+        <v>71.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>90.3</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>118000</v>
+        <v>307000</v>
       </c>
       <c r="G48" s="7">
-        <v>9000</v>
+        <v>19000</v>
       </c>
       <c r="H48" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>8800</v>
+        <v>21875</v>
       </c>
       <c r="J48" s="5">
-        <v>69.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>84.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>210000</v>
+        <v>203000</v>
       </c>
       <c r="G49" s="7">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H49" s="7">
         <v>6</v>
       </c>
       <c r="I49" s="7">
-        <v>20600</v>
+        <v>15800</v>
       </c>
       <c r="J49" s="5">
-        <v>69.8</v>
+        <v>70.7</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>89</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>237000</v>
+        <v>125000</v>
       </c>
       <c r="G50" s="7">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="H50" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I50" s="7">
-        <v>10400</v>
+        <v>8500</v>
       </c>
       <c r="J50" s="5">
-        <v>69.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>86.59999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>210000</v>
+        <v>597000</v>
       </c>
       <c r="G51" s="7">
         <v>0</v>
       </c>
       <c r="H51" s="7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I51" s="7">
-        <v>15400</v>
+        <v>27714</v>
       </c>
       <c r="J51" s="5">
-        <v>69.5</v>
+        <v>70.3</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>88.8</v>
+        <v>88.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>197000</v>
+        <v>545000</v>
       </c>
       <c r="G52" s="7">
-        <v>12000</v>
+        <v>-1000</v>
       </c>
       <c r="H52" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I52" s="7">
-        <v>10200</v>
+        <v>6667</v>
       </c>
       <c r="J52" s="5">
-        <v>69.40000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>92.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>109000</v>
+        <v>203000</v>
       </c>
       <c r="G53" s="7">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H53" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I53" s="7">
-        <v>13500</v>
+        <v>9500</v>
       </c>
       <c r="J53" s="5">
-        <v>69.2</v>
+        <v>70.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>77.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>551000</v>
+        <v>102000</v>
       </c>
       <c r="G54" s="7">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="H54" s="7">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I54" s="7">
-        <v>25923</v>
+        <v>2500</v>
       </c>
       <c r="J54" s="5">
-        <v>69.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-20T04:31:24+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-21T04:22:58+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>见鬼！求生系统把我投放到80年</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>暴君：从一空输开始，登顶南韩</t>
+  </si>
+  <si>
+    <t>型月：未婚妻露维亚，抽爆FGO</t>
+  </si>
+  <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>武道通神：我的增益永久生效</t>
+  </si>
+  <si>
+    <t>四合院：1948年开局暴富躺平</t>
+  </si>
+  <si>
+    <t>穿到六零，吃瓜看戏</t>
+  </si>
+  <si>
+    <t>名义：取代沙瑞金，拿捏汉东全局</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
     <t>大唐：憨子别动手！有话好好说！</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
     <t>西游：开局找黄狮精买功法</t>
   </si>
   <si>
-    <t>见鬼！求生系统把我投放到80年</t>
-  </si>
-  <si>
-    <t>型月：未婚妻露维亚，抽爆FGO</t>
-  </si>
-  <si>
     <t>都重生了，谁还装富二代啊</t>
   </si>
   <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>穿到六零，吃瓜看戏</t>
+    <t>全民副本：我能打造九九八十一难</t>
+  </si>
+  <si>
+    <t>亮剑：我和李云龙一起当警卫</t>
+  </si>
+  <si>
+    <t>扫黑风暴之怒海惊涛</t>
+  </si>
+  <si>
+    <t>序列车队：我能无限升级奇物</t>
+  </si>
+  <si>
+    <t>神雕杨过：我以九阴九阳压天下！</t>
+  </si>
+  <si>
+    <t>边军悍卒，绝色罪女天天求暖床</t>
+  </si>
+  <si>
+    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+  </si>
+  <si>
+    <t>每日签到：这个军医什么都会</t>
+  </si>
+  <si>
+    <t>开局最弱大帝，禁区至尊被逼疯了</t>
+  </si>
+  <si>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>全民游戏，我每天一个新天赋</t>
   </si>
   <si>
     <t>全球修仙：只有我商城降价十亿倍</t>
   </si>
   <si>
-    <t>神雕杨过：我以九阴九阳压天下！</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>武道通神：我的增益永久生效</t>
-  </si>
-  <si>
-    <t>1955，归国带飞国家工业</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+    <t>觉醒死亡笔记，开局写下邪神名字</t>
+  </si>
+  <si>
+    <t>儒道剑仙，苟在镇北王府当赘婿</t>
+  </si>
+  <si>
+    <t>我都成旧日了，诡秘才入侵现实？</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
+    <t>全民天赋，我每年融合一个自己</t>
+  </si>
+  <si>
+    <t>四合院：我在1944是个败家子</t>
+  </si>
+  <si>
+    <t>精灵：杀穿超古代的我只想退休</t>
+  </si>
+  <si>
+    <t>红楼贾赦：我的金手指是山海经</t>
+  </si>
+  <si>
+    <t>穿成许仙，我只想吃软饭</t>
+  </si>
+  <si>
+    <t>修仙家族：从打下一片位面开始</t>
+  </si>
+  <si>
+    <t>大秦：只想活命，始皇却逼我登基</t>
+  </si>
+  <si>
+    <t>饥荒求生，国运垫底咋饱荒了？</t>
+  </si>
+  <si>
+    <t>我就写个网文，真没想镇压文坛啊</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
   </si>
   <si>
     <t>天幕：进谏被罢官？那我回后世了</t>
   </si>
   <si>
-    <t>名义：取代沙瑞金，拿捏汉东全局</t>
-  </si>
-  <si>
-    <t>序列车队：我能无限升级奇物</t>
-  </si>
-  <si>
-    <t>扫黑风暴之怒海惊涛</t>
-  </si>
-  <si>
-    <t>全民副本：我能打造九九八十一难</t>
-  </si>
-  <si>
-    <t>觉醒死亡笔记，开局写下邪神名字</t>
-  </si>
-  <si>
-    <t>七零替妹下乡，我觉醒了万物图鉴</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>九叔：让你请祖师，你请雷部天将</t>
-  </si>
-  <si>
-    <t>我都成旧日了，诡秘才入侵现实？</t>
-  </si>
-  <si>
-    <t>边军悍卒，绝色罪女天天求暖床</t>
-  </si>
-  <si>
-    <t>全民游戏，我每天一个新天赋</t>
-  </si>
-  <si>
-    <t>亮剑：我和李云龙一起当警卫</t>
-  </si>
-  <si>
-    <t>四合院：1948年开局暴富躺平</t>
-  </si>
-  <si>
-    <t>说好的厌男，怎么全成病娇了</t>
-  </si>
-  <si>
-    <t>我就写个网文，真没想镇压文坛啊</t>
-  </si>
-  <si>
-    <t>全民天赋，我每年融合一个自己</t>
-  </si>
-  <si>
-    <t>饥荒求生，国运垫底咋饱荒了？</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
-  </si>
-  <si>
-    <t>儒道剑仙，苟在镇北王府当赘婿</t>
-  </si>
-  <si>
-    <t>开局最弱大帝，禁区至尊被逼疯了</t>
-  </si>
-  <si>
-    <t>港综：给兄弟花钱，我百倍返还</t>
-  </si>
-  <si>
-    <t>每日签到：这个军医什么都会</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
+    <t>未婚妻绑定模拟系统！被我吓懵！</t>
   </si>
   <si>
     <t>重生年代：我怎么多了三个前妻</t>
   </si>
   <si>
-    <t>大秦：只想活命，始皇却逼我登基</t>
-  </si>
-  <si>
-    <t>修仙家族：从打下一片位面开始</t>
-  </si>
-  <si>
-    <t>大梁最废纨绔，竟是最强世子爷</t>
-  </si>
-  <si>
-    <t>精灵女王审讯录</t>
-  </si>
-  <si>
-    <t>四合院：我在1944是个败家子</t>
+    <t>红色人生模拟，我怎么成老干部了</t>
+  </si>
+  <si>
+    <t>四合院：开局被抓壮丁</t>
+  </si>
+  <si>
+    <t>出门捡垃圾，我被美女总裁强推了</t>
+  </si>
+  <si>
+    <t>火影：九尾之夜，雷光万劫</t>
+  </si>
+  <si>
+    <t>西幻：从龙人奴隶到万龙之母！</t>
   </si>
   <si>
     <t>大明：我一个文官你给我武将系统</t>
   </si>
   <si>
-    <t>年代1958，从搬运工开始！</t>
-  </si>
-  <si>
-    <t>精灵：杀穿超古代的我只想退休</t>
+    <t>啊？我是背景通天的大佬？</t>
   </si>
   <si>
     <t>一人：你苦修功法？我直接加点！</t>
-  </si>
-  <si>
-    <t>让你去救赎，双生校花怎么恶堕了</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>100</v>
+        <v>96.5</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>250000</v>
+        <v>344000</v>
       </c>
       <c r="G5" s="7">
-        <v>40000</v>
+        <v>28000</v>
       </c>
       <c r="H5" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>19500</v>
+        <v>25000</v>
       </c>
       <c r="J5" s="5">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>242000</v>
+        <v>101000</v>
       </c>
       <c r="G6" s="7">
-        <v>23000</v>
+        <v>16000</v>
       </c>
       <c r="H6" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I6" s="7">
-        <v>24833</v>
+        <v>11571</v>
       </c>
       <c r="J6" s="5">
-        <v>79.8</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>97.2</v>
+        <v>95.7</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>316000</v>
+        <v>243000</v>
       </c>
       <c r="G7" s="7">
-        <v>28000</v>
+        <v>23000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>24500</v>
+        <v>20571</v>
       </c>
       <c r="J7" s="5">
-        <v>79.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>97.3</v>
+        <v>81.2</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>220000</v>
+        <v>2221000</v>
       </c>
       <c r="G8" s="7">
-        <v>24000</v>
+        <v>-11000</v>
       </c>
       <c r="H8" s="7">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="I8" s="7">
-        <v>20167</v>
+        <v>50595</v>
       </c>
       <c r="J8" s="5">
-        <v>78.59999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>75.8</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>1418000</v>
+        <v>363000</v>
       </c>
       <c r="G9" s="7">
-        <v>-141000</v>
+        <v>22000</v>
       </c>
       <c r="H9" s="7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I9" s="7">
-        <v>65938</v>
+        <v>25286</v>
       </c>
       <c r="J9" s="5">
-        <v>78.2</v>
+        <v>77.3</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>81.8</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>2232000</v>
+        <v>259000</v>
       </c>
       <c r="G10" s="7">
-        <v>2000</v>
+        <v>26000</v>
       </c>
       <c r="H10" s="7">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>52306</v>
+        <v>28400</v>
       </c>
       <c r="J10" s="5">
-        <v>78.09999999999999</v>
+        <v>77.3</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>95.5</v>
+        <v>95.3</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>161000</v>
+        <v>177000</v>
       </c>
       <c r="G11" s="7">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I11" s="7">
-        <v>19333</v>
+        <v>18857</v>
       </c>
       <c r="J11" s="5">
-        <v>77.40000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>92.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>722000</v>
+        <v>405000</v>
       </c>
       <c r="G12" s="7">
-        <v>23000</v>
+        <v>18000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" s="7">
-        <v>25667</v>
+        <v>22714</v>
       </c>
       <c r="J12" s="5">
-        <v>77.3</v>
+        <v>76.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>85.5</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>574000</v>
+        <v>339000</v>
       </c>
       <c r="G13" s="7">
-        <v>36000</v>
+        <v>21000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I13" s="7">
-        <v>40333</v>
+        <v>21143</v>
       </c>
       <c r="J13" s="5">
-        <v>77.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>92.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>512000</v>
+        <v>530000</v>
       </c>
       <c r="G14" s="7">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="H14" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I14" s="7">
-        <v>24333</v>
+        <v>23429</v>
       </c>
       <c r="J14" s="5">
-        <v>77</v>
+        <v>76.5</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>91.40000000000001</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>341000</v>
+        <v>267000</v>
       </c>
       <c r="G15" s="7">
-        <v>20000</v>
+        <v>17000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>25833</v>
+        <v>19143</v>
       </c>
       <c r="J15" s="5">
-        <v>76.7</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>92.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>549000</v>
+        <v>251000</v>
       </c>
       <c r="G16" s="7">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="H16" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I16" s="7">
-        <v>21833</v>
+        <v>22571</v>
       </c>
       <c r="J16" s="5">
-        <v>76.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>92.3</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>318000</v>
+        <v>1303000</v>
       </c>
       <c r="G17" s="7">
-        <v>17000</v>
+        <v>-115000</v>
       </c>
       <c r="H17" s="7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I17" s="7">
-        <v>21167</v>
+        <v>55294</v>
       </c>
       <c r="J17" s="5">
-        <v>76.09999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>91.3</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>410000</v>
+        <v>342000</v>
       </c>
       <c r="G18" s="7">
         <v>16000</v>
       </c>
       <c r="H18" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I18" s="7">
-        <v>22167</v>
+        <v>15714</v>
       </c>
       <c r="J18" s="5">
-        <v>75.8</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>94.8</v>
+        <v>93.2</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>263000</v>
+        <v>114000</v>
       </c>
       <c r="G19" s="7">
-        <v>28000</v>
+        <v>10000</v>
       </c>
       <c r="H19" s="7">
         <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>14500</v>
+        <v>14333</v>
       </c>
       <c r="J19" s="5">
-        <v>75.8</v>
+        <v>74.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>90.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>387000</v>
+        <v>247000</v>
       </c>
       <c r="G20" s="7">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="H20" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I20" s="7">
-        <v>23500</v>
+        <v>18714</v>
       </c>
       <c r="J20" s="5">
-        <v>75.7</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>91.09999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>388000</v>
+        <v>401000</v>
       </c>
       <c r="G21" s="7">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>19833</v>
+        <v>18857</v>
       </c>
       <c r="J21" s="5">
-        <v>75.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>90.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>236000</v>
+        <v>591000</v>
       </c>
       <c r="G22" s="7">
-        <v>11000</v>
+        <v>17000</v>
       </c>
       <c r="H22" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>20000</v>
+        <v>37000</v>
       </c>
       <c r="J22" s="5">
-        <v>75</v>
+        <v>74.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>92.7</v>
+        <v>93</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>326000</v>
+        <v>133000</v>
       </c>
       <c r="G23" s="7">
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="7">
         <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>15667</v>
+        <v>12167</v>
       </c>
       <c r="J23" s="5">
-        <v>74.90000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>96.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>128000</v>
+        <v>418000</v>
       </c>
       <c r="G24" s="7">
-        <v>19000</v>
+        <v>8000</v>
       </c>
       <c r="H24" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I24" s="7">
-        <v>14400</v>
+        <v>20143</v>
       </c>
       <c r="J24" s="5">
-        <v>74.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>91.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>132000</v>
+        <v>256000</v>
       </c>
       <c r="G25" s="7">
-        <v>13000</v>
+        <v>16000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I25" s="7">
-        <v>16667</v>
+        <v>16429</v>
       </c>
       <c r="J25" s="5">
-        <v>74.5</v>
+        <v>73.8</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>92.40000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>473000</v>
+        <v>465000</v>
       </c>
       <c r="G26" s="7">
-        <v>22000</v>
+        <v>6000</v>
       </c>
       <c r="H26" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>14333</v>
+        <v>17857</v>
       </c>
       <c r="J26" s="5">
-        <v>74.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1495,16 +1495,16 @@
         <v>306000</v>
       </c>
       <c r="G27" s="7">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H27" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I27" s="7">
-        <v>24000</v>
+        <v>20571</v>
       </c>
       <c r="J27" s="5">
-        <v>74.09999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>90.3</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>374000</v>
+        <v>284000</v>
       </c>
       <c r="G28" s="7">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>17333</v>
+        <v>14429</v>
       </c>
       <c r="J28" s="5">
-        <v>74</v>
+        <v>72.8</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>90.2</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>224000</v>
+        <v>703000</v>
       </c>
       <c r="G29" s="7">
-        <v>11000</v>
+        <v>-19000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>17667</v>
+        <v>19286</v>
       </c>
       <c r="J29" s="5">
-        <v>74</v>
+        <v>72.5</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>96.2</v>
+        <v>89.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>121000</v>
+        <v>138000</v>
       </c>
       <c r="G30" s="7">
-        <v>17000</v>
+        <v>10000</v>
       </c>
       <c r="H30" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I30" s="7">
-        <v>12200</v>
+        <v>13667</v>
       </c>
       <c r="J30" s="5">
-        <v>74</v>
+        <v>72.5</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>90.59999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>278000</v>
+        <v>253000</v>
       </c>
       <c r="G31" s="7">
         <v>9000</v>
       </c>
       <c r="H31" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I31" s="7">
-        <v>15833</v>
+        <v>9714</v>
       </c>
       <c r="J31" s="5">
-        <v>73.8</v>
+        <v>72.3</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>94.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>104000</v>
+        <v>230000</v>
       </c>
       <c r="G32" s="7">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H32" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>15200</v>
+        <v>16000</v>
       </c>
       <c r="J32" s="5">
-        <v>73.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>233000</v>
+        <v>397000</v>
       </c>
       <c r="G33" s="7">
-        <v>19000</v>
+        <v>27000</v>
       </c>
       <c r="H33" s="7">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I33" s="7">
-        <v>29000</v>
+        <v>22600</v>
       </c>
       <c r="J33" s="5">
-        <v>73.09999999999999</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>90.90000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>219000</v>
+        <v>236000</v>
       </c>
       <c r="G34" s="7">
-        <v>20000</v>
+        <v>3000</v>
       </c>
       <c r="H34" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I34" s="7">
-        <v>12333</v>
+        <v>17857</v>
       </c>
       <c r="J34" s="5">
-        <v>73.09999999999999</v>
+        <v>72</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>79.7</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>798000</v>
+        <v>215000</v>
       </c>
       <c r="G35" s="7">
-        <v>21000</v>
+        <v>12000</v>
       </c>
       <c r="H35" s="7">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>35333</v>
+        <v>15167</v>
       </c>
       <c r="J35" s="5">
-        <v>72.7</v>
+        <v>72</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>86.5</v>
+        <v>90.7</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>233000</v>
+        <v>556000</v>
       </c>
       <c r="G36" s="7">
-        <v>3000</v>
+        <v>11000</v>
       </c>
       <c r="H36" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>20333</v>
+        <v>7286</v>
       </c>
       <c r="J36" s="5">
-        <v>72.7</v>
+        <v>71.7</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>92.2</v>
+        <v>90</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>172000</v>
+        <v>110000</v>
       </c>
       <c r="G37" s="7">
-        <v>11000</v>
+        <v>9000</v>
       </c>
       <c r="H37" s="7">
         <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>7500</v>
+        <v>8833</v>
       </c>
       <c r="J37" s="5">
-        <v>72.59999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>84.3</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>370000</v>
+        <v>102000</v>
       </c>
       <c r="G38" s="7">
-        <v>25000</v>
+        <v>7000</v>
       </c>
       <c r="H38" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I38" s="7">
-        <v>22286</v>
+        <v>9143</v>
       </c>
       <c r="J38" s="5">
-        <v>71.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>89.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>244000</v>
+        <v>127000</v>
       </c>
       <c r="G39" s="7">
+        <v>8000</v>
+      </c>
+      <c r="H39" s="7">
+        <v>8</v>
+      </c>
+      <c r="I39" s="7">
         <v>7000</v>
       </c>
-      <c r="H39" s="7">
-        <v>7</v>
-      </c>
-      <c r="I39" s="7">
-        <v>9833</v>
-      </c>
       <c r="J39" s="5">
-        <v>71.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>85.09999999999999</v>
+        <v>89.5</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>459000</v>
+        <v>134000</v>
       </c>
       <c r="G40" s="7">
-        <v>-11000</v>
+        <v>7000</v>
       </c>
       <c r="H40" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I40" s="7">
-        <v>19833</v>
+        <v>9286</v>
       </c>
       <c r="J40" s="5">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>88</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>339000</v>
+        <v>180000</v>
       </c>
       <c r="G41" s="7">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="H41" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I41" s="7">
-        <v>13667</v>
+        <v>7571</v>
       </c>
       <c r="J41" s="5">
-        <v>71.8</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>86.7</v>
+        <v>78</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>240000</v>
+        <v>806000</v>
       </c>
       <c r="G42" s="7">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I42" s="7">
-        <v>16500</v>
+        <v>33625</v>
       </c>
       <c r="J42" s="5">
-        <v>71.8</v>
+        <v>71.3</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>79.3</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>891000</v>
+        <v>898000</v>
       </c>
       <c r="G43" s="7">
-        <v>11000</v>
+        <v>7000</v>
       </c>
       <c r="H43" s="7">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="I43" s="7">
-        <v>31300</v>
+        <v>30143</v>
       </c>
       <c r="J43" s="5">
-        <v>71.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>78.40000000000001</v>
+        <v>86.5</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>546000</v>
+        <v>268000</v>
       </c>
       <c r="G44" s="7">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H44" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I44" s="7">
-        <v>33182</v>
+        <v>13143</v>
       </c>
       <c r="J44" s="5">
-        <v>71.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>88.90000000000001</v>
+        <v>88.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>127000</v>
+        <v>210000</v>
       </c>
       <c r="G45" s="7">
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="H45" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I45" s="7">
-        <v>9667</v>
+        <v>7714</v>
       </c>
       <c r="J45" s="5">
-        <v>71.3</v>
+        <v>70.8</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>89.90000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>119000</v>
+        <v>548000</v>
       </c>
       <c r="G46" s="7">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="H46" s="7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I46" s="7">
-        <v>6833</v>
+        <v>30583</v>
       </c>
       <c r="J46" s="5">
-        <v>71.2</v>
+        <v>70.7</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>89.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>112000</v>
+        <v>150000</v>
       </c>
       <c r="G47" s="7">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="H47" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I47" s="7">
-        <v>7833</v>
+        <v>7714</v>
       </c>
       <c r="J47" s="5">
-        <v>71.2</v>
+        <v>70.5</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>82.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>307000</v>
+        <v>176000</v>
       </c>
       <c r="G48" s="7">
-        <v>19000</v>
+        <v>13000</v>
       </c>
       <c r="H48" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I48" s="7">
-        <v>21875</v>
+        <v>8571</v>
       </c>
       <c r="J48" s="5">
-        <v>70.8</v>
+        <v>70.3</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>88.7</v>
+        <v>83.8</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>203000</v>
+        <v>429000</v>
       </c>
       <c r="G49" s="7">
-        <v>15000</v>
+        <v>23000</v>
       </c>
       <c r="H49" s="7">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="I49" s="7">
-        <v>15800</v>
+        <v>16227</v>
       </c>
       <c r="J49" s="5">
-        <v>70.7</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>88.09999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>125000</v>
+        <v>229000</v>
       </c>
       <c r="G50" s="7">
-        <v>7000</v>
+        <v>90000</v>
       </c>
       <c r="H50" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I50" s="7">
-        <v>8500</v>
+        <v>25750</v>
       </c>
       <c r="J50" s="5">
-        <v>70.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>78.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>597000</v>
+        <v>144000</v>
       </c>
       <c r="G51" s="7">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H51" s="7">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="I51" s="7">
-        <v>27714</v>
+        <v>5333</v>
       </c>
       <c r="J51" s="5">
-        <v>70.3</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>88.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>545000</v>
+        <v>131000</v>
       </c>
       <c r="G52" s="7">
-        <v>-1000</v>
+        <v>6000</v>
       </c>
       <c r="H52" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I52" s="7">
-        <v>6667</v>
+        <v>8143</v>
       </c>
       <c r="J52" s="5">
-        <v>70.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>87.09999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>203000</v>
+        <v>221000</v>
       </c>
       <c r="G53" s="7">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H53" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I53" s="7">
-        <v>9500</v>
+        <v>5000</v>
       </c>
       <c r="J53" s="5">
-        <v>70.3</v>
+        <v>69.8</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>90.09999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>102000</v>
+        <v>208000</v>
       </c>
       <c r="G54" s="7">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H54" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I54" s="7">
-        <v>2500</v>
+        <v>8857</v>
       </c>
       <c r="J54" s="5">
-        <v>70.2</v>
+        <v>69.8</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-21T04:22:58+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-22T04:22:16+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>神雕杨过：我以九阴九阳压天下！</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>四合院：1948年开局暴富躺平</t>
+  </si>
+  <si>
+    <t>饰演封于修，女友神仙姐姐</t>
+  </si>
+  <si>
+    <t>重生年代：我怎么多了三个前妻</t>
+  </si>
+  <si>
+    <t>穿到六零，吃瓜看戏</t>
+  </si>
+  <si>
+    <t>型月：未婚妻露维亚，抽爆FGO</t>
+  </si>
+  <si>
     <t>见鬼！求生系统把我投放到80年</t>
   </si>
   <si>
-    <t>打开作品</t>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>名义：取代沙瑞金，拿捏汉东全局</t>
+  </si>
+  <si>
+    <t>火影：九尾之夜，雷光万劫</t>
+  </si>
+  <si>
+    <t>武道通神：我的增益永久生效</t>
+  </si>
+  <si>
+    <t>大唐：憨子别动手！有话好好说！</t>
+  </si>
+  <si>
+    <t>扫黑风暴之怒海惊涛</t>
+  </si>
+  <si>
+    <t>盗墓：八岁创雷法，震惊张海琪</t>
+  </si>
+  <si>
+    <t>亮剑：我和李云龙一起当警卫</t>
+  </si>
+  <si>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>每日签到：这个军医什么都会</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>从小学三年级开始的完美人生</t>
+  </si>
+  <si>
+    <t>全民天赋，我每年融合一个自己</t>
+  </si>
+  <si>
+    <t>都重生了，谁还装富二代啊</t>
+  </si>
+  <si>
+    <t>我都成旧日了，诡秘才入侵现实？</t>
+  </si>
+  <si>
+    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+  </si>
+  <si>
+    <t>序列车队：我能无限升级奇物</t>
+  </si>
+  <si>
+    <t>我真没想振兴大唐</t>
+  </si>
+  <si>
+    <t>大春不傻了，全村都慌了</t>
+  </si>
+  <si>
+    <t>觉醒死亡笔记，开局写下邪神名字</t>
+  </si>
+  <si>
+    <t>未婚妻绑定模拟系统！被我吓懵！</t>
+  </si>
+  <si>
+    <t>重生82年，军夫的随身空间</t>
+  </si>
+  <si>
+    <t>天幕：进谏被罢官？那我回后世了</t>
+  </si>
+  <si>
+    <t>红楼贾赦：我的金手指是山海经</t>
+  </si>
+  <si>
+    <t>儒道剑仙，苟在镇北王府当赘婿</t>
+  </si>
+  <si>
+    <t>自定义术式的我去咒回找乐子了</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
   </si>
   <si>
     <t>暴君：从一空输开始，登顶南韩</t>
   </si>
   <si>
-    <t>型月：未婚妻露维亚，抽爆FGO</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>武道通神：我的增益永久生效</t>
-  </si>
-  <si>
-    <t>四合院：1948年开局暴富躺平</t>
-  </si>
-  <si>
-    <t>穿到六零，吃瓜看戏</t>
-  </si>
-  <si>
-    <t>名义：取代沙瑞金，拿捏汉东全局</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>大唐：憨子别动手！有话好好说！</t>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>抗战：我黄埔元老开局打爆小鬼子</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>全民游戏，我每天一个新天赋</t>
+  </si>
+  <si>
+    <t>我叫九江，李景隆那个九江！</t>
+  </si>
+  <si>
+    <t>边军悍卒，绝色罪女天天求暖床</t>
   </si>
   <si>
     <t>西游：开局找黄狮精买功法</t>
   </si>
   <si>
-    <t>都重生了，谁还装富二代啊</t>
-  </si>
-  <si>
-    <t>全民副本：我能打造九九八十一难</t>
-  </si>
-  <si>
-    <t>亮剑：我和李云龙一起当警卫</t>
-  </si>
-  <si>
-    <t>扫黑风暴之怒海惊涛</t>
-  </si>
-  <si>
-    <t>序列车队：我能无限升级奇物</t>
-  </si>
-  <si>
-    <t>神雕杨过：我以九阴九阳压天下！</t>
-  </si>
-  <si>
-    <t>边军悍卒，绝色罪女天天求暖床</t>
-  </si>
-  <si>
-    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
-  </si>
-  <si>
-    <t>每日签到：这个军医什么都会</t>
-  </si>
-  <si>
-    <t>开局最弱大帝，禁区至尊被逼疯了</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>全民游戏，我每天一个新天赋</t>
-  </si>
-  <si>
-    <t>全球修仙：只有我商城降价十亿倍</t>
-  </si>
-  <si>
-    <t>觉醒死亡笔记，开局写下邪神名字</t>
-  </si>
-  <si>
-    <t>儒道剑仙，苟在镇北王府当赘婿</t>
-  </si>
-  <si>
-    <t>我都成旧日了，诡秘才入侵现实？</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
-  </si>
-  <si>
-    <t>全民天赋，我每年融合一个自己</t>
-  </si>
-  <si>
-    <t>四合院：我在1944是个败家子</t>
+    <t>重生抗战：开局激活复制系统</t>
+  </si>
+  <si>
+    <t>天渊镇守百万载，你要挖我族人骨</t>
   </si>
   <si>
     <t>精灵：杀穿超古代的我只想退休</t>
   </si>
   <si>
-    <t>红楼贾赦：我的金手指是山海经</t>
-  </si>
-  <si>
-    <t>穿成许仙，我只想吃软饭</t>
-  </si>
-  <si>
-    <t>修仙家族：从打下一片位面开始</t>
-  </si>
-  <si>
-    <t>大秦：只想活命，始皇却逼我登基</t>
-  </si>
-  <si>
-    <t>饥荒求生，国运垫底咋饱荒了？</t>
-  </si>
-  <si>
-    <t>我就写个网文，真没想镇压文坛啊</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>天幕：进谏被罢官？那我回后世了</t>
-  </si>
-  <si>
-    <t>未婚妻绑定模拟系统！被我吓懵！</t>
-  </si>
-  <si>
-    <t>重生年代：我怎么多了三个前妻</t>
-  </si>
-  <si>
-    <t>红色人生模拟，我怎么成老干部了</t>
-  </si>
-  <si>
-    <t>四合院：开局被抓壮丁</t>
-  </si>
-  <si>
-    <t>出门捡垃圾，我被美女总裁强推了</t>
-  </si>
-  <si>
-    <t>火影：九尾之夜，雷光万劫</t>
-  </si>
-  <si>
-    <t>西幻：从龙人奴隶到万龙之母！</t>
-  </si>
-  <si>
-    <t>大明：我一个文官你给我武将系统</t>
-  </si>
-  <si>
-    <t>啊？我是背景通天的大佬？</t>
+    <t>我！官方审片员！京圈被我审懵圈</t>
+  </si>
+  <si>
+    <t>伪人降临！我是全场唯一预言家</t>
   </si>
   <si>
     <t>一人：你苦修功法？我直接加点！</t>
+  </si>
+  <si>
+    <t>我在红楼世界玩修仙游戏！</t>
   </si>
 </sst>
 </file>
@@ -668,7 +668,7 @@
     <col min="15" max="15" width="28.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="28" customHeight="1">
+    <row r="1" spans="1:15" ht="27.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -687,7 +687,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" ht="35" customHeight="1">
+    <row r="2" spans="1:15" ht="35.25" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>96.5</v>
+        <v>94.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>344000</v>
+        <v>688000</v>
       </c>
       <c r="G5" s="7">
-        <v>28000</v>
+        <v>97000</v>
       </c>
       <c r="H5" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="7">
-        <v>25000</v>
+        <v>44500</v>
       </c>
       <c r="J5" s="5">
-        <v>79.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>98.7</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>101000</v>
+        <v>295000</v>
       </c>
       <c r="G6" s="7">
-        <v>16000</v>
+        <v>36000</v>
       </c>
       <c r="H6" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I6" s="7">
-        <v>11571</v>
+        <v>29667</v>
       </c>
       <c r="J6" s="5">
-        <v>77.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>95.7</v>
+        <v>86.3</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>243000</v>
+        <v>553000</v>
       </c>
       <c r="G7" s="7">
-        <v>23000</v>
+        <v>69000</v>
       </c>
       <c r="H7" s="7">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="I7" s="7">
-        <v>20571</v>
+        <v>99500</v>
       </c>
       <c r="J7" s="5">
-        <v>77.8</v>
+        <v>81.3</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>81.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>2221000</v>
+        <v>674000</v>
       </c>
       <c r="G8" s="7">
-        <v>-11000</v>
+        <v>126000</v>
       </c>
       <c r="H8" s="7">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="I8" s="7">
-        <v>50595</v>
+        <v>37923</v>
       </c>
       <c r="J8" s="5">
-        <v>77.3</v>
+        <v>81.2</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>92.59999999999999</v>
+        <v>97.5</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>363000</v>
+        <v>198000</v>
       </c>
       <c r="G9" s="7">
-        <v>22000</v>
+        <v>21000</v>
       </c>
       <c r="H9" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="7">
-        <v>25286</v>
+        <v>19125</v>
       </c>
       <c r="J9" s="5">
-        <v>77.3</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>94.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>259000</v>
+        <v>268000</v>
       </c>
       <c r="G10" s="7">
-        <v>26000</v>
+        <v>25000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I10" s="7">
-        <v>28400</v>
+        <v>21125</v>
       </c>
       <c r="J10" s="5">
-        <v>77.3</v>
+        <v>78</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>95.3</v>
+        <v>93.3</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>177000</v>
+        <v>363000</v>
       </c>
       <c r="G11" s="7">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="H11" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I11" s="7">
-        <v>18857</v>
+        <v>24250</v>
       </c>
       <c r="J11" s="5">
-        <v>77.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>92.7</v>
+        <v>81.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>405000</v>
+        <v>2220000</v>
       </c>
       <c r="G12" s="7">
-        <v>18000</v>
+        <v>-1000</v>
       </c>
       <c r="H12" s="7">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I12" s="7">
-        <v>22714</v>
+        <v>49237</v>
       </c>
       <c r="J12" s="5">
-        <v>76.7</v>
+        <v>77.2</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>93.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>339000</v>
+        <v>425000</v>
       </c>
       <c r="G13" s="7">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="H13" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" s="7">
-        <v>21143</v>
+        <v>22375</v>
       </c>
       <c r="J13" s="5">
-        <v>76.7</v>
+        <v>76.8</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>92.09999999999999</v>
+        <v>90.7</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>530000</v>
+        <v>300000</v>
       </c>
       <c r="G14" s="7">
-        <v>18000</v>
+        <v>71000</v>
       </c>
       <c r="H14" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>23429</v>
+        <v>34800</v>
       </c>
       <c r="J14" s="5">
-        <v>76.5</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>93.90000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>267000</v>
+        <v>381000</v>
       </c>
       <c r="G15" s="7">
-        <v>17000</v>
+        <v>18000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I15" s="7">
-        <v>19143</v>
+        <v>24375</v>
       </c>
       <c r="J15" s="5">
-        <v>76.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>90.7</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>251000</v>
+        <v>284000</v>
       </c>
       <c r="G16" s="7">
-        <v>9000</v>
+        <v>17000</v>
       </c>
       <c r="H16" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I16" s="7">
-        <v>22571</v>
+        <v>18875</v>
       </c>
       <c r="J16" s="5">
-        <v>75.5</v>
+        <v>76.2</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>75.59999999999999</v>
+        <v>93.2</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>1303000</v>
+        <v>262000</v>
       </c>
       <c r="G17" s="7">
-        <v>-115000</v>
+        <v>15000</v>
       </c>
       <c r="H17" s="7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="I17" s="7">
-        <v>55294</v>
+        <v>18250</v>
       </c>
       <c r="J17" s="5">
-        <v>75.40000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>92.59999999999999</v>
+        <v>99.3</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>342000</v>
+        <v>108000</v>
       </c>
       <c r="G18" s="7">
-        <v>16000</v>
+        <v>42000</v>
       </c>
       <c r="H18" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7">
-        <v>15714</v>
+        <v>4500</v>
       </c>
       <c r="J18" s="5">
-        <v>74.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>93.2</v>
+        <v>94.2</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>114000</v>
+        <v>124000</v>
       </c>
       <c r="G19" s="7">
         <v>10000</v>
       </c>
       <c r="H19" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I19" s="7">
-        <v>14333</v>
+        <v>13714</v>
       </c>
       <c r="J19" s="5">
-        <v>74.8</v>
+        <v>75.2</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>90.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>247000</v>
+        <v>319000</v>
       </c>
       <c r="G20" s="7">
-        <v>11000</v>
+        <v>13000</v>
       </c>
       <c r="H20" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>18714</v>
+        <v>19625</v>
       </c>
       <c r="J20" s="5">
-        <v>74.59999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>90.5</v>
+        <v>91.3</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>401000</v>
+        <v>273000</v>
       </c>
       <c r="G21" s="7">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I21" s="7">
-        <v>18857</v>
+        <v>16500</v>
       </c>
       <c r="J21" s="5">
-        <v>74.5</v>
+        <v>74.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>81.8</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>591000</v>
+        <v>530000</v>
       </c>
       <c r="G22" s="7">
-        <v>17000</v>
+        <v>0</v>
       </c>
       <c r="H22" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I22" s="7">
-        <v>37000</v>
+        <v>20500</v>
       </c>
       <c r="J22" s="5">
-        <v>74.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>93</v>
+        <v>89.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>133000</v>
+        <v>344000</v>
       </c>
       <c r="G23" s="7">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I23" s="7">
-        <v>12167</v>
+        <v>19125</v>
       </c>
       <c r="J23" s="5">
-        <v>74.2</v>
+        <v>73.8</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>89.2</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>418000</v>
+        <v>498000</v>
       </c>
       <c r="G24" s="7">
-        <v>8000</v>
+        <v>14000</v>
       </c>
       <c r="H24" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I24" s="7">
-        <v>20143</v>
+        <v>13875</v>
       </c>
       <c r="J24" s="5">
-        <v>74.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>90.40000000000001</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>256000</v>
+        <v>245000</v>
       </c>
       <c r="G25" s="7">
-        <v>16000</v>
+        <v>9000</v>
       </c>
       <c r="H25" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I25" s="7">
-        <v>16429</v>
+        <v>16750</v>
       </c>
       <c r="J25" s="5">
-        <v>73.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>88.8</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>465000</v>
+        <v>1230000</v>
       </c>
       <c r="G26" s="7">
-        <v>6000</v>
+        <v>-73000</v>
       </c>
       <c r="H26" s="7">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="I26" s="7">
-        <v>17857</v>
+        <v>48167</v>
       </c>
       <c r="J26" s="5">
-        <v>73.3</v>
+        <v>73.5</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>87.40000000000001</v>
+        <v>90</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>306000</v>
+        <v>241000</v>
       </c>
       <c r="G27" s="7">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="H27" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I27" s="7">
-        <v>20571</v>
+        <v>15375</v>
       </c>
       <c r="J27" s="5">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>89.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>284000</v>
+        <v>421000</v>
       </c>
       <c r="G28" s="7">
-        <v>6000</v>
+        <v>3000</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I28" s="7">
-        <v>14429</v>
+        <v>18000</v>
       </c>
       <c r="J28" s="5">
-        <v>72.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>86.59999999999999</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>703000</v>
+        <v>404000</v>
       </c>
       <c r="G29" s="7">
-        <v>-19000</v>
+        <v>3000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I29" s="7">
-        <v>19286</v>
+        <v>16875</v>
       </c>
       <c r="J29" s="5">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89.3</v>
+        <v>86.2</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>138000</v>
+        <v>275000</v>
       </c>
       <c r="G30" s="7">
-        <v>10000</v>
+        <v>32000</v>
       </c>
       <c r="H30" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>13667</v>
+        <v>26000</v>
       </c>
       <c r="J30" s="5">
-        <v>72.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>90.7</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>253000</v>
+        <v>121000</v>
       </c>
       <c r="G31" s="7">
-        <v>9000</v>
+        <v>7000</v>
       </c>
       <c r="H31" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I31" s="7">
-        <v>9714</v>
+        <v>6000</v>
       </c>
       <c r="J31" s="5">
-        <v>72.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>87.8</v>
+        <v>88.3</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>230000</v>
+        <v>146000</v>
       </c>
       <c r="G32" s="7">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="H32" s="7">
         <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>16000</v>
+        <v>12857</v>
       </c>
       <c r="J32" s="5">
-        <v>72.3</v>
+        <v>71.8</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>84.5</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>397000</v>
+        <v>224000</v>
       </c>
       <c r="G33" s="7">
-        <v>27000</v>
+        <v>14000</v>
       </c>
       <c r="H33" s="7">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I33" s="7">
-        <v>22600</v>
+        <v>8500</v>
       </c>
       <c r="J33" s="5">
-        <v>72.09999999999999</v>
+        <v>71.7</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>86.5</v>
+        <v>91.5</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>236000</v>
+        <v>105000</v>
       </c>
       <c r="G34" s="7">
-        <v>3000</v>
+        <v>10000</v>
       </c>
       <c r="H34" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I34" s="7">
-        <v>17857</v>
+        <v>5250</v>
       </c>
       <c r="J34" s="5">
-        <v>72</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>87.59999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>215000</v>
+        <v>274000</v>
       </c>
       <c r="G35" s="7">
-        <v>12000</v>
+        <v>6000</v>
       </c>
       <c r="H35" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I35" s="7">
-        <v>15167</v>
+        <v>12250</v>
       </c>
       <c r="J35" s="5">
-        <v>72</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>90.7</v>
+        <v>89.3</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>556000</v>
+        <v>118000</v>
       </c>
       <c r="G36" s="7">
-        <v>11000</v>
+        <v>8000</v>
       </c>
       <c r="H36" s="7">
         <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>7286</v>
+        <v>8714</v>
       </c>
       <c r="J36" s="5">
-        <v>71.7</v>
+        <v>71.3</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>110000</v>
+        <v>258000</v>
       </c>
       <c r="G37" s="7">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="H37" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I37" s="7">
-        <v>8833</v>
+        <v>9125</v>
       </c>
       <c r="J37" s="5">
-        <v>71.7</v>
+        <v>71.2</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>89.90000000000001</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>102000</v>
+        <v>169000</v>
       </c>
       <c r="G38" s="7">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="H38" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I38" s="7">
-        <v>9143</v>
+        <v>12667</v>
       </c>
       <c r="J38" s="5">
-        <v>71.7</v>
+        <v>71.2</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>90.59999999999999</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>127000</v>
+        <v>418000</v>
       </c>
       <c r="G39" s="7">
-        <v>8000</v>
+        <v>21000</v>
       </c>
       <c r="H39" s="7">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I39" s="7">
-        <v>7000</v>
+        <v>22500</v>
       </c>
       <c r="J39" s="5">
-        <v>71.59999999999999</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>89.5</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>134000</v>
+        <v>122000</v>
       </c>
       <c r="G40" s="7">
-        <v>7000</v>
+        <v>21000</v>
       </c>
       <c r="H40" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I40" s="7">
-        <v>9286</v>
+        <v>12750</v>
       </c>
       <c r="J40" s="5">
-        <v>71.5</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>90.09999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>180000</v>
+        <v>902000</v>
       </c>
       <c r="G41" s="7">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="H41" s="7">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="I41" s="7">
-        <v>7571</v>
+        <v>28955</v>
       </c>
       <c r="J41" s="5">
-        <v>71.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>78</v>
+        <v>86.7</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>806000</v>
+        <v>231000</v>
       </c>
       <c r="G42" s="7">
-        <v>8000</v>
+        <v>27000</v>
       </c>
       <c r="H42" s="7">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="I42" s="7">
-        <v>33625</v>
+        <v>12875</v>
       </c>
       <c r="J42" s="5">
-        <v>71.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>78.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>898000</v>
+        <v>626000</v>
       </c>
       <c r="G43" s="7">
-        <v>7000</v>
+        <v>32000</v>
       </c>
       <c r="H43" s="7">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I43" s="7">
-        <v>30143</v>
+        <v>17429</v>
       </c>
       <c r="J43" s="5">
-        <v>70.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2053,19 +2053,19 @@
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>268000</v>
+        <v>282000</v>
       </c>
       <c r="G44" s="7">
-        <v>5000</v>
+        <v>-2000</v>
       </c>
       <c r="H44" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I44" s="7">
-        <v>13143</v>
+        <v>12375</v>
       </c>
       <c r="J44" s="5">
-        <v>70.90000000000001</v>
+        <v>70.7</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>88.8</v>
+        <v>96.8</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>210000</v>
+        <v>104000</v>
       </c>
       <c r="G45" s="7">
-        <v>11000</v>
+        <v>39000</v>
       </c>
       <c r="H45" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I45" s="7">
-        <v>7714</v>
+        <v>21667</v>
       </c>
       <c r="J45" s="5">
-        <v>70.8</v>
+        <v>70.7</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>78.2</v>
+        <v>87.2</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>548000</v>
+        <v>135000</v>
       </c>
       <c r="G46" s="7">
         <v>2000</v>
       </c>
       <c r="H46" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I46" s="7">
-        <v>30583</v>
+        <v>10714</v>
       </c>
       <c r="J46" s="5">
-        <v>70.7</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,23 +2145,23 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>88.40000000000001</v>
+        <v>83.3</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>150000</v>
+        <v>242000</v>
       </c>
       <c r="G47" s="7">
-        <v>6000</v>
+        <v>-9000</v>
       </c>
       <c r="H47" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
-        <v>7714</v>
+        <v>18625</v>
       </c>
       <c r="J47" s="5">
         <v>70.5</v>
@@ -2178,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.5</v>
+        <v>88.8</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>176000</v>
+        <v>101000</v>
       </c>
       <c r="G48" s="7">
-        <v>13000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I48" s="7">
-        <v>8571</v>
+        <v>6750</v>
       </c>
       <c r="J48" s="5">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2209,28 +2209,30 @@
       <c r="A49" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B49" s="5"/>
+      <c r="B49" s="5">
+        <v>9.9</v>
+      </c>
       <c r="C49" s="5">
-        <v>83.8</v>
+        <v>90.8</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>429000</v>
+        <v>142000</v>
       </c>
       <c r="G49" s="7">
-        <v>23000</v>
+        <v>13000</v>
       </c>
       <c r="H49" s="7">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="I49" s="7">
-        <v>16227</v>
+        <v>10000</v>
       </c>
       <c r="J49" s="5">
-        <v>70.09999999999999</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2251,19 +2253,19 @@
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>229000</v>
+        <v>555000</v>
       </c>
       <c r="G50" s="7">
-        <v>90000</v>
+        <v>-1000</v>
       </c>
       <c r="H50" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I50" s="7">
-        <v>25750</v>
+        <v>6250</v>
       </c>
       <c r="J50" s="5">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>88.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>144000</v>
+        <v>192000</v>
       </c>
       <c r="G51" s="7">
-        <v>4000</v>
+        <v>15000</v>
       </c>
       <c r="H51" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I51" s="7">
-        <v>5333</v>
+        <v>7625</v>
       </c>
       <c r="J51" s="5">
-        <v>70.09999999999999</v>
+        <v>70</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>87.09999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>131000</v>
+        <v>630000</v>
       </c>
       <c r="G52" s="7">
-        <v>6000</v>
+        <v>29000</v>
       </c>
       <c r="H52" s="7">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I52" s="7">
-        <v>8143</v>
+        <v>26000</v>
       </c>
       <c r="J52" s="5">
-        <v>69.90000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>88.3</v>
+        <v>86.5</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>221000</v>
+        <v>213000</v>
       </c>
       <c r="G53" s="7">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="H53" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I53" s="7">
-        <v>5000</v>
+        <v>8375</v>
       </c>
       <c r="J53" s="5">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>86.59999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>208000</v>
+        <v>110000</v>
       </c>
       <c r="G54" s="7">
+        <v>8000</v>
+      </c>
+      <c r="H54" s="7">
+        <v>9</v>
+      </c>
+      <c r="I54" s="7">
         <v>5000</v>
       </c>
-      <c r="H54" s="7">
-        <v>8</v>
-      </c>
-      <c r="I54" s="7">
-        <v>8857</v>
-      </c>
       <c r="J54" s="5">
-        <v>69.8</v>
+        <v>69.7</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-22T04:22:16+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-23T04:28:51+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>重生年代：我怎么多了三个前妻</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
     <t>神雕杨过：我以九阴九阳压天下！</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
     <t>四合院：1948年开局暴富躺平</t>
   </si>
   <si>
+    <t>我叫九江，李景隆那个九江！</t>
+  </si>
+  <si>
+    <t>火影：九尾之夜，雷光万劫</t>
+  </si>
+  <si>
     <t>饰演封于修，女友神仙姐姐</t>
   </si>
   <si>
-    <t>重生年代：我怎么多了三个前妻</t>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>盗墓：八岁创雷法，震惊张海琪</t>
+  </si>
+  <si>
+    <t>扫黑风暴之怒海惊涛</t>
   </si>
   <si>
     <t>穿到六零，吃瓜看戏</t>
   </si>
   <si>
+    <t>大唐：憨子别动手！有话好好说！</t>
+  </si>
+  <si>
+    <t>名义：取代沙瑞金，拿捏汉东全局</t>
+  </si>
+  <si>
     <t>型月：未婚妻露维亚，抽爆FGO</t>
   </si>
   <si>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>天渊镇守百万载，你要挖我族人骨</t>
+  </si>
+  <si>
     <t>见鬼！求生系统把我投放到80年</t>
   </si>
   <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>名义：取代沙瑞金，拿捏汉东全局</t>
-  </si>
-  <si>
-    <t>火影：九尾之夜，雷光万劫</t>
+    <t>废土黑作坊：从造一级弹开始</t>
   </si>
   <si>
     <t>武道通神：我的增益永久生效</t>
   </si>
   <si>
-    <t>大唐：憨子别动手！有话好好说！</t>
-  </si>
-  <si>
-    <t>扫黑风暴之怒海惊涛</t>
-  </si>
-  <si>
-    <t>盗墓：八岁创雷法，震惊张海琪</t>
+    <t>全民天赋，我每年融合一个自己</t>
+  </si>
+  <si>
+    <t>我都成旧日了，诡秘才入侵现实？</t>
+  </si>
+  <si>
+    <t>西游：开局找黄狮精买功法</t>
   </si>
   <si>
     <t>亮剑：我和李云龙一起当警卫</t>
   </si>
   <si>
-    <t>我在美国当上帝</t>
+    <t>暴君：从一空输开始，登顶南韩</t>
+  </si>
+  <si>
+    <t>自定义术式的我去咒回找乐子了</t>
+  </si>
+  <si>
+    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+  </si>
+  <si>
+    <t>都重生了，谁还装富二代啊</t>
+  </si>
+  <si>
+    <t>洪荒：开局带着白莲绿茶拜师三清</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>天幕：进谏被罢官？那我回后世了</t>
+  </si>
+  <si>
+    <t>红楼贾赦：我的金手指是山海经</t>
+  </si>
+  <si>
+    <t>财阀大小姐的恶毒男友重生了</t>
+  </si>
+  <si>
+    <t>拒白月光不做冤大头七零留城享福</t>
+  </si>
+  <si>
+    <t>弃子归来，已是绝世高手</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
+    <t>末世轮盘：开局指定抽取序列魔药</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>重活一世，谁还要追她啊？</t>
+  </si>
+  <si>
+    <t>一人：你苦修功法？我直接加点！</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离还在藏</t>
+  </si>
+  <si>
+    <t>儒道剑仙，苟在镇北王府当赘婿</t>
+  </si>
+  <si>
+    <t>穿越民国当姑爷</t>
+  </si>
+  <si>
+    <t>精灵：杀穿超古代的我只想退休</t>
+  </si>
+  <si>
+    <t>重生抗战：开局激活复制系统</t>
   </si>
   <si>
     <t>每日签到：这个军医什么都会</t>
   </si>
   <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>从小学三年级开始的完美人生</t>
-  </si>
-  <si>
-    <t>全民天赋，我每年融合一个自己</t>
-  </si>
-  <si>
-    <t>都重生了，谁还装富二代啊</t>
-  </si>
-  <si>
-    <t>我都成旧日了，诡秘才入侵现实？</t>
-  </si>
-  <si>
-    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
-  </si>
-  <si>
-    <t>序列车队：我能无限升级奇物</t>
-  </si>
-  <si>
-    <t>我真没想振兴大唐</t>
-  </si>
-  <si>
-    <t>大春不傻了，全村都慌了</t>
-  </si>
-  <si>
     <t>觉醒死亡笔记，开局写下邪神名字</t>
   </si>
   <si>
-    <t>未婚妻绑定模拟系统！被我吓懵！</t>
-  </si>
-  <si>
-    <t>重生82年，军夫的随身空间</t>
-  </si>
-  <si>
-    <t>天幕：进谏被罢官？那我回后世了</t>
-  </si>
-  <si>
-    <t>红楼贾赦：我的金手指是山海经</t>
-  </si>
-  <si>
-    <t>儒道剑仙，苟在镇北王府当赘婿</t>
-  </si>
-  <si>
-    <t>自定义术式的我去咒回找乐子了</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
-  </si>
-  <si>
-    <t>暴君：从一空输开始，登顶南韩</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>抗战：我黄埔元老开局打爆小鬼子</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>全民游戏，我每天一个新天赋</t>
-  </si>
-  <si>
-    <t>我叫九江，李景隆那个九江！</t>
-  </si>
-  <si>
-    <t>边军悍卒，绝色罪女天天求暖床</t>
-  </si>
-  <si>
-    <t>西游：开局找黄狮精买功法</t>
-  </si>
-  <si>
-    <t>重生抗战：开局激活复制系统</t>
-  </si>
-  <si>
-    <t>天渊镇守百万载，你要挖我族人骨</t>
-  </si>
-  <si>
-    <t>精灵：杀穿超古代的我只想退休</t>
-  </si>
-  <si>
-    <t>我！官方审片员！京圈被我审懵圈</t>
-  </si>
-  <si>
     <t>伪人降临！我是全场唯一预言家</t>
   </si>
   <si>
-    <t>一人：你苦修功法？我直接加点！</t>
-  </si>
-  <si>
-    <t>我在红楼世界玩修仙游戏！</t>
+    <t>修仙家族：从打下一片位面开始</t>
+  </si>
+  <si>
+    <t>四合院：我在1944是个败家子</t>
+  </si>
+  <si>
+    <t>神通者</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>94.2</v>
+        <v>94.7</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>688000</v>
+        <v>862000</v>
       </c>
       <c r="G5" s="7">
-        <v>97000</v>
+        <v>188000</v>
       </c>
       <c r="H5" s="7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I5" s="7">
-        <v>44500</v>
+        <v>48643</v>
       </c>
       <c r="J5" s="5">
-        <v>82.90000000000001</v>
+        <v>84.2</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>98.7</v>
+        <v>92.5</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>295000</v>
+        <v>778000</v>
       </c>
       <c r="G6" s="7">
-        <v>36000</v>
+        <v>90000</v>
       </c>
       <c r="H6" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I6" s="7">
-        <v>29667</v>
+        <v>49556</v>
       </c>
       <c r="J6" s="5">
-        <v>81.7</v>
+        <v>83.3</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>86.3</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>553000</v>
+        <v>346000</v>
       </c>
       <c r="G7" s="7">
-        <v>69000</v>
+        <v>51000</v>
       </c>
       <c r="H7" s="7">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>99500</v>
+        <v>32714</v>
       </c>
       <c r="J7" s="5">
-        <v>81.3</v>
+        <v>83.2</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>94.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>674000</v>
+        <v>222000</v>
       </c>
       <c r="G8" s="7">
-        <v>126000</v>
+        <v>118000</v>
       </c>
       <c r="H8" s="7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I8" s="7">
-        <v>37923</v>
+        <v>45750</v>
       </c>
       <c r="J8" s="5">
-        <v>81.2</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>97.5</v>
+        <v>92.7</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>198000</v>
+        <v>345000</v>
       </c>
       <c r="G9" s="7">
-        <v>21000</v>
+        <v>45000</v>
       </c>
       <c r="H9" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>19125</v>
+        <v>36500</v>
       </c>
       <c r="J9" s="5">
-        <v>78.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>95.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>268000</v>
+        <v>611000</v>
       </c>
       <c r="G10" s="7">
-        <v>25000</v>
+        <v>58000</v>
       </c>
       <c r="H10" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I10" s="7">
-        <v>21125</v>
+        <v>85667</v>
       </c>
       <c r="J10" s="5">
-        <v>78</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>93.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>363000</v>
+        <v>2239000</v>
       </c>
       <c r="G11" s="7">
         <v>19000</v>
       </c>
       <c r="H11" s="7">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="I11" s="7">
-        <v>24250</v>
+        <v>48462</v>
       </c>
       <c r="J11" s="5">
-        <v>77.40000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>81.7</v>
+        <v>100</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>2220000</v>
+        <v>133000</v>
       </c>
       <c r="G12" s="7">
-        <v>-1000</v>
+        <v>25000</v>
       </c>
       <c r="H12" s="7">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="I12" s="7">
-        <v>49237</v>
+        <v>6778</v>
       </c>
       <c r="J12" s="5">
-        <v>77.2</v>
+        <v>76.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>93.09999999999999</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>425000</v>
+        <v>282000</v>
       </c>
       <c r="G13" s="7">
         <v>20000</v>
       </c>
       <c r="H13" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I13" s="7">
-        <v>22375</v>
+        <v>18444</v>
       </c>
       <c r="J13" s="5">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>90.7</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>300000</v>
+        <v>213000</v>
       </c>
       <c r="G14" s="7">
-        <v>71000</v>
+        <v>15000</v>
       </c>
       <c r="H14" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I14" s="7">
-        <v>34800</v>
+        <v>18667</v>
       </c>
       <c r="J14" s="5">
-        <v>76.59999999999999</v>
+        <v>76</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>91.2</v>
+        <v>92.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>381000</v>
+        <v>298000</v>
       </c>
       <c r="G15" s="7">
-        <v>18000</v>
+        <v>14000</v>
       </c>
       <c r="H15" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I15" s="7">
-        <v>24375</v>
+        <v>18333</v>
       </c>
       <c r="J15" s="5">
-        <v>76.3</v>
+        <v>75.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>93.59999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>284000</v>
+        <v>436000</v>
       </c>
       <c r="G16" s="7">
-        <v>17000</v>
+        <v>11000</v>
       </c>
       <c r="H16" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I16" s="7">
-        <v>18875</v>
+        <v>21111</v>
       </c>
       <c r="J16" s="5">
-        <v>76.2</v>
+        <v>75.2</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>93.2</v>
+        <v>90.8</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>262000</v>
+        <v>282000</v>
       </c>
       <c r="G17" s="7">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="H17" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I17" s="7">
-        <v>18250</v>
+        <v>20333</v>
       </c>
       <c r="J17" s="5">
-        <v>75.8</v>
+        <v>75</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>99.3</v>
+        <v>90.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>108000</v>
+        <v>329000</v>
       </c>
       <c r="G18" s="7">
-        <v>42000</v>
+        <v>10000</v>
       </c>
       <c r="H18" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I18" s="7">
-        <v>4500</v>
+        <v>18556</v>
       </c>
       <c r="J18" s="5">
-        <v>75.7</v>
+        <v>74.5</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1219,28 +1219,30 @@
       <c r="A19" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="5"/>
+      <c r="B19" s="5">
+        <v>9.9</v>
+      </c>
       <c r="C19" s="5">
-        <v>94.2</v>
+        <v>93.2</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>124000</v>
+        <v>157000</v>
       </c>
       <c r="G19" s="7">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="H19" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I19" s="7">
-        <v>13714</v>
+        <v>10833</v>
       </c>
       <c r="J19" s="5">
-        <v>75.2</v>
+        <v>74</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1256,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>90.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>319000</v>
+        <v>364000</v>
       </c>
       <c r="G20" s="7">
-        <v>13000</v>
+        <v>1000</v>
       </c>
       <c r="H20" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I20" s="7">
-        <v>19625</v>
+        <v>21667</v>
       </c>
       <c r="J20" s="5">
-        <v>74.90000000000001</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1289,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>91.3</v>
+        <v>88.8</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>273000</v>
+        <v>531000</v>
       </c>
       <c r="G21" s="7">
-        <v>17000</v>
+        <v>1000</v>
       </c>
       <c r="H21" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I21" s="7">
-        <v>16500</v>
+        <v>18333</v>
       </c>
       <c r="J21" s="5">
-        <v>74.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1322,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>88.59999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>530000</v>
+        <v>382000</v>
       </c>
       <c r="G22" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H22" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I22" s="7">
-        <v>20500</v>
+        <v>21778</v>
       </c>
       <c r="J22" s="5">
-        <v>73.90000000000001</v>
+        <v>73</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1355,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>89.2</v>
+        <v>89</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>344000</v>
+        <v>252000</v>
       </c>
       <c r="G23" s="7">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="H23" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I23" s="7">
-        <v>19125</v>
+        <v>15667</v>
       </c>
       <c r="J23" s="5">
-        <v>73.8</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1388,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.40000000000001</v>
+        <v>89.5</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>498000</v>
+        <v>251000</v>
       </c>
       <c r="G24" s="7">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="H24" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I24" s="7">
-        <v>13875</v>
+        <v>14778</v>
       </c>
       <c r="J24" s="5">
-        <v>73.7</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1421,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>89.90000000000001</v>
+        <v>87.8</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>245000</v>
+        <v>244000</v>
       </c>
       <c r="G25" s="7">
-        <v>9000</v>
+        <v>2000</v>
       </c>
       <c r="H25" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I25" s="7">
-        <v>16750</v>
+        <v>16778</v>
       </c>
       <c r="J25" s="5">
-        <v>73.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1454,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>75.40000000000001</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>1230000</v>
+        <v>129000</v>
       </c>
       <c r="G26" s="7">
-        <v>-73000</v>
+        <v>5000</v>
       </c>
       <c r="H26" s="7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="I26" s="7">
-        <v>48167</v>
+        <v>12625</v>
       </c>
       <c r="J26" s="5">
-        <v>73.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1487,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>90</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>241000</v>
+        <v>152000</v>
       </c>
       <c r="G27" s="7">
-        <v>11000</v>
+        <v>30000</v>
       </c>
       <c r="H27" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>15375</v>
+        <v>14667</v>
       </c>
       <c r="J27" s="5">
-        <v>73.3</v>
+        <v>72.3</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1520,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>88</v>
+        <v>89.2</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>421000</v>
+        <v>181000</v>
       </c>
       <c r="G28" s="7">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="H28" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>18000</v>
+        <v>12571</v>
       </c>
       <c r="J28" s="5">
-        <v>72.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1553,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>87.90000000000001</v>
+        <v>87.3</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>404000</v>
+        <v>421000</v>
       </c>
       <c r="G29" s="7">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="H29" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I29" s="7">
-        <v>16875</v>
+        <v>16000</v>
       </c>
       <c r="J29" s="5">
-        <v>72.59999999999999</v>
+        <v>72</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,23 +1586,23 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>86.2</v>
+        <v>75.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>275000</v>
+        <v>1161000</v>
       </c>
       <c r="G30" s="7">
-        <v>32000</v>
+        <v>-69000</v>
       </c>
       <c r="H30" s="7">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I30" s="7">
-        <v>26000</v>
+        <v>42000</v>
       </c>
       <c r="J30" s="5">
         <v>71.90000000000001</v>
@@ -1617,26 +1619,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>91.59999999999999</v>
+        <v>97.8</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>121000</v>
+        <v>116000</v>
       </c>
       <c r="G31" s="7">
-        <v>7000</v>
+        <v>16000</v>
       </c>
       <c r="H31" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I31" s="7">
-        <v>6000</v>
+        <v>24000</v>
       </c>
       <c r="J31" s="5">
-        <v>71.90000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1652,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>88.3</v>
+        <v>86.2</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>146000</v>
+        <v>339000</v>
       </c>
       <c r="G32" s="7">
-        <v>8000</v>
+        <v>-5000</v>
       </c>
       <c r="H32" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I32" s="7">
-        <v>12857</v>
+        <v>16444</v>
       </c>
       <c r="J32" s="5">
-        <v>71.8</v>
+        <v>71.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1685,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>90.09999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>224000</v>
+        <v>278000</v>
       </c>
       <c r="G33" s="7">
-        <v>14000</v>
+        <v>4000</v>
       </c>
       <c r="H33" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I33" s="7">
-        <v>8500</v>
+        <v>11333</v>
       </c>
       <c r="J33" s="5">
-        <v>71.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>91.5</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>105000</v>
+        <v>125000</v>
       </c>
       <c r="G34" s="7">
-        <v>10000</v>
+        <v>7000</v>
       </c>
       <c r="H34" s="7">
         <v>9</v>
       </c>
       <c r="I34" s="7">
-        <v>5250</v>
+        <v>8500</v>
       </c>
       <c r="J34" s="5">
-        <v>71.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>87.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>274000</v>
+        <v>576000</v>
       </c>
       <c r="G35" s="7">
-        <v>6000</v>
+        <v>36000</v>
       </c>
       <c r="H35" s="7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I35" s="7">
-        <v>12250</v>
+        <v>22846</v>
       </c>
       <c r="J35" s="5">
-        <v>71.40000000000001</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>89.3</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>118000</v>
+        <v>313000</v>
       </c>
       <c r="G36" s="7">
-        <v>8000</v>
+        <v>55000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I36" s="7">
-        <v>8714</v>
+        <v>44667</v>
       </c>
       <c r="J36" s="5">
-        <v>71.3</v>
+        <v>70.8</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>89</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>258000</v>
+        <v>254000</v>
       </c>
       <c r="G37" s="7">
-        <v>5000</v>
+        <v>72000</v>
       </c>
       <c r="H37" s="7">
         <v>9</v>
       </c>
       <c r="I37" s="7">
-        <v>9125</v>
+        <v>15000</v>
       </c>
       <c r="J37" s="5">
-        <v>71.2</v>
+        <v>70.7</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>87.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>169000</v>
+        <v>906000</v>
       </c>
       <c r="G38" s="7">
-        <v>10000</v>
+        <v>4000</v>
       </c>
       <c r="H38" s="7">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="I38" s="7">
-        <v>12667</v>
+        <v>27870</v>
       </c>
       <c r="J38" s="5">
-        <v>71.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>82.59999999999999</v>
+        <v>82</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>418000</v>
+        <v>434000</v>
       </c>
       <c r="G39" s="7">
-        <v>21000</v>
+        <v>16000</v>
       </c>
       <c r="H39" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I39" s="7">
-        <v>22500</v>
+        <v>22118</v>
       </c>
       <c r="J39" s="5">
-        <v>71.09999999999999</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>87.09999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>122000</v>
+        <v>103000</v>
       </c>
       <c r="G40" s="7">
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="H40" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>12750</v>
+        <v>17333</v>
       </c>
       <c r="J40" s="5">
-        <v>71.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>79.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>902000</v>
+        <v>650000</v>
       </c>
       <c r="G41" s="7">
-        <v>4000</v>
+        <v>24000</v>
       </c>
       <c r="H41" s="7">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="I41" s="7">
-        <v>28955</v>
+        <v>18250</v>
       </c>
       <c r="J41" s="5">
-        <v>70.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>86.7</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>231000</v>
+        <v>402000</v>
       </c>
       <c r="G42" s="7">
-        <v>27000</v>
+        <v>35000</v>
       </c>
       <c r="H42" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I42" s="7">
-        <v>12875</v>
+        <v>28500</v>
       </c>
       <c r="J42" s="5">
-        <v>70.90000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>84.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>626000</v>
+        <v>220000</v>
       </c>
       <c r="G43" s="7">
-        <v>32000</v>
+        <v>7000</v>
       </c>
       <c r="H43" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I43" s="7">
-        <v>17429</v>
+        <v>8222</v>
       </c>
       <c r="J43" s="5">
-        <v>70.8</v>
+        <v>70.2</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.5</v>
+        <v>86.3</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>282000</v>
+        <v>191000</v>
       </c>
       <c r="G44" s="7">
-        <v>-2000</v>
+        <v>6000</v>
       </c>
       <c r="H44" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I44" s="7">
-        <v>12375</v>
+        <v>18800</v>
       </c>
       <c r="J44" s="5">
-        <v>70.7</v>
+        <v>70.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>96.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>104000</v>
+        <v>258000</v>
       </c>
       <c r="G45" s="7">
-        <v>39000</v>
+        <v>0</v>
       </c>
       <c r="H45" s="7">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="I45" s="7">
-        <v>21667</v>
+        <v>8111</v>
       </c>
       <c r="J45" s="5">
-        <v>70.7</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>87.2</v>
+        <v>89.3</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>135000</v>
+        <v>118000</v>
       </c>
       <c r="G46" s="7">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="H46" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I46" s="7">
-        <v>10714</v>
+        <v>3222</v>
       </c>
       <c r="J46" s="5">
-        <v>70.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2145,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>83.3</v>
+        <v>88.2</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>242000</v>
+        <v>552000</v>
       </c>
       <c r="G47" s="7">
-        <v>-9000</v>
+        <v>-3000</v>
       </c>
       <c r="H47" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I47" s="7">
-        <v>18625</v>
+        <v>5222</v>
       </c>
       <c r="J47" s="5">
-        <v>70.5</v>
+        <v>69.8</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>88.8</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>101000</v>
+        <v>105000</v>
       </c>
       <c r="G48" s="7">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="H48" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I48" s="7">
-        <v>6750</v>
+        <v>6444</v>
       </c>
       <c r="J48" s="5">
-        <v>70.5</v>
+        <v>69.7</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2209,30 +2211,28 @@
       <c r="A49" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B49" s="5">
-        <v>9.9</v>
-      </c>
+      <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>90.8</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>142000</v>
+        <v>268000</v>
       </c>
       <c r="G49" s="7">
-        <v>13000</v>
+        <v>-5000</v>
       </c>
       <c r="H49" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I49" s="7">
-        <v>10000</v>
+        <v>14111</v>
       </c>
       <c r="J49" s="5">
-        <v>70.40000000000001</v>
+        <v>69.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>88.5</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>555000</v>
+        <v>147000</v>
       </c>
       <c r="G50" s="7">
-        <v>-1000</v>
+        <v>1000</v>
       </c>
       <c r="H50" s="7">
         <v>9</v>
       </c>
       <c r="I50" s="7">
-        <v>6250</v>
+        <v>11375</v>
       </c>
       <c r="J50" s="5">
-        <v>70.2</v>
+        <v>69.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>87.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>192000</v>
+        <v>651000</v>
       </c>
       <c r="G51" s="7">
-        <v>15000</v>
+        <v>21000</v>
       </c>
       <c r="H51" s="7">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="I51" s="7">
-        <v>7625</v>
+        <v>25706</v>
       </c>
       <c r="J51" s="5">
-        <v>70</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>78.8</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>630000</v>
+        <v>127000</v>
       </c>
       <c r="G52" s="7">
-        <v>29000</v>
+        <v>4000</v>
       </c>
       <c r="H52" s="7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I52" s="7">
-        <v>26000</v>
+        <v>5444</v>
       </c>
       <c r="J52" s="5">
-        <v>69.8</v>
+        <v>69.3</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,14 +2345,14 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>86.5</v>
+        <v>84</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>213000</v>
+        <v>219000</v>
       </c>
       <c r="G53" s="7">
         <v>5000</v>
@@ -2361,10 +2361,10 @@
         <v>9</v>
       </c>
       <c r="I53" s="7">
-        <v>8375</v>
+        <v>11875</v>
       </c>
       <c r="J53" s="5">
-        <v>69.7</v>
+        <v>69.2</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>88.09999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>110000</v>
+        <v>2645000</v>
       </c>
       <c r="G54" s="7">
-        <v>8000</v>
+        <v>-7000</v>
       </c>
       <c r="H54" s="7">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="I54" s="7">
-        <v>5000</v>
+        <v>15744</v>
       </c>
       <c r="J54" s="5">
-        <v>69.7</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-23T04:28:51+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-24T04:17:18+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>我叫九江，李景隆那个九江！</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>神雕杨过：我以九阴九阳压天下！</t>
+  </si>
+  <si>
+    <t>四合院：1948年开局暴富躺平</t>
+  </si>
+  <si>
+    <t>火影：九尾之夜，雷光万劫</t>
+  </si>
+  <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>饰演封于修，女友神仙姐姐</t>
+  </si>
+  <si>
+    <t>武道通神：我的增益永久生效</t>
+  </si>
+  <si>
+    <t>末世轮盘：开局指定抽取序列魔药</t>
+  </si>
+  <si>
+    <t>扫黑风暴之怒海惊涛</t>
+  </si>
+  <si>
+    <t>见鬼！求生系统把我投放到80年</t>
+  </si>
+  <si>
+    <t>高冷？外冷内齁！你们请攻略我吧</t>
+  </si>
+  <si>
+    <t>名义：取代沙瑞金，拿捏汉东全局</t>
+  </si>
+  <si>
+    <t>穿到六零，吃瓜看戏</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>亮剑：我和李云龙一起当警卫</t>
+  </si>
+  <si>
+    <t>天渊镇守百万载，你要挖我族人骨</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>型月：未婚妻露维亚，抽爆FGO</t>
+  </si>
+  <si>
     <t>重生年代：我怎么多了三个前妻</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>神雕杨过：我以九阴九阳压天下！</t>
-  </si>
-  <si>
-    <t>四合院：1948年开局暴富躺平</t>
-  </si>
-  <si>
-    <t>我叫九江，李景隆那个九江！</t>
-  </si>
-  <si>
-    <t>火影：九尾之夜，雷光万劫</t>
-  </si>
-  <si>
-    <t>饰演封于修，女友神仙姐姐</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>盗墓：八岁创雷法，震惊张海琪</t>
-  </si>
-  <si>
-    <t>扫黑风暴之怒海惊涛</t>
-  </si>
-  <si>
-    <t>穿到六零，吃瓜看戏</t>
+    <t>圣骑士是混子？我反手秒杀魔神！</t>
   </si>
   <si>
     <t>大唐：憨子别动手！有话好好说！</t>
   </si>
   <si>
-    <t>名义：取代沙瑞金，拿捏汉东全局</t>
-  </si>
-  <si>
-    <t>型月：未婚妻露维亚，抽爆FGO</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>天渊镇守百万载，你要挖我族人骨</t>
-  </si>
-  <si>
-    <t>见鬼！求生系统把我投放到80年</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>武道通神：我的增益永久生效</t>
+    <t>暴君：从一空输开始，登顶南韩</t>
   </si>
   <si>
     <t>全民天赋，我每年融合一个自己</t>
   </si>
   <si>
+    <t>西游：开局找黄狮精买功法</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离还在藏</t>
+  </si>
+  <si>
+    <t>自定义术式的我去咒回找乐子了</t>
+  </si>
+  <si>
+    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+  </si>
+  <si>
+    <t>高考出分前一晚，兑换北大录取书</t>
+  </si>
+  <si>
+    <t>入狱五年，归来仍是大佬</t>
+  </si>
+  <si>
+    <t>都重生了，谁还装富二代啊</t>
+  </si>
+  <si>
+    <t>洪荒：开局带着白莲绿茶拜师三清</t>
+  </si>
+  <si>
     <t>我都成旧日了，诡秘才入侵现实？</t>
   </si>
   <si>
-    <t>西游：开局找黄狮精买功法</t>
-  </si>
-  <si>
-    <t>亮剑：我和李云龙一起当警卫</t>
-  </si>
-  <si>
-    <t>暴君：从一空输开始，登顶南韩</t>
-  </si>
-  <si>
-    <t>自定义术式的我去咒回找乐子了</t>
-  </si>
-  <si>
-    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
-  </si>
-  <si>
-    <t>都重生了，谁还装富二代啊</t>
-  </si>
-  <si>
-    <t>洪荒：开局带着白莲绿茶拜师三清</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>天幕：进谏被罢官？那我回后世了</t>
+    <t>财阀大小姐的恶毒男友重生了</t>
+  </si>
+  <si>
+    <t>穿成警察，满城霸总排队来送业绩</t>
+  </si>
+  <si>
+    <t>全民：曝光最强修士！大秦什么鬼</t>
+  </si>
+  <si>
+    <t>精灵：杀穿超古代的我只想退休</t>
+  </si>
+  <si>
+    <t>大明：开局救了朱元璋全家</t>
+  </si>
+  <si>
+    <t>我，夜神月不是神，但富江是真鬼</t>
+  </si>
+  <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>四合院：我在1944是个败家子</t>
+  </si>
+  <si>
+    <t>咸鱼系统：前妻妹妹总拉我钓鱼</t>
+  </si>
+  <si>
+    <t>每日签到：这个军医什么都会</t>
+  </si>
+  <si>
+    <t>一人：开局复制老天师满级金光咒</t>
+  </si>
+  <si>
+    <t>我伪装成人类文明，拯救诸天万界</t>
   </si>
   <si>
     <t>红楼贾赦：我的金手指是山海经</t>
   </si>
   <si>
-    <t>财阀大小姐的恶毒男友重生了</t>
-  </si>
-  <si>
-    <t>拒白月光不做冤大头七零留城享福</t>
-  </si>
-  <si>
-    <t>弃子归来，已是绝世高手</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
-  </si>
-  <si>
-    <t>末世轮盘：开局指定抽取序列魔药</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>重活一世，谁还要追她啊？</t>
-  </si>
-  <si>
-    <t>一人：你苦修功法？我直接加点！</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离还在藏</t>
-  </si>
-  <si>
-    <t>儒道剑仙，苟在镇北王府当赘婿</t>
+    <t>觉醒死亡笔记，开局写下邪神名字</t>
   </si>
   <si>
     <t>穿越民国当姑爷</t>
   </si>
   <si>
-    <t>精灵：杀穿超古代的我只想退休</t>
-  </si>
-  <si>
-    <t>重生抗战：开局激活复制系统</t>
-  </si>
-  <si>
-    <t>每日签到：这个军医什么都会</t>
-  </si>
-  <si>
-    <t>觉醒死亡笔记，开局写下邪神名字</t>
-  </si>
-  <si>
-    <t>伪人降临！我是全场唯一预言家</t>
-  </si>
-  <si>
-    <t>修仙家族：从打下一片位面开始</t>
-  </si>
-  <si>
-    <t>四合院：我在1944是个败家子</t>
-  </si>
-  <si>
-    <t>神通者</t>
+    <t>四合院：开局被抓壮丁</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>94.7</v>
+        <v>100</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>862000</v>
+        <v>276000</v>
       </c>
       <c r="G5" s="7">
-        <v>188000</v>
+        <v>54000</v>
       </c>
       <c r="H5" s="7">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
-        <v>48643</v>
+        <v>47400</v>
       </c>
       <c r="J5" s="5">
-        <v>84.2</v>
+        <v>84.8</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>92.5</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>778000</v>
+        <v>877000</v>
       </c>
       <c r="G6" s="7">
-        <v>90000</v>
+        <v>99000</v>
       </c>
       <c r="H6" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="7">
-        <v>49556</v>
+        <v>54500</v>
       </c>
       <c r="J6" s="5">
-        <v>83.3</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -832,19 +832,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>346000</v>
+        <v>393000</v>
       </c>
       <c r="G7" s="7">
-        <v>51000</v>
+        <v>47000</v>
       </c>
       <c r="H7" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="7">
-        <v>32714</v>
+        <v>34500</v>
       </c>
       <c r="J7" s="5">
-        <v>83.2</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>100</v>
+        <v>90.7</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>222000</v>
+        <v>389000</v>
       </c>
       <c r="G8" s="7">
-        <v>118000</v>
+        <v>44000</v>
       </c>
       <c r="H8" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7">
-        <v>45750</v>
+        <v>37571</v>
       </c>
       <c r="J8" s="5">
-        <v>81.40000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>92.7</v>
+        <v>82.7</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>345000</v>
+        <v>2259000</v>
       </c>
       <c r="G9" s="7">
-        <v>45000</v>
+        <v>20000</v>
       </c>
       <c r="H9" s="7">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="I9" s="7">
-        <v>36500</v>
+        <v>47750</v>
       </c>
       <c r="J9" s="5">
-        <v>80.09999999999999</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>83.59999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>611000</v>
+        <v>645000</v>
       </c>
       <c r="G10" s="7">
-        <v>58000</v>
+        <v>34000</v>
       </c>
       <c r="H10" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7">
-        <v>85667</v>
+        <v>72750</v>
       </c>
       <c r="J10" s="5">
-        <v>79.40000000000001</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>82.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>2239000</v>
+        <v>396000</v>
       </c>
       <c r="G11" s="7">
-        <v>19000</v>
+        <v>14000</v>
       </c>
       <c r="H11" s="7">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="I11" s="7">
-        <v>48462</v>
+        <v>21000</v>
       </c>
       <c r="J11" s="5">
-        <v>77.5</v>
+        <v>75.7</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>133000</v>
+        <v>126000</v>
       </c>
       <c r="G12" s="7">
-        <v>25000</v>
+        <v>23000</v>
       </c>
       <c r="H12" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I12" s="7">
-        <v>6778</v>
+        <v>18750</v>
       </c>
       <c r="J12" s="5">
-        <v>76.7</v>
+        <v>74.5</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>94.09999999999999</v>
+        <v>90.8</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>282000</v>
+        <v>294000</v>
       </c>
       <c r="G13" s="7">
-        <v>20000</v>
+        <v>12000</v>
       </c>
       <c r="H13" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I13" s="7">
-        <v>18444</v>
+        <v>17800</v>
       </c>
       <c r="J13" s="5">
-        <v>76.40000000000001</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>93.40000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>213000</v>
+        <v>369000</v>
       </c>
       <c r="G14" s="7">
-        <v>15000</v>
+        <v>5000</v>
       </c>
       <c r="H14" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7">
-        <v>18667</v>
+        <v>20000</v>
       </c>
       <c r="J14" s="5">
-        <v>76</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>92.3</v>
+        <v>94</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>298000</v>
+        <v>170000</v>
       </c>
       <c r="G15" s="7">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="H15" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I15" s="7">
-        <v>18333</v>
+        <v>17600</v>
       </c>
       <c r="J15" s="5">
-        <v>75.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>90.8</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>436000</v>
+        <v>441000</v>
       </c>
       <c r="G16" s="7">
-        <v>11000</v>
+        <v>5000</v>
       </c>
       <c r="H16" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I16" s="7">
-        <v>21111</v>
+        <v>19500</v>
       </c>
       <c r="J16" s="5">
-        <v>75.2</v>
+        <v>74</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>90.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>282000</v>
+        <v>222000</v>
       </c>
       <c r="G17" s="7">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="H17" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I17" s="7">
-        <v>20333</v>
+        <v>17700</v>
       </c>
       <c r="J17" s="5">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>90.7</v>
+        <v>89.8</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>329000</v>
+        <v>537000</v>
       </c>
       <c r="G18" s="7">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H18" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I18" s="7">
-        <v>18556</v>
+        <v>17100</v>
       </c>
       <c r="J18" s="5">
-        <v>74.5</v>
+        <v>73.7</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1219,30 +1219,28 @@
       <c r="A19" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="5">
-        <v>9.9</v>
-      </c>
+      <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>93.2</v>
+        <v>89.8</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>157000</v>
+        <v>336000</v>
       </c>
       <c r="G19" s="7">
-        <v>15000</v>
+        <v>7000</v>
       </c>
       <c r="H19" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I19" s="7">
-        <v>10833</v>
+        <v>17400</v>
       </c>
       <c r="J19" s="5">
-        <v>74</v>
+        <v>73.7</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1256,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>88.09999999999999</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>364000</v>
+        <v>137000</v>
       </c>
       <c r="G20" s="7">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="H20" s="7">
         <v>10</v>
       </c>
       <c r="I20" s="7">
-        <v>21667</v>
+        <v>12111</v>
       </c>
       <c r="J20" s="5">
-        <v>73.90000000000001</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,28 +1285,30 @@
       <c r="A21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="5"/>
+      <c r="B21" s="5">
+        <v>9.9</v>
+      </c>
       <c r="C21" s="5">
-        <v>88.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>531000</v>
+        <v>170000</v>
       </c>
       <c r="G21" s="7">
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="H21" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>18333</v>
+        <v>11143</v>
       </c>
       <c r="J21" s="5">
-        <v>73.40000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1322,26 +1322,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>86.5</v>
+        <v>89.2</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>382000</v>
+        <v>344000</v>
       </c>
       <c r="G22" s="7">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="H22" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I22" s="7">
-        <v>21778</v>
+        <v>15300</v>
       </c>
       <c r="J22" s="5">
-        <v>73</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1355,26 +1355,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>89</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>252000</v>
+        <v>287000</v>
       </c>
       <c r="G23" s="7">
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="H23" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I23" s="7">
-        <v>15667</v>
+        <v>18800</v>
       </c>
       <c r="J23" s="5">
-        <v>72.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1388,26 +1388,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>89.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>251000</v>
+        <v>830000</v>
       </c>
       <c r="G24" s="7">
-        <v>10000</v>
+        <v>-32000</v>
       </c>
       <c r="H24" s="7">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="I24" s="7">
-        <v>14778</v>
+        <v>43267</v>
       </c>
       <c r="J24" s="5">
-        <v>72.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1421,26 +1421,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>87.8</v>
+        <v>92.5</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>244000</v>
+        <v>100000</v>
       </c>
       <c r="G25" s="7">
-        <v>2000</v>
+        <v>30000</v>
       </c>
       <c r="H25" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>16778</v>
+        <v>5833</v>
       </c>
       <c r="J25" s="5">
-        <v>72.5</v>
+        <v>72.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1454,26 +1454,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>89.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>129000</v>
+        <v>298000</v>
       </c>
       <c r="G26" s="7">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="H26" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I26" s="7">
-        <v>12625</v>
+        <v>16500</v>
       </c>
       <c r="J26" s="5">
-        <v>72.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1487,26 +1487,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>88.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>152000</v>
+        <v>172000</v>
       </c>
       <c r="G27" s="7">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="H27" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I27" s="7">
-        <v>14667</v>
+        <v>15200</v>
       </c>
       <c r="J27" s="5">
-        <v>72.3</v>
+        <v>72</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1520,26 +1520,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>89.2</v>
+        <v>87.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>181000</v>
+        <v>256000</v>
       </c>
       <c r="G28" s="7">
-        <v>12000</v>
+        <v>4000</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I28" s="7">
-        <v>12571</v>
+        <v>14500</v>
       </c>
       <c r="J28" s="5">
-        <v>72.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1553,26 +1553,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>87.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>421000</v>
+        <v>245000</v>
       </c>
       <c r="G29" s="7">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H29" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" s="7">
-        <v>16000</v>
+        <v>15200</v>
       </c>
       <c r="J29" s="5">
-        <v>72</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1586,23 +1586,23 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>75.3</v>
+        <v>86.8</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>1161000</v>
+        <v>198000</v>
       </c>
       <c r="G30" s="7">
-        <v>-69000</v>
+        <v>7000</v>
       </c>
       <c r="H30" s="7">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I30" s="7">
-        <v>42000</v>
+        <v>16833</v>
       </c>
       <c r="J30" s="5">
         <v>71.90000000000001</v>
@@ -1619,26 +1619,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>97.8</v>
+        <v>88.3</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>116000</v>
+        <v>192000</v>
       </c>
       <c r="G31" s="7">
-        <v>16000</v>
+        <v>11000</v>
       </c>
       <c r="H31" s="7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I31" s="7">
-        <v>24000</v>
+        <v>12375</v>
       </c>
       <c r="J31" s="5">
-        <v>71.8</v>
+        <v>71.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1652,26 +1652,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>86.2</v>
+        <v>87</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>339000</v>
+        <v>420000</v>
       </c>
       <c r="G32" s="7">
-        <v>-5000</v>
+        <v>-1000</v>
       </c>
       <c r="H32" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I32" s="7">
-        <v>16444</v>
+        <v>14300</v>
       </c>
       <c r="J32" s="5">
-        <v>71.5</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1685,26 +1685,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>87.8</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>278000</v>
+        <v>916000</v>
       </c>
       <c r="G33" s="7">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="H33" s="7">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I33" s="7">
-        <v>11333</v>
+        <v>27125</v>
       </c>
       <c r="J33" s="5">
-        <v>71.09999999999999</v>
+        <v>70.8</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>88.90000000000001</v>
+        <v>82.2</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>125000</v>
+        <v>451000</v>
       </c>
       <c r="G34" s="7">
-        <v>7000</v>
+        <v>17000</v>
       </c>
       <c r="H34" s="7">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="I34" s="7">
-        <v>8500</v>
+        <v>21833</v>
       </c>
       <c r="J34" s="5">
-        <v>71</v>
+        <v>70.7</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>82.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>576000</v>
+        <v>1091000</v>
       </c>
       <c r="G35" s="7">
-        <v>36000</v>
+        <v>-70000</v>
       </c>
       <c r="H35" s="7">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="I35" s="7">
-        <v>22846</v>
+        <v>36400</v>
       </c>
       <c r="J35" s="5">
-        <v>70.90000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>86.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>313000</v>
+        <v>125000</v>
       </c>
       <c r="G36" s="7">
-        <v>55000</v>
+        <v>9000</v>
       </c>
       <c r="H36" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I36" s="7">
-        <v>44667</v>
+        <v>20250</v>
       </c>
       <c r="J36" s="5">
-        <v>70.8</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>85.40000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>254000</v>
+        <v>251000</v>
       </c>
       <c r="G37" s="7">
-        <v>72000</v>
+        <v>0</v>
       </c>
       <c r="H37" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I37" s="7">
-        <v>15000</v>
+        <v>13300</v>
       </c>
       <c r="J37" s="5">
-        <v>70.7</v>
+        <v>70.2</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>79.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>906000</v>
+        <v>600000</v>
       </c>
       <c r="G38" s="7">
-        <v>4000</v>
+        <v>24000</v>
       </c>
       <c r="H38" s="7">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I38" s="7">
-        <v>27870</v>
+        <v>22929</v>
       </c>
       <c r="J38" s="5">
-        <v>70.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>82</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>434000</v>
+        <v>269000</v>
       </c>
       <c r="G39" s="7">
-        <v>16000</v>
+        <v>19000</v>
       </c>
       <c r="H39" s="7">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="I39" s="7">
-        <v>22118</v>
+        <v>25667</v>
       </c>
       <c r="J39" s="5">
-        <v>70.59999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>98.40000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>103000</v>
+        <v>100000</v>
       </c>
       <c r="G40" s="7">
-        <v>18000</v>
+        <v>3000</v>
       </c>
       <c r="H40" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>17333</v>
+        <v>14600</v>
       </c>
       <c r="J40" s="5">
-        <v>70.5</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>82.90000000000001</v>
+        <v>88.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>650000</v>
+        <v>552000</v>
       </c>
       <c r="G41" s="7">
-        <v>24000</v>
+        <v>0</v>
       </c>
       <c r="H41" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I41" s="7">
-        <v>18250</v>
+        <v>4700</v>
       </c>
       <c r="J41" s="5">
-        <v>70.2</v>
+        <v>70</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>78.40000000000001</v>
+        <v>92.5</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>402000</v>
+        <v>106000</v>
       </c>
       <c r="G42" s="7">
-        <v>35000</v>
+        <v>8000</v>
       </c>
       <c r="H42" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I42" s="7">
-        <v>28500</v>
+        <v>15250</v>
       </c>
       <c r="J42" s="5">
-        <v>70.2</v>
+        <v>69.7</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>87.5</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>220000</v>
+        <v>117000</v>
       </c>
       <c r="G43" s="7">
-        <v>7000</v>
+        <v>6000</v>
       </c>
       <c r="H43" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I43" s="7">
-        <v>8222</v>
+        <v>7500</v>
       </c>
       <c r="J43" s="5">
-        <v>70.2</v>
+        <v>69.5</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>86.3</v>
+        <v>82.7</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>191000</v>
+        <v>2659000</v>
       </c>
       <c r="G44" s="7">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="H44" s="7">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="I44" s="7">
-        <v>18800</v>
+        <v>15700</v>
       </c>
       <c r="J44" s="5">
-        <v>70.2</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>87.09999999999999</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>258000</v>
+        <v>666000</v>
       </c>
       <c r="G45" s="7">
-        <v>0</v>
+        <v>16000</v>
       </c>
       <c r="H45" s="7">
         <v>10</v>
       </c>
       <c r="I45" s="7">
-        <v>8111</v>
+        <v>18000</v>
       </c>
       <c r="J45" s="5">
-        <v>69.90000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>89.3</v>
+        <v>84.5</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>118000</v>
+        <v>225000</v>
       </c>
       <c r="G46" s="7">
-        <v>8000</v>
+        <v>6000</v>
       </c>
       <c r="H46" s="7">
         <v>10</v>
       </c>
       <c r="I46" s="7">
-        <v>3222</v>
+        <v>11222</v>
       </c>
       <c r="J46" s="5">
-        <v>69.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>88.2</v>
+        <v>84.8</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>552000</v>
+        <v>222000</v>
       </c>
       <c r="G47" s="7">
-        <v>-3000</v>
+        <v>3000</v>
       </c>
       <c r="H47" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I47" s="7">
-        <v>5222</v>
+        <v>10571</v>
       </c>
       <c r="J47" s="5">
-        <v>69.8</v>
+        <v>69.3</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>105000</v>
+        <v>263000</v>
       </c>
       <c r="G48" s="7">
-        <v>4000</v>
+        <v>-5000</v>
       </c>
       <c r="H48" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I48" s="7">
-        <v>6444</v>
+        <v>12200</v>
       </c>
       <c r="J48" s="5">
-        <v>69.7</v>
+        <v>69</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>83.59999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>268000</v>
+        <v>270000</v>
       </c>
       <c r="G49" s="7">
-        <v>-5000</v>
+        <v>19000</v>
       </c>
       <c r="H49" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I49" s="7">
-        <v>14111</v>
+        <v>14900</v>
       </c>
       <c r="J49" s="5">
-        <v>69.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>84.90000000000001</v>
+        <v>90.8</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>147000</v>
+        <v>208000</v>
       </c>
       <c r="G50" s="7">
-        <v>1000</v>
+        <v>19000</v>
       </c>
       <c r="H50" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I50" s="7">
-        <v>11375</v>
+        <v>15750</v>
       </c>
       <c r="J50" s="5">
-        <v>69.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>78.2</v>
+        <v>85.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>651000</v>
+        <v>126000</v>
       </c>
       <c r="G51" s="7">
-        <v>21000</v>
+        <v>1000</v>
       </c>
       <c r="H51" s="7">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="I51" s="7">
-        <v>25706</v>
+        <v>7667</v>
       </c>
       <c r="J51" s="5">
-        <v>69.40000000000001</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>87.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>127000</v>
+        <v>147000</v>
       </c>
       <c r="G52" s="7">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="H52" s="7">
         <v>10</v>
       </c>
       <c r="I52" s="7">
-        <v>5444</v>
+        <v>10111</v>
       </c>
       <c r="J52" s="5">
-        <v>69.3</v>
+        <v>68.8</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>84</v>
+        <v>87.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>219000</v>
+        <v>124000</v>
       </c>
       <c r="G53" s="7">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H53" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I53" s="7">
-        <v>11875</v>
+        <v>3500</v>
       </c>
       <c r="J53" s="5">
-        <v>69.2</v>
+        <v>68.8</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>81.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>2645000</v>
+        <v>200000</v>
       </c>
       <c r="G54" s="7">
-        <v>-7000</v>
+        <v>9000</v>
       </c>
       <c r="H54" s="7">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="I54" s="7">
-        <v>15744</v>
+        <v>8400</v>
       </c>
       <c r="J54" s="5">
-        <v>68.90000000000001</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-24T04:17:18+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-25T04:20:30+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,55 +70,88 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>神雕杨过：我以九阴九阳压天下！</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>四合院：1948年开局暴富躺平</t>
+  </si>
+  <si>
+    <t>持械入宋</t>
+  </si>
+  <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>饰演封于修，女友神仙姐姐</t>
+  </si>
+  <si>
+    <t>火影：九尾之夜，雷光万劫</t>
+  </si>
+  <si>
+    <t>开局狱主，烧香召唤无敌仙帝</t>
+  </si>
+  <si>
     <t>我叫九江，李景隆那个九江！</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>神雕杨过：我以九阴九阳压天下！</t>
-  </si>
-  <si>
-    <t>四合院：1948年开局暴富躺平</t>
-  </si>
-  <si>
-    <t>火影：九尾之夜，雷光万劫</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
-  </si>
-  <si>
-    <t>饰演封于修，女友神仙姐姐</t>
-  </si>
-  <si>
     <t>武道通神：我的增益永久生效</t>
   </si>
   <si>
     <t>末世轮盘：开局指定抽取序列魔药</t>
   </si>
   <si>
-    <t>扫黑风暴之怒海惊涛</t>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>高冷？外冷内齁！你们请攻略我吧</t>
+  </si>
+  <si>
+    <t>圣骑士是混子？我反手秒杀魔神！</t>
   </si>
   <si>
     <t>见鬼！求生系统把我投放到80年</t>
   </si>
   <si>
-    <t>高冷？外冷内齁！你们请攻略我吧</t>
-  </si>
-  <si>
-    <t>名义：取代沙瑞金，拿捏汉东全局</t>
+    <t>龙族：我的强化每月刷新</t>
+  </si>
+  <si>
+    <t>型月：未婚妻露维亚，抽爆FGO</t>
+  </si>
+  <si>
+    <t>穿成警察，满城霸总排队来送业绩</t>
+  </si>
+  <si>
+    <t>亮剑：我和李云龙一起当警卫</t>
+  </si>
+  <si>
+    <t>红色人生模拟，我怎么成老干部了</t>
+  </si>
+  <si>
+    <t>边军悍卒，绝色罪女天天求暖床</t>
+  </si>
+  <si>
+    <t>我伪装成人类文明，拯救诸天万界</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
   </si>
   <si>
     <t>穿到六零，吃瓜看戏</t>
   </si>
   <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>亮剑：我和李云龙一起当警卫</t>
+    <t>儒道剑仙，苟在镇北王府当赘婿</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离还在藏</t>
+  </si>
+  <si>
+    <t>洪荒：开局带着白莲绿茶拜师三清</t>
+  </si>
+  <si>
+    <t>西游：开局找黄狮精买功法</t>
   </si>
   <si>
     <t>天渊镇守百万载，你要挖我族人骨</t>
@@ -127,100 +160,67 @@
     <t>我在诸天当超能力爷</t>
   </si>
   <si>
-    <t>型月：未婚妻露维亚，抽爆FGO</t>
+    <t>自定义术式的我去咒回找乐子了</t>
+  </si>
+  <si>
+    <t>大明：开局救了朱元璋全家</t>
+  </si>
+  <si>
+    <t>四合院：从红二十五开始进步</t>
+  </si>
+  <si>
+    <t>我都成旧日了，诡秘才入侵现实？</t>
   </si>
   <si>
     <t>重生年代：我怎么多了三个前妻</t>
   </si>
   <si>
-    <t>圣骑士是混子？我反手秒杀魔神！</t>
-  </si>
-  <si>
-    <t>大唐：憨子别动手！有话好好说！</t>
+    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
+  </si>
+  <si>
+    <t>全民领主：抽到人族，但来自战锤</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
   </si>
   <si>
     <t>暴君：从一空输开始，登顶南韩</t>
   </si>
   <si>
-    <t>全民天赋，我每年融合一个自己</t>
-  </si>
-  <si>
-    <t>西游：开局找黄狮精买功法</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离还在藏</t>
-  </si>
-  <si>
-    <t>自定义术式的我去咒回找乐子了</t>
-  </si>
-  <si>
-    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
-  </si>
-  <si>
-    <t>高考出分前一晚，兑换北大录取书</t>
+    <t>鬼谷下山：九封婚书闯都市</t>
+  </si>
+  <si>
+    <t>全民：曝光最强修士！大秦什么鬼</t>
+  </si>
+  <si>
+    <t>四合院：大军进城，我系统吓跑了</t>
+  </si>
+  <si>
+    <t>明明想单推，结果被病娇包围</t>
+  </si>
+  <si>
+    <t>咸鱼系统：前妻妹妹总拉我钓鱼</t>
+  </si>
+  <si>
+    <t>神通者</t>
+  </si>
+  <si>
+    <t>都重生了，谁还装富二代啊</t>
   </si>
   <si>
     <t>入狱五年，归来仍是大佬</t>
   </si>
   <si>
-    <t>都重生了，谁还装富二代啊</t>
-  </si>
-  <si>
-    <t>洪荒：开局带着白莲绿茶拜师三清</t>
-  </si>
-  <si>
-    <t>我都成旧日了，诡秘才入侵现实？</t>
-  </si>
-  <si>
-    <t>财阀大小姐的恶毒男友重生了</t>
-  </si>
-  <si>
-    <t>穿成警察，满城霸总排队来送业绩</t>
-  </si>
-  <si>
-    <t>全民：曝光最强修士！大秦什么鬼</t>
-  </si>
-  <si>
-    <t>精灵：杀穿超古代的我只想退休</t>
-  </si>
-  <si>
-    <t>大明：开局救了朱元璋全家</t>
-  </si>
-  <si>
-    <t>我，夜神月不是神，但富江是真鬼</t>
-  </si>
-  <si>
-    <t>神通者</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>四合院：我在1944是个败家子</t>
-  </si>
-  <si>
-    <t>咸鱼系统：前妻妹妹总拉我钓鱼</t>
-  </si>
-  <si>
-    <t>每日签到：这个军医什么都会</t>
-  </si>
-  <si>
-    <t>一人：开局复制老天师满级金光咒</t>
-  </si>
-  <si>
-    <t>我伪装成人类文明，拯救诸天万界</t>
-  </si>
-  <si>
-    <t>红楼贾赦：我的金手指是山海经</t>
+    <t>海洋求生？可我是人鱼公主！</t>
+  </si>
+  <si>
+    <t>拒白月光不做冤大头七零留城享福</t>
   </si>
   <si>
     <t>觉醒死亡笔记，开局写下邪神名字</t>
   </si>
   <si>
-    <t>穿越民国当姑爷</t>
-  </si>
-  <si>
-    <t>四合院：开局被抓壮丁</t>
+    <t>霍格沃茨：马尔福竟是傲娇千金？</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>100</v>
+        <v>90.2</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>276000</v>
+        <v>967000</v>
       </c>
       <c r="G5" s="7">
-        <v>54000</v>
+        <v>90000</v>
       </c>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I5" s="7">
-        <v>47400</v>
+        <v>57727</v>
       </c>
       <c r="J5" s="5">
-        <v>84.8</v>
+        <v>84</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>92.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>877000</v>
+        <v>433000</v>
       </c>
       <c r="G6" s="7">
-        <v>99000</v>
+        <v>40000</v>
       </c>
       <c r="H6" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I6" s="7">
-        <v>54500</v>
+        <v>35111</v>
       </c>
       <c r="J6" s="5">
-        <v>84.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>393000</v>
+        <v>387000</v>
       </c>
       <c r="G7" s="7">
-        <v>47000</v>
+        <v>93000</v>
       </c>
       <c r="H7" s="7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I7" s="7">
-        <v>34500</v>
+        <v>100500</v>
       </c>
       <c r="J7" s="5">
-        <v>83.59999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>90.7</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>389000</v>
+        <v>2300000</v>
       </c>
       <c r="G8" s="7">
-        <v>44000</v>
+        <v>41000</v>
       </c>
       <c r="H8" s="7">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="I8" s="7">
-        <v>37571</v>
+        <v>47585</v>
       </c>
       <c r="J8" s="5">
-        <v>79.3</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>82.7</v>
+        <v>79</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>2259000</v>
+        <v>666000</v>
       </c>
       <c r="G9" s="7">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="H9" s="7">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>47750</v>
+        <v>62400</v>
       </c>
       <c r="J9" s="5">
-        <v>77.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>80.40000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>645000</v>
+        <v>420000</v>
       </c>
       <c r="G10" s="7">
-        <v>34000</v>
+        <v>31000</v>
       </c>
       <c r="H10" s="7">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I10" s="7">
-        <v>72750</v>
+        <v>36750</v>
       </c>
       <c r="J10" s="5">
-        <v>77.40000000000001</v>
+        <v>76.5</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>91.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>396000</v>
+        <v>103000</v>
       </c>
       <c r="G11" s="7">
-        <v>14000</v>
+        <v>16000</v>
       </c>
       <c r="H11" s="7">
         <v>11</v>
       </c>
       <c r="I11" s="7">
-        <v>21000</v>
+        <v>7700</v>
       </c>
       <c r="J11" s="5">
-        <v>75.7</v>
+        <v>76</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>99.7</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>126000</v>
+        <v>309000</v>
       </c>
       <c r="G12" s="7">
-        <v>23000</v>
+        <v>33000</v>
       </c>
       <c r="H12" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I12" s="7">
-        <v>18750</v>
+        <v>45000</v>
       </c>
       <c r="J12" s="5">
-        <v>74.5</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>90.8</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>294000</v>
+        <v>411000</v>
       </c>
       <c r="G13" s="7">
-        <v>12000</v>
+        <v>15000</v>
       </c>
       <c r="H13" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I13" s="7">
-        <v>17800</v>
+        <v>20455</v>
       </c>
       <c r="J13" s="5">
-        <v>74.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>89.2</v>
+        <v>96</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>369000</v>
+        <v>140000</v>
       </c>
       <c r="G14" s="7">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="H14" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>20000</v>
+        <v>17800</v>
       </c>
       <c r="J14" s="5">
-        <v>74.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>94</v>
+        <v>92.5</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>170000</v>
+        <v>352000</v>
       </c>
       <c r="G15" s="7">
         <v>16000</v>
       </c>
       <c r="H15" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I15" s="7">
-        <v>17600</v>
+        <v>17273</v>
       </c>
       <c r="J15" s="5">
-        <v>74.09999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>89.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>441000</v>
+        <v>184000</v>
       </c>
       <c r="G16" s="7">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="H16" s="7">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I16" s="7">
-        <v>19500</v>
+        <v>17000</v>
       </c>
       <c r="J16" s="5">
-        <v>74</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>90.09999999999999</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>222000</v>
+        <v>120000</v>
       </c>
       <c r="G17" s="7">
-        <v>9000</v>
+        <v>20000</v>
       </c>
       <c r="H17" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>17700</v>
+        <v>7857</v>
       </c>
       <c r="J17" s="5">
         <v>74</v>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>89.8</v>
+        <v>89.5</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>537000</v>
+        <v>375000</v>
       </c>
       <c r="G18" s="7">
         <v>6000</v>
       </c>
       <c r="H18" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I18" s="7">
-        <v>17100</v>
+        <v>18727</v>
       </c>
       <c r="J18" s="5">
-        <v>73.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>89.8</v>
+        <v>97.3</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>336000</v>
+        <v>260000</v>
       </c>
       <c r="G19" s="7">
-        <v>7000</v>
+        <v>31000</v>
       </c>
       <c r="H19" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I19" s="7">
-        <v>17400</v>
+        <v>1182</v>
       </c>
       <c r="J19" s="5">
-        <v>73.7</v>
+        <v>73.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,23 +1254,23 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>91.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>137000</v>
+        <v>297000</v>
       </c>
       <c r="G20" s="7">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H20" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I20" s="7">
-        <v>12111</v>
+        <v>18000</v>
       </c>
       <c r="J20" s="5">
         <v>73.59999999999999</v>
@@ -1285,30 +1285,28 @@
       <c r="A21" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="5">
-        <v>9.9</v>
-      </c>
+      <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>91.90000000000001</v>
+        <v>95</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>170000</v>
+        <v>292000</v>
       </c>
       <c r="G21" s="7">
-        <v>13000</v>
+        <v>23000</v>
       </c>
       <c r="H21" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I21" s="7">
-        <v>11143</v>
+        <v>25000</v>
       </c>
       <c r="J21" s="5">
-        <v>73.3</v>
+        <v>73.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1322,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>89.2</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>344000</v>
+        <v>145000</v>
       </c>
       <c r="G22" s="7">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="H22" s="7">
         <v>11</v>
       </c>
       <c r="I22" s="7">
-        <v>15300</v>
+        <v>11700</v>
       </c>
       <c r="J22" s="5">
-        <v>72.90000000000001</v>
+        <v>73.3</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1355,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>87.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>287000</v>
+        <v>157000</v>
       </c>
       <c r="G23" s="7">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="H23" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I23" s="7">
-        <v>18800</v>
+        <v>5545</v>
       </c>
       <c r="J23" s="5">
-        <v>72.8</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1388,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>75.90000000000001</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>830000</v>
+        <v>138000</v>
       </c>
       <c r="G24" s="7">
-        <v>-32000</v>
+        <v>8000</v>
       </c>
       <c r="H24" s="7">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I24" s="7">
-        <v>43267</v>
+        <v>7800</v>
       </c>
       <c r="J24" s="5">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1421,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>92.5</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>100000</v>
+        <v>224000</v>
       </c>
       <c r="G25" s="7">
-        <v>30000</v>
+        <v>16000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I25" s="7">
-        <v>5833</v>
+        <v>15800</v>
       </c>
       <c r="J25" s="5">
-        <v>72.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1454,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>87.40000000000001</v>
+        <v>87.7</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>298000</v>
+        <v>532000</v>
       </c>
       <c r="G26" s="7">
-        <v>0</v>
+        <v>-5000</v>
       </c>
       <c r="H26" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I26" s="7">
-        <v>16500</v>
+        <v>15091</v>
       </c>
       <c r="J26" s="5">
-        <v>72.2</v>
+        <v>72</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1487,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>87.7</v>
+        <v>86.8</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>172000</v>
+        <v>224000</v>
       </c>
       <c r="G27" s="7">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="H27" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I27" s="7">
-        <v>15200</v>
+        <v>16273</v>
       </c>
       <c r="J27" s="5">
-        <v>72</v>
+        <v>71.8</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1520,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>87.8</v>
+        <v>90.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>256000</v>
+        <v>260000</v>
       </c>
       <c r="G28" s="7">
-        <v>4000</v>
+        <v>9000</v>
       </c>
       <c r="H28" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I28" s="7">
-        <v>14500</v>
+        <v>6818</v>
       </c>
       <c r="J28" s="5">
-        <v>71.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1553,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>87.40000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>245000</v>
+        <v>205000</v>
       </c>
       <c r="G29" s="7">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="H29" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>15200</v>
+        <v>15429</v>
       </c>
       <c r="J29" s="5">
-        <v>71.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1586,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>86.8</v>
+        <v>89.5</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>198000</v>
+        <v>132000</v>
       </c>
       <c r="G30" s="7">
         <v>7000</v>
       </c>
       <c r="H30" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I30" s="7">
-        <v>16833</v>
+        <v>17600</v>
       </c>
       <c r="J30" s="5">
-        <v>71.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1619,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>88.3</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>192000</v>
+        <v>246000</v>
       </c>
       <c r="G31" s="7">
-        <v>11000</v>
+        <v>1000</v>
       </c>
       <c r="H31" s="7">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="I31" s="7">
-        <v>12375</v>
+        <v>13909</v>
       </c>
       <c r="J31" s="5">
-        <v>71.7</v>
+        <v>71.5</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,25 +1648,27 @@
       <c r="A32" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="5"/>
+      <c r="B32" s="5">
+        <v>9.9</v>
+      </c>
       <c r="C32" s="5">
-        <v>87</v>
+        <v>88.5</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>420000</v>
+        <v>178000</v>
       </c>
       <c r="G32" s="7">
-        <v>-1000</v>
+        <v>8000</v>
       </c>
       <c r="H32" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I32" s="7">
-        <v>14300</v>
+        <v>10750</v>
       </c>
       <c r="J32" s="5">
         <v>71.40000000000001</v>
@@ -1685,26 +1685,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>80.09999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>916000</v>
+        <v>342000</v>
       </c>
       <c r="G33" s="7">
-        <v>10000</v>
+        <v>-2000</v>
       </c>
       <c r="H33" s="7">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="I33" s="7">
-        <v>27125</v>
+        <v>13727</v>
       </c>
       <c r="J33" s="5">
-        <v>70.8</v>
+        <v>71.3</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>82.2</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>451000</v>
+        <v>202000</v>
       </c>
       <c r="G34" s="7">
-        <v>17000</v>
+        <v>10000</v>
       </c>
       <c r="H34" s="7">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I34" s="7">
-        <v>21833</v>
+        <v>12111</v>
       </c>
       <c r="J34" s="5">
-        <v>70.7</v>
+        <v>71.2</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>75.2</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>1091000</v>
+        <v>112000</v>
       </c>
       <c r="G35" s="7">
-        <v>-70000</v>
+        <v>6000</v>
       </c>
       <c r="H35" s="7">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I35" s="7">
-        <v>36400</v>
+        <v>13400</v>
       </c>
       <c r="J35" s="5">
-        <v>70.5</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>91.59999999999999</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>125000</v>
+        <v>318000</v>
       </c>
       <c r="G36" s="7">
-        <v>9000</v>
+        <v>40000</v>
       </c>
       <c r="H36" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I36" s="7">
-        <v>20250</v>
+        <v>37667</v>
       </c>
       <c r="J36" s="5">
-        <v>70.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>85.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>251000</v>
+        <v>253000</v>
       </c>
       <c r="G37" s="7">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="H37" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I37" s="7">
-        <v>13300</v>
+        <v>12273</v>
       </c>
       <c r="J37" s="5">
-        <v>70.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>80.59999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>600000</v>
+        <v>777000</v>
       </c>
       <c r="G38" s="7">
-        <v>24000</v>
+        <v>-53000</v>
       </c>
       <c r="H38" s="7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I38" s="7">
-        <v>22929</v>
+        <v>37250</v>
       </c>
       <c r="J38" s="5">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>93.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>269000</v>
+        <v>414000</v>
       </c>
       <c r="G39" s="7">
-        <v>19000</v>
+        <v>-6000</v>
       </c>
       <c r="H39" s="7">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I39" s="7">
-        <v>25667</v>
+        <v>12455</v>
       </c>
       <c r="J39" s="5">
-        <v>70.09999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>88.09999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>100000</v>
+        <v>124000</v>
       </c>
       <c r="G40" s="7">
-        <v>3000</v>
+        <v>18000</v>
       </c>
       <c r="H40" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I40" s="7">
-        <v>14600</v>
+        <v>19333</v>
       </c>
       <c r="J40" s="5">
-        <v>70.09999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>88.7</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>552000</v>
+        <v>689000</v>
       </c>
       <c r="G41" s="7">
-        <v>0</v>
+        <v>23000</v>
       </c>
       <c r="H41" s="7">
         <v>11</v>
       </c>
       <c r="I41" s="7">
-        <v>4700</v>
+        <v>18500</v>
       </c>
       <c r="J41" s="5">
-        <v>70</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>92.5</v>
+        <v>84</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>106000</v>
+        <v>188000</v>
       </c>
       <c r="G42" s="7">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="H42" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I42" s="7">
-        <v>15250</v>
+        <v>15273</v>
       </c>
       <c r="J42" s="5">
-        <v>69.7</v>
+        <v>70</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>86.59999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>117000</v>
+        <v>101000</v>
       </c>
       <c r="G43" s="7">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="H43" s="7">
         <v>11</v>
       </c>
       <c r="I43" s="7">
-        <v>7500</v>
+        <v>7700</v>
       </c>
       <c r="J43" s="5">
-        <v>69.5</v>
+        <v>70</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>82.7</v>
+        <v>85.2</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>2659000</v>
+        <v>101000</v>
       </c>
       <c r="G44" s="7">
-        <v>14000</v>
+        <v>1000</v>
       </c>
       <c r="H44" s="7">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="I44" s="7">
-        <v>15700</v>
+        <v>12333</v>
       </c>
       <c r="J44" s="5">
-        <v>69.40000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>81.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>666000</v>
+        <v>241000</v>
       </c>
       <c r="G45" s="7">
-        <v>16000</v>
+        <v>17000</v>
       </c>
       <c r="H45" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I45" s="7">
-        <v>18000</v>
+        <v>20250</v>
       </c>
       <c r="J45" s="5">
-        <v>69.40000000000001</v>
+        <v>69.7</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>84.5</v>
+        <v>90.5</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>225000</v>
+        <v>127000</v>
       </c>
       <c r="G46" s="7">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H46" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I46" s="7">
-        <v>11222</v>
+        <v>7600</v>
       </c>
       <c r="J46" s="5">
-        <v>69.3</v>
+        <v>69.7</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>84.8</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>222000</v>
+        <v>225000</v>
       </c>
       <c r="G47" s="7">
         <v>3000</v>
       </c>
       <c r="H47" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I47" s="7">
-        <v>10571</v>
+        <v>9625</v>
       </c>
       <c r="J47" s="5">
-        <v>69.3</v>
+        <v>69.5</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>83.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>263000</v>
+        <v>2674000</v>
       </c>
       <c r="G48" s="7">
-        <v>-5000</v>
+        <v>15000</v>
       </c>
       <c r="H48" s="7">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="I48" s="7">
-        <v>12200</v>
+        <v>15683</v>
       </c>
       <c r="J48" s="5">
-        <v>69</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>82.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>270000</v>
+        <v>1037000</v>
       </c>
       <c r="G49" s="7">
-        <v>19000</v>
+        <v>-54000</v>
       </c>
       <c r="H49" s="7">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="I49" s="7">
-        <v>14900</v>
+        <v>32095</v>
       </c>
       <c r="J49" s="5">
-        <v>68.90000000000001</v>
+        <v>69.3</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>90.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>208000</v>
+        <v>458000</v>
       </c>
       <c r="G50" s="7">
-        <v>19000</v>
+        <v>7000</v>
       </c>
       <c r="H50" s="7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="I50" s="7">
-        <v>15750</v>
+        <v>21053</v>
       </c>
       <c r="J50" s="5">
-        <v>68.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.5</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>126000</v>
+        <v>114000</v>
       </c>
       <c r="G51" s="7">
-        <v>1000</v>
+        <v>14000</v>
       </c>
       <c r="H51" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I51" s="7">
-        <v>7667</v>
+        <v>14000</v>
       </c>
       <c r="J51" s="5">
-        <v>68.90000000000001</v>
+        <v>69.2</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84.2</v>
+        <v>77.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>147000</v>
+        <v>349000</v>
       </c>
       <c r="G52" s="7">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="H52" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I52" s="7">
-        <v>10111</v>
+        <v>34000</v>
       </c>
       <c r="J52" s="5">
-        <v>68.8</v>
+        <v>69</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>87.2</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>124000</v>
+        <v>148000</v>
       </c>
       <c r="G53" s="7">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="H53" s="7">
         <v>11</v>
       </c>
       <c r="I53" s="7">
-        <v>3500</v>
+        <v>9200</v>
       </c>
       <c r="J53" s="5">
-        <v>68.8</v>
+        <v>69</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>84.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>200000</v>
+        <v>205000</v>
       </c>
       <c r="G54" s="7">
-        <v>9000</v>
+        <v>25000</v>
       </c>
       <c r="H54" s="7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I54" s="7">
-        <v>8400</v>
+        <v>24667</v>
       </c>
       <c r="J54" s="5">
-        <v>68.59999999999999</v>
+        <v>68.8</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-25T04:20:30+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-26T04:24:14+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -70,157 +70,157 @@
     <t>达标日期列表</t>
   </si>
   <si>
+    <t>持械入宋</t>
+  </si>
+  <si>
+    <t>打开作品</t>
+  </si>
+  <si>
+    <t>四合院：1948年开局暴富躺平</t>
+  </si>
+  <si>
+    <t>我都化龙了，你说功法是假的？</t>
+  </si>
+  <si>
     <t>神雕杨过：我以九阴九阳压天下！</t>
   </si>
   <si>
-    <t>打开作品</t>
-  </si>
-  <si>
-    <t>四合院：1948年开局暴富躺平</t>
-  </si>
-  <si>
-    <t>持械入宋</t>
-  </si>
-  <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
+    <t>努力就变强的我，被重生者曝光了</t>
+  </si>
+  <si>
+    <t>圣骑士是混子？我反手秒杀魔神！</t>
+  </si>
+  <si>
+    <t>我叫九江，李景隆那个九江！</t>
+  </si>
+  <si>
     <t>饰演封于修，女友神仙姐姐</t>
   </si>
   <si>
+    <t>穿成警察，满城霸总排队来送业绩</t>
+  </si>
+  <si>
+    <t>龙族：我的强化每月刷新</t>
+  </si>
+  <si>
+    <t>开局狱主，烧香召唤无敌仙帝</t>
+  </si>
+  <si>
+    <t>高冷？外冷内齁！你们请攻略我吧</t>
+  </si>
+  <si>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
     <t>火影：九尾之夜，雷光万劫</t>
   </si>
   <si>
-    <t>开局狱主，烧香召唤无敌仙帝</t>
-  </si>
-  <si>
-    <t>我叫九江，李景隆那个九江！</t>
+    <t>霍格沃茨：马尔福竟是傲娇千金？</t>
   </si>
   <si>
     <t>武道通神：我的增益永久生效</t>
   </si>
   <si>
+    <t>全民领主：抽到人族，但来自战锤</t>
+  </si>
+  <si>
+    <t>红色人生模拟，我怎么成老干部了</t>
+  </si>
+  <si>
+    <t>天幕：千古第一才女的现代生活</t>
+  </si>
+  <si>
+    <t>天渊镇守百万载，你要挖我族人骨</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离还在藏</t>
+  </si>
+  <si>
+    <t>洪荒：开局带着白莲绿茶拜师三清</t>
+  </si>
+  <si>
+    <t>美漫，从黑暗奇异博士开始</t>
+  </si>
+  <si>
+    <t>我伪装成人类文明，拯救诸天万界</t>
+  </si>
+  <si>
+    <t>型月：未婚妻露维亚，抽爆FGO</t>
+  </si>
+  <si>
+    <t>四合院：大军进城，我系统吓跑了</t>
+  </si>
+  <si>
+    <t>海洋求生？可我是人鱼公主！</t>
+  </si>
+  <si>
+    <t>暴君：从一空输开始，登顶南韩</t>
+  </si>
+  <si>
+    <t>全班同学穿越，我开局拜菩提祖师</t>
+  </si>
+  <si>
+    <t>见鬼！求生系统把我投放到80年</t>
+  </si>
+  <si>
     <t>末世轮盘：开局指定抽取序列魔药</t>
   </si>
   <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>高冷？外冷内齁！你们请攻略我吧</t>
-  </si>
-  <si>
-    <t>圣骑士是混子？我反手秒杀魔神！</t>
-  </si>
-  <si>
-    <t>见鬼！求生系统把我投放到80年</t>
-  </si>
-  <si>
-    <t>龙族：我的强化每月刷新</t>
-  </si>
-  <si>
-    <t>型月：未婚妻露维亚，抽爆FGO</t>
-  </si>
-  <si>
-    <t>穿成警察，满城霸总排队来送业绩</t>
+    <t>情迷沪上贵妇</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>明明想单推，结果被病娇包围</t>
+  </si>
+  <si>
+    <t>从二战老兵开始当调查员</t>
+  </si>
+  <si>
+    <t>四合院：从红二十五开始进步</t>
+  </si>
+  <si>
+    <t>穿到六零，吃瓜看戏</t>
+  </si>
+  <si>
+    <t>西游：开局找黄狮精买功法</t>
+  </si>
+  <si>
+    <t>重生年代：我怎么多了三个前妻</t>
+  </si>
+  <si>
+    <t>拒白月光不做冤大头七零留城享福</t>
+  </si>
+  <si>
+    <t>正光加代那些事</t>
+  </si>
+  <si>
+    <t>高武：我以子嗣模拟证武道巅峰</t>
+  </si>
+  <si>
+    <t>我，夜神月不是神，但富江是真鬼</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>大明：开局救了朱元璋全家</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
   </si>
   <si>
     <t>亮剑：我和李云龙一起当警卫</t>
   </si>
   <si>
-    <t>红色人生模拟，我怎么成老干部了</t>
-  </si>
-  <si>
-    <t>边军悍卒，绝色罪女天天求暖床</t>
-  </si>
-  <si>
-    <t>我伪装成人类文明，拯救诸天万界</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>穿到六零，吃瓜看戏</t>
-  </si>
-  <si>
-    <t>儒道剑仙，苟在镇北王府当赘婿</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离还在藏</t>
-  </si>
-  <si>
-    <t>洪荒：开局带着白莲绿茶拜师三清</t>
-  </si>
-  <si>
-    <t>西游：开局找黄狮精买功法</t>
-  </si>
-  <si>
-    <t>天渊镇守百万载，你要挖我族人骨</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>自定义术式的我去咒回找乐子了</t>
-  </si>
-  <si>
-    <t>大明：开局救了朱元璋全家</t>
-  </si>
-  <si>
-    <t>四合院：从红二十五开始进步</t>
-  </si>
-  <si>
-    <t>我都成旧日了，诡秘才入侵现实？</t>
-  </si>
-  <si>
-    <t>重生年代：我怎么多了三个前妻</t>
-  </si>
-  <si>
-    <t>崩铁：杰顿幼崽，但被卡妈捡到</t>
-  </si>
-  <si>
-    <t>全民领主：抽到人族，但来自战锤</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>暴君：从一空输开始，登顶南韩</t>
+    <t>随机遗产，开局继承三百年功力</t>
   </si>
   <si>
     <t>鬼谷下山：九封婚书闯都市</t>
-  </si>
-  <si>
-    <t>全民：曝光最强修士！大秦什么鬼</t>
-  </si>
-  <si>
-    <t>四合院：大军进城，我系统吓跑了</t>
-  </si>
-  <si>
-    <t>明明想单推，结果被病娇包围</t>
-  </si>
-  <si>
-    <t>咸鱼系统：前妻妹妹总拉我钓鱼</t>
-  </si>
-  <si>
-    <t>神通者</t>
-  </si>
-  <si>
-    <t>都重生了，谁还装富二代啊</t>
-  </si>
-  <si>
-    <t>入狱五年，归来仍是大佬</t>
-  </si>
-  <si>
-    <t>海洋求生？可我是人鱼公主！</t>
-  </si>
-  <si>
-    <t>拒白月光不做冤大头七零留城享福</t>
-  </si>
-  <si>
-    <t>觉醒死亡笔记，开局写下邪神名字</t>
-  </si>
-  <si>
-    <t>霍格沃茨：马尔福竟是傲娇千金？</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>90.2</v>
+        <v>91.7</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>967000</v>
+        <v>477000</v>
       </c>
       <c r="G5" s="7">
         <v>90000</v>
       </c>
       <c r="H5" s="7">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I5" s="7">
-        <v>57727</v>
+        <v>97000</v>
       </c>
       <c r="J5" s="5">
-        <v>84</v>
+        <v>86.7</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>98.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>433000</v>
+        <v>472000</v>
       </c>
       <c r="G6" s="7">
-        <v>40000</v>
+        <v>39000</v>
       </c>
       <c r="H6" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="7">
-        <v>35111</v>
+        <v>35500</v>
       </c>
       <c r="J6" s="5">
-        <v>82.90000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>87.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>387000</v>
+        <v>157000</v>
       </c>
       <c r="G7" s="7">
-        <v>93000</v>
+        <v>69000</v>
       </c>
       <c r="H7" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>100500</v>
+        <v>23833</v>
       </c>
       <c r="J7" s="5">
-        <v>82.3</v>
+        <v>81</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>83.59999999999999</v>
+        <v>82.8</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>2300000</v>
+        <v>994000</v>
       </c>
       <c r="G8" s="7">
-        <v>41000</v>
+        <v>27000</v>
       </c>
       <c r="H8" s="7">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="I8" s="7">
-        <v>47585</v>
+        <v>55167</v>
       </c>
       <c r="J8" s="5">
-        <v>77.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>79</v>
+        <v>84.7</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>666000</v>
+        <v>2364000</v>
       </c>
       <c r="G9" s="7">
-        <v>21000</v>
+        <v>64000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="I9" s="7">
-        <v>62400</v>
+        <v>47976</v>
       </c>
       <c r="J9" s="5">
-        <v>77</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>86.09999999999999</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>420000</v>
+        <v>529000</v>
       </c>
       <c r="G10" s="7">
-        <v>31000</v>
+        <v>85000</v>
       </c>
       <c r="H10" s="7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I10" s="7">
-        <v>36750</v>
+        <v>93500</v>
       </c>
       <c r="J10" s="5">
-        <v>76.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>98.40000000000001</v>
+        <v>99.5</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>103000</v>
+        <v>169000</v>
       </c>
       <c r="G11" s="7">
-        <v>16000</v>
+        <v>49000</v>
       </c>
       <c r="H11" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I11" s="7">
-        <v>7700</v>
+        <v>13000</v>
       </c>
       <c r="J11" s="5">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>81.09999999999999</v>
+        <v>84.3</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>309000</v>
+        <v>350000</v>
       </c>
       <c r="G12" s="7">
-        <v>33000</v>
+        <v>41000</v>
       </c>
       <c r="H12" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I12" s="7">
-        <v>45000</v>
+        <v>44429</v>
       </c>
       <c r="J12" s="5">
-        <v>75.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>91.90000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>411000</v>
+        <v>680000</v>
       </c>
       <c r="G13" s="7">
-        <v>15000</v>
+        <v>14000</v>
       </c>
       <c r="H13" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>20455</v>
+        <v>54333</v>
       </c>
       <c r="J13" s="5">
-        <v>75.7</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>96</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>140000</v>
+        <v>319000</v>
       </c>
       <c r="G14" s="7">
-        <v>14000</v>
+        <v>27000</v>
       </c>
       <c r="H14" s="7">
         <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>17800</v>
+        <v>25400</v>
       </c>
       <c r="J14" s="5">
-        <v>75.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>92.5</v>
+        <v>100</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>352000</v>
+        <v>327000</v>
       </c>
       <c r="G15" s="7">
-        <v>16000</v>
+        <v>67000</v>
       </c>
       <c r="H15" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I15" s="7">
-        <v>17273</v>
+        <v>6667</v>
       </c>
       <c r="J15" s="5">
-        <v>75.2</v>
+        <v>76.7</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>92.09999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>184000</v>
+        <v>120000</v>
       </c>
       <c r="G16" s="7">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="H16" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I16" s="7">
-        <v>17000</v>
+        <v>8545</v>
       </c>
       <c r="J16" s="5">
-        <v>74.90000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>94.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>120000</v>
+        <v>200000</v>
       </c>
       <c r="G17" s="7">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="H17" s="7">
         <v>8</v>
       </c>
       <c r="I17" s="7">
-        <v>7857</v>
+        <v>16857</v>
       </c>
       <c r="J17" s="5">
-        <v>74</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>89.5</v>
+        <v>93.2</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>375000</v>
+        <v>371000</v>
       </c>
       <c r="G18" s="7">
-        <v>6000</v>
+        <v>19000</v>
       </c>
       <c r="H18" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I18" s="7">
-        <v>18727</v>
+        <v>17417</v>
       </c>
       <c r="J18" s="5">
-        <v>73.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>97.3</v>
+        <v>84</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>260000</v>
+        <v>444000</v>
       </c>
       <c r="G19" s="7">
-        <v>31000</v>
+        <v>24000</v>
       </c>
       <c r="H19" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I19" s="7">
-        <v>1182</v>
+        <v>35333</v>
       </c>
       <c r="J19" s="5">
-        <v>73.8</v>
+        <v>75</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>89.2</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>297000</v>
+        <v>239000</v>
       </c>
       <c r="G20" s="7">
-        <v>10000</v>
+        <v>34000</v>
       </c>
       <c r="H20" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I20" s="7">
-        <v>18000</v>
+        <v>27000</v>
       </c>
       <c r="J20" s="5">
-        <v>73.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>95</v>
+        <v>90.8</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>292000</v>
+        <v>422000</v>
       </c>
       <c r="G21" s="7">
-        <v>23000</v>
+        <v>11000</v>
       </c>
       <c r="H21" s="7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I21" s="7">
-        <v>25000</v>
+        <v>19667</v>
       </c>
       <c r="J21" s="5">
-        <v>73.5</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>91.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>145000</v>
+        <v>158000</v>
       </c>
       <c r="G22" s="7">
-        <v>8000</v>
+        <v>34000</v>
       </c>
       <c r="H22" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I22" s="7">
-        <v>11700</v>
+        <v>23000</v>
       </c>
       <c r="J22" s="5">
-        <v>73.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>94.09999999999999</v>
+        <v>96</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>157000</v>
+        <v>175000</v>
       </c>
       <c r="G23" s="7">
-        <v>14000</v>
+        <v>18000</v>
       </c>
       <c r="H23" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I23" s="7">
-        <v>5545</v>
+        <v>6583</v>
       </c>
       <c r="J23" s="5">
-        <v>73.09999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.90000000000001</v>
+        <v>96.7</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>138000</v>
+        <v>101000</v>
       </c>
       <c r="G24" s="7">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="H24" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I24" s="7">
-        <v>7800</v>
+        <v>11400</v>
       </c>
       <c r="J24" s="5">
-        <v>72.5</v>
+        <v>74</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1417,28 +1417,30 @@
       <c r="A25" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5"/>
+      <c r="B25" s="5">
+        <v>9.9</v>
+      </c>
       <c r="C25" s="5">
-        <v>91.09999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>224000</v>
+        <v>192000</v>
       </c>
       <c r="G25" s="7">
-        <v>16000</v>
+        <v>14000</v>
       </c>
       <c r="H25" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I25" s="7">
-        <v>15800</v>
+        <v>11111</v>
       </c>
       <c r="J25" s="5">
-        <v>72.09999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1454,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>87.7</v>
+        <v>90.5</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>532000</v>
+        <v>218000</v>
       </c>
       <c r="G26" s="7">
-        <v>-5000</v>
+        <v>13000</v>
       </c>
       <c r="H26" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I26" s="7">
-        <v>15091</v>
+        <v>15125</v>
       </c>
       <c r="J26" s="5">
-        <v>72</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1487,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>86.8</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>224000</v>
+        <v>140000</v>
       </c>
       <c r="G27" s="7">
-        <v>2000</v>
+        <v>8000</v>
       </c>
       <c r="H27" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I27" s="7">
-        <v>16273</v>
+        <v>16000</v>
       </c>
       <c r="J27" s="5">
-        <v>71.8</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1520,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>90.7</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>260000</v>
+        <v>236000</v>
       </c>
       <c r="G28" s="7">
-        <v>9000</v>
+        <v>25000</v>
       </c>
       <c r="H28" s="7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I28" s="7">
-        <v>6818</v>
+        <v>17800</v>
       </c>
       <c r="J28" s="5">
-        <v>71.59999999999999</v>
+        <v>73.5</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1553,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>86.8</v>
+        <v>90.2</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>205000</v>
+        <v>237000</v>
       </c>
       <c r="G29" s="7">
-        <v>7000</v>
+        <v>13000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>15429</v>
+        <v>15333</v>
       </c>
       <c r="J29" s="5">
-        <v>71.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1586,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>89.5</v>
+        <v>88.8</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>132000</v>
+        <v>306000</v>
       </c>
       <c r="G30" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H30" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I30" s="7">
-        <v>17600</v>
+        <v>17250</v>
       </c>
       <c r="J30" s="5">
-        <v>71.59999999999999</v>
+        <v>73.2</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1619,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>87.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>246000</v>
+        <v>259000</v>
       </c>
       <c r="G31" s="7">
-        <v>1000</v>
+        <v>18000</v>
       </c>
       <c r="H31" s="7">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I31" s="7">
-        <v>13909</v>
+        <v>19800</v>
       </c>
       <c r="J31" s="5">
-        <v>71.5</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1648,30 +1650,28 @@
       <c r="A32" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B32" s="5">
-        <v>9.9</v>
-      </c>
+      <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>88.5</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>178000</v>
+        <v>132000</v>
       </c>
       <c r="G32" s="7">
-        <v>8000</v>
+        <v>18000</v>
       </c>
       <c r="H32" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I32" s="7">
-        <v>10750</v>
+        <v>15000</v>
       </c>
       <c r="J32" s="5">
-        <v>71.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1685,26 +1685,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>87.09999999999999</v>
+        <v>88.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>342000</v>
+        <v>214000</v>
       </c>
       <c r="G33" s="7">
-        <v>-2000</v>
+        <v>26000</v>
       </c>
       <c r="H33" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I33" s="7">
-        <v>13727</v>
+        <v>16167</v>
       </c>
       <c r="J33" s="5">
-        <v>71.3</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>87.59999999999999</v>
+        <v>98.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>202000</v>
+        <v>185000</v>
       </c>
       <c r="G34" s="7">
-        <v>10000</v>
+        <v>39000</v>
       </c>
       <c r="H34" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I34" s="7">
-        <v>12111</v>
+        <v>26333</v>
       </c>
       <c r="J34" s="5">
-        <v>71.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>90.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>112000</v>
+        <v>376000</v>
       </c>
       <c r="G35" s="7">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="H35" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I35" s="7">
-        <v>13400</v>
+        <v>17250</v>
       </c>
       <c r="J35" s="5">
-        <v>70.90000000000001</v>
+        <v>72.8</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>89.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>318000</v>
+        <v>145000</v>
       </c>
       <c r="G36" s="7">
-        <v>40000</v>
+        <v>5000</v>
       </c>
       <c r="H36" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I36" s="7">
-        <v>37667</v>
+        <v>15667</v>
       </c>
       <c r="J36" s="5">
-        <v>70.59999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>86.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>253000</v>
+        <v>119000</v>
       </c>
       <c r="G37" s="7">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="H37" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I37" s="7">
-        <v>12273</v>
+        <v>10333</v>
       </c>
       <c r="J37" s="5">
-        <v>70.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>74.5</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>777000</v>
+        <v>731000</v>
       </c>
       <c r="G38" s="7">
-        <v>-53000</v>
+        <v>42000</v>
       </c>
       <c r="H38" s="7">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I38" s="7">
-        <v>37250</v>
+        <v>20636</v>
       </c>
       <c r="J38" s="5">
-        <v>70.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>85.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>414000</v>
+        <v>135000</v>
       </c>
       <c r="G39" s="7">
-        <v>-6000</v>
+        <v>8000</v>
       </c>
       <c r="H39" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>12455</v>
+        <v>7667</v>
       </c>
       <c r="J39" s="5">
-        <v>70.3</v>
+        <v>72</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>97.09999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>124000</v>
+        <v>105000</v>
       </c>
       <c r="G40" s="7">
-        <v>18000</v>
+        <v>8000</v>
       </c>
       <c r="H40" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I40" s="7">
-        <v>19333</v>
+        <v>6250</v>
       </c>
       <c r="J40" s="5">
-        <v>70.2</v>
+        <v>72</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>82.59999999999999</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>689000</v>
+        <v>349000</v>
       </c>
       <c r="G41" s="7">
-        <v>23000</v>
+        <v>31000</v>
       </c>
       <c r="H41" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I41" s="7">
-        <v>18500</v>
+        <v>36000</v>
       </c>
       <c r="J41" s="5">
-        <v>70.09999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>84</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>188000</v>
+        <v>225000</v>
       </c>
       <c r="G42" s="7">
-        <v>16000</v>
+        <v>1000</v>
       </c>
       <c r="H42" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I42" s="7">
-        <v>15273</v>
+        <v>15000</v>
       </c>
       <c r="J42" s="5">
-        <v>70</v>
+        <v>71.3</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>87.5</v>
+        <v>87</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>101000</v>
+        <v>246000</v>
       </c>
       <c r="G43" s="7">
-        <v>4000</v>
+        <v>0</v>
       </c>
       <c r="H43" s="7">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I43" s="7">
-        <v>7700</v>
+        <v>12750</v>
       </c>
       <c r="J43" s="5">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>85.2</v>
+        <v>77</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>101000</v>
+        <v>758000</v>
       </c>
       <c r="G44" s="7">
-        <v>1000</v>
+        <v>-19000</v>
       </c>
       <c r="H44" s="7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I44" s="7">
-        <v>12333</v>
+        <v>33941</v>
       </c>
       <c r="J44" s="5">
-        <v>69.90000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>90.3</v>
+        <v>78.2</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>241000</v>
+        <v>365000</v>
       </c>
       <c r="G45" s="7">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="H45" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I45" s="7">
-        <v>20250</v>
+        <v>31000</v>
       </c>
       <c r="J45" s="5">
-        <v>69.7</v>
+        <v>70.8</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>90.5</v>
+        <v>90.2</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>127000</v>
+        <v>119000</v>
       </c>
       <c r="G46" s="7">
-        <v>7000</v>
+        <v>9000</v>
       </c>
       <c r="H46" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I46" s="7">
-        <v>7600</v>
+        <v>4333</v>
       </c>
       <c r="J46" s="5">
-        <v>69.7</v>
+        <v>70.7</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>85.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>225000</v>
+        <v>110000</v>
       </c>
       <c r="G47" s="7">
-        <v>3000</v>
+        <v>12000</v>
       </c>
       <c r="H47" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I47" s="7">
-        <v>9625</v>
+        <v>9200</v>
       </c>
       <c r="J47" s="5">
-        <v>69.5</v>
+        <v>70.7</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>82.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>2674000</v>
+        <v>126000</v>
       </c>
       <c r="G48" s="7">
-        <v>15000</v>
+        <v>7000</v>
       </c>
       <c r="H48" s="7">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="I48" s="7">
-        <v>15683</v>
+        <v>7000</v>
       </c>
       <c r="J48" s="5">
-        <v>69.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>75.09999999999999</v>
+        <v>86.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>1037000</v>
+        <v>337000</v>
       </c>
       <c r="G49" s="7">
-        <v>-54000</v>
+        <v>-5000</v>
       </c>
       <c r="H49" s="7">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="I49" s="7">
-        <v>32095</v>
+        <v>12167</v>
       </c>
       <c r="J49" s="5">
-        <v>69.3</v>
+        <v>70.5</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>79.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>458000</v>
+        <v>116000</v>
       </c>
       <c r="G50" s="7">
-        <v>7000</v>
+        <v>4000</v>
       </c>
       <c r="H50" s="7">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="I50" s="7">
-        <v>21053</v>
+        <v>11833</v>
       </c>
       <c r="J50" s="5">
-        <v>69.2</v>
+        <v>70.5</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>97.59999999999999</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>114000</v>
+        <v>518000</v>
       </c>
       <c r="G51" s="7">
-        <v>14000</v>
+        <v>-14000</v>
       </c>
       <c r="H51" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I51" s="7">
-        <v>14000</v>
+        <v>12667</v>
       </c>
       <c r="J51" s="5">
-        <v>69.2</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>77.2</v>
+        <v>86.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>349000</v>
+        <v>146000</v>
       </c>
       <c r="G52" s="7">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="H52" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I52" s="7">
-        <v>34000</v>
+        <v>10727</v>
       </c>
       <c r="J52" s="5">
-        <v>69</v>
+        <v>70.3</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>84.90000000000001</v>
+        <v>94.7</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>148000</v>
+        <v>128000</v>
       </c>
       <c r="G53" s="7">
-        <v>1000</v>
+        <v>20000</v>
       </c>
       <c r="H53" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I53" s="7">
-        <v>9200</v>
+        <v>11000</v>
       </c>
       <c r="J53" s="5">
-        <v>69</v>
+        <v>69.8</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>92.09999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>205000</v>
+        <v>104000</v>
       </c>
       <c r="G54" s="7">
-        <v>25000</v>
+        <v>3000</v>
       </c>
       <c r="H54" s="7">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="I54" s="7">
-        <v>24667</v>
+        <v>7273</v>
       </c>
       <c r="J54" s="5">
-        <v>68.8</v>
+        <v>69.8</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-26T04:24:14+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-27T04:48:34+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
-    <t>四合院：1948年开局暴富躺平</t>
-  </si>
-  <si>
     <t>我都化龙了，你说功法是假的？</t>
   </si>
   <si>
     <t>神雕杨过：我以九阴九阳压天下！</t>
   </si>
   <si>
+    <t>全民领主：抽到人族，但来自战锤</t>
+  </si>
+  <si>
+    <t>霍格沃茨：马尔福竟是傲娇千金？</t>
+  </si>
+  <si>
+    <t>穿成警察，满城霸总排队来送业绩</t>
+  </si>
+  <si>
+    <t>全班同学穿越，我开局拜菩提祖师</t>
+  </si>
+  <si>
     <t>骇夜：我在恐怖游戏里暴富</t>
   </si>
   <si>
+    <t>天幕：千古第一才女的现代生活</t>
+  </si>
+  <si>
+    <t>海洋求生？可我是人鱼公主！</t>
+  </si>
+  <si>
     <t>努力就变强的我，被重生者曝光了</t>
   </si>
   <si>
-    <t>圣骑士是混子？我反手秒杀魔神！</t>
+    <t>饰演封于修，女友神仙姐姐</t>
   </si>
   <si>
     <t>我叫九江，李景隆那个九江！</t>
   </si>
   <si>
-    <t>饰演封于修，女友神仙姐姐</t>
-  </si>
-  <si>
-    <t>穿成警察，满城霸总排队来送业绩</t>
-  </si>
-  <si>
     <t>龙族：我的强化每月刷新</t>
   </si>
   <si>
-    <t>开局狱主，烧香召唤无敌仙帝</t>
+    <t>海吞天</t>
+  </si>
+  <si>
+    <t>红色人生模拟，我怎么成老干部了</t>
+  </si>
+  <si>
+    <t>穿书女频，被病娇姐妹缠上了</t>
+  </si>
+  <si>
+    <t>破案：我能闻到凶手的味道</t>
+  </si>
+  <si>
+    <t>美漫，从黑暗奇异博士开始</t>
+  </si>
+  <si>
+    <t>海贼：门门果实？可曾听闻次元斩</t>
+  </si>
+  <si>
+    <t>四合院：大军进城，我系统吓跑了</t>
+  </si>
+  <si>
+    <t>我在美国当上帝</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离还在藏</t>
+  </si>
+  <si>
+    <t>我伪装成人类文明，拯救诸天万界</t>
+  </si>
+  <si>
+    <t>天渊镇守百万载，你要挖我族人骨</t>
+  </si>
+  <si>
+    <t>恐怖游戏：开局皮嫁骨吓哭全球！</t>
   </si>
   <si>
     <t>高冷？外冷内齁！你们请攻略我吧</t>
   </si>
   <si>
-    <t>我在美国当上帝</t>
+    <t>崩铁：迫害完她们后，我有点死了</t>
   </si>
   <si>
     <t>火影：九尾之夜，雷光万劫</t>
   </si>
   <si>
-    <t>霍格沃茨：马尔福竟是傲娇千金？</t>
-  </si>
-  <si>
-    <t>武道通神：我的增益永久生效</t>
-  </si>
-  <si>
-    <t>全民领主：抽到人族，但来自战锤</t>
-  </si>
-  <si>
-    <t>红色人生模拟，我怎么成老干部了</t>
-  </si>
-  <si>
-    <t>天幕：千古第一才女的现代生活</t>
-  </si>
-  <si>
-    <t>天渊镇守百万载，你要挖我族人骨</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离还在藏</t>
+    <t>四合院：从红二十五开始进步</t>
+  </si>
+  <si>
+    <t>cos服租赁，开局拿捏漫展女神</t>
+  </si>
+  <si>
+    <t>拒白月光不做冤大头七零留城享福</t>
   </si>
   <si>
     <t>洪荒：开局带着白莲绿茶拜师三清</t>
   </si>
   <si>
-    <t>美漫，从黑暗奇异博士开始</t>
-  </si>
-  <si>
-    <t>我伪装成人类文明，拯救诸天万界</t>
-  </si>
-  <si>
-    <t>型月：未婚妻露维亚，抽爆FGO</t>
-  </si>
-  <si>
-    <t>四合院：大军进城，我系统吓跑了</t>
-  </si>
-  <si>
-    <t>海洋求生？可我是人鱼公主！</t>
-  </si>
-  <si>
-    <t>暴君：从一空输开始，登顶南韩</t>
-  </si>
-  <si>
-    <t>全班同学穿越，我开局拜菩提祖师</t>
-  </si>
-  <si>
-    <t>见鬼！求生系统把我投放到80年</t>
+    <t>入学第一天：我娶了丰腴美人教授</t>
+  </si>
+  <si>
+    <t>穿到六零，吃瓜看戏</t>
+  </si>
+  <si>
+    <t>高武：我以子嗣模拟证武道巅峰</t>
+  </si>
+  <si>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>抗战：天道酬勤，从士兵开始崛起</t>
   </si>
   <si>
     <t>末世轮盘：开局指定抽取序列魔药</t>
   </si>
   <si>
-    <t>情迷沪上贵妇</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>明明想单推，结果被病娇包围</t>
+    <t>末日觉醒，每天一次超级四选一</t>
+  </si>
+  <si>
+    <t>九霄通天塔</t>
+  </si>
+  <si>
+    <t>我都觉醒神明序列了系统才来？</t>
+  </si>
+  <si>
+    <t>鬼谷下山：九封婚书闯都市</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>觉醒死亡笔记，开局写下邪神名字</t>
+  </si>
+  <si>
+    <t>我真没想振兴大唐</t>
+  </si>
+  <si>
+    <t>亮剑：我和李云龙一起当警卫</t>
+  </si>
+  <si>
+    <t>重生年代：我怎么多了三个前妻</t>
+  </si>
+  <si>
+    <t>随机遗产，开局继承三百年功力</t>
   </si>
   <si>
     <t>从二战老兵开始当调查员</t>
-  </si>
-  <si>
-    <t>四合院：从红二十五开始进步</t>
-  </si>
-  <si>
-    <t>穿到六零，吃瓜看戏</t>
-  </si>
-  <si>
-    <t>西游：开局找黄狮精买功法</t>
-  </si>
-  <si>
-    <t>重生年代：我怎么多了三个前妻</t>
-  </si>
-  <si>
-    <t>拒白月光不做冤大头七零留城享福</t>
-  </si>
-  <si>
-    <t>正光加代那些事</t>
-  </si>
-  <si>
-    <t>高武：我以子嗣模拟证武道巅峰</t>
-  </si>
-  <si>
-    <t>我，夜神月不是神，但富江是真鬼</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>大明：开局救了朱元璋全家</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>亮剑：我和李云龙一起当警卫</t>
-  </si>
-  <si>
-    <t>随机遗产，开局继承三百年功力</t>
-  </si>
-  <si>
-    <t>鬼谷下山：九封婚书闯都市</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>91.7</v>
+        <v>92.5</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>477000</v>
+        <v>547000</v>
       </c>
       <c r="G5" s="7">
-        <v>90000</v>
+        <v>70000</v>
       </c>
       <c r="H5" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I5" s="7">
-        <v>97000</v>
+        <v>90250</v>
       </c>
       <c r="J5" s="5">
-        <v>86.7</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>97.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>472000</v>
+        <v>218000</v>
       </c>
       <c r="G6" s="7">
-        <v>39000</v>
+        <v>61000</v>
       </c>
       <c r="H6" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I6" s="7">
-        <v>35500</v>
+        <v>29143</v>
       </c>
       <c r="J6" s="5">
-        <v>82.40000000000001</v>
+        <v>82.3</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>100</v>
+        <v>84.2</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>157000</v>
+        <v>1035000</v>
       </c>
       <c r="G7" s="7">
-        <v>69000</v>
+        <v>41000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I7" s="7">
-        <v>23833</v>
+        <v>54077</v>
       </c>
       <c r="J7" s="5">
-        <v>81</v>
+        <v>79.8</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>82.8</v>
+        <v>99.8</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>994000</v>
+        <v>198000</v>
       </c>
       <c r="G8" s="7">
-        <v>27000</v>
+        <v>40000</v>
       </c>
       <c r="H8" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I8" s="7">
-        <v>55167</v>
+        <v>26400</v>
       </c>
       <c r="J8" s="5">
-        <v>79.3</v>
+        <v>79.5</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>84.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>2364000</v>
+        <v>272000</v>
       </c>
       <c r="G9" s="7">
-        <v>64000</v>
+        <v>33000</v>
       </c>
       <c r="H9" s="7">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>47976</v>
+        <v>28200</v>
       </c>
       <c r="J9" s="5">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>83.59999999999999</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>529000</v>
+        <v>343000</v>
       </c>
       <c r="G10" s="7">
-        <v>85000</v>
+        <v>24000</v>
       </c>
       <c r="H10" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I10" s="7">
-        <v>93500</v>
+        <v>25167</v>
       </c>
       <c r="J10" s="5">
-        <v>78.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>99.5</v>
+        <v>100</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>169000</v>
+        <v>231000</v>
       </c>
       <c r="G11" s="7">
-        <v>49000</v>
+        <v>46000</v>
       </c>
       <c r="H11" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I11" s="7">
-        <v>13000</v>
+        <v>31250</v>
       </c>
       <c r="J11" s="5">
-        <v>78</v>
+        <v>77.8</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,23 +990,23 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>84.3</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>350000</v>
+        <v>2389000</v>
       </c>
       <c r="G12" s="7">
-        <v>41000</v>
+        <v>25000</v>
       </c>
       <c r="H12" s="7">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="I12" s="7">
-        <v>44429</v>
+        <v>47442</v>
       </c>
       <c r="J12" s="5">
         <v>77.5</v>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>79.59999999999999</v>
+        <v>98.5</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>680000</v>
+        <v>116000</v>
       </c>
       <c r="G13" s="7">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="H13" s="7">
         <v>7</v>
       </c>
       <c r="I13" s="7">
-        <v>54333</v>
+        <v>12000</v>
       </c>
       <c r="J13" s="5">
-        <v>77.40000000000001</v>
+        <v>77.2</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,23 +1056,23 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>95.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>319000</v>
+        <v>154000</v>
       </c>
       <c r="G14" s="7">
-        <v>27000</v>
+        <v>22000</v>
       </c>
       <c r="H14" s="7">
         <v>6</v>
       </c>
       <c r="I14" s="7">
-        <v>25400</v>
+        <v>16400</v>
       </c>
       <c r="J14" s="5">
         <v>77.09999999999999</v>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>100</v>
+        <v>81.3</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>327000</v>
+        <v>586000</v>
       </c>
       <c r="G15" s="7">
-        <v>67000</v>
+        <v>57000</v>
       </c>
       <c r="H15" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I15" s="7">
-        <v>6667</v>
+        <v>81333</v>
       </c>
       <c r="J15" s="5">
-        <v>76.7</v>
+        <v>77</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>98.7</v>
+        <v>80.7</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>120000</v>
+        <v>701000</v>
       </c>
       <c r="G16" s="7">
-        <v>17000</v>
+        <v>21000</v>
       </c>
       <c r="H16" s="7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I16" s="7">
-        <v>8545</v>
+        <v>49571</v>
       </c>
       <c r="J16" s="5">
-        <v>76.40000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>94.40000000000001</v>
+        <v>82.90000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>200000</v>
+        <v>385000</v>
       </c>
       <c r="G17" s="7">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="H17" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I17" s="7">
-        <v>16857</v>
+        <v>43250</v>
       </c>
       <c r="J17" s="5">
-        <v>76.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>93.2</v>
+        <v>97.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>371000</v>
+        <v>362000</v>
       </c>
       <c r="G18" s="7">
-        <v>19000</v>
+        <v>35000</v>
       </c>
       <c r="H18" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I18" s="7">
-        <v>17417</v>
+        <v>8846</v>
       </c>
       <c r="J18" s="5">
-        <v>75.59999999999999</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>84</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>444000</v>
+        <v>131000</v>
       </c>
       <c r="G19" s="7">
-        <v>24000</v>
+        <v>53000</v>
       </c>
       <c r="H19" s="7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I19" s="7">
-        <v>35333</v>
+        <v>3692</v>
       </c>
       <c r="J19" s="5">
-        <v>75</v>
+        <v>75.3</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>96.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>239000</v>
+        <v>196000</v>
       </c>
       <c r="G20" s="7">
-        <v>34000</v>
+        <v>21000</v>
       </c>
       <c r="H20" s="7">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I20" s="7">
-        <v>27000</v>
+        <v>7692</v>
       </c>
       <c r="J20" s="5">
-        <v>75</v>
+        <v>75.2</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>90.8</v>
+        <v>97.2</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>422000</v>
+        <v>128000</v>
       </c>
       <c r="G21" s="7">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="H21" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I21" s="7">
-        <v>19667</v>
+        <v>14800</v>
       </c>
       <c r="J21" s="5">
-        <v>74.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>98.5</v>
+        <v>96.5</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>158000</v>
+        <v>108000</v>
       </c>
       <c r="G22" s="7">
-        <v>34000</v>
+        <v>11000</v>
       </c>
       <c r="H22" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I22" s="7">
-        <v>23000</v>
+        <v>8636</v>
       </c>
       <c r="J22" s="5">
-        <v>74.90000000000001</v>
+        <v>75.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>96</v>
+        <v>91.3</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>175000</v>
+        <v>256000</v>
       </c>
       <c r="G23" s="7">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="H23" s="7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I23" s="7">
-        <v>6583</v>
+        <v>18167</v>
       </c>
       <c r="J23" s="5">
-        <v>74.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>96.7</v>
+        <v>97.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>101000</v>
+        <v>191000</v>
       </c>
       <c r="G24" s="7">
-        <v>16000</v>
+        <v>40000</v>
       </c>
       <c r="H24" s="7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" s="7">
-        <v>11400</v>
+        <v>25500</v>
       </c>
       <c r="J24" s="5">
-        <v>74</v>
+        <v>74.8</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1417,30 +1417,28 @@
       <c r="A25" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5">
-        <v>9.9</v>
-      </c>
+      <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>92.59999999999999</v>
+        <v>90.5</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>192000</v>
+        <v>274000</v>
       </c>
       <c r="G25" s="7">
-        <v>14000</v>
+        <v>15000</v>
       </c>
       <c r="H25" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I25" s="7">
-        <v>11111</v>
+        <v>19000</v>
       </c>
       <c r="J25" s="5">
-        <v>73.7</v>
+        <v>74.5</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1454,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>90.5</v>
+        <v>91.2</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>218000</v>
+        <v>383000</v>
       </c>
       <c r="G26" s="7">
-        <v>13000</v>
+        <v>12000</v>
       </c>
       <c r="H26" s="7">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="I26" s="7">
-        <v>15125</v>
+        <v>17000</v>
       </c>
       <c r="J26" s="5">
-        <v>73.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1487,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>90.09999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>140000</v>
+        <v>233000</v>
       </c>
       <c r="G27" s="7">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="H27" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>16000</v>
+        <v>15111</v>
       </c>
       <c r="J27" s="5">
-        <v>73.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1520,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>92.90000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>236000</v>
+        <v>252000</v>
       </c>
       <c r="G28" s="7">
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="H28" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I28" s="7">
-        <v>17800</v>
+        <v>15286</v>
       </c>
       <c r="J28" s="5">
-        <v>73.5</v>
+        <v>74.3</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,28 +1549,30 @@
       <c r="A29" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="5"/>
+      <c r="B29" s="5">
+        <v>9.9</v>
+      </c>
       <c r="C29" s="5">
-        <v>90.2</v>
+        <v>93.3</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>237000</v>
+        <v>208000</v>
       </c>
       <c r="G29" s="7">
-        <v>13000</v>
+        <v>16000</v>
       </c>
       <c r="H29" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I29" s="7">
-        <v>15333</v>
+        <v>11600</v>
       </c>
       <c r="J29" s="5">
-        <v>73.40000000000001</v>
+        <v>74.2</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1586,26 +1586,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>88.8</v>
+        <v>97</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>306000</v>
+        <v>117000</v>
       </c>
       <c r="G30" s="7">
-        <v>9000</v>
+        <v>53000</v>
       </c>
       <c r="H30" s="7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>17250</v>
+        <v>22250</v>
       </c>
       <c r="J30" s="5">
-        <v>73.2</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1619,26 +1619,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>91.2</v>
+        <v>90.3</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>259000</v>
+        <v>209000</v>
       </c>
       <c r="G31" s="7">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="H31" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I31" s="7">
-        <v>19800</v>
+        <v>15875</v>
       </c>
       <c r="J31" s="5">
-        <v>73.09999999999999</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1652,26 +1652,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>98.90000000000001</v>
+        <v>96.3</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>132000</v>
+        <v>184000</v>
       </c>
       <c r="G32" s="7">
-        <v>18000</v>
+        <v>24000</v>
       </c>
       <c r="H32" s="7">
         <v>5</v>
       </c>
       <c r="I32" s="7">
-        <v>15000</v>
+        <v>21500</v>
       </c>
       <c r="J32" s="5">
-        <v>73.09999999999999</v>
+        <v>73.3</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1685,26 +1685,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>88.8</v>
+        <v>81.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>214000</v>
+        <v>462000</v>
       </c>
       <c r="G33" s="7">
-        <v>26000</v>
+        <v>18000</v>
       </c>
       <c r="H33" s="7">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I33" s="7">
-        <v>16167</v>
+        <v>33600</v>
       </c>
       <c r="J33" s="5">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>98.8</v>
+        <v>84.8</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>185000</v>
+        <v>376000</v>
       </c>
       <c r="G34" s="7">
-        <v>39000</v>
+        <v>27000</v>
       </c>
       <c r="H34" s="7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>26333</v>
+        <v>34200</v>
       </c>
       <c r="J34" s="5">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>88.09999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>376000</v>
+        <v>148000</v>
       </c>
       <c r="G35" s="7">
-        <v>1000</v>
+        <v>22000</v>
       </c>
       <c r="H35" s="7">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I35" s="7">
-        <v>17250</v>
+        <v>16500</v>
       </c>
       <c r="J35" s="5">
-        <v>72.8</v>
+        <v>73.2</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>88.5</v>
+        <v>81.5</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>145000</v>
+        <v>393000</v>
       </c>
       <c r="G36" s="7">
-        <v>5000</v>
+        <v>28000</v>
       </c>
       <c r="H36" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I36" s="7">
-        <v>15667</v>
+        <v>30571</v>
       </c>
       <c r="J36" s="5">
-        <v>72.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,23 +1817,23 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>90.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>119000</v>
+        <v>145000</v>
       </c>
       <c r="G37" s="7">
-        <v>10000</v>
+        <v>5000</v>
       </c>
       <c r="H37" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I37" s="7">
-        <v>10333</v>
+        <v>14429</v>
       </c>
       <c r="J37" s="5">
         <v>72.3</v>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>85.40000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>731000</v>
+        <v>203000</v>
       </c>
       <c r="G38" s="7">
-        <v>42000</v>
+        <v>34000</v>
       </c>
       <c r="H38" s="7">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I38" s="7">
-        <v>20636</v>
+        <v>25333</v>
       </c>
       <c r="J38" s="5">
-        <v>72.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>91.09999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>135000</v>
+        <v>228000</v>
       </c>
       <c r="G39" s="7">
-        <v>8000</v>
+        <v>3000</v>
       </c>
       <c r="H39" s="7">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="I39" s="7">
-        <v>7667</v>
+        <v>14077</v>
       </c>
       <c r="J39" s="5">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>91.7</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>105000</v>
+        <v>119000</v>
       </c>
       <c r="G40" s="7">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="H40" s="7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I40" s="7">
-        <v>6250</v>
+        <v>9167</v>
       </c>
       <c r="J40" s="5">
-        <v>72</v>
+        <v>71.5</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>86.59999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>349000</v>
+        <v>762000</v>
       </c>
       <c r="G41" s="7">
         <v>31000</v>
       </c>
       <c r="H41" s="7">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I41" s="7">
-        <v>36000</v>
+        <v>21500</v>
       </c>
       <c r="J41" s="5">
-        <v>71.59999999999999</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>86.40000000000001</v>
+        <v>89.7</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>225000</v>
+        <v>100000</v>
       </c>
       <c r="G42" s="7">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="H42" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I42" s="7">
-        <v>15000</v>
+        <v>8111</v>
       </c>
       <c r="J42" s="5">
-        <v>71.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2022,19 +2022,19 @@
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>246000</v>
+        <v>149000</v>
       </c>
       <c r="G43" s="7">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="H43" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I43" s="7">
-        <v>12750</v>
+        <v>14000</v>
       </c>
       <c r="J43" s="5">
-        <v>71</v>
+        <v>71.3</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>77</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>758000</v>
+        <v>114000</v>
       </c>
       <c r="G44" s="7">
-        <v>-19000</v>
+        <v>10000</v>
       </c>
       <c r="H44" s="7">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I44" s="7">
-        <v>33941</v>
+        <v>11200</v>
       </c>
       <c r="J44" s="5">
-        <v>70.8</v>
+        <v>71.2</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>78.2</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>365000</v>
+        <v>263000</v>
       </c>
       <c r="G45" s="7">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="H45" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I45" s="7">
-        <v>31000</v>
+        <v>20800</v>
       </c>
       <c r="J45" s="5">
-        <v>70.8</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>90.2</v>
+        <v>97.7</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>119000</v>
+        <v>134000</v>
       </c>
       <c r="G46" s="7">
-        <v>9000</v>
+        <v>17000</v>
       </c>
       <c r="H46" s="7">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I46" s="7">
-        <v>4333</v>
+        <v>21000</v>
       </c>
       <c r="J46" s="5">
-        <v>70.7</v>
+        <v>71</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>91.59999999999999</v>
+        <v>89.2</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>110000</v>
+        <v>109000</v>
       </c>
       <c r="G47" s="7">
-        <v>12000</v>
+        <v>5000</v>
       </c>
       <c r="H47" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I47" s="7">
-        <v>9200</v>
+        <v>7083</v>
       </c>
       <c r="J47" s="5">
-        <v>70.7</v>
+        <v>70.8</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,23 +2180,23 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>88.90000000000001</v>
+        <v>87</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>126000</v>
+        <v>335000</v>
       </c>
       <c r="G48" s="7">
-        <v>7000</v>
+        <v>-2000</v>
       </c>
       <c r="H48" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I48" s="7">
-        <v>7000</v>
+        <v>11077</v>
       </c>
       <c r="J48" s="5">
         <v>70.59999999999999</v>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>86.2</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>337000</v>
+        <v>160000</v>
       </c>
       <c r="G49" s="7">
-        <v>-5000</v>
+        <v>7000</v>
       </c>
       <c r="H49" s="7">
         <v>13</v>
       </c>
       <c r="I49" s="7">
-        <v>12167</v>
+        <v>8667</v>
       </c>
       <c r="J49" s="5">
-        <v>70.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,23 +2246,23 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>86.40000000000001</v>
+        <v>82.7</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>116000</v>
+        <v>344000</v>
       </c>
       <c r="G50" s="7">
-        <v>4000</v>
+        <v>19000</v>
       </c>
       <c r="H50" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I50" s="7">
-        <v>11833</v>
+        <v>19900</v>
       </c>
       <c r="J50" s="5">
         <v>70.5</v>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>85.90000000000001</v>
+        <v>87.2</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>518000</v>
+        <v>148000</v>
       </c>
       <c r="G51" s="7">
-        <v>-14000</v>
+        <v>2000</v>
       </c>
       <c r="H51" s="7">
         <v>13</v>
       </c>
       <c r="I51" s="7">
-        <v>12667</v>
+        <v>10000</v>
       </c>
       <c r="J51" s="5">
-        <v>70.40000000000001</v>
+        <v>70.5</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,23 +2312,23 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>86.5</v>
+        <v>77.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>146000</v>
+        <v>742000</v>
       </c>
       <c r="G52" s="7">
-        <v>1000</v>
+        <v>-16000</v>
       </c>
       <c r="H52" s="7">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="I52" s="7">
-        <v>10727</v>
+        <v>31167</v>
       </c>
       <c r="J52" s="5">
         <v>70.3</v>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>94.7</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>128000</v>
+        <v>139000</v>
       </c>
       <c r="G53" s="7">
-        <v>20000</v>
+        <v>11000</v>
       </c>
       <c r="H53" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I53" s="7">
         <v>11000</v>
       </c>
       <c r="J53" s="5">
-        <v>69.8</v>
+        <v>70.3</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>87.2</v>
+        <v>88.3</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>104000</v>
+        <v>110000</v>
       </c>
       <c r="G54" s="7">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="H54" s="7">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I54" s="7">
-        <v>7273</v>
+        <v>6154</v>
       </c>
       <c r="J54" s="5">
-        <v>69.8</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-27T04:48:34+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-28T05:17:08+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,148 +79,148 @@
     <t>我都化龙了，你说功法是假的？</t>
   </si>
   <si>
+    <t>我叫九江，李景隆那个九江！</t>
+  </si>
+  <si>
+    <t>全民领主：抽到人族，但来自战锤</t>
+  </si>
+  <si>
+    <t>全班同学穿越，我开局拜菩提祖师</t>
+  </si>
+  <si>
+    <t>海贼：门门果实？可曾听闻次元斩</t>
+  </si>
+  <si>
+    <t>恐怖游戏：开局皮嫁骨吓哭全球！</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
     <t>神雕杨过：我以九阴九阳压天下！</t>
   </si>
   <si>
-    <t>全民领主：抽到人族，但来自战锤</t>
+    <t>穿成警察，满城霸总排队来送业绩</t>
+  </si>
+  <si>
+    <t>穿书女频，被病娇姐妹缠上了</t>
+  </si>
+  <si>
+    <t>海洋求生？可我是人鱼公主！</t>
+  </si>
+  <si>
+    <t>努力就变强的我，被重生者曝光了</t>
+  </si>
+  <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>鬼谷下山：九封婚书闯都市</t>
+  </si>
+  <si>
+    <t>饰演封于修，女友神仙姐姐</t>
   </si>
   <si>
     <t>霍格沃茨：马尔福竟是傲娇千金？</t>
   </si>
   <si>
-    <t>穿成警察，满城霸总排队来送业绩</t>
-  </si>
-  <si>
-    <t>全班同学穿越，我开局拜菩提祖师</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
+    <t>末日觉醒，每天一次超级四选一</t>
+  </si>
+  <si>
+    <t>海吞天</t>
+  </si>
+  <si>
+    <t>四合院：大军进城，我系统吓跑了</t>
+  </si>
+  <si>
+    <t>情迷沪上贵妇</t>
   </si>
   <si>
     <t>天幕：千古第一才女的现代生活</t>
   </si>
   <si>
-    <t>海洋求生？可我是人鱼公主！</t>
-  </si>
-  <si>
-    <t>努力就变强的我，被重生者曝光了</t>
-  </si>
-  <si>
-    <t>饰演封于修，女友神仙姐姐</t>
-  </si>
-  <si>
-    <t>我叫九江，李景隆那个九江！</t>
+    <t>高冷？外冷内齁！你们请攻略我吧</t>
+  </si>
+  <si>
+    <t>红色人生模拟，我怎么成老干部了</t>
+  </si>
+  <si>
+    <t>崩铁：迫害完她们后，我有点死了</t>
+  </si>
+  <si>
+    <t>我都觉醒神明序列了系统才来？</t>
+  </si>
+  <si>
+    <t>我在美国当上帝</t>
   </si>
   <si>
     <t>龙族：我的强化每月刷新</t>
   </si>
   <si>
-    <t>海吞天</t>
-  </si>
-  <si>
-    <t>红色人生模拟，我怎么成老干部了</t>
-  </si>
-  <si>
-    <t>穿书女频，被病娇姐妹缠上了</t>
+    <t>入学第一天：我娶了丰腴美人教授</t>
   </si>
   <si>
     <t>破案：我能闻到凶手的味道</t>
   </si>
   <si>
+    <t>四合院：从红二十五开始进步</t>
+  </si>
+  <si>
+    <t>洪荒：开局带着白莲绿茶拜师三清</t>
+  </si>
+  <si>
+    <t>火影：九尾之夜，雷光万劫</t>
+  </si>
+  <si>
+    <t>末世轮盘：开局指定抽取序列魔药</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离还在藏</t>
+  </si>
+  <si>
+    <t>洪荒：神话祖巫，一念生灭万界</t>
+  </si>
+  <si>
     <t>美漫，从黑暗奇异博士开始</t>
   </si>
   <si>
-    <t>海贼：门门果实？可曾听闻次元斩</t>
-  </si>
-  <si>
-    <t>四合院：大军进城，我系统吓跑了</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离还在藏</t>
+    <t>秦始皇：朕有华夏全明星阵容</t>
+  </si>
+  <si>
+    <t>拒白月光不做冤大头七零留城享福</t>
+  </si>
+  <si>
+    <t>影综，从老九门开始</t>
+  </si>
+  <si>
+    <t>从二战老兵开始当调查员</t>
+  </si>
+  <si>
+    <t>型月：未婚妻露维亚，抽爆FGO</t>
+  </si>
+  <si>
+    <t>扫黑风暴之怒海惊涛</t>
+  </si>
+  <si>
+    <t>觉醒死亡笔记，开局写下邪神名字</t>
+  </si>
+  <si>
+    <t>亮剑：我和李云龙一起当警卫</t>
+  </si>
+  <si>
+    <t>高武：我以子嗣模拟证武道巅峰</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>穿到六零，吃瓜看戏</t>
+  </si>
+  <si>
+    <t>我真没想振兴大唐</t>
   </si>
   <si>
     <t>我伪装成人类文明，拯救诸天万界</t>
-  </si>
-  <si>
-    <t>天渊镇守百万载，你要挖我族人骨</t>
-  </si>
-  <si>
-    <t>恐怖游戏：开局皮嫁骨吓哭全球！</t>
-  </si>
-  <si>
-    <t>高冷？外冷内齁！你们请攻略我吧</t>
-  </si>
-  <si>
-    <t>崩铁：迫害完她们后，我有点死了</t>
-  </si>
-  <si>
-    <t>火影：九尾之夜，雷光万劫</t>
-  </si>
-  <si>
-    <t>四合院：从红二十五开始进步</t>
-  </si>
-  <si>
-    <t>cos服租赁，开局拿捏漫展女神</t>
-  </si>
-  <si>
-    <t>拒白月光不做冤大头七零留城享福</t>
-  </si>
-  <si>
-    <t>洪荒：开局带着白莲绿茶拜师三清</t>
-  </si>
-  <si>
-    <t>入学第一天：我娶了丰腴美人教授</t>
-  </si>
-  <si>
-    <t>穿到六零，吃瓜看戏</t>
-  </si>
-  <si>
-    <t>高武：我以子嗣模拟证武道巅峰</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>抗战：天道酬勤，从士兵开始崛起</t>
-  </si>
-  <si>
-    <t>末世轮盘：开局指定抽取序列魔药</t>
-  </si>
-  <si>
-    <t>末日觉醒，每天一次超级四选一</t>
-  </si>
-  <si>
-    <t>九霄通天塔</t>
-  </si>
-  <si>
-    <t>我都觉醒神明序列了系统才来？</t>
-  </si>
-  <si>
-    <t>鬼谷下山：九封婚书闯都市</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>觉醒死亡笔记，开局写下邪神名字</t>
-  </si>
-  <si>
-    <t>我真没想振兴大唐</t>
-  </si>
-  <si>
-    <t>亮剑：我和李云龙一起当警卫</t>
-  </si>
-  <si>
-    <t>重生年代：我怎么多了三个前妻</t>
-  </si>
-  <si>
-    <t>随机遗产，开局继承三百年功力</t>
-  </si>
-  <si>
-    <t>从二战老兵开始当调查员</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>92.5</v>
+        <v>89.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>547000</v>
+        <v>611000</v>
       </c>
       <c r="G5" s="7">
-        <v>70000</v>
+        <v>64000</v>
       </c>
       <c r="H5" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I5" s="7">
-        <v>90250</v>
+        <v>85000</v>
       </c>
       <c r="J5" s="5">
-        <v>88.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -799,19 +799,19 @@
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>218000</v>
+        <v>258000</v>
       </c>
       <c r="G6" s="7">
-        <v>61000</v>
+        <v>40000</v>
       </c>
       <c r="H6" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I6" s="7">
-        <v>29143</v>
+        <v>30500</v>
       </c>
       <c r="J6" s="5">
-        <v>82.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,26 +825,26 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>84.2</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>1035000</v>
+        <v>475000</v>
       </c>
       <c r="G7" s="7">
-        <v>41000</v>
+        <v>90000</v>
       </c>
       <c r="H7" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7">
-        <v>54077</v>
+        <v>48444</v>
       </c>
       <c r="J7" s="5">
-        <v>79.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99.8</v>
+        <v>99.59999999999999</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>198000</v>
+        <v>225000</v>
       </c>
       <c r="G8" s="7">
-        <v>40000</v>
+        <v>27000</v>
       </c>
       <c r="H8" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I8" s="7">
-        <v>26400</v>
+        <v>26500</v>
       </c>
       <c r="J8" s="5">
-        <v>79.5</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>97.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>272000</v>
+        <v>262000</v>
       </c>
       <c r="G9" s="7">
-        <v>33000</v>
+        <v>31000</v>
       </c>
       <c r="H9" s="7">
         <v>6</v>
       </c>
       <c r="I9" s="7">
-        <v>28200</v>
+        <v>31200</v>
       </c>
       <c r="J9" s="5">
-        <v>78.7</v>
+        <v>80.8</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>94.40000000000001</v>
+        <v>99.3</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>343000</v>
+        <v>225000</v>
       </c>
       <c r="G10" s="7">
-        <v>24000</v>
+        <v>34000</v>
       </c>
       <c r="H10" s="7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I10" s="7">
-        <v>25167</v>
+        <v>27200</v>
       </c>
       <c r="J10" s="5">
-        <v>78.2</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>100</v>
+        <v>99.3</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>231000</v>
+        <v>159000</v>
       </c>
       <c r="G11" s="7">
-        <v>46000</v>
+        <v>42000</v>
       </c>
       <c r="H11" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" s="7">
-        <v>31250</v>
+        <v>26200</v>
       </c>
       <c r="J11" s="5">
-        <v>77.8</v>
+        <v>79.2</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>82.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>2389000</v>
+        <v>395000</v>
       </c>
       <c r="G12" s="7">
-        <v>25000</v>
+        <v>60000</v>
       </c>
       <c r="H12" s="7">
-        <v>44</v>
+        <v>15</v>
       </c>
       <c r="I12" s="7">
-        <v>47442</v>
+        <v>14571</v>
       </c>
       <c r="J12" s="5">
-        <v>77.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>98.5</v>
+        <v>82.2</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>116000</v>
+        <v>1057000</v>
       </c>
       <c r="G13" s="7">
-        <v>15000</v>
+        <v>22000</v>
       </c>
       <c r="H13" s="7">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I13" s="7">
-        <v>12000</v>
+        <v>51786</v>
       </c>
       <c r="J13" s="5">
-        <v>77.2</v>
+        <v>78.2</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>100</v>
+        <v>94.3</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>154000</v>
+        <v>368000</v>
       </c>
       <c r="G14" s="7">
-        <v>22000</v>
+        <v>25000</v>
       </c>
       <c r="H14" s="7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I14" s="7">
-        <v>16400</v>
+        <v>25143</v>
       </c>
       <c r="J14" s="5">
-        <v>77.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>81.3</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>586000</v>
+        <v>148000</v>
       </c>
       <c r="G15" s="7">
-        <v>57000</v>
+        <v>20000</v>
       </c>
       <c r="H15" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>81333</v>
+        <v>15667</v>
       </c>
       <c r="J15" s="5">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>80.7</v>
+        <v>97</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>701000</v>
+        <v>172000</v>
       </c>
       <c r="G16" s="7">
-        <v>21000</v>
+        <v>18000</v>
       </c>
       <c r="H16" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I16" s="7">
-        <v>49571</v>
+        <v>16667</v>
       </c>
       <c r="J16" s="5">
-        <v>76.8</v>
+        <v>77.5</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>82.90000000000001</v>
+        <v>80.3</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>385000</v>
+        <v>628000</v>
       </c>
       <c r="G17" s="7">
-        <v>35000</v>
+        <v>42000</v>
       </c>
       <c r="H17" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I17" s="7">
-        <v>43250</v>
+        <v>71500</v>
       </c>
       <c r="J17" s="5">
-        <v>76.40000000000001</v>
+        <v>77</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>97.7</v>
+        <v>82.2</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>362000</v>
+        <v>2397000</v>
       </c>
       <c r="G18" s="7">
-        <v>35000</v>
+        <v>8000</v>
       </c>
       <c r="H18" s="7">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="I18" s="7">
-        <v>8846</v>
+        <v>46545</v>
       </c>
       <c r="J18" s="5">
-        <v>75.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1221,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>98.90000000000001</v>
+        <v>99.7</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>131000</v>
+        <v>127000</v>
       </c>
       <c r="G19" s="7">
-        <v>53000</v>
+        <v>18000</v>
       </c>
       <c r="H19" s="7">
         <v>14</v>
       </c>
       <c r="I19" s="7">
-        <v>3692</v>
+        <v>7923</v>
       </c>
       <c r="J19" s="5">
-        <v>75.3</v>
+        <v>76.8</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>96.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>196000</v>
+        <v>729000</v>
       </c>
       <c r="G20" s="7">
-        <v>21000</v>
+        <v>28000</v>
       </c>
       <c r="H20" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>7692</v>
+        <v>46875</v>
       </c>
       <c r="J20" s="5">
-        <v>75.2</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>97.2</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>128000</v>
+        <v>290000</v>
       </c>
       <c r="G21" s="7">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="H21" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>14800</v>
+        <v>26500</v>
       </c>
       <c r="J21" s="5">
-        <v>75.2</v>
+        <v>76.5</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>96.5</v>
+        <v>97.2</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>108000</v>
+        <v>131000</v>
       </c>
       <c r="G22" s="7">
-        <v>11000</v>
+        <v>17000</v>
       </c>
       <c r="H22" s="7">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="I22" s="7">
-        <v>8636</v>
+        <v>12167</v>
       </c>
       <c r="J22" s="5">
-        <v>75.2</v>
+        <v>76.5</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>91.3</v>
+        <v>99.2</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>256000</v>
+        <v>151000</v>
       </c>
       <c r="G23" s="7">
         <v>20000</v>
       </c>
       <c r="H23" s="7">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="I23" s="7">
-        <v>18167</v>
+        <v>4857</v>
       </c>
       <c r="J23" s="5">
-        <v>74.8</v>
+        <v>75.8</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>97.2</v>
+        <v>91.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>191000</v>
+        <v>293000</v>
       </c>
       <c r="G24" s="7">
-        <v>40000</v>
+        <v>19000</v>
       </c>
       <c r="H24" s="7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I24" s="7">
-        <v>25500</v>
+        <v>19000</v>
       </c>
       <c r="J24" s="5">
-        <v>74.8</v>
+        <v>75.2</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>90.5</v>
+        <v>96.3</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>274000</v>
+        <v>130000</v>
       </c>
       <c r="G25" s="7">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="H25" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I25" s="7">
-        <v>19000</v>
+        <v>9125</v>
       </c>
       <c r="J25" s="5">
-        <v>74.5</v>
+        <v>75.2</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>91.2</v>
+        <v>94.2</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>383000</v>
+        <v>127000</v>
       </c>
       <c r="G26" s="7">
-        <v>12000</v>
+        <v>11000</v>
       </c>
       <c r="H26" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>17000</v>
+        <v>11857</v>
       </c>
       <c r="J26" s="5">
-        <v>74.40000000000001</v>
+        <v>74.8</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1492,19 +1492,19 @@
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>233000</v>
+        <v>222000</v>
       </c>
       <c r="G27" s="7">
-        <v>15000</v>
+        <v>13000</v>
       </c>
       <c r="H27" s="7">
         <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>15111</v>
+        <v>15556</v>
       </c>
       <c r="J27" s="5">
-        <v>74.40000000000001</v>
+        <v>74.5</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>91.7</v>
+        <v>94.7</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>252000</v>
+        <v>215000</v>
       </c>
       <c r="G28" s="7">
-        <v>15000</v>
+        <v>19000</v>
       </c>
       <c r="H28" s="7">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I28" s="7">
-        <v>15286</v>
+        <v>8500</v>
       </c>
       <c r="J28" s="5">
-        <v>74.3</v>
+        <v>74.2</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1549,30 +1549,28 @@
       <c r="A29" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B29" s="5">
-        <v>9.9</v>
-      </c>
+      <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>93.3</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>208000</v>
+        <v>204000</v>
       </c>
       <c r="G29" s="7">
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="H29" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I29" s="7">
-        <v>11600</v>
+        <v>21200</v>
       </c>
       <c r="J29" s="5">
-        <v>74.2</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1586,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>97</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>117000</v>
+        <v>153000</v>
       </c>
       <c r="G30" s="7">
-        <v>53000</v>
+        <v>19000</v>
       </c>
       <c r="H30" s="7">
         <v>5</v>
       </c>
       <c r="I30" s="7">
-        <v>22250</v>
+        <v>20500</v>
       </c>
       <c r="J30" s="5">
-        <v>73.90000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1619,23 +1617,23 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>90.3</v>
+        <v>90</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>209000</v>
+        <v>391000</v>
       </c>
       <c r="G31" s="7">
-        <v>9000</v>
+        <v>8000</v>
       </c>
       <c r="H31" s="7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I31" s="7">
-        <v>15875</v>
+        <v>16357</v>
       </c>
       <c r="J31" s="5">
         <v>73.59999999999999</v>
@@ -1652,26 +1650,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>96.3</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>184000</v>
+        <v>380000</v>
       </c>
       <c r="G32" s="7">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="H32" s="7">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I32" s="7">
-        <v>21500</v>
+        <v>9500</v>
       </c>
       <c r="J32" s="5">
-        <v>73.3</v>
+        <v>73.5</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1685,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>81.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>462000</v>
+        <v>225000</v>
       </c>
       <c r="G33" s="7">
-        <v>18000</v>
+        <v>22000</v>
       </c>
       <c r="H33" s="7">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="I33" s="7">
-        <v>33600</v>
+        <v>24500</v>
       </c>
       <c r="J33" s="5">
-        <v>73.2</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>84.8</v>
+        <v>92.7</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>376000</v>
+        <v>116000</v>
       </c>
       <c r="G34" s="7">
-        <v>27000</v>
+        <v>8000</v>
       </c>
       <c r="H34" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I34" s="7">
-        <v>34200</v>
+        <v>8583</v>
       </c>
       <c r="J34" s="5">
-        <v>73.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>98.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>148000</v>
+        <v>394000</v>
       </c>
       <c r="G35" s="7">
-        <v>22000</v>
+        <v>18000</v>
       </c>
       <c r="H35" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>16500</v>
+        <v>31500</v>
       </c>
       <c r="J35" s="5">
-        <v>73.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>81.5</v>
+        <v>89.2</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>393000</v>
+        <v>151000</v>
       </c>
       <c r="G36" s="7">
-        <v>28000</v>
+        <v>6000</v>
       </c>
       <c r="H36" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I36" s="7">
-        <v>30571</v>
+        <v>13375</v>
       </c>
       <c r="J36" s="5">
-        <v>72.5</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>88.5</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>145000</v>
+        <v>473000</v>
       </c>
       <c r="G37" s="7">
-        <v>5000</v>
+        <v>11000</v>
       </c>
       <c r="H37" s="7">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I37" s="7">
-        <v>14429</v>
+        <v>31545</v>
       </c>
       <c r="J37" s="5">
-        <v>72.3</v>
+        <v>71.8</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>97.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>203000</v>
+        <v>154000</v>
       </c>
       <c r="G38" s="7">
-        <v>34000</v>
+        <v>5000</v>
       </c>
       <c r="H38" s="7">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="I38" s="7">
-        <v>25333</v>
+        <v>12875</v>
       </c>
       <c r="J38" s="5">
-        <v>71.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>87.3</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>228000</v>
+        <v>237000</v>
       </c>
       <c r="G39" s="7">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="H39" s="7">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="I39" s="7">
-        <v>14077</v>
+        <v>14000</v>
       </c>
       <c r="J39" s="5">
-        <v>71.5</v>
+        <v>71.3</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>89.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>119000</v>
+        <v>120000</v>
       </c>
       <c r="G40" s="7">
-        <v>9000</v>
+        <v>13000</v>
       </c>
       <c r="H40" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I40" s="7">
-        <v>9167</v>
+        <v>16250</v>
       </c>
       <c r="J40" s="5">
-        <v>71.5</v>
+        <v>71.3</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>83.7</v>
+        <v>85.3</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>762000</v>
+        <v>262000</v>
       </c>
       <c r="G41" s="7">
-        <v>31000</v>
+        <v>6000</v>
       </c>
       <c r="H41" s="7">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I41" s="7">
-        <v>21500</v>
+        <v>16429</v>
       </c>
       <c r="J41" s="5">
-        <v>71.40000000000001</v>
+        <v>71</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>89.7</v>
+        <v>82.2</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>100000</v>
+        <v>783000</v>
       </c>
       <c r="G42" s="7">
-        <v>6000</v>
+        <v>21000</v>
       </c>
       <c r="H42" s="7">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="I42" s="7">
-        <v>8111</v>
+        <v>21462</v>
       </c>
       <c r="J42" s="5">
-        <v>71.40000000000001</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>87</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>149000</v>
+        <v>407000</v>
       </c>
       <c r="G43" s="7">
-        <v>4000</v>
+        <v>14000</v>
       </c>
       <c r="H43" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I43" s="7">
-        <v>14000</v>
+        <v>28500</v>
       </c>
       <c r="J43" s="5">
-        <v>71.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>91.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>114000</v>
+        <v>236000</v>
       </c>
       <c r="G44" s="7">
-        <v>10000</v>
+        <v>27000</v>
       </c>
       <c r="H44" s="7">
         <v>6</v>
       </c>
       <c r="I44" s="7">
-        <v>11200</v>
+        <v>26000</v>
       </c>
       <c r="J44" s="5">
-        <v>71.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>87.09999999999999</v>
+        <v>89</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>263000</v>
+        <v>115000</v>
       </c>
       <c r="G45" s="7">
-        <v>35000</v>
+        <v>5000</v>
       </c>
       <c r="H45" s="7">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="I45" s="7">
-        <v>20800</v>
+        <v>6071</v>
       </c>
       <c r="J45" s="5">
-        <v>71.09999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>97.7</v>
+        <v>85.5</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>134000</v>
+        <v>284000</v>
       </c>
       <c r="G46" s="7">
-        <v>17000</v>
+        <v>-5000</v>
       </c>
       <c r="H46" s="7">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I46" s="7">
-        <v>21000</v>
+        <v>13214</v>
       </c>
       <c r="J46" s="5">
-        <v>71</v>
+        <v>70.3</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2145,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>89.2</v>
+        <v>86.7</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>109000</v>
+        <v>262000</v>
       </c>
       <c r="G47" s="7">
-        <v>5000</v>
+        <v>-1000</v>
       </c>
       <c r="H47" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I47" s="7">
-        <v>7083</v>
+        <v>10429</v>
       </c>
       <c r="J47" s="5">
-        <v>70.8</v>
+        <v>70.3</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2178,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>335000</v>
+        <v>166000</v>
       </c>
       <c r="G48" s="7">
-        <v>-2000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="7">
         <v>14</v>
       </c>
       <c r="I48" s="7">
-        <v>11077</v>
+        <v>8462</v>
       </c>
       <c r="J48" s="5">
-        <v>70.59999999999999</v>
+        <v>70.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2211,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>88.09999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>160000</v>
+        <v>149000</v>
       </c>
       <c r="G49" s="7">
-        <v>7000</v>
+        <v>1000</v>
       </c>
       <c r="H49" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I49" s="7">
-        <v>8667</v>
+        <v>9308</v>
       </c>
       <c r="J49" s="5">
-        <v>70.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2244,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>82.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>344000</v>
+        <v>125000</v>
       </c>
       <c r="G50" s="7">
-        <v>19000</v>
+        <v>6000</v>
       </c>
       <c r="H50" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I50" s="7">
-        <v>19900</v>
+        <v>8714</v>
       </c>
       <c r="J50" s="5">
-        <v>70.5</v>
+        <v>69.7</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2277,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>87.2</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>148000</v>
+        <v>491000</v>
       </c>
       <c r="G51" s="7">
-        <v>2000</v>
+        <v>-12000</v>
       </c>
       <c r="H51" s="7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I51" s="7">
-        <v>10000</v>
+        <v>8929</v>
       </c>
       <c r="J51" s="5">
-        <v>70.5</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2310,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>77.2</v>
+        <v>84.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>742000</v>
+        <v>224000</v>
       </c>
       <c r="G52" s="7">
-        <v>-16000</v>
+        <v>-4000</v>
       </c>
       <c r="H52" s="7">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="I52" s="7">
-        <v>31167</v>
+        <v>12786</v>
       </c>
       <c r="J52" s="5">
-        <v>70.3</v>
+        <v>69.5</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2343,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>90.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>139000</v>
+        <v>358000</v>
       </c>
       <c r="G53" s="7">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="H53" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I53" s="7">
-        <v>11000</v>
+        <v>19364</v>
       </c>
       <c r="J53" s="5">
-        <v>70.3</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2376,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>88.3</v>
+        <v>83.3</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>110000</v>
+        <v>247000</v>
       </c>
       <c r="G54" s="7">
-        <v>5000</v>
+        <v>-5000</v>
       </c>
       <c r="H54" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I54" s="7">
-        <v>6154</v>
+        <v>12750</v>
       </c>
       <c r="J54" s="5">
-        <v>70.09999999999999</v>
+        <v>69</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-28T05:17:08+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-29T05:27:40+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,151 +76,151 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>我叫九江，李景隆那个九江！</t>
+  </si>
+  <si>
+    <t>海贼：门门果实？可曾听闻次元斩</t>
+  </si>
+  <si>
+    <t>全民领主：抽到人族，但来自战锤</t>
+  </si>
+  <si>
+    <t>恐怖游戏：开局皮嫁骨吓哭全球！</t>
+  </si>
+  <si>
     <t>我都化龙了，你说功法是假的？</t>
   </si>
   <si>
-    <t>我叫九江，李景隆那个九江！</t>
-  </si>
-  <si>
-    <t>全民领主：抽到人族，但来自战锤</t>
+    <t>改变历史就变强：开局对掏汉武帝</t>
+  </si>
+  <si>
+    <t>努力就变强的我，被重生者曝光了</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>穿成警察，满城霸总排队来送业绩</t>
+  </si>
+  <si>
+    <t>穿书女频，被病娇姐妹缠上了</t>
+  </si>
+  <si>
+    <t>神雕杨过：我以九阴九阳压天下！</t>
+  </si>
+  <si>
+    <t>撞见黑白无常后，我成了走阴人</t>
+  </si>
+  <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>饰演封于修，女友神仙姐姐</t>
+  </si>
+  <si>
+    <t>霍格沃茨：马尔福竟是傲娇千金？</t>
   </si>
   <si>
     <t>全班同学穿越，我开局拜菩提祖师</t>
   </si>
   <si>
-    <t>海贼：门门果实？可曾听闻次元斩</t>
-  </si>
-  <si>
-    <t>恐怖游戏：开局皮嫁骨吓哭全球！</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>神雕杨过：我以九阴九阳压天下！</t>
-  </si>
-  <si>
-    <t>穿成警察，满城霸总排队来送业绩</t>
-  </si>
-  <si>
-    <t>穿书女频，被病娇姐妹缠上了</t>
+    <t>红龙暴君：刚破壳，先把龙妹弄哭</t>
   </si>
   <si>
     <t>海洋求生？可我是人鱼公主！</t>
   </si>
   <si>
-    <t>努力就变强的我，被重生者曝光了</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
+    <t>崩铁：迫害完她们后，我有点死了</t>
+  </si>
+  <si>
+    <t>完美犯罪？我只是在清理城市垃圾</t>
+  </si>
+  <si>
+    <t>大明：开局政变，请洪武赴死！</t>
+  </si>
+  <si>
+    <t>洪荒：开局带着白莲绿茶拜师三清</t>
+  </si>
+  <si>
+    <t>天幕：千古第一才女的现代生活</t>
+  </si>
+  <si>
+    <t>正光加代那些事</t>
+  </si>
+  <si>
+    <t>让你制作奢侈品，你做龙泉印泥？</t>
+  </si>
+  <si>
+    <t>海吞天</t>
+  </si>
+  <si>
+    <t>高冷？外冷内齁！你们请攻略我吧</t>
+  </si>
+  <si>
+    <t>红色人生模拟，我怎么成老干部了</t>
+  </si>
+  <si>
+    <t>破案：我能闻到凶手的味道</t>
+  </si>
+  <si>
+    <t>关于我被诸葛亮养大这件事儿</t>
+  </si>
+  <si>
+    <t>洪荒：神话祖巫，一念生灭万界</t>
+  </si>
+  <si>
+    <t>老师，我的异能是能带出游戏道具</t>
+  </si>
+  <si>
+    <t>我都觉醒神明序列了系统才来？</t>
+  </si>
+  <si>
+    <t>四合院：从红二十五开始进步</t>
+  </si>
+  <si>
+    <t>抗战：天道酬勤，从士兵开始崛起</t>
+  </si>
+  <si>
+    <t>火影：九尾之夜，雷光万劫</t>
+  </si>
+  <si>
+    <t>美漫，从黑暗奇异博士开始</t>
+  </si>
+  <si>
+    <t>狗管，还说你不会武功</t>
+  </si>
+  <si>
+    <t>入学第一天：我娶了丰腴美人教授</t>
   </si>
   <si>
     <t>鬼谷下山：九封婚书闯都市</t>
   </si>
   <si>
-    <t>饰演封于修，女友神仙姐姐</t>
-  </si>
-  <si>
-    <t>霍格沃茨：马尔福竟是傲娇千金？</t>
+    <t>天幕通原神，开局钟离还在藏</t>
+  </si>
+  <si>
+    <t>大明：我真不是万寿帝君</t>
+  </si>
+  <si>
+    <t>开局T病毒，全民变异，财阀慌了</t>
   </si>
   <si>
     <t>末日觉醒，每天一次超级四选一</t>
   </si>
   <si>
-    <t>海吞天</t>
+    <t>全民创世：我的世界全是禁忌怪谈</t>
+  </si>
+  <si>
+    <t>骗子闯入娱乐圈</t>
   </si>
   <si>
     <t>四合院：大军进城，我系统吓跑了</t>
   </si>
   <si>
-    <t>情迷沪上贵妇</t>
-  </si>
-  <si>
-    <t>天幕：千古第一才女的现代生活</t>
-  </si>
-  <si>
-    <t>高冷？外冷内齁！你们请攻略我吧</t>
-  </si>
-  <si>
-    <t>红色人生模拟，我怎么成老干部了</t>
-  </si>
-  <si>
-    <t>崩铁：迫害完她们后，我有点死了</t>
-  </si>
-  <si>
-    <t>我都觉醒神明序列了系统才来？</t>
-  </si>
-  <si>
-    <t>我在美国当上帝</t>
-  </si>
-  <si>
-    <t>龙族：我的强化每月刷新</t>
-  </si>
-  <si>
-    <t>入学第一天：我娶了丰腴美人教授</t>
-  </si>
-  <si>
-    <t>破案：我能闻到凶手的味道</t>
-  </si>
-  <si>
-    <t>四合院：从红二十五开始进步</t>
-  </si>
-  <si>
-    <t>洪荒：开局带着白莲绿茶拜师三清</t>
-  </si>
-  <si>
-    <t>火影：九尾之夜，雷光万劫</t>
-  </si>
-  <si>
-    <t>末世轮盘：开局指定抽取序列魔药</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离还在藏</t>
-  </si>
-  <si>
-    <t>洪荒：神话祖巫，一念生灭万界</t>
-  </si>
-  <si>
-    <t>美漫，从黑暗奇异博士开始</t>
-  </si>
-  <si>
-    <t>秦始皇：朕有华夏全明星阵容</t>
-  </si>
-  <si>
-    <t>拒白月光不做冤大头七零留城享福</t>
-  </si>
-  <si>
-    <t>影综，从老九门开始</t>
-  </si>
-  <si>
-    <t>从二战老兵开始当调查员</t>
-  </si>
-  <si>
-    <t>型月：未婚妻露维亚，抽爆FGO</t>
-  </si>
-  <si>
-    <t>扫黑风暴之怒海惊涛</t>
-  </si>
-  <si>
-    <t>觉醒死亡笔记，开局写下邪神名字</t>
+    <t>重生82年，军夫的随身空间</t>
   </si>
   <si>
     <t>亮剑：我和李云龙一起当警卫</t>
-  </si>
-  <si>
-    <t>高武：我以子嗣模拟证武道巅峰</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>穿到六零，吃瓜看戏</t>
-  </si>
-  <si>
-    <t>我真没想振兴大唐</t>
-  </si>
-  <si>
-    <t>我伪装成人类文明，拯救诸天万界</t>
   </si>
 </sst>
 </file>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>89.8</v>
+        <v>87.8</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>611000</v>
+        <v>669000</v>
       </c>
       <c r="G5" s="7">
-        <v>64000</v>
+        <v>58000</v>
       </c>
       <c r="H5" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I5" s="7">
-        <v>85000</v>
+        <v>80500</v>
       </c>
       <c r="J5" s="5">
-        <v>88.59999999999999</v>
+        <v>88.40000000000001</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>100</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>258000</v>
+        <v>568000</v>
       </c>
       <c r="G6" s="7">
-        <v>40000</v>
+        <v>93000</v>
       </c>
       <c r="H6" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I6" s="7">
-        <v>30500</v>
+        <v>52900</v>
       </c>
       <c r="J6" s="5">
-        <v>82.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -825,23 +825,23 @@
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5">
-        <v>90.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>475000</v>
+        <v>259000</v>
       </c>
       <c r="G7" s="7">
-        <v>90000</v>
+        <v>34000</v>
       </c>
       <c r="H7" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I7" s="7">
-        <v>48444</v>
+        <v>28333</v>
       </c>
       <c r="J7" s="5">
         <v>82.09999999999999</v>
@@ -858,26 +858,26 @@
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5">
-        <v>99.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="D8" s="4"/>
       <c r="E8" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>225000</v>
+        <v>257000</v>
       </c>
       <c r="G8" s="7">
-        <v>27000</v>
+        <v>32000</v>
       </c>
       <c r="H8" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7">
-        <v>26500</v>
+        <v>27286</v>
       </c>
       <c r="J8" s="5">
-        <v>81.40000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>99.7</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>262000</v>
+        <v>192000</v>
       </c>
       <c r="G9" s="7">
-        <v>31000</v>
+        <v>33000</v>
       </c>
       <c r="H9" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>31200</v>
+        <v>27333</v>
       </c>
       <c r="J9" s="5">
-        <v>80.8</v>
+        <v>81.7</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>99.3</v>
+        <v>95.8</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>225000</v>
+        <v>280000</v>
       </c>
       <c r="G10" s="7">
-        <v>34000</v>
+        <v>22000</v>
       </c>
       <c r="H10" s="7">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="I10" s="7">
-        <v>27200</v>
+        <v>29556</v>
       </c>
       <c r="J10" s="5">
-        <v>79.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>99.3</v>
+        <v>100</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>159000</v>
+        <v>174000</v>
       </c>
       <c r="G11" s="7">
-        <v>42000</v>
+        <v>57000</v>
       </c>
       <c r="H11" s="7">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I11" s="7">
-        <v>26200</v>
+        <v>63000</v>
       </c>
       <c r="J11" s="5">
-        <v>79.2</v>
+        <v>79.8</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>100</v>
+        <v>80.7</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>395000</v>
+        <v>669000</v>
       </c>
       <c r="G12" s="7">
-        <v>60000</v>
+        <v>41000</v>
       </c>
       <c r="H12" s="7">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I12" s="7">
-        <v>14571</v>
+        <v>65400</v>
       </c>
       <c r="J12" s="5">
-        <v>78.59999999999999</v>
+        <v>78.7</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>82.2</v>
+        <v>97.8</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>1057000</v>
+        <v>433000</v>
       </c>
       <c r="G13" s="7">
-        <v>22000</v>
+        <v>38000</v>
       </c>
       <c r="H13" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I13" s="7">
-        <v>51786</v>
+        <v>16133</v>
       </c>
       <c r="J13" s="5">
-        <v>78.2</v>
+        <v>77.8</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>94.3</v>
+        <v>93.90000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>368000</v>
+        <v>390000</v>
       </c>
       <c r="G14" s="7">
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="H14" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I14" s="7">
-        <v>25143</v>
+        <v>24750</v>
       </c>
       <c r="J14" s="5">
-        <v>78.2</v>
+        <v>77.8</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>98.40000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>148000</v>
+        <v>168000</v>
       </c>
       <c r="G15" s="7">
         <v>20000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I15" s="7">
-        <v>15667</v>
+        <v>16286</v>
       </c>
       <c r="J15" s="5">
-        <v>78</v>
+        <v>77.5</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>97</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>172000</v>
+        <v>1075000</v>
       </c>
       <c r="G16" s="7">
         <v>18000</v>
       </c>
       <c r="H16" s="7">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I16" s="7">
-        <v>16667</v>
+        <v>49533</v>
       </c>
       <c r="J16" s="5">
-        <v>77.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>80.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>628000</v>
+        <v>113000</v>
       </c>
       <c r="G17" s="7">
-        <v>42000</v>
+        <v>29000</v>
       </c>
       <c r="H17" s="7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I17" s="7">
-        <v>71500</v>
+        <v>18600</v>
       </c>
       <c r="J17" s="5">
-        <v>77</v>
+        <v>77.3</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>82.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>2397000</v>
+        <v>2414000</v>
       </c>
       <c r="G18" s="7">
-        <v>8000</v>
+        <v>17000</v>
       </c>
       <c r="H18" s="7">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I18" s="7">
-        <v>46545</v>
+        <v>45889</v>
       </c>
       <c r="J18" s="5">
-        <v>76.8</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,23 +1221,23 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>99.7</v>
+        <v>82.5</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>127000</v>
+        <v>764000</v>
       </c>
       <c r="G19" s="7">
-        <v>18000</v>
+        <v>35000</v>
       </c>
       <c r="H19" s="7">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="I19" s="7">
-        <v>7923</v>
+        <v>45556</v>
       </c>
       <c r="J19" s="5">
         <v>76.8</v>
@@ -1254,26 +1254,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>81.59999999999999</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>729000</v>
+        <v>307000</v>
       </c>
       <c r="G20" s="7">
-        <v>28000</v>
+        <v>17000</v>
       </c>
       <c r="H20" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I20" s="7">
-        <v>46875</v>
+        <v>25143</v>
       </c>
       <c r="J20" s="5">
-        <v>76.59999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1294,19 +1294,19 @@
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>290000</v>
+        <v>271000</v>
       </c>
       <c r="G21" s="7">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="H21" s="7">
         <v>7</v>
       </c>
       <c r="I21" s="7">
-        <v>26500</v>
+        <v>27500</v>
       </c>
       <c r="J21" s="5">
-        <v>76.5</v>
+        <v>76.7</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>97.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>131000</v>
+        <v>106000</v>
       </c>
       <c r="G22" s="7">
-        <v>17000</v>
+        <v>12000</v>
       </c>
       <c r="H22" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>12167</v>
+        <v>12143</v>
       </c>
       <c r="J22" s="5">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>99.2</v>
+        <v>94.8</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>151000</v>
+        <v>188000</v>
       </c>
       <c r="G23" s="7">
-        <v>20000</v>
+        <v>16000</v>
       </c>
       <c r="H23" s="7">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="I23" s="7">
-        <v>4857</v>
+        <v>16571</v>
       </c>
       <c r="J23" s="5">
-        <v>75.8</v>
+        <v>76.3</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>91.8</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>293000</v>
+        <v>220000</v>
       </c>
       <c r="G24" s="7">
-        <v>19000</v>
+        <v>16000</v>
       </c>
       <c r="H24" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I24" s="7">
-        <v>19000</v>
+        <v>20333</v>
       </c>
       <c r="J24" s="5">
-        <v>75.2</v>
+        <v>75.7</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>96.3</v>
+        <v>95.5</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>130000</v>
+        <v>102000</v>
       </c>
       <c r="G25" s="7">
-        <v>16000</v>
+        <v>11000</v>
       </c>
       <c r="H25" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I25" s="7">
-        <v>9125</v>
+        <v>11571</v>
       </c>
       <c r="J25" s="5">
-        <v>75.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1452,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>94.2</v>
+        <v>100</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>127000</v>
+        <v>172000</v>
       </c>
       <c r="G26" s="7">
-        <v>11000</v>
+        <v>60000</v>
       </c>
       <c r="H26" s="7">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="I26" s="7">
-        <v>11857</v>
+        <v>1200</v>
       </c>
       <c r="J26" s="5">
-        <v>74.8</v>
+        <v>75.3</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1485,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>92.09999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>222000</v>
+        <v>165000</v>
       </c>
       <c r="G27" s="7">
-        <v>13000</v>
+        <v>14000</v>
       </c>
       <c r="H27" s="7">
         <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>15556</v>
+        <v>13444</v>
       </c>
       <c r="J27" s="5">
-        <v>74.5</v>
+        <v>75.3</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1518,26 +1518,26 @@
       </c>
       <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>94.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>215000</v>
+        <v>140000</v>
       </c>
       <c r="G28" s="7">
-        <v>19000</v>
+        <v>13000</v>
       </c>
       <c r="H28" s="7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I28" s="7">
-        <v>8500</v>
+        <v>12000</v>
       </c>
       <c r="J28" s="5">
-        <v>74.2</v>
+        <v>75.3</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1551,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>92.40000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>204000</v>
+        <v>152000</v>
       </c>
       <c r="G29" s="7">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="H29" s="7">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I29" s="7">
-        <v>21200</v>
+        <v>5667</v>
       </c>
       <c r="J29" s="5">
-        <v>74.09999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1584,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>97.59999999999999</v>
+        <v>98.3</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>153000</v>
+        <v>210000</v>
       </c>
       <c r="G30" s="7">
-        <v>19000</v>
+        <v>28000</v>
       </c>
       <c r="H30" s="7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I30" s="7">
-        <v>20500</v>
+        <v>32000</v>
       </c>
       <c r="J30" s="5">
-        <v>73.8</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1617,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>391000</v>
+        <v>167000</v>
       </c>
       <c r="G31" s="7">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="H31" s="7">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" s="7">
-        <v>16357</v>
+        <v>5600</v>
       </c>
       <c r="J31" s="5">
-        <v>73.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,23 +1650,23 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>92.90000000000001</v>
+        <v>90.5</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>380000</v>
+        <v>232000</v>
       </c>
       <c r="G32" s="7">
-        <v>18000</v>
+        <v>10000</v>
       </c>
       <c r="H32" s="7">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="I32" s="7">
-        <v>9500</v>
+        <v>15000</v>
       </c>
       <c r="J32" s="5">
         <v>73.5</v>
@@ -1683,26 +1683,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>95.09999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>225000</v>
+        <v>229000</v>
       </c>
       <c r="G33" s="7">
-        <v>22000</v>
+        <v>14000</v>
       </c>
       <c r="H33" s="7">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I33" s="7">
-        <v>24500</v>
+        <v>8867</v>
       </c>
       <c r="J33" s="5">
-        <v>73.40000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1716,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>92.7</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>116000</v>
+        <v>124000</v>
       </c>
       <c r="G34" s="7">
         <v>8000</v>
       </c>
       <c r="H34" s="7">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I34" s="7">
-        <v>8583</v>
+        <v>8538</v>
       </c>
       <c r="J34" s="5">
-        <v>73.09999999999999</v>
+        <v>73</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1749,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>81.90000000000001</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>394000</v>
+        <v>100000</v>
       </c>
       <c r="G35" s="7">
-        <v>18000</v>
+        <v>9000</v>
       </c>
       <c r="H35" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I35" s="7">
-        <v>31500</v>
+        <v>7455</v>
       </c>
       <c r="J35" s="5">
-        <v>72.90000000000001</v>
+        <v>72.7</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1782,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>89.2</v>
+        <v>92.2</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>151000</v>
+        <v>130000</v>
       </c>
       <c r="G36" s="7">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="H36" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>13375</v>
+        <v>15000</v>
       </c>
       <c r="J36" s="5">
-        <v>72.40000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1815,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>79.90000000000001</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>473000</v>
+        <v>135000</v>
       </c>
       <c r="G37" s="7">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="H37" s="7">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="I37" s="7">
-        <v>31545</v>
+        <v>19000</v>
       </c>
       <c r="J37" s="5">
-        <v>71.8</v>
+        <v>72.3</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1848,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>87.59999999999999</v>
+        <v>90.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>154000</v>
+        <v>162000</v>
       </c>
       <c r="G38" s="7">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="H38" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>12875</v>
+        <v>18200</v>
       </c>
       <c r="J38" s="5">
-        <v>71.40000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1881,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>86.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>237000</v>
+        <v>410000</v>
       </c>
       <c r="G39" s="7">
-        <v>4000</v>
+        <v>16000</v>
       </c>
       <c r="H39" s="7">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I39" s="7">
-        <v>14000</v>
+        <v>29286</v>
       </c>
       <c r="J39" s="5">
-        <v>71.3</v>
+        <v>72</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1914,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>95</v>
+        <v>91.2</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>120000</v>
+        <v>109000</v>
       </c>
       <c r="G40" s="7">
-        <v>13000</v>
+        <v>7000</v>
       </c>
       <c r="H40" s="7">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="I40" s="7">
-        <v>16250</v>
+        <v>7455</v>
       </c>
       <c r="J40" s="5">
-        <v>71.3</v>
+        <v>72</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1947,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>85.3</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>262000</v>
+        <v>487000</v>
       </c>
       <c r="G41" s="7">
-        <v>6000</v>
+        <v>14000</v>
       </c>
       <c r="H41" s="7">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I41" s="7">
-        <v>16429</v>
+        <v>30083</v>
       </c>
       <c r="J41" s="5">
-        <v>71</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1980,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>82.2</v>
+        <v>87.3</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>783000</v>
+        <v>271000</v>
       </c>
       <c r="G42" s="7">
-        <v>21000</v>
+        <v>9000</v>
       </c>
       <c r="H42" s="7">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I42" s="7">
-        <v>21462</v>
+        <v>15500</v>
       </c>
       <c r="J42" s="5">
-        <v>70.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2013,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>79.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>407000</v>
+        <v>119000</v>
       </c>
       <c r="G43" s="7">
-        <v>14000</v>
+        <v>12000</v>
       </c>
       <c r="H43" s="7">
         <v>9</v>
       </c>
       <c r="I43" s="7">
-        <v>28500</v>
+        <v>3750</v>
       </c>
       <c r="J43" s="5">
-        <v>70.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2046,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>83.90000000000001</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>236000</v>
+        <v>233000</v>
       </c>
       <c r="G44" s="7">
-        <v>27000</v>
+        <v>8000</v>
       </c>
       <c r="H44" s="7">
         <v>6</v>
       </c>
       <c r="I44" s="7">
-        <v>26000</v>
+        <v>21200</v>
       </c>
       <c r="J44" s="5">
-        <v>70.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2079,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>89</v>
+        <v>90.3</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>115000</v>
+        <v>133000</v>
       </c>
       <c r="G45" s="7">
-        <v>5000</v>
+        <v>6000</v>
       </c>
       <c r="H45" s="7">
         <v>15</v>
       </c>
       <c r="I45" s="7">
-        <v>6071</v>
+        <v>7786</v>
       </c>
       <c r="J45" s="5">
-        <v>70.5</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2112,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>85.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>284000</v>
+        <v>242000</v>
       </c>
       <c r="G46" s="7">
-        <v>-5000</v>
+        <v>5000</v>
       </c>
       <c r="H46" s="7">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="I46" s="7">
-        <v>13214</v>
+        <v>13182</v>
       </c>
       <c r="J46" s="5">
-        <v>70.3</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2143,28 +2143,30 @@
       <c r="A47" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="5"/>
+      <c r="B47" s="5">
+        <v>9.1</v>
+      </c>
       <c r="C47" s="5">
-        <v>86.7</v>
+        <v>83</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>262000</v>
+        <v>309000</v>
       </c>
       <c r="G47" s="7">
-        <v>-1000</v>
+        <v>23000</v>
       </c>
       <c r="H47" s="7">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I47" s="7">
-        <v>10429</v>
+        <v>30200</v>
       </c>
       <c r="J47" s="5">
-        <v>70.3</v>
+        <v>71.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2178,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.40000000000001</v>
+        <v>93.2</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>166000</v>
+        <v>200000</v>
       </c>
       <c r="G48" s="7">
-        <v>6000</v>
+        <v>21000</v>
       </c>
       <c r="H48" s="7">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I48" s="7">
-        <v>8462</v>
+        <v>31667</v>
       </c>
       <c r="J48" s="5">
-        <v>70.2</v>
+        <v>71.2</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2211,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>86.5</v>
+        <v>87.7</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>149000</v>
+        <v>138000</v>
       </c>
       <c r="G49" s="7">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="H49" s="7">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I49" s="7">
-        <v>9308</v>
+        <v>11429</v>
       </c>
       <c r="J49" s="5">
-        <v>69.90000000000001</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2244,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>86.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>125000</v>
+        <v>114000</v>
       </c>
       <c r="G50" s="7">
-        <v>6000</v>
+        <v>11000</v>
       </c>
       <c r="H50" s="7">
         <v>8</v>
       </c>
       <c r="I50" s="7">
-        <v>8714</v>
+        <v>6286</v>
       </c>
       <c r="J50" s="5">
-        <v>69.7</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2277,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>86.09999999999999</v>
+        <v>78.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>491000</v>
+        <v>512000</v>
       </c>
       <c r="G51" s="7">
-        <v>-12000</v>
+        <v>28000</v>
       </c>
       <c r="H51" s="7">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="I51" s="7">
-        <v>8929</v>
+        <v>39400</v>
       </c>
       <c r="J51" s="5">
-        <v>69.59999999999999</v>
+        <v>71</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2310,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>84.2</v>
+        <v>85.2</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>224000</v>
+        <v>294000</v>
       </c>
       <c r="G52" s="7">
-        <v>-4000</v>
+        <v>1000</v>
       </c>
       <c r="H52" s="7">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="I52" s="7">
-        <v>12786</v>
+        <v>16750</v>
       </c>
       <c r="J52" s="5">
-        <v>69.5</v>
+        <v>71</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2343,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>81</v>
+        <v>91.2</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>358000</v>
+        <v>100000</v>
       </c>
       <c r="G53" s="7">
-        <v>14000</v>
+        <v>8000</v>
       </c>
       <c r="H53" s="7">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I53" s="7">
-        <v>19364</v>
+        <v>2467</v>
       </c>
       <c r="J53" s="5">
-        <v>69.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2376,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>83.3</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>247000</v>
+        <v>152000</v>
       </c>
       <c r="G54" s="7">
-        <v>-5000</v>
+        <v>3000</v>
       </c>
       <c r="H54" s="7">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="I54" s="7">
-        <v>12750</v>
+        <v>8857</v>
       </c>
       <c r="J54" s="5">
-        <v>69</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-29T05:27:40+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-30T05:27:10+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -79,73 +79,130 @@
     <t>我叫九江，李景隆那个九江！</t>
   </si>
   <si>
+    <t>恐怖游戏：开局皮嫁骨吓哭全球！</t>
+  </si>
+  <si>
+    <t>全民领主：抽到人族，但来自战锤</t>
+  </si>
+  <si>
+    <t>撞见黑白无常后，我成了走阴人</t>
+  </si>
+  <si>
+    <t>改变历史就变强：开局对掏汉武帝</t>
+  </si>
+  <si>
+    <t>努力就变强的我，被重生者曝光了</t>
+  </si>
+  <si>
+    <t>穿书女频，被病娇姐妹缠上了</t>
+  </si>
+  <si>
+    <t>洪荒：开局带着白莲绿茶拜师三清</t>
+  </si>
+  <si>
+    <t>我都化龙了，你说功法是假的？</t>
+  </si>
+  <si>
+    <t>我都觉醒神明序列了系统才来？</t>
+  </si>
+  <si>
+    <t>神雕杨过：我以九阴九阳压天下！</t>
+  </si>
+  <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>完美犯罪？我只是在清理城市垃圾</t>
+  </si>
+  <si>
     <t>海贼：门门果实？可曾听闻次元斩</t>
   </si>
   <si>
-    <t>全民领主：抽到人族，但来自战锤</t>
-  </si>
-  <si>
-    <t>恐怖游戏：开局皮嫁骨吓哭全球！</t>
-  </si>
-  <si>
-    <t>我都化龙了，你说功法是假的？</t>
-  </si>
-  <si>
-    <t>改变历史就变强：开局对掏汉武帝</t>
-  </si>
-  <si>
-    <t>努力就变强的我，被重生者曝光了</t>
+    <t>穿成警察，满城霸总排队来送业绩</t>
   </si>
   <si>
     <t>我在诸天当超能力爷</t>
   </si>
   <si>
-    <t>穿成警察，满城霸总排队来送业绩</t>
-  </si>
-  <si>
-    <t>穿书女频，被病娇姐妹缠上了</t>
-  </si>
-  <si>
-    <t>神雕杨过：我以九阴九阳压天下！</t>
-  </si>
-  <si>
-    <t>撞见黑白无常后，我成了走阴人</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
+    <t>崩铁：迫害完她们后，我有点死了</t>
+  </si>
+  <si>
+    <t>红龙暴君：刚破壳，先把龙妹弄哭</t>
   </si>
   <si>
     <t>饰演封于修，女友神仙姐姐</t>
   </si>
   <si>
+    <t>正光加代那些事</t>
+  </si>
+  <si>
+    <t>大明：开局政变，请洪武赴死！</t>
+  </si>
+  <si>
+    <t>天幕：千古第一才女的现代生活</t>
+  </si>
+  <si>
+    <t>大明：我真不是万寿帝君</t>
+  </si>
+  <si>
+    <t>全班同学穿越，我开局拜菩提祖师</t>
+  </si>
+  <si>
+    <t>洪荒：神话祖巫，一念生灭万界</t>
+  </si>
+  <si>
+    <t>弹幕说，我未婚妻要嫁给她助理！</t>
+  </si>
+  <si>
+    <t>海洋求生？可我是人鱼公主！</t>
+  </si>
+  <si>
     <t>霍格沃茨：马尔福竟是傲娇千金？</t>
   </si>
   <si>
-    <t>全班同学穿越，我开局拜菩提祖师</t>
-  </si>
-  <si>
-    <t>红龙暴君：刚破壳，先把龙妹弄哭</t>
-  </si>
-  <si>
-    <t>海洋求生？可我是人鱼公主！</t>
-  </si>
-  <si>
-    <t>崩铁：迫害完她们后，我有点死了</t>
-  </si>
-  <si>
-    <t>完美犯罪？我只是在清理城市垃圾</t>
-  </si>
-  <si>
-    <t>大明：开局政变，请洪武赴死！</t>
-  </si>
-  <si>
-    <t>洪荒：开局带着白莲绿茶拜师三清</t>
-  </si>
-  <si>
-    <t>天幕：千古第一才女的现代生活</t>
-  </si>
-  <si>
-    <t>正光加代那些事</t>
+    <t>绝症留洋归乡？举国哭求我别死！</t>
+  </si>
+  <si>
+    <t>儒道剑仙，苟在镇北王府当赘婿</t>
+  </si>
+  <si>
+    <t>四合院：开局1948年教训禽兽</t>
+  </si>
+  <si>
+    <t>狗管，还说你不会武功</t>
+  </si>
+  <si>
+    <t>老师，我的异能是能带出游戏道具</t>
+  </si>
+  <si>
+    <t>入学第一天：我娶了丰腴美人教授</t>
+  </si>
+  <si>
+    <t>四合院：大军进城，我系统吓跑了</t>
+  </si>
+  <si>
+    <t>骗子闯入娱乐圈</t>
+  </si>
+  <si>
+    <t>四合院：我金发碧眼，说是自己人</t>
+  </si>
+  <si>
+    <t>我在儒道世界以诗词文章成圣人</t>
+  </si>
+  <si>
+    <t>四合院：从红二十五开始进步</t>
+  </si>
+  <si>
+    <t>破案：我能闻到凶手的味道</t>
+  </si>
+  <si>
+    <t>抗战：天道酬勤，从士兵开始崛起</t>
+  </si>
+  <si>
+    <t>火影：九尾之夜，雷光万劫</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离还在藏</t>
   </si>
   <si>
     <t>让你制作奢侈品，你做龙泉印泥？</t>
@@ -154,73 +211,16 @@
     <t>海吞天</t>
   </si>
   <si>
+    <t>废土黑作坊：从造一级弹开始</t>
+  </si>
+  <si>
+    <t>美漫，从黑暗奇异博士开始</t>
+  </si>
+  <si>
     <t>高冷？外冷内齁！你们请攻略我吧</t>
   </si>
   <si>
     <t>红色人生模拟，我怎么成老干部了</t>
-  </si>
-  <si>
-    <t>破案：我能闻到凶手的味道</t>
-  </si>
-  <si>
-    <t>关于我被诸葛亮养大这件事儿</t>
-  </si>
-  <si>
-    <t>洪荒：神话祖巫，一念生灭万界</t>
-  </si>
-  <si>
-    <t>老师，我的异能是能带出游戏道具</t>
-  </si>
-  <si>
-    <t>我都觉醒神明序列了系统才来？</t>
-  </si>
-  <si>
-    <t>四合院：从红二十五开始进步</t>
-  </si>
-  <si>
-    <t>抗战：天道酬勤，从士兵开始崛起</t>
-  </si>
-  <si>
-    <t>火影：九尾之夜，雷光万劫</t>
-  </si>
-  <si>
-    <t>美漫，从黑暗奇异博士开始</t>
-  </si>
-  <si>
-    <t>狗管，还说你不会武功</t>
-  </si>
-  <si>
-    <t>入学第一天：我娶了丰腴美人教授</t>
-  </si>
-  <si>
-    <t>鬼谷下山：九封婚书闯都市</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离还在藏</t>
-  </si>
-  <si>
-    <t>大明：我真不是万寿帝君</t>
-  </si>
-  <si>
-    <t>开局T病毒，全民变异，财阀慌了</t>
-  </si>
-  <si>
-    <t>末日觉醒，每天一次超级四选一</t>
-  </si>
-  <si>
-    <t>全民创世：我的世界全是禁忌怪谈</t>
-  </si>
-  <si>
-    <t>骗子闯入娱乐圈</t>
-  </si>
-  <si>
-    <t>四合院：大军进城，我系统吓跑了</t>
-  </si>
-  <si>
-    <t>重生82年，军夫的随身空间</t>
-  </si>
-  <si>
-    <t>亮剑：我和李云龙一起当警卫</t>
   </si>
 </sst>
 </file>
@@ -766,19 +766,19 @@
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>669000</v>
+        <v>726000</v>
       </c>
       <c r="G5" s="7">
-        <v>58000</v>
+        <v>57000</v>
       </c>
       <c r="H5" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I5" s="7">
-        <v>80500</v>
+        <v>77143</v>
       </c>
       <c r="J5" s="5">
-        <v>88.40000000000001</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>92.09999999999999</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>568000</v>
+        <v>655000</v>
       </c>
       <c r="G6" s="7">
-        <v>93000</v>
+        <v>87000</v>
       </c>
       <c r="H6" s="7">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I6" s="7">
-        <v>52900</v>
+        <v>56000</v>
       </c>
       <c r="J6" s="5">
-        <v>83.90000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -832,19 +832,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>259000</v>
+        <v>231000</v>
       </c>
       <c r="G7" s="7">
-        <v>34000</v>
+        <v>39000</v>
       </c>
       <c r="H7" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I7" s="7">
-        <v>28333</v>
+        <v>29000</v>
       </c>
       <c r="J7" s="5">
-        <v>82.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -865,19 +865,19 @@
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>257000</v>
+        <v>294000</v>
       </c>
       <c r="G8" s="7">
-        <v>32000</v>
+        <v>37000</v>
       </c>
       <c r="H8" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="7">
-        <v>27286</v>
+        <v>28500</v>
       </c>
       <c r="J8" s="5">
-        <v>81.8</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>99.7</v>
+        <v>100</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>192000</v>
+        <v>171000</v>
       </c>
       <c r="G9" s="7">
-        <v>33000</v>
+        <v>58000</v>
       </c>
       <c r="H9" s="7">
         <v>7</v>
       </c>
       <c r="I9" s="7">
-        <v>27333</v>
+        <v>25167</v>
       </c>
       <c r="J9" s="5">
-        <v>81.7</v>
+        <v>81.3</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,23 +924,23 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>280000</v>
+        <v>205000</v>
       </c>
       <c r="G10" s="7">
-        <v>22000</v>
+        <v>31000</v>
       </c>
       <c r="H10" s="7">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I10" s="7">
-        <v>29556</v>
+        <v>52333</v>
       </c>
       <c r="J10" s="5">
         <v>80.09999999999999</v>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>100</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>174000</v>
+        <v>709000</v>
       </c>
       <c r="G11" s="7">
-        <v>57000</v>
+        <v>40000</v>
       </c>
       <c r="H11" s="7">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I11" s="7">
-        <v>63000</v>
+        <v>61167</v>
       </c>
       <c r="J11" s="5">
-        <v>79.8</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>80.7</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>669000</v>
+        <v>204000</v>
       </c>
       <c r="G12" s="7">
-        <v>41000</v>
+        <v>36000</v>
       </c>
       <c r="H12" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I12" s="7">
-        <v>65400</v>
+        <v>18750</v>
       </c>
       <c r="J12" s="5">
-        <v>78.7</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>97.8</v>
+        <v>100</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>433000</v>
+        <v>201000</v>
       </c>
       <c r="G13" s="7">
-        <v>38000</v>
+        <v>36000</v>
       </c>
       <c r="H13" s="7">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="I13" s="7">
-        <v>16133</v>
+        <v>15700</v>
       </c>
       <c r="J13" s="5">
-        <v>77.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>93.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>390000</v>
+        <v>296000</v>
       </c>
       <c r="G14" s="7">
-        <v>22000</v>
+        <v>16000</v>
       </c>
       <c r="H14" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I14" s="7">
-        <v>24750</v>
+        <v>28200</v>
       </c>
       <c r="J14" s="5">
-        <v>77.8</v>
+        <v>78.3</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>97.09999999999999</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>168000</v>
+        <v>183000</v>
       </c>
       <c r="G15" s="7">
-        <v>20000</v>
+        <v>21000</v>
       </c>
       <c r="H15" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I15" s="7">
-        <v>16286</v>
+        <v>18667</v>
       </c>
       <c r="J15" s="5">
-        <v>77.5</v>
+        <v>78.3</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>81.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>1075000</v>
+        <v>1112000</v>
       </c>
       <c r="G16" s="7">
-        <v>18000</v>
+        <v>37000</v>
       </c>
       <c r="H16" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" s="7">
-        <v>49533</v>
+        <v>48750</v>
       </c>
       <c r="J16" s="5">
-        <v>77.40000000000001</v>
+        <v>78.2</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,23 +1155,23 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>99.40000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>113000</v>
+        <v>2449000</v>
       </c>
       <c r="G17" s="7">
-        <v>29000</v>
+        <v>35000</v>
       </c>
       <c r="H17" s="7">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="I17" s="7">
-        <v>18600</v>
+        <v>45652</v>
       </c>
       <c r="J17" s="5">
         <v>77.3</v>
@@ -1188,26 +1188,26 @@
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="5">
-        <v>82.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>2414000</v>
+        <v>118000</v>
       </c>
       <c r="G18" s="7">
-        <v>17000</v>
+        <v>16000</v>
       </c>
       <c r="H18" s="7">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="I18" s="7">
-        <v>45889</v>
+        <v>12125</v>
       </c>
       <c r="J18" s="5">
-        <v>76.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,23 +1221,23 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>82.5</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>764000</v>
+        <v>272000</v>
       </c>
       <c r="G19" s="7">
-        <v>35000</v>
+        <v>13000</v>
       </c>
       <c r="H19" s="7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I19" s="7">
-        <v>45556</v>
+        <v>26143</v>
       </c>
       <c r="J19" s="5">
         <v>76.8</v>
@@ -1261,19 +1261,19 @@
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>307000</v>
+        <v>404000</v>
       </c>
       <c r="G20" s="7">
-        <v>17000</v>
+        <v>14000</v>
       </c>
       <c r="H20" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I20" s="7">
-        <v>25143</v>
+        <v>23556</v>
       </c>
       <c r="J20" s="5">
-        <v>76.7</v>
+        <v>76.3</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1287,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>90.59999999999999</v>
+        <v>94.5</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>271000</v>
+        <v>460000</v>
       </c>
       <c r="G21" s="7">
-        <v>9000</v>
+        <v>27000</v>
       </c>
       <c r="H21" s="7">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I21" s="7">
-        <v>27500</v>
+        <v>16812</v>
       </c>
       <c r="J21" s="5">
-        <v>76.7</v>
+        <v>76.2</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1320,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>97.09999999999999</v>
+        <v>93</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>106000</v>
+        <v>239000</v>
       </c>
       <c r="G22" s="7">
-        <v>12000</v>
+        <v>19000</v>
       </c>
       <c r="H22" s="7">
         <v>8</v>
       </c>
       <c r="I22" s="7">
-        <v>12143</v>
+        <v>20143</v>
       </c>
       <c r="J22" s="5">
-        <v>76.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1353,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>94.8</v>
+        <v>96.7</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>188000</v>
+        <v>118000</v>
       </c>
       <c r="G23" s="7">
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="H23" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I23" s="7">
-        <v>16571</v>
+        <v>12125</v>
       </c>
       <c r="J23" s="5">
-        <v>76.3</v>
+        <v>76.2</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1386,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>92.09999999999999</v>
+        <v>82.2</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>220000</v>
+        <v>791000</v>
       </c>
       <c r="G24" s="7">
-        <v>16000</v>
+        <v>27000</v>
       </c>
       <c r="H24" s="7">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I24" s="7">
-        <v>20333</v>
+        <v>43700</v>
       </c>
       <c r="J24" s="5">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1419,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>95.5</v>
+        <v>98.7</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>102000</v>
+        <v>176000</v>
       </c>
       <c r="G25" s="7">
-        <v>11000</v>
+        <v>24000</v>
       </c>
       <c r="H25" s="7">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I25" s="7">
-        <v>11571</v>
+        <v>6812</v>
       </c>
       <c r="J25" s="5">
-        <v>75.40000000000001</v>
+        <v>76</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1459,19 +1459,19 @@
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>172000</v>
+        <v>199000</v>
       </c>
       <c r="G26" s="7">
-        <v>60000</v>
+        <v>27000</v>
       </c>
       <c r="H26" s="7">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" s="7">
-        <v>1200</v>
+        <v>2812</v>
       </c>
       <c r="J26" s="5">
-        <v>75.3</v>
+        <v>75.7</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,14 +1485,14 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>94.5</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>165000</v>
+        <v>154000</v>
       </c>
       <c r="G27" s="7">
         <v>14000</v>
@@ -1501,10 +1501,10 @@
         <v>10</v>
       </c>
       <c r="I27" s="7">
-        <v>13444</v>
+        <v>12222</v>
       </c>
       <c r="J27" s="5">
-        <v>75.3</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1516,28 +1516,30 @@
       <c r="A28" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="5"/>
+      <c r="B28" s="5">
+        <v>9.1</v>
+      </c>
       <c r="C28" s="5">
-        <v>95.09999999999999</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>140000</v>
+        <v>341000</v>
       </c>
       <c r="G28" s="7">
-        <v>13000</v>
+        <v>32000</v>
       </c>
       <c r="H28" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I28" s="7">
-        <v>12000</v>
+        <v>30500</v>
       </c>
       <c r="J28" s="5">
-        <v>75.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1551,26 +1553,26 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>97.59999999999999</v>
+        <v>89</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>152000</v>
+        <v>276000</v>
       </c>
       <c r="G29" s="7">
-        <v>26000</v>
+        <v>5000</v>
       </c>
       <c r="H29" s="7">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="I29" s="7">
-        <v>5667</v>
+        <v>24286</v>
       </c>
       <c r="J29" s="5">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="K29" s="4"/>
       <c r="L29" s="4"/>
@@ -1584,26 +1586,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>98.3</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>210000</v>
+        <v>141000</v>
       </c>
       <c r="G30" s="7">
-        <v>28000</v>
+        <v>11000</v>
       </c>
       <c r="H30" s="7">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I30" s="7">
-        <v>32000</v>
+        <v>14333</v>
       </c>
       <c r="J30" s="5">
-        <v>74.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1617,26 +1619,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>95</v>
+        <v>96.7</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>167000</v>
+        <v>216000</v>
       </c>
       <c r="G31" s="7">
-        <v>16000</v>
+        <v>35000</v>
       </c>
       <c r="H31" s="7">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="I31" s="7">
-        <v>5600</v>
+        <v>26250</v>
       </c>
       <c r="J31" s="5">
-        <v>73.7</v>
+        <v>74.7</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1650,26 +1652,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>90.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>232000</v>
+        <v>200000</v>
       </c>
       <c r="G32" s="7">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="H32" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I32" s="7">
-        <v>15000</v>
+        <v>16000</v>
       </c>
       <c r="J32" s="5">
-        <v>73.5</v>
+        <v>74.7</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1683,26 +1685,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>92.5</v>
+        <v>88.8</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>229000</v>
+        <v>316000</v>
       </c>
       <c r="G33" s="7">
-        <v>14000</v>
+        <v>9000</v>
       </c>
       <c r="H33" s="7">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I33" s="7">
-        <v>8867</v>
+        <v>23125</v>
       </c>
       <c r="J33" s="5">
-        <v>73.09999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1716,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>92.40000000000001</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>124000</v>
+        <v>227000</v>
       </c>
       <c r="G34" s="7">
-        <v>8000</v>
+        <v>46000</v>
       </c>
       <c r="H34" s="7">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I34" s="7">
-        <v>8538</v>
+        <v>500</v>
       </c>
       <c r="J34" s="5">
-        <v>73</v>
+        <v>74.2</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1749,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>92.40000000000001</v>
+        <v>98.2</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>100000</v>
+        <v>198000</v>
       </c>
       <c r="G35" s="7">
-        <v>9000</v>
+        <v>22000</v>
       </c>
       <c r="H35" s="7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I35" s="7">
-        <v>7455</v>
+        <v>812</v>
       </c>
       <c r="J35" s="5">
-        <v>72.7</v>
+        <v>74.2</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1782,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>92.2</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>130000</v>
+        <v>387000</v>
       </c>
       <c r="G36" s="7">
-        <v>10000</v>
+        <v>34000</v>
       </c>
       <c r="H36" s="7">
         <v>6</v>
       </c>
       <c r="I36" s="7">
-        <v>15000</v>
+        <v>34400</v>
       </c>
       <c r="J36" s="5">
-        <v>72.5</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1815,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>95.59999999999999</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>135000</v>
+        <v>133000</v>
       </c>
       <c r="G37" s="7">
         <v>14000</v>
       </c>
       <c r="H37" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I37" s="7">
-        <v>19000</v>
+        <v>4889</v>
       </c>
       <c r="J37" s="5">
-        <v>72.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1848,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>90.3</v>
+        <v>92.3</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>162000</v>
+        <v>146000</v>
       </c>
       <c r="G38" s="7">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="H38" s="7">
         <v>6</v>
       </c>
       <c r="I38" s="7">
-        <v>18200</v>
+        <v>17400</v>
       </c>
       <c r="J38" s="5">
-        <v>72.2</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1881,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>81.3</v>
+        <v>87.8</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>410000</v>
+        <v>239000</v>
       </c>
       <c r="G39" s="7">
-        <v>16000</v>
+        <v>6000</v>
       </c>
       <c r="H39" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I39" s="7">
-        <v>29286</v>
+        <v>18667</v>
       </c>
       <c r="J39" s="5">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1914,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>91.2</v>
+        <v>88.7</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>109000</v>
+        <v>305000</v>
       </c>
       <c r="G40" s="7">
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="H40" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I40" s="7">
-        <v>7455</v>
+        <v>16111</v>
       </c>
       <c r="J40" s="5">
-        <v>72</v>
+        <v>72.8</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1947,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>80.59999999999999</v>
+        <v>79</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>487000</v>
+        <v>531000</v>
       </c>
       <c r="G41" s="7">
-        <v>14000</v>
+        <v>19000</v>
       </c>
       <c r="H41" s="7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I41" s="7">
-        <v>30083</v>
+        <v>36000</v>
       </c>
       <c r="J41" s="5">
-        <v>71.90000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1980,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>87.3</v>
+        <v>92.3</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>271000</v>
+        <v>190000</v>
       </c>
       <c r="G42" s="7">
-        <v>9000</v>
+        <v>20000</v>
       </c>
       <c r="H42" s="7">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I42" s="7">
-        <v>15500</v>
+        <v>14600</v>
       </c>
       <c r="J42" s="5">
-        <v>71.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2013,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>92.40000000000001</v>
+        <v>86.7</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>119000</v>
+        <v>318000</v>
       </c>
       <c r="G43" s="7">
-        <v>12000</v>
+        <v>68000</v>
       </c>
       <c r="H43" s="7">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I43" s="7">
-        <v>3750</v>
+        <v>62000</v>
       </c>
       <c r="J43" s="5">
-        <v>71.8</v>
+        <v>72.2</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2046,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>87.90000000000001</v>
+        <v>81.7</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>233000</v>
+        <v>428000</v>
       </c>
       <c r="G44" s="7">
-        <v>8000</v>
+        <v>18000</v>
       </c>
       <c r="H44" s="7">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I44" s="7">
-        <v>21200</v>
+        <v>27875</v>
       </c>
       <c r="J44" s="5">
-        <v>71.59999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2079,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>90.3</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>133000</v>
+        <v>131000</v>
       </c>
       <c r="G45" s="7">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="H45" s="7">
         <v>15</v>
       </c>
       <c r="I45" s="7">
-        <v>7786</v>
+        <v>8429</v>
       </c>
       <c r="J45" s="5">
-        <v>71.59999999999999</v>
+        <v>71.8</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2112,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>87.40000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>242000</v>
+        <v>116000</v>
       </c>
       <c r="G46" s="7">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="H46" s="7">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I46" s="7">
-        <v>13182</v>
+        <v>7417</v>
       </c>
       <c r="J46" s="5">
-        <v>71.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2143,30 +2145,28 @@
       <c r="A47" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B47" s="5">
-        <v>9.1</v>
-      </c>
+      <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>83</v>
+        <v>80.5</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>309000</v>
+        <v>497000</v>
       </c>
       <c r="G47" s="7">
-        <v>23000</v>
+        <v>10000</v>
       </c>
       <c r="H47" s="7">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I47" s="7">
-        <v>30200</v>
+        <v>28538</v>
       </c>
       <c r="J47" s="5">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>93.2</v>
+        <v>87.8</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>200000</v>
+        <v>248000</v>
       </c>
       <c r="G48" s="7">
-        <v>21000</v>
+        <v>6000</v>
       </c>
       <c r="H48" s="7">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I48" s="7">
-        <v>31667</v>
+        <v>12583</v>
       </c>
       <c r="J48" s="5">
-        <v>71.2</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>87.7</v>
+        <v>89.7</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>138000</v>
+        <v>225000</v>
       </c>
       <c r="G49" s="7">
-        <v>7000</v>
+        <v>15000</v>
       </c>
       <c r="H49" s="7">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I49" s="7">
-        <v>11429</v>
+        <v>27750</v>
       </c>
       <c r="J49" s="5">
-        <v>71.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>90.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>114000</v>
+        <v>177000</v>
       </c>
       <c r="G50" s="7">
-        <v>11000</v>
+        <v>10000</v>
       </c>
       <c r="H50" s="7">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I50" s="7">
-        <v>6286</v>
+        <v>5875</v>
       </c>
       <c r="J50" s="5">
-        <v>71.09999999999999</v>
+        <v>71.3</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>78.5</v>
+        <v>89.5</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>512000</v>
+        <v>493000</v>
       </c>
       <c r="G51" s="7">
-        <v>28000</v>
+        <v>5000</v>
       </c>
       <c r="H51" s="7">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I51" s="7">
-        <v>39400</v>
+        <v>7938</v>
       </c>
       <c r="J51" s="5">
-        <v>71</v>
+        <v>71.2</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>85.2</v>
+        <v>86.5</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>294000</v>
+        <v>278000</v>
       </c>
       <c r="G52" s="7">
-        <v>1000</v>
+        <v>7000</v>
       </c>
       <c r="H52" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I52" s="7">
-        <v>16750</v>
+        <v>14556</v>
       </c>
       <c r="J52" s="5">
-        <v>71</v>
+        <v>71.2</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>91.2</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>100000</v>
+        <v>233000</v>
       </c>
       <c r="G53" s="7">
-        <v>8000</v>
+        <v>1000</v>
       </c>
       <c r="H53" s="7">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="I53" s="7">
-        <v>2467</v>
+        <v>13727</v>
       </c>
       <c r="J53" s="5">
-        <v>70.8</v>
+        <v>71</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>87.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>152000</v>
+        <v>235000</v>
       </c>
       <c r="G54" s="7">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="H54" s="7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I54" s="7">
-        <v>8857</v>
+        <v>8688</v>
       </c>
       <c r="J54" s="5">
-        <v>70.59999999999999</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>

--- a/data/持续收益潜力作品.xlsx
+++ b/data/持续收益潜力作品.xlsx
@@ -22,7 +22,7 @@
     <t>持续收益潜力作品</t>
   </si>
   <si>
-    <t>生成时间：2026-10-30T05:27:10+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
+    <t>生成时间：2026-10-31T05:11:30+00:00。候选名单仅依据公开榜单的连续出现、在读规模和在读变化筛选，不代表真实稿费、订阅收入或平台结算。</t>
   </si>
   <si>
     <t>作品名</t>
@@ -76,148 +76,148 @@
     <t>打开作品</t>
   </si>
   <si>
+    <t>恐怖游戏：开局皮嫁骨吓哭全球！</t>
+  </si>
+  <si>
+    <t>全民领主：抽到人族，但来自战锤</t>
+  </si>
+  <si>
+    <t>撞见黑白无常后，我成了走阴人</t>
+  </si>
+  <si>
     <t>我叫九江，李景隆那个九江！</t>
   </si>
   <si>
-    <t>恐怖游戏：开局皮嫁骨吓哭全球！</t>
-  </si>
-  <si>
-    <t>全民领主：抽到人族，但来自战锤</t>
-  </si>
-  <si>
-    <t>撞见黑白无常后，我成了走阴人</t>
-  </si>
-  <si>
     <t>改变历史就变强：开局对掏汉武帝</t>
   </si>
   <si>
+    <t>我都化龙了，你说功法是假的？</t>
+  </si>
+  <si>
     <t>努力就变强的我，被重生者曝光了</t>
   </si>
   <si>
+    <t>弹幕说，我未婚妻要嫁给她助理！</t>
+  </si>
+  <si>
     <t>穿书女频，被病娇姐妹缠上了</t>
   </si>
   <si>
+    <t>神雕杨过：我以九阴九阳压天下！</t>
+  </si>
+  <si>
+    <t>我在儒道世界以诗词文章成圣人</t>
+  </si>
+  <si>
+    <t>骇夜：我在恐怖游戏里暴富</t>
+  </si>
+  <si>
+    <t>大明：我真不是万寿帝君</t>
+  </si>
+  <si>
+    <t>我都觉醒神明序列了系统才来？</t>
+  </si>
+  <si>
+    <t>崩铁：迫害完她们后，我有点死了</t>
+  </si>
+  <si>
+    <t>洪荒：神话祖巫，一念生灭万界</t>
+  </si>
+  <si>
+    <t>绝症留洋归乡？举国哭求我别死！</t>
+  </si>
+  <si>
+    <t>入学第一天：我娶了丰腴美人教授</t>
+  </si>
+  <si>
+    <t>海贼：门门果实？可曾听闻次元斩</t>
+  </si>
+  <si>
+    <t>修仙，每天十倍收益结算</t>
+  </si>
+  <si>
+    <t>骗子闯入娱乐圈</t>
+  </si>
+  <si>
     <t>洪荒：开局带着白莲绿茶拜师三清</t>
   </si>
   <si>
-    <t>我都化龙了，你说功法是假的？</t>
-  </si>
-  <si>
-    <t>我都觉醒神明序列了系统才来？</t>
-  </si>
-  <si>
-    <t>神雕杨过：我以九阴九阳压天下！</t>
-  </si>
-  <si>
-    <t>骇夜：我在恐怖游戏里暴富</t>
+    <t>海洋求生？可我是人鱼公主！</t>
+  </si>
+  <si>
+    <t>老师，我的异能是能带出游戏道具</t>
+  </si>
+  <si>
+    <t>霍格沃茨：马尔福竟是傲娇千金？</t>
+  </si>
+  <si>
+    <t>我在诸天当超能力爷</t>
+  </si>
+  <si>
+    <t>穿越灾年有系统，我张大棒无敌了</t>
+  </si>
+  <si>
+    <t>天幕：千古第一才女的现代生活</t>
+  </si>
+  <si>
+    <t>让你制作奢侈品，你做龙泉印泥？</t>
+  </si>
+  <si>
+    <t>四合院：我金发碧眼，说是自己人</t>
+  </si>
+  <si>
+    <t>四合院：开局1948年教训禽兽</t>
+  </si>
+  <si>
+    <t>四合院：大军进城，我系统吓跑了</t>
+  </si>
+  <si>
+    <t>高冷？外冷内齁！你们请攻略我吧</t>
+  </si>
+  <si>
+    <t>红龙暴君：刚破壳，先把龙妹弄哭</t>
+  </si>
+  <si>
+    <t>狂病：从获得黑色守望开始</t>
+  </si>
+  <si>
+    <t>四合院：从红二十五开始进步</t>
+  </si>
+  <si>
+    <t>饰演封于修，女友神仙姐姐</t>
+  </si>
+  <si>
+    <t>末世死考：开局天使魅魔三选一</t>
+  </si>
+  <si>
+    <t>男人野性：纵享绝美贵妇偏爱</t>
+  </si>
+  <si>
+    <t>正光加代那些事</t>
+  </si>
+  <si>
+    <t>综漫：你管这叫日常世界？</t>
+  </si>
+  <si>
+    <t>抗战：天道酬勤，从士兵开始崛起</t>
   </si>
   <si>
     <t>完美犯罪？我只是在清理城市垃圾</t>
   </si>
   <si>
-    <t>海贼：门门果实？可曾听闻次元斩</t>
-  </si>
-  <si>
-    <t>穿成警察，满城霸总排队来送业绩</t>
-  </si>
-  <si>
-    <t>我在诸天当超能力爷</t>
-  </si>
-  <si>
-    <t>崩铁：迫害完她们后，我有点死了</t>
-  </si>
-  <si>
-    <t>红龙暴君：刚破壳，先把龙妹弄哭</t>
-  </si>
-  <si>
-    <t>饰演封于修，女友神仙姐姐</t>
-  </si>
-  <si>
-    <t>正光加代那些事</t>
-  </si>
-  <si>
-    <t>大明：开局政变，请洪武赴死！</t>
-  </si>
-  <si>
-    <t>天幕：千古第一才女的现代生活</t>
-  </si>
-  <si>
-    <t>大明：我真不是万寿帝君</t>
-  </si>
-  <si>
-    <t>全班同学穿越，我开局拜菩提祖师</t>
-  </si>
-  <si>
-    <t>洪荒：神话祖巫，一念生灭万界</t>
-  </si>
-  <si>
-    <t>弹幕说，我未婚妻要嫁给她助理！</t>
-  </si>
-  <si>
-    <t>海洋求生？可我是人鱼公主！</t>
-  </si>
-  <si>
-    <t>霍格沃茨：马尔福竟是傲娇千金？</t>
-  </si>
-  <si>
-    <t>绝症留洋归乡？举国哭求我别死！</t>
+    <t>海吞天</t>
+  </si>
+  <si>
+    <t>举报我？你家被我抄了</t>
+  </si>
+  <si>
+    <t>天幕通原神，开局钟离还在藏</t>
+  </si>
+  <si>
+    <t>废土黑作坊：从造一级弹开始</t>
   </si>
   <si>
     <t>儒道剑仙，苟在镇北王府当赘婿</t>
-  </si>
-  <si>
-    <t>四合院：开局1948年教训禽兽</t>
-  </si>
-  <si>
-    <t>狗管，还说你不会武功</t>
-  </si>
-  <si>
-    <t>老师，我的异能是能带出游戏道具</t>
-  </si>
-  <si>
-    <t>入学第一天：我娶了丰腴美人教授</t>
-  </si>
-  <si>
-    <t>四合院：大军进城，我系统吓跑了</t>
-  </si>
-  <si>
-    <t>骗子闯入娱乐圈</t>
-  </si>
-  <si>
-    <t>四合院：我金发碧眼，说是自己人</t>
-  </si>
-  <si>
-    <t>我在儒道世界以诗词文章成圣人</t>
-  </si>
-  <si>
-    <t>四合院：从红二十五开始进步</t>
-  </si>
-  <si>
-    <t>破案：我能闻到凶手的味道</t>
-  </si>
-  <si>
-    <t>抗战：天道酬勤，从士兵开始崛起</t>
-  </si>
-  <si>
-    <t>火影：九尾之夜，雷光万劫</t>
-  </si>
-  <si>
-    <t>天幕通原神，开局钟离还在藏</t>
-  </si>
-  <si>
-    <t>让你制作奢侈品，你做龙泉印泥？</t>
-  </si>
-  <si>
-    <t>海吞天</t>
-  </si>
-  <si>
-    <t>废土黑作坊：从造一级弹开始</t>
-  </si>
-  <si>
-    <t>美漫，从黑暗奇异博士开始</t>
-  </si>
-  <si>
-    <t>高冷？外冷内齁！你们请攻略我吧</t>
   </si>
   <si>
     <t>红色人生模拟，我怎么成老干部了</t>
@@ -759,26 +759,26 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="5">
-        <v>87.8</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7">
-        <v>726000</v>
+        <v>787000</v>
       </c>
       <c r="G5" s="7">
-        <v>57000</v>
+        <v>61000</v>
       </c>
       <c r="H5" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="7">
-        <v>77143</v>
+        <v>75125</v>
       </c>
       <c r="J5" s="5">
-        <v>87.59999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
@@ -792,26 +792,26 @@
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5">
-        <v>92.40000000000001</v>
+        <v>100</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F6" s="7">
-        <v>655000</v>
+        <v>276000</v>
       </c>
       <c r="G6" s="7">
-        <v>87000</v>
+        <v>45000</v>
       </c>
       <c r="H6" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="I6" s="7">
-        <v>56000</v>
+        <v>31000</v>
       </c>
       <c r="J6" s="5">
-        <v>84.8</v>
+        <v>82.8</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
@@ -832,19 +832,19 @@
         <v>18</v>
       </c>
       <c r="F7" s="7">
-        <v>231000</v>
+        <v>338000</v>
       </c>
       <c r="G7" s="7">
-        <v>39000</v>
+        <v>44000</v>
       </c>
       <c r="H7" s="7">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I7" s="7">
-        <v>29000</v>
+        <v>30222</v>
       </c>
       <c r="J7" s="5">
-        <v>82.2</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
@@ -865,19 +865,19 @@
         <v>18</v>
       </c>
       <c r="F8" s="7">
-        <v>294000</v>
+        <v>213000</v>
       </c>
       <c r="G8" s="7">
-        <v>37000</v>
+        <v>42000</v>
       </c>
       <c r="H8" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7">
-        <v>28500</v>
+        <v>27571</v>
       </c>
       <c r="J8" s="5">
-        <v>82.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
@@ -891,26 +891,26 @@
       </c>
       <c r="B9" s="5"/>
       <c r="C9" s="5">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F9" s="7">
-        <v>171000</v>
+        <v>711000</v>
       </c>
       <c r="G9" s="7">
-        <v>58000</v>
+        <v>56000</v>
       </c>
       <c r="H9" s="7">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I9" s="7">
-        <v>25167</v>
+        <v>56000</v>
       </c>
       <c r="J9" s="5">
-        <v>81.3</v>
+        <v>81.8</v>
       </c>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
@@ -924,26 +924,26 @@
       </c>
       <c r="B10" s="5"/>
       <c r="C10" s="5">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F10" s="7">
-        <v>205000</v>
+        <v>230000</v>
       </c>
       <c r="G10" s="7">
-        <v>31000</v>
+        <v>25000</v>
       </c>
       <c r="H10" s="7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I10" s="7">
-        <v>52333</v>
+        <v>45500</v>
       </c>
       <c r="J10" s="5">
-        <v>80.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
@@ -957,26 +957,26 @@
       </c>
       <c r="B11" s="5"/>
       <c r="C11" s="5">
-        <v>81.09999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F11" s="7">
-        <v>709000</v>
+        <v>319000</v>
       </c>
       <c r="G11" s="7">
-        <v>40000</v>
+        <v>23000</v>
       </c>
       <c r="H11" s="7">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I11" s="7">
-        <v>61167</v>
+        <v>27727</v>
       </c>
       <c r="J11" s="5">
-        <v>79.90000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
@@ -990,26 +990,26 @@
       </c>
       <c r="B12" s="5"/>
       <c r="C12" s="5">
-        <v>99.90000000000001</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F12" s="7">
-        <v>204000</v>
+        <v>746000</v>
       </c>
       <c r="G12" s="7">
-        <v>36000</v>
+        <v>37000</v>
       </c>
       <c r="H12" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I12" s="7">
-        <v>18750</v>
+        <v>57714</v>
       </c>
       <c r="J12" s="5">
-        <v>79.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
@@ -1023,26 +1023,26 @@
       </c>
       <c r="B13" s="5"/>
       <c r="C13" s="5">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F13" s="7">
-        <v>201000</v>
+        <v>245000</v>
       </c>
       <c r="G13" s="7">
-        <v>36000</v>
+        <v>29000</v>
       </c>
       <c r="H13" s="7">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="I13" s="7">
-        <v>15700</v>
+        <v>26800</v>
       </c>
       <c r="J13" s="5">
-        <v>78.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
@@ -1056,26 +1056,26 @@
       </c>
       <c r="B14" s="5"/>
       <c r="C14" s="5">
-        <v>93.09999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F14" s="7">
-        <v>296000</v>
+        <v>228000</v>
       </c>
       <c r="G14" s="7">
-        <v>16000</v>
+        <v>24000</v>
       </c>
       <c r="H14" s="7">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="I14" s="7">
-        <v>28200</v>
+        <v>19333</v>
       </c>
       <c r="J14" s="5">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
@@ -1089,26 +1089,26 @@
       </c>
       <c r="B15" s="5"/>
       <c r="C15" s="5">
-        <v>97.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F15" s="7">
-        <v>183000</v>
+        <v>1139000</v>
       </c>
       <c r="G15" s="7">
-        <v>21000</v>
+        <v>27000</v>
       </c>
       <c r="H15" s="7">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I15" s="7">
-        <v>18667</v>
+        <v>47471</v>
       </c>
       <c r="J15" s="5">
-        <v>78.3</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
@@ -1122,26 +1122,26 @@
       </c>
       <c r="B16" s="5"/>
       <c r="C16" s="5">
-        <v>83.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F16" s="7">
-        <v>1112000</v>
+        <v>376000</v>
       </c>
       <c r="G16" s="7">
-        <v>37000</v>
+        <v>58000</v>
       </c>
       <c r="H16" s="7">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="I16" s="7">
-        <v>48750</v>
+        <v>60667</v>
       </c>
       <c r="J16" s="5">
-        <v>78.2</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
@@ -1155,26 +1155,26 @@
       </c>
       <c r="B17" s="5"/>
       <c r="C17" s="5">
-        <v>83.40000000000001</v>
+        <v>82.8</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F17" s="7">
-        <v>2449000</v>
+        <v>2469000</v>
       </c>
       <c r="G17" s="7">
-        <v>35000</v>
+        <v>20000</v>
       </c>
       <c r="H17" s="7">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I17" s="7">
-        <v>45652</v>
+        <v>45106</v>
       </c>
       <c r="J17" s="5">
-        <v>77.3</v>
+        <v>76.8</v>
       </c>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
@@ -1186,28 +1186,30 @@
       <c r="A18" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="5"/>
+      <c r="B18" s="5">
+        <v>9.1</v>
+      </c>
       <c r="C18" s="5">
-        <v>98.7</v>
+        <v>88.5</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F18" s="7">
-        <v>118000</v>
+        <v>380000</v>
       </c>
       <c r="G18" s="7">
-        <v>16000</v>
+        <v>39000</v>
       </c>
       <c r="H18" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I18" s="7">
-        <v>12125</v>
+        <v>31714</v>
       </c>
       <c r="J18" s="5">
-        <v>77.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
@@ -1221,26 +1223,26 @@
       </c>
       <c r="B19" s="5"/>
       <c r="C19" s="5">
-        <v>91.40000000000001</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F19" s="7">
-        <v>272000</v>
+        <v>200000</v>
       </c>
       <c r="G19" s="7">
-        <v>13000</v>
+        <v>17000</v>
       </c>
       <c r="H19" s="7">
         <v>8</v>
       </c>
       <c r="I19" s="7">
-        <v>26143</v>
+        <v>18429</v>
       </c>
       <c r="J19" s="5">
-        <v>76.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="4"/>
@@ -1254,26 +1256,26 @@
       </c>
       <c r="B20" s="5"/>
       <c r="C20" s="5">
-        <v>91.59999999999999</v>
+        <v>92.5</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F20" s="7">
-        <v>404000</v>
+        <v>256000</v>
       </c>
       <c r="G20" s="7">
-        <v>14000</v>
+        <v>17000</v>
       </c>
       <c r="H20" s="7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I20" s="7">
-        <v>23556</v>
+        <v>19750</v>
       </c>
       <c r="J20" s="5">
-        <v>76.3</v>
+        <v>75.8</v>
       </c>
       <c r="K20" s="4"/>
       <c r="L20" s="4"/>
@@ -1287,26 +1289,26 @@
       </c>
       <c r="B21" s="5"/>
       <c r="C21" s="5">
-        <v>94.5</v>
+        <v>95</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F21" s="7">
-        <v>460000</v>
+        <v>155000</v>
       </c>
       <c r="G21" s="7">
-        <v>27000</v>
+        <v>14000</v>
       </c>
       <c r="H21" s="7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I21" s="7">
-        <v>16812</v>
+        <v>14286</v>
       </c>
       <c r="J21" s="5">
-        <v>76.2</v>
+        <v>75.8</v>
       </c>
       <c r="K21" s="4"/>
       <c r="L21" s="4"/>
@@ -1320,26 +1322,26 @@
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F22" s="7">
-        <v>239000</v>
+        <v>259000</v>
       </c>
       <c r="G22" s="7">
-        <v>19000</v>
+        <v>32000</v>
       </c>
       <c r="H22" s="7">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I22" s="7">
-        <v>20143</v>
+        <v>2353</v>
       </c>
       <c r="J22" s="5">
-        <v>76.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K22" s="4"/>
       <c r="L22" s="4"/>
@@ -1353,26 +1355,26 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5">
-        <v>96.7</v>
+        <v>92.5</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F23" s="7">
-        <v>118000</v>
+        <v>256000</v>
       </c>
       <c r="G23" s="7">
-        <v>12000</v>
+        <v>17000</v>
       </c>
       <c r="H23" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I23" s="7">
-        <v>12125</v>
+        <v>18429</v>
       </c>
       <c r="J23" s="5">
-        <v>76.2</v>
+        <v>75.5</v>
       </c>
       <c r="K23" s="4"/>
       <c r="L23" s="4"/>
@@ -1386,26 +1388,26 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5">
-        <v>82.2</v>
+        <v>89.8</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F24" s="7">
-        <v>791000</v>
+        <v>279000</v>
       </c>
       <c r="G24" s="7">
-        <v>27000</v>
+        <v>7000</v>
       </c>
       <c r="H24" s="7">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="I24" s="7">
-        <v>43700</v>
+        <v>23750</v>
       </c>
       <c r="J24" s="5">
-        <v>76.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="K24" s="4"/>
       <c r="L24" s="4"/>
@@ -1419,26 +1421,26 @@
       </c>
       <c r="B25" s="5"/>
       <c r="C25" s="5">
-        <v>98.7</v>
+        <v>100</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F25" s="7">
-        <v>176000</v>
+        <v>154000</v>
       </c>
       <c r="G25" s="7">
-        <v>24000</v>
+        <v>35000</v>
       </c>
       <c r="H25" s="7">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="I25" s="7">
-        <v>6812</v>
+        <v>21250</v>
       </c>
       <c r="J25" s="5">
-        <v>76</v>
+        <v>75.3</v>
       </c>
       <c r="K25" s="4"/>
       <c r="L25" s="4"/>
@@ -1452,26 +1454,26 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5">
-        <v>100</v>
+        <v>83.8</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F26" s="7">
-        <v>199000</v>
+        <v>571000</v>
       </c>
       <c r="G26" s="7">
-        <v>27000</v>
+        <v>40000</v>
       </c>
       <c r="H26" s="7">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I26" s="7">
-        <v>2812</v>
+        <v>36571</v>
       </c>
       <c r="J26" s="5">
-        <v>75.7</v>
+        <v>75.2</v>
       </c>
       <c r="K26" s="4"/>
       <c r="L26" s="4"/>
@@ -1485,26 +1487,26 @@
       </c>
       <c r="B27" s="5"/>
       <c r="C27" s="5">
-        <v>95.09999999999999</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F27" s="7">
-        <v>154000</v>
+        <v>214000</v>
       </c>
       <c r="G27" s="7">
-        <v>14000</v>
+        <v>13000</v>
       </c>
       <c r="H27" s="7">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I27" s="7">
-        <v>12222</v>
+        <v>15455</v>
       </c>
       <c r="J27" s="5">
-        <v>75.40000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K27" s="4"/>
       <c r="L27" s="4"/>
@@ -1516,30 +1518,28 @@
       <c r="A28" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="5">
-        <v>9.1</v>
-      </c>
+      <c r="B28" s="5"/>
       <c r="C28" s="5">
-        <v>86.40000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F28" s="7">
-        <v>341000</v>
+        <v>214000</v>
       </c>
       <c r="G28" s="7">
-        <v>32000</v>
+        <v>14000</v>
       </c>
       <c r="H28" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I28" s="7">
-        <v>30500</v>
+        <v>15778</v>
       </c>
       <c r="J28" s="5">
-        <v>75.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="K28" s="4"/>
       <c r="L28" s="4"/>
@@ -1553,23 +1553,23 @@
       </c>
       <c r="B29" s="5"/>
       <c r="C29" s="5">
-        <v>89</v>
+        <v>92.5</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F29" s="7">
-        <v>276000</v>
+        <v>158000</v>
       </c>
       <c r="G29" s="7">
-        <v>5000</v>
+        <v>12000</v>
       </c>
       <c r="H29" s="7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I29" s="7">
-        <v>24286</v>
+        <v>16500</v>
       </c>
       <c r="J29" s="5">
         <v>75</v>
@@ -1586,26 +1586,26 @@
       </c>
       <c r="B30" s="5"/>
       <c r="C30" s="5">
-        <v>93.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F30" s="7">
-        <v>141000</v>
+        <v>322000</v>
       </c>
       <c r="G30" s="7">
-        <v>11000</v>
+        <v>6000</v>
       </c>
       <c r="H30" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I30" s="7">
-        <v>14333</v>
+        <v>21222</v>
       </c>
       <c r="J30" s="5">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="K30" s="4"/>
       <c r="L30" s="4"/>
@@ -1619,26 +1619,26 @@
       </c>
       <c r="B31" s="5"/>
       <c r="C31" s="5">
-        <v>96.7</v>
+        <v>90.5</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F31" s="7">
-        <v>216000</v>
+        <v>470000</v>
       </c>
       <c r="G31" s="7">
-        <v>35000</v>
+        <v>10000</v>
       </c>
       <c r="H31" s="7">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I31" s="7">
-        <v>26250</v>
+        <v>16412</v>
       </c>
       <c r="J31" s="5">
-        <v>74.7</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K31" s="4"/>
       <c r="L31" s="4"/>
@@ -1652,26 +1652,26 @@
       </c>
       <c r="B32" s="5"/>
       <c r="C32" s="5">
-        <v>92.09999999999999</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F32" s="7">
-        <v>200000</v>
+        <v>284000</v>
       </c>
       <c r="G32" s="7">
-        <v>12000</v>
+        <v>69000</v>
       </c>
       <c r="H32" s="7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I32" s="7">
-        <v>16000</v>
+        <v>18429</v>
       </c>
       <c r="J32" s="5">
-        <v>74.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K32" s="4"/>
       <c r="L32" s="4"/>
@@ -1685,26 +1685,26 @@
       </c>
       <c r="B33" s="5"/>
       <c r="C33" s="5">
-        <v>88.8</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F33" s="7">
-        <v>316000</v>
+        <v>163000</v>
       </c>
       <c r="G33" s="7">
         <v>9000</v>
       </c>
       <c r="H33" s="7">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I33" s="7">
-        <v>23125</v>
+        <v>11900</v>
       </c>
       <c r="J33" s="5">
-        <v>74.59999999999999</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="K33" s="4"/>
       <c r="L33" s="4"/>
@@ -1718,26 +1718,26 @@
       </c>
       <c r="B34" s="5"/>
       <c r="C34" s="5">
-        <v>98.40000000000001</v>
+        <v>88</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F34" s="7">
-        <v>227000</v>
+        <v>235000</v>
       </c>
       <c r="G34" s="7">
-        <v>46000</v>
+        <v>10000</v>
       </c>
       <c r="H34" s="7">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="I34" s="7">
-        <v>500</v>
+        <v>24200</v>
       </c>
       <c r="J34" s="5">
-        <v>74.2</v>
+        <v>72.5</v>
       </c>
       <c r="K34" s="4"/>
       <c r="L34" s="4"/>
@@ -1751,26 +1751,26 @@
       </c>
       <c r="B35" s="5"/>
       <c r="C35" s="5">
-        <v>98.2</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F35" s="7">
-        <v>198000</v>
+        <v>204000</v>
       </c>
       <c r="G35" s="7">
-        <v>22000</v>
+        <v>14000</v>
       </c>
       <c r="H35" s="7">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I35" s="7">
-        <v>812</v>
+        <v>14500</v>
       </c>
       <c r="J35" s="5">
-        <v>74.2</v>
+        <v>72.5</v>
       </c>
       <c r="K35" s="4"/>
       <c r="L35" s="4"/>
@@ -1784,26 +1784,26 @@
       </c>
       <c r="B36" s="5"/>
       <c r="C36" s="5">
-        <v>85.09999999999999</v>
+        <v>80.8</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F36" s="7">
-        <v>387000</v>
+        <v>404000</v>
       </c>
       <c r="G36" s="7">
-        <v>34000</v>
+        <v>17000</v>
       </c>
       <c r="H36" s="7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I36" s="7">
-        <v>34400</v>
+        <v>31500</v>
       </c>
       <c r="J36" s="5">
-        <v>73.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="K36" s="4"/>
       <c r="L36" s="4"/>
@@ -1817,26 +1817,26 @@
       </c>
       <c r="B37" s="5"/>
       <c r="C37" s="5">
-        <v>94.90000000000001</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F37" s="7">
-        <v>133000</v>
+        <v>312000</v>
       </c>
       <c r="G37" s="7">
-        <v>14000</v>
+        <v>7000</v>
       </c>
       <c r="H37" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I37" s="7">
-        <v>4889</v>
+        <v>15200</v>
       </c>
       <c r="J37" s="5">
-        <v>73.40000000000001</v>
+        <v>72.3</v>
       </c>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
@@ -1850,26 +1850,26 @@
       </c>
       <c r="B38" s="5"/>
       <c r="C38" s="5">
-        <v>92.3</v>
+        <v>89</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F38" s="7">
-        <v>146000</v>
+        <v>238000</v>
       </c>
       <c r="G38" s="7">
-        <v>11000</v>
+        <v>5000</v>
       </c>
       <c r="H38" s="7">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I38" s="7">
-        <v>17400</v>
+        <v>13000</v>
       </c>
       <c r="J38" s="5">
-        <v>73.09999999999999</v>
+        <v>72.2</v>
       </c>
       <c r="K38" s="4"/>
       <c r="L38" s="4"/>
@@ -1883,26 +1883,26 @@
       </c>
       <c r="B39" s="5"/>
       <c r="C39" s="5">
-        <v>87.8</v>
+        <v>89.7</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F39" s="7">
-        <v>239000</v>
+        <v>123000</v>
       </c>
       <c r="G39" s="7">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="H39" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I39" s="7">
-        <v>18667</v>
+        <v>11333</v>
       </c>
       <c r="J39" s="5">
-        <v>73</v>
+        <v>72.2</v>
       </c>
       <c r="K39" s="4"/>
       <c r="L39" s="4"/>
@@ -1916,26 +1916,26 @@
       </c>
       <c r="B40" s="5"/>
       <c r="C40" s="5">
-        <v>88.7</v>
+        <v>95.09999999999999</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F40" s="7">
-        <v>305000</v>
+        <v>107000</v>
       </c>
       <c r="G40" s="7">
-        <v>11000</v>
+        <v>14000</v>
       </c>
       <c r="H40" s="7">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I40" s="7">
-        <v>16111</v>
+        <v>7600</v>
       </c>
       <c r="J40" s="5">
-        <v>72.8</v>
+        <v>72.2</v>
       </c>
       <c r="K40" s="4"/>
       <c r="L40" s="4"/>
@@ -1949,26 +1949,26 @@
       </c>
       <c r="B41" s="5"/>
       <c r="C41" s="5">
-        <v>79</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F41" s="7">
-        <v>531000</v>
+        <v>448000</v>
       </c>
       <c r="G41" s="7">
-        <v>19000</v>
+        <v>20000</v>
       </c>
       <c r="H41" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I41" s="7">
-        <v>36000</v>
+        <v>27000</v>
       </c>
       <c r="J41" s="5">
-        <v>72.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K41" s="4"/>
       <c r="L41" s="4"/>
@@ -1982,26 +1982,26 @@
       </c>
       <c r="B42" s="5"/>
       <c r="C42" s="5">
-        <v>92.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F42" s="7">
-        <v>190000</v>
+        <v>775000</v>
       </c>
       <c r="G42" s="7">
-        <v>20000</v>
+        <v>-16000</v>
       </c>
       <c r="H42" s="7">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="I42" s="7">
-        <v>14600</v>
+        <v>38273</v>
       </c>
       <c r="J42" s="5">
-        <v>72.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="K42" s="4"/>
       <c r="L42" s="4"/>
@@ -2015,26 +2015,26 @@
       </c>
       <c r="B43" s="5"/>
       <c r="C43" s="5">
-        <v>86.7</v>
+        <v>88.7</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F43" s="7">
-        <v>318000</v>
+        <v>383000</v>
       </c>
       <c r="G43" s="7">
-        <v>68000</v>
+        <v>72000</v>
       </c>
       <c r="H43" s="7">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I43" s="7">
-        <v>62000</v>
+        <v>10964</v>
       </c>
       <c r="J43" s="5">
-        <v>72.2</v>
+        <v>71.5</v>
       </c>
       <c r="K43" s="4"/>
       <c r="L43" s="4"/>
@@ -2048,26 +2048,26 @@
       </c>
       <c r="B44" s="5"/>
       <c r="C44" s="5">
-        <v>81.7</v>
+        <v>93</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F44" s="7">
-        <v>428000</v>
+        <v>137000</v>
       </c>
       <c r="G44" s="7">
-        <v>18000</v>
+        <v>15000</v>
       </c>
       <c r="H44" s="7">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I44" s="7">
-        <v>27875</v>
+        <v>21000</v>
       </c>
       <c r="J44" s="5">
-        <v>71.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="K44" s="4"/>
       <c r="L44" s="4"/>
@@ -2081,26 +2081,26 @@
       </c>
       <c r="B45" s="5"/>
       <c r="C45" s="5">
-        <v>90.40000000000001</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F45" s="7">
-        <v>131000</v>
+        <v>187000</v>
       </c>
       <c r="G45" s="7">
-        <v>7000</v>
+        <v>11000</v>
       </c>
       <c r="H45" s="7">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I45" s="7">
-        <v>8429</v>
+        <v>7059</v>
       </c>
       <c r="J45" s="5">
-        <v>71.8</v>
+        <v>71.3</v>
       </c>
       <c r="K45" s="4"/>
       <c r="L45" s="4"/>
@@ -2114,26 +2114,26 @@
       </c>
       <c r="B46" s="5"/>
       <c r="C46" s="5">
-        <v>90.90000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F46" s="7">
-        <v>116000</v>
+        <v>208000</v>
       </c>
       <c r="G46" s="7">
-        <v>7000</v>
+        <v>10000</v>
       </c>
       <c r="H46" s="7">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="I46" s="7">
-        <v>7417</v>
+        <v>18400</v>
       </c>
       <c r="J46" s="5">
-        <v>71.8</v>
+        <v>71.2</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="4"/>
@@ -2147,26 +2147,26 @@
       </c>
       <c r="B47" s="5"/>
       <c r="C47" s="5">
-        <v>80.5</v>
+        <v>89.8</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F47" s="7">
-        <v>497000</v>
+        <v>122000</v>
       </c>
       <c r="G47" s="7">
-        <v>10000</v>
+        <v>6000</v>
       </c>
       <c r="H47" s="7">
         <v>14</v>
       </c>
       <c r="I47" s="7">
-        <v>28538</v>
+        <v>7308</v>
       </c>
       <c r="J47" s="5">
-        <v>71.40000000000001</v>
+        <v>71.2</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="4"/>
@@ -2180,26 +2180,26 @@
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5">
-        <v>87.8</v>
+        <v>87.2</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F48" s="7">
-        <v>248000</v>
+        <v>122000</v>
       </c>
       <c r="G48" s="7">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="H48" s="7">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I48" s="7">
-        <v>12583</v>
+        <v>11222</v>
       </c>
       <c r="J48" s="5">
-        <v>71.40000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
@@ -2213,26 +2213,26 @@
       </c>
       <c r="B49" s="5"/>
       <c r="C49" s="5">
-        <v>89.7</v>
+        <v>89.2</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F49" s="7">
-        <v>225000</v>
+        <v>185000</v>
       </c>
       <c r="G49" s="7">
-        <v>15000</v>
+        <v>8000</v>
       </c>
       <c r="H49" s="7">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I49" s="7">
-        <v>27750</v>
+        <v>6000</v>
       </c>
       <c r="J49" s="5">
-        <v>71.3</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
@@ -2246,26 +2246,26 @@
       </c>
       <c r="B50" s="5"/>
       <c r="C50" s="5">
-        <v>90.59999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F50" s="7">
-        <v>177000</v>
+        <v>286000</v>
       </c>
       <c r="G50" s="7">
-        <v>10000</v>
+        <v>29000</v>
       </c>
       <c r="H50" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I50" s="7">
-        <v>5875</v>
+        <v>14353</v>
       </c>
       <c r="J50" s="5">
-        <v>71.3</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
@@ -2279,26 +2279,26 @@
       </c>
       <c r="B51" s="5"/>
       <c r="C51" s="5">
-        <v>89.5</v>
+        <v>85.7</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F51" s="7">
-        <v>493000</v>
+        <v>251000</v>
       </c>
       <c r="G51" s="7">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="H51" s="7">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I51" s="7">
-        <v>7938</v>
+        <v>11846</v>
       </c>
       <c r="J51" s="5">
-        <v>71.2</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
@@ -2312,26 +2312,26 @@
       </c>
       <c r="B52" s="5"/>
       <c r="C52" s="5">
-        <v>86.5</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F52" s="7">
-        <v>278000</v>
+        <v>489000</v>
       </c>
       <c r="G52" s="7">
-        <v>7000</v>
+        <v>-4000</v>
       </c>
       <c r="H52" s="7">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="I52" s="7">
-        <v>14556</v>
+        <v>7235</v>
       </c>
       <c r="J52" s="5">
-        <v>71.2</v>
+        <v>70</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
@@ -2345,26 +2345,26 @@
       </c>
       <c r="B53" s="5"/>
       <c r="C53" s="5">
-        <v>86.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F53" s="7">
-        <v>233000</v>
+        <v>207000</v>
       </c>
       <c r="G53" s="7">
-        <v>1000</v>
+        <v>9000</v>
       </c>
       <c r="H53" s="7">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="I53" s="7">
-        <v>13727</v>
+        <v>1294</v>
       </c>
       <c r="J53" s="5">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="4"/>
@@ -2378,26 +2378,26 @@
       </c>
       <c r="B54" s="5"/>
       <c r="C54" s="5">
-        <v>88.59999999999999</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="6" t="s">
         <v>18</v>
       </c>
       <c r="F54" s="7">
-        <v>235000</v>
+        <v>237000</v>
       </c>
       <c r="G54" s="7">
-        <v>6000</v>
+        <v>2000</v>
       </c>
       <c r="H54" s="7">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I54" s="7">
-        <v>8688</v>
+        <v>8294</v>
       </c>
       <c r="J54" s="5">
-        <v>70.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="K54" s="4"/>
       <c r="L54" s="4"/>
